--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.202625</t>
-  </si>
-  <si>
-    <t>25.02.202626</t>
-  </si>
-  <si>
-    <t>25.02.202627</t>
-  </si>
-  <si>
-    <t>25.02.202628</t>
-  </si>
-  <si>
-    <t>25.02.202629</t>
-  </si>
-  <si>
-    <t>25.02.202630</t>
-  </si>
-  <si>
-    <t>25.02.202631</t>
-  </si>
-  <si>
-    <t>25.02.202632</t>
-  </si>
-  <si>
-    <t>25.02.202633</t>
-  </si>
-  <si>
-    <t>25.02.202634</t>
-  </si>
-  <si>
-    <t>25.02.202635</t>
-  </si>
-  <si>
-    <t>25.02.202636</t>
-  </si>
-  <si>
-    <t>25.02.202637</t>
-  </si>
-  <si>
-    <t>25.02.202638</t>
-  </si>
-  <si>
-    <t>25.02.202639</t>
-  </si>
-  <si>
-    <t>25.02.202640</t>
-  </si>
-  <si>
-    <t>25.02.202641</t>
-  </si>
-  <si>
-    <t>25.02.202642</t>
-  </si>
-  <si>
-    <t>25.02.202643</t>
-  </si>
-  <si>
-    <t>25.02.202644</t>
-  </si>
-  <si>
-    <t>25.02.202645</t>
-  </si>
-  <si>
-    <t>25.02.202646</t>
-  </si>
-  <si>
-    <t>25.02.202647</t>
-  </si>
-  <si>
-    <t>25.02.202648</t>
-  </si>
-  <si>
-    <t>25.02.202649</t>
-  </si>
-  <si>
-    <t>25.02.202650</t>
-  </si>
-  <si>
-    <t>25.02.202651</t>
-  </si>
-  <si>
-    <t>25.02.202652</t>
-  </si>
-  <si>
-    <t>25.02.202653</t>
-  </si>
-  <si>
-    <t>25.02.202654</t>
-  </si>
-  <si>
-    <t>25.02.202655</t>
-  </si>
-  <si>
-    <t>25.02.202656</t>
-  </si>
-  <si>
-    <t>25.02.202657</t>
-  </si>
-  <si>
-    <t>25.02.202658</t>
-  </si>
-  <si>
-    <t>25.02.202659</t>
-  </si>
-  <si>
-    <t>25.02.202660</t>
-  </si>
-  <si>
-    <t>25.02.202661</t>
-  </si>
-  <si>
-    <t>25.02.202662</t>
-  </si>
-  <si>
-    <t>25.02.202663</t>
-  </si>
-  <si>
-    <t>25.02.202664</t>
-  </si>
-  <si>
-    <t>25.02.202665</t>
-  </si>
-  <si>
-    <t>25.02.202666</t>
-  </si>
-  <si>
-    <t>25.02.202667</t>
-  </si>
-  <si>
-    <t>25.02.202668</t>
-  </si>
-  <si>
-    <t>25.02.202669</t>
-  </si>
-  <si>
-    <t>25.02.202670</t>
-  </si>
-  <si>
-    <t>25.02.202671</t>
-  </si>
-  <si>
-    <t>25.02.202672</t>
-  </si>
-  <si>
-    <t>25.02.202673</t>
-  </si>
-  <si>
-    <t>25.02.202674</t>
-  </si>
-  <si>
-    <t>25.02.202675</t>
-  </si>
-  <si>
-    <t>25.02.202676</t>
-  </si>
-  <si>
-    <t>25.02.202677</t>
-  </si>
-  <si>
-    <t>25.02.202678</t>
-  </si>
-  <si>
-    <t>25.02.202679</t>
-  </si>
-  <si>
-    <t>25.02.202680</t>
-  </si>
-  <si>
-    <t>25.02.202681</t>
-  </si>
-  <si>
-    <t>25.02.202682</t>
-  </si>
-  <si>
-    <t>25.02.202683</t>
-  </si>
-  <si>
-    <t>25.02.202684</t>
-  </si>
-  <si>
-    <t>25.02.202685</t>
-  </si>
-  <si>
-    <t>25.02.202686</t>
-  </si>
-  <si>
-    <t>25.02.202687</t>
-  </si>
-  <si>
-    <t>25.02.202688</t>
-  </si>
-  <si>
-    <t>25.02.202689</t>
-  </si>
-  <si>
-    <t>25.02.202690</t>
-  </si>
-  <si>
-    <t>25.02.202691</t>
-  </si>
-  <si>
-    <t>25.02.202692</t>
-  </si>
-  <si>
-    <t>25.02.202693</t>
-  </si>
-  <si>
-    <t>25.02.202694</t>
-  </si>
-  <si>
-    <t>25.02.202695</t>
-  </si>
-  <si>
-    <t>25.02.202696</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.202624</t>
-  </si>
-  <si>
-    <t>26.02.202625</t>
-  </si>
-  <si>
-    <t>26.02.202626</t>
-  </si>
-  <si>
-    <t>26.02.202627</t>
-  </si>
-  <si>
-    <t>26.02.202628</t>
-  </si>
-  <si>
-    <t>26.02.202629</t>
-  </si>
-  <si>
-    <t>26.02.202630</t>
-  </si>
-  <si>
-    <t>26.02.202631</t>
-  </si>
-  <si>
-    <t>26.02.202632</t>
-  </si>
-  <si>
-    <t>26.02.202633</t>
-  </si>
-  <si>
-    <t>26.02.202634</t>
-  </si>
-  <si>
-    <t>26.02.202635</t>
-  </si>
-  <si>
-    <t>26.02.202636</t>
-  </si>
-  <si>
-    <t>26.02.202637</t>
-  </si>
-  <si>
-    <t>26.02.202638</t>
-  </si>
-  <si>
-    <t>26.02.202639</t>
-  </si>
-  <si>
-    <t>26.02.202640</t>
-  </si>
-  <si>
-    <t>26.02.202641</t>
-  </si>
-  <si>
-    <t>26.02.202642</t>
-  </si>
-  <si>
-    <t>26.02.202643</t>
-  </si>
-  <si>
-    <t>26.02.202644</t>
-  </si>
-  <si>
-    <t>26.02.202645</t>
-  </si>
-  <si>
-    <t>26.02.202646</t>
-  </si>
-  <si>
-    <t>26.02.202647</t>
-  </si>
-  <si>
-    <t>26.02.202648</t>
-  </si>
-  <si>
-    <t>26.02.202649</t>
-  </si>
-  <si>
-    <t>26.02.202650</t>
-  </si>
-  <si>
-    <t>26.02.202651</t>
-  </si>
-  <si>
-    <t>26.02.202652</t>
-  </si>
-  <si>
-    <t>26.02.202653</t>
-  </si>
-  <si>
-    <t>26.02.202654</t>
-  </si>
-  <si>
-    <t>26.02.202655</t>
-  </si>
-  <si>
-    <t>26.02.202656</t>
-  </si>
-  <si>
-    <t>26.02.202657</t>
-  </si>
-  <si>
-    <t>26.02.202658</t>
-  </si>
-  <si>
-    <t>26.02.202659</t>
-  </si>
-  <si>
-    <t>26.02.202660</t>
-  </si>
-  <si>
-    <t>26.02.202661</t>
-  </si>
-  <si>
-    <t>26.02.202662</t>
-  </si>
-  <si>
-    <t>26.02.202663</t>
-  </si>
-  <si>
-    <t>26.02.202664</t>
-  </si>
-  <si>
-    <t>26.02.202665</t>
-  </si>
-  <si>
-    <t>26.02.202666</t>
-  </si>
-  <si>
-    <t>26.02.202667</t>
-  </si>
-  <si>
-    <t>26.02.202668</t>
-  </si>
-  <si>
-    <t>26.02.202669</t>
-  </si>
-  <si>
-    <t>26.02.202670</t>
-  </si>
-  <si>
-    <t>26.02.202671</t>
-  </si>
-  <si>
-    <t>26.02.202672</t>
-  </si>
-  <si>
-    <t>26.02.202673</t>
-  </si>
-  <si>
-    <t>26.02.202674</t>
-  </si>
-  <si>
-    <t>26.02.202675</t>
-  </si>
-  <si>
-    <t>26.02.202676</t>
-  </si>
-  <si>
-    <t>26.02.202677</t>
-  </si>
-  <si>
-    <t>26.02.202678</t>
-  </si>
-  <si>
-    <t>26.02.202679</t>
-  </si>
-  <si>
-    <t>26.02.202680</t>
-  </si>
-  <si>
-    <t>26.02.202681</t>
-  </si>
-  <si>
-    <t>26.02.202682</t>
-  </si>
-  <si>
-    <t>26.02.202683</t>
-  </si>
-  <si>
-    <t>26.02.202684</t>
-  </si>
-  <si>
-    <t>26.02.202685</t>
-  </si>
-  <si>
-    <t>26.02.202686</t>
-  </si>
-  <si>
-    <t>26.02.202687</t>
-  </si>
-  <si>
-    <t>26.02.202688</t>
-  </si>
-  <si>
-    <t>26.02.202689</t>
-  </si>
-  <si>
-    <t>26.02.202690</t>
-  </si>
-  <si>
-    <t>26.02.202691</t>
-  </si>
-  <si>
-    <t>26.02.202692</t>
-  </si>
-  <si>
-    <t>26.02.202693</t>
-  </si>
-  <si>
-    <t>26.02.202694</t>
-  </si>
-  <si>
-    <t>26.02.202695</t>
-  </si>
-  <si>
-    <t>26.02.202696</t>
+    <t>12.03.20261</t>
+  </si>
+  <si>
+    <t>12.03.20262</t>
+  </si>
+  <si>
+    <t>12.03.20263</t>
+  </si>
+  <si>
+    <t>12.03.20264</t>
+  </si>
+  <si>
+    <t>12.03.20265</t>
+  </si>
+  <si>
+    <t>12.03.20266</t>
+  </si>
+  <si>
+    <t>12.03.20267</t>
+  </si>
+  <si>
+    <t>12.03.20268</t>
+  </si>
+  <si>
+    <t>12.03.20269</t>
+  </si>
+  <si>
+    <t>12.03.202610</t>
+  </si>
+  <si>
+    <t>12.03.202611</t>
+  </si>
+  <si>
+    <t>12.03.202612</t>
+  </si>
+  <si>
+    <t>12.03.202613</t>
+  </si>
+  <si>
+    <t>12.03.202614</t>
+  </si>
+  <si>
+    <t>12.03.202615</t>
+  </si>
+  <si>
+    <t>12.03.202616</t>
+  </si>
+  <si>
+    <t>12.03.202617</t>
+  </si>
+  <si>
+    <t>12.03.202618</t>
+  </si>
+  <si>
+    <t>12.03.202619</t>
+  </si>
+  <si>
+    <t>12.03.202620</t>
+  </si>
+  <si>
+    <t>12.03.202621</t>
+  </si>
+  <si>
+    <t>12.03.202622</t>
+  </si>
+  <si>
+    <t>12.03.202623</t>
+  </si>
+  <si>
+    <t>12.03.202624</t>
+  </si>
+  <si>
+    <t>12.03.202625</t>
+  </si>
+  <si>
+    <t>12.03.202626</t>
+  </si>
+  <si>
+    <t>12.03.202627</t>
+  </si>
+  <si>
+    <t>12.03.202628</t>
+  </si>
+  <si>
+    <t>12.03.202629</t>
+  </si>
+  <si>
+    <t>12.03.202630</t>
+  </si>
+  <si>
+    <t>12.03.202631</t>
+  </si>
+  <si>
+    <t>12.03.202632</t>
+  </si>
+  <si>
+    <t>12.03.202633</t>
+  </si>
+  <si>
+    <t>12.03.202634</t>
+  </si>
+  <si>
+    <t>12.03.202635</t>
+  </si>
+  <si>
+    <t>12.03.202636</t>
+  </si>
+  <si>
+    <t>12.03.202637</t>
+  </si>
+  <si>
+    <t>12.03.202638</t>
+  </si>
+  <si>
+    <t>12.03.202639</t>
+  </si>
+  <si>
+    <t>12.03.202640</t>
+  </si>
+  <si>
+    <t>12.03.202641</t>
+  </si>
+  <si>
+    <t>12.03.202642</t>
+  </si>
+  <si>
+    <t>12.03.202643</t>
+  </si>
+  <si>
+    <t>12.03.202644</t>
+  </si>
+  <si>
+    <t>12.03.202645</t>
+  </si>
+  <si>
+    <t>12.03.202646</t>
+  </si>
+  <si>
+    <t>12.03.202647</t>
+  </si>
+  <si>
+    <t>12.03.202648</t>
+  </si>
+  <si>
+    <t>12.03.202649</t>
+  </si>
+  <si>
+    <t>12.03.202650</t>
+  </si>
+  <si>
+    <t>12.03.202651</t>
+  </si>
+  <si>
+    <t>12.03.202652</t>
+  </si>
+  <si>
+    <t>12.03.202653</t>
+  </si>
+  <si>
+    <t>12.03.202654</t>
+  </si>
+  <si>
+    <t>12.03.202655</t>
+  </si>
+  <si>
+    <t>12.03.202656</t>
+  </si>
+  <si>
+    <t>12.03.202657</t>
+  </si>
+  <si>
+    <t>12.03.202658</t>
+  </si>
+  <si>
+    <t>12.03.202659</t>
+  </si>
+  <si>
+    <t>12.03.202660</t>
+  </si>
+  <si>
+    <t>12.03.202661</t>
+  </si>
+  <si>
+    <t>12.03.202662</t>
+  </si>
+  <si>
+    <t>12.03.202663</t>
+  </si>
+  <si>
+    <t>12.03.202664</t>
+  </si>
+  <si>
+    <t>12.03.202665</t>
+  </si>
+  <si>
+    <t>12.03.202666</t>
+  </si>
+  <si>
+    <t>12.03.202667</t>
+  </si>
+  <si>
+    <t>12.03.202668</t>
+  </si>
+  <si>
+    <t>12.03.202669</t>
+  </si>
+  <si>
+    <t>12.03.202670</t>
+  </si>
+  <si>
+    <t>12.03.202671</t>
+  </si>
+  <si>
+    <t>12.03.202672</t>
+  </si>
+  <si>
+    <t>12.03.202673</t>
+  </si>
+  <si>
+    <t>12.03.202674</t>
+  </si>
+  <si>
+    <t>12.03.202675</t>
+  </si>
+  <si>
+    <t>12.03.202676</t>
+  </si>
+  <si>
+    <t>12.03.202677</t>
+  </si>
+  <si>
+    <t>12.03.202678</t>
+  </si>
+  <si>
+    <t>12.03.202679</t>
+  </si>
+  <si>
+    <t>12.03.202680</t>
+  </si>
+  <si>
+    <t>12.03.202681</t>
+  </si>
+  <si>
+    <t>12.03.202682</t>
+  </si>
+  <si>
+    <t>12.03.202683</t>
+  </si>
+  <si>
+    <t>12.03.202684</t>
+  </si>
+  <si>
+    <t>12.03.202685</t>
+  </si>
+  <si>
+    <t>12.03.202686</t>
+  </si>
+  <si>
+    <t>12.03.202687</t>
+  </si>
+  <si>
+    <t>12.03.202688</t>
+  </si>
+  <si>
+    <t>12.03.202689</t>
+  </si>
+  <si>
+    <t>12.03.202690</t>
+  </si>
+  <si>
+    <t>12.03.202691</t>
+  </si>
+  <si>
+    <t>12.03.202692</t>
+  </si>
+  <si>
+    <t>12.03.202693</t>
+  </si>
+  <si>
+    <t>12.03.202694</t>
+  </si>
+  <si>
+    <t>12.03.202695</t>
+  </si>
+  <si>
+    <t>12.03.202696</t>
+  </si>
+  <si>
+    <t>13.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20262</t>
+  </si>
+  <si>
+    <t>13.03.20263</t>
+  </si>
+  <si>
+    <t>13.03.20264</t>
+  </si>
+  <si>
+    <t>13.03.20265</t>
+  </si>
+  <si>
+    <t>13.03.20266</t>
+  </si>
+  <si>
+    <t>13.03.20267</t>
+  </si>
+  <si>
+    <t>13.03.20268</t>
+  </si>
+  <si>
+    <t>13.03.20269</t>
+  </si>
+  <si>
+    <t>13.03.202610</t>
+  </si>
+  <si>
+    <t>13.03.202611</t>
+  </si>
+  <si>
+    <t>13.03.202612</t>
+  </si>
+  <si>
+    <t>13.03.202613</t>
+  </si>
+  <si>
+    <t>13.03.202614</t>
+  </si>
+  <si>
+    <t>13.03.202615</t>
+  </si>
+  <si>
+    <t>13.03.202616</t>
+  </si>
+  <si>
+    <t>13.03.202617</t>
+  </si>
+  <si>
+    <t>13.03.202618</t>
+  </si>
+  <si>
+    <t>13.03.202619</t>
+  </si>
+  <si>
+    <t>13.03.202620</t>
+  </si>
+  <si>
+    <t>13.03.202621</t>
+  </si>
+  <si>
+    <t>13.03.202622</t>
+  </si>
+  <si>
+    <t>13.03.202623</t>
+  </si>
+  <si>
+    <t>13.03.202624</t>
+  </si>
+  <si>
+    <t>13.03.202625</t>
+  </si>
+  <si>
+    <t>13.03.202626</t>
+  </si>
+  <si>
+    <t>13.03.202627</t>
+  </si>
+  <si>
+    <t>13.03.202628</t>
+  </si>
+  <si>
+    <t>13.03.202629</t>
+  </si>
+  <si>
+    <t>13.03.202630</t>
+  </si>
+  <si>
+    <t>13.03.202631</t>
+  </si>
+  <si>
+    <t>13.03.202632</t>
+  </si>
+  <si>
+    <t>13.03.202633</t>
+  </si>
+  <si>
+    <t>13.03.202634</t>
+  </si>
+  <si>
+    <t>13.03.202635</t>
+  </si>
+  <si>
+    <t>13.03.202636</t>
+  </si>
+  <si>
+    <t>13.03.202637</t>
+  </si>
+  <si>
+    <t>13.03.202638</t>
+  </si>
+  <si>
+    <t>13.03.202639</t>
+  </si>
+  <si>
+    <t>13.03.202640</t>
+  </si>
+  <si>
+    <t>13.03.202641</t>
+  </si>
+  <si>
+    <t>13.03.202642</t>
+  </si>
+  <si>
+    <t>13.03.202643</t>
+  </si>
+  <si>
+    <t>13.03.202644</t>
+  </si>
+  <si>
+    <t>13.03.202645</t>
+  </si>
+  <si>
+    <t>13.03.202646</t>
+  </si>
+  <si>
+    <t>13.03.202647</t>
+  </si>
+  <si>
+    <t>13.03.202648</t>
+  </si>
+  <si>
+    <t>13.03.202649</t>
+  </si>
+  <si>
+    <t>13.03.202650</t>
+  </si>
+  <si>
+    <t>13.03.202651</t>
+  </si>
+  <si>
+    <t>13.03.202652</t>
+  </si>
+  <si>
+    <t>13.03.202653</t>
+  </si>
+  <si>
+    <t>13.03.202654</t>
+  </si>
+  <si>
+    <t>13.03.202655</t>
+  </si>
+  <si>
+    <t>13.03.202656</t>
+  </si>
+  <si>
+    <t>13.03.202657</t>
+  </si>
+  <si>
+    <t>13.03.202658</t>
+  </si>
+  <si>
+    <t>13.03.202659</t>
+  </si>
+  <si>
+    <t>13.03.202660</t>
+  </si>
+  <si>
+    <t>13.03.202661</t>
+  </si>
+  <si>
+    <t>13.03.202662</t>
+  </si>
+  <si>
+    <t>13.03.202663</t>
+  </si>
+  <si>
+    <t>13.03.202664</t>
+  </si>
+  <si>
+    <t>13.03.202665</t>
+  </si>
+  <si>
+    <t>13.03.202666</t>
+  </si>
+  <si>
+    <t>13.03.202667</t>
+  </si>
+  <si>
+    <t>13.03.202668</t>
+  </si>
+  <si>
+    <t>13.03.202669</t>
+  </si>
+  <si>
+    <t>13.03.202670</t>
+  </si>
+  <si>
+    <t>13.03.202671</t>
+  </si>
+  <si>
+    <t>13.03.202672</t>
+  </si>
+  <si>
+    <t>13.03.202673</t>
+  </si>
+  <si>
+    <t>13.03.202674</t>
+  </si>
+  <si>
+    <t>13.03.202675</t>
+  </si>
+  <si>
+    <t>13.03.202676</t>
+  </si>
+  <si>
+    <t>13.03.202677</t>
+  </si>
+  <si>
+    <t>13.03.202678</t>
+  </si>
+  <si>
+    <t>13.03.202679</t>
+  </si>
+  <si>
+    <t>13.03.202680</t>
+  </si>
+  <si>
+    <t>13.03.202681</t>
+  </si>
+  <si>
+    <t>13.03.202682</t>
+  </si>
+  <si>
+    <t>13.03.202683</t>
+  </si>
+  <si>
+    <t>13.03.202684</t>
+  </si>
+  <si>
+    <t>13.03.202685</t>
+  </si>
+  <si>
+    <t>13.03.202686</t>
+  </si>
+  <si>
+    <t>13.03.202687</t>
+  </si>
+  <si>
+    <t>13.03.202688</t>
+  </si>
+  <si>
+    <t>13.03.202689</t>
+  </si>
+  <si>
+    <t>13.03.202690</t>
+  </si>
+  <si>
+    <t>13.03.202691</t>
+  </si>
+  <si>
+    <t>13.03.202692</t>
+  </si>
+  <si>
+    <t>13.03.202693</t>
+  </si>
+  <si>
+    <t>13.03.202694</t>
+  </si>
+  <si>
+    <t>13.03.202695</t>
+  </si>
+  <si>
+    <t>13.03.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,19 +1000,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="B2">
-        <v>1.051</v>
+        <v>0.035</v>
       </c>
       <c r="C2">
-        <v>0.207</v>
+        <v>1.928</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1023,19 +1023,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46078.01041666666</v>
+        <v>46093.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.794</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.02</v>
+        <v>13.653</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1046,19 +1046,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46078.02083333334</v>
+        <v>46093.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>6.47</v>
+        <v>18.57</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46078.03125</v>
+        <v>46093.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>37.611</v>
+        <v>10.801</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46078.04166666666</v>
+        <v>46093.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>65.438</v>
+        <v>6.398</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46078.05208333334</v>
+        <v>46093.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>35.141</v>
+        <v>5.881</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1138,19 +1138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46078.0625</v>
+        <v>46093.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>11.876</v>
+        <v>6.426</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46078.07291666666</v>
+        <v>46093.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="C9">
-        <v>18.681</v>
+        <v>1.055</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1184,19 +1184,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46078.08333333334</v>
+        <v>46093.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1.122</v>
       </c>
       <c r="C10">
-        <v>16.25</v>
+        <v>2.145</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1207,19 +1207,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46078.09375</v>
+        <v>46093.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1.504</v>
       </c>
       <c r="C11">
-        <v>6.714</v>
+        <v>0.13</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1230,19 +1230,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46078.10416666666</v>
+        <v>46093.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.882</v>
+        <v>0.208</v>
       </c>
       <c r="C12">
-        <v>0.138</v>
+        <v>0.782</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46078.11458333334</v>
+        <v>46093.11458333334</v>
       </c>
       <c r="B13">
-        <v>3.909</v>
+        <v>4.153</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1276,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46078.125</v>
+        <v>46093.125</v>
       </c>
       <c r="B14">
-        <v>7.067</v>
+        <v>0.127</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46078.13541666666</v>
+        <v>46093.13541666666</v>
       </c>
       <c r="B15">
-        <v>3.564</v>
+        <v>0.674</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46078.14583333334</v>
+        <v>46093.14583333334</v>
       </c>
       <c r="B16">
-        <v>21.899</v>
+        <v>7.965</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46078.15625</v>
+        <v>46093.15625</v>
       </c>
       <c r="B17">
-        <v>11.278</v>
+        <v>18.746</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46078.16666666666</v>
+        <v>46093.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.204</v>
+        <v>23.084</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46078.17708333334</v>
+        <v>46093.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.812</v>
+        <v>3.423</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46078.1875</v>
+        <v>46093.1875</v>
       </c>
       <c r="B20">
-        <v>3.451</v>
+        <v>13.953</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46078.19791666666</v>
+        <v>46093.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.15</v>
+        <v>42.356</v>
       </c>
       <c r="C21">
-        <v>3.677</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46078.20833333334</v>
+        <v>46093.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.696</v>
+        <v>10.03</v>
       </c>
       <c r="C22">
-        <v>6.624</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46078.21875</v>
+        <v>46093.21875</v>
       </c>
       <c r="B23">
-        <v>0.196</v>
+        <v>0.112</v>
       </c>
       <c r="C23">
-        <v>35.079</v>
+        <v>0.051</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46078.22916666666</v>
+        <v>46093.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.012</v>
+        <v>4.181</v>
       </c>
       <c r="C24">
-        <v>18.91</v>
+        <v>0.022</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46078.23958333334</v>
+        <v>46093.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.447</v>
+        <v>5.254</v>
       </c>
       <c r="C25">
-        <v>2.197</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46078.25</v>
+        <v>46093.25</v>
       </c>
       <c r="B26">
-        <v>1.479</v>
+        <v>0.281</v>
       </c>
       <c r="C26">
-        <v>11.782</v>
+        <v>4.54</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46078.26041666666</v>
+        <v>46093.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.493</v>
+        <v>0.047</v>
       </c>
       <c r="C27">
-        <v>6.911</v>
+        <v>3.677</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46078.27083333334</v>
+        <v>46093.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C28">
-        <v>11.147</v>
+        <v>6.94</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46078.28125</v>
+        <v>46093.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1.486</v>
       </c>
       <c r="C29">
-        <v>5.851</v>
+        <v>0.089</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,19 +1644,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46078.29166666666</v>
+        <v>46093.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.09</v>
+        <v>13.147</v>
       </c>
       <c r="C30">
-        <v>1.211</v>
+        <v>0.038</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46078.30208333334</v>
+        <v>46093.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.221</v>
+        <v>4.325</v>
       </c>
       <c r="C31">
-        <v>8.266999999999999</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46078.3125</v>
+        <v>46093.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="C32">
-        <v>24.159</v>
+        <v>0.631</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46078.32291666666</v>
+        <v>46093.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="C33">
-        <v>38.383</v>
+        <v>3.871</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46078.33333333334</v>
+        <v>46093.33333333334</v>
       </c>
       <c r="B34">
-        <v>2.113</v>
+        <v>4.971</v>
       </c>
       <c r="C34">
-        <v>12.367</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46078.34375</v>
+        <v>46093.34375</v>
       </c>
       <c r="B35">
-        <v>1.645</v>
+        <v>5.746</v>
       </c>
       <c r="C35">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46078.35416666666</v>
+        <v>46093.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>10.239</v>
       </c>
       <c r="C36">
-        <v>32.318</v>
+        <v>0.018</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +1805,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46078.36458333334</v>
+        <v>46093.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="C37">
-        <v>41.165</v>
+        <v>5.422</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46078.375</v>
+        <v>46093.375</v>
       </c>
       <c r="B38">
-        <v>14.1</v>
+        <v>6.007</v>
       </c>
       <c r="C38">
-        <v>3.044</v>
+        <v>2.701</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46078.38541666666</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="B39">
-        <v>3.402</v>
+        <v>0.045</v>
       </c>
       <c r="C39">
-        <v>2.72</v>
+        <v>6.591</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E39">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46078.39583333334</v>
+        <v>46093.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>24.814</v>
+        <v>13.222</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E40">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46078.40625</v>
+        <v>46093.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>28.109</v>
+        <v>23.116</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E41">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46078.41666666666</v>
+        <v>46093.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2.288</v>
       </c>
       <c r="C42">
-        <v>13.67</v>
+        <v>6.415</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>24.25</v>
       </c>
       <c r="E42">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46078.42708333334</v>
+        <v>46093.42708333334</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>11.44</v>
+        <v>12.618</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>24.25</v>
       </c>
       <c r="E43">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46078.4375</v>
+        <v>46093.4375</v>
       </c>
       <c r="B44">
-        <v>2.817</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0.5639999999999999</v>
+        <v>3.587</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46078.44791666666</v>
+        <v>46093.44791666666</v>
       </c>
       <c r="B45">
-        <v>6.63</v>
+        <v>0.158</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46078.45833333334</v>
+        <v>46093.45833333334</v>
       </c>
       <c r="B46">
-        <v>10.902</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>28.099</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46078.46875</v>
+        <v>46093.46875</v>
       </c>
       <c r="B47">
-        <v>8.867000000000001</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>24.582</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46078.47916666666</v>
+        <v>46093.47916666666</v>
       </c>
       <c r="B48">
-        <v>10.554</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>31.849</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46078.48958333334</v>
+        <v>46093.48958333334</v>
       </c>
       <c r="B49">
-        <v>19.781</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>29.386</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2104,13 +2104,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46078.5</v>
+        <v>46093.5</v>
       </c>
       <c r="B50">
-        <v>10.344</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0.003</v>
+        <v>14.305</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2127,16 +2127,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46078.51041666666</v>
+        <v>46093.51041666666</v>
       </c>
       <c r="B51">
-        <v>4.386</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>0.1</v>
+        <v>20.702</v>
       </c>
       <c r="D51">
-        <v>28.75</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2150,16 +2150,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46078.52083333334</v>
+        <v>46093.52083333334</v>
       </c>
       <c r="B52">
-        <v>2.989</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0.292</v>
+        <v>50.814</v>
       </c>
       <c r="D52">
-        <v>28.75</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2173,16 +2173,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46078.53125</v>
+        <v>46093.53125</v>
       </c>
       <c r="B53">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1.047</v>
+        <v>60.88</v>
       </c>
       <c r="D53">
-        <v>28.75</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46078.54166666666</v>
+        <v>46093.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>1.282</v>
+        <v>82.60599999999999</v>
       </c>
       <c r="D54">
-        <v>21.25</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46078.55208333334</v>
+        <v>46093.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>6.485</v>
+        <v>15.016</v>
       </c>
       <c r="D55">
-        <v>21.25</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46078.5625</v>
+        <v>46093.5625</v>
       </c>
       <c r="B56">
-        <v>0.013</v>
+        <v>0.652</v>
       </c>
       <c r="C56">
-        <v>1.823</v>
+        <v>2.454</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46078.57291666666</v>
+        <v>46093.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="C57">
-        <v>12.871</v>
+        <v>2.853</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46078.58333333334</v>
+        <v>46093.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C58">
-        <v>39.245</v>
+        <v>12.715</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46078.59375</v>
+        <v>46093.59375</v>
       </c>
       <c r="B59">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>6.996</v>
+        <v>27.696</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46078.60416666666</v>
+        <v>46093.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0.096</v>
+        <v>28.789</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46078.61458333334</v>
+        <v>46093.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.336</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>0.396</v>
+        <v>16.526</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>25</v>
+        <v>68.5</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46078.625</v>
+        <v>46093.625</v>
       </c>
       <c r="B62">
-        <v>0.035</v>
+        <v>0.018</v>
       </c>
       <c r="C62">
-        <v>9.821</v>
+        <v>8.723000000000001</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46078.63541666666</v>
+        <v>46093.63541666666</v>
       </c>
       <c r="B63">
-        <v>1.799</v>
+        <v>0.958</v>
       </c>
       <c r="C63">
-        <v>0.604</v>
+        <v>0.103</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46078.64583333334</v>
+        <v>46093.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.762</v>
+        <v>0.377</v>
       </c>
       <c r="C64">
-        <v>0.117</v>
+        <v>0.058</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>64.75</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46078.65625</v>
+        <v>46093.65625</v>
       </c>
       <c r="B65">
-        <v>0.08599999999999999</v>
+        <v>11.173</v>
       </c>
       <c r="C65">
-        <v>3.701</v>
+        <v>0.257</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46078.66666666666</v>
+        <v>46093.66666666666</v>
       </c>
       <c r="B66">
-        <v>1.194</v>
+        <v>3.559</v>
       </c>
       <c r="C66">
-        <v>14.964</v>
+        <v>2.172</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2495,13 +2495,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46078.67708333334</v>
+        <v>46093.67708333334</v>
       </c>
       <c r="B67">
-        <v>2.002</v>
+        <v>7.879</v>
       </c>
       <c r="C67">
-        <v>1.249</v>
+        <v>0.017</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46078.6875</v>
+        <v>46093.6875</v>
       </c>
       <c r="B68">
-        <v>8.173</v>
+        <v>18.859</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46078.69791666666</v>
+        <v>46093.69791666666</v>
       </c>
       <c r="B69">
-        <v>2.407</v>
+        <v>37.73</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2564,13 +2564,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46078.70833333334</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.152</v>
+        <v>4.472</v>
       </c>
       <c r="C70">
-        <v>9.414</v>
+        <v>0.011</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46078.71875</v>
+        <v>46093.71875</v>
       </c>
       <c r="B71">
-        <v>2.769</v>
+        <v>1.579</v>
       </c>
       <c r="C71">
-        <v>0.073</v>
+        <v>0.042</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46078.72916666666</v>
+        <v>46093.72916666666</v>
       </c>
       <c r="B72">
-        <v>21.32</v>
+        <v>11.348</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46078.73958333334</v>
+        <v>46093.73958333334</v>
       </c>
       <c r="B73">
-        <v>33.236</v>
+        <v>30.555</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46078.75</v>
+        <v>46093.75</v>
       </c>
       <c r="B74">
-        <v>6.712</v>
+        <v>23.451</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46078.76041666666</v>
+        <v>46093.76041666666</v>
       </c>
       <c r="B75">
-        <v>3.386</v>
+        <v>17.039</v>
       </c>
       <c r="C75">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46078.77083333334</v>
+        <v>46093.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.319</v>
+        <v>19.579</v>
       </c>
       <c r="C76">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46078.78125</v>
+        <v>46093.78125</v>
       </c>
       <c r="B77">
-        <v>0.245</v>
+        <v>4.645</v>
       </c>
       <c r="C77">
-        <v>0.278</v>
+        <v>0.196</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46078.79166666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.604</v>
+        <v>0.045</v>
       </c>
       <c r="C78">
-        <v>0.13</v>
+        <v>15.033</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,13 +2771,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46078.80208333334</v>
+        <v>46093.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.399</v>
+        <v>0.01</v>
       </c>
       <c r="C79">
-        <v>0.041</v>
+        <v>1.885</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46078.8125</v>
+        <v>46093.8125</v>
       </c>
       <c r="B80">
-        <v>0.329</v>
+        <v>0.389</v>
       </c>
       <c r="C80">
-        <v>2.815</v>
+        <v>0.554</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46078.82291666666</v>
+        <v>46093.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="C81">
-        <v>9.566000000000001</v>
+        <v>3.296</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46078.83333333334</v>
+        <v>46093.83333333334</v>
       </c>
       <c r="B82">
-        <v>4.504</v>
+        <v>0.917</v>
       </c>
       <c r="C82">
-        <v>0.5669999999999999</v>
+        <v>0.739</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46078.84375</v>
+        <v>46093.84375</v>
       </c>
       <c r="B83">
-        <v>1.13</v>
+        <v>4.454</v>
       </c>
       <c r="C83">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46078.85416666666</v>
+        <v>46093.85416666666</v>
       </c>
       <c r="B84">
-        <v>1.033</v>
+        <v>0.287</v>
       </c>
       <c r="C84">
-        <v>0.016</v>
+        <v>0.645</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46078.86458333334</v>
+        <v>46093.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.984</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>0.024</v>
+        <v>1.531</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46078.875</v>
+        <v>46093.875</v>
       </c>
       <c r="B86">
-        <v>9.16</v>
+        <v>13.43</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46078.88541666666</v>
+        <v>46093.88541666666</v>
       </c>
       <c r="B87">
-        <v>6.521</v>
+        <v>17.079</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46078.89583333334</v>
+        <v>46093.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.256</v>
+        <v>4.446</v>
       </c>
       <c r="C88">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46078.90625</v>
+        <v>46093.90625</v>
       </c>
       <c r="B89">
-        <v>0.109</v>
+        <v>3.424</v>
       </c>
       <c r="C89">
-        <v>1.107</v>
+        <v>0.045</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46078.91666666666</v>
+        <v>46093.91666666666</v>
       </c>
       <c r="B90">
-        <v>12.063</v>
+        <v>23.618</v>
       </c>
       <c r="C90">
-        <v>0.131</v>
+        <v>0.003</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46078.92708333334</v>
+        <v>46093.92708333334</v>
       </c>
       <c r="B91">
-        <v>3.172</v>
+        <v>37.254</v>
       </c>
       <c r="C91">
-        <v>1.256</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,16 +3070,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46078.9375</v>
+        <v>46093.9375</v>
       </c>
       <c r="B92">
-        <v>0.003</v>
+        <v>10.933</v>
       </c>
       <c r="C92">
-        <v>2.916</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3093,16 +3093,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46078.94791666666</v>
+        <v>46093.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.773</v>
+        <v>1.519</v>
       </c>
       <c r="C93">
-        <v>3.533</v>
+        <v>0.529</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3116,16 +3116,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.913</v>
+        <v>0.924</v>
       </c>
       <c r="C94">
-        <v>10.998</v>
+        <v>0.552</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3139,16 +3139,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B95">
-        <v>0.913</v>
+        <v>0.924</v>
       </c>
       <c r="C95">
-        <v>10.998</v>
+        <v>0.552</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>5.176</v>
       </c>
       <c r="C96">
-        <v>2.089</v>
+        <v>0.522</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3185,16 +3185,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>5.176</v>
       </c>
       <c r="C97">
-        <v>2.089</v>
+        <v>0.522</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3208,19 +3208,19 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B98">
-        <v>0.274</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>0.102</v>
+        <v>8.94</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E98">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>95</v>
@@ -3231,19 +3231,19 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B99">
-        <v>0.274</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>0.102</v>
+        <v>8.94</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E99">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>95</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B100">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>0.226</v>
+        <v>13.718</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3277,16 +3277,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B101">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>0.226</v>
+        <v>13.718</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B102">
-        <v>0.192</v>
+        <v>18.511</v>
       </c>
       <c r="C102">
-        <v>2.9</v>
+        <v>0.04</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B103">
-        <v>0.192</v>
+        <v>18.511</v>
       </c>
       <c r="C103">
-        <v>2.9</v>
+        <v>0.04</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B104">
-        <v>0.007</v>
+        <v>18.22</v>
       </c>
       <c r="C104">
-        <v>8.631</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B105">
-        <v>0.007</v>
+        <v>18.22</v>
       </c>
       <c r="C105">
-        <v>8.631</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B106">
-        <v>0.003</v>
+        <v>8.359</v>
       </c>
       <c r="C106">
-        <v>5.175</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B107">
-        <v>0.003</v>
+        <v>8.359</v>
       </c>
       <c r="C107">
-        <v>5.175</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B108">
-        <v>0.01</v>
+        <v>1.45</v>
       </c>
       <c r="C108">
-        <v>4.985</v>
+        <v>0.707</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B109">
-        <v>0.01</v>
+        <v>1.45</v>
       </c>
       <c r="C109">
-        <v>4.985</v>
+        <v>0.707</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B110">
-        <v>0.03</v>
+        <v>6.055</v>
       </c>
       <c r="C110">
-        <v>4.476</v>
+        <v>0.926</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B111">
-        <v>0.079</v>
+        <v>1.666</v>
       </c>
       <c r="C111">
-        <v>0.204</v>
+        <v>0.007</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B112">
-        <v>0.209</v>
+        <v>0.011</v>
       </c>
       <c r="C112">
-        <v>0.03</v>
+        <v>3.766</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0.6820000000000001</v>
+        <v>10.291</v>
       </c>
       <c r="D113">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B114">
-        <v>0.227</v>
+        <v>0.134</v>
       </c>
       <c r="C114">
-        <v>0.233</v>
+        <v>2.983</v>
       </c>
       <c r="D114">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,16 +3599,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B115">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0.272</v>
+        <v>2.095</v>
       </c>
       <c r="D115">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>1.642</v>
+        <v>8.278</v>
       </c>
       <c r="D116">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +3645,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B117">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>0.218</v>
+        <v>17.532</v>
       </c>
       <c r="D117">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +3668,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B118">
-        <v>3.738</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>0.028</v>
+        <v>3.895</v>
       </c>
       <c r="D118">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +3691,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B119">
-        <v>2.751</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>0.005</v>
+        <v>8.69</v>
       </c>
       <c r="D119">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B120">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>3.379</v>
+        <v>5.865</v>
       </c>
       <c r="D120">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>11.469</v>
+        <v>9.692</v>
       </c>
       <c r="D121">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122">
-        <v>26.199</v>
+        <v>4.503</v>
       </c>
       <c r="D122">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C123">
-        <v>34.57</v>
+        <v>0.097</v>
       </c>
       <c r="D123">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B124">
-        <v>0.146</v>
+        <v>0.115</v>
       </c>
       <c r="C124">
-        <v>4.703</v>
+        <v>0.254</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B125">
-        <v>20.26</v>
+        <v>0.249</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.363</v>
+        <v>0.047</v>
       </c>
       <c r="C126">
-        <v>0.121</v>
+        <v>7.787</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B127">
-        <v>0.291</v>
+        <v>0.047</v>
       </c>
       <c r="C127">
-        <v>0.107</v>
+        <v>0.145</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B128">
-        <v>3.532</v>
+        <v>0.017</v>
       </c>
       <c r="C128">
-        <v>0.131</v>
+        <v>1.607</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B129">
-        <v>4.036</v>
+        <v>0.012</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>3.772</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B130">
-        <v>4.936</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>2.71</v>
+        <v>19.283</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B131">
-        <v>5.534</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>25.801</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,13 +3990,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>0.228</v>
+        <v>52.646</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B133">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>0.264</v>
+        <v>67.589</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4036,19 +4036,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>0.253</v>
+        <v>30.997</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F134">
         <v>29</v>
@@ -4059,19 +4059,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.873</v>
+        <v>0.007</v>
       </c>
       <c r="C135">
-        <v>5.585</v>
+        <v>18.253</v>
       </c>
       <c r="D135">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F135">
         <v>30</v>
@@ -4082,19 +4082,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>32.591</v>
+        <v>32.309</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F136">
         <v>31</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>50.548</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F137">
         <v>32</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
       <c r="C138">
-        <v>35.354</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>33</v>
@@ -4151,19 +4151,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>48.763</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>34</v>
@@ -4174,19 +4174,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>64.649</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>35</v>
@@ -4197,19 +4197,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>76.04300000000001</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>36</v>
@@ -4220,19 +4220,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B142">
-        <v>8.266</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>10.317</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>37</v>
@@ -4243,19 +4243,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B143">
-        <v>1.192</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>38</v>
@@ -4266,19 +4266,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B144">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C144">
-        <v>10.044</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>39</v>
@@ -4289,19 +4289,19 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>27.542</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <v>40</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4324,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>41</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="E147">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>42</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.03.20261</t>
-  </si>
-  <si>
-    <t>12.03.20262</t>
-  </si>
-  <si>
-    <t>12.03.20263</t>
-  </si>
-  <si>
-    <t>12.03.20264</t>
-  </si>
-  <si>
-    <t>12.03.20265</t>
-  </si>
-  <si>
-    <t>12.03.20266</t>
-  </si>
-  <si>
-    <t>12.03.20267</t>
-  </si>
-  <si>
-    <t>12.03.20268</t>
-  </si>
-  <si>
-    <t>12.03.20269</t>
-  </si>
-  <si>
-    <t>12.03.202610</t>
-  </si>
-  <si>
-    <t>12.03.202611</t>
-  </si>
-  <si>
-    <t>12.03.202612</t>
-  </si>
-  <si>
-    <t>12.03.202613</t>
-  </si>
-  <si>
-    <t>12.03.202614</t>
-  </si>
-  <si>
-    <t>12.03.202615</t>
-  </si>
-  <si>
-    <t>12.03.202616</t>
-  </si>
-  <si>
-    <t>12.03.202617</t>
-  </si>
-  <si>
-    <t>12.03.202618</t>
-  </si>
-  <si>
-    <t>12.03.202619</t>
-  </si>
-  <si>
-    <t>12.03.202620</t>
-  </si>
-  <si>
-    <t>12.03.202621</t>
-  </si>
-  <si>
-    <t>12.03.202622</t>
-  </si>
-  <si>
-    <t>12.03.202623</t>
-  </si>
-  <si>
-    <t>12.03.202624</t>
-  </si>
-  <si>
-    <t>12.03.202625</t>
-  </si>
-  <si>
-    <t>12.03.202626</t>
-  </si>
-  <si>
-    <t>12.03.202627</t>
-  </si>
-  <si>
-    <t>12.03.202628</t>
-  </si>
-  <si>
-    <t>12.03.202629</t>
-  </si>
-  <si>
-    <t>12.03.202630</t>
-  </si>
-  <si>
-    <t>12.03.202631</t>
-  </si>
-  <si>
-    <t>12.03.202632</t>
-  </si>
-  <si>
-    <t>12.03.202633</t>
-  </si>
-  <si>
-    <t>12.03.202634</t>
-  </si>
-  <si>
-    <t>12.03.202635</t>
-  </si>
-  <si>
-    <t>12.03.202636</t>
-  </si>
-  <si>
-    <t>12.03.202637</t>
-  </si>
-  <si>
-    <t>12.03.202638</t>
-  </si>
-  <si>
-    <t>12.03.202639</t>
-  </si>
-  <si>
-    <t>12.03.202640</t>
-  </si>
-  <si>
-    <t>12.03.202641</t>
-  </si>
-  <si>
-    <t>12.03.202642</t>
-  </si>
-  <si>
-    <t>12.03.202643</t>
-  </si>
-  <si>
-    <t>12.03.202644</t>
-  </si>
-  <si>
-    <t>12.03.202645</t>
-  </si>
-  <si>
-    <t>12.03.202646</t>
-  </si>
-  <si>
-    <t>12.03.202647</t>
-  </si>
-  <si>
-    <t>12.03.202648</t>
-  </si>
-  <si>
-    <t>12.03.202649</t>
-  </si>
-  <si>
-    <t>12.03.202650</t>
-  </si>
-  <si>
-    <t>12.03.202651</t>
-  </si>
-  <si>
-    <t>12.03.202652</t>
-  </si>
-  <si>
-    <t>12.03.202653</t>
-  </si>
-  <si>
-    <t>12.03.202654</t>
-  </si>
-  <si>
-    <t>12.03.202655</t>
-  </si>
-  <si>
-    <t>12.03.202656</t>
-  </si>
-  <si>
-    <t>12.03.202657</t>
-  </si>
-  <si>
-    <t>12.03.202658</t>
-  </si>
-  <si>
-    <t>12.03.202659</t>
-  </si>
-  <si>
-    <t>12.03.202660</t>
-  </si>
-  <si>
-    <t>12.03.202661</t>
-  </si>
-  <si>
-    <t>12.03.202662</t>
-  </si>
-  <si>
-    <t>12.03.202663</t>
-  </si>
-  <si>
-    <t>12.03.202664</t>
-  </si>
-  <si>
-    <t>12.03.202665</t>
-  </si>
-  <si>
-    <t>12.03.202666</t>
-  </si>
-  <si>
-    <t>12.03.202667</t>
-  </si>
-  <si>
-    <t>12.03.202668</t>
-  </si>
-  <si>
-    <t>12.03.202669</t>
-  </si>
-  <si>
-    <t>12.03.202670</t>
-  </si>
-  <si>
-    <t>12.03.202671</t>
-  </si>
-  <si>
-    <t>12.03.202672</t>
-  </si>
-  <si>
-    <t>12.03.202673</t>
-  </si>
-  <si>
-    <t>12.03.202674</t>
-  </si>
-  <si>
-    <t>12.03.202675</t>
-  </si>
-  <si>
-    <t>12.03.202676</t>
-  </si>
-  <si>
-    <t>12.03.202677</t>
-  </si>
-  <si>
-    <t>12.03.202678</t>
-  </si>
-  <si>
-    <t>12.03.202679</t>
-  </si>
-  <si>
-    <t>12.03.202680</t>
-  </si>
-  <si>
-    <t>12.03.202681</t>
-  </si>
-  <si>
-    <t>12.03.202682</t>
-  </si>
-  <si>
-    <t>12.03.202683</t>
-  </si>
-  <si>
-    <t>12.03.202684</t>
-  </si>
-  <si>
-    <t>12.03.202685</t>
-  </si>
-  <si>
-    <t>12.03.202686</t>
-  </si>
-  <si>
-    <t>12.03.202687</t>
-  </si>
-  <si>
-    <t>12.03.202688</t>
-  </si>
-  <si>
-    <t>12.03.202689</t>
-  </si>
-  <si>
-    <t>12.03.202690</t>
-  </si>
-  <si>
-    <t>12.03.202691</t>
-  </si>
-  <si>
-    <t>12.03.202692</t>
-  </si>
-  <si>
-    <t>12.03.202693</t>
-  </si>
-  <si>
-    <t>12.03.202694</t>
-  </si>
-  <si>
-    <t>12.03.202695</t>
-  </si>
-  <si>
-    <t>12.03.202696</t>
-  </si>
-  <si>
-    <t>13.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20262</t>
-  </si>
-  <si>
-    <t>13.03.20263</t>
-  </si>
-  <si>
-    <t>13.03.20264</t>
-  </si>
-  <si>
-    <t>13.03.20265</t>
-  </si>
-  <si>
-    <t>13.03.20266</t>
-  </si>
-  <si>
-    <t>13.03.20267</t>
-  </si>
-  <si>
-    <t>13.03.20268</t>
-  </si>
-  <si>
-    <t>13.03.20269</t>
-  </si>
-  <si>
-    <t>13.03.202610</t>
-  </si>
-  <si>
-    <t>13.03.202611</t>
-  </si>
-  <si>
-    <t>13.03.202612</t>
-  </si>
-  <si>
-    <t>13.03.202613</t>
-  </si>
-  <si>
-    <t>13.03.202614</t>
-  </si>
-  <si>
-    <t>13.03.202615</t>
-  </si>
-  <si>
-    <t>13.03.202616</t>
-  </si>
-  <si>
-    <t>13.03.202617</t>
-  </si>
-  <si>
-    <t>13.03.202618</t>
-  </si>
-  <si>
-    <t>13.03.202619</t>
-  </si>
-  <si>
-    <t>13.03.202620</t>
-  </si>
-  <si>
-    <t>13.03.202621</t>
-  </si>
-  <si>
-    <t>13.03.202622</t>
-  </si>
-  <si>
-    <t>13.03.202623</t>
-  </si>
-  <si>
-    <t>13.03.202624</t>
-  </si>
-  <si>
-    <t>13.03.202625</t>
-  </si>
-  <si>
-    <t>13.03.202626</t>
-  </si>
-  <si>
-    <t>13.03.202627</t>
-  </si>
-  <si>
-    <t>13.03.202628</t>
-  </si>
-  <si>
-    <t>13.03.202629</t>
-  </si>
-  <si>
-    <t>13.03.202630</t>
-  </si>
-  <si>
-    <t>13.03.202631</t>
-  </si>
-  <si>
-    <t>13.03.202632</t>
-  </si>
-  <si>
-    <t>13.03.202633</t>
-  </si>
-  <si>
-    <t>13.03.202634</t>
-  </si>
-  <si>
-    <t>13.03.202635</t>
-  </si>
-  <si>
-    <t>13.03.202636</t>
-  </si>
-  <si>
-    <t>13.03.202637</t>
-  </si>
-  <si>
-    <t>13.03.202638</t>
-  </si>
-  <si>
-    <t>13.03.202639</t>
-  </si>
-  <si>
-    <t>13.03.202640</t>
-  </si>
-  <si>
-    <t>13.03.202641</t>
-  </si>
-  <si>
-    <t>13.03.202642</t>
-  </si>
-  <si>
-    <t>13.03.202643</t>
-  </si>
-  <si>
-    <t>13.03.202644</t>
-  </si>
-  <si>
-    <t>13.03.202645</t>
-  </si>
-  <si>
-    <t>13.03.202646</t>
-  </si>
-  <si>
-    <t>13.03.202647</t>
-  </si>
-  <si>
-    <t>13.03.202648</t>
-  </si>
-  <si>
-    <t>13.03.202649</t>
-  </si>
-  <si>
-    <t>13.03.202650</t>
-  </si>
-  <si>
-    <t>13.03.202651</t>
-  </si>
-  <si>
-    <t>13.03.202652</t>
-  </si>
-  <si>
-    <t>13.03.202653</t>
-  </si>
-  <si>
-    <t>13.03.202654</t>
-  </si>
-  <si>
-    <t>13.03.202655</t>
-  </si>
-  <si>
-    <t>13.03.202656</t>
-  </si>
-  <si>
-    <t>13.03.202657</t>
-  </si>
-  <si>
-    <t>13.03.202658</t>
-  </si>
-  <si>
-    <t>13.03.202659</t>
-  </si>
-  <si>
-    <t>13.03.202660</t>
-  </si>
-  <si>
-    <t>13.03.202661</t>
-  </si>
-  <si>
-    <t>13.03.202662</t>
-  </si>
-  <si>
-    <t>13.03.202663</t>
-  </si>
-  <si>
-    <t>13.03.202664</t>
-  </si>
-  <si>
-    <t>13.03.202665</t>
-  </si>
-  <si>
-    <t>13.03.202666</t>
-  </si>
-  <si>
-    <t>13.03.202667</t>
-  </si>
-  <si>
-    <t>13.03.202668</t>
-  </si>
-  <si>
-    <t>13.03.202669</t>
-  </si>
-  <si>
-    <t>13.03.202670</t>
-  </si>
-  <si>
-    <t>13.03.202671</t>
-  </si>
-  <si>
-    <t>13.03.202672</t>
-  </si>
-  <si>
-    <t>13.03.202673</t>
-  </si>
-  <si>
-    <t>13.03.202674</t>
-  </si>
-  <si>
-    <t>13.03.202675</t>
-  </si>
-  <si>
-    <t>13.03.202676</t>
-  </si>
-  <si>
-    <t>13.03.202677</t>
-  </si>
-  <si>
-    <t>13.03.202678</t>
-  </si>
-  <si>
-    <t>13.03.202679</t>
-  </si>
-  <si>
-    <t>13.03.202680</t>
-  </si>
-  <si>
-    <t>13.03.202681</t>
-  </si>
-  <si>
-    <t>13.03.202682</t>
-  </si>
-  <si>
-    <t>13.03.202683</t>
-  </si>
-  <si>
-    <t>13.03.202684</t>
-  </si>
-  <si>
-    <t>13.03.202685</t>
-  </si>
-  <si>
-    <t>13.03.202686</t>
-  </si>
-  <si>
-    <t>13.03.202687</t>
-  </si>
-  <si>
-    <t>13.03.202688</t>
-  </si>
-  <si>
-    <t>13.03.202689</t>
-  </si>
-  <si>
-    <t>13.03.202690</t>
-  </si>
-  <si>
-    <t>13.03.202691</t>
-  </si>
-  <si>
-    <t>13.03.202692</t>
-  </si>
-  <si>
-    <t>13.03.202693</t>
-  </si>
-  <si>
-    <t>13.03.202694</t>
-  </si>
-  <si>
-    <t>13.03.202695</t>
-  </si>
-  <si>
-    <t>13.03.202696</t>
+    <t>25.03.20261</t>
+  </si>
+  <si>
+    <t>25.03.20262</t>
+  </si>
+  <si>
+    <t>25.03.20263</t>
+  </si>
+  <si>
+    <t>25.03.20264</t>
+  </si>
+  <si>
+    <t>25.03.20265</t>
+  </si>
+  <si>
+    <t>25.03.20266</t>
+  </si>
+  <si>
+    <t>25.03.20267</t>
+  </si>
+  <si>
+    <t>25.03.20268</t>
+  </si>
+  <si>
+    <t>25.03.20269</t>
+  </si>
+  <si>
+    <t>25.03.202610</t>
+  </si>
+  <si>
+    <t>25.03.202611</t>
+  </si>
+  <si>
+    <t>25.03.202612</t>
+  </si>
+  <si>
+    <t>25.03.202613</t>
+  </si>
+  <si>
+    <t>25.03.202614</t>
+  </si>
+  <si>
+    <t>25.03.202615</t>
+  </si>
+  <si>
+    <t>25.03.202616</t>
+  </si>
+  <si>
+    <t>25.03.202617</t>
+  </si>
+  <si>
+    <t>25.03.202618</t>
+  </si>
+  <si>
+    <t>25.03.202619</t>
+  </si>
+  <si>
+    <t>25.03.202620</t>
+  </si>
+  <si>
+    <t>25.03.202621</t>
+  </si>
+  <si>
+    <t>25.03.202622</t>
+  </si>
+  <si>
+    <t>25.03.202623</t>
+  </si>
+  <si>
+    <t>25.03.202624</t>
+  </si>
+  <si>
+    <t>25.03.202625</t>
+  </si>
+  <si>
+    <t>25.03.202626</t>
+  </si>
+  <si>
+    <t>25.03.202627</t>
+  </si>
+  <si>
+    <t>25.03.202628</t>
+  </si>
+  <si>
+    <t>25.03.202629</t>
+  </si>
+  <si>
+    <t>25.03.202630</t>
+  </si>
+  <si>
+    <t>25.03.202631</t>
+  </si>
+  <si>
+    <t>25.03.202632</t>
+  </si>
+  <si>
+    <t>25.03.202633</t>
+  </si>
+  <si>
+    <t>25.03.202634</t>
+  </si>
+  <si>
+    <t>25.03.202635</t>
+  </si>
+  <si>
+    <t>25.03.202636</t>
+  </si>
+  <si>
+    <t>25.03.202637</t>
+  </si>
+  <si>
+    <t>25.03.202638</t>
+  </si>
+  <si>
+    <t>25.03.202639</t>
+  </si>
+  <si>
+    <t>25.03.202640</t>
+  </si>
+  <si>
+    <t>25.03.202641</t>
+  </si>
+  <si>
+    <t>25.03.202642</t>
+  </si>
+  <si>
+    <t>25.03.202643</t>
+  </si>
+  <si>
+    <t>25.03.202644</t>
+  </si>
+  <si>
+    <t>25.03.202645</t>
+  </si>
+  <si>
+    <t>25.03.202646</t>
+  </si>
+  <si>
+    <t>25.03.202647</t>
+  </si>
+  <si>
+    <t>25.03.202648</t>
+  </si>
+  <si>
+    <t>25.03.202649</t>
+  </si>
+  <si>
+    <t>25.03.202650</t>
+  </si>
+  <si>
+    <t>25.03.202651</t>
+  </si>
+  <si>
+    <t>25.03.202652</t>
+  </si>
+  <si>
+    <t>25.03.202653</t>
+  </si>
+  <si>
+    <t>25.03.202654</t>
+  </si>
+  <si>
+    <t>25.03.202655</t>
+  </si>
+  <si>
+    <t>25.03.202656</t>
+  </si>
+  <si>
+    <t>25.03.202657</t>
+  </si>
+  <si>
+    <t>25.03.202658</t>
+  </si>
+  <si>
+    <t>25.03.202659</t>
+  </si>
+  <si>
+    <t>25.03.202660</t>
+  </si>
+  <si>
+    <t>25.03.202661</t>
+  </si>
+  <si>
+    <t>25.03.202662</t>
+  </si>
+  <si>
+    <t>25.03.202663</t>
+  </si>
+  <si>
+    <t>25.03.202664</t>
+  </si>
+  <si>
+    <t>25.03.202665</t>
+  </si>
+  <si>
+    <t>25.03.202666</t>
+  </si>
+  <si>
+    <t>25.03.202667</t>
+  </si>
+  <si>
+    <t>25.03.202668</t>
+  </si>
+  <si>
+    <t>25.03.202669</t>
+  </si>
+  <si>
+    <t>25.03.202670</t>
+  </si>
+  <si>
+    <t>25.03.202671</t>
+  </si>
+  <si>
+    <t>25.03.202672</t>
+  </si>
+  <si>
+    <t>25.03.202673</t>
+  </si>
+  <si>
+    <t>25.03.202674</t>
+  </si>
+  <si>
+    <t>25.03.202675</t>
+  </si>
+  <si>
+    <t>25.03.202676</t>
+  </si>
+  <si>
+    <t>25.03.202677</t>
+  </si>
+  <si>
+    <t>25.03.202678</t>
+  </si>
+  <si>
+    <t>25.03.202679</t>
+  </si>
+  <si>
+    <t>25.03.202680</t>
+  </si>
+  <si>
+    <t>25.03.202681</t>
+  </si>
+  <si>
+    <t>25.03.202682</t>
+  </si>
+  <si>
+    <t>25.03.202683</t>
+  </si>
+  <si>
+    <t>25.03.202684</t>
+  </si>
+  <si>
+    <t>25.03.202685</t>
+  </si>
+  <si>
+    <t>25.03.202686</t>
+  </si>
+  <si>
+    <t>25.03.202687</t>
+  </si>
+  <si>
+    <t>25.03.202688</t>
+  </si>
+  <si>
+    <t>25.03.202689</t>
+  </si>
+  <si>
+    <t>25.03.202690</t>
+  </si>
+  <si>
+    <t>25.03.202691</t>
+  </si>
+  <si>
+    <t>25.03.202692</t>
+  </si>
+  <si>
+    <t>25.03.202693</t>
+  </si>
+  <si>
+    <t>25.03.202694</t>
+  </si>
+  <si>
+    <t>25.03.202695</t>
+  </si>
+  <si>
+    <t>25.03.202696</t>
+  </si>
+  <si>
+    <t>26.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20262</t>
+  </si>
+  <si>
+    <t>26.03.20263</t>
+  </si>
+  <si>
+    <t>26.03.20264</t>
+  </si>
+  <si>
+    <t>26.03.20265</t>
+  </si>
+  <si>
+    <t>26.03.20266</t>
+  </si>
+  <si>
+    <t>26.03.20267</t>
+  </si>
+  <si>
+    <t>26.03.20268</t>
+  </si>
+  <si>
+    <t>26.03.20269</t>
+  </si>
+  <si>
+    <t>26.03.202610</t>
+  </si>
+  <si>
+    <t>26.03.202611</t>
+  </si>
+  <si>
+    <t>26.03.202612</t>
+  </si>
+  <si>
+    <t>26.03.202613</t>
+  </si>
+  <si>
+    <t>26.03.202614</t>
+  </si>
+  <si>
+    <t>26.03.202615</t>
+  </si>
+  <si>
+    <t>26.03.202616</t>
+  </si>
+  <si>
+    <t>26.03.202617</t>
+  </si>
+  <si>
+    <t>26.03.202618</t>
+  </si>
+  <si>
+    <t>26.03.202619</t>
+  </si>
+  <si>
+    <t>26.03.202620</t>
+  </si>
+  <si>
+    <t>26.03.202621</t>
+  </si>
+  <si>
+    <t>26.03.202622</t>
+  </si>
+  <si>
+    <t>26.03.202623</t>
+  </si>
+  <si>
+    <t>26.03.202624</t>
+  </si>
+  <si>
+    <t>26.03.202625</t>
+  </si>
+  <si>
+    <t>26.03.202626</t>
+  </si>
+  <si>
+    <t>26.03.202627</t>
+  </si>
+  <si>
+    <t>26.03.202628</t>
+  </si>
+  <si>
+    <t>26.03.202629</t>
+  </si>
+  <si>
+    <t>26.03.202630</t>
+  </si>
+  <si>
+    <t>26.03.202631</t>
+  </si>
+  <si>
+    <t>26.03.202632</t>
+  </si>
+  <si>
+    <t>26.03.202633</t>
+  </si>
+  <si>
+    <t>26.03.202634</t>
+  </si>
+  <si>
+    <t>26.03.202635</t>
+  </si>
+  <si>
+    <t>26.03.202636</t>
+  </si>
+  <si>
+    <t>26.03.202637</t>
+  </si>
+  <si>
+    <t>26.03.202638</t>
+  </si>
+  <si>
+    <t>26.03.202639</t>
+  </si>
+  <si>
+    <t>26.03.202640</t>
+  </si>
+  <si>
+    <t>26.03.202641</t>
+  </si>
+  <si>
+    <t>26.03.202642</t>
+  </si>
+  <si>
+    <t>26.03.202643</t>
+  </si>
+  <si>
+    <t>26.03.202644</t>
+  </si>
+  <si>
+    <t>26.03.202645</t>
+  </si>
+  <si>
+    <t>26.03.202646</t>
+  </si>
+  <si>
+    <t>26.03.202647</t>
+  </si>
+  <si>
+    <t>26.03.202648</t>
+  </si>
+  <si>
+    <t>26.03.202649</t>
+  </si>
+  <si>
+    <t>26.03.202650</t>
+  </si>
+  <si>
+    <t>26.03.202651</t>
+  </si>
+  <si>
+    <t>26.03.202652</t>
+  </si>
+  <si>
+    <t>26.03.202653</t>
+  </si>
+  <si>
+    <t>26.03.202654</t>
+  </si>
+  <si>
+    <t>26.03.202655</t>
+  </si>
+  <si>
+    <t>26.03.202656</t>
+  </si>
+  <si>
+    <t>26.03.202657</t>
+  </si>
+  <si>
+    <t>26.03.202658</t>
+  </si>
+  <si>
+    <t>26.03.202659</t>
+  </si>
+  <si>
+    <t>26.03.202660</t>
+  </si>
+  <si>
+    <t>26.03.202661</t>
+  </si>
+  <si>
+    <t>26.03.202662</t>
+  </si>
+  <si>
+    <t>26.03.202663</t>
+  </si>
+  <si>
+    <t>26.03.202664</t>
+  </si>
+  <si>
+    <t>26.03.202665</t>
+  </si>
+  <si>
+    <t>26.03.202666</t>
+  </si>
+  <si>
+    <t>26.03.202667</t>
+  </si>
+  <si>
+    <t>26.03.202668</t>
+  </si>
+  <si>
+    <t>26.03.202669</t>
+  </si>
+  <si>
+    <t>26.03.202670</t>
+  </si>
+  <si>
+    <t>26.03.202671</t>
+  </si>
+  <si>
+    <t>26.03.202672</t>
+  </si>
+  <si>
+    <t>26.03.202673</t>
+  </si>
+  <si>
+    <t>26.03.202674</t>
+  </si>
+  <si>
+    <t>26.03.202675</t>
+  </si>
+  <si>
+    <t>26.03.202676</t>
+  </si>
+  <si>
+    <t>26.03.202677</t>
+  </si>
+  <si>
+    <t>26.03.202678</t>
+  </si>
+  <si>
+    <t>26.03.202679</t>
+  </si>
+  <si>
+    <t>26.03.202680</t>
+  </si>
+  <si>
+    <t>26.03.202681</t>
+  </si>
+  <si>
+    <t>26.03.202682</t>
+  </si>
+  <si>
+    <t>26.03.202683</t>
+  </si>
+  <si>
+    <t>26.03.202684</t>
+  </si>
+  <si>
+    <t>26.03.202685</t>
+  </si>
+  <si>
+    <t>26.03.202686</t>
+  </si>
+  <si>
+    <t>26.03.202687</t>
+  </si>
+  <si>
+    <t>26.03.202688</t>
+  </si>
+  <si>
+    <t>26.03.202689</t>
+  </si>
+  <si>
+    <t>26.03.202690</t>
+  </si>
+  <si>
+    <t>26.03.202691</t>
+  </si>
+  <si>
+    <t>26.03.202692</t>
+  </si>
+  <si>
+    <t>26.03.202693</t>
+  </si>
+  <si>
+    <t>26.03.202694</t>
+  </si>
+  <si>
+    <t>26.03.202695</t>
+  </si>
+  <si>
+    <t>26.03.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="B2">
-        <v>0.035</v>
+        <v>0.146</v>
       </c>
       <c r="C2">
-        <v>1.928</v>
+        <v>1.425</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46093.01041666666</v>
+        <v>46106.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>13.653</v>
+        <v>11.1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46093.02083333334</v>
+        <v>46106.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>18.57</v>
+        <v>11.283</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46093.03125</v>
+        <v>46106.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>10.801</v>
+        <v>13.041</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46093.04166666666</v>
+        <v>46106.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>6.398</v>
+        <v>4.188</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46093.05208333334</v>
+        <v>46106.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>5.881</v>
+        <v>12.09</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46093.0625</v>
+        <v>46106.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>6.426</v>
+        <v>11.789</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46093.07291666666</v>
+        <v>46106.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.055</v>
+        <v>6.359</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46093.08333333334</v>
+        <v>46106.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.122</v>
+        <v>0.011</v>
       </c>
       <c r="C10">
-        <v>2.145</v>
+        <v>6.182</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46093.09375</v>
+        <v>46106.09375</v>
       </c>
       <c r="B11">
-        <v>1.504</v>
+        <v>0.171</v>
       </c>
       <c r="C11">
-        <v>0.13</v>
+        <v>0.111</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46093.10416666666</v>
+        <v>46106.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.782</v>
+        <v>3.254</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46093.11458333334</v>
+        <v>46106.11458333334</v>
       </c>
       <c r="B13">
-        <v>4.153</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2.731</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46093.125</v>
+        <v>46106.125</v>
       </c>
       <c r="B14">
-        <v>0.127</v>
+        <v>1.494</v>
       </c>
       <c r="C14">
-        <v>0.053</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46093.13541666666</v>
+        <v>46106.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.674</v>
+        <v>1.003</v>
       </c>
       <c r="C15">
-        <v>0.01</v>
+        <v>0.067</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46093.14583333334</v>
+        <v>46106.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.965</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46093.15625</v>
+        <v>46106.15625</v>
       </c>
       <c r="B17">
-        <v>18.746</v>
+        <v>21.894</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46093.16666666666</v>
+        <v>46106.16666666666</v>
       </c>
       <c r="B18">
-        <v>23.084</v>
+        <v>24.466</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46093.17708333334</v>
+        <v>46106.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.423</v>
+        <v>27.457</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46093.1875</v>
+        <v>46106.1875</v>
       </c>
       <c r="B20">
-        <v>13.953</v>
+        <v>42.257</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46093.19791666666</v>
+        <v>46106.19791666666</v>
       </c>
       <c r="B21">
-        <v>42.356</v>
+        <v>37.22</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46093.20833333334</v>
+        <v>46106.20833333334</v>
       </c>
       <c r="B22">
-        <v>10.03</v>
+        <v>23.697</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46093.21875</v>
+        <v>46106.21875</v>
       </c>
       <c r="B23">
-        <v>0.112</v>
+        <v>12.013</v>
       </c>
       <c r="C23">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46093.22916666666</v>
+        <v>46106.22916666666</v>
       </c>
       <c r="B24">
-        <v>4.181</v>
+        <v>1.39</v>
       </c>
       <c r="C24">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46093.23958333334</v>
+        <v>46106.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.254</v>
+        <v>4.32</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46093.25</v>
+        <v>46106.25</v>
       </c>
       <c r="B26">
-        <v>0.281</v>
+        <v>1.839</v>
       </c>
       <c r="C26">
-        <v>4.54</v>
+        <v>2.982</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46093.26041666666</v>
+        <v>46106.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>3.677</v>
+        <v>15.226</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46093.27083333334</v>
+        <v>46106.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>6.94</v>
+        <v>12.332</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46093.28125</v>
+        <v>46106.28125</v>
       </c>
       <c r="B29">
-        <v>1.486</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.089</v>
+        <v>2.073</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46093.29166666666</v>
+        <v>46106.29166666666</v>
       </c>
       <c r="B30">
-        <v>13.147</v>
+        <v>0.187</v>
       </c>
       <c r="C30">
-        <v>0.038</v>
+        <v>0.354</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46093.30208333334</v>
+        <v>46106.30208333334</v>
       </c>
       <c r="B31">
-        <v>4.325</v>
+        <v>3.735</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46093.3125</v>
+        <v>46106.3125</v>
       </c>
       <c r="B32">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.631</v>
+        <v>6.915</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46093.32291666666</v>
+        <v>46106.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>3.871</v>
+        <v>20.603</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46093.33333333334</v>
+        <v>46106.33333333334</v>
       </c>
       <c r="B34">
-        <v>4.971</v>
+        <v>18.017</v>
       </c>
       <c r="C34">
-        <v>0.5620000000000001</v>
+        <v>1.937</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46093.34375</v>
+        <v>46106.34375</v>
       </c>
       <c r="B35">
-        <v>5.746</v>
+        <v>19.241</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>49.75</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46093.35416666666</v>
+        <v>46106.35416666666</v>
       </c>
       <c r="B36">
-        <v>10.239</v>
+        <v>2.144</v>
       </c>
       <c r="C36">
-        <v>0.018</v>
+        <v>0.217</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46093.36458333334</v>
+        <v>46106.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.394</v>
+        <v>0.041</v>
       </c>
       <c r="C37">
-        <v>5.422</v>
+        <v>3.005</v>
       </c>
       <c r="D37">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46093.375</v>
+        <v>46106.375</v>
       </c>
       <c r="B38">
-        <v>6.007</v>
+        <v>0.127</v>
       </c>
       <c r="C38">
-        <v>2.701</v>
+        <v>4.225</v>
       </c>
       <c r="D38">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46093.38541666666</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="C39">
-        <v>6.591</v>
+        <v>1.037</v>
       </c>
       <c r="D39">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46093.39583333334</v>
+        <v>46106.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>13.222</v>
+        <v>29.507</v>
       </c>
       <c r="D40">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46093.40625</v>
+        <v>46106.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>23.116</v>
+        <v>34.758</v>
       </c>
       <c r="D41">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46093.41666666666</v>
+        <v>46106.41666666666</v>
       </c>
       <c r="B42">
-        <v>2.288</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>6.415</v>
+        <v>11.528</v>
       </c>
       <c r="D42">
-        <v>24.25</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46093.42708333334</v>
+        <v>46106.42708333334</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>12.618</v>
+        <v>36.655</v>
       </c>
       <c r="D43">
-        <v>24.25</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46093.4375</v>
+        <v>46106.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>0.209</v>
       </c>
       <c r="C44">
-        <v>3.587</v>
+        <v>9.109</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46093.44791666666</v>
+        <v>46106.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>9.276999999999999</v>
+        <v>16.005</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46093.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C46">
-        <v>28.099</v>
+        <v>11.142</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46093.46875</v>
+        <v>46106.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>24.582</v>
+        <v>15.264</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46093.47916666666</v>
+        <v>46106.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>5.442</v>
       </c>
       <c r="C48">
-        <v>31.849</v>
+        <v>0.52</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46093.48958333334</v>
+        <v>46106.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>7.156</v>
       </c>
       <c r="C49">
-        <v>29.386</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46093.5</v>
+        <v>46106.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="C50">
-        <v>14.305</v>
+        <v>15.446</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46093.51041666666</v>
+        <v>46106.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>20.702</v>
+        <v>19.201</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46093.52083333334</v>
+        <v>46106.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>0.952</v>
       </c>
       <c r="C52">
-        <v>50.814</v>
+        <v>2.53</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46093.53125</v>
+        <v>46106.53125</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>60.88</v>
+        <v>12.988</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46093.54166666666</v>
+        <v>46106.54166666666</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>82.60599999999999</v>
+        <v>27.698</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46093.55208333334</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>15.016</v>
+        <v>10.446</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46093.5625</v>
+        <v>46106.5625</v>
       </c>
       <c r="B56">
-        <v>0.652</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>2.454</v>
+        <v>19.417</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46093.57291666666</v>
+        <v>46106.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>2.853</v>
+        <v>22.067</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46093.58333333334</v>
+        <v>46106.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>12.715</v>
+        <v>49.6</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46093.59375</v>
+        <v>46106.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>27.696</v>
+        <v>20.581</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46093.60416666666</v>
+        <v>46106.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="C60">
-        <v>28.789</v>
+        <v>12.439</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46093.61458333334</v>
+        <v>46106.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="C61">
-        <v>16.526</v>
+        <v>4.649</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>68.5</v>
+        <v>50</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46093.625</v>
+        <v>46106.625</v>
       </c>
       <c r="B62">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>8.723000000000001</v>
+        <v>30.578</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46093.63541666666</v>
+        <v>46106.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.958</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0.103</v>
+        <v>28.27</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46093.64583333334</v>
+        <v>46106.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.377</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0.058</v>
+        <v>32.152</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>64.75</v>
+        <v>50</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46093.65625</v>
+        <v>46106.65625</v>
       </c>
       <c r="B65">
-        <v>11.173</v>
+        <v>0.757</v>
       </c>
       <c r="C65">
-        <v>0.257</v>
+        <v>0.46</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46093.66666666666</v>
+        <v>46106.66666666666</v>
       </c>
       <c r="B66">
-        <v>3.559</v>
+        <v>0.092</v>
       </c>
       <c r="C66">
-        <v>2.172</v>
+        <v>0.422</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>47.75</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46093.67708333334</v>
+        <v>46106.67708333334</v>
       </c>
       <c r="B67">
-        <v>7.879</v>
+        <v>0.5</v>
       </c>
       <c r="C67">
-        <v>0.017</v>
+        <v>4.268</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46093.6875</v>
+        <v>46106.6875</v>
       </c>
       <c r="B68">
-        <v>18.859</v>
+        <v>1.297</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46093.69791666666</v>
+        <v>46106.69791666666</v>
       </c>
       <c r="B69">
-        <v>37.73</v>
+        <v>0.733</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>4.092</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46093.70833333334</v>
+        <v>46106.70833333334</v>
       </c>
       <c r="B70">
-        <v>4.472</v>
+        <v>0.016</v>
       </c>
       <c r="C70">
-        <v>0.011</v>
+        <v>4.206</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46093.71875</v>
+        <v>46106.71875</v>
       </c>
       <c r="B71">
-        <v>1.579</v>
+        <v>0.012</v>
       </c>
       <c r="C71">
-        <v>0.042</v>
+        <v>8.099</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46093.72916666666</v>
+        <v>46106.72916666666</v>
       </c>
       <c r="B72">
-        <v>11.348</v>
+        <v>0.053</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>9.673</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46093.73958333334</v>
+        <v>46106.73958333334</v>
       </c>
       <c r="B73">
-        <v>30.555</v>
+        <v>0.135</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46093.75</v>
+        <v>46106.75</v>
       </c>
       <c r="B74">
-        <v>23.451</v>
+        <v>0.187</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46093.76041666666</v>
+        <v>46106.76041666666</v>
       </c>
       <c r="B75">
-        <v>17.039</v>
+        <v>0.132</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="D75">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46093.77083333334</v>
+        <v>46106.77083333334</v>
       </c>
       <c r="B76">
-        <v>19.579</v>
+        <v>0.751</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="D76">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46093.78125</v>
+        <v>46106.78125</v>
       </c>
       <c r="B77">
-        <v>4.645</v>
+        <v>0.341</v>
       </c>
       <c r="C77">
-        <v>0.196</v>
+        <v>0.004</v>
       </c>
       <c r="D77">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46093.79166666666</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.045</v>
+        <v>0.096</v>
       </c>
       <c r="C78">
-        <v>15.033</v>
+        <v>0.108</v>
       </c>
       <c r="D78">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,13 +2771,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46093.80208333334</v>
+        <v>46106.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.01</v>
+        <v>0.153</v>
       </c>
       <c r="C79">
-        <v>1.885</v>
+        <v>0.036</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46093.8125</v>
+        <v>46106.8125</v>
       </c>
       <c r="B80">
-        <v>0.389</v>
+        <v>0.026</v>
       </c>
       <c r="C80">
-        <v>0.554</v>
+        <v>0.164</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46093.82291666666</v>
+        <v>46106.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.048</v>
+        <v>0.053</v>
       </c>
       <c r="C81">
-        <v>3.296</v>
+        <v>0.434</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46093.83333333334</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.917</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>0.739</v>
+        <v>2.684</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46093.84375</v>
+        <v>46106.84375</v>
       </c>
       <c r="B83">
-        <v>4.454</v>
+        <v>0.021</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46093.85416666666</v>
+        <v>46106.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.287</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>0.645</v>
+        <v>19.367</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46093.86458333334</v>
+        <v>46106.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>1.531</v>
+        <v>20.388</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46093.875</v>
+        <v>46106.875</v>
       </c>
       <c r="B86">
-        <v>13.43</v>
+        <v>0.582</v>
       </c>
       <c r="C86">
-        <v>0.167</v>
+        <v>3.29</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46093.88541666666</v>
+        <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>17.079</v>
+        <v>0.529</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>4.043</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46093.89583333334</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>4.446</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>5.553</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46093.90625</v>
+        <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>3.424</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>0.045</v>
+        <v>32.151</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46093.91666666666</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>23.618</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>0.003</v>
+        <v>15.649</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46093.92708333334</v>
+        <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>37.254</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>5.952</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,16 +3070,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46093.9375</v>
+        <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>10.933</v>
+        <v>0.036</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>2.514</v>
       </c>
       <c r="D92">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3093,16 +3093,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46093.94791666666</v>
+        <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.519</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>0.529</v>
+        <v>9.631</v>
       </c>
       <c r="D93">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3116,16 +3116,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.924</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>0.552</v>
+        <v>23.717</v>
       </c>
       <c r="D94">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3139,16 +3139,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B95">
-        <v>0.924</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>0.552</v>
+        <v>23.717</v>
       </c>
       <c r="D95">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B96">
-        <v>5.176</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0.522</v>
+        <v>14.734</v>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3185,16 +3185,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B97">
-        <v>5.176</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0.522</v>
+        <v>14.734</v>
       </c>
       <c r="D97">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3208,16 +3208,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="C98">
-        <v>8.94</v>
+        <v>3.639</v>
       </c>
       <c r="D98">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="C99">
-        <v>8.94</v>
+        <v>3.639</v>
       </c>
       <c r="D99">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>13.718</v>
+        <v>14.017</v>
       </c>
       <c r="D100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3277,16 +3277,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>13.718</v>
+        <v>14.017</v>
       </c>
       <c r="D101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B102">
-        <v>18.511</v>
+        <v>1.306</v>
       </c>
       <c r="C102">
-        <v>0.04</v>
+        <v>1.95</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B103">
-        <v>18.511</v>
+        <v>1.306</v>
       </c>
       <c r="C103">
-        <v>0.04</v>
+        <v>1.95</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B104">
-        <v>18.22</v>
+        <v>4.221</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B105">
-        <v>18.22</v>
+        <v>4.221</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B106">
-        <v>8.359</v>
+        <v>0.155</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B107">
-        <v>8.359</v>
+        <v>0.155</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B108">
-        <v>1.45</v>
+        <v>0.694</v>
       </c>
       <c r="C108">
-        <v>0.707</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B109">
-        <v>1.45</v>
+        <v>0.694</v>
       </c>
       <c r="C109">
-        <v>0.707</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B110">
-        <v>6.055</v>
+        <v>3.031</v>
       </c>
       <c r="C110">
-        <v>0.926</v>
+        <v>0.016</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B111">
-        <v>1.666</v>
+        <v>4.522</v>
       </c>
       <c r="C111">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B112">
-        <v>0.011</v>
+        <v>0.021</v>
       </c>
       <c r="C112">
-        <v>3.766</v>
+        <v>0.994</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>10.291</v>
+        <v>0.783</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B114">
-        <v>0.134</v>
+        <v>0.022</v>
       </c>
       <c r="C114">
-        <v>2.983</v>
+        <v>0.275</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>1.289</v>
       </c>
       <c r="C115">
-        <v>2.095</v>
+        <v>2.177</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>8.278</v>
+        <v>2.204</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>0.738</v>
       </c>
       <c r="C117">
-        <v>17.532</v>
+        <v>0.442</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>3.753</v>
       </c>
       <c r="C118">
-        <v>3.895</v>
+        <v>0.201</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="C119">
-        <v>8.69</v>
+        <v>0.115</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>0.287</v>
       </c>
       <c r="C120">
-        <v>5.865</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="C121">
-        <v>9.692</v>
+        <v>0.233</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C122">
-        <v>4.503</v>
+        <v>1.433</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B123">
-        <v>0.08699999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="C123">
-        <v>0.097</v>
+        <v>0.081</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B124">
-        <v>0.115</v>
+        <v>4.248</v>
       </c>
       <c r="C124">
-        <v>0.254</v>
+        <v>0.002</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.249</v>
+        <v>14.835</v>
       </c>
       <c r="C125">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.047</v>
+        <v>1.357</v>
       </c>
       <c r="C126">
-        <v>7.787</v>
+        <v>4.389</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B127">
-        <v>0.047</v>
+        <v>0.02</v>
       </c>
       <c r="C127">
-        <v>0.145</v>
+        <v>3.225</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B128">
-        <v>0.017</v>
+        <v>0.002</v>
       </c>
       <c r="C128">
-        <v>1.607</v>
+        <v>2.598</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B129">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="C129">
-        <v>3.772</v>
+        <v>1.456</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="C130">
-        <v>19.283</v>
+        <v>3.289</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="C131">
-        <v>25.801</v>
+        <v>0.047</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,13 +3990,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>0.867</v>
       </c>
       <c r="C132">
-        <v>52.646</v>
+        <v>0.006</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>2.345</v>
       </c>
       <c r="C133">
-        <v>67.589</v>
+        <v>0.005</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4036,19 +4036,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>15.963</v>
       </c>
       <c r="C134">
-        <v>30.997</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>29</v>
@@ -4059,19 +4059,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.007</v>
+        <v>23.973</v>
       </c>
       <c r="C135">
-        <v>18.253</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E135">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>30</v>
@@ -4082,19 +4082,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>3.619</v>
       </c>
       <c r="C136">
-        <v>32.309</v>
+        <v>0.005</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E136">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>31</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>40.093</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E137">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>32</v>
@@ -4128,16 +4128,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>0.407</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.04.20261</t>
-  </si>
-  <si>
-    <t>09.04.20262</t>
-  </si>
-  <si>
-    <t>09.04.20263</t>
-  </si>
-  <si>
-    <t>09.04.20264</t>
-  </si>
-  <si>
-    <t>09.04.20265</t>
-  </si>
-  <si>
-    <t>09.04.20266</t>
-  </si>
-  <si>
-    <t>09.04.20267</t>
-  </si>
-  <si>
-    <t>09.04.20268</t>
-  </si>
-  <si>
-    <t>09.04.20269</t>
-  </si>
-  <si>
-    <t>09.04.202610</t>
-  </si>
-  <si>
-    <t>09.04.202611</t>
-  </si>
-  <si>
-    <t>09.04.202612</t>
-  </si>
-  <si>
-    <t>09.04.202613</t>
-  </si>
-  <si>
-    <t>09.04.202614</t>
-  </si>
-  <si>
-    <t>09.04.202615</t>
-  </si>
-  <si>
-    <t>09.04.202616</t>
-  </si>
-  <si>
-    <t>09.04.202617</t>
-  </si>
-  <si>
-    <t>09.04.202618</t>
-  </si>
-  <si>
-    <t>09.04.202619</t>
-  </si>
-  <si>
-    <t>09.04.202620</t>
-  </si>
-  <si>
-    <t>09.04.202621</t>
-  </si>
-  <si>
-    <t>09.04.202622</t>
-  </si>
-  <si>
-    <t>09.04.202623</t>
-  </si>
-  <si>
-    <t>09.04.202624</t>
-  </si>
-  <si>
-    <t>09.04.202625</t>
-  </si>
-  <si>
-    <t>09.04.202626</t>
-  </si>
-  <si>
-    <t>09.04.202627</t>
-  </si>
-  <si>
-    <t>09.04.202628</t>
-  </si>
-  <si>
-    <t>09.04.202629</t>
-  </si>
-  <si>
-    <t>09.04.202630</t>
-  </si>
-  <si>
-    <t>09.04.202631</t>
-  </si>
-  <si>
-    <t>09.04.202632</t>
-  </si>
-  <si>
-    <t>09.04.202633</t>
-  </si>
-  <si>
-    <t>09.04.202634</t>
-  </si>
-  <si>
-    <t>09.04.202635</t>
-  </si>
-  <si>
-    <t>09.04.202636</t>
-  </si>
-  <si>
-    <t>09.04.202637</t>
-  </si>
-  <si>
-    <t>09.04.202638</t>
-  </si>
-  <si>
-    <t>09.04.202639</t>
-  </si>
-  <si>
-    <t>09.04.202640</t>
-  </si>
-  <si>
-    <t>09.04.202641</t>
-  </si>
-  <si>
-    <t>09.04.202642</t>
-  </si>
-  <si>
-    <t>09.04.202643</t>
-  </si>
-  <si>
-    <t>09.04.202644</t>
-  </si>
-  <si>
-    <t>09.04.202645</t>
-  </si>
-  <si>
-    <t>09.04.202646</t>
-  </si>
-  <si>
-    <t>09.04.202647</t>
-  </si>
-  <si>
-    <t>09.04.202648</t>
-  </si>
-  <si>
-    <t>09.04.202649</t>
-  </si>
-  <si>
-    <t>09.04.202650</t>
-  </si>
-  <si>
-    <t>09.04.202651</t>
-  </si>
-  <si>
-    <t>09.04.202652</t>
-  </si>
-  <si>
-    <t>09.04.202653</t>
-  </si>
-  <si>
-    <t>09.04.202654</t>
-  </si>
-  <si>
-    <t>09.04.202655</t>
-  </si>
-  <si>
-    <t>09.04.202656</t>
-  </si>
-  <si>
-    <t>09.04.202657</t>
-  </si>
-  <si>
-    <t>09.04.202658</t>
-  </si>
-  <si>
-    <t>09.04.202659</t>
-  </si>
-  <si>
-    <t>09.04.202660</t>
-  </si>
-  <si>
-    <t>09.04.202661</t>
-  </si>
-  <si>
-    <t>09.04.202662</t>
-  </si>
-  <si>
-    <t>09.04.202663</t>
-  </si>
-  <si>
-    <t>09.04.202664</t>
-  </si>
-  <si>
-    <t>09.04.202665</t>
-  </si>
-  <si>
-    <t>09.04.202666</t>
-  </si>
-  <si>
-    <t>09.04.202667</t>
-  </si>
-  <si>
-    <t>09.04.202668</t>
-  </si>
-  <si>
-    <t>09.04.202669</t>
-  </si>
-  <si>
-    <t>09.04.202670</t>
-  </si>
-  <si>
-    <t>09.04.202671</t>
-  </si>
-  <si>
-    <t>09.04.202672</t>
-  </si>
-  <si>
-    <t>09.04.202673</t>
-  </si>
-  <si>
-    <t>09.04.202674</t>
-  </si>
-  <si>
-    <t>09.04.202675</t>
-  </si>
-  <si>
-    <t>09.04.202676</t>
-  </si>
-  <si>
-    <t>09.04.202677</t>
-  </si>
-  <si>
-    <t>09.04.202678</t>
-  </si>
-  <si>
-    <t>09.04.202679</t>
-  </si>
-  <si>
-    <t>09.04.202680</t>
-  </si>
-  <si>
-    <t>09.04.202681</t>
-  </si>
-  <si>
-    <t>09.04.202682</t>
-  </si>
-  <si>
-    <t>09.04.202683</t>
-  </si>
-  <si>
-    <t>09.04.202684</t>
-  </si>
-  <si>
-    <t>09.04.202685</t>
-  </si>
-  <si>
-    <t>09.04.202686</t>
-  </si>
-  <si>
-    <t>09.04.202687</t>
-  </si>
-  <si>
-    <t>09.04.202688</t>
-  </si>
-  <si>
-    <t>09.04.202689</t>
-  </si>
-  <si>
-    <t>09.04.202690</t>
-  </si>
-  <si>
-    <t>09.04.202691</t>
-  </si>
-  <si>
-    <t>09.04.202692</t>
-  </si>
-  <si>
-    <t>09.04.202693</t>
-  </si>
-  <si>
-    <t>09.04.202694</t>
-  </si>
-  <si>
-    <t>09.04.202695</t>
-  </si>
-  <si>
-    <t>09.04.202696</t>
-  </si>
-  <si>
-    <t>10.04.20261</t>
-  </si>
-  <si>
-    <t>10.04.20262</t>
-  </si>
-  <si>
-    <t>10.04.20263</t>
-  </si>
-  <si>
-    <t>10.04.20264</t>
-  </si>
-  <si>
-    <t>10.04.20265</t>
-  </si>
-  <si>
-    <t>10.04.20266</t>
-  </si>
-  <si>
-    <t>10.04.20267</t>
-  </si>
-  <si>
-    <t>10.04.20268</t>
-  </si>
-  <si>
-    <t>10.04.20269</t>
-  </si>
-  <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>10.04.202624</t>
-  </si>
-  <si>
-    <t>10.04.202625</t>
-  </si>
-  <si>
-    <t>10.04.202626</t>
-  </si>
-  <si>
-    <t>10.04.202627</t>
-  </si>
-  <si>
-    <t>10.04.202628</t>
-  </si>
-  <si>
-    <t>10.04.202629</t>
-  </si>
-  <si>
-    <t>10.04.202630</t>
-  </si>
-  <si>
-    <t>10.04.202631</t>
-  </si>
-  <si>
-    <t>10.04.202632</t>
-  </si>
-  <si>
-    <t>10.04.202633</t>
-  </si>
-  <si>
-    <t>10.04.202634</t>
-  </si>
-  <si>
-    <t>10.04.202635</t>
-  </si>
-  <si>
-    <t>10.04.202636</t>
-  </si>
-  <si>
-    <t>10.04.202637</t>
-  </si>
-  <si>
-    <t>10.04.202638</t>
-  </si>
-  <si>
-    <t>10.04.202639</t>
-  </si>
-  <si>
-    <t>10.04.202640</t>
-  </si>
-  <si>
-    <t>10.04.202641</t>
-  </si>
-  <si>
-    <t>10.04.202642</t>
-  </si>
-  <si>
-    <t>10.04.202643</t>
-  </si>
-  <si>
-    <t>10.04.202644</t>
-  </si>
-  <si>
-    <t>10.04.202645</t>
-  </si>
-  <si>
-    <t>10.04.202646</t>
-  </si>
-  <si>
-    <t>10.04.202647</t>
-  </si>
-  <si>
-    <t>10.04.202648</t>
-  </si>
-  <si>
-    <t>10.04.202649</t>
-  </si>
-  <si>
-    <t>10.04.202650</t>
-  </si>
-  <si>
-    <t>10.04.202651</t>
-  </si>
-  <si>
-    <t>10.04.202652</t>
-  </si>
-  <si>
-    <t>10.04.202653</t>
-  </si>
-  <si>
-    <t>10.04.202654</t>
-  </si>
-  <si>
-    <t>10.04.202655</t>
-  </si>
-  <si>
-    <t>10.04.202656</t>
-  </si>
-  <si>
-    <t>10.04.202657</t>
-  </si>
-  <si>
-    <t>10.04.202658</t>
-  </si>
-  <si>
-    <t>10.04.202659</t>
-  </si>
-  <si>
-    <t>10.04.202660</t>
-  </si>
-  <si>
-    <t>10.04.202661</t>
-  </si>
-  <si>
-    <t>10.04.202662</t>
-  </si>
-  <si>
-    <t>10.04.202663</t>
-  </si>
-  <si>
-    <t>10.04.202664</t>
-  </si>
-  <si>
-    <t>10.04.202665</t>
-  </si>
-  <si>
-    <t>10.04.202666</t>
-  </si>
-  <si>
-    <t>10.04.202667</t>
-  </si>
-  <si>
-    <t>10.04.202668</t>
-  </si>
-  <si>
-    <t>10.04.202669</t>
-  </si>
-  <si>
-    <t>10.04.202670</t>
-  </si>
-  <si>
-    <t>10.04.202671</t>
-  </si>
-  <si>
-    <t>10.04.202672</t>
-  </si>
-  <si>
-    <t>10.04.202673</t>
-  </si>
-  <si>
-    <t>10.04.202674</t>
-  </si>
-  <si>
-    <t>10.04.202675</t>
-  </si>
-  <si>
-    <t>10.04.202676</t>
-  </si>
-  <si>
-    <t>10.04.202677</t>
-  </si>
-  <si>
-    <t>10.04.202678</t>
-  </si>
-  <si>
-    <t>10.04.202679</t>
-  </si>
-  <si>
-    <t>10.04.202680</t>
-  </si>
-  <si>
-    <t>10.04.202681</t>
-  </si>
-  <si>
-    <t>10.04.202682</t>
-  </si>
-  <si>
-    <t>10.04.202683</t>
-  </si>
-  <si>
-    <t>10.04.202684</t>
-  </si>
-  <si>
-    <t>10.04.202685</t>
-  </si>
-  <si>
-    <t>10.04.202686</t>
-  </si>
-  <si>
-    <t>10.04.202687</t>
-  </si>
-  <si>
-    <t>10.04.202688</t>
-  </si>
-  <si>
-    <t>10.04.202689</t>
-  </si>
-  <si>
-    <t>10.04.202690</t>
-  </si>
-  <si>
-    <t>10.04.202691</t>
-  </si>
-  <si>
-    <t>10.04.202692</t>
-  </si>
-  <si>
-    <t>10.04.202693</t>
-  </si>
-  <si>
-    <t>10.04.202694</t>
-  </si>
-  <si>
-    <t>10.04.202695</t>
-  </si>
-  <si>
-    <t>10.04.202696</t>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.202624</t>
+  </si>
+  <si>
+    <t>16.04.202625</t>
+  </si>
+  <si>
+    <t>16.04.202626</t>
+  </si>
+  <si>
+    <t>16.04.202627</t>
+  </si>
+  <si>
+    <t>16.04.202628</t>
+  </si>
+  <si>
+    <t>16.04.202629</t>
+  </si>
+  <si>
+    <t>16.04.202630</t>
+  </si>
+  <si>
+    <t>16.04.202631</t>
+  </si>
+  <si>
+    <t>16.04.202632</t>
+  </si>
+  <si>
+    <t>16.04.202633</t>
+  </si>
+  <si>
+    <t>16.04.202634</t>
+  </si>
+  <si>
+    <t>16.04.202635</t>
+  </si>
+  <si>
+    <t>16.04.202636</t>
+  </si>
+  <si>
+    <t>16.04.202637</t>
+  </si>
+  <si>
+    <t>16.04.202638</t>
+  </si>
+  <si>
+    <t>16.04.202639</t>
+  </si>
+  <si>
+    <t>16.04.202640</t>
+  </si>
+  <si>
+    <t>16.04.202641</t>
+  </si>
+  <si>
+    <t>16.04.202642</t>
+  </si>
+  <si>
+    <t>16.04.202643</t>
+  </si>
+  <si>
+    <t>16.04.202644</t>
+  </si>
+  <si>
+    <t>16.04.202645</t>
+  </si>
+  <si>
+    <t>16.04.202646</t>
+  </si>
+  <si>
+    <t>16.04.202647</t>
+  </si>
+  <si>
+    <t>16.04.202648</t>
+  </si>
+  <si>
+    <t>16.04.202649</t>
+  </si>
+  <si>
+    <t>16.04.202650</t>
+  </si>
+  <si>
+    <t>16.04.202651</t>
+  </si>
+  <si>
+    <t>16.04.202652</t>
+  </si>
+  <si>
+    <t>16.04.202653</t>
+  </si>
+  <si>
+    <t>16.04.202654</t>
+  </si>
+  <si>
+    <t>16.04.202655</t>
+  </si>
+  <si>
+    <t>16.04.202656</t>
+  </si>
+  <si>
+    <t>16.04.202657</t>
+  </si>
+  <si>
+    <t>16.04.202658</t>
+  </si>
+  <si>
+    <t>16.04.202659</t>
+  </si>
+  <si>
+    <t>16.04.202660</t>
+  </si>
+  <si>
+    <t>16.04.202661</t>
+  </si>
+  <si>
+    <t>16.04.202662</t>
+  </si>
+  <si>
+    <t>16.04.202663</t>
+  </si>
+  <si>
+    <t>16.04.202664</t>
+  </si>
+  <si>
+    <t>16.04.202665</t>
+  </si>
+  <si>
+    <t>16.04.202666</t>
+  </si>
+  <si>
+    <t>16.04.202667</t>
+  </si>
+  <si>
+    <t>16.04.202668</t>
+  </si>
+  <si>
+    <t>16.04.202669</t>
+  </si>
+  <si>
+    <t>16.04.202670</t>
+  </si>
+  <si>
+    <t>16.04.202671</t>
+  </si>
+  <si>
+    <t>16.04.202672</t>
+  </si>
+  <si>
+    <t>16.04.202673</t>
+  </si>
+  <si>
+    <t>16.04.202674</t>
+  </si>
+  <si>
+    <t>16.04.202675</t>
+  </si>
+  <si>
+    <t>16.04.202676</t>
+  </si>
+  <si>
+    <t>16.04.202677</t>
+  </si>
+  <si>
+    <t>16.04.202678</t>
+  </si>
+  <si>
+    <t>16.04.202679</t>
+  </si>
+  <si>
+    <t>16.04.202680</t>
+  </si>
+  <si>
+    <t>16.04.202681</t>
+  </si>
+  <si>
+    <t>16.04.202682</t>
+  </si>
+  <si>
+    <t>16.04.202683</t>
+  </si>
+  <si>
+    <t>16.04.202684</t>
+  </si>
+  <si>
+    <t>16.04.202685</t>
+  </si>
+  <si>
+    <t>16.04.202686</t>
+  </si>
+  <si>
+    <t>16.04.202687</t>
+  </si>
+  <si>
+    <t>16.04.202688</t>
+  </si>
+  <si>
+    <t>16.04.202689</t>
+  </si>
+  <si>
+    <t>16.04.202690</t>
+  </si>
+  <si>
+    <t>16.04.202691</t>
+  </si>
+  <si>
+    <t>16.04.202692</t>
+  </si>
+  <si>
+    <t>16.04.202693</t>
+  </si>
+  <si>
+    <t>16.04.202694</t>
+  </si>
+  <si>
+    <t>16.04.202695</t>
+  </si>
+  <si>
+    <t>16.04.202696</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
+  </si>
+  <si>
+    <t>17.04.202610</t>
+  </si>
+  <si>
+    <t>17.04.202611</t>
+  </si>
+  <si>
+    <t>17.04.202612</t>
+  </si>
+  <si>
+    <t>17.04.202613</t>
+  </si>
+  <si>
+    <t>17.04.202614</t>
+  </si>
+  <si>
+    <t>17.04.202615</t>
+  </si>
+  <si>
+    <t>17.04.202616</t>
+  </si>
+  <si>
+    <t>17.04.202617</t>
+  </si>
+  <si>
+    <t>17.04.202618</t>
+  </si>
+  <si>
+    <t>17.04.202619</t>
+  </si>
+  <si>
+    <t>17.04.202620</t>
+  </si>
+  <si>
+    <t>17.04.202621</t>
+  </si>
+  <si>
+    <t>17.04.202622</t>
+  </si>
+  <si>
+    <t>17.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.202624</t>
+  </si>
+  <si>
+    <t>17.04.202625</t>
+  </si>
+  <si>
+    <t>17.04.202626</t>
+  </si>
+  <si>
+    <t>17.04.202627</t>
+  </si>
+  <si>
+    <t>17.04.202628</t>
+  </si>
+  <si>
+    <t>17.04.202629</t>
+  </si>
+  <si>
+    <t>17.04.202630</t>
+  </si>
+  <si>
+    <t>17.04.202631</t>
+  </si>
+  <si>
+    <t>17.04.202632</t>
+  </si>
+  <si>
+    <t>17.04.202633</t>
+  </si>
+  <si>
+    <t>17.04.202634</t>
+  </si>
+  <si>
+    <t>17.04.202635</t>
+  </si>
+  <si>
+    <t>17.04.202636</t>
+  </si>
+  <si>
+    <t>17.04.202637</t>
+  </si>
+  <si>
+    <t>17.04.202638</t>
+  </si>
+  <si>
+    <t>17.04.202639</t>
+  </si>
+  <si>
+    <t>17.04.202640</t>
+  </si>
+  <si>
+    <t>17.04.202641</t>
+  </si>
+  <si>
+    <t>17.04.202642</t>
+  </si>
+  <si>
+    <t>17.04.202643</t>
+  </si>
+  <si>
+    <t>17.04.202644</t>
+  </si>
+  <si>
+    <t>17.04.202645</t>
+  </si>
+  <si>
+    <t>17.04.202646</t>
+  </si>
+  <si>
+    <t>17.04.202647</t>
+  </si>
+  <si>
+    <t>17.04.202648</t>
+  </si>
+  <si>
+    <t>17.04.202649</t>
+  </si>
+  <si>
+    <t>17.04.202650</t>
+  </si>
+  <si>
+    <t>17.04.202651</t>
+  </si>
+  <si>
+    <t>17.04.202652</t>
+  </si>
+  <si>
+    <t>17.04.202653</t>
+  </si>
+  <si>
+    <t>17.04.202654</t>
+  </si>
+  <si>
+    <t>17.04.202655</t>
+  </si>
+  <si>
+    <t>17.04.202656</t>
+  </si>
+  <si>
+    <t>17.04.202657</t>
+  </si>
+  <si>
+    <t>17.04.202658</t>
+  </si>
+  <si>
+    <t>17.04.202659</t>
+  </si>
+  <si>
+    <t>17.04.202660</t>
+  </si>
+  <si>
+    <t>17.04.202661</t>
+  </si>
+  <si>
+    <t>17.04.202662</t>
+  </si>
+  <si>
+    <t>17.04.202663</t>
+  </si>
+  <si>
+    <t>17.04.202664</t>
+  </si>
+  <si>
+    <t>17.04.202665</t>
+  </si>
+  <si>
+    <t>17.04.202666</t>
+  </si>
+  <si>
+    <t>17.04.202667</t>
+  </si>
+  <si>
+    <t>17.04.202668</t>
+  </si>
+  <si>
+    <t>17.04.202669</t>
+  </si>
+  <si>
+    <t>17.04.202670</t>
+  </si>
+  <si>
+    <t>17.04.202671</t>
+  </si>
+  <si>
+    <t>17.04.202672</t>
+  </si>
+  <si>
+    <t>17.04.202673</t>
+  </si>
+  <si>
+    <t>17.04.202674</t>
+  </si>
+  <si>
+    <t>17.04.202675</t>
+  </si>
+  <si>
+    <t>17.04.202676</t>
+  </si>
+  <si>
+    <t>17.04.202677</t>
+  </si>
+  <si>
+    <t>17.04.202678</t>
+  </si>
+  <si>
+    <t>17.04.202679</t>
+  </si>
+  <si>
+    <t>17.04.202680</t>
+  </si>
+  <si>
+    <t>17.04.202681</t>
+  </si>
+  <si>
+    <t>17.04.202682</t>
+  </si>
+  <si>
+    <t>17.04.202683</t>
+  </si>
+  <si>
+    <t>17.04.202684</t>
+  </si>
+  <si>
+    <t>17.04.202685</t>
+  </si>
+  <si>
+    <t>17.04.202686</t>
+  </si>
+  <si>
+    <t>17.04.202687</t>
+  </si>
+  <si>
+    <t>17.04.202688</t>
+  </si>
+  <si>
+    <t>17.04.202689</t>
+  </si>
+  <si>
+    <t>17.04.202690</t>
+  </si>
+  <si>
+    <t>17.04.202691</t>
+  </si>
+  <si>
+    <t>17.04.202692</t>
+  </si>
+  <si>
+    <t>17.04.202693</t>
+  </si>
+  <si>
+    <t>17.04.202694</t>
+  </si>
+  <si>
+    <t>17.04.202695</t>
+  </si>
+  <si>
+    <t>17.04.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,16 +1000,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B2">
-        <v>20.978</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.635</v>
+        <v>40.469</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1023,16 +1023,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46128.01041666666</v>
       </c>
       <c r="B3">
-        <v>3.475</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.008</v>
+        <v>27.606</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1046,16 +1046,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46128.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.411</v>
+        <v>32.229</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1069,16 +1069,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46128.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>4.936</v>
+        <v>31.849</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46128.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>5.412</v>
+        <v>37.673</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46128.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>11.636</v>
+        <v>30.832</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46128.0625</v>
       </c>
       <c r="B8">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1.979</v>
+        <v>36.19</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46128.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.201</v>
+        <v>28.395</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46128.08333333334</v>
       </c>
       <c r="B10">
-        <v>2.709</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.033</v>
+        <v>17.273</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46128.09375</v>
       </c>
       <c r="B11">
-        <v>3.542</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.013</v>
+        <v>12.97</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46128.10416666666</v>
       </c>
       <c r="B12">
-        <v>7.738</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>29.278</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46128.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.321</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.018</v>
+        <v>20.66</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46128.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>4.333</v>
+        <v>20.511</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46128.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0.466</v>
+        <v>6.597</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46128.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0.988</v>
+        <v>14.93</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46128.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>16.568</v>
+        <v>5.623</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46128.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>19.37</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>17.663</v>
+        <v>3.548</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46128.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>13.57</v>
+        <v>19.942</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46128.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>6.481</v>
+        <v>9.683</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46128.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1.926</v>
+        <v>20.202</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46128.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C23">
-        <v>7.98</v>
+        <v>1.376</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46128.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>18.032</v>
+        <v>2.61</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46128.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="C25">
-        <v>24.55</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46128.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="C26">
-        <v>23.277</v>
+        <v>5.244</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46128.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.17</v>
+        <v>0.004</v>
       </c>
       <c r="C27">
-        <v>0.232</v>
+        <v>2.746</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46128.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.215</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.055</v>
+        <v>25.261</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46128.28125</v>
       </c>
       <c r="B29">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>4.708</v>
+        <v>44.245</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46128.29166666666</v>
       </c>
       <c r="B30">
-        <v>13.008</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.032</v>
+        <v>21.512</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,13 +1667,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46128.30208333334</v>
       </c>
       <c r="B31">
-        <v>25.82</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>9.317</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46128.3125</v>
       </c>
       <c r="B32">
-        <v>9.718</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.01</v>
+        <v>3.612</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>39.25</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46128.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>2.337</v>
+        <v>10.224</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>39.25</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>17.335</v>
       </c>
       <c r="C34">
-        <v>10.592</v>
+        <v>0.531</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46128.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>4.802</v>
       </c>
       <c r="C35">
-        <v>18.247</v>
+        <v>0.043</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>8.791</v>
       </c>
       <c r="C36">
-        <v>24.083</v>
+        <v>0.002</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="C37">
-        <v>41.204</v>
+        <v>6.233</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>14.75</v>
+        <v>49</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46128.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="C38">
-        <v>28.821</v>
+        <v>3.218</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>15.153</v>
+        <v>2.598</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>42.5</v>
+        <v>50</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46128.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>5.301</v>
+        <v>11.399</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>42.5</v>
+        <v>50</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46128.40625</v>
       </c>
       <c r="B41">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>4.85</v>
+        <v>45.62</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>42.5</v>
+        <v>50</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46128.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.345</v>
+        <v>4.673</v>
       </c>
       <c r="C42">
-        <v>0.065</v>
+        <v>5.18</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>42.5</v>
+        <v>74</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46128.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.381</v>
+        <v>0.826</v>
       </c>
       <c r="C43">
-        <v>0.082</v>
+        <v>0.768</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>42.5</v>
+        <v>70.5</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46128.4375</v>
       </c>
       <c r="B44">
         <v>0.019</v>
       </c>
       <c r="C44">
-        <v>0.735</v>
+        <v>4.379</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46128.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.623</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>8.24</v>
+        <v>35.847</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46128.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.268</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>5.318</v>
+        <v>36.689</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46128.46875</v>
       </c>
       <c r="B47">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0.649</v>
+        <v>35.741</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>84.75</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46128.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>17.101</v>
+        <v>18.838</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46128.48958333334</v>
       </c>
       <c r="B49">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>1.968</v>
+        <v>6.561</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46128.5</v>
       </c>
       <c r="B50">
-        <v>11.839</v>
+        <v>0.37</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46128.51041666666</v>
       </c>
       <c r="B51">
-        <v>1.298</v>
+        <v>5.134</v>
       </c>
       <c r="C51">
-        <v>0.806</v>
+        <v>0.015</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46128.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.008</v>
+        <v>1.438</v>
       </c>
       <c r="C52">
-        <v>4.039</v>
+        <v>0.949</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46128.53125</v>
       </c>
       <c r="B53">
-        <v>0.066</v>
+        <v>0.14</v>
       </c>
       <c r="C53">
-        <v>0.547</v>
+        <v>0.801</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46128.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.091</v>
+        <v>0.57</v>
       </c>
       <c r="C54">
-        <v>0.55</v>
+        <v>0.022</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.04</v>
+        <v>0.135</v>
       </c>
       <c r="C55">
-        <v>0.882</v>
+        <v>3.594</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46128.5625</v>
       </c>
       <c r="B56">
-        <v>0.082</v>
+        <v>2.211</v>
       </c>
       <c r="C56">
-        <v>8.175000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46128.57291666666</v>
       </c>
       <c r="B57">
+        <v>0.718</v>
+      </c>
+      <c r="C57">
         <v>0.023</v>
       </c>
-      <c r="C57">
-        <v>4.16</v>
-      </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46128.58333333334</v>
       </c>
       <c r="B58">
-        <v>1.772</v>
+        <v>13.174</v>
       </c>
       <c r="C58">
-        <v>0.016</v>
+        <v>0.075</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46128.59375</v>
       </c>
       <c r="B59">
-        <v>0.348</v>
+        <v>17.003</v>
       </c>
       <c r="C59">
-        <v>0.508</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46128.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.014</v>
+        <v>5.995</v>
       </c>
       <c r="C60">
-        <v>21.571</v>
+        <v>0.026</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46128.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="C61">
-        <v>18.269</v>
+        <v>17.273</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46128.625</v>
       </c>
       <c r="B62">
-        <v>2.223</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>0.033</v>
+        <v>25.714</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46128.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0.103</v>
+        <v>2.006</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,16 +2426,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46128.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.735</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>1.125</v>
+        <v>7.292</v>
       </c>
       <c r="D64">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46128.65625</v>
       </c>
       <c r="B65">
-        <v>0.593</v>
+        <v>0.023</v>
       </c>
       <c r="C65">
-        <v>0.425</v>
+        <v>1.279</v>
       </c>
       <c r="D65">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46128.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>12.983</v>
+        <v>26.015</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46128.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="C67">
-        <v>10.889</v>
+        <v>0.482</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46128.6875</v>
       </c>
       <c r="B68">
-        <v>0.556</v>
+        <v>1.123</v>
       </c>
       <c r="C68">
-        <v>8.438000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46128.69791666666</v>
       </c>
       <c r="B69">
-        <v>0.5679999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="C69">
-        <v>0.73</v>
+        <v>1.668</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,13 +2564,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46128.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>5.073</v>
+        <v>6.509</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46128.71875</v>
       </c>
       <c r="B71">
-        <v>0.052</v>
+        <v>0.26</v>
       </c>
       <c r="C71">
-        <v>0.168</v>
+        <v>10.138</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46128.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.059</v>
+        <v>0.876</v>
       </c>
       <c r="C72">
-        <v>0.261</v>
+        <v>0.223</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46128.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.038</v>
+        <v>16.281</v>
       </c>
       <c r="C73">
-        <v>9.368</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,19 +2656,19 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46128.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1.501</v>
       </c>
       <c r="C74">
-        <v>60.827</v>
+        <v>10.046</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46128.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.01</v>
+        <v>6.034</v>
       </c>
       <c r="C75">
-        <v>35.56</v>
+        <v>2.513</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46128.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.126</v>
+        <v>0.493</v>
       </c>
       <c r="C76">
-        <v>1.724</v>
+        <v>0.875</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>50.25</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,19 +2725,19 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46128.78125</v>
       </c>
       <c r="B77">
-        <v>1.525</v>
+        <v>0.447</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>6.309</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="B78">
-        <v>5.254</v>
+        <v>0.173</v>
       </c>
       <c r="C78">
-        <v>0.007</v>
+        <v>2.259</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>63.25</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46128.80208333334</v>
       </c>
       <c r="B79">
-        <v>24.538</v>
+        <v>4.727</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>68.25</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46128.8125</v>
       </c>
       <c r="B80">
-        <v>11.468</v>
+        <v>4.748</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46128.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.03</v>
+        <v>0.57</v>
       </c>
       <c r="C81">
-        <v>11.678</v>
+        <v>0.153</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46128.83333333334</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>10.973</v>
       </c>
       <c r="C82">
-        <v>2.138</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46128.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>12.906</v>
       </c>
       <c r="C83">
-        <v>3.107</v>
+        <v>0.01</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46128.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="C84">
-        <v>22.878</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46128.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.003</v>
+        <v>0.139</v>
       </c>
       <c r="C85">
-        <v>2.27</v>
+        <v>0.204</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46128.875</v>
       </c>
       <c r="B86">
-        <v>2.218</v>
+        <v>12.359</v>
       </c>
       <c r="C86">
-        <v>1.05</v>
+        <v>2.454</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46128.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.319</v>
+        <v>0.019</v>
       </c>
       <c r="C87">
-        <v>1.265</v>
+        <v>2.673</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46128.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>10.838</v>
+        <v>5.261</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46128.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>19.405</v>
+        <v>17.782</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46128.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>4.933</v>
+        <v>25.903</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46128.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>10.432</v>
+        <v>14.113</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46128.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>15.51</v>
+        <v>4.772</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46128.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C93">
-        <v>5.488</v>
+        <v>3.599</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46128.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.168</v>
+        <v>0.152</v>
       </c>
       <c r="C94">
-        <v>1.53</v>
+        <v>0.473</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46128.96875</v>
       </c>
       <c r="B95">
-        <v>0.671</v>
+        <v>0.047</v>
       </c>
       <c r="C95">
-        <v>0.004</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46128.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.193</v>
+        <v>0.024</v>
       </c>
       <c r="C96">
-        <v>0.475</v>
+        <v>3.623</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46128.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="C97">
-        <v>12.069</v>
+        <v>2.839</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B98">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>8.484999999999999</v>
+        <v>2.547</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B99">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>8.484999999999999</v>
+        <v>2.547</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B100">
-        <v>1.824</v>
+        <v>4.869</v>
       </c>
       <c r="C100">
-        <v>0.008999999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B101">
-        <v>1.824</v>
+        <v>4.869</v>
       </c>
       <c r="C101">
-        <v>0.008999999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B102">
-        <v>0.016</v>
+        <v>0.919</v>
       </c>
       <c r="C102">
-        <v>2.218</v>
+        <v>1.117</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B103">
-        <v>0.016</v>
+        <v>0.919</v>
       </c>
       <c r="C103">
-        <v>2.218</v>
+        <v>1.117</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B104">
-        <v>0.472</v>
+        <v>0.011</v>
       </c>
       <c r="C104">
-        <v>0.701</v>
+        <v>4.377</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B105">
-        <v>0.472</v>
+        <v>0.011</v>
       </c>
       <c r="C105">
-        <v>0.701</v>
+        <v>4.377</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B106">
-        <v>0.056</v>
+        <v>0.461</v>
       </c>
       <c r="C106">
-        <v>1.438</v>
+        <v>3.365</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B107">
-        <v>0.056</v>
+        <v>0.461</v>
       </c>
       <c r="C107">
-        <v>1.438</v>
+        <v>3.365</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B108">
-        <v>0.525</v>
+        <v>1.447</v>
       </c>
       <c r="C108">
-        <v>0.737</v>
+        <v>1.936</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B109">
-        <v>0.525</v>
+        <v>1.447</v>
       </c>
       <c r="C109">
-        <v>0.737</v>
+        <v>1.936</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B110">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0.13</v>
+        <v>5.393</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B111">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0.13</v>
+        <v>5.393</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B112">
-        <v>0.805</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0.414</v>
+        <v>20.985</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.805</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0.414</v>
+        <v>20.985</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46122.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114">
-        <v>5.388</v>
+        <v>5.158</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46122.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>2.271</v>
+        <v>26.602</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46122.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>1.018</v>
+        <v>18.896</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46122.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B117">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>1.776</v>
+        <v>13.726</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46122.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B118">
-        <v>8.598000000000001</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>0.926</v>
+        <v>2.865</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46122.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="C119">
-        <v>17.398</v>
+        <v>0.827</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46122.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>22.801</v>
+        <v>2.592</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46122.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="C121">
-        <v>29.586</v>
+        <v>0.101</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46122.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C122">
-        <v>18.203</v>
+        <v>5.349</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46122.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B123">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0.598</v>
+        <v>13.509</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46122.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="C124">
-        <v>8.108000000000001</v>
+        <v>5.026</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46122.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C125">
-        <v>1.439</v>
+        <v>1.453</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46122.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B126">
-        <v>1.286</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>2.229</v>
+        <v>13.293</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46122.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B127">
-        <v>10.623</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>11.561</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46122.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B128">
-        <v>1.18</v>
+        <v>0.03</v>
       </c>
       <c r="C128">
-        <v>0.08599999999999999</v>
+        <v>3.924</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46122.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B129">
-        <v>0.188</v>
+        <v>0.424</v>
       </c>
       <c r="C129">
-        <v>6.967</v>
+        <v>0.604</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46122.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B130">
-        <v>8.499000000000001</v>
+        <v>10.711</v>
       </c>
       <c r="C130">
-        <v>0.231</v>
+        <v>2.93</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46122.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B131">
-        <v>2.658</v>
+        <v>12.573</v>
       </c>
       <c r="C131">
-        <v>1.233</v>
+        <v>0.022</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,13 +3990,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46122.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="C132">
-        <v>7.66</v>
+        <v>1.727</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46122.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B133">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="C133">
-        <v>2.855</v>
+        <v>3.397</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46122.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.414</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>0.182</v>
+        <v>13.55</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46122.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.253</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>0.235</v>
+        <v>11.35</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46122.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B136">
-        <v>0.759</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0.046</v>
+        <v>14.828</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,13 +4105,13 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46122.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B137">
-        <v>0.148</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>0.785</v>
+        <v>10.305</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46122.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B138">
-        <v>10.5</v>
+        <v>0.015</v>
       </c>
       <c r="C138">
-        <v>0.011</v>
+        <v>7.132</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46122.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B139">
-        <v>13.593</v>
+        <v>1.56</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46122.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B140">
-        <v>6.856</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>0.015</v>
+        <v>29.332</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,13 +4197,13 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46122.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B141">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>5.753</v>
+        <v>43.822</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46122.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>7.162</v>
       </c>
       <c r="C142">
-        <v>8.324999999999999</v>
+        <v>5.128</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4243,13 +4243,13 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46122.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>1.589</v>
       </c>
       <c r="C143">
-        <v>5.322</v>
+        <v>5.948</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46122.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B144">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="C144">
-        <v>3.849</v>
+        <v>12.638</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4289,13 +4289,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46122.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>14.561</v>
+        <v>6.788</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,19 +4312,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46122.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B146">
-        <v>16.227</v>
+        <v>0.214</v>
       </c>
       <c r="C146">
-        <v>0.6820000000000001</v>
+        <v>6.271</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>41</v>
@@ -4335,19 +4335,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46122.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>11.018</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>42</v>
@@ -4358,13 +4358,13 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46122.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>10.383</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -4381,13 +4381,13 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46122.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>12.236</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4404,13 +4404,13 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46122.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>20.646</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4427,13 +4427,13 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46122.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>4.993</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4450,13 +4450,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46122.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>7.469</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4473,13 +4473,13 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46122.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>15.825</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4496,13 +4496,13 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46122.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>38.147</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4519,13 +4519,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46122.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>36.798</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4542,19 +4542,19 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46122.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>12.045</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F156">
         <v>51</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46122.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F157">
         <v>52</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46122.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46122.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46122.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46122.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46122.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46122.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46122.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46122.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46122.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46122.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46122.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46122.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46122.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46122.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46122.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46122.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46122.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46122.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46122.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46122.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46122.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46122.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46122.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46122.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46122.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46122.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46122.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46122.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46122.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46122.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46122.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46122.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46122.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46122.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46122.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46122.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46122.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46122.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46122.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46122.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46122.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46122.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46122.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46122.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="391">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.202624</t>
-  </si>
-  <si>
-    <t>16.04.202625</t>
-  </si>
-  <si>
-    <t>16.04.202626</t>
-  </si>
-  <si>
-    <t>16.04.202627</t>
-  </si>
-  <si>
-    <t>16.04.202628</t>
-  </si>
-  <si>
-    <t>16.04.202629</t>
-  </si>
-  <si>
-    <t>16.04.202630</t>
-  </si>
-  <si>
-    <t>16.04.202631</t>
-  </si>
-  <si>
-    <t>16.04.202632</t>
-  </si>
-  <si>
-    <t>16.04.202633</t>
-  </si>
-  <si>
-    <t>16.04.202634</t>
-  </si>
-  <si>
-    <t>16.04.202635</t>
-  </si>
-  <si>
-    <t>16.04.202636</t>
-  </si>
-  <si>
-    <t>16.04.202637</t>
-  </si>
-  <si>
-    <t>16.04.202638</t>
-  </si>
-  <si>
-    <t>16.04.202639</t>
-  </si>
-  <si>
-    <t>16.04.202640</t>
-  </si>
-  <si>
-    <t>16.04.202641</t>
-  </si>
-  <si>
-    <t>16.04.202642</t>
-  </si>
-  <si>
-    <t>16.04.202643</t>
-  </si>
-  <si>
-    <t>16.04.202644</t>
-  </si>
-  <si>
-    <t>16.04.202645</t>
-  </si>
-  <si>
-    <t>16.04.202646</t>
-  </si>
-  <si>
-    <t>16.04.202647</t>
-  </si>
-  <si>
-    <t>16.04.202648</t>
-  </si>
-  <si>
-    <t>16.04.202649</t>
-  </si>
-  <si>
-    <t>16.04.202650</t>
-  </si>
-  <si>
-    <t>16.04.202651</t>
-  </si>
-  <si>
-    <t>16.04.202652</t>
-  </si>
-  <si>
-    <t>16.04.202653</t>
-  </si>
-  <si>
-    <t>16.04.202654</t>
-  </si>
-  <si>
-    <t>16.04.202655</t>
-  </si>
-  <si>
-    <t>16.04.202656</t>
-  </si>
-  <si>
-    <t>16.04.202657</t>
-  </si>
-  <si>
-    <t>16.04.202658</t>
-  </si>
-  <si>
-    <t>16.04.202659</t>
-  </si>
-  <si>
-    <t>16.04.202660</t>
-  </si>
-  <si>
-    <t>16.04.202661</t>
-  </si>
-  <si>
-    <t>16.04.202662</t>
-  </si>
-  <si>
-    <t>16.04.202663</t>
-  </si>
-  <si>
-    <t>16.04.202664</t>
-  </si>
-  <si>
-    <t>16.04.202665</t>
-  </si>
-  <si>
-    <t>16.04.202666</t>
-  </si>
-  <si>
-    <t>16.04.202667</t>
-  </si>
-  <si>
-    <t>16.04.202668</t>
-  </si>
-  <si>
-    <t>16.04.202669</t>
-  </si>
-  <si>
-    <t>16.04.202670</t>
-  </si>
-  <si>
-    <t>16.04.202671</t>
-  </si>
-  <si>
-    <t>16.04.202672</t>
-  </si>
-  <si>
-    <t>16.04.202673</t>
-  </si>
-  <si>
-    <t>16.04.202674</t>
-  </si>
-  <si>
-    <t>16.04.202675</t>
-  </si>
-  <si>
-    <t>16.04.202676</t>
-  </si>
-  <si>
-    <t>16.04.202677</t>
-  </si>
-  <si>
-    <t>16.04.202678</t>
-  </si>
-  <si>
-    <t>16.04.202679</t>
-  </si>
-  <si>
-    <t>16.04.202680</t>
-  </si>
-  <si>
-    <t>16.04.202681</t>
-  </si>
-  <si>
-    <t>16.04.202682</t>
-  </si>
-  <si>
-    <t>16.04.202683</t>
-  </si>
-  <si>
-    <t>16.04.202684</t>
-  </si>
-  <si>
-    <t>16.04.202685</t>
-  </si>
-  <si>
-    <t>16.04.202686</t>
-  </si>
-  <si>
-    <t>16.04.202687</t>
-  </si>
-  <si>
-    <t>16.04.202688</t>
-  </si>
-  <si>
-    <t>16.04.202689</t>
-  </si>
-  <si>
-    <t>16.04.202690</t>
-  </si>
-  <si>
-    <t>16.04.202691</t>
-  </si>
-  <si>
-    <t>16.04.202692</t>
-  </si>
-  <si>
-    <t>16.04.202693</t>
-  </si>
-  <si>
-    <t>16.04.202694</t>
-  </si>
-  <si>
-    <t>16.04.202695</t>
-  </si>
-  <si>
-    <t>16.04.202696</t>
-  </si>
-  <si>
     <t>17.04.20261</t>
   </si>
   <si>
@@ -611,6 +323,870 @@
   </si>
   <si>
     <t>17.04.202696</t>
+  </si>
+  <si>
+    <t>18.04.20261</t>
+  </si>
+  <si>
+    <t>18.04.20262</t>
+  </si>
+  <si>
+    <t>18.04.20263</t>
+  </si>
+  <si>
+    <t>18.04.20264</t>
+  </si>
+  <si>
+    <t>18.04.20265</t>
+  </si>
+  <si>
+    <t>18.04.20266</t>
+  </si>
+  <si>
+    <t>18.04.20267</t>
+  </si>
+  <si>
+    <t>18.04.20268</t>
+  </si>
+  <si>
+    <t>18.04.20269</t>
+  </si>
+  <si>
+    <t>18.04.202610</t>
+  </si>
+  <si>
+    <t>18.04.202611</t>
+  </si>
+  <si>
+    <t>18.04.202612</t>
+  </si>
+  <si>
+    <t>18.04.202613</t>
+  </si>
+  <si>
+    <t>18.04.202614</t>
+  </si>
+  <si>
+    <t>18.04.202615</t>
+  </si>
+  <si>
+    <t>18.04.202616</t>
+  </si>
+  <si>
+    <t>18.04.202617</t>
+  </si>
+  <si>
+    <t>18.04.202618</t>
+  </si>
+  <si>
+    <t>18.04.202619</t>
+  </si>
+  <si>
+    <t>18.04.202620</t>
+  </si>
+  <si>
+    <t>18.04.202621</t>
+  </si>
+  <si>
+    <t>18.04.202622</t>
+  </si>
+  <si>
+    <t>18.04.202623</t>
+  </si>
+  <si>
+    <t>18.04.202624</t>
+  </si>
+  <si>
+    <t>18.04.202625</t>
+  </si>
+  <si>
+    <t>18.04.202626</t>
+  </si>
+  <si>
+    <t>18.04.202627</t>
+  </si>
+  <si>
+    <t>18.04.202628</t>
+  </si>
+  <si>
+    <t>18.04.202629</t>
+  </si>
+  <si>
+    <t>18.04.202630</t>
+  </si>
+  <si>
+    <t>18.04.202631</t>
+  </si>
+  <si>
+    <t>18.04.202632</t>
+  </si>
+  <si>
+    <t>18.04.202633</t>
+  </si>
+  <si>
+    <t>18.04.202634</t>
+  </si>
+  <si>
+    <t>18.04.202635</t>
+  </si>
+  <si>
+    <t>18.04.202636</t>
+  </si>
+  <si>
+    <t>18.04.202637</t>
+  </si>
+  <si>
+    <t>18.04.202638</t>
+  </si>
+  <si>
+    <t>18.04.202639</t>
+  </si>
+  <si>
+    <t>18.04.202640</t>
+  </si>
+  <si>
+    <t>18.04.202641</t>
+  </si>
+  <si>
+    <t>18.04.202642</t>
+  </si>
+  <si>
+    <t>18.04.202643</t>
+  </si>
+  <si>
+    <t>18.04.202644</t>
+  </si>
+  <si>
+    <t>18.04.202645</t>
+  </si>
+  <si>
+    <t>18.04.202646</t>
+  </si>
+  <si>
+    <t>18.04.202647</t>
+  </si>
+  <si>
+    <t>18.04.202648</t>
+  </si>
+  <si>
+    <t>18.04.202649</t>
+  </si>
+  <si>
+    <t>18.04.202650</t>
+  </si>
+  <si>
+    <t>18.04.202651</t>
+  </si>
+  <si>
+    <t>18.04.202652</t>
+  </si>
+  <si>
+    <t>18.04.202653</t>
+  </si>
+  <si>
+    <t>18.04.202654</t>
+  </si>
+  <si>
+    <t>18.04.202655</t>
+  </si>
+  <si>
+    <t>18.04.202656</t>
+  </si>
+  <si>
+    <t>18.04.202657</t>
+  </si>
+  <si>
+    <t>18.04.202658</t>
+  </si>
+  <si>
+    <t>18.04.202659</t>
+  </si>
+  <si>
+    <t>18.04.202660</t>
+  </si>
+  <si>
+    <t>18.04.202661</t>
+  </si>
+  <si>
+    <t>18.04.202662</t>
+  </si>
+  <si>
+    <t>18.04.202663</t>
+  </si>
+  <si>
+    <t>18.04.202664</t>
+  </si>
+  <si>
+    <t>18.04.202665</t>
+  </si>
+  <si>
+    <t>18.04.202666</t>
+  </si>
+  <si>
+    <t>18.04.202667</t>
+  </si>
+  <si>
+    <t>18.04.202668</t>
+  </si>
+  <si>
+    <t>18.04.202669</t>
+  </si>
+  <si>
+    <t>18.04.202670</t>
+  </si>
+  <si>
+    <t>18.04.202671</t>
+  </si>
+  <si>
+    <t>18.04.202672</t>
+  </si>
+  <si>
+    <t>18.04.202673</t>
+  </si>
+  <si>
+    <t>18.04.202674</t>
+  </si>
+  <si>
+    <t>18.04.202675</t>
+  </si>
+  <si>
+    <t>18.04.202676</t>
+  </si>
+  <si>
+    <t>18.04.202677</t>
+  </si>
+  <si>
+    <t>18.04.202678</t>
+  </si>
+  <si>
+    <t>18.04.202679</t>
+  </si>
+  <si>
+    <t>18.04.202680</t>
+  </si>
+  <si>
+    <t>18.04.202681</t>
+  </si>
+  <si>
+    <t>18.04.202682</t>
+  </si>
+  <si>
+    <t>18.04.202683</t>
+  </si>
+  <si>
+    <t>18.04.202684</t>
+  </si>
+  <si>
+    <t>18.04.202685</t>
+  </si>
+  <si>
+    <t>18.04.202686</t>
+  </si>
+  <si>
+    <t>18.04.202687</t>
+  </si>
+  <si>
+    <t>18.04.202688</t>
+  </si>
+  <si>
+    <t>18.04.202689</t>
+  </si>
+  <si>
+    <t>18.04.202690</t>
+  </si>
+  <si>
+    <t>18.04.202691</t>
+  </si>
+  <si>
+    <t>18.04.202692</t>
+  </si>
+  <si>
+    <t>18.04.202693</t>
+  </si>
+  <si>
+    <t>18.04.202694</t>
+  </si>
+  <si>
+    <t>18.04.202695</t>
+  </si>
+  <si>
+    <t>18.04.202696</t>
+  </si>
+  <si>
+    <t>19.04.20261</t>
+  </si>
+  <si>
+    <t>19.04.20262</t>
+  </si>
+  <si>
+    <t>19.04.20263</t>
+  </si>
+  <si>
+    <t>19.04.20264</t>
+  </si>
+  <si>
+    <t>19.04.20265</t>
+  </si>
+  <si>
+    <t>19.04.20266</t>
+  </si>
+  <si>
+    <t>19.04.20267</t>
+  </si>
+  <si>
+    <t>19.04.20268</t>
+  </si>
+  <si>
+    <t>19.04.20269</t>
+  </si>
+  <si>
+    <t>19.04.202610</t>
+  </si>
+  <si>
+    <t>19.04.202611</t>
+  </si>
+  <si>
+    <t>19.04.202612</t>
+  </si>
+  <si>
+    <t>19.04.202613</t>
+  </si>
+  <si>
+    <t>19.04.202614</t>
+  </si>
+  <si>
+    <t>19.04.202615</t>
+  </si>
+  <si>
+    <t>19.04.202616</t>
+  </si>
+  <si>
+    <t>19.04.202617</t>
+  </si>
+  <si>
+    <t>19.04.202618</t>
+  </si>
+  <si>
+    <t>19.04.202619</t>
+  </si>
+  <si>
+    <t>19.04.202620</t>
+  </si>
+  <si>
+    <t>19.04.202621</t>
+  </si>
+  <si>
+    <t>19.04.202622</t>
+  </si>
+  <si>
+    <t>19.04.202623</t>
+  </si>
+  <si>
+    <t>19.04.202624</t>
+  </si>
+  <si>
+    <t>19.04.202625</t>
+  </si>
+  <si>
+    <t>19.04.202626</t>
+  </si>
+  <si>
+    <t>19.04.202627</t>
+  </si>
+  <si>
+    <t>19.04.202628</t>
+  </si>
+  <si>
+    <t>19.04.202629</t>
+  </si>
+  <si>
+    <t>19.04.202630</t>
+  </si>
+  <si>
+    <t>19.04.202631</t>
+  </si>
+  <si>
+    <t>19.04.202632</t>
+  </si>
+  <si>
+    <t>19.04.202633</t>
+  </si>
+  <si>
+    <t>19.04.202634</t>
+  </si>
+  <si>
+    <t>19.04.202635</t>
+  </si>
+  <si>
+    <t>19.04.202636</t>
+  </si>
+  <si>
+    <t>19.04.202637</t>
+  </si>
+  <si>
+    <t>19.04.202638</t>
+  </si>
+  <si>
+    <t>19.04.202639</t>
+  </si>
+  <si>
+    <t>19.04.202640</t>
+  </si>
+  <si>
+    <t>19.04.202641</t>
+  </si>
+  <si>
+    <t>19.04.202642</t>
+  </si>
+  <si>
+    <t>19.04.202643</t>
+  </si>
+  <si>
+    <t>19.04.202644</t>
+  </si>
+  <si>
+    <t>19.04.202645</t>
+  </si>
+  <si>
+    <t>19.04.202646</t>
+  </si>
+  <si>
+    <t>19.04.202647</t>
+  </si>
+  <si>
+    <t>19.04.202648</t>
+  </si>
+  <si>
+    <t>19.04.202649</t>
+  </si>
+  <si>
+    <t>19.04.202650</t>
+  </si>
+  <si>
+    <t>19.04.202651</t>
+  </si>
+  <si>
+    <t>19.04.202652</t>
+  </si>
+  <si>
+    <t>19.04.202653</t>
+  </si>
+  <si>
+    <t>19.04.202654</t>
+  </si>
+  <si>
+    <t>19.04.202655</t>
+  </si>
+  <si>
+    <t>19.04.202656</t>
+  </si>
+  <si>
+    <t>19.04.202657</t>
+  </si>
+  <si>
+    <t>19.04.202658</t>
+  </si>
+  <si>
+    <t>19.04.202659</t>
+  </si>
+  <si>
+    <t>19.04.202660</t>
+  </si>
+  <si>
+    <t>19.04.202661</t>
+  </si>
+  <si>
+    <t>19.04.202662</t>
+  </si>
+  <si>
+    <t>19.04.202663</t>
+  </si>
+  <si>
+    <t>19.04.202664</t>
+  </si>
+  <si>
+    <t>19.04.202665</t>
+  </si>
+  <si>
+    <t>19.04.202666</t>
+  </si>
+  <si>
+    <t>19.04.202667</t>
+  </si>
+  <si>
+    <t>19.04.202668</t>
+  </si>
+  <si>
+    <t>19.04.202669</t>
+  </si>
+  <si>
+    <t>19.04.202670</t>
+  </si>
+  <si>
+    <t>19.04.202671</t>
+  </si>
+  <si>
+    <t>19.04.202672</t>
+  </si>
+  <si>
+    <t>19.04.202673</t>
+  </si>
+  <si>
+    <t>19.04.202674</t>
+  </si>
+  <si>
+    <t>19.04.202675</t>
+  </si>
+  <si>
+    <t>19.04.202676</t>
+  </si>
+  <si>
+    <t>19.04.202677</t>
+  </si>
+  <si>
+    <t>19.04.202678</t>
+  </si>
+  <si>
+    <t>19.04.202679</t>
+  </si>
+  <si>
+    <t>19.04.202680</t>
+  </si>
+  <si>
+    <t>19.04.202681</t>
+  </si>
+  <si>
+    <t>19.04.202682</t>
+  </si>
+  <si>
+    <t>19.04.202683</t>
+  </si>
+  <si>
+    <t>19.04.202684</t>
+  </si>
+  <si>
+    <t>19.04.202685</t>
+  </si>
+  <si>
+    <t>19.04.202686</t>
+  </si>
+  <si>
+    <t>19.04.202687</t>
+  </si>
+  <si>
+    <t>19.04.202688</t>
+  </si>
+  <si>
+    <t>19.04.202689</t>
+  </si>
+  <si>
+    <t>19.04.202690</t>
+  </si>
+  <si>
+    <t>19.04.202691</t>
+  </si>
+  <si>
+    <t>19.04.202692</t>
+  </si>
+  <si>
+    <t>19.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202694</t>
+  </si>
+  <si>
+    <t>19.04.202695</t>
+  </si>
+  <si>
+    <t>19.04.202696</t>
+  </si>
+  <si>
+    <t>20.04.20261</t>
+  </si>
+  <si>
+    <t>20.04.20262</t>
+  </si>
+  <si>
+    <t>20.04.20263</t>
+  </si>
+  <si>
+    <t>20.04.20264</t>
+  </si>
+  <si>
+    <t>20.04.20265</t>
+  </si>
+  <si>
+    <t>20.04.20266</t>
+  </si>
+  <si>
+    <t>20.04.20267</t>
+  </si>
+  <si>
+    <t>20.04.20268</t>
+  </si>
+  <si>
+    <t>20.04.20269</t>
+  </si>
+  <si>
+    <t>20.04.202610</t>
+  </si>
+  <si>
+    <t>20.04.202611</t>
+  </si>
+  <si>
+    <t>20.04.202612</t>
+  </si>
+  <si>
+    <t>20.04.202613</t>
+  </si>
+  <si>
+    <t>20.04.202614</t>
+  </si>
+  <si>
+    <t>20.04.202615</t>
+  </si>
+  <si>
+    <t>20.04.202616</t>
+  </si>
+  <si>
+    <t>20.04.202617</t>
+  </si>
+  <si>
+    <t>20.04.202618</t>
+  </si>
+  <si>
+    <t>20.04.202619</t>
+  </si>
+  <si>
+    <t>20.04.202620</t>
+  </si>
+  <si>
+    <t>20.04.202621</t>
+  </si>
+  <si>
+    <t>20.04.202622</t>
+  </si>
+  <si>
+    <t>20.04.202623</t>
+  </si>
+  <si>
+    <t>20.04.202624</t>
+  </si>
+  <si>
+    <t>20.04.202625</t>
+  </si>
+  <si>
+    <t>20.04.202626</t>
+  </si>
+  <si>
+    <t>20.04.202627</t>
+  </si>
+  <si>
+    <t>20.04.202628</t>
+  </si>
+  <si>
+    <t>20.04.202629</t>
+  </si>
+  <si>
+    <t>20.04.202630</t>
+  </si>
+  <si>
+    <t>20.04.202631</t>
+  </si>
+  <si>
+    <t>20.04.202632</t>
+  </si>
+  <si>
+    <t>20.04.202633</t>
+  </si>
+  <si>
+    <t>20.04.202634</t>
+  </si>
+  <si>
+    <t>20.04.202635</t>
+  </si>
+  <si>
+    <t>20.04.202636</t>
+  </si>
+  <si>
+    <t>20.04.202637</t>
+  </si>
+  <si>
+    <t>20.04.202638</t>
+  </si>
+  <si>
+    <t>20.04.202639</t>
+  </si>
+  <si>
+    <t>20.04.202640</t>
+  </si>
+  <si>
+    <t>20.04.202641</t>
+  </si>
+  <si>
+    <t>20.04.202642</t>
+  </si>
+  <si>
+    <t>20.04.202643</t>
+  </si>
+  <si>
+    <t>20.04.202644</t>
+  </si>
+  <si>
+    <t>20.04.202645</t>
+  </si>
+  <si>
+    <t>20.04.202646</t>
+  </si>
+  <si>
+    <t>20.04.202647</t>
+  </si>
+  <si>
+    <t>20.04.202648</t>
+  </si>
+  <si>
+    <t>20.04.202649</t>
+  </si>
+  <si>
+    <t>20.04.202650</t>
+  </si>
+  <si>
+    <t>20.04.202651</t>
+  </si>
+  <si>
+    <t>20.04.202652</t>
+  </si>
+  <si>
+    <t>20.04.202653</t>
+  </si>
+  <si>
+    <t>20.04.202654</t>
+  </si>
+  <si>
+    <t>20.04.202655</t>
+  </si>
+  <si>
+    <t>20.04.202656</t>
+  </si>
+  <si>
+    <t>20.04.202657</t>
+  </si>
+  <si>
+    <t>20.04.202658</t>
+  </si>
+  <si>
+    <t>20.04.202659</t>
+  </si>
+  <si>
+    <t>20.04.202660</t>
+  </si>
+  <si>
+    <t>20.04.202661</t>
+  </si>
+  <si>
+    <t>20.04.202662</t>
+  </si>
+  <si>
+    <t>20.04.202663</t>
+  </si>
+  <si>
+    <t>20.04.202664</t>
+  </si>
+  <si>
+    <t>20.04.202665</t>
+  </si>
+  <si>
+    <t>20.04.202666</t>
+  </si>
+  <si>
+    <t>20.04.202667</t>
+  </si>
+  <si>
+    <t>20.04.202668</t>
+  </si>
+  <si>
+    <t>20.04.202669</t>
+  </si>
+  <si>
+    <t>20.04.202670</t>
+  </si>
+  <si>
+    <t>20.04.202671</t>
+  </si>
+  <si>
+    <t>20.04.202672</t>
+  </si>
+  <si>
+    <t>20.04.202673</t>
+  </si>
+  <si>
+    <t>20.04.202674</t>
+  </si>
+  <si>
+    <t>20.04.202675</t>
+  </si>
+  <si>
+    <t>20.04.202676</t>
+  </si>
+  <si>
+    <t>20.04.202677</t>
+  </si>
+  <si>
+    <t>20.04.202678</t>
+  </si>
+  <si>
+    <t>20.04.202679</t>
+  </si>
+  <si>
+    <t>20.04.202680</t>
+  </si>
+  <si>
+    <t>20.04.202681</t>
+  </si>
+  <si>
+    <t>20.04.202682</t>
+  </si>
+  <si>
+    <t>20.04.202683</t>
+  </si>
+  <si>
+    <t>20.04.202684</t>
+  </si>
+  <si>
+    <t>20.04.202685</t>
+  </si>
+  <si>
+    <t>20.04.202686</t>
+  </si>
+  <si>
+    <t>20.04.202687</t>
+  </si>
+  <si>
+    <t>20.04.202688</t>
+  </si>
+  <si>
+    <t>20.04.202689</t>
+  </si>
+  <si>
+    <t>20.04.202690</t>
+  </si>
+  <si>
+    <t>20.04.202691</t>
+  </si>
+  <si>
+    <t>20.04.202692</t>
+  </si>
+  <si>
+    <t>20.04.202693</t>
+  </si>
+  <si>
+    <t>20.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202695</t>
+  </si>
+  <si>
+    <t>20.04.202696</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G409"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1000,13 +1576,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>40.469</v>
+        <v>2.547</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1599,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46128.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>4.869</v>
       </c>
       <c r="C3">
-        <v>27.606</v>
+        <v>0.021</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1622,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46128.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.919</v>
       </c>
       <c r="C4">
-        <v>32.229</v>
+        <v>1.117</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1645,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46128.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C5">
-        <v>31.849</v>
+        <v>4.377</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1668,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46128.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.461</v>
       </c>
       <c r="C6">
-        <v>37.673</v>
+        <v>3.365</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1691,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46128.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1.447</v>
       </c>
       <c r="C7">
-        <v>30.832</v>
+        <v>1.936</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1714,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46128.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>36.19</v>
+        <v>5.393</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1737,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46128.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>28.395</v>
+        <v>20.985</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1760,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46128.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>17.273</v>
+        <v>5.158</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1783,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46128.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>12.97</v>
+        <v>26.602</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1806,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46128.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>29.278</v>
+        <v>18.896</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1829,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46128.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>20.66</v>
+        <v>13.726</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1852,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46128.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>20.511</v>
+        <v>2.865</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1875,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46128.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="C15">
-        <v>6.597</v>
+        <v>0.827</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1898,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46128.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>14.93</v>
+        <v>2.592</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1921,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46128.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="C17">
-        <v>5.623</v>
+        <v>0.101</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1944,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46128.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C18">
-        <v>8.531000000000001</v>
+        <v>5.349</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1967,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46128.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>3.548</v>
+        <v>13.509</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1990,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46128.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="C20">
-        <v>19.942</v>
+        <v>5.026</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +2013,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46128.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C21">
-        <v>9.683</v>
+        <v>1.453</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +2036,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46128.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>20.202</v>
+        <v>13.293</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +2059,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46128.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>1.376</v>
+        <v>11.561</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +2082,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46128.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C24">
-        <v>2.61</v>
+        <v>3.924</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +2105,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46128.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.833</v>
+        <v>0.424</v>
       </c>
       <c r="C25">
-        <v>8.311999999999999</v>
+        <v>0.604</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +2128,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46128.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>0.388</v>
+        <v>10.711</v>
       </c>
       <c r="C26">
-        <v>5.244</v>
+        <v>2.93</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +2151,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46128.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.004</v>
+        <v>12.573</v>
       </c>
       <c r="C27">
-        <v>2.746</v>
+        <v>0.022</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,13 +2174,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46128.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="C28">
-        <v>25.261</v>
+        <v>1.727</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +2197,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46128.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C29">
-        <v>44.245</v>
+        <v>3.397</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +2220,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46128.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>21.512</v>
+        <v>13.55</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,13 +2243,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46128.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>9.317</v>
+        <v>11.35</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1690,19 +2266,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46128.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>3.612</v>
+        <v>14.828</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>39.25</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +2289,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46128.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>10.224</v>
+        <v>10.305</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>39.25</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +2312,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46128.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>17.335</v>
+        <v>0.015</v>
       </c>
       <c r="C34">
-        <v>0.531</v>
+        <v>7.132</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +2335,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46128.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>4.802</v>
+        <v>1.56</v>
       </c>
       <c r="C35">
-        <v>0.043</v>
+        <v>3.22</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +2358,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46128.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>8.791</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.002</v>
+        <v>29.332</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +2381,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46128.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>6.233</v>
+        <v>43.822</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +2404,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46128.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>0.514</v>
+        <v>7.162</v>
       </c>
       <c r="C38">
-        <v>3.218</v>
+        <v>5.128</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +2427,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46128.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1.589</v>
       </c>
       <c r="C39">
-        <v>2.598</v>
+        <v>5.948</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +2450,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46128.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>11.399</v>
+        <v>12.638</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +2473,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46128.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>45.62</v>
+        <v>6.788</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +2496,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46128.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>4.673</v>
+        <v>0.214</v>
       </c>
       <c r="C42">
-        <v>5.18</v>
+        <v>6.271</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +2519,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46128.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.768</v>
+        <v>11.018</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>70.5</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +2542,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46128.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>4.379</v>
+        <v>10.383</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +2565,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46128.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>35.847</v>
+        <v>12.236</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2588,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46128.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>36.689</v>
+        <v>20.646</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>82.5</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2611,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46128.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C47">
-        <v>35.741</v>
+        <v>4.993</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>84.75</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2634,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46128.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C48">
-        <v>18.838</v>
+        <v>7.469</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2657,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46128.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>6.561</v>
+        <v>15.825</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2680,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46128.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0.24</v>
+        <v>38.147</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2703,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46128.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>5.134</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>0.015</v>
+        <v>36.798</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2726,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46128.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>1.438</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0.949</v>
+        <v>12.045</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2749,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46128.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0.801</v>
+        <v>15.588</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2772,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46128.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.57</v>
+        <v>0.012</v>
       </c>
       <c r="C54">
-        <v>0.022</v>
+        <v>1.88</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2795,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46128.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.135</v>
+        <v>0.014</v>
       </c>
       <c r="C55">
-        <v>3.594</v>
+        <v>0.901</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2818,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46128.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>2.211</v>
+        <v>0.038</v>
       </c>
       <c r="C56">
-        <v>1.07</v>
+        <v>21.578</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2841,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46128.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.718</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0.023</v>
+        <v>31.759</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>51</v>
+        <v>37.5</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2864,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46128.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>13.174</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>0.075</v>
+        <v>27.32</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>51</v>
+        <v>37.5</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,13 +2887,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46128.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>17.003</v>
+        <v>2.32</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2910,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46128.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>5.995</v>
+        <v>0.633</v>
       </c>
       <c r="C60">
-        <v>0.026</v>
+        <v>0.3</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,19 +2933,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46128.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.041</v>
+        <v>1.779</v>
       </c>
       <c r="C61">
-        <v>17.273</v>
+        <v>1.624</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2956,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46128.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C62">
-        <v>25.714</v>
+        <v>12.032</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2979,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46128.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="C63">
-        <v>2.006</v>
+        <v>6.733</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +3002,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46128.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="C64">
-        <v>7.292</v>
+        <v>1.665</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +3025,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46128.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>0.023</v>
+        <v>5.015</v>
       </c>
       <c r="C65">
-        <v>1.279</v>
+        <v>0.124</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +3048,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46128.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>8.882999999999999</v>
       </c>
       <c r="C66">
-        <v>26.015</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +3071,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46128.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.367</v>
+        <v>24.155</v>
       </c>
       <c r="C67">
-        <v>0.482</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +3094,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46128.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>1.123</v>
+        <v>12.843</v>
       </c>
       <c r="C68">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +3117,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46128.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>0.827</v>
+        <v>13.099</v>
       </c>
       <c r="C69">
-        <v>1.668</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,13 +3140,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46128.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="C70">
-        <v>6.509</v>
+        <v>0.096</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,13 +3163,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46128.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>0.26</v>
+        <v>4.637</v>
       </c>
       <c r="C71">
-        <v>10.138</v>
+        <v>0.119</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,13 +3186,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46128.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.876</v>
+        <v>14.384</v>
       </c>
       <c r="C72">
-        <v>0.223</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,13 +3209,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46128.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>16.281</v>
+        <v>0.98</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>11.323</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,13 +3232,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46128.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>1.501</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>10.046</v>
+        <v>16.156</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,13 +3255,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46128.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>6.034</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>2.513</v>
+        <v>12.683</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2702,13 +3278,13 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46128.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.493</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>0.875</v>
+        <v>6.097</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2725,13 +3301,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46128.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>0.447</v>
+        <v>0.045</v>
       </c>
       <c r="C77">
-        <v>6.309</v>
+        <v>1.327</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2748,13 +3324,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46128.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.173</v>
+        <v>0.001</v>
       </c>
       <c r="C78">
-        <v>2.259</v>
+        <v>40.914</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2771,13 +3347,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46128.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>4.727</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0.057</v>
+        <v>17.488</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2794,13 +3370,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46128.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>4.748</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>0.032</v>
+        <v>11.631</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +3393,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46128.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.57</v>
+        <v>0.033</v>
       </c>
       <c r="C81">
-        <v>0.153</v>
+        <v>0.529</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +3416,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46128.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>10.973</v>
+        <v>0.015</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>17.353</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +3439,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46128.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>12.906</v>
+        <v>0.062</v>
       </c>
       <c r="C83">
-        <v>0.01</v>
+        <v>2.245</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +3462,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46128.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.382</v>
+        <v>1.735</v>
       </c>
       <c r="C84">
-        <v>0.08799999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +3485,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46128.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.139</v>
+        <v>4.277</v>
       </c>
       <c r="C85">
-        <v>0.204</v>
+        <v>3.513</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +3508,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46128.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>12.359</v>
+        <v>2.944</v>
       </c>
       <c r="C86">
-        <v>2.454</v>
+        <v>0.409</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +3531,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46128.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.019</v>
+        <v>10.916</v>
       </c>
       <c r="C87">
-        <v>2.673</v>
+        <v>0.008</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +3554,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46128.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="C88">
-        <v>5.261</v>
+        <v>3.523</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3577,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46128.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C89">
-        <v>17.782</v>
+        <v>4.287</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3600,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46128.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1.755</v>
       </c>
       <c r="C90">
-        <v>25.903</v>
+        <v>0.288</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3623,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46128.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>5.575</v>
       </c>
       <c r="C91">
-        <v>14.113</v>
+        <v>0.109</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3646,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46128.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>2.395</v>
       </c>
       <c r="C92">
-        <v>4.772</v>
+        <v>0.754</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3669,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46128.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="C93">
-        <v>3.599</v>
+        <v>1.149</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3692,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46128.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.152</v>
+        <v>1.828</v>
       </c>
       <c r="C94">
-        <v>0.473</v>
+        <v>1.682</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3715,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46128.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
-        <v>0.047</v>
+        <v>0.84</v>
       </c>
       <c r="C95">
-        <v>0.5679999999999999</v>
+        <v>0.216</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3738,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46128.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.024</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C96">
-        <v>3.623</v>
+        <v>0.393</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3761,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46128.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.063</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C97">
-        <v>2.839</v>
+        <v>4.954</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3784,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="C98">
-        <v>2.547</v>
+        <v>3.032</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3807,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="C99">
-        <v>2.547</v>
+        <v>3.032</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3830,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B100">
-        <v>4.869</v>
+        <v>1.502</v>
       </c>
       <c r="C100">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3853,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B101">
-        <v>4.869</v>
+        <v>1.502</v>
       </c>
       <c r="C101">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B102">
-        <v>0.919</v>
+        <v>11.083</v>
       </c>
       <c r="C102">
-        <v>1.117</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3899,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B103">
-        <v>0.919</v>
+        <v>11.083</v>
       </c>
       <c r="C103">
-        <v>1.117</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3922,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B104">
-        <v>0.011</v>
+        <v>3.237</v>
       </c>
       <c r="C104">
-        <v>4.377</v>
+        <v>0.008</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3945,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B105">
-        <v>0.011</v>
+        <v>3.237</v>
       </c>
       <c r="C105">
-        <v>4.377</v>
+        <v>0.008</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3968,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B106">
-        <v>0.461</v>
+        <v>8.506</v>
       </c>
       <c r="C106">
-        <v>3.365</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3991,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B107">
-        <v>0.461</v>
+        <v>8.506</v>
       </c>
       <c r="C107">
-        <v>3.365</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +4014,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B108">
-        <v>1.447</v>
+        <v>3.052</v>
       </c>
       <c r="C108">
-        <v>1.936</v>
+        <v>0.27</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +4037,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B109">
-        <v>1.447</v>
+        <v>3.052</v>
       </c>
       <c r="C109">
-        <v>1.936</v>
+        <v>0.27</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +4060,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>4.527</v>
       </c>
       <c r="C110">
-        <v>5.393</v>
+        <v>0.079</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +4083,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>4.527</v>
       </c>
       <c r="C111">
-        <v>5.393</v>
+        <v>0.079</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +4106,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="C112">
-        <v>20.985</v>
+        <v>2.744</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +4129,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="C113">
-        <v>20.985</v>
+        <v>2.744</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +4152,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46129.08333333334</v>
+        <v>46130.08333333334</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="C114">
-        <v>5.158</v>
+        <v>1.474</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +4175,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46129.09375</v>
+        <v>46130.09375</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="C115">
-        <v>26.602</v>
+        <v>1.212</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +4198,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46129.10416666666</v>
+        <v>46130.10416666666</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C116">
-        <v>18.896</v>
+        <v>1.397</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +4221,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46129.11458333334</v>
+        <v>46130.11458333334</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>13.726</v>
+        <v>9.347</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +4244,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46129.125</v>
+        <v>46130.125</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118">
-        <v>2.865</v>
+        <v>10.511</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46129.13541666666</v>
+        <v>46130.13541666666</v>
       </c>
       <c r="B119">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>0.827</v>
+        <v>12.171</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +4290,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46129.14583333334</v>
+        <v>46130.14583333334</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>2.592</v>
+        <v>1.235</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +4313,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46129.15625</v>
+        <v>46130.15625</v>
       </c>
       <c r="B121">
-        <v>0.142</v>
+        <v>0.103</v>
       </c>
       <c r="C121">
-        <v>0.101</v>
+        <v>3.252</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +4336,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46129.16666666666</v>
+        <v>46130.16666666666</v>
       </c>
       <c r="B122">
-        <v>0.001</v>
+        <v>8.048</v>
       </c>
       <c r="C122">
-        <v>5.349</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +4359,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46129.17708333334</v>
+        <v>46130.17708333334</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>14.469</v>
       </c>
       <c r="C123">
-        <v>13.509</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +4382,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46129.1875</v>
+        <v>46130.1875</v>
       </c>
       <c r="B124">
-        <v>0.055</v>
+        <v>50.856</v>
       </c>
       <c r="C124">
-        <v>5.026</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +4405,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46129.19791666666</v>
+        <v>46130.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.08500000000000001</v>
+        <v>68.102</v>
       </c>
       <c r="C125">
-        <v>1.453</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,16 +4428,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46129.20833333334</v>
+        <v>46130.20833333334</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>84.056</v>
       </c>
       <c r="C126">
-        <v>13.293</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +4451,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46129.21875</v>
+        <v>46130.21875</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>4.551</v>
       </c>
       <c r="C127">
-        <v>11.561</v>
+        <v>6.759</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +4474,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46129.22916666666</v>
+        <v>46130.22916666666</v>
       </c>
       <c r="B128">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>3.924</v>
+        <v>9.672000000000001</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,16 +4497,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46129.23958333334</v>
+        <v>46130.23958333334</v>
       </c>
       <c r="B129">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>0.604</v>
+        <v>9.167</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3944,16 +4520,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46129.25</v>
+        <v>46130.25</v>
       </c>
       <c r="B130">
-        <v>10.711</v>
+        <v>0.207</v>
       </c>
       <c r="C130">
-        <v>2.93</v>
+        <v>0.273</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -3967,16 +4543,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46129.26041666666</v>
+        <v>46130.26041666666</v>
       </c>
       <c r="B131">
-        <v>12.573</v>
+        <v>2.573</v>
       </c>
       <c r="C131">
-        <v>0.022</v>
+        <v>0.914</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -3990,16 +4566,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46129.27083333334</v>
+        <v>46130.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.079</v>
+        <v>42.876</v>
       </c>
       <c r="C132">
-        <v>1.727</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4589,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46129.28125</v>
+        <v>46130.28125</v>
       </c>
       <c r="B133">
-        <v>0.004</v>
+        <v>38.795</v>
       </c>
       <c r="C133">
-        <v>3.397</v>
+        <v>0.002</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,13 +4612,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46129.29166666666</v>
+        <v>46130.29166666666</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>9.923999999999999</v>
       </c>
       <c r="C134">
-        <v>13.55</v>
+        <v>0.056</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,16 +4635,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46129.30208333334</v>
+        <v>46130.30208333334</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>13.436</v>
       </c>
       <c r="C135">
-        <v>11.35</v>
+        <v>0.033</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,16 +4658,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46129.3125</v>
+        <v>46130.3125</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C136">
-        <v>14.828</v>
+        <v>5.914</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4105,16 +4681,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46129.32291666666</v>
+        <v>46130.32291666666</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="C137">
-        <v>10.305</v>
+        <v>6.268</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>87.25</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4128,16 +4704,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46129.33333333334</v>
+        <v>46130.33333333334</v>
       </c>
       <c r="B138">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>7.132</v>
+        <v>6.487</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4151,16 +4727,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46129.34375</v>
+        <v>46130.34375</v>
       </c>
       <c r="B139">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>3.22</v>
+        <v>42.252</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46129.35416666666</v>
+        <v>46130.35416666666</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>29.332</v>
+        <v>22.283</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4197,16 +4773,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46129.36458333334</v>
+        <v>46130.36458333334</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>9.584</v>
       </c>
       <c r="C141">
-        <v>43.822</v>
+        <v>2.938</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>32.25</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4220,16 +4796,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46129.375</v>
+        <v>46130.375</v>
       </c>
       <c r="B142">
-        <v>7.162</v>
+        <v>2.367</v>
       </c>
       <c r="C142">
-        <v>5.128</v>
+        <v>4.074</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4243,16 +4819,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46129.38541666666</v>
+        <v>46130.38541666666</v>
       </c>
       <c r="B143">
-        <v>1.589</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>5.948</v>
+        <v>30.724</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4266,13 +4842,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46129.39583333334</v>
+        <v>46130.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>12.638</v>
+        <v>50.95</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4289,13 +4865,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46129.40625</v>
+        <v>46130.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>6.788</v>
+        <v>66.36</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,19 +4888,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46129.41666666666</v>
+        <v>46130.41666666666</v>
       </c>
       <c r="B146">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>6.271</v>
+        <v>19.56</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F146">
         <v>41</v>
@@ -4335,19 +4911,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46129.42708333334</v>
+        <v>46130.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>11.018</v>
+        <v>35.821</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F147">
         <v>42</v>
@@ -4358,19 +4934,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46129.4375</v>
+        <v>46130.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>10.383</v>
+        <v>31.247</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F148">
         <v>43</v>
@@ -4381,19 +4957,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46129.44791666666</v>
+        <v>46130.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>12.236</v>
+        <v>17.168</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F149">
         <v>44</v>
@@ -4404,19 +4980,19 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46129.45833333334</v>
+        <v>46130.45833333334</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C150">
-        <v>20.646</v>
+        <v>5.783</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F150">
         <v>45</v>
@@ -4427,19 +5003,19 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46129.46875</v>
+        <v>46130.46875</v>
       </c>
       <c r="B151">
-        <v>0.008999999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="C151">
-        <v>4.993</v>
+        <v>4.069</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F151">
         <v>46</v>
@@ -4450,19 +5026,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46129.47916666666</v>
+        <v>46130.47916666666</v>
       </c>
       <c r="B152">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>7.469</v>
+        <v>24.972</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F152">
         <v>47</v>
@@ -4473,19 +5049,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46129.48958333334</v>
+        <v>46130.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>15.825</v>
+        <v>28.168</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F153">
         <v>48</v>
@@ -4496,19 +5072,19 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46129.5</v>
+        <v>46130.5</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="C154">
-        <v>38.147</v>
+        <v>1.991</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -4519,19 +5095,19 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46129.51041666666</v>
+        <v>46130.51041666666</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="C155">
-        <v>36.798</v>
+        <v>0.5</v>
       </c>
       <c r="D155">
         <v>0</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F155">
         <v>50</v>
@@ -4542,19 +5118,19 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46129.52083333334</v>
+        <v>46130.52083333334</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="C156">
-        <v>12.045</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F156">
         <v>51</v>
@@ -4565,19 +5141,19 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46129.53125</v>
+        <v>46130.53125</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>20</v>
+        <v>62.5</v>
       </c>
       <c r="F157">
         <v>52</v>
@@ -4588,19 +5164,19 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46129.54166666666</v>
+        <v>46130.54166666666</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F158">
         <v>53</v>
@@ -4611,19 +5187,19 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46129.55208333334</v>
+        <v>46130.55208333334</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>3.188</v>
       </c>
       <c r="D159">
         <v>0</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F159">
         <v>54</v>
@@ -4634,19 +5210,19 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46129.5625</v>
+        <v>46130.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>14.819</v>
       </c>
       <c r="D160">
         <v>0</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F160">
         <v>55</v>
@@ -4657,19 +5233,19 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46129.57291666666</v>
+        <v>46130.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>4.869</v>
       </c>
       <c r="D161">
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F161">
         <v>56</v>
@@ -4680,19 +5256,19 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46129.58333333334</v>
+        <v>46130.58333333334</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>2.586</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F162">
         <v>57</v>
@@ -4703,10 +5279,10 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46129.59375</v>
+        <v>46130.59375</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>6.016</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -4715,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F163">
         <v>58</v>
@@ -4726,10 +5302,10 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46129.60416666666</v>
+        <v>46130.60416666666</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>9.845000000000001</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -4738,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F164">
         <v>59</v>
@@ -4749,10 +5325,10 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46129.61458333334</v>
+        <v>46130.61458333334</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>14.629</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -4761,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F165">
         <v>60</v>
@@ -4772,19 +5348,19 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46129.625</v>
+        <v>46130.625</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>1.746</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="D166">
         <v>0</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F166">
         <v>61</v>
@@ -4795,19 +5371,19 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46129.63541666666</v>
+        <v>46130.63541666666</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>21.17</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D167">
         <v>0</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F167">
         <v>62</v>
@@ -4818,10 +5394,10 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46129.64583333334</v>
+        <v>46130.64583333334</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>48.159</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -4841,10 +5417,10 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46129.65625</v>
+        <v>46130.65625</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>18.517</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -4864,13 +5440,13 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46129.66666666666</v>
+        <v>46130.66666666666</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -4887,13 +5463,13 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46129.67708333334</v>
+        <v>46130.67708333334</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>7.348</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -4910,13 +5486,13 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46129.6875</v>
+        <v>46130.6875</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>14.238</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -4933,10 +5509,10 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46129.69791666666</v>
+        <v>46130.69791666666</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>14.128</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -4956,13 +5532,13 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46129.70833333334</v>
+        <v>46130.70833333334</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>28.158</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -4979,13 +5555,13 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46129.71875</v>
+        <v>46130.71875</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>1.961</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>13.852</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -5002,13 +5578,13 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46129.72916666666</v>
+        <v>46130.72916666666</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>8.358000000000001</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -5025,13 +5601,13 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46129.73958333334</v>
+        <v>46130.73958333334</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>0.753</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5048,13 +5624,13 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46129.75</v>
+        <v>46130.75</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>0.606</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -5071,13 +5647,13 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46129.76041666666</v>
+        <v>46130.76041666666</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1.986</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -5094,13 +5670,13 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46129.77083333334</v>
+        <v>46130.77083333334</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>2.088</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -5117,13 +5693,13 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46129.78125</v>
+        <v>46130.78125</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>6.029</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -5140,13 +5716,13 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46129.79166666666</v>
+        <v>46130.79166666666</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>3.284</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5163,13 +5739,13 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46129.80208333334</v>
+        <v>46130.80208333334</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>5.184</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5186,13 +5762,13 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46129.8125</v>
+        <v>46130.8125</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>3.436</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5209,10 +5785,10 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46129.82291666666</v>
+        <v>46130.82291666666</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>3.185</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -5232,10 +5808,10 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46129.83333333334</v>
+        <v>46130.83333333334</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>15.651</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -5255,13 +5831,13 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46129.84375</v>
+        <v>46130.84375</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>31.041</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -5278,10 +5854,10 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46129.85416666666</v>
+        <v>46130.85416666666</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>47.338</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -5301,10 +5877,10 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46129.86458333334</v>
+        <v>46130.86458333334</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>38.521</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -5324,13 +5900,13 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46129.875</v>
+        <v>46130.875</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>18.724</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -5347,16 +5923,16 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46129.88541666666</v>
+        <v>46130.88541666666</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>10.304</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -5370,16 +5946,16 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46129.89583333334</v>
+        <v>46130.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>14.938</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -5393,13 +5969,13 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46129.90625</v>
+        <v>46130.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>8.007</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -5416,13 +5992,13 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46129.91666666666</v>
+        <v>46130.91666666666</v>
       </c>
       <c r="B194">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -5439,10 +6015,10 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46129.92708333334</v>
+        <v>46130.92708333334</v>
       </c>
       <c r="B195">
-        <v>0</v>
+        <v>5.715</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -5462,13 +6038,13 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46129.9375</v>
+        <v>46130.9375</v>
       </c>
       <c r="B196">
-        <v>0</v>
+        <v>8.535</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -5485,13 +6061,13 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46129.94791666666</v>
+        <v>46130.94791666666</v>
       </c>
       <c r="B197">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -5508,13 +6084,13 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46129.95833333334</v>
+        <v>46130.95833333334</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -5531,13 +6107,13 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46129.96875</v>
+        <v>46130.96875</v>
       </c>
       <c r="B199">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -5554,13 +6130,13 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46129.97916666666</v>
+        <v>46130.97916666666</v>
       </c>
       <c r="B200">
-        <v>0</v>
+        <v>1.661</v>
       </c>
       <c r="C200">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -5577,13 +6153,13 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46129.98958333334</v>
+        <v>46130.98958333334</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>4.582</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -5596,6 +6172,4790 @@
       </c>
       <c r="G201" t="s">
         <v>198</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B202">
+        <v>5.046</v>
+      </c>
+      <c r="C202">
+        <v>0.041</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B203">
+        <v>5.046</v>
+      </c>
+      <c r="C203">
+        <v>0.041</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B204">
+        <v>2.99</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>2</v>
+      </c>
+      <c r="G204" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B205">
+        <v>2.99</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>2</v>
+      </c>
+      <c r="G205" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B206">
+        <v>10.363</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>3</v>
+      </c>
+      <c r="G206" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B207">
+        <v>10.363</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>3</v>
+      </c>
+      <c r="G207" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B208">
+        <v>1.646</v>
+      </c>
+      <c r="C208">
+        <v>0.732</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>4</v>
+      </c>
+      <c r="G208" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B209">
+        <v>1.646</v>
+      </c>
+      <c r="C209">
+        <v>0.732</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>4</v>
+      </c>
+      <c r="G209" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>3.822</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>5</v>
+      </c>
+      <c r="G210" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>3.822</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>5</v>
+      </c>
+      <c r="G211" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B212">
+        <v>1.042</v>
+      </c>
+      <c r="C212">
+        <v>0.337</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="F212">
+        <v>6</v>
+      </c>
+      <c r="G212" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B213">
+        <v>1.042</v>
+      </c>
+      <c r="C213">
+        <v>0.337</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>6</v>
+      </c>
+      <c r="G213" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B214">
+        <v>0.046</v>
+      </c>
+      <c r="C214">
+        <v>7.717</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>7</v>
+      </c>
+      <c r="G214" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B215">
+        <v>0.046</v>
+      </c>
+      <c r="C215">
+        <v>7.717</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+      <c r="F215">
+        <v>7</v>
+      </c>
+      <c r="G215" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>8.981</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>8</v>
+      </c>
+      <c r="G216" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>8.981</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>8</v>
+      </c>
+      <c r="G217" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="2">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="B218">
+        <v>0.731</v>
+      </c>
+      <c r="C218">
+        <v>0.646</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>9</v>
+      </c>
+      <c r="G218" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="2">
+        <v>46131.09375</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>2.621</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>10</v>
+      </c>
+      <c r="G219" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="2">
+        <v>46131.10416666666</v>
+      </c>
+      <c r="B220">
+        <v>0.725</v>
+      </c>
+      <c r="C220">
+        <v>0.465</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>11</v>
+      </c>
+      <c r="G220" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="2">
+        <v>46131.11458333334</v>
+      </c>
+      <c r="B221">
+        <v>3.347</v>
+      </c>
+      <c r="C221">
+        <v>0.032</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>12</v>
+      </c>
+      <c r="G221" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
+        <v>46131.125</v>
+      </c>
+      <c r="B222">
+        <v>4.811</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>13</v>
+      </c>
+      <c r="G222" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
+        <v>46131.13541666666</v>
+      </c>
+      <c r="B223">
+        <v>0.134</v>
+      </c>
+      <c r="C223">
+        <v>0.696</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>14</v>
+      </c>
+      <c r="G223" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
+        <v>46131.14583333334</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>6.57</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>15</v>
+      </c>
+      <c r="G224" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
+        <v>46131.15625</v>
+      </c>
+      <c r="B225">
+        <v>0.004</v>
+      </c>
+      <c r="C225">
+        <v>2.162</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>16</v>
+      </c>
+      <c r="G225" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
+        <v>46131.16666666666</v>
+      </c>
+      <c r="B226">
+        <v>0.805</v>
+      </c>
+      <c r="C226">
+        <v>0.089</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>17</v>
+      </c>
+      <c r="G226" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
+        <v>46131.17708333334</v>
+      </c>
+      <c r="B227">
+        <v>5.967</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>18</v>
+      </c>
+      <c r="G227" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
+        <v>46131.1875</v>
+      </c>
+      <c r="B228">
+        <v>21.226</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>19</v>
+      </c>
+      <c r="G228" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
+        <v>46131.19791666666</v>
+      </c>
+      <c r="B229">
+        <v>11.674</v>
+      </c>
+      <c r="C229">
+        <v>0.014</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>20</v>
+      </c>
+      <c r="G229" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
+        <v>46131.20833333334</v>
+      </c>
+      <c r="B230">
+        <v>15.715</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>21</v>
+      </c>
+      <c r="G230" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
+        <v>46131.21875</v>
+      </c>
+      <c r="B231">
+        <v>1.706</v>
+      </c>
+      <c r="C231">
+        <v>0.014</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>22</v>
+      </c>
+      <c r="G231" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>46131.22916666666</v>
+      </c>
+      <c r="B232">
+        <v>0.125</v>
+      </c>
+      <c r="C232">
+        <v>0.438</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>23</v>
+      </c>
+      <c r="G232" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
+        <v>46131.23958333334</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>3.872</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
+        <v>46131.25</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>4.802</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>25</v>
+      </c>
+      <c r="G234" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
+        <v>46131.26041666666</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>7.309</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
+        <v>46131.27083333334</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>23.712</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="2">
+        <v>46131.28125</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>32.229</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237">
+        <v>28</v>
+      </c>
+      <c r="G237" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="2">
+        <v>46131.29166666666</v>
+      </c>
+      <c r="B238">
+        <v>0.019</v>
+      </c>
+      <c r="C238">
+        <v>5.373</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238">
+        <v>29</v>
+      </c>
+      <c r="G238" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="2">
+        <v>46131.30208333334</v>
+      </c>
+      <c r="B239">
+        <v>0.172</v>
+      </c>
+      <c r="C239">
+        <v>1.031</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>30</v>
+      </c>
+      <c r="G239" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="2">
+        <v>46131.3125</v>
+      </c>
+      <c r="B240">
+        <v>0.016</v>
+      </c>
+      <c r="C240">
+        <v>7.179</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>31</v>
+      </c>
+      <c r="G240" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="2">
+        <v>46131.32291666666</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>30.48</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>32</v>
+      </c>
+      <c r="G241" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="2">
+        <v>46131.33333333334</v>
+      </c>
+      <c r="B242">
+        <v>0.109</v>
+      </c>
+      <c r="C242">
+        <v>3.141</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+      <c r="F242">
+        <v>33</v>
+      </c>
+      <c r="G242" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="2">
+        <v>46131.34375</v>
+      </c>
+      <c r="B243">
+        <v>3.624</v>
+      </c>
+      <c r="C243">
+        <v>3.361</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>34</v>
+      </c>
+      <c r="G243" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="2">
+        <v>46131.35416666666</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>13.037</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>35</v>
+      </c>
+      <c r="G244" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="2">
+        <v>46131.36458333334</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>28.274</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245">
+        <v>36</v>
+      </c>
+      <c r="G245" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="2">
+        <v>46131.375</v>
+      </c>
+      <c r="B246">
+        <v>0.216</v>
+      </c>
+      <c r="C246">
+        <v>3.729</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
+      <c r="F246">
+        <v>37</v>
+      </c>
+      <c r="G246" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="2">
+        <v>46131.38541666666</v>
+      </c>
+      <c r="B247">
+        <v>0.39</v>
+      </c>
+      <c r="C247">
+        <v>0.221</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>38</v>
+      </c>
+      <c r="G247" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="2">
+        <v>46131.39583333334</v>
+      </c>
+      <c r="B248">
+        <v>0.049</v>
+      </c>
+      <c r="C248">
+        <v>3.561</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+      <c r="F248">
+        <v>39</v>
+      </c>
+      <c r="G248" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="2">
+        <v>46131.40625</v>
+      </c>
+      <c r="B249">
+        <v>0.255</v>
+      </c>
+      <c r="C249">
+        <v>3.817</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>40</v>
+      </c>
+      <c r="G249" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="2">
+        <v>46131.41666666666</v>
+      </c>
+      <c r="B250">
+        <v>3.315</v>
+      </c>
+      <c r="C250">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>41</v>
+      </c>
+      <c r="G250" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="2">
+        <v>46131.42708333334</v>
+      </c>
+      <c r="B251">
+        <v>0.099</v>
+      </c>
+      <c r="C251">
+        <v>5.24</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>42</v>
+      </c>
+      <c r="G251" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="2">
+        <v>46131.4375</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>18.609</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>43</v>
+      </c>
+      <c r="G252" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="2">
+        <v>46131.44791666666</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>25.907</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>44</v>
+      </c>
+      <c r="G253" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="2">
+        <v>46131.45833333334</v>
+      </c>
+      <c r="B254">
+        <v>0.138</v>
+      </c>
+      <c r="C254">
+        <v>7.205</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>45</v>
+      </c>
+      <c r="G254" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="2">
+        <v>46131.46875</v>
+      </c>
+      <c r="B255">
+        <v>8.739000000000001</v>
+      </c>
+      <c r="C255">
+        <v>0.028</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>46</v>
+      </c>
+      <c r="G255" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="2">
+        <v>46131.47916666666</v>
+      </c>
+      <c r="B256">
+        <v>0.008</v>
+      </c>
+      <c r="C256">
+        <v>4.723</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>47</v>
+      </c>
+      <c r="G256" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="2">
+        <v>46131.48958333334</v>
+      </c>
+      <c r="B257">
+        <v>0.001</v>
+      </c>
+      <c r="C257">
+        <v>3.222</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>48</v>
+      </c>
+      <c r="G257" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="2">
+        <v>46131.5</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>18.887</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>49</v>
+      </c>
+      <c r="G258" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="2">
+        <v>46131.51041666666</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>32.869</v>
+      </c>
+      <c r="D259">
+        <v>0</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>50</v>
+      </c>
+      <c r="G259" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="2">
+        <v>46131.52083333334</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>36.367</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>51</v>
+      </c>
+      <c r="G260" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="2">
+        <v>46131.53125</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>12.762</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>52</v>
+      </c>
+      <c r="G261" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="2">
+        <v>46131.54166666666</v>
+      </c>
+      <c r="B262">
+        <v>0.019</v>
+      </c>
+      <c r="C262">
+        <v>5.008</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>53</v>
+      </c>
+      <c r="G262" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="2">
+        <v>46131.55208333334</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>34.229</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>54</v>
+      </c>
+      <c r="G263" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="2">
+        <v>46131.5625</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>17.825</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>55</v>
+      </c>
+      <c r="G264" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="2">
+        <v>46131.57291666666</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>38.759</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>56</v>
+      </c>
+      <c r="G265" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="2">
+        <v>46131.58333333334</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>10.889</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>57</v>
+      </c>
+      <c r="G266" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="2">
+        <v>46131.59375</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>11.68</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>58</v>
+      </c>
+      <c r="G267" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="2">
+        <v>46131.60416666666</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>40.848</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>59</v>
+      </c>
+      <c r="G268" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="2">
+        <v>46131.61458333334</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>46.144</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>60</v>
+      </c>
+      <c r="G269" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="2">
+        <v>46131.625</v>
+      </c>
+      <c r="B270">
+        <v>0.002</v>
+      </c>
+      <c r="C270">
+        <v>10.253</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>25</v>
+      </c>
+      <c r="F270">
+        <v>61</v>
+      </c>
+      <c r="G270" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="2">
+        <v>46131.63541666666</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>6.386</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>25</v>
+      </c>
+      <c r="F271">
+        <v>62</v>
+      </c>
+      <c r="G271" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="2">
+        <v>46131.64583333334</v>
+      </c>
+      <c r="B272">
+        <v>0.193</v>
+      </c>
+      <c r="C272">
+        <v>0.335</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>25</v>
+      </c>
+      <c r="F272">
+        <v>63</v>
+      </c>
+      <c r="G272" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="2">
+        <v>46131.65625</v>
+      </c>
+      <c r="B273">
+        <v>0.618</v>
+      </c>
+      <c r="C273">
+        <v>0.167</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>25</v>
+      </c>
+      <c r="F273">
+        <v>64</v>
+      </c>
+      <c r="G273" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="2">
+        <v>46131.66666666666</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>23.475</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>65</v>
+      </c>
+      <c r="G274" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="2">
+        <v>46131.67708333334</v>
+      </c>
+      <c r="B275">
+        <v>0.021</v>
+      </c>
+      <c r="C275">
+        <v>2.014</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>66</v>
+      </c>
+      <c r="G275" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="2">
+        <v>46131.6875</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>7.286</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>67</v>
+      </c>
+      <c r="G276" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="2">
+        <v>46131.69791666666</v>
+      </c>
+      <c r="B277">
+        <v>0.273</v>
+      </c>
+      <c r="C277">
+        <v>0.722</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>68</v>
+      </c>
+      <c r="G277" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="2">
+        <v>46131.70833333334</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>27.748</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>69</v>
+      </c>
+      <c r="G278" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="2">
+        <v>46131.71875</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>21.769</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>70</v>
+      </c>
+      <c r="G279" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="2">
+        <v>46131.72916666666</v>
+      </c>
+      <c r="B280">
+        <v>0.044</v>
+      </c>
+      <c r="C280">
+        <v>2.865</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>71</v>
+      </c>
+      <c r="G280" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="2">
+        <v>46131.73958333334</v>
+      </c>
+      <c r="B281">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C281">
+        <v>8.146000000000001</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>72</v>
+      </c>
+      <c r="G281" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="2">
+        <v>46131.75</v>
+      </c>
+      <c r="B282">
+        <v>0.224</v>
+      </c>
+      <c r="C282">
+        <v>0.379</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>73</v>
+      </c>
+      <c r="G282" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="2">
+        <v>46131.76041666666</v>
+      </c>
+      <c r="B283">
+        <v>0.123</v>
+      </c>
+      <c r="C283">
+        <v>0.267</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>74</v>
+      </c>
+      <c r="G283" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="2">
+        <v>46131.77083333334</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>5.77</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>75</v>
+      </c>
+      <c r="G284" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="2">
+        <v>46131.78125</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>17.149</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>76</v>
+      </c>
+      <c r="G285" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="2">
+        <v>46131.79166666666</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>17.572</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>77</v>
+      </c>
+      <c r="G286" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="2">
+        <v>46131.80208333334</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>5.815</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>78</v>
+      </c>
+      <c r="G287" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="2">
+        <v>46131.8125</v>
+      </c>
+      <c r="B288">
+        <v>0.223</v>
+      </c>
+      <c r="C288">
+        <v>0.077</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>25</v>
+      </c>
+      <c r="F288">
+        <v>79</v>
+      </c>
+      <c r="G288" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="2">
+        <v>46131.82291666666</v>
+      </c>
+      <c r="B289">
+        <v>0.053</v>
+      </c>
+      <c r="C289">
+        <v>0.417</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>25</v>
+      </c>
+      <c r="F289">
+        <v>80</v>
+      </c>
+      <c r="G289" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="2">
+        <v>46131.83333333334</v>
+      </c>
+      <c r="B290">
+        <v>0.117</v>
+      </c>
+      <c r="C290">
+        <v>0.075</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>25</v>
+      </c>
+      <c r="F290">
+        <v>81</v>
+      </c>
+      <c r="G290" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="2">
+        <v>46131.84375</v>
+      </c>
+      <c r="B291">
+        <v>0.136</v>
+      </c>
+      <c r="C291">
+        <v>0.108</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>25</v>
+      </c>
+      <c r="F291">
+        <v>82</v>
+      </c>
+      <c r="G291" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="2">
+        <v>46131.85416666666</v>
+      </c>
+      <c r="B292">
+        <v>0.048</v>
+      </c>
+      <c r="C292">
+        <v>5.308</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>25</v>
+      </c>
+      <c r="F292">
+        <v>83</v>
+      </c>
+      <c r="G292" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="2">
+        <v>46131.86458333334</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>8.039</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>25</v>
+      </c>
+      <c r="F293">
+        <v>84</v>
+      </c>
+      <c r="G293" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="2">
+        <v>46131.875</v>
+      </c>
+      <c r="B294">
+        <v>0.074</v>
+      </c>
+      <c r="C294">
+        <v>9.526</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>25</v>
+      </c>
+      <c r="F294">
+        <v>85</v>
+      </c>
+      <c r="G294" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="2">
+        <v>46131.88541666666</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>18.529</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>25</v>
+      </c>
+      <c r="F295">
+        <v>86</v>
+      </c>
+      <c r="G295" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="2">
+        <v>46131.89583333334</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>15.99</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>25</v>
+      </c>
+      <c r="F296">
+        <v>87</v>
+      </c>
+      <c r="G296" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="2">
+        <v>46131.90625</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>17.831</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>25</v>
+      </c>
+      <c r="F297">
+        <v>88</v>
+      </c>
+      <c r="G297" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="2">
+        <v>46131.91666666666</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>6.413</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>42.5</v>
+      </c>
+      <c r="F298">
+        <v>89</v>
+      </c>
+      <c r="G298" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="2">
+        <v>46131.92708333334</v>
+      </c>
+      <c r="B299">
+        <v>0.018</v>
+      </c>
+      <c r="C299">
+        <v>2.878</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>42.5</v>
+      </c>
+      <c r="F299">
+        <v>90</v>
+      </c>
+      <c r="G299" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="2">
+        <v>46131.9375</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>10.17</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>42.5</v>
+      </c>
+      <c r="F300">
+        <v>91</v>
+      </c>
+      <c r="G300" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="2">
+        <v>46131.94791666666</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>18.629</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>42.5</v>
+      </c>
+      <c r="F301">
+        <v>92</v>
+      </c>
+      <c r="G301" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="2">
+        <v>46131.95833333334</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>9.536</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>42.5</v>
+      </c>
+      <c r="F302">
+        <v>93</v>
+      </c>
+      <c r="G302" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="2">
+        <v>46131.96875</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>20.717</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>42.5</v>
+      </c>
+      <c r="F303">
+        <v>94</v>
+      </c>
+      <c r="G303" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="2">
+        <v>46131.97916666666</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>10.901</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>42.5</v>
+      </c>
+      <c r="F304">
+        <v>95</v>
+      </c>
+      <c r="G304" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="2">
+        <v>46131.98958333334</v>
+      </c>
+      <c r="B305">
+        <v>0.005</v>
+      </c>
+      <c r="C305">
+        <v>5.567</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>48.25</v>
+      </c>
+      <c r="F305">
+        <v>96</v>
+      </c>
+      <c r="G305" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B306">
+        <v>0.004</v>
+      </c>
+      <c r="C306">
+        <v>3.658</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>41.5</v>
+      </c>
+      <c r="F306">
+        <v>1</v>
+      </c>
+      <c r="G306" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B307">
+        <v>0.004</v>
+      </c>
+      <c r="C307">
+        <v>3.658</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>41.5</v>
+      </c>
+      <c r="F307">
+        <v>1</v>
+      </c>
+      <c r="G307" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B308">
+        <v>0.064</v>
+      </c>
+      <c r="C308">
+        <v>0.548</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>41.5</v>
+      </c>
+      <c r="F308">
+        <v>2</v>
+      </c>
+      <c r="G308" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B309">
+        <v>0.064</v>
+      </c>
+      <c r="C309">
+        <v>0.548</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>41.5</v>
+      </c>
+      <c r="F309">
+        <v>2</v>
+      </c>
+      <c r="G309" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>6.74</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>30</v>
+      </c>
+      <c r="F310">
+        <v>3</v>
+      </c>
+      <c r="G310" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>6.74</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>30</v>
+      </c>
+      <c r="F311">
+        <v>3</v>
+      </c>
+      <c r="G311" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>6.306</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>30</v>
+      </c>
+      <c r="F312">
+        <v>4</v>
+      </c>
+      <c r="G312" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>6.306</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>30</v>
+      </c>
+      <c r="F313">
+        <v>4</v>
+      </c>
+      <c r="G313" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>19.334</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>30</v>
+      </c>
+      <c r="F314">
+        <v>5</v>
+      </c>
+      <c r="G314" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>19.334</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>30</v>
+      </c>
+      <c r="F315">
+        <v>5</v>
+      </c>
+      <c r="G315" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>17.86</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>30</v>
+      </c>
+      <c r="F316">
+        <v>6</v>
+      </c>
+      <c r="G316" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>17.86</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>30</v>
+      </c>
+      <c r="F317">
+        <v>6</v>
+      </c>
+      <c r="G317" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>5.939</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>30</v>
+      </c>
+      <c r="F318">
+        <v>7</v>
+      </c>
+      <c r="G318" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>5.939</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319">
+        <v>7</v>
+      </c>
+      <c r="G319" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B320">
+        <v>0.704</v>
+      </c>
+      <c r="C320">
+        <v>3.274</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>62.5</v>
+      </c>
+      <c r="F320">
+        <v>8</v>
+      </c>
+      <c r="G320" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B321">
+        <v>0.704</v>
+      </c>
+      <c r="C321">
+        <v>3.274</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>62.5</v>
+      </c>
+      <c r="F321">
+        <v>8</v>
+      </c>
+      <c r="G321" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="2">
+        <v>46132.08333333334</v>
+      </c>
+      <c r="B322">
+        <v>0.295</v>
+      </c>
+      <c r="C322">
+        <v>0.978</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>62.5</v>
+      </c>
+      <c r="F322">
+        <v>9</v>
+      </c>
+      <c r="G322" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="2">
+        <v>46132.09375</v>
+      </c>
+      <c r="B323">
+        <v>2.942</v>
+      </c>
+      <c r="C323">
+        <v>0.021</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>61.5</v>
+      </c>
+      <c r="F323">
+        <v>10</v>
+      </c>
+      <c r="G323" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="2">
+        <v>46132.10416666666</v>
+      </c>
+      <c r="B324">
+        <v>0.049</v>
+      </c>
+      <c r="C324">
+        <v>1.75</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>61.5</v>
+      </c>
+      <c r="F324">
+        <v>11</v>
+      </c>
+      <c r="G324" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" s="2">
+        <v>46132.11458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>22.589</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>27.75</v>
+      </c>
+      <c r="F325">
+        <v>12</v>
+      </c>
+      <c r="G325" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" s="2">
+        <v>46132.125</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>21.054</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>30</v>
+      </c>
+      <c r="F326">
+        <v>13</v>
+      </c>
+      <c r="G326" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" s="2">
+        <v>46132.13541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>22.432</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>30</v>
+      </c>
+      <c r="F327">
+        <v>14</v>
+      </c>
+      <c r="G327" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" s="2">
+        <v>46132.14583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>30</v>
+      </c>
+      <c r="F328">
+        <v>15</v>
+      </c>
+      <c r="G328" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" s="2">
+        <v>46132.15625</v>
+      </c>
+      <c r="B329">
+        <v>0.043</v>
+      </c>
+      <c r="C329">
+        <v>4.847</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>30</v>
+      </c>
+      <c r="F329">
+        <v>16</v>
+      </c>
+      <c r="G329" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" s="2">
+        <v>46132.16666666666</v>
+      </c>
+      <c r="B330">
+        <v>0.173</v>
+      </c>
+      <c r="C330">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>37.5</v>
+      </c>
+      <c r="F330">
+        <v>17</v>
+      </c>
+      <c r="G330" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" s="2">
+        <v>46132.17708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>2.24</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>37.5</v>
+      </c>
+      <c r="F331">
+        <v>18</v>
+      </c>
+      <c r="G331" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="2">
+        <v>46132.1875</v>
+      </c>
+      <c r="B332">
+        <v>0.056</v>
+      </c>
+      <c r="C332">
+        <v>1.003</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>37.5</v>
+      </c>
+      <c r="F332">
+        <v>19</v>
+      </c>
+      <c r="G332" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" s="2">
+        <v>46132.19791666666</v>
+      </c>
+      <c r="B333">
+        <v>11.519</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>37.5</v>
+      </c>
+      <c r="F333">
+        <v>20</v>
+      </c>
+      <c r="G333" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" s="2">
+        <v>46132.20833333334</v>
+      </c>
+      <c r="B334">
+        <v>4.567</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>37.5</v>
+      </c>
+      <c r="F334">
+        <v>21</v>
+      </c>
+      <c r="G334" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" s="2">
+        <v>46132.21875</v>
+      </c>
+      <c r="B335">
+        <v>9.507999999999999</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>37.5</v>
+      </c>
+      <c r="F335">
+        <v>22</v>
+      </c>
+      <c r="G335" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="2">
+        <v>46132.22916666666</v>
+      </c>
+      <c r="B336">
+        <v>4.926</v>
+      </c>
+      <c r="C336">
+        <v>0.095</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>25</v>
+      </c>
+      <c r="F336">
+        <v>23</v>
+      </c>
+      <c r="G336" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="2">
+        <v>46132.23958333334</v>
+      </c>
+      <c r="B337">
+        <v>10.283</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>25</v>
+      </c>
+      <c r="F337">
+        <v>24</v>
+      </c>
+      <c r="G337" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" s="2">
+        <v>46132.25</v>
+      </c>
+      <c r="B338">
+        <v>1.329</v>
+      </c>
+      <c r="C338">
+        <v>6.411</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>25</v>
+      </c>
+      <c r="F338">
+        <v>25</v>
+      </c>
+      <c r="G338" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="2">
+        <v>46132.26041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>14.067</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>25</v>
+      </c>
+      <c r="F339">
+        <v>26</v>
+      </c>
+      <c r="G339" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="2">
+        <v>46132.27083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>16.054</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>27</v>
+      </c>
+      <c r="G340" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="2">
+        <v>46132.28125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>26.84</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>28</v>
+      </c>
+      <c r="G341" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" s="2">
+        <v>46132.29166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>48.748</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>29</v>
+      </c>
+      <c r="G342" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" s="2">
+        <v>46132.30208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>62.539</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>0</v>
+      </c>
+      <c r="F343">
+        <v>30</v>
+      </c>
+      <c r="G343" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" s="2">
+        <v>46132.3125</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>75.53100000000001</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>0</v>
+      </c>
+      <c r="F344">
+        <v>31</v>
+      </c>
+      <c r="G344" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" s="2">
+        <v>46132.32291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>26.53</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>65</v>
+      </c>
+      <c r="F345">
+        <v>32</v>
+      </c>
+      <c r="G345" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" s="2">
+        <v>46132.33333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>67.25</v>
+      </c>
+      <c r="F346">
+        <v>33</v>
+      </c>
+      <c r="G346" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" s="2">
+        <v>46132.34375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>67.25</v>
+      </c>
+      <c r="F347">
+        <v>34</v>
+      </c>
+      <c r="G347" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" s="2">
+        <v>46132.35416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>0</v>
+      </c>
+      <c r="F348">
+        <v>35</v>
+      </c>
+      <c r="G348" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" s="2">
+        <v>46132.36458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>0</v>
+      </c>
+      <c r="F349">
+        <v>36</v>
+      </c>
+      <c r="G349" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" s="2">
+        <v>46132.375</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>0</v>
+      </c>
+      <c r="F350">
+        <v>37</v>
+      </c>
+      <c r="G350" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" s="2">
+        <v>46132.38541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>0</v>
+      </c>
+      <c r="F351">
+        <v>38</v>
+      </c>
+      <c r="G351" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" s="2">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>0</v>
+      </c>
+      <c r="F352">
+        <v>39</v>
+      </c>
+      <c r="G352" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" s="2">
+        <v>46132.40625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>0</v>
+      </c>
+      <c r="F353">
+        <v>40</v>
+      </c>
+      <c r="G353" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" s="2">
+        <v>46132.41666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>0</v>
+      </c>
+      <c r="F354">
+        <v>41</v>
+      </c>
+      <c r="G354" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" s="2">
+        <v>46132.42708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>0</v>
+      </c>
+      <c r="F355">
+        <v>42</v>
+      </c>
+      <c r="G355" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" s="2">
+        <v>46132.4375</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
+      <c r="F356">
+        <v>43</v>
+      </c>
+      <c r="G356" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" s="2">
+        <v>46132.44791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>0</v>
+      </c>
+      <c r="F357">
+        <v>44</v>
+      </c>
+      <c r="G357" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" s="2">
+        <v>46132.45833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>0</v>
+      </c>
+      <c r="F358">
+        <v>45</v>
+      </c>
+      <c r="G358" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" s="2">
+        <v>46132.46875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>0</v>
+      </c>
+      <c r="F359">
+        <v>46</v>
+      </c>
+      <c r="G359" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" s="2">
+        <v>46132.47916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
+      <c r="F360">
+        <v>47</v>
+      </c>
+      <c r="G360" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" s="2">
+        <v>46132.48958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
+      <c r="F361">
+        <v>48</v>
+      </c>
+      <c r="G361" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" s="2">
+        <v>46132.5</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+      <c r="F362">
+        <v>49</v>
+      </c>
+      <c r="G362" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" s="2">
+        <v>46132.51041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
+      <c r="F363">
+        <v>50</v>
+      </c>
+      <c r="G363" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" s="2">
+        <v>46132.52083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+      <c r="F364">
+        <v>51</v>
+      </c>
+      <c r="G364" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" s="2">
+        <v>46132.53125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+      <c r="F365">
+        <v>52</v>
+      </c>
+      <c r="G365" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" s="2">
+        <v>46132.54166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+      <c r="F366">
+        <v>53</v>
+      </c>
+      <c r="G366" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="2">
+        <v>46132.55208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>0</v>
+      </c>
+      <c r="F367">
+        <v>54</v>
+      </c>
+      <c r="G367" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" s="2">
+        <v>46132.5625</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>0</v>
+      </c>
+      <c r="F368">
+        <v>55</v>
+      </c>
+      <c r="G368" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" s="2">
+        <v>46132.57291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>0</v>
+      </c>
+      <c r="F369">
+        <v>56</v>
+      </c>
+      <c r="G369" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" s="2">
+        <v>46132.58333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
+      <c r="F370">
+        <v>57</v>
+      </c>
+      <c r="G370" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" s="2">
+        <v>46132.59375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
+      <c r="F371">
+        <v>58</v>
+      </c>
+      <c r="G371" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" s="2">
+        <v>46132.60416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
+      <c r="F372">
+        <v>59</v>
+      </c>
+      <c r="G372" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" s="2">
+        <v>46132.61458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>60</v>
+      </c>
+      <c r="G373" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" s="2">
+        <v>46132.625</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>61</v>
+      </c>
+      <c r="G374" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" s="2">
+        <v>46132.63541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>62</v>
+      </c>
+      <c r="G375" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" s="2">
+        <v>46132.64583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+      <c r="F376">
+        <v>63</v>
+      </c>
+      <c r="G376" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" s="2">
+        <v>46132.65625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+      <c r="F377">
+        <v>64</v>
+      </c>
+      <c r="G377" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" s="2">
+        <v>46132.66666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>65</v>
+      </c>
+      <c r="G378" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" s="2">
+        <v>46132.67708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+      <c r="F379">
+        <v>66</v>
+      </c>
+      <c r="G379" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" s="2">
+        <v>46132.6875</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+      <c r="F380">
+        <v>67</v>
+      </c>
+      <c r="G380" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" s="2">
+        <v>46132.69791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
+      <c r="F381">
+        <v>68</v>
+      </c>
+      <c r="G381" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" s="2">
+        <v>46132.70833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>0</v>
+      </c>
+      <c r="F382">
+        <v>69</v>
+      </c>
+      <c r="G382" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" s="2">
+        <v>46132.71875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
+      <c r="F383">
+        <v>70</v>
+      </c>
+      <c r="G383" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" s="2">
+        <v>46132.72916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>0</v>
+      </c>
+      <c r="F384">
+        <v>71</v>
+      </c>
+      <c r="G384" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" s="2">
+        <v>46132.73958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
+      <c r="F385">
+        <v>72</v>
+      </c>
+      <c r="G385" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7">
+      <c r="A386" s="2">
+        <v>46132.75</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+      <c r="E386">
+        <v>0</v>
+      </c>
+      <c r="F386">
+        <v>73</v>
+      </c>
+      <c r="G386" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" s="2">
+        <v>46132.76041666666</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+      <c r="E387">
+        <v>0</v>
+      </c>
+      <c r="F387">
+        <v>74</v>
+      </c>
+      <c r="G387" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" s="2">
+        <v>46132.77083333334</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>0</v>
+      </c>
+      <c r="E388">
+        <v>0</v>
+      </c>
+      <c r="F388">
+        <v>75</v>
+      </c>
+      <c r="G388" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" s="2">
+        <v>46132.78125</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>0</v>
+      </c>
+      <c r="E389">
+        <v>0</v>
+      </c>
+      <c r="F389">
+        <v>76</v>
+      </c>
+      <c r="G389" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" s="2">
+        <v>46132.79166666666</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>0</v>
+      </c>
+      <c r="E390">
+        <v>0</v>
+      </c>
+      <c r="F390">
+        <v>77</v>
+      </c>
+      <c r="G390" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" s="2">
+        <v>46132.80208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>0</v>
+      </c>
+      <c r="E391">
+        <v>0</v>
+      </c>
+      <c r="F391">
+        <v>78</v>
+      </c>
+      <c r="G391" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" s="2">
+        <v>46132.8125</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>0</v>
+      </c>
+      <c r="E392">
+        <v>0</v>
+      </c>
+      <c r="F392">
+        <v>79</v>
+      </c>
+      <c r="G392" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" s="2">
+        <v>46132.82291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+      <c r="E393">
+        <v>0</v>
+      </c>
+      <c r="F393">
+        <v>80</v>
+      </c>
+      <c r="G393" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="A394" s="2">
+        <v>46132.83333333334</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>0</v>
+      </c>
+      <c r="E394">
+        <v>0</v>
+      </c>
+      <c r="F394">
+        <v>81</v>
+      </c>
+      <c r="G394" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" s="2">
+        <v>46132.84375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="E395">
+        <v>0</v>
+      </c>
+      <c r="F395">
+        <v>82</v>
+      </c>
+      <c r="G395" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="A396" s="2">
+        <v>46132.85416666666</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+      <c r="E396">
+        <v>0</v>
+      </c>
+      <c r="F396">
+        <v>83</v>
+      </c>
+      <c r="G396" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
+      <c r="A397" s="2">
+        <v>46132.86458333334</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+      <c r="E397">
+        <v>0</v>
+      </c>
+      <c r="F397">
+        <v>84</v>
+      </c>
+      <c r="G397" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
+      <c r="A398" s="2">
+        <v>46132.875</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>0</v>
+      </c>
+      <c r="E398">
+        <v>0</v>
+      </c>
+      <c r="F398">
+        <v>85</v>
+      </c>
+      <c r="G398" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
+      <c r="A399" s="2">
+        <v>46132.88541666666</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+      <c r="E399">
+        <v>0</v>
+      </c>
+      <c r="F399">
+        <v>86</v>
+      </c>
+      <c r="G399" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
+      <c r="A400" s="2">
+        <v>46132.89583333334</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+      <c r="E400">
+        <v>0</v>
+      </c>
+      <c r="F400">
+        <v>87</v>
+      </c>
+      <c r="G400" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401" s="2">
+        <v>46132.90625</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>0</v>
+      </c>
+      <c r="E401">
+        <v>0</v>
+      </c>
+      <c r="F401">
+        <v>88</v>
+      </c>
+      <c r="G401" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" s="2">
+        <v>46132.91666666666</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+      <c r="E402">
+        <v>0</v>
+      </c>
+      <c r="F402">
+        <v>89</v>
+      </c>
+      <c r="G402" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
+      <c r="A403" s="2">
+        <v>46132.92708333334</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+      <c r="E403">
+        <v>0</v>
+      </c>
+      <c r="F403">
+        <v>90</v>
+      </c>
+      <c r="G403" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
+      <c r="A404" s="2">
+        <v>46132.9375</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+      <c r="E404">
+        <v>0</v>
+      </c>
+      <c r="F404">
+        <v>91</v>
+      </c>
+      <c r="G404" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7">
+      <c r="A405" s="2">
+        <v>46132.94791666666</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+      <c r="E405">
+        <v>0</v>
+      </c>
+      <c r="F405">
+        <v>92</v>
+      </c>
+      <c r="G405" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406" s="2">
+        <v>46132.95833333334</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+      <c r="E406">
+        <v>0</v>
+      </c>
+      <c r="F406">
+        <v>93</v>
+      </c>
+      <c r="G406" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
+      <c r="A407" s="2">
+        <v>46132.96875</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>0</v>
+      </c>
+      <c r="E407">
+        <v>0</v>
+      </c>
+      <c r="F407">
+        <v>94</v>
+      </c>
+      <c r="G407" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
+      <c r="A408" s="2">
+        <v>46132.97916666666</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+      <c r="E408">
+        <v>0</v>
+      </c>
+      <c r="F408">
+        <v>95</v>
+      </c>
+      <c r="G408" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
+      <c r="A409" s="2">
+        <v>46132.98958333334</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>0</v>
+      </c>
+      <c r="E409">
+        <v>0</v>
+      </c>
+      <c r="F409">
+        <v>96</v>
+      </c>
+      <c r="G409" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.04.20261</t>
-  </si>
-  <si>
-    <t>20.04.20262</t>
-  </si>
-  <si>
-    <t>20.04.20263</t>
-  </si>
-  <si>
-    <t>20.04.20264</t>
-  </si>
-  <si>
-    <t>20.04.20265</t>
-  </si>
-  <si>
-    <t>20.04.20266</t>
-  </si>
-  <si>
-    <t>20.04.20267</t>
-  </si>
-  <si>
-    <t>20.04.20268</t>
-  </si>
-  <si>
-    <t>20.04.20269</t>
-  </si>
-  <si>
-    <t>20.04.202610</t>
-  </si>
-  <si>
-    <t>20.04.202611</t>
-  </si>
-  <si>
-    <t>20.04.202612</t>
-  </si>
-  <si>
-    <t>20.04.202613</t>
-  </si>
-  <si>
-    <t>20.04.202614</t>
-  </si>
-  <si>
-    <t>20.04.202615</t>
-  </si>
-  <si>
-    <t>20.04.202616</t>
-  </si>
-  <si>
-    <t>20.04.202617</t>
-  </si>
-  <si>
-    <t>20.04.202618</t>
-  </si>
-  <si>
-    <t>20.04.202619</t>
-  </si>
-  <si>
-    <t>20.04.202620</t>
-  </si>
-  <si>
-    <t>20.04.202621</t>
-  </si>
-  <si>
-    <t>20.04.202622</t>
-  </si>
-  <si>
-    <t>20.04.202623</t>
-  </si>
-  <si>
-    <t>20.04.202624</t>
-  </si>
-  <si>
-    <t>20.04.202625</t>
-  </si>
-  <si>
-    <t>20.04.202626</t>
-  </si>
-  <si>
-    <t>20.04.202627</t>
-  </si>
-  <si>
-    <t>20.04.202628</t>
-  </si>
-  <si>
-    <t>20.04.202629</t>
-  </si>
-  <si>
-    <t>20.04.202630</t>
-  </si>
-  <si>
-    <t>20.04.202631</t>
-  </si>
-  <si>
-    <t>20.04.202632</t>
-  </si>
-  <si>
-    <t>20.04.202633</t>
-  </si>
-  <si>
-    <t>20.04.202634</t>
-  </si>
-  <si>
-    <t>20.04.202635</t>
-  </si>
-  <si>
-    <t>20.04.202636</t>
-  </si>
-  <si>
-    <t>20.04.202637</t>
-  </si>
-  <si>
-    <t>20.04.202638</t>
-  </si>
-  <si>
-    <t>20.04.202639</t>
-  </si>
-  <si>
-    <t>20.04.202640</t>
-  </si>
-  <si>
-    <t>20.04.202641</t>
-  </si>
-  <si>
-    <t>20.04.202642</t>
-  </si>
-  <si>
-    <t>20.04.202643</t>
-  </si>
-  <si>
-    <t>20.04.202644</t>
-  </si>
-  <si>
-    <t>20.04.202645</t>
-  </si>
-  <si>
-    <t>20.04.202646</t>
-  </si>
-  <si>
-    <t>20.04.202647</t>
-  </si>
-  <si>
-    <t>20.04.202648</t>
-  </si>
-  <si>
-    <t>20.04.202649</t>
-  </si>
-  <si>
-    <t>20.04.202650</t>
-  </si>
-  <si>
-    <t>20.04.202651</t>
-  </si>
-  <si>
-    <t>20.04.202652</t>
-  </si>
-  <si>
-    <t>20.04.202653</t>
-  </si>
-  <si>
-    <t>20.04.202654</t>
-  </si>
-  <si>
-    <t>20.04.202655</t>
-  </si>
-  <si>
-    <t>20.04.202656</t>
-  </si>
-  <si>
-    <t>20.04.202657</t>
-  </si>
-  <si>
-    <t>20.04.202658</t>
-  </si>
-  <si>
-    <t>20.04.202659</t>
-  </si>
-  <si>
-    <t>20.04.202660</t>
-  </si>
-  <si>
-    <t>20.04.202661</t>
-  </si>
-  <si>
-    <t>20.04.202662</t>
-  </si>
-  <si>
-    <t>20.04.202663</t>
-  </si>
-  <si>
-    <t>20.04.202664</t>
-  </si>
-  <si>
-    <t>20.04.202665</t>
-  </si>
-  <si>
-    <t>20.04.202666</t>
-  </si>
-  <si>
-    <t>20.04.202667</t>
-  </si>
-  <si>
-    <t>20.04.202668</t>
-  </si>
-  <si>
-    <t>20.04.202669</t>
-  </si>
-  <si>
-    <t>20.04.202670</t>
-  </si>
-  <si>
-    <t>20.04.202671</t>
-  </si>
-  <si>
-    <t>20.04.202672</t>
-  </si>
-  <si>
-    <t>20.04.202673</t>
-  </si>
-  <si>
-    <t>20.04.202674</t>
-  </si>
-  <si>
-    <t>20.04.202675</t>
-  </si>
-  <si>
-    <t>20.04.202676</t>
-  </si>
-  <si>
-    <t>20.04.202677</t>
-  </si>
-  <si>
-    <t>20.04.202678</t>
-  </si>
-  <si>
-    <t>20.04.202679</t>
-  </si>
-  <si>
-    <t>20.04.202680</t>
-  </si>
-  <si>
-    <t>20.04.202681</t>
-  </si>
-  <si>
-    <t>20.04.202682</t>
-  </si>
-  <si>
-    <t>20.04.202683</t>
-  </si>
-  <si>
-    <t>20.04.202684</t>
-  </si>
-  <si>
-    <t>20.04.202685</t>
-  </si>
-  <si>
-    <t>20.04.202686</t>
-  </si>
-  <si>
-    <t>20.04.202687</t>
-  </si>
-  <si>
-    <t>20.04.202688</t>
-  </si>
-  <si>
-    <t>20.04.202689</t>
-  </si>
-  <si>
-    <t>20.04.202690</t>
-  </si>
-  <si>
-    <t>20.04.202691</t>
-  </si>
-  <si>
-    <t>20.04.202692</t>
-  </si>
-  <si>
-    <t>20.04.202693</t>
-  </si>
-  <si>
-    <t>20.04.202694</t>
-  </si>
-  <si>
-    <t>20.04.202695</t>
-  </si>
-  <si>
-    <t>20.04.202696</t>
-  </si>
-  <si>
     <t>21.04.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>21.04.202696</t>
+  </si>
+  <si>
+    <t>22.04.20261</t>
+  </si>
+  <si>
+    <t>22.04.20262</t>
+  </si>
+  <si>
+    <t>22.04.20263</t>
+  </si>
+  <si>
+    <t>22.04.20264</t>
+  </si>
+  <si>
+    <t>22.04.20265</t>
+  </si>
+  <si>
+    <t>22.04.20266</t>
+  </si>
+  <si>
+    <t>22.04.20267</t>
+  </si>
+  <si>
+    <t>22.04.20268</t>
+  </si>
+  <si>
+    <t>22.04.20269</t>
+  </si>
+  <si>
+    <t>22.04.202610</t>
+  </si>
+  <si>
+    <t>22.04.202611</t>
+  </si>
+  <si>
+    <t>22.04.202612</t>
+  </si>
+  <si>
+    <t>22.04.202613</t>
+  </si>
+  <si>
+    <t>22.04.202614</t>
+  </si>
+  <si>
+    <t>22.04.202615</t>
+  </si>
+  <si>
+    <t>22.04.202616</t>
+  </si>
+  <si>
+    <t>22.04.202617</t>
+  </si>
+  <si>
+    <t>22.04.202618</t>
+  </si>
+  <si>
+    <t>22.04.202619</t>
+  </si>
+  <si>
+    <t>22.04.202620</t>
+  </si>
+  <si>
+    <t>22.04.202621</t>
+  </si>
+  <si>
+    <t>22.04.202622</t>
+  </si>
+  <si>
+    <t>22.04.202623</t>
+  </si>
+  <si>
+    <t>22.04.202624</t>
+  </si>
+  <si>
+    <t>22.04.202625</t>
+  </si>
+  <si>
+    <t>22.04.202626</t>
+  </si>
+  <si>
+    <t>22.04.202627</t>
+  </si>
+  <si>
+    <t>22.04.202628</t>
+  </si>
+  <si>
+    <t>22.04.202629</t>
+  </si>
+  <si>
+    <t>22.04.202630</t>
+  </si>
+  <si>
+    <t>22.04.202631</t>
+  </si>
+  <si>
+    <t>22.04.202632</t>
+  </si>
+  <si>
+    <t>22.04.202633</t>
+  </si>
+  <si>
+    <t>22.04.202634</t>
+  </si>
+  <si>
+    <t>22.04.202635</t>
+  </si>
+  <si>
+    <t>22.04.202636</t>
+  </si>
+  <si>
+    <t>22.04.202637</t>
+  </si>
+  <si>
+    <t>22.04.202638</t>
+  </si>
+  <si>
+    <t>22.04.202639</t>
+  </si>
+  <si>
+    <t>22.04.202640</t>
+  </si>
+  <si>
+    <t>22.04.202641</t>
+  </si>
+  <si>
+    <t>22.04.202642</t>
+  </si>
+  <si>
+    <t>22.04.202643</t>
+  </si>
+  <si>
+    <t>22.04.202644</t>
+  </si>
+  <si>
+    <t>22.04.202645</t>
+  </si>
+  <si>
+    <t>22.04.202646</t>
+  </si>
+  <si>
+    <t>22.04.202647</t>
+  </si>
+  <si>
+    <t>22.04.202648</t>
+  </si>
+  <si>
+    <t>22.04.202649</t>
+  </si>
+  <si>
+    <t>22.04.202650</t>
+  </si>
+  <si>
+    <t>22.04.202651</t>
+  </si>
+  <si>
+    <t>22.04.202652</t>
+  </si>
+  <si>
+    <t>22.04.202653</t>
+  </si>
+  <si>
+    <t>22.04.202654</t>
+  </si>
+  <si>
+    <t>22.04.202655</t>
+  </si>
+  <si>
+    <t>22.04.202656</t>
+  </si>
+  <si>
+    <t>22.04.202657</t>
+  </si>
+  <si>
+    <t>22.04.202658</t>
+  </si>
+  <si>
+    <t>22.04.202659</t>
+  </si>
+  <si>
+    <t>22.04.202660</t>
+  </si>
+  <si>
+    <t>22.04.202661</t>
+  </si>
+  <si>
+    <t>22.04.202662</t>
+  </si>
+  <si>
+    <t>22.04.202663</t>
+  </si>
+  <si>
+    <t>22.04.202664</t>
+  </si>
+  <si>
+    <t>22.04.202665</t>
+  </si>
+  <si>
+    <t>22.04.202666</t>
+  </si>
+  <si>
+    <t>22.04.202667</t>
+  </si>
+  <si>
+    <t>22.04.202668</t>
+  </si>
+  <si>
+    <t>22.04.202669</t>
+  </si>
+  <si>
+    <t>22.04.202670</t>
+  </si>
+  <si>
+    <t>22.04.202671</t>
+  </si>
+  <si>
+    <t>22.04.202672</t>
+  </si>
+  <si>
+    <t>22.04.202673</t>
+  </si>
+  <si>
+    <t>22.04.202674</t>
+  </si>
+  <si>
+    <t>22.04.202675</t>
+  </si>
+  <si>
+    <t>22.04.202676</t>
+  </si>
+  <si>
+    <t>22.04.202677</t>
+  </si>
+  <si>
+    <t>22.04.202678</t>
+  </si>
+  <si>
+    <t>22.04.202679</t>
+  </si>
+  <si>
+    <t>22.04.202680</t>
+  </si>
+  <si>
+    <t>22.04.202681</t>
+  </si>
+  <si>
+    <t>22.04.202682</t>
+  </si>
+  <si>
+    <t>22.04.202683</t>
+  </si>
+  <si>
+    <t>22.04.202684</t>
+  </si>
+  <si>
+    <t>22.04.202685</t>
+  </si>
+  <si>
+    <t>22.04.202686</t>
+  </si>
+  <si>
+    <t>22.04.202687</t>
+  </si>
+  <si>
+    <t>22.04.202688</t>
+  </si>
+  <si>
+    <t>22.04.202689</t>
+  </si>
+  <si>
+    <t>22.04.202690</t>
+  </si>
+  <si>
+    <t>22.04.202691</t>
+  </si>
+  <si>
+    <t>22.04.202692</t>
+  </si>
+  <si>
+    <t>22.04.202693</t>
+  </si>
+  <si>
+    <t>22.04.202694</t>
+  </si>
+  <si>
+    <t>22.04.202695</t>
+  </si>
+  <si>
+    <t>22.04.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,19 +1000,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>3.658</v>
+        <v>6.6</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>41.5</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1023,19 +1023,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.548</v>
+        <v>2.719</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>41.5</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1046,19 +1046,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>6.74</v>
+        <v>19.815</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1069,19 +1069,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>6.306</v>
+        <v>56.953</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1092,19 +1092,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>19.334</v>
+        <v>47.547</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>17.86</v>
+        <v>15.928</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1138,19 +1138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>5.939</v>
+        <v>72.093</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.704</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>3.274</v>
+        <v>24.24</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>62.5</v>
+        <v>71.25</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1184,19 +1184,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.978</v>
+        <v>11.147</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>62.5</v>
+        <v>71.25</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1207,19 +1207,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>2.942</v>
+        <v>0.218</v>
       </c>
       <c r="C11">
-        <v>0.021</v>
+        <v>0.201</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>61.5</v>
+        <v>71.25</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1230,19 +1230,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.049</v>
+        <v>0.46</v>
       </c>
       <c r="C12">
-        <v>1.75</v>
+        <v>0.577</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>61.5</v>
+        <v>71.25</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1253,19 +1253,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>21.496</v>
       </c>
       <c r="C13">
-        <v>22.589</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>27.75</v>
+        <v>75</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1276,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>9.848000000000001</v>
       </c>
       <c r="C14">
-        <v>21.054</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>64.75</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>17.012</v>
       </c>
       <c r="C15">
-        <v>22.432</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,19 +1322,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>18.005</v>
       </c>
       <c r="C16">
-        <v>8.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1345,19 +1345,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>0.043</v>
+        <v>41.113</v>
       </c>
       <c r="C17">
-        <v>4.847</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -1368,19 +1368,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.173</v>
+        <v>18.008</v>
       </c>
       <c r="C18">
-        <v>0.5610000000000001</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>37.5</v>
+        <v>64.75</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1391,19 +1391,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>18.411</v>
       </c>
       <c r="C19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>37.5</v>
+        <v>67.25</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,19 +1414,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>0.056</v>
+        <v>8.215</v>
       </c>
       <c r="C20">
-        <v>1.003</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>37.5</v>
+        <v>67.75</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>11.519</v>
+        <v>17.059</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>37.5</v>
+        <v>68.5</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>4.567</v>
+        <v>14.877</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>37.5</v>
+        <v>73.25</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,19 +1483,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>9.507999999999999</v>
+        <v>3.292</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -1506,19 +1506,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>4.926</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.095</v>
+        <v>16.799</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -1529,19 +1529,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>10.283</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>19.26</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>1.329</v>
+        <v>2.614</v>
       </c>
       <c r="C26">
-        <v>6.411</v>
+        <v>3.34</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C27">
-        <v>14.067</v>
+        <v>11.915</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C28">
-        <v>16.054</v>
+        <v>8.801</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1.602</v>
       </c>
       <c r="C29">
-        <v>26.84</v>
+        <v>0.038</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="C30">
-        <v>48.748</v>
+        <v>6.067</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,13 +1667,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1.844</v>
       </c>
       <c r="C31">
-        <v>62.539</v>
+        <v>0.711</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1.829</v>
       </c>
       <c r="C32">
-        <v>75.53100000000001</v>
+        <v>0.347</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C33">
-        <v>26.53</v>
+        <v>2.785</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.019</v>
+        <v>30.208</v>
       </c>
       <c r="C34">
-        <v>5.897</v>
+        <v>0.904</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>67.25</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>0.366</v>
+        <v>19.251</v>
       </c>
       <c r="C35">
-        <v>0.134</v>
+        <v>1.436</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>67.25</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.052</v>
+        <v>4.493</v>
       </c>
       <c r="C36">
-        <v>0.639</v>
+        <v>0.099</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>67.25</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>7.672</v>
       </c>
       <c r="C37">
-        <v>28.127</v>
+        <v>1.512</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>67.25</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>7.584</v>
+        <v>8.129</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.273</v>
+        <v>0.48</v>
       </c>
       <c r="C39">
-        <v>4.916</v>
+        <v>2.117</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="C40">
-        <v>15.39</v>
+        <v>0.006</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>44.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>19.724</v>
       </c>
       <c r="C41">
-        <v>14.749</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>44.5</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>6.214</v>
+        <v>46.866</v>
       </c>
       <c r="C42">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.001</v>
+        <v>4.49</v>
       </c>
       <c r="C43">
-        <v>14.397</v>
+        <v>0.005</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E43">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>8.666</v>
       </c>
       <c r="C44">
-        <v>18.888</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E44">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>3.068</v>
       </c>
       <c r="C45">
-        <v>19.923</v>
+        <v>0.057</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E45">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>20.771</v>
+        <v>7.884</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E46">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="C47">
-        <v>33.29</v>
+        <v>0.769</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E47">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>46.855</v>
+        <v>2.804</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E48">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C49">
-        <v>73.19799999999999</v>
+        <v>12.73</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E49">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C50">
-        <v>70.13200000000001</v>
+        <v>4.971</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E50">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C51">
-        <v>28.775</v>
+        <v>1.8</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E51">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>12.509</v>
+        <v>4.041</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>0.161</v>
+        <v>15.216</v>
       </c>
       <c r="C53">
-        <v>2.999</v>
+        <v>0.714</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>63.09</v>
       </c>
       <c r="C54">
-        <v>47.733</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>17.066</v>
       </c>
       <c r="C55">
-        <v>73.667</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="C56">
-        <v>88.682</v>
+        <v>1.045</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E56">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.036</v>
+        <v>0.019</v>
       </c>
       <c r="C57">
-        <v>16.496</v>
+        <v>2.065</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E57">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.953</v>
+        <v>1.783</v>
       </c>
       <c r="C58">
-        <v>0.985</v>
+        <v>0.04</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>1.127</v>
+        <v>6.531</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1.734</v>
       </c>
       <c r="C60">
-        <v>20.531</v>
+        <v>0.036</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>6.127</v>
       </c>
       <c r="C61">
-        <v>34.428</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="C62">
-        <v>33.612</v>
+        <v>0.417</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.095</v>
+        <v>0.264</v>
       </c>
       <c r="C63">
-        <v>1.145</v>
+        <v>0.267</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C64">
-        <v>2.615</v>
+        <v>0.324</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>0.038</v>
+        <v>2.15</v>
       </c>
       <c r="C65">
-        <v>4.388</v>
+        <v>0.068</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>1.757</v>
+        <v>0.271</v>
       </c>
       <c r="C66">
-        <v>19.597</v>
+        <v>0.497</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>31.784</v>
+        <v>0.442</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>20.792</v>
+        <v>0.385</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>11.369</v>
+        <v>4.069</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>0.746</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>15.845</v>
+        <v>1.9</v>
       </c>
       <c r="C70">
-        <v>0.076</v>
+        <v>0.54</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>6.052</v>
+        <v>3.109</v>
       </c>
       <c r="C71">
-        <v>0.723</v>
+        <v>0.004</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.141</v>
+        <v>2.865</v>
       </c>
       <c r="C72">
-        <v>12.446</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>9.816000000000001</v>
       </c>
       <c r="C73">
-        <v>25.376</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="C74">
-        <v>26.27</v>
+        <v>1.249</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>27.971</v>
       </c>
       <c r="C75">
-        <v>23.931</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>5.333</v>
+        <v>35.195</v>
       </c>
       <c r="C76">
-        <v>0.649</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>73.25</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>6.777</v>
+        <v>47.354</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>73.75</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.443</v>
+        <v>31.202</v>
       </c>
       <c r="C78">
-        <v>32.457</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>65.75</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>4.177</v>
+        <v>45.021</v>
       </c>
       <c r="C79">
-        <v>0.439</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>99.5</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>13.441</v>
+        <v>35.902</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E80">
-        <v>99.5</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>10.71</v>
+        <v>40.171</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E81">
-        <v>56.25</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,19 +2840,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>38.812</v>
+        <v>2.517</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="E82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2863,16 +2863,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>31.255</v>
+        <v>2.918</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>9.117000000000001</v>
+        <v>0.395</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>0.305</v>
       </c>
       <c r="D84">
         <v>25</v>
@@ -2909,16 +2909,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>4.811</v>
+        <v>0.006</v>
       </c>
       <c r="C85">
-        <v>1.325</v>
+        <v>2.884</v>
       </c>
       <c r="D85">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -2932,16 +2932,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>1.407</v>
+        <v>36.666</v>
       </c>
       <c r="C86">
-        <v>8.935</v>
+        <v>0.29</v>
       </c>
       <c r="D86">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>35.482</v>
       </c>
       <c r="C87">
-        <v>7.874</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>17.619</v>
       </c>
       <c r="C88">
-        <v>20.488</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>21.614</v>
       </c>
       <c r="C89">
-        <v>53.653</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>12.029</v>
       </c>
       <c r="C90">
-        <v>38.436</v>
+        <v>0.278</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>5.865</v>
       </c>
       <c r="C91">
-        <v>19.159</v>
+        <v>0.082</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C92">
-        <v>25.061</v>
+        <v>0.298</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.949</v>
       </c>
       <c r="C93">
-        <v>30.823</v>
+        <v>1.97</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.296</v>
+        <v>7.681</v>
       </c>
       <c r="C94">
-        <v>3.482</v>
+        <v>0.048</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>0.056</v>
+        <v>2.555</v>
       </c>
       <c r="C95">
-        <v>0.138</v>
+        <v>0.008</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.137</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C96">
-        <v>0.05</v>
+        <v>0.064</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
-        <v>8.042999999999999</v>
+        <v>1.356</v>
       </c>
       <c r="C97">
-        <v>0.402</v>
+        <v>0.456</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>4.102</v>
       </c>
       <c r="C98">
-        <v>6.6</v>
+        <v>0.107</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>4.102</v>
       </c>
       <c r="C99">
-        <v>6.6</v>
+        <v>0.107</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>10.96</v>
       </c>
       <c r="C100">
-        <v>2.719</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>10.96</v>
       </c>
       <c r="C101">
-        <v>2.719</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>11.526</v>
       </c>
       <c r="C102">
-        <v>19.815</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>11.526</v>
       </c>
       <c r="C103">
-        <v>19.815</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>6.746</v>
       </c>
       <c r="C104">
-        <v>56.953</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>6.746</v>
       </c>
       <c r="C105">
-        <v>56.953</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>7.013</v>
       </c>
       <c r="C106">
-        <v>47.547</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>7.013</v>
       </c>
       <c r="C107">
-        <v>47.547</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>20.177</v>
       </c>
       <c r="C108">
-        <v>15.928</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>20.177</v>
       </c>
       <c r="C109">
-        <v>15.928</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>21.242</v>
       </c>
       <c r="C110">
-        <v>72.093</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>21.242</v>
       </c>
       <c r="C111">
-        <v>72.093</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,19 +3530,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>5.349</v>
       </c>
       <c r="C112">
-        <v>24.24</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>71.25</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>8</v>
@@ -3553,19 +3553,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>5.349</v>
       </c>
       <c r="C113">
-        <v>24.24</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>71.25</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>8</v>
@@ -3576,19 +3576,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46133.08333333334</v>
+        <v>46134.08333333334</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1.139</v>
       </c>
       <c r="C114">
-        <v>11.147</v>
+        <v>0.11</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>71.25</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>9</v>
@@ -3599,19 +3599,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46133.09375</v>
+        <v>46134.09375</v>
       </c>
       <c r="B115">
-        <v>0.218</v>
+        <v>5.038</v>
       </c>
       <c r="C115">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>71.25</v>
+        <v>0</v>
       </c>
       <c r="F115">
         <v>10</v>
@@ -3622,19 +3622,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46133.10416666666</v>
+        <v>46134.10416666666</v>
       </c>
       <c r="B116">
-        <v>0.46</v>
+        <v>7.304</v>
       </c>
       <c r="C116">
-        <v>0.577</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>71.25</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>11</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46133.11458333334</v>
+        <v>46134.11458333334</v>
       </c>
       <c r="B117">
-        <v>21.496</v>
+        <v>3.821</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>12</v>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46133.125</v>
+        <v>46134.125</v>
       </c>
       <c r="B118">
-        <v>9.848000000000001</v>
+        <v>5.28</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>64.75</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>13</v>
@@ -3691,19 +3691,19 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46133.13541666666</v>
+        <v>46134.13541666666</v>
       </c>
       <c r="B119">
-        <v>17.012</v>
+        <v>1.567</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>14</v>
@@ -3714,19 +3714,19 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46133.14583333334</v>
+        <v>46134.14583333334</v>
       </c>
       <c r="B120">
-        <v>18.005</v>
+        <v>0.219</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="D120">
         <v>0</v>
       </c>
       <c r="E120">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="F120">
         <v>15</v>
@@ -3737,19 +3737,19 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46133.15625</v>
+        <v>46134.15625</v>
       </c>
       <c r="B121">
-        <v>41.113</v>
+        <v>1.85</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>16</v>
@@ -3760,19 +3760,19 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46133.16666666666</v>
+        <v>46134.16666666666</v>
       </c>
       <c r="B122">
-        <v>18.008</v>
+        <v>0.44</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>64.75</v>
+        <v>0</v>
       </c>
       <c r="F122">
         <v>17</v>
@@ -3783,19 +3783,19 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46133.17708333334</v>
+        <v>46134.17708333334</v>
       </c>
       <c r="B123">
-        <v>18.411</v>
+        <v>2.425</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123">
-        <v>67.25</v>
+        <v>0</v>
       </c>
       <c r="F123">
         <v>18</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46133.1875</v>
+        <v>46134.1875</v>
       </c>
       <c r="B124">
-        <v>8.215</v>
+        <v>13.145</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>67.75</v>
+        <v>0</v>
       </c>
       <c r="F124">
         <v>19</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46133.19791666666</v>
+        <v>46134.19791666666</v>
       </c>
       <c r="B125">
-        <v>17.059</v>
+        <v>5.993</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <v>68.5</v>
+        <v>0</v>
       </c>
       <c r="F125">
         <v>20</v>
@@ -3852,19 +3852,19 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46133.20833333334</v>
+        <v>46134.20833333334</v>
       </c>
       <c r="B126">
-        <v>14.877</v>
+        <v>2.874</v>
       </c>
       <c r="C126">
-        <v>0.467</v>
+        <v>1.896</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>73.25</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>21</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46133.21875</v>
+        <v>46134.21875</v>
       </c>
       <c r="B127">
-        <v>3.292</v>
+        <v>1.65</v>
       </c>
       <c r="C127">
-        <v>0.177</v>
+        <v>0.014</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46133.22916666666</v>
+        <v>46134.22916666666</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>0.829</v>
       </c>
       <c r="C128">
-        <v>16.799</v>
+        <v>0.002</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46133.23958333334</v>
+        <v>46134.23958333334</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="C129">
-        <v>19.26</v>
+        <v>0.04</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,19 +3944,19 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46133.25</v>
+        <v>46134.25</v>
       </c>
       <c r="B130">
-        <v>2.614</v>
+        <v>1.177</v>
       </c>
       <c r="C130">
-        <v>3.34</v>
+        <v>7.744</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F130">
         <v>25</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46133.26041666666</v>
+        <v>46134.26041666666</v>
       </c>
       <c r="B131">
-        <v>0.6870000000000001</v>
+        <v>2.475</v>
       </c>
       <c r="C131">
-        <v>11.915</v>
+        <v>0.004</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>26</v>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46133.27083333334</v>
+        <v>46134.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.006</v>
+        <v>2.679</v>
       </c>
       <c r="C132">
-        <v>8.801</v>
+        <v>0.003</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>27</v>
@@ -4013,19 +4013,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46133.28125</v>
+        <v>46134.28125</v>
       </c>
       <c r="B133">
-        <v>1.602</v>
+        <v>0.982</v>
       </c>
       <c r="C133">
-        <v>0.038</v>
+        <v>0.206</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>28</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46133.29166666666</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
       <c r="C134">
-        <v>6.067</v>
+        <v>0.671</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46133.30208333334</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="B135">
-        <v>1.844</v>
+        <v>0.019</v>
       </c>
       <c r="C135">
-        <v>0.711</v>
+        <v>8.234</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46133.3125</v>
+        <v>46134.3125</v>
       </c>
       <c r="B136">
-        <v>1.829</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0.347</v>
+        <v>17.516</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46133.32291666666</v>
+        <v>46134.32291666666</v>
       </c>
       <c r="B137">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="C137">
-        <v>2.785</v>
+        <v>4.131</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F137">
         <v>32</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46133.33333333334</v>
+        <v>46134.33333333334</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>0.791</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F138">
         <v>33</v>
@@ -4151,19 +4151,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46133.34375</v>
+        <v>46134.34375</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>3.501</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F139">
         <v>34</v>
@@ -4174,19 +4174,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46133.35416666666</v>
+        <v>46134.35416666666</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>8.728999999999999</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F140">
         <v>35</v>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46133.36458333334</v>
+        <v>46134.36458333334</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>7.194</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F141">
         <v>36</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46133.375</v>
+        <v>46134.375</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>20.478</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -4232,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F142">
         <v>37</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46133.38541666666</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>6.551</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F143">
         <v>38</v>
@@ -4266,19 +4266,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46133.39583333334</v>
+        <v>46134.39583333334</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>2.169</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>2.796</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F144">
         <v>39</v>
@@ -4289,13 +4289,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46133.40625</v>
+        <v>46134.40625</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>2.807</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46133.41666666666</v>
+        <v>46134.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>31.798</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4335,13 +4335,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46133.42708333334</v>
+        <v>46134.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>67.464</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46133.4375</v>
+        <v>46134.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F148">
         <v>43</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46133.44791666666</v>
+        <v>46134.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F149">
         <v>44</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46133.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46133.46875</v>
+        <v>46134.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46133.47916666666</v>
+        <v>46134.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46133.48958333334</v>
+        <v>46134.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46133.5</v>
+        <v>46134.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46133.51041666666</v>
+        <v>46134.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46133.52083333334</v>
+        <v>46134.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46133.53125</v>
+        <v>46134.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46133.54166666666</v>
+        <v>46134.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46133.55208333334</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46133.5625</v>
+        <v>46134.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46133.57291666666</v>
+        <v>46134.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46133.58333333334</v>
+        <v>46134.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46133.59375</v>
+        <v>46134.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46133.60416666666</v>
+        <v>46134.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46133.61458333334</v>
+        <v>46134.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46133.625</v>
+        <v>46134.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46133.63541666666</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46133.64583333334</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46133.65625</v>
+        <v>46134.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46133.66666666666</v>
+        <v>46134.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46133.67708333334</v>
+        <v>46134.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46133.6875</v>
+        <v>46134.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46133.69791666666</v>
+        <v>46134.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46133.70833333334</v>
+        <v>46134.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46133.71875</v>
+        <v>46134.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46133.72916666666</v>
+        <v>46134.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46133.73958333334</v>
+        <v>46134.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46133.75</v>
+        <v>46134.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46133.76041666666</v>
+        <v>46134.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46133.77083333334</v>
+        <v>46134.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46133.78125</v>
+        <v>46134.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46133.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46133.80208333334</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46133.8125</v>
+        <v>46134.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46133.82291666666</v>
+        <v>46134.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46133.83333333334</v>
+        <v>46134.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46133.84375</v>
+        <v>46134.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46133.85416666666</v>
+        <v>46134.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46133.86458333334</v>
+        <v>46134.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46133.875</v>
+        <v>46134.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46133.88541666666</v>
+        <v>46134.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46133.89583333334</v>
+        <v>46134.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46133.90625</v>
+        <v>46134.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46133.91666666666</v>
+        <v>46134.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46133.92708333334</v>
+        <v>46134.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46133.9375</v>
+        <v>46134.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46133.94791666666</v>
+        <v>46134.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46133.95833333334</v>
+        <v>46134.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46133.96875</v>
+        <v>46134.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46133.97916666666</v>
+        <v>46134.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46133.98958333334</v>
+        <v>46134.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>05.05.20261</t>
-  </si>
-  <si>
-    <t>05.05.20262</t>
-  </si>
-  <si>
-    <t>05.05.20263</t>
-  </si>
-  <si>
-    <t>05.05.20264</t>
-  </si>
-  <si>
-    <t>05.05.20265</t>
-  </si>
-  <si>
-    <t>05.05.20266</t>
-  </si>
-  <si>
-    <t>05.05.20267</t>
-  </si>
-  <si>
-    <t>05.05.20268</t>
-  </si>
-  <si>
-    <t>05.05.20269</t>
-  </si>
-  <si>
-    <t>05.05.202610</t>
-  </si>
-  <si>
-    <t>05.05.202611</t>
-  </si>
-  <si>
-    <t>05.05.202612</t>
-  </si>
-  <si>
-    <t>05.05.202613</t>
-  </si>
-  <si>
-    <t>05.05.202614</t>
-  </si>
-  <si>
-    <t>05.05.202615</t>
-  </si>
-  <si>
-    <t>05.05.202616</t>
-  </si>
-  <si>
-    <t>05.05.202617</t>
-  </si>
-  <si>
-    <t>05.05.202618</t>
-  </si>
-  <si>
-    <t>05.05.202619</t>
-  </si>
-  <si>
-    <t>05.05.202620</t>
-  </si>
-  <si>
-    <t>05.05.202621</t>
-  </si>
-  <si>
-    <t>05.05.202622</t>
-  </si>
-  <si>
-    <t>05.05.202623</t>
-  </si>
-  <si>
-    <t>05.05.202624</t>
-  </si>
-  <si>
-    <t>05.05.202625</t>
-  </si>
-  <si>
-    <t>05.05.202626</t>
-  </si>
-  <si>
-    <t>05.05.202627</t>
-  </si>
-  <si>
-    <t>05.05.202628</t>
-  </si>
-  <si>
-    <t>05.05.202629</t>
-  </si>
-  <si>
-    <t>05.05.202630</t>
-  </si>
-  <si>
-    <t>05.05.202631</t>
-  </si>
-  <si>
-    <t>05.05.202632</t>
-  </si>
-  <si>
-    <t>05.05.202633</t>
-  </si>
-  <si>
-    <t>05.05.202634</t>
-  </si>
-  <si>
-    <t>05.05.202635</t>
-  </si>
-  <si>
-    <t>05.05.202636</t>
-  </si>
-  <si>
-    <t>05.05.202637</t>
-  </si>
-  <si>
-    <t>05.05.202638</t>
-  </si>
-  <si>
-    <t>05.05.202639</t>
-  </si>
-  <si>
-    <t>05.05.202640</t>
-  </si>
-  <si>
-    <t>05.05.202641</t>
-  </si>
-  <si>
-    <t>05.05.202642</t>
-  </si>
-  <si>
-    <t>05.05.202643</t>
-  </si>
-  <si>
-    <t>05.05.202644</t>
-  </si>
-  <si>
-    <t>05.05.202645</t>
-  </si>
-  <si>
-    <t>05.05.202646</t>
-  </si>
-  <si>
-    <t>05.05.202647</t>
-  </si>
-  <si>
-    <t>05.05.202648</t>
-  </si>
-  <si>
-    <t>05.05.202649</t>
-  </si>
-  <si>
-    <t>05.05.202650</t>
-  </si>
-  <si>
-    <t>05.05.202651</t>
-  </si>
-  <si>
-    <t>05.05.202652</t>
-  </si>
-  <si>
-    <t>05.05.202653</t>
-  </si>
-  <si>
-    <t>05.05.202654</t>
-  </si>
-  <si>
-    <t>05.05.202655</t>
-  </si>
-  <si>
-    <t>05.05.202656</t>
-  </si>
-  <si>
-    <t>05.05.202657</t>
-  </si>
-  <si>
-    <t>05.05.202658</t>
-  </si>
-  <si>
-    <t>05.05.202659</t>
-  </si>
-  <si>
-    <t>05.05.202660</t>
-  </si>
-  <si>
-    <t>05.05.202661</t>
-  </si>
-  <si>
-    <t>05.05.202662</t>
-  </si>
-  <si>
-    <t>05.05.202663</t>
-  </si>
-  <si>
-    <t>05.05.202664</t>
-  </si>
-  <si>
-    <t>05.05.202665</t>
-  </si>
-  <si>
-    <t>05.05.202666</t>
-  </si>
-  <si>
-    <t>05.05.202667</t>
-  </si>
-  <si>
-    <t>05.05.202668</t>
-  </si>
-  <si>
-    <t>05.05.202669</t>
-  </si>
-  <si>
-    <t>05.05.202670</t>
-  </si>
-  <si>
-    <t>05.05.202671</t>
-  </si>
-  <si>
-    <t>05.05.202672</t>
-  </si>
-  <si>
-    <t>05.05.202673</t>
-  </si>
-  <si>
-    <t>05.05.202674</t>
-  </si>
-  <si>
-    <t>05.05.202675</t>
-  </si>
-  <si>
-    <t>05.05.202676</t>
-  </si>
-  <si>
-    <t>05.05.202677</t>
-  </si>
-  <si>
-    <t>05.05.202678</t>
-  </si>
-  <si>
-    <t>05.05.202679</t>
-  </si>
-  <si>
-    <t>05.05.202680</t>
-  </si>
-  <si>
-    <t>05.05.202681</t>
-  </si>
-  <si>
-    <t>05.05.202682</t>
-  </si>
-  <si>
-    <t>05.05.202683</t>
-  </si>
-  <si>
-    <t>05.05.202684</t>
-  </si>
-  <si>
-    <t>05.05.202685</t>
-  </si>
-  <si>
-    <t>05.05.202686</t>
-  </si>
-  <si>
-    <t>05.05.202687</t>
-  </si>
-  <si>
-    <t>05.05.202688</t>
-  </si>
-  <si>
-    <t>05.05.202689</t>
-  </si>
-  <si>
-    <t>05.05.202690</t>
-  </si>
-  <si>
-    <t>05.05.202691</t>
-  </si>
-  <si>
-    <t>05.05.202692</t>
-  </si>
-  <si>
-    <t>05.05.202693</t>
-  </si>
-  <si>
-    <t>05.05.202694</t>
-  </si>
-  <si>
-    <t>05.05.202695</t>
-  </si>
-  <si>
-    <t>05.05.202696</t>
-  </si>
-  <si>
-    <t>06.05.20261</t>
-  </si>
-  <si>
-    <t>06.05.20262</t>
-  </si>
-  <si>
-    <t>06.05.20263</t>
-  </si>
-  <si>
-    <t>06.05.20264</t>
-  </si>
-  <si>
-    <t>06.05.20265</t>
-  </si>
-  <si>
-    <t>06.05.20266</t>
-  </si>
-  <si>
-    <t>06.05.20267</t>
-  </si>
-  <si>
-    <t>06.05.20268</t>
-  </si>
-  <si>
-    <t>06.05.20269</t>
-  </si>
-  <si>
-    <t>06.05.202610</t>
-  </si>
-  <si>
-    <t>06.05.202611</t>
-  </si>
-  <si>
-    <t>06.05.202612</t>
-  </si>
-  <si>
-    <t>06.05.202613</t>
-  </si>
-  <si>
-    <t>06.05.202614</t>
-  </si>
-  <si>
-    <t>06.05.202615</t>
-  </si>
-  <si>
-    <t>06.05.202616</t>
-  </si>
-  <si>
-    <t>06.05.202617</t>
-  </si>
-  <si>
-    <t>06.05.202618</t>
-  </si>
-  <si>
-    <t>06.05.202619</t>
-  </si>
-  <si>
-    <t>06.05.202620</t>
-  </si>
-  <si>
-    <t>06.05.202621</t>
-  </si>
-  <si>
-    <t>06.05.202622</t>
-  </si>
-  <si>
-    <t>06.05.202623</t>
-  </si>
-  <si>
-    <t>06.05.202624</t>
-  </si>
-  <si>
-    <t>06.05.202625</t>
-  </si>
-  <si>
-    <t>06.05.202626</t>
-  </si>
-  <si>
-    <t>06.05.202627</t>
-  </si>
-  <si>
-    <t>06.05.202628</t>
-  </si>
-  <si>
-    <t>06.05.202629</t>
-  </si>
-  <si>
-    <t>06.05.202630</t>
-  </si>
-  <si>
-    <t>06.05.202631</t>
-  </si>
-  <si>
-    <t>06.05.202632</t>
-  </si>
-  <si>
-    <t>06.05.202633</t>
-  </si>
-  <si>
-    <t>06.05.202634</t>
-  </si>
-  <si>
-    <t>06.05.202635</t>
-  </si>
-  <si>
-    <t>06.05.202636</t>
-  </si>
-  <si>
-    <t>06.05.202637</t>
-  </si>
-  <si>
-    <t>06.05.202638</t>
-  </si>
-  <si>
-    <t>06.05.202639</t>
-  </si>
-  <si>
-    <t>06.05.202640</t>
-  </si>
-  <si>
-    <t>06.05.202641</t>
-  </si>
-  <si>
-    <t>06.05.202642</t>
-  </si>
-  <si>
-    <t>06.05.202643</t>
-  </si>
-  <si>
-    <t>06.05.202644</t>
-  </si>
-  <si>
-    <t>06.05.202645</t>
-  </si>
-  <si>
-    <t>06.05.202646</t>
-  </si>
-  <si>
-    <t>06.05.202647</t>
-  </si>
-  <si>
-    <t>06.05.202648</t>
-  </si>
-  <si>
-    <t>06.05.202649</t>
-  </si>
-  <si>
-    <t>06.05.202650</t>
-  </si>
-  <si>
-    <t>06.05.202651</t>
-  </si>
-  <si>
-    <t>06.05.202652</t>
-  </si>
-  <si>
-    <t>06.05.202653</t>
-  </si>
-  <si>
-    <t>06.05.202654</t>
-  </si>
-  <si>
-    <t>06.05.202655</t>
-  </si>
-  <si>
-    <t>06.05.202656</t>
-  </si>
-  <si>
-    <t>06.05.202657</t>
-  </si>
-  <si>
-    <t>06.05.202658</t>
-  </si>
-  <si>
-    <t>06.05.202659</t>
-  </si>
-  <si>
-    <t>06.05.202660</t>
-  </si>
-  <si>
-    <t>06.05.202661</t>
-  </si>
-  <si>
-    <t>06.05.202662</t>
-  </si>
-  <si>
-    <t>06.05.202663</t>
-  </si>
-  <si>
-    <t>06.05.202664</t>
-  </si>
-  <si>
-    <t>06.05.202665</t>
-  </si>
-  <si>
-    <t>06.05.202666</t>
-  </si>
-  <si>
-    <t>06.05.202667</t>
-  </si>
-  <si>
-    <t>06.05.202668</t>
-  </si>
-  <si>
-    <t>06.05.202669</t>
-  </si>
-  <si>
-    <t>06.05.202670</t>
-  </si>
-  <si>
-    <t>06.05.202671</t>
-  </si>
-  <si>
-    <t>06.05.202672</t>
-  </si>
-  <si>
-    <t>06.05.202673</t>
-  </si>
-  <si>
-    <t>06.05.202674</t>
-  </si>
-  <si>
-    <t>06.05.202675</t>
-  </si>
-  <si>
-    <t>06.05.202676</t>
-  </si>
-  <si>
-    <t>06.05.202677</t>
-  </si>
-  <si>
-    <t>06.05.202678</t>
-  </si>
-  <si>
-    <t>06.05.202679</t>
-  </si>
-  <si>
-    <t>06.05.202680</t>
-  </si>
-  <si>
-    <t>06.05.202681</t>
-  </si>
-  <si>
-    <t>06.05.202682</t>
-  </si>
-  <si>
-    <t>06.05.202683</t>
-  </si>
-  <si>
-    <t>06.05.202684</t>
-  </si>
-  <si>
-    <t>06.05.202685</t>
-  </si>
-  <si>
-    <t>06.05.202686</t>
-  </si>
-  <si>
-    <t>06.05.202687</t>
-  </si>
-  <si>
-    <t>06.05.202688</t>
-  </si>
-  <si>
-    <t>06.05.202689</t>
-  </si>
-  <si>
-    <t>06.05.202690</t>
-  </si>
-  <si>
-    <t>06.05.202691</t>
-  </si>
-  <si>
-    <t>06.05.202692</t>
-  </si>
-  <si>
-    <t>06.05.202693</t>
-  </si>
-  <si>
-    <t>06.05.202694</t>
-  </si>
-  <si>
-    <t>06.05.202695</t>
-  </si>
-  <si>
-    <t>06.05.202696</t>
+    <t>07.05.20261</t>
+  </si>
+  <si>
+    <t>07.05.20262</t>
+  </si>
+  <si>
+    <t>07.05.20263</t>
+  </si>
+  <si>
+    <t>07.05.20264</t>
+  </si>
+  <si>
+    <t>07.05.20265</t>
+  </si>
+  <si>
+    <t>07.05.20266</t>
+  </si>
+  <si>
+    <t>07.05.20267</t>
+  </si>
+  <si>
+    <t>07.05.20268</t>
+  </si>
+  <si>
+    <t>07.05.20269</t>
+  </si>
+  <si>
+    <t>07.05.202610</t>
+  </si>
+  <si>
+    <t>07.05.202611</t>
+  </si>
+  <si>
+    <t>07.05.202612</t>
+  </si>
+  <si>
+    <t>07.05.202613</t>
+  </si>
+  <si>
+    <t>07.05.202614</t>
+  </si>
+  <si>
+    <t>07.05.202615</t>
+  </si>
+  <si>
+    <t>07.05.202616</t>
+  </si>
+  <si>
+    <t>07.05.202617</t>
+  </si>
+  <si>
+    <t>07.05.202618</t>
+  </si>
+  <si>
+    <t>07.05.202619</t>
+  </si>
+  <si>
+    <t>07.05.202620</t>
+  </si>
+  <si>
+    <t>07.05.202621</t>
+  </si>
+  <si>
+    <t>07.05.202622</t>
+  </si>
+  <si>
+    <t>07.05.202623</t>
+  </si>
+  <si>
+    <t>07.05.202624</t>
+  </si>
+  <si>
+    <t>07.05.202625</t>
+  </si>
+  <si>
+    <t>07.05.202626</t>
+  </si>
+  <si>
+    <t>07.05.202627</t>
+  </si>
+  <si>
+    <t>07.05.202628</t>
+  </si>
+  <si>
+    <t>07.05.202629</t>
+  </si>
+  <si>
+    <t>07.05.202630</t>
+  </si>
+  <si>
+    <t>07.05.202631</t>
+  </si>
+  <si>
+    <t>07.05.202632</t>
+  </si>
+  <si>
+    <t>07.05.202633</t>
+  </si>
+  <si>
+    <t>07.05.202634</t>
+  </si>
+  <si>
+    <t>07.05.202635</t>
+  </si>
+  <si>
+    <t>07.05.202636</t>
+  </si>
+  <si>
+    <t>07.05.202637</t>
+  </si>
+  <si>
+    <t>07.05.202638</t>
+  </si>
+  <si>
+    <t>07.05.202639</t>
+  </si>
+  <si>
+    <t>07.05.202640</t>
+  </si>
+  <si>
+    <t>07.05.202641</t>
+  </si>
+  <si>
+    <t>07.05.202642</t>
+  </si>
+  <si>
+    <t>07.05.202643</t>
+  </si>
+  <si>
+    <t>07.05.202644</t>
+  </si>
+  <si>
+    <t>07.05.202645</t>
+  </si>
+  <si>
+    <t>07.05.202646</t>
+  </si>
+  <si>
+    <t>07.05.202647</t>
+  </si>
+  <si>
+    <t>07.05.202648</t>
+  </si>
+  <si>
+    <t>07.05.202649</t>
+  </si>
+  <si>
+    <t>07.05.202650</t>
+  </si>
+  <si>
+    <t>07.05.202651</t>
+  </si>
+  <si>
+    <t>07.05.202652</t>
+  </si>
+  <si>
+    <t>07.05.202653</t>
+  </si>
+  <si>
+    <t>07.05.202654</t>
+  </si>
+  <si>
+    <t>07.05.202655</t>
+  </si>
+  <si>
+    <t>07.05.202656</t>
+  </si>
+  <si>
+    <t>07.05.202657</t>
+  </si>
+  <si>
+    <t>07.05.202658</t>
+  </si>
+  <si>
+    <t>07.05.202659</t>
+  </si>
+  <si>
+    <t>07.05.202660</t>
+  </si>
+  <si>
+    <t>07.05.202661</t>
+  </si>
+  <si>
+    <t>07.05.202662</t>
+  </si>
+  <si>
+    <t>07.05.202663</t>
+  </si>
+  <si>
+    <t>07.05.202664</t>
+  </si>
+  <si>
+    <t>07.05.202665</t>
+  </si>
+  <si>
+    <t>07.05.202666</t>
+  </si>
+  <si>
+    <t>07.05.202667</t>
+  </si>
+  <si>
+    <t>07.05.202668</t>
+  </si>
+  <si>
+    <t>07.05.202669</t>
+  </si>
+  <si>
+    <t>07.05.202670</t>
+  </si>
+  <si>
+    <t>07.05.202671</t>
+  </si>
+  <si>
+    <t>07.05.202672</t>
+  </si>
+  <si>
+    <t>07.05.202673</t>
+  </si>
+  <si>
+    <t>07.05.202674</t>
+  </si>
+  <si>
+    <t>07.05.202675</t>
+  </si>
+  <si>
+    <t>07.05.202676</t>
+  </si>
+  <si>
+    <t>07.05.202677</t>
+  </si>
+  <si>
+    <t>07.05.202678</t>
+  </si>
+  <si>
+    <t>07.05.202679</t>
+  </si>
+  <si>
+    <t>07.05.202680</t>
+  </si>
+  <si>
+    <t>07.05.202681</t>
+  </si>
+  <si>
+    <t>07.05.202682</t>
+  </si>
+  <si>
+    <t>07.05.202683</t>
+  </si>
+  <si>
+    <t>07.05.202684</t>
+  </si>
+  <si>
+    <t>07.05.202685</t>
+  </si>
+  <si>
+    <t>07.05.202686</t>
+  </si>
+  <si>
+    <t>07.05.202687</t>
+  </si>
+  <si>
+    <t>07.05.202688</t>
+  </si>
+  <si>
+    <t>07.05.202689</t>
+  </si>
+  <si>
+    <t>07.05.202690</t>
+  </si>
+  <si>
+    <t>07.05.202691</t>
+  </si>
+  <si>
+    <t>07.05.202692</t>
+  </si>
+  <si>
+    <t>07.05.202693</t>
+  </si>
+  <si>
+    <t>07.05.202694</t>
+  </si>
+  <si>
+    <t>07.05.202695</t>
+  </si>
+  <si>
+    <t>07.05.202696</t>
+  </si>
+  <si>
+    <t>08.05.20261</t>
+  </si>
+  <si>
+    <t>08.05.20262</t>
+  </si>
+  <si>
+    <t>08.05.20263</t>
+  </si>
+  <si>
+    <t>08.05.20264</t>
+  </si>
+  <si>
+    <t>08.05.20265</t>
+  </si>
+  <si>
+    <t>08.05.20266</t>
+  </si>
+  <si>
+    <t>08.05.20267</t>
+  </si>
+  <si>
+    <t>08.05.20268</t>
+  </si>
+  <si>
+    <t>08.05.20269</t>
+  </si>
+  <si>
+    <t>08.05.202610</t>
+  </si>
+  <si>
+    <t>08.05.202611</t>
+  </si>
+  <si>
+    <t>08.05.202612</t>
+  </si>
+  <si>
+    <t>08.05.202613</t>
+  </si>
+  <si>
+    <t>08.05.202614</t>
+  </si>
+  <si>
+    <t>08.05.202615</t>
+  </si>
+  <si>
+    <t>08.05.202616</t>
+  </si>
+  <si>
+    <t>08.05.202617</t>
+  </si>
+  <si>
+    <t>08.05.202618</t>
+  </si>
+  <si>
+    <t>08.05.202619</t>
+  </si>
+  <si>
+    <t>08.05.202620</t>
+  </si>
+  <si>
+    <t>08.05.202621</t>
+  </si>
+  <si>
+    <t>08.05.202622</t>
+  </si>
+  <si>
+    <t>08.05.202623</t>
+  </si>
+  <si>
+    <t>08.05.202624</t>
+  </si>
+  <si>
+    <t>08.05.202625</t>
+  </si>
+  <si>
+    <t>08.05.202626</t>
+  </si>
+  <si>
+    <t>08.05.202627</t>
+  </si>
+  <si>
+    <t>08.05.202628</t>
+  </si>
+  <si>
+    <t>08.05.202629</t>
+  </si>
+  <si>
+    <t>08.05.202630</t>
+  </si>
+  <si>
+    <t>08.05.202631</t>
+  </si>
+  <si>
+    <t>08.05.202632</t>
+  </si>
+  <si>
+    <t>08.05.202633</t>
+  </si>
+  <si>
+    <t>08.05.202634</t>
+  </si>
+  <si>
+    <t>08.05.202635</t>
+  </si>
+  <si>
+    <t>08.05.202636</t>
+  </si>
+  <si>
+    <t>08.05.202637</t>
+  </si>
+  <si>
+    <t>08.05.202638</t>
+  </si>
+  <si>
+    <t>08.05.202639</t>
+  </si>
+  <si>
+    <t>08.05.202640</t>
+  </si>
+  <si>
+    <t>08.05.202641</t>
+  </si>
+  <si>
+    <t>08.05.202642</t>
+  </si>
+  <si>
+    <t>08.05.202643</t>
+  </si>
+  <si>
+    <t>08.05.202644</t>
+  </si>
+  <si>
+    <t>08.05.202645</t>
+  </si>
+  <si>
+    <t>08.05.202646</t>
+  </si>
+  <si>
+    <t>08.05.202647</t>
+  </si>
+  <si>
+    <t>08.05.202648</t>
+  </si>
+  <si>
+    <t>08.05.202649</t>
+  </si>
+  <si>
+    <t>08.05.202650</t>
+  </si>
+  <si>
+    <t>08.05.202651</t>
+  </si>
+  <si>
+    <t>08.05.202652</t>
+  </si>
+  <si>
+    <t>08.05.202653</t>
+  </si>
+  <si>
+    <t>08.05.202654</t>
+  </si>
+  <si>
+    <t>08.05.202655</t>
+  </si>
+  <si>
+    <t>08.05.202656</t>
+  </si>
+  <si>
+    <t>08.05.202657</t>
+  </si>
+  <si>
+    <t>08.05.202658</t>
+  </si>
+  <si>
+    <t>08.05.202659</t>
+  </si>
+  <si>
+    <t>08.05.202660</t>
+  </si>
+  <si>
+    <t>08.05.202661</t>
+  </si>
+  <si>
+    <t>08.05.202662</t>
+  </si>
+  <si>
+    <t>08.05.202663</t>
+  </si>
+  <si>
+    <t>08.05.202664</t>
+  </si>
+  <si>
+    <t>08.05.202665</t>
+  </si>
+  <si>
+    <t>08.05.202666</t>
+  </si>
+  <si>
+    <t>08.05.202667</t>
+  </si>
+  <si>
+    <t>08.05.202668</t>
+  </si>
+  <si>
+    <t>08.05.202669</t>
+  </si>
+  <si>
+    <t>08.05.202670</t>
+  </si>
+  <si>
+    <t>08.05.202671</t>
+  </si>
+  <si>
+    <t>08.05.202672</t>
+  </si>
+  <si>
+    <t>08.05.202673</t>
+  </si>
+  <si>
+    <t>08.05.202674</t>
+  </si>
+  <si>
+    <t>08.05.202675</t>
+  </si>
+  <si>
+    <t>08.05.202676</t>
+  </si>
+  <si>
+    <t>08.05.202677</t>
+  </si>
+  <si>
+    <t>08.05.202678</t>
+  </si>
+  <si>
+    <t>08.05.202679</t>
+  </si>
+  <si>
+    <t>08.05.202680</t>
+  </si>
+  <si>
+    <t>08.05.202681</t>
+  </si>
+  <si>
+    <t>08.05.202682</t>
+  </si>
+  <si>
+    <t>08.05.202683</t>
+  </si>
+  <si>
+    <t>08.05.202684</t>
+  </si>
+  <si>
+    <t>08.05.202685</t>
+  </si>
+  <si>
+    <t>08.05.202686</t>
+  </si>
+  <si>
+    <t>08.05.202687</t>
+  </si>
+  <si>
+    <t>08.05.202688</t>
+  </si>
+  <si>
+    <t>08.05.202689</t>
+  </si>
+  <si>
+    <t>08.05.202690</t>
+  </si>
+  <si>
+    <t>08.05.202691</t>
+  </si>
+  <si>
+    <t>08.05.202692</t>
+  </si>
+  <si>
+    <t>08.05.202693</t>
+  </si>
+  <si>
+    <t>08.05.202694</t>
+  </si>
+  <si>
+    <t>08.05.202695</t>
+  </si>
+  <si>
+    <t>08.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,16 +1000,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C2">
-        <v>16.471</v>
+        <v>1.272</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1023,16 +1023,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46147.01041666666</v>
+        <v>46149.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.279</v>
+        <v>0.002</v>
       </c>
       <c r="C3">
-        <v>0.322</v>
+        <v>4.127</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46147.02083333334</v>
+        <v>46149.02083333334</v>
       </c>
       <c r="B4">
-        <v>17.724</v>
+        <v>0.026</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46147.03125</v>
+        <v>46149.03125</v>
       </c>
       <c r="B5">
-        <v>35.395</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>17.63</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,16 +1092,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46147.04166666666</v>
+        <v>46149.04166666666</v>
       </c>
       <c r="B6">
-        <v>23.101</v>
+        <v>0.108</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1115,16 +1115,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46147.05208333334</v>
+        <v>46149.05208333334</v>
       </c>
       <c r="B7">
-        <v>28.657</v>
+        <v>0.107</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1138,16 +1138,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46147.0625</v>
+        <v>46149.0625</v>
       </c>
       <c r="B8">
-        <v>33.666</v>
+        <v>0.134</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>4.002</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1161,16 +1161,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46147.07291666666</v>
+        <v>46149.07291666666</v>
       </c>
       <c r="B9">
-        <v>36.79</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>21.301</v>
       </c>
       <c r="D9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1184,16 +1184,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46147.08333333334</v>
+        <v>46149.08333333334</v>
       </c>
       <c r="B10">
-        <v>20.162</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>6.815</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1207,16 +1207,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46147.09375</v>
+        <v>46149.09375</v>
       </c>
       <c r="B11">
-        <v>14.119</v>
+        <v>0.057</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2.563</v>
       </c>
       <c r="D11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1230,16 +1230,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46147.10416666666</v>
+        <v>46149.10416666666</v>
       </c>
       <c r="B12">
-        <v>23.055</v>
+        <v>0.001</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1.185</v>
       </c>
       <c r="D12">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1253,16 +1253,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46147.11458333334</v>
+        <v>46149.11458333334</v>
       </c>
       <c r="B13">
-        <v>9.871</v>
+        <v>0.05</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2.641</v>
       </c>
       <c r="D13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1276,16 +1276,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46147.125</v>
+        <v>46149.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>2.182</v>
+        <v>11.617</v>
       </c>
       <c r="D14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1299,16 +1299,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46147.13541666666</v>
+        <v>46149.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>4.853</v>
+        <v>8.843</v>
       </c>
       <c r="D15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1322,16 +1322,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46147.14583333334</v>
+        <v>46149.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.638</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0.045</v>
+        <v>13.031</v>
       </c>
       <c r="D16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46147.15625</v>
+        <v>46149.15625</v>
       </c>
       <c r="B17">
-        <v>2.986</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.091</v>
+        <v>8.565</v>
       </c>
       <c r="D17">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1368,16 +1368,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46147.16666666666</v>
+        <v>46149.16666666666</v>
       </c>
       <c r="B18">
-        <v>57.641</v>
+        <v>0.005</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>11.242</v>
       </c>
       <c r="D18">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1391,16 +1391,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46147.17708333334</v>
+        <v>46149.17708333334</v>
       </c>
       <c r="B19">
-        <v>21.808</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>26.116</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46147.1875</v>
+        <v>46149.1875</v>
       </c>
       <c r="B20">
-        <v>36.531</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>23.771</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46147.19791666666</v>
+        <v>46149.19791666666</v>
       </c>
       <c r="B21">
-        <v>30.914</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>27.086</v>
       </c>
       <c r="D21">
-        <v>98.5</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1460,16 +1460,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46147.20833333334</v>
+        <v>46149.20833333334</v>
       </c>
       <c r="B22">
-        <v>12.886</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>29.599</v>
       </c>
       <c r="D22">
-        <v>98.5</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1483,16 +1483,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46147.21875</v>
+        <v>46149.21875</v>
       </c>
       <c r="B23">
-        <v>18.846</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>29.279</v>
       </c>
       <c r="D23">
-        <v>98.5</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1506,16 +1506,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46147.22916666666</v>
+        <v>46149.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.392</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>1.11</v>
+        <v>16.211</v>
       </c>
       <c r="D24">
-        <v>116.5</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1529,16 +1529,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46147.23958333334</v>
+        <v>46149.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.707</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1.215</v>
+        <v>14.446</v>
       </c>
       <c r="D25">
-        <v>119.5</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1552,16 +1552,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46147.25</v>
+        <v>46149.25</v>
       </c>
       <c r="B26">
-        <v>32.449</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>18.054</v>
       </c>
       <c r="D26">
-        <v>121.5</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1575,16 +1575,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46147.26041666666</v>
+        <v>46149.26041666666</v>
       </c>
       <c r="B27">
-        <v>6.013</v>
+        <v>0.02</v>
       </c>
       <c r="C27">
-        <v>0.107</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="D27">
-        <v>139.5</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46147.27083333334</v>
+        <v>46149.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="C28">
-        <v>6.596</v>
+        <v>3.732</v>
       </c>
       <c r="D28">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46147.28125</v>
+        <v>46149.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="C29">
-        <v>33.255</v>
+        <v>0.858</v>
       </c>
       <c r="D29">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,19 +1644,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46147.29166666666</v>
+        <v>46149.29166666666</v>
       </c>
       <c r="B30">
-        <v>24.223</v>
+        <v>14.367</v>
       </c>
       <c r="C30">
-        <v>0.878</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,10 +1667,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46147.30208333334</v>
+        <v>46149.30208333334</v>
       </c>
       <c r="B31">
-        <v>38.381</v>
+        <v>18.569</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46147.3125</v>
+        <v>46149.3125</v>
       </c>
       <c r="B32">
-        <v>15.814</v>
+        <v>18.173</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46147.32291666666</v>
+        <v>46149.32291666666</v>
       </c>
       <c r="B33">
-        <v>28.41</v>
+        <v>1.141</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46147.33333333334</v>
+        <v>46149.33333333334</v>
       </c>
       <c r="B34">
-        <v>75.374</v>
+        <v>4.3</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46147.34375</v>
+        <v>46149.34375</v>
       </c>
       <c r="B35">
-        <v>88.93300000000001</v>
+        <v>10.841</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46147.35416666666</v>
+        <v>46149.35416666666</v>
       </c>
       <c r="B36">
-        <v>86.43600000000001</v>
+        <v>12.686</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +1805,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46147.36458333334</v>
+        <v>46149.36458333334</v>
       </c>
       <c r="B37">
-        <v>28.082</v>
+        <v>12.309</v>
       </c>
       <c r="C37">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="D37">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46147.375</v>
+        <v>46149.375</v>
       </c>
       <c r="B38">
-        <v>42.777</v>
+        <v>23.443</v>
       </c>
       <c r="C38">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>76.75</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46147.38541666666</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="B39">
-        <v>25.095</v>
+        <v>18.379</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>76.75</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46147.39583333334</v>
+        <v>46149.39583333334</v>
       </c>
       <c r="B40">
-        <v>13.759</v>
+        <v>16.636</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>76.75</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46147.40625</v>
+        <v>46149.40625</v>
       </c>
       <c r="B41">
-        <v>2.97</v>
+        <v>2.322</v>
       </c>
       <c r="C41">
-        <v>2.456</v>
+        <v>0.056</v>
       </c>
       <c r="D41">
-        <v>76.75</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1920,16 +1920,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46147.41666666666</v>
+        <v>46149.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2.111</v>
       </c>
       <c r="C42">
-        <v>5.169</v>
+        <v>0.616</v>
       </c>
       <c r="D42">
-        <v>81.5</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1943,16 +1943,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46147.42708333334</v>
+        <v>46149.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C43">
-        <v>6.85</v>
+        <v>10.108</v>
       </c>
       <c r="D43">
-        <v>81.5</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46147.4375</v>
+        <v>46149.4375</v>
       </c>
       <c r="B44">
-        <v>4.039</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>1.664</v>
+        <v>9.699</v>
       </c>
       <c r="D44">
-        <v>81.5</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1989,16 +1989,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46147.44791666666</v>
+        <v>46149.44791666666</v>
       </c>
       <c r="B45">
-        <v>4.604</v>
+        <v>0.015</v>
       </c>
       <c r="C45">
-        <v>8.589</v>
+        <v>2.955</v>
       </c>
       <c r="D45">
-        <v>81.5</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2012,16 +2012,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46147.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>0.665</v>
       </c>
       <c r="C46">
-        <v>29.042</v>
+        <v>0.173</v>
       </c>
       <c r="D46">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2035,16 +2035,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46147.46875</v>
+        <v>46149.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="C47">
-        <v>18.129</v>
+        <v>1.69</v>
       </c>
       <c r="D47">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2058,16 +2058,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46147.47916666666</v>
+        <v>46149.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="C48">
-        <v>15.136</v>
+        <v>4.124</v>
       </c>
       <c r="D48">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2081,16 +2081,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46147.48958333334</v>
+        <v>46149.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1.707</v>
       </c>
       <c r="C49">
-        <v>23.534</v>
+        <v>0.107</v>
       </c>
       <c r="D49">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2104,16 +2104,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46147.5</v>
+        <v>46149.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="C50">
-        <v>79.47199999999999</v>
+        <v>0.173</v>
       </c>
       <c r="D50">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46147.51041666666</v>
+        <v>46149.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="C51">
-        <v>67.98099999999999</v>
+        <v>0.144</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46147.52083333334</v>
+        <v>46149.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.029</v>
+        <v>0.324</v>
       </c>
       <c r="C52">
-        <v>2.923</v>
+        <v>0.044</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46147.53125</v>
+        <v>46149.53125</v>
       </c>
       <c r="B53">
-        <v>0.192</v>
+        <v>0.14</v>
       </c>
       <c r="C53">
-        <v>0.258</v>
+        <v>0.198</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46147.54166666666</v>
+        <v>46149.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.289</v>
+        <v>10.492</v>
       </c>
       <c r="C54">
-        <v>0.07199999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46147.55208333334</v>
+        <v>46149.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.068</v>
+        <v>11.772</v>
       </c>
       <c r="C55">
-        <v>4.798</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46147.5625</v>
+        <v>46149.5625</v>
       </c>
       <c r="B56">
-        <v>0.031</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C56">
-        <v>7.496</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46147.57291666666</v>
+        <v>46149.57291666666</v>
       </c>
       <c r="B57">
-        <v>4.116</v>
+        <v>0.589</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46147.58333333334</v>
+        <v>46149.58333333334</v>
       </c>
       <c r="B58">
-        <v>24.107</v>
+        <v>0.786</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46147.59375</v>
+        <v>46149.59375</v>
       </c>
       <c r="B59">
-        <v>4.714</v>
+        <v>0.098</v>
       </c>
       <c r="C59">
-        <v>1.195</v>
+        <v>0.742</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46147.60416666666</v>
+        <v>46149.60416666666</v>
       </c>
       <c r="B60">
-        <v>1.734</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0.161</v>
+        <v>2.537</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46147.61458333334</v>
+        <v>46149.61458333334</v>
       </c>
       <c r="B61">
-        <v>8.590999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="C61">
-        <v>1.255</v>
+        <v>0.773</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46147.625</v>
+        <v>46149.625</v>
       </c>
       <c r="B62">
-        <v>23.482</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>14.057</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46147.63541666666</v>
+        <v>46149.63541666666</v>
       </c>
       <c r="B63">
-        <v>18.001</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>19.762</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46147.64583333334</v>
+        <v>46149.64583333334</v>
       </c>
       <c r="B64">
-        <v>18.64</v>
+        <v>1.251</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46147.65625</v>
+        <v>46149.65625</v>
       </c>
       <c r="B65">
-        <v>22.956</v>
+        <v>3.251</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46147.66666666666</v>
+        <v>46149.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.08799999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="C66">
-        <v>14.648</v>
+        <v>0.053</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46147.67708333334</v>
+        <v>46149.67708333334</v>
       </c>
       <c r="B67">
-        <v>1.348</v>
+        <v>15.446</v>
       </c>
       <c r="C67">
-        <v>1.211</v>
+        <v>0.052</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>35.75</v>
+        <v>25</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46147.6875</v>
+        <v>46149.6875</v>
       </c>
       <c r="B68">
-        <v>0.354</v>
+        <v>8.827</v>
       </c>
       <c r="C68">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46147.69791666666</v>
+        <v>46149.69791666666</v>
       </c>
       <c r="B69">
-        <v>0.295</v>
+        <v>2.692</v>
       </c>
       <c r="C69">
-        <v>0.231</v>
+        <v>0.056</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46147.70833333334</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.167</v>
+        <v>0.077</v>
       </c>
       <c r="C70">
-        <v>0.88</v>
+        <v>6.443</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46147.71875</v>
+        <v>46149.71875</v>
       </c>
       <c r="B71">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>0.169</v>
+        <v>9.911</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +2610,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46147.72916666666</v>
+        <v>46149.72916666666</v>
       </c>
       <c r="B72">
-        <v>19.734</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>5.237</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46147.73958333334</v>
+        <v>46149.73958333334</v>
       </c>
       <c r="B73">
-        <v>43.915</v>
+        <v>0.097</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1.203</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,19 +2656,19 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46147.75</v>
+        <v>46149.75</v>
       </c>
       <c r="B74">
-        <v>8.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>14.055</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46147.76041666666</v>
+        <v>46149.76041666666</v>
       </c>
       <c r="B75">
-        <v>5.792</v>
+        <v>0.177</v>
       </c>
       <c r="C75">
-        <v>0.005</v>
+        <v>0.257</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46147.77083333334</v>
+        <v>46149.77083333334</v>
       </c>
       <c r="B76">
-        <v>8.305</v>
+        <v>0.019</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>9.84</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,13 +2725,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46147.78125</v>
+        <v>46149.78125</v>
       </c>
       <c r="B77">
-        <v>4.674</v>
+        <v>0.048</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>4.064</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46147.79166666666</v>
+        <v>46149.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>0.159</v>
+        <v>27.468</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2771,13 +2771,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46147.80208333334</v>
+        <v>46149.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0.228</v>
+        <v>32.294</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46147.8125</v>
+        <v>46149.8125</v>
       </c>
       <c r="B80">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>0.208</v>
+        <v>13.022</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46147.82291666666</v>
+        <v>46149.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.366</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C81">
-        <v>0.039</v>
+        <v>0.145</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46147.83333333334</v>
+        <v>46149.83333333334</v>
       </c>
       <c r="B82">
-        <v>13.762</v>
+        <v>0.169</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46147.84375</v>
+        <v>46149.84375</v>
       </c>
       <c r="B83">
-        <v>12.596</v>
+        <v>0.068</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2.835</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46147.85416666666</v>
+        <v>46149.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.526</v>
+        <v>0.037</v>
       </c>
       <c r="C84">
-        <v>0.025</v>
+        <v>1.317</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46147.86458333334</v>
+        <v>46149.86458333334</v>
       </c>
       <c r="B85">
-        <v>4.49</v>
+        <v>2.009</v>
       </c>
       <c r="C85">
-        <v>0.081</v>
+        <v>0.147</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46147.875</v>
+        <v>46149.875</v>
       </c>
       <c r="B86">
-        <v>0.017</v>
+        <v>10.858</v>
       </c>
       <c r="C86">
-        <v>0.547</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46147.88541666666</v>
+        <v>46149.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.548</v>
+        <v>6.991</v>
       </c>
       <c r="C87">
-        <v>0.099</v>
+        <v>0.003</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46147.89583333334</v>
+        <v>46149.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.205</v>
+        <v>2.014</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46147.90625</v>
+        <v>46149.90625</v>
       </c>
       <c r="B89">
-        <v>19.394</v>
+        <v>0.096</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>10.667</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3024,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46147.91666666666</v>
+        <v>46149.91666666666</v>
       </c>
       <c r="B90">
-        <v>25.366</v>
+        <v>4.37</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1.428</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,19 +3047,19 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46147.92708333334</v>
+        <v>46149.92708333334</v>
       </c>
       <c r="B91">
-        <v>36.18</v>
+        <v>0.057</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>4.452</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>90</v>
@@ -3070,19 +3070,19 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46147.9375</v>
+        <v>46149.9375</v>
       </c>
       <c r="B92">
-        <v>34.163</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>10.288</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F92">
         <v>91</v>
@@ -3093,19 +3093,19 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46147.94791666666</v>
+        <v>46149.94791666666</v>
       </c>
       <c r="B93">
-        <v>37.26</v>
+        <v>0.032</v>
       </c>
       <c r="C93">
-        <v>0.09</v>
+        <v>6.161</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -3116,19 +3116,19 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46147.95833333334</v>
+        <v>46149.95833333334</v>
       </c>
       <c r="B94">
-        <v>5.827</v>
+        <v>0.011</v>
       </c>
       <c r="C94">
-        <v>1.498</v>
+        <v>2.945</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>93</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46147.96875</v>
+        <v>46149.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>1.481</v>
+        <v>6.783</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46147.97916666666</v>
+        <v>46149.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>8.551</v>
+        <v>9.795</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46147.98958333334</v>
+        <v>46149.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>13.727</v>
+        <v>14.65</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="C98">
-        <v>21.315</v>
+        <v>2.684</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="C99">
-        <v>21.315</v>
+        <v>2.684</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="C100">
-        <v>19.348</v>
+        <v>0.247</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="C101">
-        <v>19.348</v>
+        <v>0.247</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="C102">
-        <v>31.625</v>
+        <v>0.243</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="C103">
-        <v>31.625</v>
+        <v>0.243</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,19 +3346,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="C104">
-        <v>15.92</v>
+        <v>11.698</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F104">
         <v>4</v>
@@ -3369,19 +3369,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="C105">
-        <v>15.92</v>
+        <v>11.698</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F105">
         <v>4</v>
@@ -3392,19 +3392,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B106">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>5.312</v>
+        <v>12.069</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F106">
         <v>5</v>
@@ -3415,19 +3415,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B107">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>5.312</v>
+        <v>12.069</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F107">
         <v>5</v>
@@ -3438,19 +3438,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B108">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>1.93</v>
+        <v>17.239</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F108">
         <v>6</v>
@@ -3461,19 +3461,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B109">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>1.93</v>
+        <v>17.239</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F109">
         <v>6</v>
@@ -3484,19 +3484,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B110">
-        <v>0.505</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>1.226</v>
+        <v>22.787</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F110">
         <v>7</v>
@@ -3507,19 +3507,19 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B111">
-        <v>0.505</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1.226</v>
+        <v>22.787</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F111">
         <v>7</v>
@@ -3530,19 +3530,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B112">
-        <v>0.334</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0.643</v>
+        <v>8.433</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F112">
         <v>8</v>
@@ -3553,19 +3553,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.334</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0.643</v>
+        <v>8.433</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F113">
         <v>8</v>
@@ -3576,19 +3576,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B114">
-        <v>1.578</v>
+        <v>0.004</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>5.178</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F114">
         <v>9</v>
@@ -3599,19 +3599,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B115">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0.035</v>
+        <v>13.364</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F115">
         <v>10</v>
@@ -3622,19 +3622,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B116">
-        <v>0.723</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0.034</v>
+        <v>13.082</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F116">
         <v>11</v>
@@ -3645,19 +3645,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B117">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>0.99</v>
+        <v>3.615</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F117">
         <v>12</v>
@@ -3668,19 +3668,19 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B118">
-        <v>1.408</v>
+        <v>0.048</v>
       </c>
       <c r="C118">
-        <v>2.485</v>
+        <v>1.719</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F118">
         <v>13</v>
@@ -3691,19 +3691,19 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B119">
-        <v>2.168</v>
+        <v>5.025</v>
       </c>
       <c r="C119">
-        <v>0.281</v>
+        <v>0.053</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F119">
         <v>14</v>
@@ -3714,19 +3714,19 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B120">
-        <v>3.043</v>
+        <v>2.94</v>
       </c>
       <c r="C120">
-        <v>1.45</v>
+        <v>0.019</v>
       </c>
       <c r="D120">
         <v>0</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F120">
         <v>15</v>
@@ -3737,19 +3737,19 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B121">
-        <v>2.316</v>
+        <v>0.85</v>
       </c>
       <c r="C121">
-        <v>0.08500000000000001</v>
+        <v>0.308</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F121">
         <v>16</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B122">
-        <v>0.099</v>
+        <v>0.044</v>
       </c>
       <c r="C122">
-        <v>0.551</v>
+        <v>0.431</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C123">
-        <v>3.989</v>
+        <v>5.458</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B124">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>3.564</v>
+        <v>21.887</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.021</v>
+        <v>0.026</v>
       </c>
       <c r="C125">
-        <v>0.681</v>
+        <v>5.043</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="C126">
-        <v>1.281</v>
+        <v>4.944</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,19 +3875,19 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B127">
-        <v>0.134</v>
+        <v>0.363</v>
       </c>
       <c r="C127">
-        <v>0.222</v>
+        <v>1.282</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F127">
         <v>22</v>
@@ -3898,19 +3898,19 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B128">
-        <v>0.374</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>0.075</v>
+        <v>7.964</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -3921,19 +3921,19 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B129">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>2.41</v>
+        <v>16.537</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F129">
         <v>24</v>
@@ -3944,19 +3944,19 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B130">
-        <v>0.022</v>
+        <v>0.249</v>
       </c>
       <c r="C130">
-        <v>1.881</v>
+        <v>18.042</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F130">
         <v>25</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="C131">
-        <v>16.901</v>
+        <v>0.331</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F131">
         <v>26</v>
@@ -3990,13 +3990,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="C132">
-        <v>32.209</v>
+        <v>0.161</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>0.262</v>
       </c>
       <c r="C133">
-        <v>42.05</v>
+        <v>0.101</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4036,19 +4036,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C134">
-        <v>7.988</v>
+        <v>0.751</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>29</v>
@@ -4059,19 +4059,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="C135">
-        <v>7.766</v>
+        <v>0.908</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>30</v>
@@ -4082,19 +4082,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B136">
-        <v>1.287</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0.407</v>
+        <v>9.247</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>31</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>10.968</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>32</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.05.20261</t>
-  </si>
-  <si>
-    <t>07.05.20262</t>
-  </si>
-  <si>
-    <t>07.05.20263</t>
-  </si>
-  <si>
-    <t>07.05.20264</t>
-  </si>
-  <si>
-    <t>07.05.20265</t>
-  </si>
-  <si>
-    <t>07.05.20266</t>
-  </si>
-  <si>
-    <t>07.05.20267</t>
-  </si>
-  <si>
-    <t>07.05.20268</t>
-  </si>
-  <si>
-    <t>07.05.20269</t>
-  </si>
-  <si>
-    <t>07.05.202610</t>
-  </si>
-  <si>
-    <t>07.05.202611</t>
-  </si>
-  <si>
-    <t>07.05.202612</t>
-  </si>
-  <si>
-    <t>07.05.202613</t>
-  </si>
-  <si>
-    <t>07.05.202614</t>
-  </si>
-  <si>
-    <t>07.05.202615</t>
-  </si>
-  <si>
-    <t>07.05.202616</t>
-  </si>
-  <si>
-    <t>07.05.202617</t>
-  </si>
-  <si>
-    <t>07.05.202618</t>
-  </si>
-  <si>
-    <t>07.05.202619</t>
-  </si>
-  <si>
-    <t>07.05.202620</t>
-  </si>
-  <si>
-    <t>07.05.202621</t>
-  </si>
-  <si>
-    <t>07.05.202622</t>
-  </si>
-  <si>
-    <t>07.05.202623</t>
-  </si>
-  <si>
-    <t>07.05.202624</t>
-  </si>
-  <si>
-    <t>07.05.202625</t>
-  </si>
-  <si>
-    <t>07.05.202626</t>
-  </si>
-  <si>
-    <t>07.05.202627</t>
-  </si>
-  <si>
-    <t>07.05.202628</t>
-  </si>
-  <si>
-    <t>07.05.202629</t>
-  </si>
-  <si>
-    <t>07.05.202630</t>
-  </si>
-  <si>
-    <t>07.05.202631</t>
-  </si>
-  <si>
-    <t>07.05.202632</t>
-  </si>
-  <si>
-    <t>07.05.202633</t>
-  </si>
-  <si>
-    <t>07.05.202634</t>
-  </si>
-  <si>
-    <t>07.05.202635</t>
-  </si>
-  <si>
-    <t>07.05.202636</t>
-  </si>
-  <si>
-    <t>07.05.202637</t>
-  </si>
-  <si>
-    <t>07.05.202638</t>
-  </si>
-  <si>
-    <t>07.05.202639</t>
-  </si>
-  <si>
-    <t>07.05.202640</t>
-  </si>
-  <si>
-    <t>07.05.202641</t>
-  </si>
-  <si>
-    <t>07.05.202642</t>
-  </si>
-  <si>
-    <t>07.05.202643</t>
-  </si>
-  <si>
-    <t>07.05.202644</t>
-  </si>
-  <si>
-    <t>07.05.202645</t>
-  </si>
-  <si>
-    <t>07.05.202646</t>
-  </si>
-  <si>
-    <t>07.05.202647</t>
-  </si>
-  <si>
-    <t>07.05.202648</t>
-  </si>
-  <si>
-    <t>07.05.202649</t>
-  </si>
-  <si>
-    <t>07.05.202650</t>
-  </si>
-  <si>
-    <t>07.05.202651</t>
-  </si>
-  <si>
-    <t>07.05.202652</t>
-  </si>
-  <si>
-    <t>07.05.202653</t>
-  </si>
-  <si>
-    <t>07.05.202654</t>
-  </si>
-  <si>
-    <t>07.05.202655</t>
-  </si>
-  <si>
-    <t>07.05.202656</t>
-  </si>
-  <si>
-    <t>07.05.202657</t>
-  </si>
-  <si>
-    <t>07.05.202658</t>
-  </si>
-  <si>
-    <t>07.05.202659</t>
-  </si>
-  <si>
-    <t>07.05.202660</t>
-  </si>
-  <si>
-    <t>07.05.202661</t>
-  </si>
-  <si>
-    <t>07.05.202662</t>
-  </si>
-  <si>
-    <t>07.05.202663</t>
-  </si>
-  <si>
-    <t>07.05.202664</t>
-  </si>
-  <si>
-    <t>07.05.202665</t>
-  </si>
-  <si>
-    <t>07.05.202666</t>
-  </si>
-  <si>
-    <t>07.05.202667</t>
-  </si>
-  <si>
-    <t>07.05.202668</t>
-  </si>
-  <si>
-    <t>07.05.202669</t>
-  </si>
-  <si>
-    <t>07.05.202670</t>
-  </si>
-  <si>
-    <t>07.05.202671</t>
-  </si>
-  <si>
-    <t>07.05.202672</t>
-  </si>
-  <si>
-    <t>07.05.202673</t>
-  </si>
-  <si>
-    <t>07.05.202674</t>
-  </si>
-  <si>
-    <t>07.05.202675</t>
-  </si>
-  <si>
-    <t>07.05.202676</t>
-  </si>
-  <si>
-    <t>07.05.202677</t>
-  </si>
-  <si>
-    <t>07.05.202678</t>
-  </si>
-  <si>
-    <t>07.05.202679</t>
-  </si>
-  <si>
-    <t>07.05.202680</t>
-  </si>
-  <si>
-    <t>07.05.202681</t>
-  </si>
-  <si>
-    <t>07.05.202682</t>
-  </si>
-  <si>
-    <t>07.05.202683</t>
-  </si>
-  <si>
-    <t>07.05.202684</t>
-  </si>
-  <si>
-    <t>07.05.202685</t>
-  </si>
-  <si>
-    <t>07.05.202686</t>
-  </si>
-  <si>
-    <t>07.05.202687</t>
-  </si>
-  <si>
-    <t>07.05.202688</t>
-  </si>
-  <si>
-    <t>07.05.202689</t>
-  </si>
-  <si>
-    <t>07.05.202690</t>
-  </si>
-  <si>
-    <t>07.05.202691</t>
-  </si>
-  <si>
-    <t>07.05.202692</t>
-  </si>
-  <si>
-    <t>07.05.202693</t>
-  </si>
-  <si>
-    <t>07.05.202694</t>
-  </si>
-  <si>
-    <t>07.05.202695</t>
-  </si>
-  <si>
-    <t>07.05.202696</t>
-  </si>
-  <si>
-    <t>08.05.20261</t>
-  </si>
-  <si>
-    <t>08.05.20262</t>
-  </si>
-  <si>
-    <t>08.05.20263</t>
-  </si>
-  <si>
-    <t>08.05.20264</t>
-  </si>
-  <si>
-    <t>08.05.20265</t>
-  </si>
-  <si>
-    <t>08.05.20266</t>
-  </si>
-  <si>
-    <t>08.05.20267</t>
-  </si>
-  <si>
-    <t>08.05.20268</t>
-  </si>
-  <si>
-    <t>08.05.20269</t>
-  </si>
-  <si>
-    <t>08.05.202610</t>
-  </si>
-  <si>
-    <t>08.05.202611</t>
-  </si>
-  <si>
-    <t>08.05.202612</t>
-  </si>
-  <si>
-    <t>08.05.202613</t>
-  </si>
-  <si>
-    <t>08.05.202614</t>
-  </si>
-  <si>
-    <t>08.05.202615</t>
-  </si>
-  <si>
-    <t>08.05.202616</t>
-  </si>
-  <si>
-    <t>08.05.202617</t>
-  </si>
-  <si>
-    <t>08.05.202618</t>
-  </si>
-  <si>
-    <t>08.05.202619</t>
-  </si>
-  <si>
-    <t>08.05.202620</t>
-  </si>
-  <si>
-    <t>08.05.202621</t>
-  </si>
-  <si>
-    <t>08.05.202622</t>
-  </si>
-  <si>
-    <t>08.05.202623</t>
-  </si>
-  <si>
-    <t>08.05.202624</t>
-  </si>
-  <si>
-    <t>08.05.202625</t>
-  </si>
-  <si>
-    <t>08.05.202626</t>
-  </si>
-  <si>
-    <t>08.05.202627</t>
-  </si>
-  <si>
-    <t>08.05.202628</t>
-  </si>
-  <si>
-    <t>08.05.202629</t>
-  </si>
-  <si>
-    <t>08.05.202630</t>
-  </si>
-  <si>
-    <t>08.05.202631</t>
-  </si>
-  <si>
-    <t>08.05.202632</t>
-  </si>
-  <si>
-    <t>08.05.202633</t>
-  </si>
-  <si>
-    <t>08.05.202634</t>
-  </si>
-  <si>
-    <t>08.05.202635</t>
-  </si>
-  <si>
-    <t>08.05.202636</t>
-  </si>
-  <si>
-    <t>08.05.202637</t>
-  </si>
-  <si>
-    <t>08.05.202638</t>
-  </si>
-  <si>
-    <t>08.05.202639</t>
-  </si>
-  <si>
-    <t>08.05.202640</t>
-  </si>
-  <si>
-    <t>08.05.202641</t>
-  </si>
-  <si>
-    <t>08.05.202642</t>
-  </si>
-  <si>
-    <t>08.05.202643</t>
-  </si>
-  <si>
-    <t>08.05.202644</t>
-  </si>
-  <si>
-    <t>08.05.202645</t>
-  </si>
-  <si>
-    <t>08.05.202646</t>
-  </si>
-  <si>
-    <t>08.05.202647</t>
-  </si>
-  <si>
-    <t>08.05.202648</t>
-  </si>
-  <si>
-    <t>08.05.202649</t>
-  </si>
-  <si>
-    <t>08.05.202650</t>
-  </si>
-  <si>
-    <t>08.05.202651</t>
-  </si>
-  <si>
-    <t>08.05.202652</t>
-  </si>
-  <si>
-    <t>08.05.202653</t>
-  </si>
-  <si>
-    <t>08.05.202654</t>
-  </si>
-  <si>
-    <t>08.05.202655</t>
-  </si>
-  <si>
-    <t>08.05.202656</t>
-  </si>
-  <si>
-    <t>08.05.202657</t>
-  </si>
-  <si>
-    <t>08.05.202658</t>
-  </si>
-  <si>
-    <t>08.05.202659</t>
-  </si>
-  <si>
-    <t>08.05.202660</t>
-  </si>
-  <si>
-    <t>08.05.202661</t>
-  </si>
-  <si>
-    <t>08.05.202662</t>
-  </si>
-  <si>
-    <t>08.05.202663</t>
-  </si>
-  <si>
-    <t>08.05.202664</t>
-  </si>
-  <si>
-    <t>08.05.202665</t>
-  </si>
-  <si>
-    <t>08.05.202666</t>
-  </si>
-  <si>
-    <t>08.05.202667</t>
-  </si>
-  <si>
-    <t>08.05.202668</t>
-  </si>
-  <si>
-    <t>08.05.202669</t>
-  </si>
-  <si>
-    <t>08.05.202670</t>
-  </si>
-  <si>
-    <t>08.05.202671</t>
-  </si>
-  <si>
-    <t>08.05.202672</t>
-  </si>
-  <si>
-    <t>08.05.202673</t>
-  </si>
-  <si>
-    <t>08.05.202674</t>
-  </si>
-  <si>
-    <t>08.05.202675</t>
-  </si>
-  <si>
-    <t>08.05.202676</t>
-  </si>
-  <si>
-    <t>08.05.202677</t>
-  </si>
-  <si>
-    <t>08.05.202678</t>
-  </si>
-  <si>
-    <t>08.05.202679</t>
-  </si>
-  <si>
-    <t>08.05.202680</t>
-  </si>
-  <si>
-    <t>08.05.202681</t>
-  </si>
-  <si>
-    <t>08.05.202682</t>
-  </si>
-  <si>
-    <t>08.05.202683</t>
-  </si>
-  <si>
-    <t>08.05.202684</t>
-  </si>
-  <si>
-    <t>08.05.202685</t>
-  </si>
-  <si>
-    <t>08.05.202686</t>
-  </si>
-  <si>
-    <t>08.05.202687</t>
-  </si>
-  <si>
-    <t>08.05.202688</t>
-  </si>
-  <si>
-    <t>08.05.202689</t>
-  </si>
-  <si>
-    <t>08.05.202690</t>
-  </si>
-  <si>
-    <t>08.05.202691</t>
-  </si>
-  <si>
-    <t>08.05.202692</t>
-  </si>
-  <si>
-    <t>08.05.202693</t>
-  </si>
-  <si>
-    <t>08.05.202694</t>
-  </si>
-  <si>
-    <t>08.05.202695</t>
-  </si>
-  <si>
-    <t>08.05.202696</t>
+    <t>11.05.20261</t>
+  </si>
+  <si>
+    <t>11.05.20262</t>
+  </si>
+  <si>
+    <t>11.05.20263</t>
+  </si>
+  <si>
+    <t>11.05.20264</t>
+  </si>
+  <si>
+    <t>11.05.20265</t>
+  </si>
+  <si>
+    <t>11.05.20266</t>
+  </si>
+  <si>
+    <t>11.05.20267</t>
+  </si>
+  <si>
+    <t>11.05.20268</t>
+  </si>
+  <si>
+    <t>11.05.20269</t>
+  </si>
+  <si>
+    <t>11.05.202610</t>
+  </si>
+  <si>
+    <t>11.05.202611</t>
+  </si>
+  <si>
+    <t>11.05.202612</t>
+  </si>
+  <si>
+    <t>11.05.202613</t>
+  </si>
+  <si>
+    <t>11.05.202614</t>
+  </si>
+  <si>
+    <t>11.05.202615</t>
+  </si>
+  <si>
+    <t>11.05.202616</t>
+  </si>
+  <si>
+    <t>11.05.202617</t>
+  </si>
+  <si>
+    <t>11.05.202618</t>
+  </si>
+  <si>
+    <t>11.05.202619</t>
+  </si>
+  <si>
+    <t>11.05.202620</t>
+  </si>
+  <si>
+    <t>11.05.202621</t>
+  </si>
+  <si>
+    <t>11.05.202622</t>
+  </si>
+  <si>
+    <t>11.05.202623</t>
+  </si>
+  <si>
+    <t>11.05.202624</t>
+  </si>
+  <si>
+    <t>11.05.202625</t>
+  </si>
+  <si>
+    <t>11.05.202626</t>
+  </si>
+  <si>
+    <t>11.05.202627</t>
+  </si>
+  <si>
+    <t>11.05.202628</t>
+  </si>
+  <si>
+    <t>11.05.202629</t>
+  </si>
+  <si>
+    <t>11.05.202630</t>
+  </si>
+  <si>
+    <t>11.05.202631</t>
+  </si>
+  <si>
+    <t>11.05.202632</t>
+  </si>
+  <si>
+    <t>11.05.202633</t>
+  </si>
+  <si>
+    <t>11.05.202634</t>
+  </si>
+  <si>
+    <t>11.05.202635</t>
+  </si>
+  <si>
+    <t>11.05.202636</t>
+  </si>
+  <si>
+    <t>11.05.202637</t>
+  </si>
+  <si>
+    <t>11.05.202638</t>
+  </si>
+  <si>
+    <t>11.05.202639</t>
+  </si>
+  <si>
+    <t>11.05.202640</t>
+  </si>
+  <si>
+    <t>11.05.202641</t>
+  </si>
+  <si>
+    <t>11.05.202642</t>
+  </si>
+  <si>
+    <t>11.05.202643</t>
+  </si>
+  <si>
+    <t>11.05.202644</t>
+  </si>
+  <si>
+    <t>11.05.202645</t>
+  </si>
+  <si>
+    <t>11.05.202646</t>
+  </si>
+  <si>
+    <t>11.05.202647</t>
+  </si>
+  <si>
+    <t>11.05.202648</t>
+  </si>
+  <si>
+    <t>11.05.202649</t>
+  </si>
+  <si>
+    <t>11.05.202650</t>
+  </si>
+  <si>
+    <t>11.05.202651</t>
+  </si>
+  <si>
+    <t>11.05.202652</t>
+  </si>
+  <si>
+    <t>11.05.202653</t>
+  </si>
+  <si>
+    <t>11.05.202654</t>
+  </si>
+  <si>
+    <t>11.05.202655</t>
+  </si>
+  <si>
+    <t>11.05.202656</t>
+  </si>
+  <si>
+    <t>11.05.202657</t>
+  </si>
+  <si>
+    <t>11.05.202658</t>
+  </si>
+  <si>
+    <t>11.05.202659</t>
+  </si>
+  <si>
+    <t>11.05.202660</t>
+  </si>
+  <si>
+    <t>11.05.202661</t>
+  </si>
+  <si>
+    <t>11.05.202662</t>
+  </si>
+  <si>
+    <t>11.05.202663</t>
+  </si>
+  <si>
+    <t>11.05.202664</t>
+  </si>
+  <si>
+    <t>11.05.202665</t>
+  </si>
+  <si>
+    <t>11.05.202666</t>
+  </si>
+  <si>
+    <t>11.05.202667</t>
+  </si>
+  <si>
+    <t>11.05.202668</t>
+  </si>
+  <si>
+    <t>11.05.202669</t>
+  </si>
+  <si>
+    <t>11.05.202670</t>
+  </si>
+  <si>
+    <t>11.05.202671</t>
+  </si>
+  <si>
+    <t>11.05.202672</t>
+  </si>
+  <si>
+    <t>11.05.202673</t>
+  </si>
+  <si>
+    <t>11.05.202674</t>
+  </si>
+  <si>
+    <t>11.05.202675</t>
+  </si>
+  <si>
+    <t>11.05.202676</t>
+  </si>
+  <si>
+    <t>11.05.202677</t>
+  </si>
+  <si>
+    <t>11.05.202678</t>
+  </si>
+  <si>
+    <t>11.05.202679</t>
+  </si>
+  <si>
+    <t>11.05.202680</t>
+  </si>
+  <si>
+    <t>11.05.202681</t>
+  </si>
+  <si>
+    <t>11.05.202682</t>
+  </si>
+  <si>
+    <t>11.05.202683</t>
+  </si>
+  <si>
+    <t>11.05.202684</t>
+  </si>
+  <si>
+    <t>11.05.202685</t>
+  </si>
+  <si>
+    <t>11.05.202686</t>
+  </si>
+  <si>
+    <t>11.05.202687</t>
+  </si>
+  <si>
+    <t>11.05.202688</t>
+  </si>
+  <si>
+    <t>11.05.202689</t>
+  </si>
+  <si>
+    <t>11.05.202690</t>
+  </si>
+  <si>
+    <t>11.05.202691</t>
+  </si>
+  <si>
+    <t>11.05.202692</t>
+  </si>
+  <si>
+    <t>11.05.202693</t>
+  </si>
+  <si>
+    <t>11.05.202694</t>
+  </si>
+  <si>
+    <t>11.05.202695</t>
+  </si>
+  <si>
+    <t>11.05.202696</t>
+  </si>
+  <si>
+    <t>12.05.20261</t>
+  </si>
+  <si>
+    <t>12.05.20262</t>
+  </si>
+  <si>
+    <t>12.05.20263</t>
+  </si>
+  <si>
+    <t>12.05.20264</t>
+  </si>
+  <si>
+    <t>12.05.20265</t>
+  </si>
+  <si>
+    <t>12.05.20266</t>
+  </si>
+  <si>
+    <t>12.05.20267</t>
+  </si>
+  <si>
+    <t>12.05.20268</t>
+  </si>
+  <si>
+    <t>12.05.20269</t>
+  </si>
+  <si>
+    <t>12.05.202610</t>
+  </si>
+  <si>
+    <t>12.05.202611</t>
+  </si>
+  <si>
+    <t>12.05.202612</t>
+  </si>
+  <si>
+    <t>12.05.202613</t>
+  </si>
+  <si>
+    <t>12.05.202614</t>
+  </si>
+  <si>
+    <t>12.05.202615</t>
+  </si>
+  <si>
+    <t>12.05.202616</t>
+  </si>
+  <si>
+    <t>12.05.202617</t>
+  </si>
+  <si>
+    <t>12.05.202618</t>
+  </si>
+  <si>
+    <t>12.05.202619</t>
+  </si>
+  <si>
+    <t>12.05.202620</t>
+  </si>
+  <si>
+    <t>12.05.202621</t>
+  </si>
+  <si>
+    <t>12.05.202622</t>
+  </si>
+  <si>
+    <t>12.05.202623</t>
+  </si>
+  <si>
+    <t>12.05.202624</t>
+  </si>
+  <si>
+    <t>12.05.202625</t>
+  </si>
+  <si>
+    <t>12.05.202626</t>
+  </si>
+  <si>
+    <t>12.05.202627</t>
+  </si>
+  <si>
+    <t>12.05.202628</t>
+  </si>
+  <si>
+    <t>12.05.202629</t>
+  </si>
+  <si>
+    <t>12.05.202630</t>
+  </si>
+  <si>
+    <t>12.05.202631</t>
+  </si>
+  <si>
+    <t>12.05.202632</t>
+  </si>
+  <si>
+    <t>12.05.202633</t>
+  </si>
+  <si>
+    <t>12.05.202634</t>
+  </si>
+  <si>
+    <t>12.05.202635</t>
+  </si>
+  <si>
+    <t>12.05.202636</t>
+  </si>
+  <si>
+    <t>12.05.202637</t>
+  </si>
+  <si>
+    <t>12.05.202638</t>
+  </si>
+  <si>
+    <t>12.05.202639</t>
+  </si>
+  <si>
+    <t>12.05.202640</t>
+  </si>
+  <si>
+    <t>12.05.202641</t>
+  </si>
+  <si>
+    <t>12.05.202642</t>
+  </si>
+  <si>
+    <t>12.05.202643</t>
+  </si>
+  <si>
+    <t>12.05.202644</t>
+  </si>
+  <si>
+    <t>12.05.202645</t>
+  </si>
+  <si>
+    <t>12.05.202646</t>
+  </si>
+  <si>
+    <t>12.05.202647</t>
+  </si>
+  <si>
+    <t>12.05.202648</t>
+  </si>
+  <si>
+    <t>12.05.202649</t>
+  </si>
+  <si>
+    <t>12.05.202650</t>
+  </si>
+  <si>
+    <t>12.05.202651</t>
+  </si>
+  <si>
+    <t>12.05.202652</t>
+  </si>
+  <si>
+    <t>12.05.202653</t>
+  </si>
+  <si>
+    <t>12.05.202654</t>
+  </si>
+  <si>
+    <t>12.05.202655</t>
+  </si>
+  <si>
+    <t>12.05.202656</t>
+  </si>
+  <si>
+    <t>12.05.202657</t>
+  </si>
+  <si>
+    <t>12.05.202658</t>
+  </si>
+  <si>
+    <t>12.05.202659</t>
+  </si>
+  <si>
+    <t>12.05.202660</t>
+  </si>
+  <si>
+    <t>12.05.202661</t>
+  </si>
+  <si>
+    <t>12.05.202662</t>
+  </si>
+  <si>
+    <t>12.05.202663</t>
+  </si>
+  <si>
+    <t>12.05.202664</t>
+  </si>
+  <si>
+    <t>12.05.202665</t>
+  </si>
+  <si>
+    <t>12.05.202666</t>
+  </si>
+  <si>
+    <t>12.05.202667</t>
+  </si>
+  <si>
+    <t>12.05.202668</t>
+  </si>
+  <si>
+    <t>12.05.202669</t>
+  </si>
+  <si>
+    <t>12.05.202670</t>
+  </si>
+  <si>
+    <t>12.05.202671</t>
+  </si>
+  <si>
+    <t>12.05.202672</t>
+  </si>
+  <si>
+    <t>12.05.202673</t>
+  </si>
+  <si>
+    <t>12.05.202674</t>
+  </si>
+  <si>
+    <t>12.05.202675</t>
+  </si>
+  <si>
+    <t>12.05.202676</t>
+  </si>
+  <si>
+    <t>12.05.202677</t>
+  </si>
+  <si>
+    <t>12.05.202678</t>
+  </si>
+  <si>
+    <t>12.05.202679</t>
+  </si>
+  <si>
+    <t>12.05.202680</t>
+  </si>
+  <si>
+    <t>12.05.202681</t>
+  </si>
+  <si>
+    <t>12.05.202682</t>
+  </si>
+  <si>
+    <t>12.05.202683</t>
+  </si>
+  <si>
+    <t>12.05.202684</t>
+  </si>
+  <si>
+    <t>12.05.202685</t>
+  </si>
+  <si>
+    <t>12.05.202686</t>
+  </si>
+  <si>
+    <t>12.05.202687</t>
+  </si>
+  <si>
+    <t>12.05.202688</t>
+  </si>
+  <si>
+    <t>12.05.202689</t>
+  </si>
+  <si>
+    <t>12.05.202690</t>
+  </si>
+  <si>
+    <t>12.05.202691</t>
+  </si>
+  <si>
+    <t>12.05.202692</t>
+  </si>
+  <si>
+    <t>12.05.202693</t>
+  </si>
+  <si>
+    <t>12.05.202694</t>
+  </si>
+  <si>
+    <t>12.05.202695</t>
+  </si>
+  <si>
+    <t>12.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B2">
-        <v>0.002</v>
+        <v>11.501</v>
       </c>
       <c r="C2">
-        <v>1.272</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46149.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.002</v>
+        <v>9.332000000000001</v>
       </c>
       <c r="C3">
-        <v>4.127</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46149.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.026</v>
+        <v>3.909</v>
       </c>
       <c r="C4">
-        <v>2.31</v>
+        <v>0.003</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46149.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="C5">
-        <v>17.63</v>
+        <v>0.04</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46149.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46149.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.107</v>
+        <v>14.841</v>
       </c>
       <c r="C7">
-        <v>0.268</v>
+        <v>0.018</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46149.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>4.002</v>
+        <v>1.649</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46149.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.659</v>
       </c>
       <c r="C9">
-        <v>21.301</v>
+        <v>0.256</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46149.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2.289</v>
       </c>
       <c r="C10">
-        <v>6.815</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46149.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>0.057</v>
+        <v>6.098</v>
       </c>
       <c r="C11">
-        <v>2.563</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46149.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.001</v>
+        <v>1.598</v>
       </c>
       <c r="C12">
-        <v>1.185</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46149.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.05</v>
+        <v>1.554</v>
       </c>
       <c r="C13">
-        <v>2.641</v>
+        <v>0.047</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46149.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2.681</v>
       </c>
       <c r="C14">
-        <v>11.617</v>
+        <v>0.03</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46149.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>8.609</v>
       </c>
       <c r="C15">
-        <v>8.843</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46149.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="C16">
-        <v>13.031</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46149.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="C17">
-        <v>8.565</v>
+        <v>0.002</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46149.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.005</v>
+        <v>0.597</v>
       </c>
       <c r="C18">
-        <v>11.242</v>
+        <v>0.038</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46149.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>5.651</v>
       </c>
       <c r="C19">
-        <v>26.116</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46149.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>5.072</v>
       </c>
       <c r="C20">
-        <v>23.771</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46149.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="C21">
-        <v>27.086</v>
+        <v>0.199</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46149.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C22">
-        <v>29.599</v>
+        <v>3.208</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46149.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C23">
-        <v>29.279</v>
+        <v>0.413</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46149.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>16.211</v>
+        <v>18.241</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46149.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>14.446</v>
+        <v>22.498</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46149.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>18.054</v>
+        <v>30.591</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46149.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>9.061999999999999</v>
+        <v>27.877</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46149.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>3.732</v>
+        <v>31.746</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46149.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>0.488</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.858</v>
+        <v>7.498</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,19 +1644,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46149.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>14.367</v>
+        <v>0.004</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>10.228</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46149.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>18.569</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>13.407</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46149.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>18.173</v>
+        <v>0.032</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>6.058</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46149.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>1.141</v>
+        <v>0.097</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>9.682</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46149.33333333334</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>29.829</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46149.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>10.841</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>34.261</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46149.35416666666</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>12.686</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>50.253</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46149.36458333334</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>12.309</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.004</v>
+        <v>44.965</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46149.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>23.443</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>5.457</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46149.38541666666</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>18.379</v>
+        <v>0.109</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.491</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46149.39583333334</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>16.636</v>
+        <v>0.164</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>7.112</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46149.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>2.322</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.056</v>
+        <v>11.224</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46149.41666666666</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>2.111</v>
+        <v>0.233</v>
       </c>
       <c r="C42">
-        <v>0.616</v>
+        <v>0.26</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>62.25</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46149.42708333334</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.011</v>
+        <v>2.77</v>
       </c>
       <c r="C43">
-        <v>10.108</v>
+        <v>0.208</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>59.25</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46149.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>0.512</v>
       </c>
       <c r="C44">
-        <v>9.699</v>
+        <v>0.064</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46149.44791666666</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.015</v>
+        <v>0.046</v>
       </c>
       <c r="C45">
-        <v>2.955</v>
+        <v>9.291</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46149.45833333334</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.665</v>
+        <v>4.762</v>
       </c>
       <c r="C46">
-        <v>0.173</v>
+        <v>4.616</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46149.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>0.195</v>
+        <v>0.848</v>
       </c>
       <c r="C47">
-        <v>1.69</v>
+        <v>2.879</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46149.47916666666</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.075</v>
+        <v>0.126</v>
       </c>
       <c r="C48">
-        <v>4.124</v>
+        <v>4.375</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46149.48958333334</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>1.707</v>
+        <v>2.326</v>
       </c>
       <c r="C49">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46149.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>0.153</v>
+        <v>4.995</v>
       </c>
       <c r="C50">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46149.51041666666</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.282</v>
+        <v>6.47</v>
       </c>
       <c r="C51">
-        <v>0.144</v>
+        <v>0.004</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46149.52083333334</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.324</v>
+        <v>0.08</v>
       </c>
       <c r="C52">
-        <v>0.044</v>
+        <v>1.904</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46149.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="C53">
-        <v>0.198</v>
+        <v>22.474</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,13 +2196,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46149.54166666666</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>10.492</v>
+        <v>1.349</v>
       </c>
       <c r="C54">
-        <v>0.022</v>
+        <v>3.971</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2219,13 +2219,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46149.55208333334</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>11.772</v>
+        <v>5.345</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46149.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>9.640000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>10.115</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46149.57291666666</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.589</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0.091</v>
+        <v>32.847</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46149.58333333334</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>0.526</v>
+        <v>50.774</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46149.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>0.742</v>
+        <v>46.839</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46149.60416666666</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C60">
-        <v>2.537</v>
+        <v>14.571</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46149.61458333334</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.152</v>
+        <v>0.013</v>
       </c>
       <c r="C61">
-        <v>0.773</v>
+        <v>6.209</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46149.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>14.057</v>
+        <v>12.136</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>32.25</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46149.63541666666</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>19.762</v>
+        <v>9.228999999999999</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>32.25</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46149.64583333334</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>1.251</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0.178</v>
+        <v>20.395</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>25</v>
+        <v>32.25</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46149.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>3.251</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>27.728</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>25</v>
+        <v>32.25</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46149.66666666666</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>0.053</v>
+        <v>6.834</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>60.25</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46149.67708333334</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>15.446</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>0.052</v>
+        <v>18.402</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>25</v>
+        <v>60.25</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46149.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>8.827</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>6.519</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>60.25</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46149.69791666666</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>2.692</v>
+        <v>1.673</v>
       </c>
       <c r="C69">
-        <v>0.056</v>
+        <v>1.056</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>60.25</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46149.70833333334</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.077</v>
+        <v>0.548</v>
       </c>
       <c r="C70">
-        <v>6.443</v>
+        <v>0.099</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46149.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>20.154</v>
       </c>
       <c r="C71">
-        <v>9.911</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +2610,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46149.72916666666</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>10.625</v>
       </c>
       <c r="C72">
-        <v>5.237</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46149.73958333334</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.097</v>
+        <v>16.277</v>
       </c>
       <c r="C73">
-        <v>1.203</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46149.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>2.047</v>
       </c>
       <c r="C74">
-        <v>14.055</v>
+        <v>5.627</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46149.76041666666</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.177</v>
+        <v>3.999</v>
       </c>
       <c r="C75">
-        <v>0.257</v>
+        <v>0.025</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2702,13 +2702,13 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46149.77083333334</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.019</v>
+        <v>13.935</v>
       </c>
       <c r="C76">
-        <v>9.84</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2725,13 +2725,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46149.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>0.048</v>
+        <v>6.254</v>
       </c>
       <c r="C77">
-        <v>4.064</v>
+        <v>1.36</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46149.79166666666</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="C78">
-        <v>27.468</v>
+        <v>3.01</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2771,13 +2771,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46149.80208333334</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="C79">
-        <v>32.294</v>
+        <v>0.592</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46149.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="C80">
-        <v>13.022</v>
+        <v>0.829</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46149.82291666666</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>0.145</v>
+        <v>11.89</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46149.83333333334</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.169</v>
+        <v>0.037</v>
       </c>
       <c r="C82">
-        <v>0.045</v>
+        <v>6.706</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46149.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>0.068</v>
+        <v>0.14</v>
       </c>
       <c r="C83">
-        <v>2.835</v>
+        <v>5.473</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46149.85416666666</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.037</v>
+        <v>0.508</v>
       </c>
       <c r="C84">
-        <v>1.317</v>
+        <v>0.202</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46149.86458333334</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>2.009</v>
+        <v>0.013</v>
       </c>
       <c r="C85">
-        <v>0.147</v>
+        <v>3.311</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46149.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>10.858</v>
+        <v>0.628</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>4.972</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46149.88541666666</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>6.991</v>
+        <v>1.31</v>
       </c>
       <c r="C87">
-        <v>0.003</v>
+        <v>2.056</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46149.89583333334</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.014</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0.093</v>
+        <v>4.695</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46149.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>10.667</v>
+        <v>15.307</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46149.91666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>1.428</v>
+        <v>19.844</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46149.92708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>4.452</v>
+        <v>8.925000000000001</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46149.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>10.288</v>
+        <v>7.324</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46149.94791666666</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.032</v>
+        <v>0.475</v>
       </c>
       <c r="C93">
-        <v>6.161</v>
+        <v>3.01</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46149.95833333334</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.011</v>
+        <v>0.601</v>
       </c>
       <c r="C94">
-        <v>2.945</v>
+        <v>1.62</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46149.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>6.783</v>
+        <v>29.025</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,19 +3162,19 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46149.97916666666</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="C96">
-        <v>9.795</v>
+        <v>4.405</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -3185,19 +3185,19 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46149.98958333334</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="C97">
-        <v>14.65</v>
+        <v>1.684</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -3208,19 +3208,19 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B98">
-        <v>0.083</v>
+        <v>3.145</v>
       </c>
       <c r="C98">
-        <v>2.684</v>
+        <v>0.626</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -3231,19 +3231,19 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B99">
-        <v>0.083</v>
+        <v>3.145</v>
       </c>
       <c r="C99">
-        <v>2.684</v>
+        <v>0.626</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -3254,19 +3254,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B100">
-        <v>0.056</v>
+        <v>2.684</v>
       </c>
       <c r="C100">
-        <v>0.247</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F100">
         <v>2</v>
@@ -3277,19 +3277,19 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B101">
-        <v>0.056</v>
+        <v>2.684</v>
       </c>
       <c r="C101">
-        <v>0.247</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3300,19 +3300,19 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B102">
-        <v>0.047</v>
+        <v>0.18</v>
       </c>
       <c r="C102">
-        <v>0.243</v>
+        <v>0.022</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F102">
         <v>3</v>
@@ -3323,19 +3323,19 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B103">
-        <v>0.047</v>
+        <v>0.18</v>
       </c>
       <c r="C103">
-        <v>0.243</v>
+        <v>0.022</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F103">
         <v>3</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B104">
-        <v>0.064</v>
+        <v>10.269</v>
       </c>
       <c r="C104">
-        <v>11.698</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B105">
-        <v>0.064</v>
+        <v>10.269</v>
       </c>
       <c r="C105">
-        <v>11.698</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,19 +3392,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="C106">
-        <v>12.069</v>
+        <v>0.083</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F106">
         <v>5</v>
@@ -3415,19 +3415,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="C107">
-        <v>12.069</v>
+        <v>0.083</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F107">
         <v>5</v>
@@ -3438,19 +3438,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="C108">
-        <v>17.239</v>
+        <v>1.35</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F108">
         <v>6</v>
@@ -3461,19 +3461,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="C109">
-        <v>17.239</v>
+        <v>1.35</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F109">
         <v>6</v>
@@ -3484,19 +3484,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>22.787</v>
+        <v>10.183</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F110">
         <v>7</v>
@@ -3507,19 +3507,19 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>22.787</v>
+        <v>10.183</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F111">
         <v>7</v>
@@ -3530,19 +3530,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C112">
-        <v>8.433</v>
+        <v>17.258</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F112">
         <v>8</v>
@@ -3553,19 +3553,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C113">
-        <v>8.433</v>
+        <v>17.258</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F113">
         <v>8</v>
@@ -3576,19 +3576,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B114">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>5.178</v>
+        <v>6.76</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F114">
         <v>9</v>
@@ -3599,19 +3599,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>13.364</v>
+        <v>7.684</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F115">
         <v>10</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="C116">
-        <v>13.082</v>
+        <v>4.82</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>3.615</v>
+        <v>3.616</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B118">
-        <v>0.048</v>
+        <v>2.498</v>
       </c>
       <c r="C118">
-        <v>1.719</v>
+        <v>0.014</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B119">
-        <v>5.025</v>
+        <v>0.341</v>
       </c>
       <c r="C119">
-        <v>0.053</v>
+        <v>0.026</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,19 +3714,19 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B120">
-        <v>2.94</v>
+        <v>7.381</v>
       </c>
       <c r="C120">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
       </c>
       <c r="E120">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="F120">
         <v>15</v>
@@ -3737,19 +3737,19 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B121">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="C121">
-        <v>0.308</v>
+        <v>0.058</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>16</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B122">
-        <v>0.044</v>
+        <v>10.641</v>
       </c>
       <c r="C122">
-        <v>0.431</v>
+        <v>0.05</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B123">
-        <v>0.008999999999999999</v>
+        <v>30.227</v>
       </c>
       <c r="C123">
-        <v>5.458</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>10.928</v>
       </c>
       <c r="C124">
-        <v>21.887</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.026</v>
+        <v>18.29</v>
       </c>
       <c r="C125">
-        <v>5.043</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>4.944</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,19 +3875,19 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B127">
-        <v>0.363</v>
+        <v>0.174</v>
       </c>
       <c r="C127">
-        <v>1.282</v>
+        <v>0.949</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E127">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F127">
         <v>22</v>
@@ -3898,19 +3898,19 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>1.574</v>
       </c>
       <c r="C128">
-        <v>7.964</v>
+        <v>0.885</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E128">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -3921,19 +3921,19 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1.144</v>
       </c>
       <c r="C129">
-        <v>16.537</v>
+        <v>1.121</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E129">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F129">
         <v>24</v>
@@ -3944,19 +3944,19 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B130">
-        <v>0.249</v>
+        <v>8.755000000000001</v>
       </c>
       <c r="C130">
-        <v>18.042</v>
+        <v>0.379</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F130">
         <v>25</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B131">
-        <v>0.126</v>
+        <v>6.638</v>
       </c>
       <c r="C131">
-        <v>0.331</v>
+        <v>0.067</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>26</v>
@@ -3990,13 +3990,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.295</v>
+        <v>0.027</v>
       </c>
       <c r="C132">
-        <v>0.161</v>
+        <v>11.474</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B133">
-        <v>0.262</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>0.101</v>
+        <v>19.881</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.07099999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="C134">
-        <v>0.751</v>
+        <v>8.41</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.165</v>
+        <v>0.02</v>
       </c>
       <c r="C135">
-        <v>0.908</v>
+        <v>23.679</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>9.247</v>
+        <v>31.485</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="C137">
-        <v>10.968</v>
+        <v>8.817</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>43.25</v>
       </c>
       <c r="F137">
         <v>32</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>3.666</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F138">
         <v>33</v>
@@ -4151,10 +4151,10 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>41.285</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F139">
         <v>34</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>24.987</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,13 +4197,13 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46150.36458333334</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>17.586</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4220,16 +4220,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>25.188</v>
       </c>
       <c r="C142">
         <v>0</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4243,16 +4243,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46150.38541666666</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>20.124</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>93.25</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4266,16 +4266,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46150.39583333334</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>11.48</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4289,16 +4289,16 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>42.849</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -4312,16 +4312,16 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46150.41666666666</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>39.324</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -4335,13 +4335,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46150.42708333334</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>30.347</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4358,13 +4358,13 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>8.499000000000001</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46150.44791666666</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46150.45833333334</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46150.47916666666</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46150.48958333334</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46150.51041666666</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46150.52083333334</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46150.54166666666</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46150.55208333334</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46150.57291666666</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46150.58333333334</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46150.60416666666</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46150.61458333334</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46150.63541666666</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46150.64583333334</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46150.66666666666</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46150.67708333334</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46150.69791666666</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46150.70833333334</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46150.72916666666</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46150.73958333334</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46150.76041666666</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46150.77083333334</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46150.79166666666</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46150.80208333334</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46150.82291666666</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46150.83333333334</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46150.85416666666</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46150.86458333334</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46150.88541666666</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46150.89583333334</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46150.91666666666</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46150.92708333334</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46150.94791666666</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46150.95833333334</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46150.97916666666</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46150.98958333334</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.05.20261</t>
-  </si>
-  <si>
-    <t>11.05.20262</t>
-  </si>
-  <si>
-    <t>11.05.20263</t>
-  </si>
-  <si>
-    <t>11.05.20264</t>
-  </si>
-  <si>
-    <t>11.05.20265</t>
-  </si>
-  <si>
-    <t>11.05.20266</t>
-  </si>
-  <si>
-    <t>11.05.20267</t>
-  </si>
-  <si>
-    <t>11.05.20268</t>
-  </si>
-  <si>
-    <t>11.05.20269</t>
-  </si>
-  <si>
-    <t>11.05.202610</t>
-  </si>
-  <si>
-    <t>11.05.202611</t>
-  </si>
-  <si>
-    <t>11.05.202612</t>
-  </si>
-  <si>
-    <t>11.05.202613</t>
-  </si>
-  <si>
-    <t>11.05.202614</t>
-  </si>
-  <si>
-    <t>11.05.202615</t>
-  </si>
-  <si>
-    <t>11.05.202616</t>
-  </si>
-  <si>
-    <t>11.05.202617</t>
-  </si>
-  <si>
-    <t>11.05.202618</t>
-  </si>
-  <si>
-    <t>11.05.202619</t>
-  </si>
-  <si>
-    <t>11.05.202620</t>
-  </si>
-  <si>
-    <t>11.05.202621</t>
-  </si>
-  <si>
-    <t>11.05.202622</t>
-  </si>
-  <si>
-    <t>11.05.202623</t>
-  </si>
-  <si>
-    <t>11.05.202624</t>
-  </si>
-  <si>
-    <t>11.05.202625</t>
-  </si>
-  <si>
-    <t>11.05.202626</t>
-  </si>
-  <si>
-    <t>11.05.202627</t>
-  </si>
-  <si>
-    <t>11.05.202628</t>
-  </si>
-  <si>
-    <t>11.05.202629</t>
-  </si>
-  <si>
-    <t>11.05.202630</t>
-  </si>
-  <si>
-    <t>11.05.202631</t>
-  </si>
-  <si>
-    <t>11.05.202632</t>
-  </si>
-  <si>
-    <t>11.05.202633</t>
-  </si>
-  <si>
-    <t>11.05.202634</t>
-  </si>
-  <si>
-    <t>11.05.202635</t>
-  </si>
-  <si>
-    <t>11.05.202636</t>
-  </si>
-  <si>
-    <t>11.05.202637</t>
-  </si>
-  <si>
-    <t>11.05.202638</t>
-  </si>
-  <si>
-    <t>11.05.202639</t>
-  </si>
-  <si>
-    <t>11.05.202640</t>
-  </si>
-  <si>
-    <t>11.05.202641</t>
-  </si>
-  <si>
-    <t>11.05.202642</t>
-  </si>
-  <si>
-    <t>11.05.202643</t>
-  </si>
-  <si>
-    <t>11.05.202644</t>
-  </si>
-  <si>
-    <t>11.05.202645</t>
-  </si>
-  <si>
-    <t>11.05.202646</t>
-  </si>
-  <si>
-    <t>11.05.202647</t>
-  </si>
-  <si>
-    <t>11.05.202648</t>
-  </si>
-  <si>
-    <t>11.05.202649</t>
-  </si>
-  <si>
-    <t>11.05.202650</t>
-  </si>
-  <si>
-    <t>11.05.202651</t>
-  </si>
-  <si>
-    <t>11.05.202652</t>
-  </si>
-  <si>
-    <t>11.05.202653</t>
-  </si>
-  <si>
-    <t>11.05.202654</t>
-  </si>
-  <si>
-    <t>11.05.202655</t>
-  </si>
-  <si>
-    <t>11.05.202656</t>
-  </si>
-  <si>
-    <t>11.05.202657</t>
-  </si>
-  <si>
-    <t>11.05.202658</t>
-  </si>
-  <si>
-    <t>11.05.202659</t>
-  </si>
-  <si>
-    <t>11.05.202660</t>
-  </si>
-  <si>
-    <t>11.05.202661</t>
-  </si>
-  <si>
-    <t>11.05.202662</t>
-  </si>
-  <si>
-    <t>11.05.202663</t>
-  </si>
-  <si>
-    <t>11.05.202664</t>
-  </si>
-  <si>
-    <t>11.05.202665</t>
-  </si>
-  <si>
-    <t>11.05.202666</t>
-  </si>
-  <si>
-    <t>11.05.202667</t>
-  </si>
-  <si>
-    <t>11.05.202668</t>
-  </si>
-  <si>
-    <t>11.05.202669</t>
-  </si>
-  <si>
-    <t>11.05.202670</t>
-  </si>
-  <si>
-    <t>11.05.202671</t>
-  </si>
-  <si>
-    <t>11.05.202672</t>
-  </si>
-  <si>
-    <t>11.05.202673</t>
-  </si>
-  <si>
-    <t>11.05.202674</t>
-  </si>
-  <si>
-    <t>11.05.202675</t>
-  </si>
-  <si>
-    <t>11.05.202676</t>
-  </si>
-  <si>
-    <t>11.05.202677</t>
-  </si>
-  <si>
-    <t>11.05.202678</t>
-  </si>
-  <si>
-    <t>11.05.202679</t>
-  </si>
-  <si>
-    <t>11.05.202680</t>
-  </si>
-  <si>
-    <t>11.05.202681</t>
-  </si>
-  <si>
-    <t>11.05.202682</t>
-  </si>
-  <si>
-    <t>11.05.202683</t>
-  </si>
-  <si>
-    <t>11.05.202684</t>
-  </si>
-  <si>
-    <t>11.05.202685</t>
-  </si>
-  <si>
-    <t>11.05.202686</t>
-  </si>
-  <si>
-    <t>11.05.202687</t>
-  </si>
-  <si>
-    <t>11.05.202688</t>
-  </si>
-  <si>
-    <t>11.05.202689</t>
-  </si>
-  <si>
-    <t>11.05.202690</t>
-  </si>
-  <si>
-    <t>11.05.202691</t>
-  </si>
-  <si>
-    <t>11.05.202692</t>
-  </si>
-  <si>
-    <t>11.05.202693</t>
-  </si>
-  <si>
-    <t>11.05.202694</t>
-  </si>
-  <si>
-    <t>11.05.202695</t>
-  </si>
-  <si>
-    <t>11.05.202696</t>
-  </si>
-  <si>
-    <t>12.05.20261</t>
-  </si>
-  <si>
-    <t>12.05.20262</t>
-  </si>
-  <si>
-    <t>12.05.20263</t>
-  </si>
-  <si>
-    <t>12.05.20264</t>
-  </si>
-  <si>
-    <t>12.05.20265</t>
-  </si>
-  <si>
-    <t>12.05.20266</t>
-  </si>
-  <si>
-    <t>12.05.20267</t>
-  </si>
-  <si>
-    <t>12.05.20268</t>
-  </si>
-  <si>
-    <t>12.05.20269</t>
-  </si>
-  <si>
-    <t>12.05.202610</t>
-  </si>
-  <si>
-    <t>12.05.202611</t>
-  </si>
-  <si>
-    <t>12.05.202612</t>
-  </si>
-  <si>
-    <t>12.05.202613</t>
-  </si>
-  <si>
-    <t>12.05.202614</t>
-  </si>
-  <si>
-    <t>12.05.202615</t>
-  </si>
-  <si>
-    <t>12.05.202616</t>
-  </si>
-  <si>
-    <t>12.05.202617</t>
-  </si>
-  <si>
-    <t>12.05.202618</t>
-  </si>
-  <si>
-    <t>12.05.202619</t>
-  </si>
-  <si>
-    <t>12.05.202620</t>
-  </si>
-  <si>
-    <t>12.05.202621</t>
-  </si>
-  <si>
-    <t>12.05.202622</t>
-  </si>
-  <si>
-    <t>12.05.202623</t>
-  </si>
-  <si>
-    <t>12.05.202624</t>
-  </si>
-  <si>
-    <t>12.05.202625</t>
-  </si>
-  <si>
-    <t>12.05.202626</t>
-  </si>
-  <si>
-    <t>12.05.202627</t>
-  </si>
-  <si>
-    <t>12.05.202628</t>
-  </si>
-  <si>
-    <t>12.05.202629</t>
-  </si>
-  <si>
-    <t>12.05.202630</t>
-  </si>
-  <si>
-    <t>12.05.202631</t>
-  </si>
-  <si>
-    <t>12.05.202632</t>
-  </si>
-  <si>
-    <t>12.05.202633</t>
-  </si>
-  <si>
-    <t>12.05.202634</t>
-  </si>
-  <si>
-    <t>12.05.202635</t>
-  </si>
-  <si>
-    <t>12.05.202636</t>
-  </si>
-  <si>
-    <t>12.05.202637</t>
-  </si>
-  <si>
-    <t>12.05.202638</t>
-  </si>
-  <si>
-    <t>12.05.202639</t>
-  </si>
-  <si>
-    <t>12.05.202640</t>
-  </si>
-  <si>
-    <t>12.05.202641</t>
-  </si>
-  <si>
-    <t>12.05.202642</t>
-  </si>
-  <si>
-    <t>12.05.202643</t>
-  </si>
-  <si>
-    <t>12.05.202644</t>
-  </si>
-  <si>
-    <t>12.05.202645</t>
-  </si>
-  <si>
-    <t>12.05.202646</t>
-  </si>
-  <si>
-    <t>12.05.202647</t>
-  </si>
-  <si>
-    <t>12.05.202648</t>
-  </si>
-  <si>
-    <t>12.05.202649</t>
-  </si>
-  <si>
-    <t>12.05.202650</t>
-  </si>
-  <si>
-    <t>12.05.202651</t>
-  </si>
-  <si>
-    <t>12.05.202652</t>
-  </si>
-  <si>
-    <t>12.05.202653</t>
-  </si>
-  <si>
-    <t>12.05.202654</t>
-  </si>
-  <si>
-    <t>12.05.202655</t>
-  </si>
-  <si>
-    <t>12.05.202656</t>
-  </si>
-  <si>
-    <t>12.05.202657</t>
-  </si>
-  <si>
-    <t>12.05.202658</t>
-  </si>
-  <si>
-    <t>12.05.202659</t>
-  </si>
-  <si>
-    <t>12.05.202660</t>
-  </si>
-  <si>
-    <t>12.05.202661</t>
-  </si>
-  <si>
-    <t>12.05.202662</t>
-  </si>
-  <si>
-    <t>12.05.202663</t>
-  </si>
-  <si>
-    <t>12.05.202664</t>
-  </si>
-  <si>
-    <t>12.05.202665</t>
-  </si>
-  <si>
-    <t>12.05.202666</t>
-  </si>
-  <si>
-    <t>12.05.202667</t>
-  </si>
-  <si>
-    <t>12.05.202668</t>
-  </si>
-  <si>
-    <t>12.05.202669</t>
-  </si>
-  <si>
-    <t>12.05.202670</t>
-  </si>
-  <si>
-    <t>12.05.202671</t>
-  </si>
-  <si>
-    <t>12.05.202672</t>
-  </si>
-  <si>
-    <t>12.05.202673</t>
-  </si>
-  <si>
-    <t>12.05.202674</t>
-  </si>
-  <si>
-    <t>12.05.202675</t>
-  </si>
-  <si>
-    <t>12.05.202676</t>
-  </si>
-  <si>
-    <t>12.05.202677</t>
-  </si>
-  <si>
-    <t>12.05.202678</t>
-  </si>
-  <si>
-    <t>12.05.202679</t>
-  </si>
-  <si>
-    <t>12.05.202680</t>
-  </si>
-  <si>
-    <t>12.05.202681</t>
-  </si>
-  <si>
-    <t>12.05.202682</t>
-  </si>
-  <si>
-    <t>12.05.202683</t>
-  </si>
-  <si>
-    <t>12.05.202684</t>
-  </si>
-  <si>
-    <t>12.05.202685</t>
-  </si>
-  <si>
-    <t>12.05.202686</t>
-  </si>
-  <si>
-    <t>12.05.202687</t>
-  </si>
-  <si>
-    <t>12.05.202688</t>
-  </si>
-  <si>
-    <t>12.05.202689</t>
-  </si>
-  <si>
-    <t>12.05.202690</t>
-  </si>
-  <si>
-    <t>12.05.202691</t>
-  </si>
-  <si>
-    <t>12.05.202692</t>
-  </si>
-  <si>
-    <t>12.05.202693</t>
-  </si>
-  <si>
-    <t>12.05.202694</t>
-  </si>
-  <si>
-    <t>12.05.202695</t>
-  </si>
-  <si>
-    <t>12.05.202696</t>
+    <t>13.05.20261</t>
+  </si>
+  <si>
+    <t>13.05.20262</t>
+  </si>
+  <si>
+    <t>13.05.20263</t>
+  </si>
+  <si>
+    <t>13.05.20264</t>
+  </si>
+  <si>
+    <t>13.05.20265</t>
+  </si>
+  <si>
+    <t>13.05.20266</t>
+  </si>
+  <si>
+    <t>13.05.20267</t>
+  </si>
+  <si>
+    <t>13.05.20268</t>
+  </si>
+  <si>
+    <t>13.05.20269</t>
+  </si>
+  <si>
+    <t>13.05.202610</t>
+  </si>
+  <si>
+    <t>13.05.202611</t>
+  </si>
+  <si>
+    <t>13.05.202612</t>
+  </si>
+  <si>
+    <t>13.05.202613</t>
+  </si>
+  <si>
+    <t>13.05.202614</t>
+  </si>
+  <si>
+    <t>13.05.202615</t>
+  </si>
+  <si>
+    <t>13.05.202616</t>
+  </si>
+  <si>
+    <t>13.05.202617</t>
+  </si>
+  <si>
+    <t>13.05.202618</t>
+  </si>
+  <si>
+    <t>13.05.202619</t>
+  </si>
+  <si>
+    <t>13.05.202620</t>
+  </si>
+  <si>
+    <t>13.05.202621</t>
+  </si>
+  <si>
+    <t>13.05.202622</t>
+  </si>
+  <si>
+    <t>13.05.202623</t>
+  </si>
+  <si>
+    <t>13.05.202624</t>
+  </si>
+  <si>
+    <t>13.05.202625</t>
+  </si>
+  <si>
+    <t>13.05.202626</t>
+  </si>
+  <si>
+    <t>13.05.202627</t>
+  </si>
+  <si>
+    <t>13.05.202628</t>
+  </si>
+  <si>
+    <t>13.05.202629</t>
+  </si>
+  <si>
+    <t>13.05.202630</t>
+  </si>
+  <si>
+    <t>13.05.202631</t>
+  </si>
+  <si>
+    <t>13.05.202632</t>
+  </si>
+  <si>
+    <t>13.05.202633</t>
+  </si>
+  <si>
+    <t>13.05.202634</t>
+  </si>
+  <si>
+    <t>13.05.202635</t>
+  </si>
+  <si>
+    <t>13.05.202636</t>
+  </si>
+  <si>
+    <t>13.05.202637</t>
+  </si>
+  <si>
+    <t>13.05.202638</t>
+  </si>
+  <si>
+    <t>13.05.202639</t>
+  </si>
+  <si>
+    <t>13.05.202640</t>
+  </si>
+  <si>
+    <t>13.05.202641</t>
+  </si>
+  <si>
+    <t>13.05.202642</t>
+  </si>
+  <si>
+    <t>13.05.202643</t>
+  </si>
+  <si>
+    <t>13.05.202644</t>
+  </si>
+  <si>
+    <t>13.05.202645</t>
+  </si>
+  <si>
+    <t>13.05.202646</t>
+  </si>
+  <si>
+    <t>13.05.202647</t>
+  </si>
+  <si>
+    <t>13.05.202648</t>
+  </si>
+  <si>
+    <t>13.05.202649</t>
+  </si>
+  <si>
+    <t>13.05.202650</t>
+  </si>
+  <si>
+    <t>13.05.202651</t>
+  </si>
+  <si>
+    <t>13.05.202652</t>
+  </si>
+  <si>
+    <t>13.05.202653</t>
+  </si>
+  <si>
+    <t>13.05.202654</t>
+  </si>
+  <si>
+    <t>13.05.202655</t>
+  </si>
+  <si>
+    <t>13.05.202656</t>
+  </si>
+  <si>
+    <t>13.05.202657</t>
+  </si>
+  <si>
+    <t>13.05.202658</t>
+  </si>
+  <si>
+    <t>13.05.202659</t>
+  </si>
+  <si>
+    <t>13.05.202660</t>
+  </si>
+  <si>
+    <t>13.05.202661</t>
+  </si>
+  <si>
+    <t>13.05.202662</t>
+  </si>
+  <si>
+    <t>13.05.202663</t>
+  </si>
+  <si>
+    <t>13.05.202664</t>
+  </si>
+  <si>
+    <t>13.05.202665</t>
+  </si>
+  <si>
+    <t>13.05.202666</t>
+  </si>
+  <si>
+    <t>13.05.202667</t>
+  </si>
+  <si>
+    <t>13.05.202668</t>
+  </si>
+  <si>
+    <t>13.05.202669</t>
+  </si>
+  <si>
+    <t>13.05.202670</t>
+  </si>
+  <si>
+    <t>13.05.202671</t>
+  </si>
+  <si>
+    <t>13.05.202672</t>
+  </si>
+  <si>
+    <t>13.05.202673</t>
+  </si>
+  <si>
+    <t>13.05.202674</t>
+  </si>
+  <si>
+    <t>13.05.202675</t>
+  </si>
+  <si>
+    <t>13.05.202676</t>
+  </si>
+  <si>
+    <t>13.05.202677</t>
+  </si>
+  <si>
+    <t>13.05.202678</t>
+  </si>
+  <si>
+    <t>13.05.202679</t>
+  </si>
+  <si>
+    <t>13.05.202680</t>
+  </si>
+  <si>
+    <t>13.05.202681</t>
+  </si>
+  <si>
+    <t>13.05.202682</t>
+  </si>
+  <si>
+    <t>13.05.202683</t>
+  </si>
+  <si>
+    <t>13.05.202684</t>
+  </si>
+  <si>
+    <t>13.05.202685</t>
+  </si>
+  <si>
+    <t>13.05.202686</t>
+  </si>
+  <si>
+    <t>13.05.202687</t>
+  </si>
+  <si>
+    <t>13.05.202688</t>
+  </si>
+  <si>
+    <t>13.05.202689</t>
+  </si>
+  <si>
+    <t>13.05.202690</t>
+  </si>
+  <si>
+    <t>13.05.202691</t>
+  </si>
+  <si>
+    <t>13.05.202692</t>
+  </si>
+  <si>
+    <t>13.05.202693</t>
+  </si>
+  <si>
+    <t>13.05.202694</t>
+  </si>
+  <si>
+    <t>13.05.202695</t>
+  </si>
+  <si>
+    <t>13.05.202696</t>
+  </si>
+  <si>
+    <t>14.05.20261</t>
+  </si>
+  <si>
+    <t>14.05.20262</t>
+  </si>
+  <si>
+    <t>14.05.20263</t>
+  </si>
+  <si>
+    <t>14.05.20264</t>
+  </si>
+  <si>
+    <t>14.05.20265</t>
+  </si>
+  <si>
+    <t>14.05.20266</t>
+  </si>
+  <si>
+    <t>14.05.20267</t>
+  </si>
+  <si>
+    <t>14.05.20268</t>
+  </si>
+  <si>
+    <t>14.05.20269</t>
+  </si>
+  <si>
+    <t>14.05.202610</t>
+  </si>
+  <si>
+    <t>14.05.202611</t>
+  </si>
+  <si>
+    <t>14.05.202612</t>
+  </si>
+  <si>
+    <t>14.05.202613</t>
+  </si>
+  <si>
+    <t>14.05.202614</t>
+  </si>
+  <si>
+    <t>14.05.202615</t>
+  </si>
+  <si>
+    <t>14.05.202616</t>
+  </si>
+  <si>
+    <t>14.05.202617</t>
+  </si>
+  <si>
+    <t>14.05.202618</t>
+  </si>
+  <si>
+    <t>14.05.202619</t>
+  </si>
+  <si>
+    <t>14.05.202620</t>
+  </si>
+  <si>
+    <t>14.05.202621</t>
+  </si>
+  <si>
+    <t>14.05.202622</t>
+  </si>
+  <si>
+    <t>14.05.202623</t>
+  </si>
+  <si>
+    <t>14.05.202624</t>
+  </si>
+  <si>
+    <t>14.05.202625</t>
+  </si>
+  <si>
+    <t>14.05.202626</t>
+  </si>
+  <si>
+    <t>14.05.202627</t>
+  </si>
+  <si>
+    <t>14.05.202628</t>
+  </si>
+  <si>
+    <t>14.05.202629</t>
+  </si>
+  <si>
+    <t>14.05.202630</t>
+  </si>
+  <si>
+    <t>14.05.202631</t>
+  </si>
+  <si>
+    <t>14.05.202632</t>
+  </si>
+  <si>
+    <t>14.05.202633</t>
+  </si>
+  <si>
+    <t>14.05.202634</t>
+  </si>
+  <si>
+    <t>14.05.202635</t>
+  </si>
+  <si>
+    <t>14.05.202636</t>
+  </si>
+  <si>
+    <t>14.05.202637</t>
+  </si>
+  <si>
+    <t>14.05.202638</t>
+  </si>
+  <si>
+    <t>14.05.202639</t>
+  </si>
+  <si>
+    <t>14.05.202640</t>
+  </si>
+  <si>
+    <t>14.05.202641</t>
+  </si>
+  <si>
+    <t>14.05.202642</t>
+  </si>
+  <si>
+    <t>14.05.202643</t>
+  </si>
+  <si>
+    <t>14.05.202644</t>
+  </si>
+  <si>
+    <t>14.05.202645</t>
+  </si>
+  <si>
+    <t>14.05.202646</t>
+  </si>
+  <si>
+    <t>14.05.202647</t>
+  </si>
+  <si>
+    <t>14.05.202648</t>
+  </si>
+  <si>
+    <t>14.05.202649</t>
+  </si>
+  <si>
+    <t>14.05.202650</t>
+  </si>
+  <si>
+    <t>14.05.202651</t>
+  </si>
+  <si>
+    <t>14.05.202652</t>
+  </si>
+  <si>
+    <t>14.05.202653</t>
+  </si>
+  <si>
+    <t>14.05.202654</t>
+  </si>
+  <si>
+    <t>14.05.202655</t>
+  </si>
+  <si>
+    <t>14.05.202656</t>
+  </si>
+  <si>
+    <t>14.05.202657</t>
+  </si>
+  <si>
+    <t>14.05.202658</t>
+  </si>
+  <si>
+    <t>14.05.202659</t>
+  </si>
+  <si>
+    <t>14.05.202660</t>
+  </si>
+  <si>
+    <t>14.05.202661</t>
+  </si>
+  <si>
+    <t>14.05.202662</t>
+  </si>
+  <si>
+    <t>14.05.202663</t>
+  </si>
+  <si>
+    <t>14.05.202664</t>
+  </si>
+  <si>
+    <t>14.05.202665</t>
+  </si>
+  <si>
+    <t>14.05.202666</t>
+  </si>
+  <si>
+    <t>14.05.202667</t>
+  </si>
+  <si>
+    <t>14.05.202668</t>
+  </si>
+  <si>
+    <t>14.05.202669</t>
+  </si>
+  <si>
+    <t>14.05.202670</t>
+  </si>
+  <si>
+    <t>14.05.202671</t>
+  </si>
+  <si>
+    <t>14.05.202672</t>
+  </si>
+  <si>
+    <t>14.05.202673</t>
+  </si>
+  <si>
+    <t>14.05.202674</t>
+  </si>
+  <si>
+    <t>14.05.202675</t>
+  </si>
+  <si>
+    <t>14.05.202676</t>
+  </si>
+  <si>
+    <t>14.05.202677</t>
+  </si>
+  <si>
+    <t>14.05.202678</t>
+  </si>
+  <si>
+    <t>14.05.202679</t>
+  </si>
+  <si>
+    <t>14.05.202680</t>
+  </si>
+  <si>
+    <t>14.05.202681</t>
+  </si>
+  <si>
+    <t>14.05.202682</t>
+  </si>
+  <si>
+    <t>14.05.202683</t>
+  </si>
+  <si>
+    <t>14.05.202684</t>
+  </si>
+  <si>
+    <t>14.05.202685</t>
+  </si>
+  <si>
+    <t>14.05.202686</t>
+  </si>
+  <si>
+    <t>14.05.202687</t>
+  </si>
+  <si>
+    <t>14.05.202688</t>
+  </si>
+  <si>
+    <t>14.05.202689</t>
+  </si>
+  <si>
+    <t>14.05.202690</t>
+  </si>
+  <si>
+    <t>14.05.202691</t>
+  </si>
+  <si>
+    <t>14.05.202692</t>
+  </si>
+  <si>
+    <t>14.05.202693</t>
+  </si>
+  <si>
+    <t>14.05.202694</t>
+  </si>
+  <si>
+    <t>14.05.202695</t>
+  </si>
+  <si>
+    <t>14.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>11.501</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>30.354</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>9.332000000000001</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>13.044</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>3.909</v>
+        <v>0.259</v>
       </c>
       <c r="C4">
-        <v>0.003</v>
+        <v>0.442</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>0.228</v>
+        <v>0.21</v>
       </c>
       <c r="C5">
-        <v>0.04</v>
+        <v>0.296</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>5.482</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>14.841</v>
+        <v>0.062</v>
       </c>
       <c r="C7">
-        <v>0.018</v>
+        <v>0.313</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="C8">
-        <v>1.649</v>
+        <v>0.209</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.659</v>
+        <v>0.113</v>
       </c>
       <c r="C9">
-        <v>0.256</v>
+        <v>0.113</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>2.289</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>6.098</v>
+        <v>1.065</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.598</v>
+        <v>0.094</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.554</v>
+        <v>0.055</v>
       </c>
       <c r="C13">
-        <v>0.047</v>
+        <v>0.448</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>2.681</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0.03</v>
+        <v>12.56</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>8.609</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>18.254</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>6.236</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.002</v>
+        <v>24.51</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.597</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0.038</v>
+        <v>38.98</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>5.651</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>15.312</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>5.072</v>
+        <v>6.457</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.311</v>
+        <v>2.527</v>
       </c>
       <c r="C21">
-        <v>0.199</v>
+        <v>0.18</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.008</v>
+        <v>0.047</v>
       </c>
       <c r="C22">
-        <v>3.208</v>
+        <v>1.526</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>0.15</v>
+        <v>0.006</v>
       </c>
       <c r="C23">
-        <v>0.413</v>
+        <v>12.487</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>18.241</v>
+        <v>18.074</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>22.498</v>
+        <v>10.909</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="C26">
-        <v>30.591</v>
+        <v>21.624</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="C27">
-        <v>27.877</v>
+        <v>0.303</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="C28">
-        <v>31.746</v>
+        <v>0.06</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="C29">
-        <v>7.498</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,19 +1644,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.004</v>
+        <v>10.926</v>
       </c>
       <c r="C30">
-        <v>10.228</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>6.827</v>
       </c>
       <c r="C31">
-        <v>13.407</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>0.032</v>
+        <v>5.253</v>
       </c>
       <c r="C32">
-        <v>6.058</v>
+        <v>0.021</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.097</v>
+        <v>0.678</v>
       </c>
       <c r="C33">
-        <v>9.682</v>
+        <v>0.187</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="C34">
-        <v>29.829</v>
+        <v>0.194</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="C35">
-        <v>34.261</v>
+        <v>0.251</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="C36">
-        <v>50.253</v>
+        <v>2.673</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>44.965</v>
+        <v>19.071</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>5.457</v>
+        <v>17.907</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.491</v>
+        <v>17.884</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.164</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>7.112</v>
+        <v>9.659000000000001</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C41">
-        <v>11.224</v>
+        <v>1.005</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.233</v>
+        <v>2.391</v>
       </c>
       <c r="C42">
-        <v>0.26</v>
+        <v>0.003</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>62.25</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>2.77</v>
+        <v>6.681</v>
       </c>
       <c r="C43">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>59.25</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>0.512</v>
+        <v>16.88</v>
       </c>
       <c r="C44">
-        <v>0.064</v>
+        <v>0.004</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.046</v>
+        <v>11.524</v>
       </c>
       <c r="C45">
-        <v>9.291</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>4.762</v>
+        <v>2.542</v>
       </c>
       <c r="C46">
-        <v>4.616</v>
+        <v>0.003</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>0.848</v>
+        <v>0.006</v>
       </c>
       <c r="C47">
-        <v>2.879</v>
+        <v>9.779</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.126</v>
+        <v>0.102</v>
       </c>
       <c r="C48">
-        <v>4.375</v>
+        <v>1.439</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>2.326</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>13.094</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>4.995</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>30.011</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>0.004</v>
+        <v>32.887</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>1.904</v>
+        <v>39.682</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>22.474</v>
+        <v>3.124</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,13 +2196,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>1.349</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>3.971</v>
+        <v>4.182</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2219,13 +2219,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>5.345</v>
+        <v>0.01</v>
       </c>
       <c r="C55">
-        <v>0.03</v>
+        <v>22.346</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>10.115</v>
+        <v>50.409</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>32.847</v>
+        <v>20.846</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>50.774</v>
+        <v>13.719</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="C59">
-        <v>46.839</v>
+        <v>0.858</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.006</v>
+        <v>0.126</v>
       </c>
       <c r="C60">
-        <v>14.571</v>
+        <v>0.308</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="C61">
-        <v>6.209</v>
+        <v>7.028</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>12.136</v>
+        <v>12.739</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>32.25</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>9.228999999999999</v>
+        <v>16.961</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>32.25</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>20.395</v>
+        <v>12.412</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>32.25</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="C65">
-        <v>27.728</v>
+        <v>0.734</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>32.25</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>4.895</v>
       </c>
       <c r="C66">
-        <v>6.834</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>60.25</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>2.691</v>
       </c>
       <c r="C67">
-        <v>18.402</v>
+        <v>0.776</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>60.25</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>6.209</v>
       </c>
       <c r="C68">
-        <v>6.519</v>
+        <v>0.597</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>60.25</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>1.673</v>
+        <v>1.668</v>
       </c>
       <c r="C69">
-        <v>1.056</v>
+        <v>0.414</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>60.25</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.548</v>
+        <v>8.538</v>
       </c>
       <c r="C70">
-        <v>0.099</v>
+        <v>0.659</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>20.154</v>
+        <v>2.772</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +2610,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>10.625</v>
+        <v>0.285</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>4.654</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>16.277</v>
+        <v>1.059</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>2.047</v>
+        <v>0.697</v>
       </c>
       <c r="C74">
-        <v>5.627</v>
+        <v>15.344</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>3.999</v>
+        <v>1.39</v>
       </c>
       <c r="C75">
-        <v>0.025</v>
+        <v>0.278</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2702,13 +2702,13 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>13.935</v>
+        <v>0.59</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>4.386</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2725,13 +2725,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>6.254</v>
+        <v>0.124</v>
       </c>
       <c r="C77">
-        <v>1.36</v>
+        <v>0.228</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.857</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>3.01</v>
+        <v>28.933</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.044</v>
+        <v>3.274</v>
       </c>
       <c r="C79">
-        <v>0.592</v>
+        <v>0.065</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>0.093</v>
+        <v>1.215</v>
       </c>
       <c r="C80">
-        <v>0.829</v>
+        <v>5.97</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>2.196</v>
       </c>
       <c r="C81">
-        <v>11.89</v>
+        <v>0.106</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.037</v>
+        <v>0.201</v>
       </c>
       <c r="C82">
-        <v>6.706</v>
+        <v>0.381</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,19 +2863,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>0.14</v>
+        <v>0.104</v>
       </c>
       <c r="C83">
-        <v>5.473</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -2886,19 +2886,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.508</v>
+        <v>1.415</v>
       </c>
       <c r="C84">
-        <v>0.202</v>
+        <v>0.019</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F84">
         <v>83</v>
@@ -2909,19 +2909,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.013</v>
+        <v>0.253</v>
       </c>
       <c r="C85">
-        <v>3.311</v>
+        <v>0.186</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F85">
         <v>84</v>
@@ -2932,19 +2932,19 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>0.628</v>
+        <v>5.245</v>
       </c>
       <c r="C86">
-        <v>4.972</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F86">
         <v>85</v>
@@ -2955,19 +2955,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>1.31</v>
+        <v>5.116</v>
       </c>
       <c r="C87">
-        <v>2.056</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="C88">
-        <v>4.695</v>
+        <v>0.63</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>16.358</v>
       </c>
       <c r="C89">
-        <v>15.307</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3024,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>23.776</v>
       </c>
       <c r="C90">
-        <v>19.844</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>2.793</v>
       </c>
       <c r="C91">
-        <v>8.925000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>4.937</v>
       </c>
       <c r="C92">
-        <v>7.324</v>
+        <v>0.335</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>3.01</v>
+        <v>15.33</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.601</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>1.62</v>
+        <v>12.663</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>29.025</v>
+        <v>35.505</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,19 +3162,19 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>4.405</v>
+        <v>20.134</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -3185,19 +3185,19 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.426</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>1.684</v>
+        <v>15.242</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -3208,19 +3208,19 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
-        <v>3.145</v>
+        <v>21.296</v>
       </c>
       <c r="C98">
-        <v>0.626</v>
+        <v>0.676</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -3231,19 +3231,19 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B99">
-        <v>3.145</v>
+        <v>21.296</v>
       </c>
       <c r="C99">
-        <v>0.626</v>
+        <v>0.676</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B100">
-        <v>2.684</v>
+        <v>8.619</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>2</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B101">
-        <v>2.684</v>
+        <v>8.619</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3300,19 +3300,19 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B102">
-        <v>0.18</v>
+        <v>6.252</v>
       </c>
       <c r="C102">
-        <v>0.022</v>
+        <v>0.221</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>3</v>
@@ -3323,19 +3323,19 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B103">
-        <v>0.18</v>
+        <v>6.252</v>
       </c>
       <c r="C103">
-        <v>0.022</v>
+        <v>0.221</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>3</v>
@@ -3346,19 +3346,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B104">
-        <v>10.269</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>10.249</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>4</v>
@@ -3369,19 +3369,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B105">
-        <v>10.269</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>10.249</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>4</v>
@@ -3392,19 +3392,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B106">
-        <v>0.728</v>
+        <v>6.186</v>
       </c>
       <c r="C106">
-        <v>0.083</v>
+        <v>0.302</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>5</v>
@@ -3415,19 +3415,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B107">
-        <v>0.728</v>
+        <v>6.186</v>
       </c>
       <c r="C107">
-        <v>0.083</v>
+        <v>0.302</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>5</v>
@@ -3438,19 +3438,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B108">
-        <v>0.092</v>
+        <v>0.027</v>
       </c>
       <c r="C108">
-        <v>1.35</v>
+        <v>3.083</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>6</v>
@@ -3461,19 +3461,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B109">
-        <v>0.092</v>
+        <v>0.027</v>
       </c>
       <c r="C109">
-        <v>1.35</v>
+        <v>3.083</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>6</v>
@@ -3484,19 +3484,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>10.183</v>
+        <v>6.538</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>7</v>
@@ -3507,19 +3507,19 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>10.183</v>
+        <v>6.538</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>7</v>
@@ -3530,19 +3530,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B112">
-        <v>0.002</v>
+        <v>0.497</v>
       </c>
       <c r="C112">
-        <v>17.258</v>
+        <v>1.567</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>8</v>
@@ -3553,19 +3553,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.002</v>
+        <v>0.497</v>
       </c>
       <c r="C113">
-        <v>17.258</v>
+        <v>1.567</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>8</v>
@@ -3576,19 +3576,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="C114">
-        <v>6.76</v>
+        <v>0.179</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>9</v>
@@ -3599,19 +3599,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="C115">
-        <v>7.684</v>
+        <v>0.611</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F115">
         <v>10</v>
@@ -3622,19 +3622,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B116">
-        <v>0.188</v>
+        <v>0.014</v>
       </c>
       <c r="C116">
-        <v>4.82</v>
+        <v>1.011</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>11</v>
@@ -3645,19 +3645,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>4.552</v>
       </c>
       <c r="C117">
-        <v>3.616</v>
+        <v>0.104</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>12</v>
@@ -3668,19 +3668,19 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B118">
-        <v>2.498</v>
+        <v>6.626</v>
       </c>
       <c r="C118">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>13</v>
@@ -3691,19 +3691,19 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B119">
-        <v>0.341</v>
+        <v>3.245</v>
       </c>
       <c r="C119">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>14</v>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B120">
-        <v>7.381</v>
+        <v>2.298</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F120">
         <v>15</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B121">
-        <v>0.88</v>
+        <v>4.855</v>
       </c>
       <c r="C121">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B122">
-        <v>10.641</v>
+        <v>2.196</v>
       </c>
       <c r="C122">
-        <v>0.05</v>
+        <v>0.005</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B123">
-        <v>30.227</v>
+        <v>0.17</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B124">
-        <v>10.928</v>
+        <v>3.11</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D124">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B125">
-        <v>18.29</v>
+        <v>2.32</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D125">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>1.162</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="D126">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +3875,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B127">
-        <v>0.174</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C127">
-        <v>0.949</v>
+        <v>0.114</v>
       </c>
       <c r="D127">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B128">
-        <v>1.574</v>
+        <v>5.909</v>
       </c>
       <c r="C128">
-        <v>0.885</v>
+        <v>0.015</v>
       </c>
       <c r="D128">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,16 +3921,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B129">
-        <v>1.144</v>
+        <v>1.627</v>
       </c>
       <c r="C129">
-        <v>1.121</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D129">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B130">
-        <v>8.755000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="C130">
-        <v>0.379</v>
+        <v>0.012</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B131">
-        <v>6.638</v>
+        <v>7.578</v>
       </c>
       <c r="C131">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,13 +3990,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.027</v>
+        <v>0.823</v>
       </c>
       <c r="C132">
-        <v>11.474</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>8.182</v>
       </c>
       <c r="C133">
-        <v>19.881</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.026</v>
+        <v>24.259</v>
       </c>
       <c r="C134">
-        <v>8.41</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.02</v>
+        <v>12.675</v>
       </c>
       <c r="C135">
-        <v>23.679</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>1.783</v>
       </c>
       <c r="C136">
-        <v>31.485</v>
+        <v>2.623</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B137">
-        <v>0.245</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>8.817</v>
+        <v>6.118</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>43.25</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>32</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B138">
-        <v>3.666</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>0.003</v>
+        <v>29.044</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>33</v>
@@ -4151,19 +4151,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B139">
-        <v>41.285</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>34</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B140">
-        <v>24.987</v>
+        <v>0.153</v>
       </c>
       <c r="C140">
-        <v>0.006</v>
+        <v>0.877</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,19 +4197,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B141">
-        <v>17.586</v>
+        <v>1.174</v>
       </c>
       <c r="C141">
-        <v>0.008999999999999999</v>
+        <v>3.431</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F141">
         <v>36</v>
@@ -4220,19 +4220,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B142">
-        <v>25.188</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>29.068</v>
       </c>
       <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
         <v>37.5</v>
-      </c>
-      <c r="E142">
-        <v>0</v>
       </c>
       <c r="F142">
         <v>37</v>
@@ -4243,19 +4243,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B143">
-        <v>20.124</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>0.011</v>
+        <v>27.247</v>
       </c>
       <c r="D143">
-        <v>93.25</v>
+        <v>0</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F143">
         <v>38</v>
@@ -4266,19 +4266,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>11.48</v>
+        <v>30.827</v>
       </c>
       <c r="D144">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F144">
         <v>39</v>
@@ -4289,19 +4289,19 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>42.849</v>
+        <v>21.278</v>
       </c>
       <c r="D145">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F145">
         <v>40</v>
@@ -4312,19 +4312,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="C146">
-        <v>39.324</v>
+        <v>2.756</v>
       </c>
       <c r="D146">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F146">
         <v>41</v>
@@ -4335,19 +4335,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="C147">
-        <v>30.347</v>
+        <v>0.625</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F147">
         <v>42</v>
@@ -4358,19 +4358,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B148">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>8.499000000000001</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F148">
         <v>43</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F149">
         <v>44</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.05.20261</t>
-  </si>
-  <si>
-    <t>13.05.20262</t>
-  </si>
-  <si>
-    <t>13.05.20263</t>
-  </si>
-  <si>
-    <t>13.05.20264</t>
-  </si>
-  <si>
-    <t>13.05.20265</t>
-  </si>
-  <si>
-    <t>13.05.20266</t>
-  </si>
-  <si>
-    <t>13.05.20267</t>
-  </si>
-  <si>
-    <t>13.05.20268</t>
-  </si>
-  <si>
-    <t>13.05.20269</t>
-  </si>
-  <si>
-    <t>13.05.202610</t>
-  </si>
-  <si>
-    <t>13.05.202611</t>
-  </si>
-  <si>
-    <t>13.05.202612</t>
-  </si>
-  <si>
-    <t>13.05.202613</t>
-  </si>
-  <si>
-    <t>13.05.202614</t>
-  </si>
-  <si>
-    <t>13.05.202615</t>
-  </si>
-  <si>
-    <t>13.05.202616</t>
-  </si>
-  <si>
-    <t>13.05.202617</t>
-  </si>
-  <si>
-    <t>13.05.202618</t>
-  </si>
-  <si>
-    <t>13.05.202619</t>
-  </si>
-  <si>
-    <t>13.05.202620</t>
-  </si>
-  <si>
-    <t>13.05.202621</t>
-  </si>
-  <si>
-    <t>13.05.202622</t>
-  </si>
-  <si>
-    <t>13.05.202623</t>
-  </si>
-  <si>
-    <t>13.05.202624</t>
-  </si>
-  <si>
-    <t>13.05.202625</t>
-  </si>
-  <si>
-    <t>13.05.202626</t>
-  </si>
-  <si>
-    <t>13.05.202627</t>
-  </si>
-  <si>
-    <t>13.05.202628</t>
-  </si>
-  <si>
-    <t>13.05.202629</t>
-  </si>
-  <si>
-    <t>13.05.202630</t>
-  </si>
-  <si>
-    <t>13.05.202631</t>
-  </si>
-  <si>
-    <t>13.05.202632</t>
-  </si>
-  <si>
-    <t>13.05.202633</t>
-  </si>
-  <si>
-    <t>13.05.202634</t>
-  </si>
-  <si>
-    <t>13.05.202635</t>
-  </si>
-  <si>
-    <t>13.05.202636</t>
-  </si>
-  <si>
-    <t>13.05.202637</t>
-  </si>
-  <si>
-    <t>13.05.202638</t>
-  </si>
-  <si>
-    <t>13.05.202639</t>
-  </si>
-  <si>
-    <t>13.05.202640</t>
-  </si>
-  <si>
-    <t>13.05.202641</t>
-  </si>
-  <si>
-    <t>13.05.202642</t>
-  </si>
-  <si>
-    <t>13.05.202643</t>
-  </si>
-  <si>
-    <t>13.05.202644</t>
-  </si>
-  <si>
-    <t>13.05.202645</t>
-  </si>
-  <si>
-    <t>13.05.202646</t>
-  </si>
-  <si>
-    <t>13.05.202647</t>
-  </si>
-  <si>
-    <t>13.05.202648</t>
-  </si>
-  <si>
-    <t>13.05.202649</t>
-  </si>
-  <si>
-    <t>13.05.202650</t>
-  </si>
-  <si>
-    <t>13.05.202651</t>
-  </si>
-  <si>
-    <t>13.05.202652</t>
-  </si>
-  <si>
-    <t>13.05.202653</t>
-  </si>
-  <si>
-    <t>13.05.202654</t>
-  </si>
-  <si>
-    <t>13.05.202655</t>
-  </si>
-  <si>
-    <t>13.05.202656</t>
-  </si>
-  <si>
-    <t>13.05.202657</t>
-  </si>
-  <si>
-    <t>13.05.202658</t>
-  </si>
-  <si>
-    <t>13.05.202659</t>
-  </si>
-  <si>
-    <t>13.05.202660</t>
-  </si>
-  <si>
-    <t>13.05.202661</t>
-  </si>
-  <si>
-    <t>13.05.202662</t>
-  </si>
-  <si>
-    <t>13.05.202663</t>
-  </si>
-  <si>
-    <t>13.05.202664</t>
-  </si>
-  <si>
-    <t>13.05.202665</t>
-  </si>
-  <si>
-    <t>13.05.202666</t>
-  </si>
-  <si>
-    <t>13.05.202667</t>
-  </si>
-  <si>
-    <t>13.05.202668</t>
-  </si>
-  <si>
-    <t>13.05.202669</t>
-  </si>
-  <si>
-    <t>13.05.202670</t>
-  </si>
-  <si>
-    <t>13.05.202671</t>
-  </si>
-  <si>
-    <t>13.05.202672</t>
-  </si>
-  <si>
-    <t>13.05.202673</t>
-  </si>
-  <si>
-    <t>13.05.202674</t>
-  </si>
-  <si>
-    <t>13.05.202675</t>
-  </si>
-  <si>
-    <t>13.05.202676</t>
-  </si>
-  <si>
-    <t>13.05.202677</t>
-  </si>
-  <si>
-    <t>13.05.202678</t>
-  </si>
-  <si>
-    <t>13.05.202679</t>
-  </si>
-  <si>
-    <t>13.05.202680</t>
-  </si>
-  <si>
-    <t>13.05.202681</t>
-  </si>
-  <si>
-    <t>13.05.202682</t>
-  </si>
-  <si>
-    <t>13.05.202683</t>
-  </si>
-  <si>
-    <t>13.05.202684</t>
-  </si>
-  <si>
-    <t>13.05.202685</t>
-  </si>
-  <si>
-    <t>13.05.202686</t>
-  </si>
-  <si>
-    <t>13.05.202687</t>
-  </si>
-  <si>
-    <t>13.05.202688</t>
-  </si>
-  <si>
-    <t>13.05.202689</t>
-  </si>
-  <si>
-    <t>13.05.202690</t>
-  </si>
-  <si>
-    <t>13.05.202691</t>
-  </si>
-  <si>
-    <t>13.05.202692</t>
-  </si>
-  <si>
-    <t>13.05.202693</t>
-  </si>
-  <si>
-    <t>13.05.202694</t>
-  </si>
-  <si>
-    <t>13.05.202695</t>
-  </si>
-  <si>
-    <t>13.05.202696</t>
-  </si>
-  <si>
     <t>14.05.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>14.05.202696</t>
+  </si>
+  <si>
+    <t>15.05.20261</t>
+  </si>
+  <si>
+    <t>15.05.20262</t>
+  </si>
+  <si>
+    <t>15.05.20263</t>
+  </si>
+  <si>
+    <t>15.05.20264</t>
+  </si>
+  <si>
+    <t>15.05.20265</t>
+  </si>
+  <si>
+    <t>15.05.20266</t>
+  </si>
+  <si>
+    <t>15.05.20267</t>
+  </si>
+  <si>
+    <t>15.05.20268</t>
+  </si>
+  <si>
+    <t>15.05.20269</t>
+  </si>
+  <si>
+    <t>15.05.202610</t>
+  </si>
+  <si>
+    <t>15.05.202611</t>
+  </si>
+  <si>
+    <t>15.05.202612</t>
+  </si>
+  <si>
+    <t>15.05.202613</t>
+  </si>
+  <si>
+    <t>15.05.202614</t>
+  </si>
+  <si>
+    <t>15.05.202615</t>
+  </si>
+  <si>
+    <t>15.05.202616</t>
+  </si>
+  <si>
+    <t>15.05.202617</t>
+  </si>
+  <si>
+    <t>15.05.202618</t>
+  </si>
+  <si>
+    <t>15.05.202619</t>
+  </si>
+  <si>
+    <t>15.05.202620</t>
+  </si>
+  <si>
+    <t>15.05.202621</t>
+  </si>
+  <si>
+    <t>15.05.202622</t>
+  </si>
+  <si>
+    <t>15.05.202623</t>
+  </si>
+  <si>
+    <t>15.05.202624</t>
+  </si>
+  <si>
+    <t>15.05.202625</t>
+  </si>
+  <si>
+    <t>15.05.202626</t>
+  </si>
+  <si>
+    <t>15.05.202627</t>
+  </si>
+  <si>
+    <t>15.05.202628</t>
+  </si>
+  <si>
+    <t>15.05.202629</t>
+  </si>
+  <si>
+    <t>15.05.202630</t>
+  </si>
+  <si>
+    <t>15.05.202631</t>
+  </si>
+  <si>
+    <t>15.05.202632</t>
+  </si>
+  <si>
+    <t>15.05.202633</t>
+  </si>
+  <si>
+    <t>15.05.202634</t>
+  </si>
+  <si>
+    <t>15.05.202635</t>
+  </si>
+  <si>
+    <t>15.05.202636</t>
+  </si>
+  <si>
+    <t>15.05.202637</t>
+  </si>
+  <si>
+    <t>15.05.202638</t>
+  </si>
+  <si>
+    <t>15.05.202639</t>
+  </si>
+  <si>
+    <t>15.05.202640</t>
+  </si>
+  <si>
+    <t>15.05.202641</t>
+  </si>
+  <si>
+    <t>15.05.202642</t>
+  </si>
+  <si>
+    <t>15.05.202643</t>
+  </si>
+  <si>
+    <t>15.05.202644</t>
+  </si>
+  <si>
+    <t>15.05.202645</t>
+  </si>
+  <si>
+    <t>15.05.202646</t>
+  </si>
+  <si>
+    <t>15.05.202647</t>
+  </si>
+  <si>
+    <t>15.05.202648</t>
+  </si>
+  <si>
+    <t>15.05.202649</t>
+  </si>
+  <si>
+    <t>15.05.202650</t>
+  </si>
+  <si>
+    <t>15.05.202651</t>
+  </si>
+  <si>
+    <t>15.05.202652</t>
+  </si>
+  <si>
+    <t>15.05.202653</t>
+  </si>
+  <si>
+    <t>15.05.202654</t>
+  </si>
+  <si>
+    <t>15.05.202655</t>
+  </si>
+  <si>
+    <t>15.05.202656</t>
+  </si>
+  <si>
+    <t>15.05.202657</t>
+  </si>
+  <si>
+    <t>15.05.202658</t>
+  </si>
+  <si>
+    <t>15.05.202659</t>
+  </si>
+  <si>
+    <t>15.05.202660</t>
+  </si>
+  <si>
+    <t>15.05.202661</t>
+  </si>
+  <si>
+    <t>15.05.202662</t>
+  </si>
+  <si>
+    <t>15.05.202663</t>
+  </si>
+  <si>
+    <t>15.05.202664</t>
+  </si>
+  <si>
+    <t>15.05.202665</t>
+  </si>
+  <si>
+    <t>15.05.202666</t>
+  </si>
+  <si>
+    <t>15.05.202667</t>
+  </si>
+  <si>
+    <t>15.05.202668</t>
+  </si>
+  <si>
+    <t>15.05.202669</t>
+  </si>
+  <si>
+    <t>15.05.202670</t>
+  </si>
+  <si>
+    <t>15.05.202671</t>
+  </si>
+  <si>
+    <t>15.05.202672</t>
+  </si>
+  <si>
+    <t>15.05.202673</t>
+  </si>
+  <si>
+    <t>15.05.202674</t>
+  </si>
+  <si>
+    <t>15.05.202675</t>
+  </si>
+  <si>
+    <t>15.05.202676</t>
+  </si>
+  <si>
+    <t>15.05.202677</t>
+  </si>
+  <si>
+    <t>15.05.202678</t>
+  </si>
+  <si>
+    <t>15.05.202679</t>
+  </si>
+  <si>
+    <t>15.05.202680</t>
+  </si>
+  <si>
+    <t>15.05.202681</t>
+  </si>
+  <si>
+    <t>15.05.202682</t>
+  </si>
+  <si>
+    <t>15.05.202683</t>
+  </si>
+  <si>
+    <t>15.05.202684</t>
+  </si>
+  <si>
+    <t>15.05.202685</t>
+  </si>
+  <si>
+    <t>15.05.202686</t>
+  </si>
+  <si>
+    <t>15.05.202687</t>
+  </si>
+  <si>
+    <t>15.05.202688</t>
+  </si>
+  <si>
+    <t>15.05.202689</t>
+  </si>
+  <si>
+    <t>15.05.202690</t>
+  </si>
+  <si>
+    <t>15.05.202691</t>
+  </si>
+  <si>
+    <t>15.05.202692</t>
+  </si>
+  <si>
+    <t>15.05.202693</t>
+  </si>
+  <si>
+    <t>15.05.202694</t>
+  </si>
+  <si>
+    <t>15.05.202695</t>
+  </si>
+  <si>
+    <t>15.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>21.296</v>
       </c>
       <c r="C2">
-        <v>30.354</v>
+        <v>0.676</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>8.619</v>
       </c>
       <c r="C3">
-        <v>13.044</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.259</v>
+        <v>6.252</v>
       </c>
       <c r="C4">
-        <v>0.442</v>
+        <v>0.221</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B5">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.296</v>
+        <v>10.249</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.128</v>
+        <v>6.186</v>
       </c>
       <c r="C6">
-        <v>5.482</v>
+        <v>0.302</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.062</v>
+        <v>0.027</v>
       </c>
       <c r="C7">
-        <v>0.313</v>
+        <v>3.083</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B8">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.209</v>
+        <v>6.538</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.113</v>
+        <v>0.497</v>
       </c>
       <c r="C9">
-        <v>0.113</v>
+        <v>1.567</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.08400000000000001</v>
+        <v>0.225</v>
       </c>
       <c r="C10">
-        <v>0.15</v>
+        <v>0.179</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B11">
-        <v>1.065</v>
+        <v>0.093</v>
       </c>
       <c r="C11">
-        <v>0.005</v>
+        <v>0.611</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.094</v>
+        <v>0.014</v>
       </c>
       <c r="C12">
-        <v>0.663</v>
+        <v>1.011</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.055</v>
+        <v>4.552</v>
       </c>
       <c r="C13">
-        <v>0.448</v>
+        <v>0.104</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>6.626</v>
       </c>
       <c r="C14">
-        <v>12.56</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>3.245</v>
       </c>
       <c r="C15">
-        <v>18.254</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2.298</v>
       </c>
       <c r="C16">
-        <v>6.236</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>4.855</v>
       </c>
       <c r="C17">
-        <v>24.51</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2.196</v>
       </c>
       <c r="C18">
-        <v>38.98</v>
+        <v>0.005</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="C19">
-        <v>15.312</v>
+        <v>0.064</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B20">
-        <v>6.457</v>
+        <v>3.11</v>
       </c>
       <c r="C20">
-        <v>1.031</v>
+        <v>0.017</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.527</v>
+        <v>2.32</v>
       </c>
       <c r="C21">
-        <v>0.18</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.047</v>
+        <v>1.162</v>
       </c>
       <c r="C22">
-        <v>1.526</v>
+        <v>0.029</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B23">
-        <v>0.006</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C23">
-        <v>12.487</v>
+        <v>0.114</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>5.909</v>
       </c>
       <c r="C24">
-        <v>18.074</v>
+        <v>0.015</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1.627</v>
       </c>
       <c r="C25">
-        <v>10.909</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B26">
-        <v>0.056</v>
+        <v>6.47</v>
       </c>
       <c r="C26">
-        <v>21.624</v>
+        <v>0.012</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.166</v>
+        <v>7.578</v>
       </c>
       <c r="C27">
-        <v>0.303</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.654</v>
+        <v>0.823</v>
       </c>
       <c r="C28">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B29">
-        <v>7.9</v>
+        <v>8.182</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B30">
-        <v>10.926</v>
+        <v>24.259</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,10 +1667,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B31">
-        <v>6.827</v>
+        <v>12.675</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B32">
-        <v>5.253</v>
+        <v>1.783</v>
       </c>
       <c r="C32">
-        <v>0.021</v>
+        <v>2.623</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,13 +1713,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.678</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.187</v>
+        <v>6.118</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.194</v>
+        <v>29.044</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1759,13 +1759,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B35">
-        <v>0.249</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.251</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1782,13 +1782,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.257</v>
+        <v>0.153</v>
       </c>
       <c r="C36">
-        <v>2.673</v>
+        <v>0.877</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1.174</v>
       </c>
       <c r="C37">
-        <v>19.071</v>
+        <v>3.431</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>17.907</v>
+        <v>29.068</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>17.884</v>
+        <v>27.247</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>9.659000000000001</v>
+        <v>30.827</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B41">
-        <v>0.9389999999999999</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1.005</v>
+        <v>21.278</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B42">
-        <v>2.391</v>
+        <v>0.173</v>
       </c>
       <c r="C42">
-        <v>0.003</v>
+        <v>2.756</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B43">
-        <v>6.681</v>
+        <v>0.029</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B44">
-        <v>16.88</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0.004</v>
+        <v>26.82</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B45">
-        <v>11.524</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>46.857</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B46">
-        <v>2.542</v>
+        <v>0.032</v>
       </c>
       <c r="C46">
-        <v>0.003</v>
+        <v>6.227</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B47">
-        <v>0.006</v>
+        <v>0.164</v>
       </c>
       <c r="C47">
-        <v>9.779</v>
+        <v>0.28</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.102</v>
+        <v>0.089</v>
       </c>
       <c r="C48">
-        <v>1.439</v>
+        <v>5.479</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>13.094</v>
+        <v>3.807</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="C50">
-        <v>30.011</v>
+        <v>4.644</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>32.887</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C52">
-        <v>39.682</v>
+        <v>12.729</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1.128</v>
       </c>
       <c r="C53">
-        <v>3.124</v>
+        <v>0.223</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="C54">
-        <v>4.182</v>
+        <v>0.279</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.01</v>
+        <v>6.101</v>
       </c>
       <c r="C55">
-        <v>22.346</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>12.435</v>
       </c>
       <c r="C56">
-        <v>50.409</v>
+        <v>0.052</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>2.199</v>
       </c>
       <c r="C57">
-        <v>20.846</v>
+        <v>3.85</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>13.719</v>
+        <v>12.291</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B59">
-        <v>0.077</v>
+        <v>0.011</v>
       </c>
       <c r="C59">
-        <v>0.858</v>
+        <v>4.374</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.126</v>
+        <v>0.062</v>
       </c>
       <c r="C60">
-        <v>0.308</v>
+        <v>2.35</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="C61">
-        <v>7.028</v>
+        <v>11.564</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>12.739</v>
+        <v>33.133</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>16.961</v>
+        <v>17.479</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>12.412</v>
+        <v>17.821</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B65">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>0.734</v>
+        <v>22.053</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B66">
-        <v>4.895</v>
+        <v>0.091</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B67">
-        <v>2.691</v>
+        <v>0.161</v>
       </c>
       <c r="C67">
-        <v>0.776</v>
+        <v>0.293</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B68">
-        <v>6.209</v>
+        <v>0.043</v>
       </c>
       <c r="C68">
-        <v>0.597</v>
+        <v>6.309</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B69">
-        <v>1.668</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>0.414</v>
+        <v>19.076</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B70">
-        <v>8.538</v>
+        <v>0.612</v>
       </c>
       <c r="C70">
-        <v>0.659</v>
+        <v>0.473</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B71">
-        <v>2.772</v>
+        <v>1.699</v>
       </c>
       <c r="C71">
-        <v>0.301</v>
+        <v>6.377</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>49.25</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +2610,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.285</v>
+        <v>6.649</v>
       </c>
       <c r="C72">
-        <v>4.654</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B73">
-        <v>1.059</v>
+        <v>1.494</v>
       </c>
       <c r="C73">
-        <v>0.229</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B74">
-        <v>0.697</v>
+        <v>0.006</v>
       </c>
       <c r="C74">
-        <v>15.344</v>
+        <v>2.725</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B75">
-        <v>1.39</v>
+        <v>2.242</v>
       </c>
       <c r="C75">
-        <v>0.278</v>
+        <v>1.093</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2702,13 +2702,13 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.59</v>
+        <v>4.469</v>
       </c>
       <c r="C76">
-        <v>4.386</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2725,13 +2725,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B77">
-        <v>0.124</v>
+        <v>21.567</v>
       </c>
       <c r="C77">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>6.219</v>
       </c>
       <c r="C78">
-        <v>28.933</v>
+        <v>0.015</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B79">
-        <v>3.274</v>
+        <v>8.959</v>
       </c>
       <c r="C79">
-        <v>0.065</v>
+        <v>0.003</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B80">
-        <v>1.215</v>
+        <v>18.048</v>
       </c>
       <c r="C80">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B81">
-        <v>2.196</v>
+        <v>32.16</v>
       </c>
       <c r="C81">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.201</v>
+        <v>33.44</v>
       </c>
       <c r="C82">
-        <v>0.381</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,19 +2863,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B83">
-        <v>0.104</v>
+        <v>32.689</v>
       </c>
       <c r="C83">
-        <v>0.8090000000000001</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -2886,19 +2886,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B84">
-        <v>1.415</v>
+        <v>31.61</v>
       </c>
       <c r="C84">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>83</v>
@@ -2909,19 +2909,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.253</v>
+        <v>60.721</v>
       </c>
       <c r="C85">
-        <v>0.186</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F85">
         <v>84</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B86">
-        <v>5.245</v>
+        <v>74.947</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F86">
         <v>85</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B87">
-        <v>5.116</v>
+        <v>80.181</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.305</v>
+        <v>10.579</v>
       </c>
       <c r="C88">
-        <v>0.63</v>
+        <v>0.061</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E88">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B89">
-        <v>16.358</v>
+        <v>0.757</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E89">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3024,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B90">
-        <v>23.776</v>
+        <v>0.407</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E90">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.793</v>
+        <v>0.055</v>
       </c>
       <c r="C91">
-        <v>0.008999999999999999</v>
+        <v>0.372</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B92">
-        <v>4.937</v>
+        <v>0.358</v>
       </c>
       <c r="C92">
-        <v>0.335</v>
+        <v>0.107</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="C93">
-        <v>15.33</v>
+        <v>0.178</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>1.556</v>
       </c>
       <c r="C94">
-        <v>12.663</v>
+        <v>0.155</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>35.505</v>
+        <v>5.737</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C96">
-        <v>20.134</v>
+        <v>4.139</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>15.242</v>
+        <v>0.575</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B98">
-        <v>21.296</v>
+        <v>0.364</v>
       </c>
       <c r="C98">
-        <v>0.676</v>
+        <v>0.059</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B99">
-        <v>21.296</v>
+        <v>0.364</v>
       </c>
       <c r="C99">
-        <v>0.676</v>
+        <v>0.059</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B100">
-        <v>8.619</v>
+        <v>0.012</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B101">
-        <v>8.619</v>
+        <v>0.012</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B102">
-        <v>6.252</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>0.221</v>
+        <v>4.767</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B103">
-        <v>6.252</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0.221</v>
+        <v>4.767</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>10.249</v>
+        <v>12.899</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>10.249</v>
+        <v>12.899</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B106">
-        <v>6.186</v>
+        <v>0.001</v>
       </c>
       <c r="C106">
-        <v>0.302</v>
+        <v>7.051</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B107">
-        <v>6.186</v>
+        <v>0.001</v>
       </c>
       <c r="C107">
-        <v>0.302</v>
+        <v>7.051</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B108">
-        <v>0.027</v>
+        <v>1.021</v>
       </c>
       <c r="C108">
-        <v>3.083</v>
+        <v>0.004</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B109">
-        <v>0.027</v>
+        <v>1.021</v>
       </c>
       <c r="C109">
-        <v>3.083</v>
+        <v>0.004</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="C110">
-        <v>6.538</v>
+        <v>5.597</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="C111">
-        <v>6.538</v>
+        <v>5.597</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B112">
-        <v>0.497</v>
+        <v>0.028</v>
       </c>
       <c r="C112">
-        <v>1.567</v>
+        <v>1.427</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.497</v>
+        <v>0.028</v>
       </c>
       <c r="C113">
-        <v>1.567</v>
+        <v>1.427</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46156.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B114">
-        <v>0.225</v>
+        <v>5.673</v>
       </c>
       <c r="C114">
-        <v>0.179</v>
+        <v>0.187</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46156.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B115">
-        <v>0.093</v>
+        <v>0.213</v>
       </c>
       <c r="C115">
-        <v>0.611</v>
+        <v>0.148</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46156.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B116">
-        <v>0.014</v>
+        <v>3.304</v>
       </c>
       <c r="C116">
-        <v>1.011</v>
+        <v>0.028</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46156.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B117">
-        <v>4.552</v>
+        <v>4.051</v>
       </c>
       <c r="C117">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46156.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B118">
-        <v>6.626</v>
+        <v>2.157</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46156.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B119">
-        <v>3.245</v>
+        <v>0.024</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>2.035</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46156.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B120">
-        <v>2.298</v>
+        <v>0.035</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>0.897</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46156.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B121">
-        <v>4.855</v>
+        <v>0.061</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46156.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B122">
-        <v>2.196</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>0.005</v>
+        <v>5.915</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46156.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B123">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0.064</v>
+        <v>39.571</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46156.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B124">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0.017</v>
+        <v>41.602</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46156.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B125">
-        <v>2.32</v>
+        <v>0.026</v>
       </c>
       <c r="C125">
-        <v>0.08400000000000001</v>
+        <v>6.124</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46156.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B126">
-        <v>1.162</v>
+        <v>0.058</v>
       </c>
       <c r="C126">
-        <v>0.029</v>
+        <v>3.799</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46156.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B127">
-        <v>0.5659999999999999</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>0.114</v>
+        <v>2.6</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46156.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B128">
-        <v>5.909</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>0.015</v>
+        <v>2.86</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46156.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B129">
-        <v>1.627</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>0.06900000000000001</v>
+        <v>4.071</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46156.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B130">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>0.012</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46156.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B131">
-        <v>7.578</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,13 +3990,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46156.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.823</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>15.759</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46156.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B133">
-        <v>8.182</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>25.306</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46156.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B134">
-        <v>24.259</v>
+        <v>0.362</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>3.515</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46156.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B135">
-        <v>12.675</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>13.834</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46156.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B136">
-        <v>1.783</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>2.623</v>
+        <v>10.982</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,13 +4105,13 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46156.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>6.118</v>
+        <v>22.297</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46156.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
       <c r="C138">
-        <v>29.044</v>
+        <v>6.265</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46156.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="C139">
-        <v>8.010999999999999</v>
+        <v>0.187</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46156.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B140">
-        <v>0.153</v>
+        <v>0.132</v>
       </c>
       <c r="C140">
-        <v>0.877</v>
+        <v>0.125</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,19 +4197,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46156.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B141">
-        <v>1.174</v>
+        <v>0.168</v>
       </c>
       <c r="C141">
-        <v>3.431</v>
+        <v>0.082</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>36</v>
@@ -4220,19 +4220,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46156.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>2.917</v>
       </c>
       <c r="C142">
-        <v>29.068</v>
+        <v>0.199</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>37</v>
@@ -4243,19 +4243,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46156.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="C143">
-        <v>27.247</v>
+        <v>0.359</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>38</v>
@@ -4266,19 +4266,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46156.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="C144">
-        <v>30.827</v>
+        <v>0.41</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>39</v>
@@ -4289,19 +4289,19 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46156.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>21.278</v>
+        <v>5.679</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <v>40</v>
@@ -4312,19 +4312,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46156.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B146">
-        <v>0.173</v>
+        <v>0.034</v>
       </c>
       <c r="C146">
-        <v>2.756</v>
+        <v>2.079</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>41</v>
@@ -4335,19 +4335,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46156.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B147">
-        <v>0.029</v>
+        <v>0.393</v>
       </c>
       <c r="C147">
-        <v>0.625</v>
+        <v>7.014</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>42</v>
@@ -4358,19 +4358,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46156.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>13.755</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>43</v>
@@ -4381,19 +4381,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46156.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>16.603</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>44</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46156.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46156.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46156.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46156.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46156.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46156.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46156.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46156.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46156.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46156.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46156.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46156.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46156.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46156.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46156.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46156.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46156.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46156.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46156.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46156.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46156.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46156.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46156.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46156.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46156.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46156.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46156.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46156.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46156.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46156.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46156.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46156.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46156.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46156.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46156.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46156.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46156.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46156.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46156.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46156.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46156.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46156.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46156.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46156.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46156.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46156.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46156.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46156.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46156.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46156.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46156.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46156.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.05.20261</t>
-  </si>
-  <si>
-    <t>14.05.20262</t>
-  </si>
-  <si>
-    <t>14.05.20263</t>
-  </si>
-  <si>
-    <t>14.05.20264</t>
-  </si>
-  <si>
-    <t>14.05.20265</t>
-  </si>
-  <si>
-    <t>14.05.20266</t>
-  </si>
-  <si>
-    <t>14.05.20267</t>
-  </si>
-  <si>
-    <t>14.05.20268</t>
-  </si>
-  <si>
-    <t>14.05.20269</t>
-  </si>
-  <si>
-    <t>14.05.202610</t>
-  </si>
-  <si>
-    <t>14.05.202611</t>
-  </si>
-  <si>
-    <t>14.05.202612</t>
-  </si>
-  <si>
-    <t>14.05.202613</t>
-  </si>
-  <si>
-    <t>14.05.202614</t>
-  </si>
-  <si>
-    <t>14.05.202615</t>
-  </si>
-  <si>
-    <t>14.05.202616</t>
-  </si>
-  <si>
-    <t>14.05.202617</t>
-  </si>
-  <si>
-    <t>14.05.202618</t>
-  </si>
-  <si>
-    <t>14.05.202619</t>
-  </si>
-  <si>
-    <t>14.05.202620</t>
-  </si>
-  <si>
-    <t>14.05.202621</t>
-  </si>
-  <si>
-    <t>14.05.202622</t>
-  </si>
-  <si>
-    <t>14.05.202623</t>
-  </si>
-  <si>
-    <t>14.05.202624</t>
-  </si>
-  <si>
-    <t>14.05.202625</t>
-  </si>
-  <si>
-    <t>14.05.202626</t>
-  </si>
-  <si>
-    <t>14.05.202627</t>
-  </si>
-  <si>
-    <t>14.05.202628</t>
-  </si>
-  <si>
-    <t>14.05.202629</t>
-  </si>
-  <si>
-    <t>14.05.202630</t>
-  </si>
-  <si>
-    <t>14.05.202631</t>
-  </si>
-  <si>
-    <t>14.05.202632</t>
-  </si>
-  <si>
-    <t>14.05.202633</t>
-  </si>
-  <si>
-    <t>14.05.202634</t>
-  </si>
-  <si>
-    <t>14.05.202635</t>
-  </si>
-  <si>
-    <t>14.05.202636</t>
-  </si>
-  <si>
-    <t>14.05.202637</t>
-  </si>
-  <si>
-    <t>14.05.202638</t>
-  </si>
-  <si>
-    <t>14.05.202639</t>
-  </si>
-  <si>
-    <t>14.05.202640</t>
-  </si>
-  <si>
-    <t>14.05.202641</t>
-  </si>
-  <si>
-    <t>14.05.202642</t>
-  </si>
-  <si>
-    <t>14.05.202643</t>
-  </si>
-  <si>
-    <t>14.05.202644</t>
-  </si>
-  <si>
-    <t>14.05.202645</t>
-  </si>
-  <si>
-    <t>14.05.202646</t>
-  </si>
-  <si>
-    <t>14.05.202647</t>
-  </si>
-  <si>
-    <t>14.05.202648</t>
-  </si>
-  <si>
-    <t>14.05.202649</t>
-  </si>
-  <si>
-    <t>14.05.202650</t>
-  </si>
-  <si>
-    <t>14.05.202651</t>
-  </si>
-  <si>
-    <t>14.05.202652</t>
-  </si>
-  <si>
-    <t>14.05.202653</t>
-  </si>
-  <si>
-    <t>14.05.202654</t>
-  </si>
-  <si>
-    <t>14.05.202655</t>
-  </si>
-  <si>
-    <t>14.05.202656</t>
-  </si>
-  <si>
-    <t>14.05.202657</t>
-  </si>
-  <si>
-    <t>14.05.202658</t>
-  </si>
-  <si>
-    <t>14.05.202659</t>
-  </si>
-  <si>
-    <t>14.05.202660</t>
-  </si>
-  <si>
-    <t>14.05.202661</t>
-  </si>
-  <si>
-    <t>14.05.202662</t>
-  </si>
-  <si>
-    <t>14.05.202663</t>
-  </si>
-  <si>
-    <t>14.05.202664</t>
-  </si>
-  <si>
-    <t>14.05.202665</t>
-  </si>
-  <si>
-    <t>14.05.202666</t>
-  </si>
-  <si>
-    <t>14.05.202667</t>
-  </si>
-  <si>
-    <t>14.05.202668</t>
-  </si>
-  <si>
-    <t>14.05.202669</t>
-  </si>
-  <si>
-    <t>14.05.202670</t>
-  </si>
-  <si>
-    <t>14.05.202671</t>
-  </si>
-  <si>
-    <t>14.05.202672</t>
-  </si>
-  <si>
-    <t>14.05.202673</t>
-  </si>
-  <si>
-    <t>14.05.202674</t>
-  </si>
-  <si>
-    <t>14.05.202675</t>
-  </si>
-  <si>
-    <t>14.05.202676</t>
-  </si>
-  <si>
-    <t>14.05.202677</t>
-  </si>
-  <si>
-    <t>14.05.202678</t>
-  </si>
-  <si>
-    <t>14.05.202679</t>
-  </si>
-  <si>
-    <t>14.05.202680</t>
-  </si>
-  <si>
-    <t>14.05.202681</t>
-  </si>
-  <si>
-    <t>14.05.202682</t>
-  </si>
-  <si>
-    <t>14.05.202683</t>
-  </si>
-  <si>
-    <t>14.05.202684</t>
-  </si>
-  <si>
-    <t>14.05.202685</t>
-  </si>
-  <si>
-    <t>14.05.202686</t>
-  </si>
-  <si>
-    <t>14.05.202687</t>
-  </si>
-  <si>
-    <t>14.05.202688</t>
-  </si>
-  <si>
-    <t>14.05.202689</t>
-  </si>
-  <si>
-    <t>14.05.202690</t>
-  </si>
-  <si>
-    <t>14.05.202691</t>
-  </si>
-  <si>
-    <t>14.05.202692</t>
-  </si>
-  <si>
-    <t>14.05.202693</t>
-  </si>
-  <si>
-    <t>14.05.202694</t>
-  </si>
-  <si>
-    <t>14.05.202695</t>
-  </si>
-  <si>
-    <t>14.05.202696</t>
-  </si>
-  <si>
-    <t>15.05.20261</t>
-  </si>
-  <si>
-    <t>15.05.20262</t>
-  </si>
-  <si>
-    <t>15.05.20263</t>
-  </si>
-  <si>
-    <t>15.05.20264</t>
-  </si>
-  <si>
-    <t>15.05.20265</t>
-  </si>
-  <si>
-    <t>15.05.20266</t>
-  </si>
-  <si>
-    <t>15.05.20267</t>
-  </si>
-  <si>
-    <t>15.05.20268</t>
-  </si>
-  <si>
-    <t>15.05.20269</t>
-  </si>
-  <si>
-    <t>15.05.202610</t>
-  </si>
-  <si>
-    <t>15.05.202611</t>
-  </si>
-  <si>
-    <t>15.05.202612</t>
-  </si>
-  <si>
-    <t>15.05.202613</t>
-  </si>
-  <si>
-    <t>15.05.202614</t>
-  </si>
-  <si>
-    <t>15.05.202615</t>
-  </si>
-  <si>
-    <t>15.05.202616</t>
-  </si>
-  <si>
-    <t>15.05.202617</t>
-  </si>
-  <si>
-    <t>15.05.202618</t>
-  </si>
-  <si>
-    <t>15.05.202619</t>
-  </si>
-  <si>
-    <t>15.05.202620</t>
-  </si>
-  <si>
-    <t>15.05.202621</t>
-  </si>
-  <si>
-    <t>15.05.202622</t>
-  </si>
-  <si>
-    <t>15.05.202623</t>
-  </si>
-  <si>
-    <t>15.05.202624</t>
-  </si>
-  <si>
-    <t>15.05.202625</t>
-  </si>
-  <si>
-    <t>15.05.202626</t>
-  </si>
-  <si>
-    <t>15.05.202627</t>
-  </si>
-  <si>
-    <t>15.05.202628</t>
-  </si>
-  <si>
-    <t>15.05.202629</t>
-  </si>
-  <si>
-    <t>15.05.202630</t>
-  </si>
-  <si>
-    <t>15.05.202631</t>
-  </si>
-  <si>
-    <t>15.05.202632</t>
-  </si>
-  <si>
-    <t>15.05.202633</t>
-  </si>
-  <si>
-    <t>15.05.202634</t>
-  </si>
-  <si>
-    <t>15.05.202635</t>
-  </si>
-  <si>
-    <t>15.05.202636</t>
-  </si>
-  <si>
-    <t>15.05.202637</t>
-  </si>
-  <si>
-    <t>15.05.202638</t>
-  </si>
-  <si>
-    <t>15.05.202639</t>
-  </si>
-  <si>
-    <t>15.05.202640</t>
-  </si>
-  <si>
-    <t>15.05.202641</t>
-  </si>
-  <si>
-    <t>15.05.202642</t>
-  </si>
-  <si>
-    <t>15.05.202643</t>
-  </si>
-  <si>
-    <t>15.05.202644</t>
-  </si>
-  <si>
-    <t>15.05.202645</t>
-  </si>
-  <si>
-    <t>15.05.202646</t>
-  </si>
-  <si>
-    <t>15.05.202647</t>
-  </si>
-  <si>
-    <t>15.05.202648</t>
-  </si>
-  <si>
-    <t>15.05.202649</t>
-  </si>
-  <si>
-    <t>15.05.202650</t>
-  </si>
-  <si>
-    <t>15.05.202651</t>
-  </si>
-  <si>
-    <t>15.05.202652</t>
-  </si>
-  <si>
-    <t>15.05.202653</t>
-  </si>
-  <si>
-    <t>15.05.202654</t>
-  </si>
-  <si>
-    <t>15.05.202655</t>
-  </si>
-  <si>
-    <t>15.05.202656</t>
-  </si>
-  <si>
-    <t>15.05.202657</t>
-  </si>
-  <si>
-    <t>15.05.202658</t>
-  </si>
-  <si>
-    <t>15.05.202659</t>
-  </si>
-  <si>
-    <t>15.05.202660</t>
-  </si>
-  <si>
-    <t>15.05.202661</t>
-  </si>
-  <si>
-    <t>15.05.202662</t>
-  </si>
-  <si>
-    <t>15.05.202663</t>
-  </si>
-  <si>
-    <t>15.05.202664</t>
-  </si>
-  <si>
-    <t>15.05.202665</t>
-  </si>
-  <si>
-    <t>15.05.202666</t>
-  </si>
-  <si>
-    <t>15.05.202667</t>
-  </si>
-  <si>
-    <t>15.05.202668</t>
-  </si>
-  <si>
-    <t>15.05.202669</t>
-  </si>
-  <si>
-    <t>15.05.202670</t>
-  </si>
-  <si>
-    <t>15.05.202671</t>
-  </si>
-  <si>
-    <t>15.05.202672</t>
-  </si>
-  <si>
-    <t>15.05.202673</t>
-  </si>
-  <si>
-    <t>15.05.202674</t>
-  </si>
-  <si>
-    <t>15.05.202675</t>
-  </si>
-  <si>
-    <t>15.05.202676</t>
-  </si>
-  <si>
-    <t>15.05.202677</t>
-  </si>
-  <si>
-    <t>15.05.202678</t>
-  </si>
-  <si>
-    <t>15.05.202679</t>
-  </si>
-  <si>
-    <t>15.05.202680</t>
-  </si>
-  <si>
-    <t>15.05.202681</t>
-  </si>
-  <si>
-    <t>15.05.202682</t>
-  </si>
-  <si>
-    <t>15.05.202683</t>
-  </si>
-  <si>
-    <t>15.05.202684</t>
-  </si>
-  <si>
-    <t>15.05.202685</t>
-  </si>
-  <si>
-    <t>15.05.202686</t>
-  </si>
-  <si>
-    <t>15.05.202687</t>
-  </si>
-  <si>
-    <t>15.05.202688</t>
-  </si>
-  <si>
-    <t>15.05.202689</t>
-  </si>
-  <si>
-    <t>15.05.202690</t>
-  </si>
-  <si>
-    <t>15.05.202691</t>
-  </si>
-  <si>
-    <t>15.05.202692</t>
-  </si>
-  <si>
-    <t>15.05.202693</t>
-  </si>
-  <si>
-    <t>15.05.202694</t>
-  </si>
-  <si>
-    <t>15.05.202695</t>
-  </si>
-  <si>
-    <t>15.05.202696</t>
+    <t>20.05.20261</t>
+  </si>
+  <si>
+    <t>20.05.20262</t>
+  </si>
+  <si>
+    <t>20.05.20263</t>
+  </si>
+  <si>
+    <t>20.05.20264</t>
+  </si>
+  <si>
+    <t>20.05.20265</t>
+  </si>
+  <si>
+    <t>20.05.20266</t>
+  </si>
+  <si>
+    <t>20.05.20267</t>
+  </si>
+  <si>
+    <t>20.05.20268</t>
+  </si>
+  <si>
+    <t>20.05.20269</t>
+  </si>
+  <si>
+    <t>20.05.202610</t>
+  </si>
+  <si>
+    <t>20.05.202611</t>
+  </si>
+  <si>
+    <t>20.05.202612</t>
+  </si>
+  <si>
+    <t>20.05.202613</t>
+  </si>
+  <si>
+    <t>20.05.202614</t>
+  </si>
+  <si>
+    <t>20.05.202615</t>
+  </si>
+  <si>
+    <t>20.05.202616</t>
+  </si>
+  <si>
+    <t>20.05.202617</t>
+  </si>
+  <si>
+    <t>20.05.202618</t>
+  </si>
+  <si>
+    <t>20.05.202619</t>
+  </si>
+  <si>
+    <t>20.05.202620</t>
+  </si>
+  <si>
+    <t>20.05.202621</t>
+  </si>
+  <si>
+    <t>20.05.202622</t>
+  </si>
+  <si>
+    <t>20.05.202623</t>
+  </si>
+  <si>
+    <t>20.05.202624</t>
+  </si>
+  <si>
+    <t>20.05.202625</t>
+  </si>
+  <si>
+    <t>20.05.202626</t>
+  </si>
+  <si>
+    <t>20.05.202627</t>
+  </si>
+  <si>
+    <t>20.05.202628</t>
+  </si>
+  <si>
+    <t>20.05.202629</t>
+  </si>
+  <si>
+    <t>20.05.202630</t>
+  </si>
+  <si>
+    <t>20.05.202631</t>
+  </si>
+  <si>
+    <t>20.05.202632</t>
+  </si>
+  <si>
+    <t>20.05.202633</t>
+  </si>
+  <si>
+    <t>20.05.202634</t>
+  </si>
+  <si>
+    <t>20.05.202635</t>
+  </si>
+  <si>
+    <t>20.05.202636</t>
+  </si>
+  <si>
+    <t>20.05.202637</t>
+  </si>
+  <si>
+    <t>20.05.202638</t>
+  </si>
+  <si>
+    <t>20.05.202639</t>
+  </si>
+  <si>
+    <t>20.05.202640</t>
+  </si>
+  <si>
+    <t>20.05.202641</t>
+  </si>
+  <si>
+    <t>20.05.202642</t>
+  </si>
+  <si>
+    <t>20.05.202643</t>
+  </si>
+  <si>
+    <t>20.05.202644</t>
+  </si>
+  <si>
+    <t>20.05.202645</t>
+  </si>
+  <si>
+    <t>20.05.202646</t>
+  </si>
+  <si>
+    <t>20.05.202647</t>
+  </si>
+  <si>
+    <t>20.05.202648</t>
+  </si>
+  <si>
+    <t>20.05.202649</t>
+  </si>
+  <si>
+    <t>20.05.202650</t>
+  </si>
+  <si>
+    <t>20.05.202651</t>
+  </si>
+  <si>
+    <t>20.05.202652</t>
+  </si>
+  <si>
+    <t>20.05.202653</t>
+  </si>
+  <si>
+    <t>20.05.202654</t>
+  </si>
+  <si>
+    <t>20.05.202655</t>
+  </si>
+  <si>
+    <t>20.05.202656</t>
+  </si>
+  <si>
+    <t>20.05.202657</t>
+  </si>
+  <si>
+    <t>20.05.202658</t>
+  </si>
+  <si>
+    <t>20.05.202659</t>
+  </si>
+  <si>
+    <t>20.05.202660</t>
+  </si>
+  <si>
+    <t>20.05.202661</t>
+  </si>
+  <si>
+    <t>20.05.202662</t>
+  </si>
+  <si>
+    <t>20.05.202663</t>
+  </si>
+  <si>
+    <t>20.05.202664</t>
+  </si>
+  <si>
+    <t>20.05.202665</t>
+  </si>
+  <si>
+    <t>20.05.202666</t>
+  </si>
+  <si>
+    <t>20.05.202667</t>
+  </si>
+  <si>
+    <t>20.05.202668</t>
+  </si>
+  <si>
+    <t>20.05.202669</t>
+  </si>
+  <si>
+    <t>20.05.202670</t>
+  </si>
+  <si>
+    <t>20.05.202671</t>
+  </si>
+  <si>
+    <t>20.05.202672</t>
+  </si>
+  <si>
+    <t>20.05.202673</t>
+  </si>
+  <si>
+    <t>20.05.202674</t>
+  </si>
+  <si>
+    <t>20.05.202675</t>
+  </si>
+  <si>
+    <t>20.05.202676</t>
+  </si>
+  <si>
+    <t>20.05.202677</t>
+  </si>
+  <si>
+    <t>20.05.202678</t>
+  </si>
+  <si>
+    <t>20.05.202679</t>
+  </si>
+  <si>
+    <t>20.05.202680</t>
+  </si>
+  <si>
+    <t>20.05.202681</t>
+  </si>
+  <si>
+    <t>20.05.202682</t>
+  </si>
+  <si>
+    <t>20.05.202683</t>
+  </si>
+  <si>
+    <t>20.05.202684</t>
+  </si>
+  <si>
+    <t>20.05.202685</t>
+  </si>
+  <si>
+    <t>20.05.202686</t>
+  </si>
+  <si>
+    <t>20.05.202687</t>
+  </si>
+  <si>
+    <t>20.05.202688</t>
+  </si>
+  <si>
+    <t>20.05.202689</t>
+  </si>
+  <si>
+    <t>20.05.202690</t>
+  </si>
+  <si>
+    <t>20.05.202691</t>
+  </si>
+  <si>
+    <t>20.05.202692</t>
+  </si>
+  <si>
+    <t>20.05.202693</t>
+  </si>
+  <si>
+    <t>20.05.202694</t>
+  </si>
+  <si>
+    <t>20.05.202695</t>
+  </si>
+  <si>
+    <t>20.05.202696</t>
+  </si>
+  <si>
+    <t>21.05.20261</t>
+  </si>
+  <si>
+    <t>21.05.20262</t>
+  </si>
+  <si>
+    <t>21.05.20263</t>
+  </si>
+  <si>
+    <t>21.05.20264</t>
+  </si>
+  <si>
+    <t>21.05.20265</t>
+  </si>
+  <si>
+    <t>21.05.20266</t>
+  </si>
+  <si>
+    <t>21.05.20267</t>
+  </si>
+  <si>
+    <t>21.05.20268</t>
+  </si>
+  <si>
+    <t>21.05.20269</t>
+  </si>
+  <si>
+    <t>21.05.202610</t>
+  </si>
+  <si>
+    <t>21.05.202611</t>
+  </si>
+  <si>
+    <t>21.05.202612</t>
+  </si>
+  <si>
+    <t>21.05.202613</t>
+  </si>
+  <si>
+    <t>21.05.202614</t>
+  </si>
+  <si>
+    <t>21.05.202615</t>
+  </si>
+  <si>
+    <t>21.05.202616</t>
+  </si>
+  <si>
+    <t>21.05.202617</t>
+  </si>
+  <si>
+    <t>21.05.202618</t>
+  </si>
+  <si>
+    <t>21.05.202619</t>
+  </si>
+  <si>
+    <t>21.05.202620</t>
+  </si>
+  <si>
+    <t>21.05.202621</t>
+  </si>
+  <si>
+    <t>21.05.202622</t>
+  </si>
+  <si>
+    <t>21.05.202623</t>
+  </si>
+  <si>
+    <t>21.05.202624</t>
+  </si>
+  <si>
+    <t>21.05.202625</t>
+  </si>
+  <si>
+    <t>21.05.202626</t>
+  </si>
+  <si>
+    <t>21.05.202627</t>
+  </si>
+  <si>
+    <t>21.05.202628</t>
+  </si>
+  <si>
+    <t>21.05.202629</t>
+  </si>
+  <si>
+    <t>21.05.202630</t>
+  </si>
+  <si>
+    <t>21.05.202631</t>
+  </si>
+  <si>
+    <t>21.05.202632</t>
+  </si>
+  <si>
+    <t>21.05.202633</t>
+  </si>
+  <si>
+    <t>21.05.202634</t>
+  </si>
+  <si>
+    <t>21.05.202635</t>
+  </si>
+  <si>
+    <t>21.05.202636</t>
+  </si>
+  <si>
+    <t>21.05.202637</t>
+  </si>
+  <si>
+    <t>21.05.202638</t>
+  </si>
+  <si>
+    <t>21.05.202639</t>
+  </si>
+  <si>
+    <t>21.05.202640</t>
+  </si>
+  <si>
+    <t>21.05.202641</t>
+  </si>
+  <si>
+    <t>21.05.202642</t>
+  </si>
+  <si>
+    <t>21.05.202643</t>
+  </si>
+  <si>
+    <t>21.05.202644</t>
+  </si>
+  <si>
+    <t>21.05.202645</t>
+  </si>
+  <si>
+    <t>21.05.202646</t>
+  </si>
+  <si>
+    <t>21.05.202647</t>
+  </si>
+  <si>
+    <t>21.05.202648</t>
+  </si>
+  <si>
+    <t>21.05.202649</t>
+  </si>
+  <si>
+    <t>21.05.202650</t>
+  </si>
+  <si>
+    <t>21.05.202651</t>
+  </si>
+  <si>
+    <t>21.05.202652</t>
+  </si>
+  <si>
+    <t>21.05.202653</t>
+  </si>
+  <si>
+    <t>21.05.202654</t>
+  </si>
+  <si>
+    <t>21.05.202655</t>
+  </si>
+  <si>
+    <t>21.05.202656</t>
+  </si>
+  <si>
+    <t>21.05.202657</t>
+  </si>
+  <si>
+    <t>21.05.202658</t>
+  </si>
+  <si>
+    <t>21.05.202659</t>
+  </si>
+  <si>
+    <t>21.05.202660</t>
+  </si>
+  <si>
+    <t>21.05.202661</t>
+  </si>
+  <si>
+    <t>21.05.202662</t>
+  </si>
+  <si>
+    <t>21.05.202663</t>
+  </si>
+  <si>
+    <t>21.05.202664</t>
+  </si>
+  <si>
+    <t>21.05.202665</t>
+  </si>
+  <si>
+    <t>21.05.202666</t>
+  </si>
+  <si>
+    <t>21.05.202667</t>
+  </si>
+  <si>
+    <t>21.05.202668</t>
+  </si>
+  <si>
+    <t>21.05.202669</t>
+  </si>
+  <si>
+    <t>21.05.202670</t>
+  </si>
+  <si>
+    <t>21.05.202671</t>
+  </si>
+  <si>
+    <t>21.05.202672</t>
+  </si>
+  <si>
+    <t>21.05.202673</t>
+  </si>
+  <si>
+    <t>21.05.202674</t>
+  </si>
+  <si>
+    <t>21.05.202675</t>
+  </si>
+  <si>
+    <t>21.05.202676</t>
+  </si>
+  <si>
+    <t>21.05.202677</t>
+  </si>
+  <si>
+    <t>21.05.202678</t>
+  </si>
+  <si>
+    <t>21.05.202679</t>
+  </si>
+  <si>
+    <t>21.05.202680</t>
+  </si>
+  <si>
+    <t>21.05.202681</t>
+  </si>
+  <si>
+    <t>21.05.202682</t>
+  </si>
+  <si>
+    <t>21.05.202683</t>
+  </si>
+  <si>
+    <t>21.05.202684</t>
+  </si>
+  <si>
+    <t>21.05.202685</t>
+  </si>
+  <si>
+    <t>21.05.202686</t>
+  </si>
+  <si>
+    <t>21.05.202687</t>
+  </si>
+  <si>
+    <t>21.05.202688</t>
+  </si>
+  <si>
+    <t>21.05.202689</t>
+  </si>
+  <si>
+    <t>21.05.202690</t>
+  </si>
+  <si>
+    <t>21.05.202691</t>
+  </si>
+  <si>
+    <t>21.05.202692</t>
+  </si>
+  <si>
+    <t>21.05.202693</t>
+  </si>
+  <si>
+    <t>21.05.202694</t>
+  </si>
+  <si>
+    <t>21.05.202695</t>
+  </si>
+  <si>
+    <t>21.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B2">
-        <v>21.296</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C2">
-        <v>0.676</v>
+        <v>5.87</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46156.01041666666</v>
+        <v>46162.01041666666</v>
       </c>
       <c r="B3">
-        <v>8.619</v>
+        <v>4.884</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46156.02083333334</v>
+        <v>46162.02083333334</v>
       </c>
       <c r="B4">
-        <v>6.252</v>
+        <v>12.394</v>
       </c>
       <c r="C4">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46156.03125</v>
+        <v>46162.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2.457</v>
       </c>
       <c r="C5">
-        <v>10.249</v>
+        <v>0.007</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46156.04166666666</v>
+        <v>46162.04166666666</v>
       </c>
       <c r="B6">
-        <v>6.186</v>
+        <v>31.536</v>
       </c>
       <c r="C6">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46156.05208333334</v>
+        <v>46162.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.027</v>
+        <v>38.784</v>
       </c>
       <c r="C7">
-        <v>3.083</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46156.0625</v>
+        <v>46162.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>34.733</v>
       </c>
       <c r="C8">
-        <v>6.538</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46156.07291666666</v>
+        <v>46162.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.497</v>
+        <v>19.143</v>
       </c>
       <c r="C9">
-        <v>1.567</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46156.08333333334</v>
+        <v>46162.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.225</v>
+        <v>7.241</v>
       </c>
       <c r="C10">
-        <v>0.179</v>
+        <v>0.102</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46156.09375</v>
+        <v>46162.09375</v>
       </c>
       <c r="B11">
-        <v>0.093</v>
+        <v>0.874</v>
       </c>
       <c r="C11">
-        <v>0.611</v>
+        <v>0.38</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46156.10416666666</v>
+        <v>46162.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.014</v>
+        <v>0.974</v>
       </c>
       <c r="C12">
-        <v>1.011</v>
+        <v>0.083</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46156.11458333334</v>
+        <v>46162.11458333334</v>
       </c>
       <c r="B13">
-        <v>4.552</v>
+        <v>0.121</v>
       </c>
       <c r="C13">
-        <v>0.104</v>
+        <v>0.293</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46156.125</v>
+        <v>46162.125</v>
       </c>
       <c r="B14">
-        <v>6.626</v>
+        <v>0.022</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2.058</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46156.13541666666</v>
+        <v>46162.13541666666</v>
       </c>
       <c r="B15">
-        <v>3.245</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>26.463</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46156.14583333334</v>
+        <v>46162.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.298</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>14.405</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46156.15625</v>
+        <v>46162.15625</v>
       </c>
       <c r="B17">
-        <v>4.855</v>
+        <v>0.043</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>3.415</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46156.16666666666</v>
+        <v>46162.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.196</v>
+        <v>0.231</v>
       </c>
       <c r="C18">
-        <v>0.005</v>
+        <v>0.398</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46156.17708333334</v>
+        <v>46162.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.17</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C19">
-        <v>0.064</v>
+        <v>2.171</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46156.1875</v>
+        <v>46162.1875</v>
       </c>
       <c r="B20">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.017</v>
+        <v>9.231</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46156.19791666666</v>
+        <v>46162.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0.08400000000000001</v>
+        <v>23.185</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46156.20833333334</v>
+        <v>46162.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.162</v>
+        <v>0.016</v>
       </c>
       <c r="C22">
-        <v>0.029</v>
+        <v>5.665</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46156.21875</v>
+        <v>46162.21875</v>
       </c>
       <c r="B23">
-        <v>0.5659999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C23">
-        <v>0.114</v>
+        <v>0.253</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46156.22916666666</v>
+        <v>46162.22916666666</v>
       </c>
       <c r="B24">
-        <v>5.909</v>
+        <v>0.174</v>
       </c>
       <c r="C24">
-        <v>0.015</v>
+        <v>0.211</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,19 +1529,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46156.23958333334</v>
+        <v>46162.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.627</v>
+        <v>0.329</v>
       </c>
       <c r="C25">
-        <v>0.06900000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -1552,19 +1552,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46156.25</v>
+        <v>46162.25</v>
       </c>
       <c r="B26">
-        <v>6.47</v>
+        <v>0.02</v>
       </c>
       <c r="C26">
-        <v>0.012</v>
+        <v>2.811</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F26">
         <v>25</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46156.26041666666</v>
+        <v>46162.26041666666</v>
       </c>
       <c r="B27">
-        <v>7.578</v>
+        <v>4.108</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46156.27083333334</v>
+        <v>46162.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.823</v>
+        <v>12.655</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46156.28125</v>
+        <v>46162.28125</v>
       </c>
       <c r="B29">
-        <v>8.182</v>
+        <v>11.545</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46156.29166666666</v>
+        <v>46162.29166666666</v>
       </c>
       <c r="B30">
-        <v>24.259</v>
+        <v>40.035</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,10 +1667,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46156.30208333334</v>
+        <v>46162.30208333334</v>
       </c>
       <c r="B31">
-        <v>12.675</v>
+        <v>70.27800000000001</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,16 +1690,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46156.3125</v>
+        <v>46162.3125</v>
       </c>
       <c r="B32">
-        <v>1.783</v>
+        <v>47.733</v>
       </c>
       <c r="C32">
-        <v>2.623</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46156.32291666666</v>
+        <v>46162.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="C33">
-        <v>6.118</v>
+        <v>0.146</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46156.33333333334</v>
+        <v>46162.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>40.714</v>
       </c>
       <c r="C34">
-        <v>29.044</v>
+        <v>0.013</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46156.34375</v>
+        <v>46162.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>37.168</v>
       </c>
       <c r="C35">
-        <v>8.010999999999999</v>
+        <v>0.303</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46156.35416666666</v>
+        <v>46162.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.153</v>
+        <v>0.122</v>
       </c>
       <c r="C36">
-        <v>0.877</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46156.36458333334</v>
+        <v>46162.36458333334</v>
       </c>
       <c r="B37">
-        <v>1.174</v>
+        <v>0.077</v>
       </c>
       <c r="C37">
-        <v>3.431</v>
+        <v>7.954</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E37">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46156.375</v>
+        <v>46162.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="C38">
-        <v>29.068</v>
+        <v>1.916</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E38">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46156.38541666666</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>12.869</v>
       </c>
       <c r="C39">
-        <v>27.247</v>
+        <v>2.433</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E39">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46156.39583333334</v>
+        <v>46162.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>30.827</v>
+        <v>17.447</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E40">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46156.40625</v>
+        <v>46162.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2.683</v>
       </c>
       <c r="C41">
-        <v>21.278</v>
+        <v>5.812</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46156.41666666666</v>
+        <v>46162.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>2.756</v>
+        <v>9.967000000000001</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46156.42708333334</v>
+        <v>46162.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.625</v>
+        <v>5.983</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46156.4375</v>
+        <v>46162.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C44">
-        <v>26.82</v>
+        <v>9.193</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46156.44791666666</v>
+        <v>46162.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>46.857</v>
+        <v>15.742</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46156.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.032</v>
+        <v>0.307</v>
       </c>
       <c r="C46">
-        <v>6.227</v>
+        <v>0.33</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46156.46875</v>
+        <v>46162.46875</v>
       </c>
       <c r="B47">
-        <v>0.164</v>
+        <v>1.58</v>
       </c>
       <c r="C47">
-        <v>0.28</v>
+        <v>0.011</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46156.47916666666</v>
+        <v>46162.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.089</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="C48">
-        <v>5.479</v>
+        <v>0.095</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46156.48958333334</v>
+        <v>46162.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="C49">
-        <v>3.807</v>
+        <v>0.272</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E49">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46156.5</v>
+        <v>46162.5</v>
       </c>
       <c r="B50">
-        <v>0.87</v>
+        <v>22.882</v>
       </c>
       <c r="C50">
-        <v>4.644</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E50">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46156.51041666666</v>
+        <v>46162.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>9.202</v>
       </c>
       <c r="C51">
-        <v>8.826000000000001</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E51">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46156.52083333334</v>
+        <v>46162.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.004</v>
+        <v>0.103</v>
       </c>
       <c r="C52">
-        <v>12.729</v>
+        <v>4.456</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E52">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46156.53125</v>
+        <v>46162.53125</v>
       </c>
       <c r="B53">
-        <v>1.128</v>
+        <v>0.346</v>
       </c>
       <c r="C53">
-        <v>0.223</v>
+        <v>0.28</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46156.54166666666</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="B54">
-        <v>4.95</v>
+        <v>29.004</v>
       </c>
       <c r="C54">
-        <v>0.279</v>
+        <v>0.017</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E54">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46156.55208333334</v>
+        <v>46162.55208333334</v>
       </c>
       <c r="B55">
-        <v>6.101</v>
+        <v>30.188</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46156.5625</v>
+        <v>46162.5625</v>
       </c>
       <c r="B56">
-        <v>12.435</v>
+        <v>15.527</v>
       </c>
       <c r="C56">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E56">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46156.57291666666</v>
+        <v>46162.57291666666</v>
       </c>
       <c r="B57">
-        <v>2.199</v>
+        <v>3.599</v>
       </c>
       <c r="C57">
-        <v>3.85</v>
+        <v>0.201</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E57">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,16 +2288,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46156.58333333334</v>
+        <v>46162.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>5.805</v>
       </c>
       <c r="C58">
-        <v>12.291</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2311,16 +2311,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46156.59375</v>
+        <v>46162.59375</v>
       </c>
       <c r="B59">
-        <v>0.011</v>
+        <v>0.132</v>
       </c>
       <c r="C59">
-        <v>4.374</v>
+        <v>0.138</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46156.60416666666</v>
+        <v>46162.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.062</v>
+        <v>0.124</v>
       </c>
       <c r="C60">
-        <v>2.35</v>
+        <v>0.663</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46156.61458333334</v>
+        <v>46162.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>11.564</v>
+        <v>36.94</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46156.625</v>
+        <v>46162.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="C62">
-        <v>33.133</v>
+        <v>3.155</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46156.63541666666</v>
+        <v>46162.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="C63">
-        <v>17.479</v>
+        <v>0.262</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46156.64583333334</v>
+        <v>46162.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>17.821</v>
+        <v>18.718</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46156.65625</v>
+        <v>46162.65625</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
-        <v>22.053</v>
+        <v>13.827</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46156.66666666666</v>
+        <v>46162.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.091</v>
+        <v>1.02</v>
       </c>
       <c r="C66">
-        <v>0.8120000000000001</v>
+        <v>11.075</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46156.67708333334</v>
+        <v>46162.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.161</v>
+        <v>1.444</v>
       </c>
       <c r="C67">
-        <v>0.293</v>
+        <v>0.08</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46156.6875</v>
+        <v>46162.6875</v>
       </c>
       <c r="B68">
-        <v>0.043</v>
+        <v>0.205</v>
       </c>
       <c r="C68">
-        <v>6.309</v>
+        <v>0.505</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46156.69791666666</v>
+        <v>46162.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="C69">
-        <v>19.076</v>
+        <v>0.875</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46156.70833333334</v>
+        <v>46162.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.612</v>
+        <v>0.002</v>
       </c>
       <c r="C70">
-        <v>0.473</v>
+        <v>13.933</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46156.71875</v>
+        <v>46162.71875</v>
       </c>
       <c r="B71">
-        <v>1.699</v>
+        <v>0.44</v>
       </c>
       <c r="C71">
-        <v>6.377</v>
+        <v>0.068</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>49.25</v>
+        <v>48.5</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +2610,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46156.72916666666</v>
+        <v>46162.72916666666</v>
       </c>
       <c r="B72">
-        <v>6.649</v>
+        <v>0.016</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>17.53</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>25</v>
+        <v>48.5</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46156.73958333334</v>
+        <v>46162.73958333334</v>
       </c>
       <c r="B73">
-        <v>1.494</v>
+        <v>0.128</v>
       </c>
       <c r="C73">
-        <v>0.08699999999999999</v>
+        <v>0.645</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,19 +2656,19 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46156.75</v>
+        <v>46162.75</v>
       </c>
       <c r="B74">
-        <v>0.006</v>
+        <v>0.03</v>
       </c>
       <c r="C74">
-        <v>2.725</v>
+        <v>1.609</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46156.76041666666</v>
+        <v>46162.76041666666</v>
       </c>
       <c r="B75">
-        <v>2.242</v>
+        <v>0.324</v>
       </c>
       <c r="C75">
-        <v>1.093</v>
+        <v>0.139</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46156.77083333334</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B76">
-        <v>4.469</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46156.78125</v>
+        <v>46162.78125</v>
       </c>
       <c r="B77">
-        <v>21.567</v>
+        <v>8.067</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46156.79166666666</v>
+        <v>46162.79166666666</v>
       </c>
       <c r="B78">
-        <v>6.219</v>
+        <v>1.157</v>
       </c>
       <c r="C78">
-        <v>0.015</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46156.80208333334</v>
+        <v>46162.80208333334</v>
       </c>
       <c r="B79">
-        <v>8.959</v>
+        <v>2.011</v>
       </c>
       <c r="C79">
-        <v>0.003</v>
+        <v>0.238</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46156.8125</v>
+        <v>46162.8125</v>
       </c>
       <c r="B80">
-        <v>18.048</v>
+        <v>3.399</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>0.955</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46156.82291666666</v>
+        <v>46162.82291666666</v>
       </c>
       <c r="B81">
-        <v>32.16</v>
+        <v>1.954</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46156.83333333334</v>
+        <v>46162.83333333334</v>
       </c>
       <c r="B82">
-        <v>33.44</v>
+        <v>18.734</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46156.84375</v>
+        <v>46162.84375</v>
       </c>
       <c r="B83">
-        <v>32.689</v>
+        <v>16.798</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46156.85416666666</v>
+        <v>46162.85416666666</v>
       </c>
       <c r="B84">
-        <v>31.61</v>
+        <v>5.662</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46156.86458333334</v>
+        <v>46162.86458333334</v>
       </c>
       <c r="B85">
-        <v>60.721</v>
+        <v>2.432</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1.819</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46156.875</v>
+        <v>46162.875</v>
       </c>
       <c r="B86">
-        <v>74.947</v>
+        <v>2.696</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>0.481</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46156.88541666666</v>
+        <v>46162.88541666666</v>
       </c>
       <c r="B87">
-        <v>80.181</v>
+        <v>3.716</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,16 +2978,16 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46156.89583333334</v>
+        <v>46162.89583333334</v>
       </c>
       <c r="B88">
-        <v>10.579</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C88">
-        <v>0.061</v>
+        <v>0.542</v>
       </c>
       <c r="D88">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3001,16 +3001,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46156.90625</v>
+        <v>46162.90625</v>
       </c>
       <c r="B89">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>0.422</v>
+        <v>20.653</v>
       </c>
       <c r="D89">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3024,16 +3024,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46156.91666666666</v>
+        <v>46162.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.407</v>
+        <v>0.048</v>
       </c>
       <c r="C90">
-        <v>0.24</v>
+        <v>5.297</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46156.92708333334</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="C91">
-        <v>0.372</v>
+        <v>3.055</v>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46156.9375</v>
+        <v>46162.9375</v>
       </c>
       <c r="B92">
-        <v>0.358</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>0.107</v>
+        <v>6.959</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46156.94791666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.111</v>
+        <v>0.026</v>
       </c>
       <c r="C93">
-        <v>0.178</v>
+        <v>11.654</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46156.95833333334</v>
+        <v>46162.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.556</v>
+        <v>0.001</v>
       </c>
       <c r="C94">
-        <v>0.155</v>
+        <v>3.202</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46156.96875</v>
+        <v>46162.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C95">
-        <v>5.737</v>
+        <v>7.13</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46156.97916666666</v>
+        <v>46162.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>4.139</v>
+        <v>7.205</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46156.98958333334</v>
+        <v>46162.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>0.575</v>
+        <v>9.352</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B98">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>0.059</v>
+        <v>3.594</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B99">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>0.059</v>
+        <v>3.594</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B100">
-        <v>0.012</v>
+        <v>2.001</v>
       </c>
       <c r="C100">
-        <v>1.14</v>
+        <v>0.315</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B101">
-        <v>0.012</v>
+        <v>2.001</v>
       </c>
       <c r="C101">
-        <v>1.14</v>
+        <v>0.315</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="C102">
-        <v>4.767</v>
+        <v>2.015</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="C103">
-        <v>4.767</v>
+        <v>2.015</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C104">
-        <v>12.899</v>
+        <v>0.712</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C105">
-        <v>12.899</v>
+        <v>0.712</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B106">
-        <v>0.001</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="C106">
-        <v>7.051</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B107">
-        <v>0.001</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="C107">
-        <v>7.051</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B108">
-        <v>1.021</v>
+        <v>1.644</v>
       </c>
       <c r="C108">
         <v>0.004</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B109">
-        <v>1.021</v>
+        <v>1.644</v>
       </c>
       <c r="C109">
         <v>0.004</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B110">
-        <v>0.067</v>
+        <v>1.048</v>
       </c>
       <c r="C110">
-        <v>5.597</v>
+        <v>0.364</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B111">
-        <v>0.067</v>
+        <v>1.048</v>
       </c>
       <c r="C111">
-        <v>5.597</v>
+        <v>0.364</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B112">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>1.427</v>
+        <v>2.083</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>1.427</v>
+        <v>2.083</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B114">
-        <v>5.673</v>
+        <v>0.027</v>
       </c>
       <c r="C114">
-        <v>0.187</v>
+        <v>5.964</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B115">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0.148</v>
+        <v>17.356</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B116">
-        <v>3.304</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0.028</v>
+        <v>8.409000000000001</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B117">
-        <v>4.051</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>10.107</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B118">
-        <v>2.157</v>
+        <v>0.003</v>
       </c>
       <c r="C118">
-        <v>0.008999999999999999</v>
+        <v>2.355</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B119">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>2.035</v>
+        <v>11.29</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B120">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0.897</v>
+        <v>11.468</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B121">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0.34</v>
+        <v>9.199</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="C122">
-        <v>5.915</v>
+        <v>2.319</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>39.571</v>
+        <v>5.101</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>41.602</v>
+        <v>6.898</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.026</v>
+        <v>0.099</v>
       </c>
       <c r="C125">
-        <v>6.124</v>
+        <v>7.79</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.058</v>
+        <v>0.024</v>
       </c>
       <c r="C126">
-        <v>3.799</v>
+        <v>1.892</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>1.275</v>
       </c>
       <c r="C128">
-        <v>2.86</v>
+        <v>1.254</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>5.022</v>
       </c>
       <c r="C129">
-        <v>4.071</v>
+        <v>0.002</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>29.416</v>
       </c>
       <c r="C130">
-        <v>9.061999999999999</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>41.656</v>
       </c>
       <c r="C131">
-        <v>8.986000000000001</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,16 +3990,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>30.084</v>
       </c>
       <c r="C132">
-        <v>15.759</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4013,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>17.146</v>
       </c>
       <c r="C133">
-        <v>25.306</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,16 +4036,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.362</v>
+        <v>4.035</v>
       </c>
       <c r="C134">
-        <v>3.515</v>
+        <v>0.076</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="C135">
-        <v>13.834</v>
+        <v>1.415</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>1.534</v>
       </c>
       <c r="C136">
-        <v>10.982</v>
+        <v>1.002</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,13 +4105,13 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>16.611</v>
       </c>
       <c r="C137">
-        <v>22.297</v>
+        <v>0.002</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>0.757</v>
       </c>
       <c r="C138">
-        <v>6.265</v>
+        <v>2.055</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B139">
-        <v>0.11</v>
+        <v>0.122</v>
       </c>
       <c r="C139">
-        <v>0.187</v>
+        <v>1.739</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B140">
-        <v>0.132</v>
+        <v>0.211</v>
       </c>
       <c r="C140">
-        <v>0.125</v>
+        <v>0.495</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,13 +4197,13 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B141">
-        <v>0.168</v>
+        <v>0.28</v>
       </c>
       <c r="C141">
-        <v>0.082</v>
+        <v>0.137</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B142">
-        <v>2.917</v>
+        <v>0.283</v>
       </c>
       <c r="C142">
-        <v>0.199</v>
+        <v>0.282</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4243,13 +4243,13 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B143">
-        <v>0.142</v>
+        <v>0.165</v>
       </c>
       <c r="C143">
-        <v>0.359</v>
+        <v>0.194</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B144">
-        <v>0.112</v>
+        <v>14.799</v>
       </c>
       <c r="C144">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4289,13 +4289,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>12.949</v>
       </c>
       <c r="C145">
-        <v>5.679</v>
+        <v>0.209</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B146">
-        <v>0.034</v>
+        <v>1.96</v>
       </c>
       <c r="C146">
-        <v>2.079</v>
+        <v>0.479</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4335,16 +4335,16 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B147">
-        <v>0.393</v>
+        <v>0.633</v>
       </c>
       <c r="C147">
-        <v>7.014</v>
+        <v>2.824</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -4358,16 +4358,16 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>13.755</v>
+        <v>11.791</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -4381,13 +4381,13 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B149">
-        <v>0.01</v>
+        <v>0.92</v>
       </c>
       <c r="C149">
-        <v>16.603</v>
+        <v>3.06</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4404,13 +4404,13 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>50.59</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4427,13 +4427,13 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>0.665</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4450,13 +4450,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4473,13 +4473,13 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>0.384</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4496,13 +4496,13 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>13.585</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4519,13 +4519,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4542,13 +4542,13 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>28.454</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.05.20261</t>
-  </si>
-  <si>
-    <t>20.05.20262</t>
-  </si>
-  <si>
-    <t>20.05.20263</t>
-  </si>
-  <si>
-    <t>20.05.20264</t>
-  </si>
-  <si>
-    <t>20.05.20265</t>
-  </si>
-  <si>
-    <t>20.05.20266</t>
-  </si>
-  <si>
-    <t>20.05.20267</t>
-  </si>
-  <si>
-    <t>20.05.20268</t>
-  </si>
-  <si>
-    <t>20.05.20269</t>
-  </si>
-  <si>
-    <t>20.05.202610</t>
-  </si>
-  <si>
-    <t>20.05.202611</t>
-  </si>
-  <si>
-    <t>20.05.202612</t>
-  </si>
-  <si>
-    <t>20.05.202613</t>
-  </si>
-  <si>
-    <t>20.05.202614</t>
-  </si>
-  <si>
-    <t>20.05.202615</t>
-  </si>
-  <si>
-    <t>20.05.202616</t>
-  </si>
-  <si>
-    <t>20.05.202617</t>
-  </si>
-  <si>
-    <t>20.05.202618</t>
-  </si>
-  <si>
-    <t>20.05.202619</t>
-  </si>
-  <si>
-    <t>20.05.202620</t>
-  </si>
-  <si>
-    <t>20.05.202621</t>
-  </si>
-  <si>
-    <t>20.05.202622</t>
-  </si>
-  <si>
-    <t>20.05.202623</t>
-  </si>
-  <si>
-    <t>20.05.202624</t>
-  </si>
-  <si>
-    <t>20.05.202625</t>
-  </si>
-  <si>
-    <t>20.05.202626</t>
-  </si>
-  <si>
-    <t>20.05.202627</t>
-  </si>
-  <si>
-    <t>20.05.202628</t>
-  </si>
-  <si>
-    <t>20.05.202629</t>
-  </si>
-  <si>
-    <t>20.05.202630</t>
-  </si>
-  <si>
-    <t>20.05.202631</t>
-  </si>
-  <si>
-    <t>20.05.202632</t>
-  </si>
-  <si>
-    <t>20.05.202633</t>
-  </si>
-  <si>
-    <t>20.05.202634</t>
-  </si>
-  <si>
-    <t>20.05.202635</t>
-  </si>
-  <si>
-    <t>20.05.202636</t>
-  </si>
-  <si>
-    <t>20.05.202637</t>
-  </si>
-  <si>
-    <t>20.05.202638</t>
-  </si>
-  <si>
-    <t>20.05.202639</t>
-  </si>
-  <si>
-    <t>20.05.202640</t>
-  </si>
-  <si>
-    <t>20.05.202641</t>
-  </si>
-  <si>
-    <t>20.05.202642</t>
-  </si>
-  <si>
-    <t>20.05.202643</t>
-  </si>
-  <si>
-    <t>20.05.202644</t>
-  </si>
-  <si>
-    <t>20.05.202645</t>
-  </si>
-  <si>
-    <t>20.05.202646</t>
-  </si>
-  <si>
-    <t>20.05.202647</t>
-  </si>
-  <si>
-    <t>20.05.202648</t>
-  </si>
-  <si>
-    <t>20.05.202649</t>
-  </si>
-  <si>
-    <t>20.05.202650</t>
-  </si>
-  <si>
-    <t>20.05.202651</t>
-  </si>
-  <si>
-    <t>20.05.202652</t>
-  </si>
-  <si>
-    <t>20.05.202653</t>
-  </si>
-  <si>
-    <t>20.05.202654</t>
-  </si>
-  <si>
-    <t>20.05.202655</t>
-  </si>
-  <si>
-    <t>20.05.202656</t>
-  </si>
-  <si>
-    <t>20.05.202657</t>
-  </si>
-  <si>
-    <t>20.05.202658</t>
-  </si>
-  <si>
-    <t>20.05.202659</t>
-  </si>
-  <si>
-    <t>20.05.202660</t>
-  </si>
-  <si>
-    <t>20.05.202661</t>
-  </si>
-  <si>
-    <t>20.05.202662</t>
-  </si>
-  <si>
-    <t>20.05.202663</t>
-  </si>
-  <si>
-    <t>20.05.202664</t>
-  </si>
-  <si>
-    <t>20.05.202665</t>
-  </si>
-  <si>
-    <t>20.05.202666</t>
-  </si>
-  <si>
-    <t>20.05.202667</t>
-  </si>
-  <si>
-    <t>20.05.202668</t>
-  </si>
-  <si>
-    <t>20.05.202669</t>
-  </si>
-  <si>
-    <t>20.05.202670</t>
-  </si>
-  <si>
-    <t>20.05.202671</t>
-  </si>
-  <si>
-    <t>20.05.202672</t>
-  </si>
-  <si>
-    <t>20.05.202673</t>
-  </si>
-  <si>
-    <t>20.05.202674</t>
-  </si>
-  <si>
-    <t>20.05.202675</t>
-  </si>
-  <si>
-    <t>20.05.202676</t>
-  </si>
-  <si>
-    <t>20.05.202677</t>
-  </si>
-  <si>
-    <t>20.05.202678</t>
-  </si>
-  <si>
-    <t>20.05.202679</t>
-  </si>
-  <si>
-    <t>20.05.202680</t>
-  </si>
-  <si>
-    <t>20.05.202681</t>
-  </si>
-  <si>
-    <t>20.05.202682</t>
-  </si>
-  <si>
-    <t>20.05.202683</t>
-  </si>
-  <si>
-    <t>20.05.202684</t>
-  </si>
-  <si>
-    <t>20.05.202685</t>
-  </si>
-  <si>
-    <t>20.05.202686</t>
-  </si>
-  <si>
-    <t>20.05.202687</t>
-  </si>
-  <si>
-    <t>20.05.202688</t>
-  </si>
-  <si>
-    <t>20.05.202689</t>
-  </si>
-  <si>
-    <t>20.05.202690</t>
-  </si>
-  <si>
-    <t>20.05.202691</t>
-  </si>
-  <si>
-    <t>20.05.202692</t>
-  </si>
-  <si>
-    <t>20.05.202693</t>
-  </si>
-  <si>
-    <t>20.05.202694</t>
-  </si>
-  <si>
-    <t>20.05.202695</t>
-  </si>
-  <si>
-    <t>20.05.202696</t>
-  </si>
-  <si>
     <t>21.05.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>21.05.202696</t>
+  </si>
+  <si>
+    <t>22.05.20261</t>
+  </si>
+  <si>
+    <t>22.05.20262</t>
+  </si>
+  <si>
+    <t>22.05.20263</t>
+  </si>
+  <si>
+    <t>22.05.20264</t>
+  </si>
+  <si>
+    <t>22.05.20265</t>
+  </si>
+  <si>
+    <t>22.05.20266</t>
+  </si>
+  <si>
+    <t>22.05.20267</t>
+  </si>
+  <si>
+    <t>22.05.20268</t>
+  </si>
+  <si>
+    <t>22.05.20269</t>
+  </si>
+  <si>
+    <t>22.05.202610</t>
+  </si>
+  <si>
+    <t>22.05.202611</t>
+  </si>
+  <si>
+    <t>22.05.202612</t>
+  </si>
+  <si>
+    <t>22.05.202613</t>
+  </si>
+  <si>
+    <t>22.05.202614</t>
+  </si>
+  <si>
+    <t>22.05.202615</t>
+  </si>
+  <si>
+    <t>22.05.202616</t>
+  </si>
+  <si>
+    <t>22.05.202617</t>
+  </si>
+  <si>
+    <t>22.05.202618</t>
+  </si>
+  <si>
+    <t>22.05.202619</t>
+  </si>
+  <si>
+    <t>22.05.202620</t>
+  </si>
+  <si>
+    <t>22.05.202621</t>
+  </si>
+  <si>
+    <t>22.05.202622</t>
+  </si>
+  <si>
+    <t>22.05.202623</t>
+  </si>
+  <si>
+    <t>22.05.202624</t>
+  </si>
+  <si>
+    <t>22.05.202625</t>
+  </si>
+  <si>
+    <t>22.05.202626</t>
+  </si>
+  <si>
+    <t>22.05.202627</t>
+  </si>
+  <si>
+    <t>22.05.202628</t>
+  </si>
+  <si>
+    <t>22.05.202629</t>
+  </si>
+  <si>
+    <t>22.05.202630</t>
+  </si>
+  <si>
+    <t>22.05.202631</t>
+  </si>
+  <si>
+    <t>22.05.202632</t>
+  </si>
+  <si>
+    <t>22.05.202633</t>
+  </si>
+  <si>
+    <t>22.05.202634</t>
+  </si>
+  <si>
+    <t>22.05.202635</t>
+  </si>
+  <si>
+    <t>22.05.202636</t>
+  </si>
+  <si>
+    <t>22.05.202637</t>
+  </si>
+  <si>
+    <t>22.05.202638</t>
+  </si>
+  <si>
+    <t>22.05.202639</t>
+  </si>
+  <si>
+    <t>22.05.202640</t>
+  </si>
+  <si>
+    <t>22.05.202641</t>
+  </si>
+  <si>
+    <t>22.05.202642</t>
+  </si>
+  <si>
+    <t>22.05.202643</t>
+  </si>
+  <si>
+    <t>22.05.202644</t>
+  </si>
+  <si>
+    <t>22.05.202645</t>
+  </si>
+  <si>
+    <t>22.05.202646</t>
+  </si>
+  <si>
+    <t>22.05.202647</t>
+  </si>
+  <si>
+    <t>22.05.202648</t>
+  </si>
+  <si>
+    <t>22.05.202649</t>
+  </si>
+  <si>
+    <t>22.05.202650</t>
+  </si>
+  <si>
+    <t>22.05.202651</t>
+  </si>
+  <si>
+    <t>22.05.202652</t>
+  </si>
+  <si>
+    <t>22.05.202653</t>
+  </si>
+  <si>
+    <t>22.05.202654</t>
+  </si>
+  <si>
+    <t>22.05.202655</t>
+  </si>
+  <si>
+    <t>22.05.202656</t>
+  </si>
+  <si>
+    <t>22.05.202657</t>
+  </si>
+  <si>
+    <t>22.05.202658</t>
+  </si>
+  <si>
+    <t>22.05.202659</t>
+  </si>
+  <si>
+    <t>22.05.202660</t>
+  </si>
+  <si>
+    <t>22.05.202661</t>
+  </si>
+  <si>
+    <t>22.05.202662</t>
+  </si>
+  <si>
+    <t>22.05.202663</t>
+  </si>
+  <si>
+    <t>22.05.202664</t>
+  </si>
+  <si>
+    <t>22.05.202665</t>
+  </si>
+  <si>
+    <t>22.05.202666</t>
+  </si>
+  <si>
+    <t>22.05.202667</t>
+  </si>
+  <si>
+    <t>22.05.202668</t>
+  </si>
+  <si>
+    <t>22.05.202669</t>
+  </si>
+  <si>
+    <t>22.05.202670</t>
+  </si>
+  <si>
+    <t>22.05.202671</t>
+  </si>
+  <si>
+    <t>22.05.202672</t>
+  </si>
+  <si>
+    <t>22.05.202673</t>
+  </si>
+  <si>
+    <t>22.05.202674</t>
+  </si>
+  <si>
+    <t>22.05.202675</t>
+  </si>
+  <si>
+    <t>22.05.202676</t>
+  </si>
+  <si>
+    <t>22.05.202677</t>
+  </si>
+  <si>
+    <t>22.05.202678</t>
+  </si>
+  <si>
+    <t>22.05.202679</t>
+  </si>
+  <si>
+    <t>22.05.202680</t>
+  </si>
+  <si>
+    <t>22.05.202681</t>
+  </si>
+  <si>
+    <t>22.05.202682</t>
+  </si>
+  <si>
+    <t>22.05.202683</t>
+  </si>
+  <si>
+    <t>22.05.202684</t>
+  </si>
+  <si>
+    <t>22.05.202685</t>
+  </si>
+  <si>
+    <t>22.05.202686</t>
+  </si>
+  <si>
+    <t>22.05.202687</t>
+  </si>
+  <si>
+    <t>22.05.202688</t>
+  </si>
+  <si>
+    <t>22.05.202689</t>
+  </si>
+  <si>
+    <t>22.05.202690</t>
+  </si>
+  <si>
+    <t>22.05.202691</t>
+  </si>
+  <si>
+    <t>22.05.202692</t>
+  </si>
+  <si>
+    <t>22.05.202693</t>
+  </si>
+  <si>
+    <t>22.05.202694</t>
+  </si>
+  <si>
+    <t>22.05.202695</t>
+  </si>
+  <si>
+    <t>22.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>5.87</v>
+        <v>3.594</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46162.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>4.884</v>
+        <v>2.001</v>
       </c>
       <c r="C3">
-        <v>0.033</v>
+        <v>0.315</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46162.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
-        <v>12.394</v>
+        <v>0.436</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>2.015</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46162.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
-        <v>2.457</v>
+        <v>0.08</v>
       </c>
       <c r="C5">
-        <v>0.007</v>
+        <v>0.712</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46162.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>31.536</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46162.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>38.784</v>
+        <v>1.644</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46162.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>34.733</v>
+        <v>1.048</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46162.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>19.143</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2.083</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46162.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>7.241</v>
+        <v>0.027</v>
       </c>
       <c r="C10">
-        <v>0.102</v>
+        <v>5.964</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46162.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>0.874</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.38</v>
+        <v>17.356</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46162.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.974</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.083</v>
+        <v>8.409000000000001</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46162.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.293</v>
+        <v>10.107</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46162.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>0.022</v>
+        <v>0.003</v>
       </c>
       <c r="C14">
-        <v>2.058</v>
+        <v>2.355</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46162.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>26.463</v>
+        <v>11.29</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46162.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>14.405</v>
+        <v>11.468</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46162.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>3.415</v>
+        <v>9.199</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46162.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.231</v>
+        <v>0.047</v>
       </c>
       <c r="C18">
-        <v>0.398</v>
+        <v>2.319</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46162.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>2.171</v>
+        <v>5.101</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46162.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>9.231</v>
+        <v>6.898</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46162.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="C21">
-        <v>23.185</v>
+        <v>7.79</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46162.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.016</v>
+        <v>0.024</v>
       </c>
       <c r="C22">
-        <v>5.665</v>
+        <v>1.892</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46162.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0.253</v>
+        <v>2.16</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46162.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.174</v>
+        <v>1.275</v>
       </c>
       <c r="C24">
-        <v>0.211</v>
+        <v>1.254</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,19 +1529,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46162.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.329</v>
+        <v>5.022</v>
       </c>
       <c r="C25">
-        <v>0.112</v>
+        <v>0.002</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -1552,19 +1552,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46162.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>0.02</v>
+        <v>29.416</v>
       </c>
       <c r="C26">
-        <v>2.811</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>25</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46162.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>4.108</v>
+        <v>41.656</v>
       </c>
       <c r="C27">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46162.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>12.655</v>
+        <v>30.084</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46162.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>11.545</v>
+        <v>17.146</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E29">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,19 +1644,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46162.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>40.035</v>
+        <v>4.035</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="E30">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46162.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>70.27800000000001</v>
+        <v>0.074</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1.415</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="E31">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,16 +1690,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46162.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>47.733</v>
+        <v>1.534</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1.002</v>
       </c>
       <c r="D32">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46162.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.529</v>
+        <v>16.611</v>
       </c>
       <c r="C33">
-        <v>0.146</v>
+        <v>0.002</v>
       </c>
       <c r="D33">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46162.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>40.714</v>
+        <v>0.757</v>
       </c>
       <c r="C34">
-        <v>0.013</v>
+        <v>2.055</v>
       </c>
       <c r="D34">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46162.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>37.168</v>
+        <v>0.122</v>
       </c>
       <c r="C35">
-        <v>0.303</v>
+        <v>1.739</v>
       </c>
       <c r="D35">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46162.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.122</v>
+        <v>0.211</v>
       </c>
       <c r="C36">
-        <v>0.6879999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="D36">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +1805,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46162.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.077</v>
+        <v>0.28</v>
       </c>
       <c r="C37">
-        <v>7.954</v>
+        <v>0.137</v>
       </c>
       <c r="D37">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46162.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>17.3</v>
+        <v>0.283</v>
       </c>
       <c r="C38">
-        <v>1.916</v>
+        <v>0.282</v>
       </c>
       <c r="D38">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46162.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>12.869</v>
+        <v>0.165</v>
       </c>
       <c r="C39">
-        <v>2.433</v>
+        <v>0.194</v>
       </c>
       <c r="D39">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46162.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>14.799</v>
       </c>
       <c r="C40">
-        <v>17.447</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,13 +1897,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46162.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>2.683</v>
+        <v>12.949</v>
       </c>
       <c r="C41">
-        <v>5.812</v>
+        <v>0.209</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1920,13 +1920,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46162.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="C42">
-        <v>9.967000000000001</v>
+        <v>0.479</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1943,16 +1943,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46162.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="C43">
-        <v>5.983</v>
+        <v>2.824</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46162.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>9.193</v>
+        <v>11.791</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1989,13 +1989,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46162.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="C45">
-        <v>15.742</v>
+        <v>3.06</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46162.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.307</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>0.33</v>
+        <v>50.59</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46162.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>1.58</v>
+        <v>0.122</v>
       </c>
       <c r="C47">
-        <v>0.011</v>
+        <v>0.665</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46162.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.8080000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="C48">
-        <v>0.095</v>
+        <v>0.279</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2081,16 +2081,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46162.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.358</v>
+        <v>0.384</v>
       </c>
       <c r="C49">
-        <v>0.272</v>
+        <v>1.18</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2104,16 +2104,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46162.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>22.882</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>13.585</v>
       </c>
       <c r="D50">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2127,16 +2127,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46162.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>9.202</v>
+        <v>0.008</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="D51">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2150,16 +2150,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46162.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.103</v>
+        <v>10.1</v>
       </c>
       <c r="C52">
-        <v>4.456</v>
+        <v>0.053</v>
       </c>
       <c r="D52">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2173,16 +2173,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46162.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>0.346</v>
+        <v>28.454</v>
       </c>
       <c r="C53">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46162.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>29.004</v>
+        <v>32.963</v>
       </c>
       <c r="C54">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46162.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>30.188</v>
+        <v>43.384</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46162.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>15.527</v>
+        <v>51.597</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46162.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>3.599</v>
+        <v>20.696</v>
       </c>
       <c r="C57">
-        <v>0.201</v>
+        <v>0.026</v>
       </c>
       <c r="D57">
         <v>37.5</v>
@@ -2288,16 +2288,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46162.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>5.805</v>
+        <v>0.542</v>
       </c>
       <c r="C58">
-        <v>0.08599999999999999</v>
+        <v>0.435</v>
       </c>
       <c r="D58">
-        <v>12.5</v>
+        <v>58.5</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2311,16 +2311,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46162.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>0.138</v>
+        <v>44.335</v>
       </c>
       <c r="D59">
-        <v>12.5</v>
+        <v>58.5</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46162.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.124</v>
+        <v>0.228</v>
       </c>
       <c r="C60">
-        <v>0.663</v>
+        <v>16.403</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46162.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>36.94</v>
+        <v>23.371</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46162.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>3.155</v>
+        <v>8.632</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46162.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0.262</v>
+        <v>67.101</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46162.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>18.718</v>
+        <v>56.668</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46162.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="C65">
-        <v>13.827</v>
+        <v>1.217</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46162.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>1.02</v>
+        <v>0.252</v>
       </c>
       <c r="C66">
-        <v>11.075</v>
+        <v>0.343</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46162.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>1.444</v>
+        <v>0.008</v>
       </c>
       <c r="C67">
-        <v>0.08</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46162.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>0.205</v>
+        <v>0.06</v>
       </c>
       <c r="C68">
-        <v>0.505</v>
+        <v>5.27</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46162.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>0.875</v>
+        <v>8.237</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46162.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.002</v>
+        <v>0.111</v>
       </c>
       <c r="C70">
-        <v>13.933</v>
+        <v>0.902</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46162.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>0.44</v>
+        <v>0.015</v>
       </c>
       <c r="C71">
-        <v>0.068</v>
+        <v>12.979</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +2610,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46162.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>17.53</v>
+        <v>12.905</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46162.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>0.645</v>
+        <v>11.025</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>29.5</v>
+        <v>45.5</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,19 +2656,19 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46162.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>1.609</v>
+        <v>61.815</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46162.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.324</v>
+        <v>8.305</v>
       </c>
       <c r="C75">
-        <v>0.139</v>
+        <v>5.184</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46162.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>8.175000000000001</v>
+        <v>8.714</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46162.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>8.067</v>
+        <v>7.664</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46162.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.157</v>
+        <v>1.447</v>
       </c>
       <c r="C78">
-        <v>8.300000000000001</v>
+        <v>1.027</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46162.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>2.011</v>
+        <v>0.052</v>
       </c>
       <c r="C79">
-        <v>0.238</v>
+        <v>3.32</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46162.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>3.399</v>
+        <v>0.075</v>
       </c>
       <c r="C80">
-        <v>0.955</v>
+        <v>0.366</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46162.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>1.954</v>
+        <v>0.118</v>
       </c>
       <c r="C81">
-        <v>0.301</v>
+        <v>0.191</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,19 +2840,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46162.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>18.734</v>
+        <v>0.234</v>
       </c>
       <c r="C82">
-        <v>0.089</v>
+        <v>0.214</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2863,19 +2863,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46162.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>16.798</v>
+        <v>0.026</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1.895</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -2886,19 +2886,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46162.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>5.662</v>
+        <v>0.076</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F84">
         <v>83</v>
@@ -2909,19 +2909,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46162.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>2.432</v>
+        <v>0.052</v>
       </c>
       <c r="C85">
-        <v>1.819</v>
+        <v>0.411</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F85">
         <v>84</v>
@@ -2932,19 +2932,19 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46162.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>2.696</v>
+        <v>11.987</v>
       </c>
       <c r="C86">
-        <v>0.481</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F86">
         <v>85</v>
@@ -2955,19 +2955,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46162.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>3.716</v>
+        <v>12.234</v>
       </c>
       <c r="C87">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46162.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.8159999999999999</v>
+        <v>8.103999999999999</v>
       </c>
       <c r="C88">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46162.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>0.476</v>
       </c>
       <c r="C89">
-        <v>20.653</v>
+        <v>0.851</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46162.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.048</v>
+        <v>0.067</v>
       </c>
       <c r="C90">
-        <v>5.297</v>
+        <v>0.902</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46162.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.06</v>
+        <v>0.096</v>
       </c>
       <c r="C91">
-        <v>3.055</v>
+        <v>0.63</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46162.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="C92">
-        <v>6.959</v>
+        <v>0.452</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46162.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.026</v>
+        <v>0.107</v>
       </c>
       <c r="C93">
-        <v>11.654</v>
+        <v>0.621</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46162.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.001</v>
+        <v>0.472</v>
       </c>
       <c r="C94">
-        <v>3.202</v>
+        <v>0.241</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46162.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
-        <v>0.004</v>
+        <v>0.028</v>
       </c>
       <c r="C95">
-        <v>7.13</v>
+        <v>2.939</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46162.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>7.205</v>
+        <v>2.558</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46162.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>9.352</v>
+        <v>10.741</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="C98">
-        <v>3.594</v>
+        <v>0.333</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="C99">
-        <v>3.594</v>
+        <v>0.333</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B100">
-        <v>2.001</v>
+        <v>4.098</v>
       </c>
       <c r="C100">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B101">
-        <v>2.001</v>
+        <v>4.098</v>
       </c>
       <c r="C101">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B102">
-        <v>0.436</v>
+        <v>2.915</v>
       </c>
       <c r="C102">
-        <v>2.015</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B103">
-        <v>0.436</v>
+        <v>2.915</v>
       </c>
       <c r="C103">
-        <v>2.015</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B104">
-        <v>0.08</v>
+        <v>1.305</v>
       </c>
       <c r="C104">
-        <v>0.712</v>
+        <v>0.019</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B105">
-        <v>0.08</v>
+        <v>1.305</v>
       </c>
       <c r="C105">
-        <v>0.712</v>
+        <v>0.019</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B106">
-        <v>8.733000000000001</v>
+        <v>3.335</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B107">
-        <v>8.733000000000001</v>
+        <v>3.335</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B108">
-        <v>1.644</v>
+        <v>3.071</v>
       </c>
       <c r="C108">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B109">
-        <v>1.644</v>
+        <v>3.071</v>
       </c>
       <c r="C109">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B110">
-        <v>1.048</v>
+        <v>4.036</v>
       </c>
       <c r="C110">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B111">
-        <v>1.048</v>
+        <v>4.036</v>
       </c>
       <c r="C111">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="C112">
-        <v>2.083</v>
+        <v>0.46</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="C113">
-        <v>2.083</v>
+        <v>0.46</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B114">
-        <v>0.027</v>
+        <v>0.001</v>
       </c>
       <c r="C114">
-        <v>5.964</v>
+        <v>0.38</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="C115">
-        <v>17.356</v>
+        <v>0.798</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>8.409000000000001</v>
+        <v>2.985</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>2.244</v>
       </c>
       <c r="C117">
-        <v>10.107</v>
+        <v>1.231</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B118">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="C118">
-        <v>2.355</v>
+        <v>9.554</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>11.29</v>
+        <v>10.242</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="C120">
-        <v>11.468</v>
+        <v>0.844</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="C121">
-        <v>9.199</v>
+        <v>0.114</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B122">
-        <v>0.047</v>
+        <v>0.347</v>
       </c>
       <c r="C122">
-        <v>2.319</v>
+        <v>1.665</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>2.578</v>
       </c>
       <c r="C123">
-        <v>5.101</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>3.235</v>
       </c>
       <c r="C124">
-        <v>6.898</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.099</v>
+        <v>6.989</v>
       </c>
       <c r="C125">
-        <v>7.79</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.024</v>
+        <v>4.993</v>
       </c>
       <c r="C126">
-        <v>1.892</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>6.705</v>
       </c>
       <c r="C127">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B128">
-        <v>1.275</v>
+        <v>10.144</v>
       </c>
       <c r="C128">
-        <v>1.254</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B129">
-        <v>5.022</v>
+        <v>1.878</v>
       </c>
       <c r="C129">
-        <v>0.002</v>
+        <v>0.211</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B130">
-        <v>29.416</v>
+        <v>4.791</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>4.091</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B131">
-        <v>41.656</v>
+        <v>7.649</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3990,16 +3990,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B132">
-        <v>30.084</v>
+        <v>11.06</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4013,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B133">
-        <v>17.146</v>
+        <v>20.781</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,16 +4036,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B134">
-        <v>4.035</v>
+        <v>20.185</v>
       </c>
       <c r="C134">
-        <v>0.076</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.074</v>
+        <v>20.137</v>
       </c>
       <c r="C135">
-        <v>1.415</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B136">
-        <v>1.534</v>
+        <v>22.527</v>
       </c>
       <c r="C136">
-        <v>1.002</v>
+        <v>0.002</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,16 +4105,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B137">
-        <v>16.611</v>
+        <v>0.052</v>
       </c>
       <c r="C137">
-        <v>0.002</v>
+        <v>2.449</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4128,16 +4128,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B138">
-        <v>0.757</v>
+        <v>0.138</v>
       </c>
       <c r="C138">
-        <v>2.055</v>
+        <v>4.748</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4151,16 +4151,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B139">
-        <v>0.122</v>
+        <v>0.001</v>
       </c>
       <c r="C139">
-        <v>1.739</v>
+        <v>4.143</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4174,16 +4174,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B140">
-        <v>0.211</v>
+        <v>12.768</v>
       </c>
       <c r="C140">
-        <v>0.495</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4197,16 +4197,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B141">
-        <v>0.28</v>
+        <v>1.892</v>
       </c>
       <c r="C141">
-        <v>0.137</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4220,16 +4220,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B142">
-        <v>0.283</v>
+        <v>7.163</v>
       </c>
       <c r="C142">
-        <v>0.282</v>
+        <v>0.049</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4243,16 +4243,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B143">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="C143">
-        <v>0.194</v>
+        <v>2.463</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4266,16 +4266,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B144">
-        <v>14.799</v>
+        <v>0.051</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>2.384</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4289,13 +4289,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B145">
-        <v>12.949</v>
+        <v>1.316</v>
       </c>
       <c r="C145">
-        <v>0.209</v>
+        <v>0.282</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B146">
-        <v>1.96</v>
+        <v>3.911</v>
       </c>
       <c r="C146">
-        <v>0.479</v>
+        <v>0.064</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4335,16 +4335,16 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B147">
-        <v>0.633</v>
+        <v>3.214</v>
       </c>
       <c r="C147">
-        <v>2.824</v>
+        <v>0.132</v>
       </c>
       <c r="D147">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -4358,16 +4358,16 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>9.846</v>
       </c>
       <c r="C148">
-        <v>11.791</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -4381,13 +4381,13 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B149">
-        <v>0.92</v>
+        <v>22.633</v>
       </c>
       <c r="C149">
-        <v>3.06</v>
+        <v>0.797</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4404,13 +4404,13 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>0.661</v>
       </c>
       <c r="C150">
-        <v>50.59</v>
+        <v>1.628</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4427,13 +4427,13 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B151">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>0.665</v>
+        <v>6.629</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4450,13 +4450,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B152">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>0.279</v>
+        <v>27.333</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4473,13 +4473,13 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B153">
-        <v>0.384</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>1.18</v>
+        <v>34.045</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4496,13 +4496,13 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>13.585</v>
+        <v>18.656</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4519,13 +4519,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B155">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>6.74</v>
+        <v>22.431</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4542,13 +4542,13 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B156">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B157">
-        <v>28.454</v>
+        <v>0</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="391">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.05.20261</t>
-  </si>
-  <si>
-    <t>21.05.20262</t>
-  </si>
-  <si>
-    <t>21.05.20263</t>
-  </si>
-  <si>
-    <t>21.05.20264</t>
-  </si>
-  <si>
-    <t>21.05.20265</t>
-  </si>
-  <si>
-    <t>21.05.20266</t>
-  </si>
-  <si>
-    <t>21.05.20267</t>
-  </si>
-  <si>
-    <t>21.05.20268</t>
-  </si>
-  <si>
-    <t>21.05.20269</t>
-  </si>
-  <si>
-    <t>21.05.202610</t>
-  </si>
-  <si>
-    <t>21.05.202611</t>
-  </si>
-  <si>
-    <t>21.05.202612</t>
-  </si>
-  <si>
-    <t>21.05.202613</t>
-  </si>
-  <si>
-    <t>21.05.202614</t>
-  </si>
-  <si>
-    <t>21.05.202615</t>
-  </si>
-  <si>
-    <t>21.05.202616</t>
-  </si>
-  <si>
-    <t>21.05.202617</t>
-  </si>
-  <si>
-    <t>21.05.202618</t>
-  </si>
-  <si>
-    <t>21.05.202619</t>
-  </si>
-  <si>
-    <t>21.05.202620</t>
-  </si>
-  <si>
-    <t>21.05.202621</t>
-  </si>
-  <si>
-    <t>21.05.202622</t>
-  </si>
-  <si>
-    <t>21.05.202623</t>
-  </si>
-  <si>
-    <t>21.05.202624</t>
-  </si>
-  <si>
-    <t>21.05.202625</t>
-  </si>
-  <si>
-    <t>21.05.202626</t>
-  </si>
-  <si>
-    <t>21.05.202627</t>
-  </si>
-  <si>
-    <t>21.05.202628</t>
-  </si>
-  <si>
-    <t>21.05.202629</t>
-  </si>
-  <si>
-    <t>21.05.202630</t>
-  </si>
-  <si>
-    <t>21.05.202631</t>
-  </si>
-  <si>
-    <t>21.05.202632</t>
-  </si>
-  <si>
-    <t>21.05.202633</t>
-  </si>
-  <si>
-    <t>21.05.202634</t>
-  </si>
-  <si>
-    <t>21.05.202635</t>
-  </si>
-  <si>
-    <t>21.05.202636</t>
-  </si>
-  <si>
-    <t>21.05.202637</t>
-  </si>
-  <si>
-    <t>21.05.202638</t>
-  </si>
-  <si>
-    <t>21.05.202639</t>
-  </si>
-  <si>
-    <t>21.05.202640</t>
-  </si>
-  <si>
-    <t>21.05.202641</t>
-  </si>
-  <si>
-    <t>21.05.202642</t>
-  </si>
-  <si>
-    <t>21.05.202643</t>
-  </si>
-  <si>
-    <t>21.05.202644</t>
-  </si>
-  <si>
-    <t>21.05.202645</t>
-  </si>
-  <si>
-    <t>21.05.202646</t>
-  </si>
-  <si>
-    <t>21.05.202647</t>
-  </si>
-  <si>
-    <t>21.05.202648</t>
-  </si>
-  <si>
-    <t>21.05.202649</t>
-  </si>
-  <si>
-    <t>21.05.202650</t>
-  </si>
-  <si>
-    <t>21.05.202651</t>
-  </si>
-  <si>
-    <t>21.05.202652</t>
-  </si>
-  <si>
-    <t>21.05.202653</t>
-  </si>
-  <si>
-    <t>21.05.202654</t>
-  </si>
-  <si>
-    <t>21.05.202655</t>
-  </si>
-  <si>
-    <t>21.05.202656</t>
-  </si>
-  <si>
-    <t>21.05.202657</t>
-  </si>
-  <si>
-    <t>21.05.202658</t>
-  </si>
-  <si>
-    <t>21.05.202659</t>
-  </si>
-  <si>
-    <t>21.05.202660</t>
-  </si>
-  <si>
-    <t>21.05.202661</t>
-  </si>
-  <si>
-    <t>21.05.202662</t>
-  </si>
-  <si>
-    <t>21.05.202663</t>
-  </si>
-  <si>
-    <t>21.05.202664</t>
-  </si>
-  <si>
-    <t>21.05.202665</t>
-  </si>
-  <si>
-    <t>21.05.202666</t>
-  </si>
-  <si>
-    <t>21.05.202667</t>
-  </si>
-  <si>
-    <t>21.05.202668</t>
-  </si>
-  <si>
-    <t>21.05.202669</t>
-  </si>
-  <si>
-    <t>21.05.202670</t>
-  </si>
-  <si>
-    <t>21.05.202671</t>
-  </si>
-  <si>
-    <t>21.05.202672</t>
-  </si>
-  <si>
-    <t>21.05.202673</t>
-  </si>
-  <si>
-    <t>21.05.202674</t>
-  </si>
-  <si>
-    <t>21.05.202675</t>
-  </si>
-  <si>
-    <t>21.05.202676</t>
-  </si>
-  <si>
-    <t>21.05.202677</t>
-  </si>
-  <si>
-    <t>21.05.202678</t>
-  </si>
-  <si>
-    <t>21.05.202679</t>
-  </si>
-  <si>
-    <t>21.05.202680</t>
-  </si>
-  <si>
-    <t>21.05.202681</t>
-  </si>
-  <si>
-    <t>21.05.202682</t>
-  </si>
-  <si>
-    <t>21.05.202683</t>
-  </si>
-  <si>
-    <t>21.05.202684</t>
-  </si>
-  <si>
-    <t>21.05.202685</t>
-  </si>
-  <si>
-    <t>21.05.202686</t>
-  </si>
-  <si>
-    <t>21.05.202687</t>
-  </si>
-  <si>
-    <t>21.05.202688</t>
-  </si>
-  <si>
-    <t>21.05.202689</t>
-  </si>
-  <si>
-    <t>21.05.202690</t>
-  </si>
-  <si>
-    <t>21.05.202691</t>
-  </si>
-  <si>
-    <t>21.05.202692</t>
-  </si>
-  <si>
-    <t>21.05.202693</t>
-  </si>
-  <si>
-    <t>21.05.202694</t>
-  </si>
-  <si>
-    <t>21.05.202695</t>
-  </si>
-  <si>
-    <t>21.05.202696</t>
-  </si>
-  <si>
     <t>22.05.20261</t>
   </si>
   <si>
@@ -611,6 +323,870 @@
   </si>
   <si>
     <t>22.05.202696</t>
+  </si>
+  <si>
+    <t>23.05.20261</t>
+  </si>
+  <si>
+    <t>23.05.20262</t>
+  </si>
+  <si>
+    <t>23.05.20263</t>
+  </si>
+  <si>
+    <t>23.05.20264</t>
+  </si>
+  <si>
+    <t>23.05.20265</t>
+  </si>
+  <si>
+    <t>23.05.20266</t>
+  </si>
+  <si>
+    <t>23.05.20267</t>
+  </si>
+  <si>
+    <t>23.05.20268</t>
+  </si>
+  <si>
+    <t>23.05.20269</t>
+  </si>
+  <si>
+    <t>23.05.202610</t>
+  </si>
+  <si>
+    <t>23.05.202611</t>
+  </si>
+  <si>
+    <t>23.05.202612</t>
+  </si>
+  <si>
+    <t>23.05.202613</t>
+  </si>
+  <si>
+    <t>23.05.202614</t>
+  </si>
+  <si>
+    <t>23.05.202615</t>
+  </si>
+  <si>
+    <t>23.05.202616</t>
+  </si>
+  <si>
+    <t>23.05.202617</t>
+  </si>
+  <si>
+    <t>23.05.202618</t>
+  </si>
+  <si>
+    <t>23.05.202619</t>
+  </si>
+  <si>
+    <t>23.05.202620</t>
+  </si>
+  <si>
+    <t>23.05.202621</t>
+  </si>
+  <si>
+    <t>23.05.202622</t>
+  </si>
+  <si>
+    <t>23.05.202623</t>
+  </si>
+  <si>
+    <t>23.05.202624</t>
+  </si>
+  <si>
+    <t>23.05.202625</t>
+  </si>
+  <si>
+    <t>23.05.202626</t>
+  </si>
+  <si>
+    <t>23.05.202627</t>
+  </si>
+  <si>
+    <t>23.05.202628</t>
+  </si>
+  <si>
+    <t>23.05.202629</t>
+  </si>
+  <si>
+    <t>23.05.202630</t>
+  </si>
+  <si>
+    <t>23.05.202631</t>
+  </si>
+  <si>
+    <t>23.05.202632</t>
+  </si>
+  <si>
+    <t>23.05.202633</t>
+  </si>
+  <si>
+    <t>23.05.202634</t>
+  </si>
+  <si>
+    <t>23.05.202635</t>
+  </si>
+  <si>
+    <t>23.05.202636</t>
+  </si>
+  <si>
+    <t>23.05.202637</t>
+  </si>
+  <si>
+    <t>23.05.202638</t>
+  </si>
+  <si>
+    <t>23.05.202639</t>
+  </si>
+  <si>
+    <t>23.05.202640</t>
+  </si>
+  <si>
+    <t>23.05.202641</t>
+  </si>
+  <si>
+    <t>23.05.202642</t>
+  </si>
+  <si>
+    <t>23.05.202643</t>
+  </si>
+  <si>
+    <t>23.05.202644</t>
+  </si>
+  <si>
+    <t>23.05.202645</t>
+  </si>
+  <si>
+    <t>23.05.202646</t>
+  </si>
+  <si>
+    <t>23.05.202647</t>
+  </si>
+  <si>
+    <t>23.05.202648</t>
+  </si>
+  <si>
+    <t>23.05.202649</t>
+  </si>
+  <si>
+    <t>23.05.202650</t>
+  </si>
+  <si>
+    <t>23.05.202651</t>
+  </si>
+  <si>
+    <t>23.05.202652</t>
+  </si>
+  <si>
+    <t>23.05.202653</t>
+  </si>
+  <si>
+    <t>23.05.202654</t>
+  </si>
+  <si>
+    <t>23.05.202655</t>
+  </si>
+  <si>
+    <t>23.05.202656</t>
+  </si>
+  <si>
+    <t>23.05.202657</t>
+  </si>
+  <si>
+    <t>23.05.202658</t>
+  </si>
+  <si>
+    <t>23.05.202659</t>
+  </si>
+  <si>
+    <t>23.05.202660</t>
+  </si>
+  <si>
+    <t>23.05.202661</t>
+  </si>
+  <si>
+    <t>23.05.202662</t>
+  </si>
+  <si>
+    <t>23.05.202663</t>
+  </si>
+  <si>
+    <t>23.05.202664</t>
+  </si>
+  <si>
+    <t>23.05.202665</t>
+  </si>
+  <si>
+    <t>23.05.202666</t>
+  </si>
+  <si>
+    <t>23.05.202667</t>
+  </si>
+  <si>
+    <t>23.05.202668</t>
+  </si>
+  <si>
+    <t>23.05.202669</t>
+  </si>
+  <si>
+    <t>23.05.202670</t>
+  </si>
+  <si>
+    <t>23.05.202671</t>
+  </si>
+  <si>
+    <t>23.05.202672</t>
+  </si>
+  <si>
+    <t>23.05.202673</t>
+  </si>
+  <si>
+    <t>23.05.202674</t>
+  </si>
+  <si>
+    <t>23.05.202675</t>
+  </si>
+  <si>
+    <t>23.05.202676</t>
+  </si>
+  <si>
+    <t>23.05.202677</t>
+  </si>
+  <si>
+    <t>23.05.202678</t>
+  </si>
+  <si>
+    <t>23.05.202679</t>
+  </si>
+  <si>
+    <t>23.05.202680</t>
+  </si>
+  <si>
+    <t>23.05.202681</t>
+  </si>
+  <si>
+    <t>23.05.202682</t>
+  </si>
+  <si>
+    <t>23.05.202683</t>
+  </si>
+  <si>
+    <t>23.05.202684</t>
+  </si>
+  <si>
+    <t>23.05.202685</t>
+  </si>
+  <si>
+    <t>23.05.202686</t>
+  </si>
+  <si>
+    <t>23.05.202687</t>
+  </si>
+  <si>
+    <t>23.05.202688</t>
+  </si>
+  <si>
+    <t>23.05.202689</t>
+  </si>
+  <si>
+    <t>23.05.202690</t>
+  </si>
+  <si>
+    <t>23.05.202691</t>
+  </si>
+  <si>
+    <t>23.05.202692</t>
+  </si>
+  <si>
+    <t>23.05.202693</t>
+  </si>
+  <si>
+    <t>23.05.202694</t>
+  </si>
+  <si>
+    <t>23.05.202695</t>
+  </si>
+  <si>
+    <t>23.05.202696</t>
+  </si>
+  <si>
+    <t>24.05.20261</t>
+  </si>
+  <si>
+    <t>24.05.20262</t>
+  </si>
+  <si>
+    <t>24.05.20263</t>
+  </si>
+  <si>
+    <t>24.05.20264</t>
+  </si>
+  <si>
+    <t>24.05.20265</t>
+  </si>
+  <si>
+    <t>24.05.20266</t>
+  </si>
+  <si>
+    <t>24.05.20267</t>
+  </si>
+  <si>
+    <t>24.05.20268</t>
+  </si>
+  <si>
+    <t>24.05.20269</t>
+  </si>
+  <si>
+    <t>24.05.202610</t>
+  </si>
+  <si>
+    <t>24.05.202611</t>
+  </si>
+  <si>
+    <t>24.05.202612</t>
+  </si>
+  <si>
+    <t>24.05.202613</t>
+  </si>
+  <si>
+    <t>24.05.202614</t>
+  </si>
+  <si>
+    <t>24.05.202615</t>
+  </si>
+  <si>
+    <t>24.05.202616</t>
+  </si>
+  <si>
+    <t>24.05.202617</t>
+  </si>
+  <si>
+    <t>24.05.202618</t>
+  </si>
+  <si>
+    <t>24.05.202619</t>
+  </si>
+  <si>
+    <t>24.05.202620</t>
+  </si>
+  <si>
+    <t>24.05.202621</t>
+  </si>
+  <si>
+    <t>24.05.202622</t>
+  </si>
+  <si>
+    <t>24.05.202623</t>
+  </si>
+  <si>
+    <t>24.05.202624</t>
+  </si>
+  <si>
+    <t>24.05.202625</t>
+  </si>
+  <si>
+    <t>24.05.202626</t>
+  </si>
+  <si>
+    <t>24.05.202627</t>
+  </si>
+  <si>
+    <t>24.05.202628</t>
+  </si>
+  <si>
+    <t>24.05.202629</t>
+  </si>
+  <si>
+    <t>24.05.202630</t>
+  </si>
+  <si>
+    <t>24.05.202631</t>
+  </si>
+  <si>
+    <t>24.05.202632</t>
+  </si>
+  <si>
+    <t>24.05.202633</t>
+  </si>
+  <si>
+    <t>24.05.202634</t>
+  </si>
+  <si>
+    <t>24.05.202635</t>
+  </si>
+  <si>
+    <t>24.05.202636</t>
+  </si>
+  <si>
+    <t>24.05.202637</t>
+  </si>
+  <si>
+    <t>24.05.202638</t>
+  </si>
+  <si>
+    <t>24.05.202639</t>
+  </si>
+  <si>
+    <t>24.05.202640</t>
+  </si>
+  <si>
+    <t>24.05.202641</t>
+  </si>
+  <si>
+    <t>24.05.202642</t>
+  </si>
+  <si>
+    <t>24.05.202643</t>
+  </si>
+  <si>
+    <t>24.05.202644</t>
+  </si>
+  <si>
+    <t>24.05.202645</t>
+  </si>
+  <si>
+    <t>24.05.202646</t>
+  </si>
+  <si>
+    <t>24.05.202647</t>
+  </si>
+  <si>
+    <t>24.05.202648</t>
+  </si>
+  <si>
+    <t>24.05.202649</t>
+  </si>
+  <si>
+    <t>24.05.202650</t>
+  </si>
+  <si>
+    <t>24.05.202651</t>
+  </si>
+  <si>
+    <t>24.05.202652</t>
+  </si>
+  <si>
+    <t>24.05.202653</t>
+  </si>
+  <si>
+    <t>24.05.202654</t>
+  </si>
+  <si>
+    <t>24.05.202655</t>
+  </si>
+  <si>
+    <t>24.05.202656</t>
+  </si>
+  <si>
+    <t>24.05.202657</t>
+  </si>
+  <si>
+    <t>24.05.202658</t>
+  </si>
+  <si>
+    <t>24.05.202659</t>
+  </si>
+  <si>
+    <t>24.05.202660</t>
+  </si>
+  <si>
+    <t>24.05.202661</t>
+  </si>
+  <si>
+    <t>24.05.202662</t>
+  </si>
+  <si>
+    <t>24.05.202663</t>
+  </si>
+  <si>
+    <t>24.05.202664</t>
+  </si>
+  <si>
+    <t>24.05.202665</t>
+  </si>
+  <si>
+    <t>24.05.202666</t>
+  </si>
+  <si>
+    <t>24.05.202667</t>
+  </si>
+  <si>
+    <t>24.05.202668</t>
+  </si>
+  <si>
+    <t>24.05.202669</t>
+  </si>
+  <si>
+    <t>24.05.202670</t>
+  </si>
+  <si>
+    <t>24.05.202671</t>
+  </si>
+  <si>
+    <t>24.05.202672</t>
+  </si>
+  <si>
+    <t>24.05.202673</t>
+  </si>
+  <si>
+    <t>24.05.202674</t>
+  </si>
+  <si>
+    <t>24.05.202675</t>
+  </si>
+  <si>
+    <t>24.05.202676</t>
+  </si>
+  <si>
+    <t>24.05.202677</t>
+  </si>
+  <si>
+    <t>24.05.202678</t>
+  </si>
+  <si>
+    <t>24.05.202679</t>
+  </si>
+  <si>
+    <t>24.05.202680</t>
+  </si>
+  <si>
+    <t>24.05.202681</t>
+  </si>
+  <si>
+    <t>24.05.202682</t>
+  </si>
+  <si>
+    <t>24.05.202683</t>
+  </si>
+  <si>
+    <t>24.05.202684</t>
+  </si>
+  <si>
+    <t>24.05.202685</t>
+  </si>
+  <si>
+    <t>24.05.202686</t>
+  </si>
+  <si>
+    <t>24.05.202687</t>
+  </si>
+  <si>
+    <t>24.05.202688</t>
+  </si>
+  <si>
+    <t>24.05.202689</t>
+  </si>
+  <si>
+    <t>24.05.202690</t>
+  </si>
+  <si>
+    <t>24.05.202691</t>
+  </si>
+  <si>
+    <t>24.05.202692</t>
+  </si>
+  <si>
+    <t>24.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202694</t>
+  </si>
+  <si>
+    <t>24.05.202695</t>
+  </si>
+  <si>
+    <t>24.05.202696</t>
+  </si>
+  <si>
+    <t>25.05.20261</t>
+  </si>
+  <si>
+    <t>25.05.20262</t>
+  </si>
+  <si>
+    <t>25.05.20263</t>
+  </si>
+  <si>
+    <t>25.05.20264</t>
+  </si>
+  <si>
+    <t>25.05.20265</t>
+  </si>
+  <si>
+    <t>25.05.20266</t>
+  </si>
+  <si>
+    <t>25.05.20267</t>
+  </si>
+  <si>
+    <t>25.05.20268</t>
+  </si>
+  <si>
+    <t>25.05.20269</t>
+  </si>
+  <si>
+    <t>25.05.202610</t>
+  </si>
+  <si>
+    <t>25.05.202611</t>
+  </si>
+  <si>
+    <t>25.05.202612</t>
+  </si>
+  <si>
+    <t>25.05.202613</t>
+  </si>
+  <si>
+    <t>25.05.202614</t>
+  </si>
+  <si>
+    <t>25.05.202615</t>
+  </si>
+  <si>
+    <t>25.05.202616</t>
+  </si>
+  <si>
+    <t>25.05.202617</t>
+  </si>
+  <si>
+    <t>25.05.202618</t>
+  </si>
+  <si>
+    <t>25.05.202619</t>
+  </si>
+  <si>
+    <t>25.05.202620</t>
+  </si>
+  <si>
+    <t>25.05.202621</t>
+  </si>
+  <si>
+    <t>25.05.202622</t>
+  </si>
+  <si>
+    <t>25.05.202623</t>
+  </si>
+  <si>
+    <t>25.05.202624</t>
+  </si>
+  <si>
+    <t>25.05.202625</t>
+  </si>
+  <si>
+    <t>25.05.202626</t>
+  </si>
+  <si>
+    <t>25.05.202627</t>
+  </si>
+  <si>
+    <t>25.05.202628</t>
+  </si>
+  <si>
+    <t>25.05.202629</t>
+  </si>
+  <si>
+    <t>25.05.202630</t>
+  </si>
+  <si>
+    <t>25.05.202631</t>
+  </si>
+  <si>
+    <t>25.05.202632</t>
+  </si>
+  <si>
+    <t>25.05.202633</t>
+  </si>
+  <si>
+    <t>25.05.202634</t>
+  </si>
+  <si>
+    <t>25.05.202635</t>
+  </si>
+  <si>
+    <t>25.05.202636</t>
+  </si>
+  <si>
+    <t>25.05.202637</t>
+  </si>
+  <si>
+    <t>25.05.202638</t>
+  </si>
+  <si>
+    <t>25.05.202639</t>
+  </si>
+  <si>
+    <t>25.05.202640</t>
+  </si>
+  <si>
+    <t>25.05.202641</t>
+  </si>
+  <si>
+    <t>25.05.202642</t>
+  </si>
+  <si>
+    <t>25.05.202643</t>
+  </si>
+  <si>
+    <t>25.05.202644</t>
+  </si>
+  <si>
+    <t>25.05.202645</t>
+  </si>
+  <si>
+    <t>25.05.202646</t>
+  </si>
+  <si>
+    <t>25.05.202647</t>
+  </si>
+  <si>
+    <t>25.05.202648</t>
+  </si>
+  <si>
+    <t>25.05.202649</t>
+  </si>
+  <si>
+    <t>25.05.202650</t>
+  </si>
+  <si>
+    <t>25.05.202651</t>
+  </si>
+  <si>
+    <t>25.05.202652</t>
+  </si>
+  <si>
+    <t>25.05.202653</t>
+  </si>
+  <si>
+    <t>25.05.202654</t>
+  </si>
+  <si>
+    <t>25.05.202655</t>
+  </si>
+  <si>
+    <t>25.05.202656</t>
+  </si>
+  <si>
+    <t>25.05.202657</t>
+  </si>
+  <si>
+    <t>25.05.202658</t>
+  </si>
+  <si>
+    <t>25.05.202659</t>
+  </si>
+  <si>
+    <t>25.05.202660</t>
+  </si>
+  <si>
+    <t>25.05.202661</t>
+  </si>
+  <si>
+    <t>25.05.202662</t>
+  </si>
+  <si>
+    <t>25.05.202663</t>
+  </si>
+  <si>
+    <t>25.05.202664</t>
+  </si>
+  <si>
+    <t>25.05.202665</t>
+  </si>
+  <si>
+    <t>25.05.202666</t>
+  </si>
+  <si>
+    <t>25.05.202667</t>
+  </si>
+  <si>
+    <t>25.05.202668</t>
+  </si>
+  <si>
+    <t>25.05.202669</t>
+  </si>
+  <si>
+    <t>25.05.202670</t>
+  </si>
+  <si>
+    <t>25.05.202671</t>
+  </si>
+  <si>
+    <t>25.05.202672</t>
+  </si>
+  <si>
+    <t>25.05.202673</t>
+  </si>
+  <si>
+    <t>25.05.202674</t>
+  </si>
+  <si>
+    <t>25.05.202675</t>
+  </si>
+  <si>
+    <t>25.05.202676</t>
+  </si>
+  <si>
+    <t>25.05.202677</t>
+  </si>
+  <si>
+    <t>25.05.202678</t>
+  </si>
+  <si>
+    <t>25.05.202679</t>
+  </si>
+  <si>
+    <t>25.05.202680</t>
+  </si>
+  <si>
+    <t>25.05.202681</t>
+  </si>
+  <si>
+    <t>25.05.202682</t>
+  </si>
+  <si>
+    <t>25.05.202683</t>
+  </si>
+  <si>
+    <t>25.05.202684</t>
+  </si>
+  <si>
+    <t>25.05.202685</t>
+  </si>
+  <si>
+    <t>25.05.202686</t>
+  </si>
+  <si>
+    <t>25.05.202687</t>
+  </si>
+  <si>
+    <t>25.05.202688</t>
+  </si>
+  <si>
+    <t>25.05.202689</t>
+  </si>
+  <si>
+    <t>25.05.202690</t>
+  </si>
+  <si>
+    <t>25.05.202691</t>
+  </si>
+  <si>
+    <t>25.05.202692</t>
+  </si>
+  <si>
+    <t>25.05.202693</t>
+  </si>
+  <si>
+    <t>25.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202695</t>
+  </si>
+  <si>
+    <t>25.05.202696</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G409"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1000,13 +1576,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="C2">
-        <v>3.594</v>
+        <v>0.333</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1599,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
-        <v>2.001</v>
+        <v>4.098</v>
       </c>
       <c r="C3">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1622,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.436</v>
+        <v>2.915</v>
       </c>
       <c r="C4">
-        <v>2.015</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1645,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
-        <v>0.08</v>
+        <v>1.305</v>
       </c>
       <c r="C5">
-        <v>0.712</v>
+        <v>0.019</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1668,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>8.733000000000001</v>
+        <v>3.335</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1691,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.644</v>
+        <v>3.071</v>
       </c>
       <c r="C7">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1714,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>1.048</v>
+        <v>4.036</v>
       </c>
       <c r="C8">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1737,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="C9">
-        <v>2.083</v>
+        <v>0.46</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1760,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.027</v>
+        <v>0.001</v>
       </c>
       <c r="C10">
-        <v>5.964</v>
+        <v>0.38</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1783,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="C11">
-        <v>17.356</v>
+        <v>0.798</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1806,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>8.409000000000001</v>
+        <v>2.985</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1829,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2.244</v>
       </c>
       <c r="C13">
-        <v>10.107</v>
+        <v>1.231</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1852,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="C14">
-        <v>2.355</v>
+        <v>9.554</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1875,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>11.29</v>
+        <v>10.242</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1898,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="C16">
-        <v>11.468</v>
+        <v>0.844</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1921,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="C17">
-        <v>9.199</v>
+        <v>0.114</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1944,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.047</v>
+        <v>0.347</v>
       </c>
       <c r="C18">
-        <v>2.319</v>
+        <v>1.665</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1967,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2.578</v>
       </c>
       <c r="C19">
-        <v>5.101</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1990,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>3.235</v>
       </c>
       <c r="C20">
-        <v>6.898</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +2013,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.099</v>
+        <v>6.989</v>
       </c>
       <c r="C21">
-        <v>7.79</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +2036,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.024</v>
+        <v>4.993</v>
       </c>
       <c r="C22">
-        <v>1.892</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +2059,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>6.705</v>
       </c>
       <c r="C23">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +2082,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.275</v>
+        <v>10.144</v>
       </c>
       <c r="C24">
-        <v>1.254</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +2105,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.022</v>
+        <v>1.878</v>
       </c>
       <c r="C25">
-        <v>0.002</v>
+        <v>0.211</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +2128,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>29.416</v>
+        <v>4.791</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>4.091</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,10 +2151,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>41.656</v>
+        <v>7.649</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1598,16 +2174,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>30.084</v>
+        <v>11.06</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1621,16 +2197,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>17.146</v>
+        <v>20.781</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1644,16 +2220,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>4.035</v>
+        <v>20.185</v>
       </c>
       <c r="C30">
-        <v>0.076</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1667,16 +2243,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.074</v>
+        <v>20.137</v>
       </c>
       <c r="C31">
-        <v>1.415</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1690,13 +2266,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>1.534</v>
+        <v>22.527</v>
       </c>
       <c r="C32">
-        <v>1.002</v>
+        <v>0.002</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1713,16 +2289,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>16.611</v>
+        <v>0.052</v>
       </c>
       <c r="C33">
-        <v>0.002</v>
+        <v>2.449</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,16 +2312,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.757</v>
+        <v>0.138</v>
       </c>
       <c r="C34">
-        <v>2.055</v>
+        <v>4.748</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +2335,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>0.122</v>
+        <v>0.001</v>
       </c>
       <c r="C35">
-        <v>1.739</v>
+        <v>4.143</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,16 +2358,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.211</v>
+        <v>12.768</v>
       </c>
       <c r="C36">
-        <v>0.495</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +2381,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.28</v>
+        <v>1.892</v>
       </c>
       <c r="C37">
-        <v>0.137</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,16 +2404,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>0.283</v>
+        <v>7.163</v>
       </c>
       <c r="C38">
-        <v>0.282</v>
+        <v>0.049</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1851,16 +2427,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="C39">
-        <v>0.194</v>
+        <v>2.463</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>14.799</v>
+        <v>0.051</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2.384</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,13 +2473,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>12.949</v>
+        <v>1.316</v>
       </c>
       <c r="C41">
-        <v>0.209</v>
+        <v>0.282</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1920,13 +2496,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>1.96</v>
+        <v>3.911</v>
       </c>
       <c r="C42">
-        <v>0.479</v>
+        <v>0.064</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1943,16 +2519,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.633</v>
+        <v>3.214</v>
       </c>
       <c r="C43">
-        <v>2.824</v>
+        <v>0.132</v>
       </c>
       <c r="D43">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1966,16 +2542,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>9.846</v>
       </c>
       <c r="C44">
-        <v>11.791</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1989,13 +2565,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.92</v>
+        <v>22.633</v>
       </c>
       <c r="C45">
-        <v>3.06</v>
+        <v>0.797</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2012,13 +2588,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>0.661</v>
       </c>
       <c r="C46">
-        <v>50.59</v>
+        <v>1.628</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2035,13 +2611,13 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0.665</v>
+        <v>6.629</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2058,13 +2634,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>0.279</v>
+        <v>27.333</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2081,13 +2657,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.384</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>1.18</v>
+        <v>34.045</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2104,13 +2680,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>13.585</v>
+        <v>18.656</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>6.74</v>
+        <v>22.431</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2150,13 +2726,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0.053</v>
+        <v>27.376</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,13 +2749,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>28.454</v>
+        <v>0.005</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>14.461</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,13 +2772,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>32.963</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>38.331</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2219,19 +2795,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>43.384</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>32.097</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2818,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>51.597</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>40.385</v>
       </c>
       <c r="D56">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2841,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>20.696</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0.026</v>
+        <v>48.823</v>
       </c>
       <c r="D57">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2864,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.542</v>
+        <v>1.598</v>
       </c>
       <c r="C58">
-        <v>0.435</v>
+        <v>4.57</v>
       </c>
       <c r="D58">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2887,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>2.043</v>
       </c>
       <c r="C59">
-        <v>44.335</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D59">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,13 +2910,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>16.403</v>
+        <v>17.165</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2933,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C61">
-        <v>23.371</v>
+        <v>12.8</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2956,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>8.632</v>
+        <v>50.106</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2979,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>67.101</v>
+        <v>71.55200000000001</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,19 +3002,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>56.668</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +3025,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>1.217</v>
+        <v>10.363</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,13 +3048,13 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.252</v>
+        <v>1.45</v>
       </c>
       <c r="C66">
-        <v>0.343</v>
+        <v>2.583</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2495,13 +3071,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.008</v>
+        <v>0.724</v>
       </c>
       <c r="C67">
-        <v>8.420999999999999</v>
+        <v>0.578</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2518,13 +3094,13 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>0.06</v>
+        <v>0.131</v>
       </c>
       <c r="C68">
-        <v>5.27</v>
+        <v>0.245</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2541,13 +3117,13 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>7.727</v>
       </c>
       <c r="C69">
-        <v>8.237</v>
+        <v>0.005</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2564,19 +3140,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.111</v>
+        <v>5.961</v>
       </c>
       <c r="C70">
-        <v>0.902</v>
+        <v>4.516</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>46.75</v>
+        <v>50</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,19 +3163,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>0.015</v>
+        <v>18.721</v>
       </c>
       <c r="C71">
-        <v>12.979</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +3186,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>30.477</v>
       </c>
       <c r="C72">
-        <v>12.905</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +3209,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="C73">
-        <v>11.025</v>
+        <v>0.075</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,19 +3232,19 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1.723</v>
       </c>
       <c r="C74">
-        <v>61.815</v>
+        <v>7.695</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -2679,19 +3255,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>8.305</v>
+        <v>12.634</v>
       </c>
       <c r="C75">
-        <v>5.184</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -2702,10 +3278,10 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>8.714</v>
+        <v>37.179</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2714,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,10 +3301,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>7.664</v>
+        <v>34.59</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2737,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +3324,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.447</v>
+        <v>4.242</v>
       </c>
       <c r="C78">
-        <v>1.027</v>
+        <v>0.927</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +3347,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.052</v>
+        <v>8.069000000000001</v>
       </c>
       <c r="C79">
-        <v>3.32</v>
+        <v>0.056</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +3370,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>0.075</v>
+        <v>34.059</v>
       </c>
       <c r="C80">
-        <v>0.366</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +3393,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.118</v>
+        <v>34.33</v>
       </c>
       <c r="C81">
-        <v>0.191</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,19 +3416,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.234</v>
+        <v>35.598</v>
       </c>
       <c r="C82">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2863,19 +3439,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>0.026</v>
+        <v>15.412</v>
       </c>
       <c r="C83">
-        <v>1.895</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -2886,19 +3462,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.076</v>
+        <v>6.737</v>
       </c>
       <c r="C84">
-        <v>0.157</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>83</v>
@@ -2909,19 +3485,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.052</v>
+        <v>2.534</v>
       </c>
       <c r="C85">
-        <v>0.411</v>
+        <v>0.108</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F85">
         <v>84</v>
@@ -2932,10 +3508,10 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>11.987</v>
+        <v>14.644</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2944,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F86">
         <v>85</v>
@@ -2955,19 +3531,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>12.234</v>
+        <v>4.78</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +3554,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>8.103999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>3.282</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3577,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>0.476</v>
+        <v>0.002</v>
       </c>
       <c r="C89">
-        <v>0.851</v>
+        <v>4.426</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,13 +3600,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.067</v>
+        <v>1.187</v>
       </c>
       <c r="C90">
-        <v>0.902</v>
+        <v>0.012</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3623,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.096</v>
+        <v>7.235</v>
       </c>
       <c r="C91">
-        <v>0.63</v>
+        <v>0.03</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3646,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>0.237</v>
+        <v>13.974</v>
       </c>
       <c r="C92">
-        <v>0.452</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3669,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.107</v>
+        <v>0.22</v>
       </c>
       <c r="C93">
-        <v>0.621</v>
+        <v>0.042</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3692,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.472</v>
+        <v>21.768</v>
       </c>
       <c r="C94">
-        <v>0.241</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3715,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
-        <v>0.028</v>
+        <v>11.291</v>
       </c>
       <c r="C95">
-        <v>2.939</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3738,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>17.573</v>
       </c>
       <c r="C96">
-        <v>2.558</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3761,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>13.915</v>
       </c>
       <c r="C97">
-        <v>10.741</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3784,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98">
-        <v>9.132999999999999</v>
+        <v>45.685</v>
       </c>
       <c r="C98">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3807,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B99">
-        <v>9.132999999999999</v>
+        <v>45.685</v>
       </c>
       <c r="C99">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,10 +3830,10 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B100">
-        <v>4.098</v>
+        <v>25.941</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -3277,10 +3853,10 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B101">
-        <v>4.098</v>
+        <v>25.941</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -3300,16 +3876,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B102">
-        <v>2.915</v>
+        <v>4.13</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3323,16 +3899,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B103">
-        <v>2.915</v>
+        <v>4.13</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3346,16 +3922,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B104">
-        <v>1.305</v>
+        <v>16.156</v>
       </c>
       <c r="C104">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3369,16 +3945,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B105">
-        <v>1.305</v>
+        <v>16.156</v>
       </c>
       <c r="C105">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3392,16 +3968,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B106">
-        <v>3.335</v>
+        <v>14.306</v>
       </c>
       <c r="C106">
-        <v>0.268</v>
+        <v>0.042</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3415,16 +3991,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B107">
-        <v>3.335</v>
+        <v>14.306</v>
       </c>
       <c r="C107">
-        <v>0.268</v>
+        <v>0.042</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3438,16 +4014,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B108">
-        <v>3.071</v>
+        <v>3.38</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3461,16 +4037,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B109">
-        <v>3.071</v>
+        <v>3.38</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3484,16 +4060,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B110">
-        <v>4.036</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>4.343</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3507,16 +4083,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B111">
-        <v>4.036</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>4.343</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3530,16 +4106,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B112">
-        <v>0.136</v>
+        <v>0.002</v>
       </c>
       <c r="C112">
-        <v>0.46</v>
+        <v>3.315</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +4129,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.136</v>
+        <v>0.002</v>
       </c>
       <c r="C113">
-        <v>0.46</v>
+        <v>3.315</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,13 +4152,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46164.08333333334</v>
+        <v>46165.08333333334</v>
       </c>
       <c r="B114">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>0.38</v>
+        <v>5.642</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,16 +4175,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46164.09375</v>
+        <v>46165.09375</v>
       </c>
       <c r="B115">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0.798</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,13 +4198,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46164.10416666666</v>
+        <v>46165.10416666666</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C116">
-        <v>2.985</v>
+        <v>11.345</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +4221,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46164.11458333334</v>
+        <v>46165.11458333334</v>
       </c>
       <c r="B117">
-        <v>2.244</v>
+        <v>1.197</v>
       </c>
       <c r="C117">
-        <v>1.231</v>
+        <v>0.027</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +4244,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46164.125</v>
+        <v>46165.125</v>
       </c>
       <c r="B118">
-        <v>0.015</v>
+        <v>0.191</v>
       </c>
       <c r="C118">
-        <v>9.554</v>
+        <v>0.164</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46164.13541666666</v>
+        <v>46165.13541666666</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>1.646</v>
       </c>
       <c r="C119">
-        <v>10.242</v>
+        <v>0.06</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +4290,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46164.14583333334</v>
+        <v>46165.14583333334</v>
       </c>
       <c r="B120">
-        <v>0.285</v>
+        <v>0.043</v>
       </c>
       <c r="C120">
-        <v>0.844</v>
+        <v>0.345</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +4313,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46164.15625</v>
+        <v>46165.15625</v>
       </c>
       <c r="B121">
-        <v>0.417</v>
+        <v>0.473</v>
       </c>
       <c r="C121">
-        <v>0.114</v>
+        <v>0.016</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +4336,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46164.16666666666</v>
+        <v>46165.16666666666</v>
       </c>
       <c r="B122">
-        <v>0.347</v>
+        <v>3.566</v>
       </c>
       <c r="C122">
-        <v>1.665</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +4359,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46164.17708333334</v>
+        <v>46165.17708333334</v>
       </c>
       <c r="B123">
-        <v>2.578</v>
+        <v>0.349</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +4382,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46164.1875</v>
+        <v>46165.1875</v>
       </c>
       <c r="B124">
-        <v>3.235</v>
+        <v>0.113</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +4405,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46164.19791666666</v>
+        <v>46165.19791666666</v>
       </c>
       <c r="B125">
-        <v>6.989</v>
+        <v>0.046</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>4.203</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +4428,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46164.20833333334</v>
+        <v>46165.20833333334</v>
       </c>
       <c r="B126">
-        <v>4.993</v>
+        <v>0.118</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +4451,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46164.21875</v>
+        <v>46165.21875</v>
       </c>
       <c r="B127">
-        <v>6.705</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +4474,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46164.22916666666</v>
+        <v>46165.22916666666</v>
       </c>
       <c r="B128">
-        <v>10.144</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>5.259</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +4497,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46164.23958333334</v>
+        <v>46165.23958333334</v>
       </c>
       <c r="B129">
-        <v>1.878</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>0.211</v>
+        <v>11.466</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +4520,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46164.25</v>
+        <v>46165.25</v>
       </c>
       <c r="B130">
-        <v>4.791</v>
+        <v>0.23</v>
       </c>
       <c r="C130">
-        <v>4.091</v>
+        <v>0.353</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,13 +4543,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46164.26041666666</v>
+        <v>46165.26041666666</v>
       </c>
       <c r="B131">
-        <v>7.649</v>
+        <v>1.02</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,10 +4566,10 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46164.27083333334</v>
+        <v>46165.27083333334</v>
       </c>
       <c r="B132">
-        <v>11.06</v>
+        <v>13.003</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -4013,10 +4589,10 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46164.28125</v>
+        <v>46165.28125</v>
       </c>
       <c r="B133">
-        <v>20.781</v>
+        <v>20.148</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -4036,10 +4612,10 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46164.29166666666</v>
+        <v>46165.29166666666</v>
       </c>
       <c r="B134">
-        <v>20.185</v>
+        <v>4.114</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -4059,10 +4635,10 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46164.30208333334</v>
+        <v>46165.30208333334</v>
       </c>
       <c r="B135">
-        <v>20.137</v>
+        <v>26.326</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -4082,16 +4658,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46164.3125</v>
+        <v>46165.3125</v>
       </c>
       <c r="B136">
-        <v>22.527</v>
+        <v>8.423</v>
       </c>
       <c r="C136">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>35.25</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4105,16 +4681,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46164.32291666666</v>
+        <v>46165.32291666666</v>
       </c>
       <c r="B137">
-        <v>0.052</v>
+        <v>0.118</v>
       </c>
       <c r="C137">
-        <v>2.449</v>
+        <v>0.782</v>
       </c>
       <c r="D137">
-        <v>50</v>
+        <v>35.25</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4128,16 +4704,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46164.33333333334</v>
+        <v>46165.33333333334</v>
       </c>
       <c r="B138">
-        <v>0.138</v>
+        <v>2.771</v>
       </c>
       <c r="C138">
-        <v>4.748</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D138">
-        <v>50</v>
+        <v>32.5</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4151,16 +4727,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46164.34375</v>
+        <v>46165.34375</v>
       </c>
       <c r="B139">
-        <v>0.001</v>
+        <v>0.217</v>
       </c>
       <c r="C139">
-        <v>4.143</v>
+        <v>1.094</v>
       </c>
       <c r="D139">
-        <v>50</v>
+        <v>32.5</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46164.35416666666</v>
+        <v>46165.35416666666</v>
       </c>
       <c r="B140">
-        <v>12.768</v>
+        <v>0.217</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="D140">
-        <v>25</v>
+        <v>32.5</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4197,16 +4773,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46164.36458333334</v>
+        <v>46165.36458333334</v>
       </c>
       <c r="B141">
-        <v>1.892</v>
+        <v>0.157</v>
       </c>
       <c r="C141">
-        <v>0.07099999999999999</v>
+        <v>0.221</v>
       </c>
       <c r="D141">
-        <v>25</v>
+        <v>32.5</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4220,16 +4796,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46164.375</v>
+        <v>46165.375</v>
       </c>
       <c r="B142">
-        <v>7.163</v>
+        <v>14.403</v>
       </c>
       <c r="C142">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>25</v>
+        <v>32.5</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4243,16 +4819,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46164.38541666666</v>
+        <v>46165.38541666666</v>
       </c>
       <c r="B143">
-        <v>0.175</v>
+        <v>35.721</v>
       </c>
       <c r="C143">
-        <v>2.463</v>
+        <v>0</v>
       </c>
       <c r="D143">
-        <v>25</v>
+        <v>32.5</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4266,16 +4842,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46164.39583333334</v>
+        <v>46165.39583333334</v>
       </c>
       <c r="B144">
-        <v>0.051</v>
+        <v>1.086</v>
       </c>
       <c r="C144">
-        <v>2.384</v>
+        <v>3.83</v>
       </c>
       <c r="D144">
-        <v>25</v>
+        <v>32.5</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4289,16 +4865,16 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46164.40625</v>
+        <v>46165.40625</v>
       </c>
       <c r="B145">
-        <v>1.316</v>
+        <v>0</v>
       </c>
       <c r="C145">
-        <v>0.282</v>
+        <v>52.987</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -4312,13 +4888,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46164.41666666666</v>
+        <v>46165.41666666666</v>
       </c>
       <c r="B146">
-        <v>3.911</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>0.064</v>
+        <v>13.363</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4335,13 +4911,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46164.42708333334</v>
+        <v>46165.42708333334</v>
       </c>
       <c r="B147">
-        <v>3.214</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>0.132</v>
+        <v>2.839</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4358,13 +4934,13 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46164.4375</v>
+        <v>46165.4375</v>
       </c>
       <c r="B148">
-        <v>9.846</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>7.433</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -4381,13 +4957,13 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46164.44791666666</v>
+        <v>46165.44791666666</v>
       </c>
       <c r="B149">
-        <v>22.633</v>
+        <v>0.556</v>
       </c>
       <c r="C149">
-        <v>0.797</v>
+        <v>9.066000000000001</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4404,13 +4980,13 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46164.45833333334</v>
+        <v>46165.45833333334</v>
       </c>
       <c r="B150">
-        <v>0.661</v>
+        <v>14.667</v>
       </c>
       <c r="C150">
-        <v>1.628</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4427,13 +5003,13 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46164.46875</v>
+        <v>46165.46875</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>11.957</v>
       </c>
       <c r="C151">
-        <v>6.629</v>
+        <v>1.857</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4450,13 +5026,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46164.47916666666</v>
+        <v>46165.47916666666</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C152">
-        <v>27.333</v>
+        <v>6.302</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4473,13 +5049,13 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46164.48958333334</v>
+        <v>46165.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>34.045</v>
+        <v>12.845</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4496,13 +5072,13 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46164.5</v>
+        <v>46165.5</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>1.475</v>
       </c>
       <c r="C154">
-        <v>18.656</v>
+        <v>0.05</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4519,13 +5095,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46164.51041666666</v>
+        <v>46165.51041666666</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>3.705</v>
       </c>
       <c r="C155">
-        <v>22.431</v>
+        <v>4.274</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4542,13 +5118,13 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46164.52083333334</v>
+        <v>46165.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>42.427</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4565,13 +5141,13 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46164.53125</v>
+        <v>46165.53125</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>0.657</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>32.327</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -4588,10 +5164,10 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46164.54166666666</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>28.85</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -4600,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F158">
         <v>53</v>
@@ -4611,13 +5187,13 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46164.55208333334</v>
+        <v>46165.55208333334</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>8.957000000000001</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -4634,13 +5210,13 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46164.5625</v>
+        <v>46165.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>16.824</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -4657,13 +5233,13 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46164.57291666666</v>
+        <v>46165.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>12.759</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -4680,13 +5256,13 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46164.58333333334</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>16.51</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -4703,13 +5279,13 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46164.59375</v>
+        <v>46165.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>14.544</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -4726,13 +5302,13 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46164.60416666666</v>
+        <v>46165.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>13.373</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -4749,13 +5325,13 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46164.61458333334</v>
+        <v>46165.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>18.641</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -4772,13 +5348,13 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46164.625</v>
+        <v>46165.625</v>
       </c>
       <c r="B166">
         <v>0</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>55.161</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -4795,13 +5371,13 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46164.63541666666</v>
+        <v>46165.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>48.127</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -4818,13 +5394,13 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46164.64583333334</v>
+        <v>46165.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>15.453</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -4841,13 +5417,13 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46164.65625</v>
+        <v>46165.65625</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>4.883</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -4864,13 +5440,13 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46164.66666666666</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>66.456</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -4887,13 +5463,13 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46164.67708333334</v>
+        <v>46165.67708333334</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>24.478</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -4910,13 +5486,13 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46164.6875</v>
+        <v>46165.6875</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>1.604</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>5.587</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -4933,13 +5509,13 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46164.69791666666</v>
+        <v>46165.69791666666</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -4956,13 +5532,13 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46164.70833333334</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>16.824</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -4979,13 +5555,13 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46164.71875</v>
+        <v>46165.71875</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>0.317</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -5002,13 +5578,13 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46164.72916666666</v>
+        <v>46165.72916666666</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>3.512</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -5025,13 +5601,13 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46164.73958333334</v>
+        <v>46165.73958333334</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>5.392</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5048,13 +5624,13 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46164.75</v>
+        <v>46165.75</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>5.612</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>0.979</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -5071,10 +5647,10 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46164.76041666666</v>
+        <v>46165.76041666666</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>26.433</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -5094,10 +5670,10 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46164.77083333334</v>
+        <v>46165.77083333334</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>39.682</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -5117,10 +5693,10 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46164.78125</v>
+        <v>46165.78125</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>50.096</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -5140,13 +5716,13 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46164.79166666666</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>9.961</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5163,13 +5739,13 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46164.80208333334</v>
+        <v>46165.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>7.196</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5186,13 +5762,13 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46164.8125</v>
+        <v>46165.8125</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>0.284</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5209,13 +5785,13 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46164.82291666666</v>
+        <v>46165.82291666666</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>1.341</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -5232,13 +5808,13 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46164.83333333334</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -5255,13 +5831,13 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46164.84375</v>
+        <v>46165.84375</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>8.956</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -5278,10 +5854,10 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46164.85416666666</v>
+        <v>46165.85416666666</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>14.361</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -5301,10 +5877,10 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46164.86458333334</v>
+        <v>46165.86458333334</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>62.322</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -5324,10 +5900,10 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46164.875</v>
+        <v>46165.875</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>71.77800000000001</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -5347,16 +5923,16 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46164.88541666666</v>
+        <v>46165.88541666666</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>41.287</v>
       </c>
       <c r="C191">
         <v>0</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -5370,16 +5946,16 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46164.89583333334</v>
+        <v>46165.89583333334</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>14.379</v>
       </c>
       <c r="C192">
         <v>0</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -5393,16 +5969,16 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46164.90625</v>
+        <v>46165.90625</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>70.535</v>
       </c>
       <c r="C193">
         <v>0</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -5416,16 +5992,16 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46164.91666666666</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B194">
-        <v>0</v>
+        <v>84.857</v>
       </c>
       <c r="C194">
         <v>0</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -5439,16 +6015,16 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46164.92708333334</v>
+        <v>46165.92708333334</v>
       </c>
       <c r="B195">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="C195">
         <v>0</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -5462,16 +6038,16 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46164.9375</v>
+        <v>46165.9375</v>
       </c>
       <c r="B196">
-        <v>0</v>
+        <v>87.298</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -5485,16 +6061,16 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46164.94791666666</v>
+        <v>46165.94791666666</v>
       </c>
       <c r="B197">
-        <v>0</v>
+        <v>92.233</v>
       </c>
       <c r="C197">
         <v>0</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -5508,16 +6084,16 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46164.95833333334</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>67.524</v>
       </c>
       <c r="C198">
         <v>0</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -5531,16 +6107,16 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46164.96875</v>
+        <v>46165.96875</v>
       </c>
       <c r="B199">
-        <v>0</v>
+        <v>2.671</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>6.007</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -5554,16 +6130,16 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46164.97916666666</v>
+        <v>46165.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
       </c>
       <c r="C200">
-        <v>0</v>
+        <v>13.062</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>169.5</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -5577,16 +6153,16 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46164.98958333334</v>
+        <v>46165.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>38.349</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>156.5</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -5596,6 +6172,4790 @@
       </c>
       <c r="G201" t="s">
         <v>198</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>12.288</v>
+      </c>
+      <c r="D202">
+        <v>100</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>12.288</v>
+      </c>
+      <c r="D203">
+        <v>100</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B204">
+        <v>0.273</v>
+      </c>
+      <c r="C204">
+        <v>0.116</v>
+      </c>
+      <c r="D204">
+        <v>45</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>2</v>
+      </c>
+      <c r="G204" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B205">
+        <v>0.273</v>
+      </c>
+      <c r="C205">
+        <v>0.116</v>
+      </c>
+      <c r="D205">
+        <v>45</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>2</v>
+      </c>
+      <c r="G205" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B206">
+        <v>0.887</v>
+      </c>
+      <c r="C206">
+        <v>5.078</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>3</v>
+      </c>
+      <c r="G206" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B207">
+        <v>0.887</v>
+      </c>
+      <c r="C207">
+        <v>5.078</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>3</v>
+      </c>
+      <c r="G207" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>9.784000000000001</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>4</v>
+      </c>
+      <c r="G208" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>9.784000000000001</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>4</v>
+      </c>
+      <c r="G209" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B210">
+        <v>0.186</v>
+      </c>
+      <c r="C210">
+        <v>3.377</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>5</v>
+      </c>
+      <c r="G210" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B211">
+        <v>0.186</v>
+      </c>
+      <c r="C211">
+        <v>3.377</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>5</v>
+      </c>
+      <c r="G211" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>5.874</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="F212">
+        <v>6</v>
+      </c>
+      <c r="G212" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>5.874</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>6</v>
+      </c>
+      <c r="G213" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>5.812</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>7</v>
+      </c>
+      <c r="G214" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>5.812</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+      <c r="F215">
+        <v>7</v>
+      </c>
+      <c r="G215" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B216">
+        <v>0.146</v>
+      </c>
+      <c r="C216">
+        <v>8.198</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>8</v>
+      </c>
+      <c r="G216" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B217">
+        <v>0.146</v>
+      </c>
+      <c r="C217">
+        <v>8.198</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>8</v>
+      </c>
+      <c r="G217" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="2">
+        <v>46166.08333333334</v>
+      </c>
+      <c r="B218">
+        <v>2.04</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>9</v>
+      </c>
+      <c r="G218" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="2">
+        <v>46166.09375</v>
+      </c>
+      <c r="B219">
+        <v>0.336</v>
+      </c>
+      <c r="C219">
+        <v>6.305</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>10</v>
+      </c>
+      <c r="G219" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="2">
+        <v>46166.10416666666</v>
+      </c>
+      <c r="B220">
+        <v>0.018</v>
+      </c>
+      <c r="C220">
+        <v>4.087</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>11</v>
+      </c>
+      <c r="G220" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="2">
+        <v>46166.11458333334</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>3.217</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>12</v>
+      </c>
+      <c r="G221" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
+        <v>46166.125</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>14.722</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>13</v>
+      </c>
+      <c r="G222" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
+        <v>46166.13541666666</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>19.088</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>14</v>
+      </c>
+      <c r="G223" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
+        <v>46166.14583333334</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>19.857</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>15</v>
+      </c>
+      <c r="G224" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
+        <v>46166.15625</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>12.654</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>16</v>
+      </c>
+      <c r="G225" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
+        <v>46166.16666666666</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>4.103</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>17</v>
+      </c>
+      <c r="G226" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
+        <v>46166.17708333334</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>5.833</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>18</v>
+      </c>
+      <c r="G227" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
+        <v>46166.1875</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>6.969</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>19</v>
+      </c>
+      <c r="G228" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
+        <v>46166.19791666666</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>2.648</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>20</v>
+      </c>
+      <c r="G229" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
+        <v>46166.20833333334</v>
+      </c>
+      <c r="B230">
+        <v>0.319</v>
+      </c>
+      <c r="C230">
+        <v>0.277</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>21</v>
+      </c>
+      <c r="G230" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
+        <v>46166.21875</v>
+      </c>
+      <c r="B231">
+        <v>0.149</v>
+      </c>
+      <c r="C231">
+        <v>0.098</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>22</v>
+      </c>
+      <c r="G231" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>46166.22916666666</v>
+      </c>
+      <c r="B232">
+        <v>0.012</v>
+      </c>
+      <c r="C232">
+        <v>0.477</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>23</v>
+      </c>
+      <c r="G232" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
+        <v>46166.23958333334</v>
+      </c>
+      <c r="B233">
+        <v>0.023</v>
+      </c>
+      <c r="C233">
+        <v>0.772</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
+        <v>46166.25</v>
+      </c>
+      <c r="B234">
+        <v>0.31</v>
+      </c>
+      <c r="C234">
+        <v>0.037</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>25</v>
+      </c>
+      <c r="G234" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
+        <v>46166.26041666666</v>
+      </c>
+      <c r="B235">
+        <v>0.333</v>
+      </c>
+      <c r="C235">
+        <v>0.12</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
+        <v>46166.27083333334</v>
+      </c>
+      <c r="B236">
+        <v>16.073</v>
+      </c>
+      <c r="C236">
+        <v>0.001</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="2">
+        <v>46166.28125</v>
+      </c>
+      <c r="B237">
+        <v>0.407</v>
+      </c>
+      <c r="C237">
+        <v>0.18</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237">
+        <v>28</v>
+      </c>
+      <c r="G237" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="2">
+        <v>46166.29166666666</v>
+      </c>
+      <c r="B238">
+        <v>1.402</v>
+      </c>
+      <c r="C238">
+        <v>0.042</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238">
+        <v>29</v>
+      </c>
+      <c r="G238" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="2">
+        <v>46166.30208333334</v>
+      </c>
+      <c r="B239">
+        <v>13.211</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>30</v>
+      </c>
+      <c r="G239" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="2">
+        <v>46166.3125</v>
+      </c>
+      <c r="B240">
+        <v>0.122</v>
+      </c>
+      <c r="C240">
+        <v>0.165</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>31</v>
+      </c>
+      <c r="G240" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="2">
+        <v>46166.32291666666</v>
+      </c>
+      <c r="B241">
+        <v>0.278</v>
+      </c>
+      <c r="C241">
+        <v>0.262</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>32</v>
+      </c>
+      <c r="G241" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="2">
+        <v>46166.33333333334</v>
+      </c>
+      <c r="B242">
+        <v>0.375</v>
+      </c>
+      <c r="C242">
+        <v>0.195</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+      <c r="F242">
+        <v>33</v>
+      </c>
+      <c r="G242" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="2">
+        <v>46166.34375</v>
+      </c>
+      <c r="B243">
+        <v>0.082</v>
+      </c>
+      <c r="C243">
+        <v>1.507</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>34</v>
+      </c>
+      <c r="G243" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="2">
+        <v>46166.35416666666</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>8.936999999999999</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>35</v>
+      </c>
+      <c r="G244" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="2">
+        <v>46166.36458333334</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>19.701</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245">
+        <v>36</v>
+      </c>
+      <c r="G245" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="2">
+        <v>46166.375</v>
+      </c>
+      <c r="B246">
+        <v>0.358</v>
+      </c>
+      <c r="C246">
+        <v>3.372</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
+      <c r="F246">
+        <v>37</v>
+      </c>
+      <c r="G246" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="2">
+        <v>46166.38541666666</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>9.629</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>38</v>
+      </c>
+      <c r="G247" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="2">
+        <v>46166.39583333334</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>7.828</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+      <c r="F248">
+        <v>39</v>
+      </c>
+      <c r="G248" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="2">
+        <v>46166.40625</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>8.893000000000001</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>40</v>
+      </c>
+      <c r="G249" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="2">
+        <v>46166.41666666666</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>16.217</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>41</v>
+      </c>
+      <c r="G250" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="2">
+        <v>46166.42708333334</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>4.277</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>42</v>
+      </c>
+      <c r="G251" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="2">
+        <v>46166.4375</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>4.865</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>43</v>
+      </c>
+      <c r="G252" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="2">
+        <v>46166.44791666666</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>3.664</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>44</v>
+      </c>
+      <c r="G253" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="2">
+        <v>46166.45833333334</v>
+      </c>
+      <c r="B254">
+        <v>0.162</v>
+      </c>
+      <c r="C254">
+        <v>0.854</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>45</v>
+      </c>
+      <c r="G254" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="2">
+        <v>46166.46875</v>
+      </c>
+      <c r="B255">
+        <v>1.574</v>
+      </c>
+      <c r="C255">
+        <v>0.055</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>46</v>
+      </c>
+      <c r="G255" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="2">
+        <v>46166.47916666666</v>
+      </c>
+      <c r="B256">
+        <v>0.606</v>
+      </c>
+      <c r="C256">
+        <v>4.522</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>47</v>
+      </c>
+      <c r="G256" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="2">
+        <v>46166.48958333334</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>21.077</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>48</v>
+      </c>
+      <c r="G257" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="2">
+        <v>46166.5</v>
+      </c>
+      <c r="B258">
+        <v>0.1</v>
+      </c>
+      <c r="C258">
+        <v>3.526</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>49</v>
+      </c>
+      <c r="G258" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="2">
+        <v>46166.51041666666</v>
+      </c>
+      <c r="B259">
+        <v>0.048</v>
+      </c>
+      <c r="C259">
+        <v>2.239</v>
+      </c>
+      <c r="D259">
+        <v>0</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>50</v>
+      </c>
+      <c r="G259" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="2">
+        <v>46166.52083333334</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>39.182</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>51</v>
+      </c>
+      <c r="G260" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="2">
+        <v>46166.53125</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>29.199</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>52</v>
+      </c>
+      <c r="G261" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="2">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>27.426</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>53</v>
+      </c>
+      <c r="G262" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="2">
+        <v>46166.55208333334</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>33.754</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>54</v>
+      </c>
+      <c r="G263" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="2">
+        <v>46166.5625</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>27.974</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>55</v>
+      </c>
+      <c r="G264" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="2">
+        <v>46166.57291666666</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>35.324</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>56</v>
+      </c>
+      <c r="G265" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="2">
+        <v>46166.58333333334</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>7.669</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>57</v>
+      </c>
+      <c r="G266" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="2">
+        <v>46166.59375</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>28.24</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>58</v>
+      </c>
+      <c r="G267" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="2">
+        <v>46166.60416666666</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>36.922</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>59</v>
+      </c>
+      <c r="G268" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="2">
+        <v>46166.61458333334</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>19.725</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>60</v>
+      </c>
+      <c r="G269" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="2">
+        <v>46166.625</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>36.54</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>61</v>
+      </c>
+      <c r="G270" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="2">
+        <v>46166.63541666666</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>26.867</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>62</v>
+      </c>
+      <c r="G271" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="2">
+        <v>46166.64583333334</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>28.23</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>63</v>
+      </c>
+      <c r="G272" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="2">
+        <v>46166.65625</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>21.483</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>64</v>
+      </c>
+      <c r="G273" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="2">
+        <v>46166.66666666666</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>19.493</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>65</v>
+      </c>
+      <c r="G274" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="2">
+        <v>46166.67708333334</v>
+      </c>
+      <c r="B275">
+        <v>2.185</v>
+      </c>
+      <c r="C275">
+        <v>0.46</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>66</v>
+      </c>
+      <c r="G275" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="2">
+        <v>46166.6875</v>
+      </c>
+      <c r="B276">
+        <v>1.197</v>
+      </c>
+      <c r="C276">
+        <v>0.288</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>67</v>
+      </c>
+      <c r="G276" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="2">
+        <v>46166.69791666666</v>
+      </c>
+      <c r="B277">
+        <v>6.373</v>
+      </c>
+      <c r="C277">
+        <v>0.007</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>68</v>
+      </c>
+      <c r="G277" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="2">
+        <v>46166.70833333334</v>
+      </c>
+      <c r="B278">
+        <v>0.093</v>
+      </c>
+      <c r="C278">
+        <v>17.348</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>69</v>
+      </c>
+      <c r="G278" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="2">
+        <v>46166.71875</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>25.775</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>70</v>
+      </c>
+      <c r="G279" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="2">
+        <v>46166.72916666666</v>
+      </c>
+      <c r="B280">
+        <v>0.048</v>
+      </c>
+      <c r="C280">
+        <v>1.355</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>71</v>
+      </c>
+      <c r="G280" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="2">
+        <v>46166.73958333334</v>
+      </c>
+      <c r="B281">
+        <v>0.006</v>
+      </c>
+      <c r="C281">
+        <v>4.302</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>72</v>
+      </c>
+      <c r="G281" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="2">
+        <v>46166.75</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>10.684</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>73</v>
+      </c>
+      <c r="G282" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="2">
+        <v>46166.76041666666</v>
+      </c>
+      <c r="B283">
+        <v>1.21</v>
+      </c>
+      <c r="C283">
+        <v>5.785</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>74</v>
+      </c>
+      <c r="G283" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="2">
+        <v>46166.77083333334</v>
+      </c>
+      <c r="B284">
+        <v>14.679</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>75</v>
+      </c>
+      <c r="G284" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="2">
+        <v>46166.78125</v>
+      </c>
+      <c r="B285">
+        <v>35.589</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>76</v>
+      </c>
+      <c r="G285" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="2">
+        <v>46166.79166666666</v>
+      </c>
+      <c r="B286">
+        <v>16.459</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>77</v>
+      </c>
+      <c r="G286" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="2">
+        <v>46166.80208333334</v>
+      </c>
+      <c r="B287">
+        <v>15.642</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>78</v>
+      </c>
+      <c r="G287" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="2">
+        <v>46166.8125</v>
+      </c>
+      <c r="B288">
+        <v>15.665</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>79</v>
+      </c>
+      <c r="G288" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="2">
+        <v>46166.82291666666</v>
+      </c>
+      <c r="B289">
+        <v>12.327</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>80</v>
+      </c>
+      <c r="G289" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="2">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B290">
+        <v>7.936</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>81</v>
+      </c>
+      <c r="G290" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="2">
+        <v>46166.84375</v>
+      </c>
+      <c r="B291">
+        <v>11.828</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>82</v>
+      </c>
+      <c r="G291" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="2">
+        <v>46166.85416666666</v>
+      </c>
+      <c r="B292">
+        <v>3.629</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>83</v>
+      </c>
+      <c r="G292" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="2">
+        <v>46166.86458333334</v>
+      </c>
+      <c r="B293">
+        <v>5.929</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>84</v>
+      </c>
+      <c r="G293" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="2">
+        <v>46166.875</v>
+      </c>
+      <c r="B294">
+        <v>16.894</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>85</v>
+      </c>
+      <c r="G294" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="2">
+        <v>46166.88541666666</v>
+      </c>
+      <c r="B295">
+        <v>13.071</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>86</v>
+      </c>
+      <c r="G295" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="2">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="B296">
+        <v>3.743</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>87</v>
+      </c>
+      <c r="G296" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="2">
+        <v>46166.90625</v>
+      </c>
+      <c r="B297">
+        <v>2.257</v>
+      </c>
+      <c r="C297">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>88</v>
+      </c>
+      <c r="G297" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="2">
+        <v>46166.91666666666</v>
+      </c>
+      <c r="B298">
+        <v>2.138</v>
+      </c>
+      <c r="C298">
+        <v>0.411</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>89</v>
+      </c>
+      <c r="G298" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="2">
+        <v>46166.92708333334</v>
+      </c>
+      <c r="B299">
+        <v>0.194</v>
+      </c>
+      <c r="C299">
+        <v>0.286</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>90</v>
+      </c>
+      <c r="G299" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="2">
+        <v>46166.9375</v>
+      </c>
+      <c r="B300">
+        <v>0.182</v>
+      </c>
+      <c r="C300">
+        <v>1.447</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>91</v>
+      </c>
+      <c r="G300" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="2">
+        <v>46166.94791666666</v>
+      </c>
+      <c r="B301">
+        <v>0.003</v>
+      </c>
+      <c r="C301">
+        <v>2.51</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>92</v>
+      </c>
+      <c r="G301" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="2">
+        <v>46166.95833333334</v>
+      </c>
+      <c r="B302">
+        <v>6.351</v>
+      </c>
+      <c r="C302">
+        <v>0.475</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>93</v>
+      </c>
+      <c r="G302" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="2">
+        <v>46166.96875</v>
+      </c>
+      <c r="B303">
+        <v>0.187</v>
+      </c>
+      <c r="C303">
+        <v>0.51</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>94</v>
+      </c>
+      <c r="G303" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="2">
+        <v>46166.97916666666</v>
+      </c>
+      <c r="B304">
+        <v>0.599</v>
+      </c>
+      <c r="C304">
+        <v>0.343</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>95</v>
+      </c>
+      <c r="G304" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="2">
+        <v>46166.98958333334</v>
+      </c>
+      <c r="B305">
+        <v>0.476</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>96</v>
+      </c>
+      <c r="G305" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B306">
+        <v>8.308999999999999</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
+      <c r="F306">
+        <v>1</v>
+      </c>
+      <c r="G306" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B307">
+        <v>8.308999999999999</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>1</v>
+      </c>
+      <c r="G307" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B308">
+        <v>12.973</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+      <c r="F308">
+        <v>2</v>
+      </c>
+      <c r="G308" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B309">
+        <v>12.973</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>2</v>
+      </c>
+      <c r="G309" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B310">
+        <v>10.17</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+      <c r="F310">
+        <v>3</v>
+      </c>
+      <c r="G310" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B311">
+        <v>10.17</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>3</v>
+      </c>
+      <c r="G311" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B312">
+        <v>2.064</v>
+      </c>
+      <c r="C312">
+        <v>0.022</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>4</v>
+      </c>
+      <c r="G312" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B313">
+        <v>2.064</v>
+      </c>
+      <c r="C313">
+        <v>0.022</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>4</v>
+      </c>
+      <c r="G313" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B314">
+        <v>26.543</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>5</v>
+      </c>
+      <c r="G314" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B315">
+        <v>26.543</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
+      <c r="F315">
+        <v>5</v>
+      </c>
+      <c r="G315" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B316">
+        <v>22.384</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>6</v>
+      </c>
+      <c r="G316" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B317">
+        <v>22.384</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>6</v>
+      </c>
+      <c r="G317" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B318">
+        <v>24.633</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>7</v>
+      </c>
+      <c r="G318" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B319">
+        <v>24.633</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>7</v>
+      </c>
+      <c r="G319" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B320">
+        <v>19.187</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>8</v>
+      </c>
+      <c r="G320" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B321">
+        <v>19.187</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>8</v>
+      </c>
+      <c r="G321" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="2">
+        <v>46167.08333333334</v>
+      </c>
+      <c r="B322">
+        <v>5.547</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>9</v>
+      </c>
+      <c r="G322" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="2">
+        <v>46167.09375</v>
+      </c>
+      <c r="B323">
+        <v>0.39</v>
+      </c>
+      <c r="C323">
+        <v>0.057</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>10</v>
+      </c>
+      <c r="G323" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="2">
+        <v>46167.10416666666</v>
+      </c>
+      <c r="B324">
+        <v>0.02</v>
+      </c>
+      <c r="C324">
+        <v>0.244</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>11</v>
+      </c>
+      <c r="G324" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" s="2">
+        <v>46167.11458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0.323</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>12</v>
+      </c>
+      <c r="G325" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" s="2">
+        <v>46167.125</v>
+      </c>
+      <c r="B326">
+        <v>0.038</v>
+      </c>
+      <c r="C326">
+        <v>0.135</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>13</v>
+      </c>
+      <c r="G326" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" s="2">
+        <v>46167.13541666666</v>
+      </c>
+      <c r="B327">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="C327">
+        <v>11.935</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>14</v>
+      </c>
+      <c r="G327" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" s="2">
+        <v>46167.14583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>23.624</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>15</v>
+      </c>
+      <c r="G328" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" s="2">
+        <v>46167.15625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>6.668</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>16</v>
+      </c>
+      <c r="G329" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" s="2">
+        <v>46167.16666666666</v>
+      </c>
+      <c r="B330">
+        <v>0.229</v>
+      </c>
+      <c r="C330">
+        <v>0.051</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>17</v>
+      </c>
+      <c r="G330" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" s="2">
+        <v>46167.17708333334</v>
+      </c>
+      <c r="B331">
+        <v>0.138</v>
+      </c>
+      <c r="C331">
+        <v>0.022</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>18</v>
+      </c>
+      <c r="G331" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="2">
+        <v>46167.1875</v>
+      </c>
+      <c r="B332">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C332">
+        <v>0.122</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>19</v>
+      </c>
+      <c r="G332" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" s="2">
+        <v>46167.19791666666</v>
+      </c>
+      <c r="B333">
+        <v>0.315</v>
+      </c>
+      <c r="C333">
+        <v>0.206</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>20</v>
+      </c>
+      <c r="G333" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" s="2">
+        <v>46167.20833333334</v>
+      </c>
+      <c r="B334">
+        <v>0.05</v>
+      </c>
+      <c r="C334">
+        <v>9.083</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>21</v>
+      </c>
+      <c r="G334" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" s="2">
+        <v>46167.21875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>17.002</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>22</v>
+      </c>
+      <c r="G335" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="2">
+        <v>46167.22916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>28.015</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>23</v>
+      </c>
+      <c r="G336" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="2">
+        <v>46167.23958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>19.651</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>24</v>
+      </c>
+      <c r="G337" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" s="2">
+        <v>46167.25</v>
+      </c>
+      <c r="B338">
+        <v>0.023</v>
+      </c>
+      <c r="C338">
+        <v>8.307</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>25</v>
+      </c>
+      <c r="G338" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="2">
+        <v>46167.26041666666</v>
+      </c>
+      <c r="B339">
+        <v>0.005</v>
+      </c>
+      <c r="C339">
+        <v>0.459</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>26</v>
+      </c>
+      <c r="G339" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="2">
+        <v>46167.27083333334</v>
+      </c>
+      <c r="B340">
+        <v>0.097</v>
+      </c>
+      <c r="C340">
+        <v>11.562</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>27</v>
+      </c>
+      <c r="G340" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="2">
+        <v>46167.28125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>36.197</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>28</v>
+      </c>
+      <c r="G341" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" s="2">
+        <v>46167.29166666666</v>
+      </c>
+      <c r="B342">
+        <v>0.013</v>
+      </c>
+      <c r="C342">
+        <v>7.198</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>29</v>
+      </c>
+      <c r="G342" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" s="2">
+        <v>46167.30208333334</v>
+      </c>
+      <c r="B343">
+        <v>0.278</v>
+      </c>
+      <c r="C343">
+        <v>0.8</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>50</v>
+      </c>
+      <c r="F343">
+        <v>30</v>
+      </c>
+      <c r="G343" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" s="2">
+        <v>46167.3125</v>
+      </c>
+      <c r="B344">
+        <v>4.029</v>
+      </c>
+      <c r="C344">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>50</v>
+      </c>
+      <c r="F344">
+        <v>31</v>
+      </c>
+      <c r="G344" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" s="2">
+        <v>46167.32291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>9.936999999999999</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>50</v>
+      </c>
+      <c r="F345">
+        <v>32</v>
+      </c>
+      <c r="G345" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" s="2">
+        <v>46167.33333333334</v>
+      </c>
+      <c r="B346">
+        <v>15.223</v>
+      </c>
+      <c r="C346">
+        <v>2.724</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>50</v>
+      </c>
+      <c r="F346">
+        <v>33</v>
+      </c>
+      <c r="G346" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" s="2">
+        <v>46167.34375</v>
+      </c>
+      <c r="B347">
+        <v>6.218</v>
+      </c>
+      <c r="C347">
+        <v>0.002</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>50</v>
+      </c>
+      <c r="F347">
+        <v>34</v>
+      </c>
+      <c r="G347" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" s="2">
+        <v>46167.35416666666</v>
+      </c>
+      <c r="B348">
+        <v>1.241</v>
+      </c>
+      <c r="C348">
+        <v>0.825</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>50</v>
+      </c>
+      <c r="F348">
+        <v>35</v>
+      </c>
+      <c r="G348" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" s="2">
+        <v>46167.36458333334</v>
+      </c>
+      <c r="B349">
+        <v>5.031</v>
+      </c>
+      <c r="C349">
+        <v>0.755</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>50</v>
+      </c>
+      <c r="F349">
+        <v>36</v>
+      </c>
+      <c r="G349" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" s="2">
+        <v>46167.375</v>
+      </c>
+      <c r="B350">
+        <v>0.029</v>
+      </c>
+      <c r="C350">
+        <v>0.844</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>50</v>
+      </c>
+      <c r="F350">
+        <v>37</v>
+      </c>
+      <c r="G350" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" s="2">
+        <v>46167.38541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>20.221</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>0</v>
+      </c>
+      <c r="F351">
+        <v>38</v>
+      </c>
+      <c r="G351" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" s="2">
+        <v>46167.39583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>19.07</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>0</v>
+      </c>
+      <c r="F352">
+        <v>39</v>
+      </c>
+      <c r="G352" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" s="2">
+        <v>46167.40625</v>
+      </c>
+      <c r="B353">
+        <v>0.986</v>
+      </c>
+      <c r="C353">
+        <v>3.291</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>37.5</v>
+      </c>
+      <c r="F353">
+        <v>40</v>
+      </c>
+      <c r="G353" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" s="2">
+        <v>46167.41666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>6.866</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>37.5</v>
+      </c>
+      <c r="F354">
+        <v>41</v>
+      </c>
+      <c r="G354" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" s="2">
+        <v>46167.42708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>3.434</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>37.5</v>
+      </c>
+      <c r="F355">
+        <v>42</v>
+      </c>
+      <c r="G355" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" s="2">
+        <v>46167.4375</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>25.446</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
+      <c r="F356">
+        <v>43</v>
+      </c>
+      <c r="G356" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" s="2">
+        <v>46167.44791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>41.503</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>0</v>
+      </c>
+      <c r="F357">
+        <v>44</v>
+      </c>
+      <c r="G357" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" s="2">
+        <v>46167.45833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>50</v>
+      </c>
+      <c r="F358">
+        <v>45</v>
+      </c>
+      <c r="G358" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" s="2">
+        <v>46167.46875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>50</v>
+      </c>
+      <c r="F359">
+        <v>46</v>
+      </c>
+      <c r="G359" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" s="2">
+        <v>46167.47916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
+      <c r="F360">
+        <v>47</v>
+      </c>
+      <c r="G360" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" s="2">
+        <v>46167.48958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
+      <c r="F361">
+        <v>48</v>
+      </c>
+      <c r="G361" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" s="2">
+        <v>46167.5</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+      <c r="F362">
+        <v>49</v>
+      </c>
+      <c r="G362" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" s="2">
+        <v>46167.51041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
+      <c r="F363">
+        <v>50</v>
+      </c>
+      <c r="G363" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" s="2">
+        <v>46167.52083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+      <c r="F364">
+        <v>51</v>
+      </c>
+      <c r="G364" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" s="2">
+        <v>46167.53125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+      <c r="F365">
+        <v>52</v>
+      </c>
+      <c r="G365" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" s="2">
+        <v>46167.54166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+      <c r="F366">
+        <v>53</v>
+      </c>
+      <c r="G366" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="2">
+        <v>46167.55208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>0</v>
+      </c>
+      <c r="F367">
+        <v>54</v>
+      </c>
+      <c r="G367" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" s="2">
+        <v>46167.5625</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>0</v>
+      </c>
+      <c r="F368">
+        <v>55</v>
+      </c>
+      <c r="G368" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" s="2">
+        <v>46167.57291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>0</v>
+      </c>
+      <c r="F369">
+        <v>56</v>
+      </c>
+      <c r="G369" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" s="2">
+        <v>46167.58333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
+      <c r="F370">
+        <v>57</v>
+      </c>
+      <c r="G370" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" s="2">
+        <v>46167.59375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
+      <c r="F371">
+        <v>58</v>
+      </c>
+      <c r="G371" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" s="2">
+        <v>46167.60416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
+      <c r="F372">
+        <v>59</v>
+      </c>
+      <c r="G372" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" s="2">
+        <v>46167.61458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>60</v>
+      </c>
+      <c r="G373" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" s="2">
+        <v>46167.625</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>61</v>
+      </c>
+      <c r="G374" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" s="2">
+        <v>46167.63541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>62</v>
+      </c>
+      <c r="G375" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" s="2">
+        <v>46167.64583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+      <c r="F376">
+        <v>63</v>
+      </c>
+      <c r="G376" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" s="2">
+        <v>46167.65625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+      <c r="F377">
+        <v>64</v>
+      </c>
+      <c r="G377" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" s="2">
+        <v>46167.66666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>65</v>
+      </c>
+      <c r="G378" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" s="2">
+        <v>46167.67708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+      <c r="F379">
+        <v>66</v>
+      </c>
+      <c r="G379" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" s="2">
+        <v>46167.6875</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+      <c r="F380">
+        <v>67</v>
+      </c>
+      <c r="G380" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" s="2">
+        <v>46167.69791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
+      <c r="F381">
+        <v>68</v>
+      </c>
+      <c r="G381" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" s="2">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>0</v>
+      </c>
+      <c r="F382">
+        <v>69</v>
+      </c>
+      <c r="G382" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" s="2">
+        <v>46167.71875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
+      <c r="F383">
+        <v>70</v>
+      </c>
+      <c r="G383" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" s="2">
+        <v>46167.72916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>0</v>
+      </c>
+      <c r="F384">
+        <v>71</v>
+      </c>
+      <c r="G384" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" s="2">
+        <v>46167.73958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
+      <c r="F385">
+        <v>72</v>
+      </c>
+      <c r="G385" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7">
+      <c r="A386" s="2">
+        <v>46167.75</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+      <c r="E386">
+        <v>0</v>
+      </c>
+      <c r="F386">
+        <v>73</v>
+      </c>
+      <c r="G386" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" s="2">
+        <v>46167.76041666666</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+      <c r="E387">
+        <v>0</v>
+      </c>
+      <c r="F387">
+        <v>74</v>
+      </c>
+      <c r="G387" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" s="2">
+        <v>46167.77083333334</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>0</v>
+      </c>
+      <c r="E388">
+        <v>0</v>
+      </c>
+      <c r="F388">
+        <v>75</v>
+      </c>
+      <c r="G388" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" s="2">
+        <v>46167.78125</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>0</v>
+      </c>
+      <c r="E389">
+        <v>0</v>
+      </c>
+      <c r="F389">
+        <v>76</v>
+      </c>
+      <c r="G389" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" s="2">
+        <v>46167.79166666666</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>0</v>
+      </c>
+      <c r="E390">
+        <v>0</v>
+      </c>
+      <c r="F390">
+        <v>77</v>
+      </c>
+      <c r="G390" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" s="2">
+        <v>46167.80208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>0</v>
+      </c>
+      <c r="E391">
+        <v>0</v>
+      </c>
+      <c r="F391">
+        <v>78</v>
+      </c>
+      <c r="G391" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" s="2">
+        <v>46167.8125</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>0</v>
+      </c>
+      <c r="E392">
+        <v>0</v>
+      </c>
+      <c r="F392">
+        <v>79</v>
+      </c>
+      <c r="G392" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" s="2">
+        <v>46167.82291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+      <c r="E393">
+        <v>0</v>
+      </c>
+      <c r="F393">
+        <v>80</v>
+      </c>
+      <c r="G393" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="A394" s="2">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>0</v>
+      </c>
+      <c r="E394">
+        <v>0</v>
+      </c>
+      <c r="F394">
+        <v>81</v>
+      </c>
+      <c r="G394" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" s="2">
+        <v>46167.84375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="E395">
+        <v>0</v>
+      </c>
+      <c r="F395">
+        <v>82</v>
+      </c>
+      <c r="G395" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="A396" s="2">
+        <v>46167.85416666666</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+      <c r="E396">
+        <v>0</v>
+      </c>
+      <c r="F396">
+        <v>83</v>
+      </c>
+      <c r="G396" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
+      <c r="A397" s="2">
+        <v>46167.86458333334</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+      <c r="E397">
+        <v>0</v>
+      </c>
+      <c r="F397">
+        <v>84</v>
+      </c>
+      <c r="G397" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
+      <c r="A398" s="2">
+        <v>46167.875</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>0</v>
+      </c>
+      <c r="E398">
+        <v>0</v>
+      </c>
+      <c r="F398">
+        <v>85</v>
+      </c>
+      <c r="G398" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
+      <c r="A399" s="2">
+        <v>46167.88541666666</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+      <c r="E399">
+        <v>0</v>
+      </c>
+      <c r="F399">
+        <v>86</v>
+      </c>
+      <c r="G399" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
+      <c r="A400" s="2">
+        <v>46167.89583333334</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+      <c r="E400">
+        <v>0</v>
+      </c>
+      <c r="F400">
+        <v>87</v>
+      </c>
+      <c r="G400" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401" s="2">
+        <v>46167.90625</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>0</v>
+      </c>
+      <c r="E401">
+        <v>0</v>
+      </c>
+      <c r="F401">
+        <v>88</v>
+      </c>
+      <c r="G401" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" s="2">
+        <v>46167.91666666666</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+      <c r="E402">
+        <v>0</v>
+      </c>
+      <c r="F402">
+        <v>89</v>
+      </c>
+      <c r="G402" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
+      <c r="A403" s="2">
+        <v>46167.92708333334</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+      <c r="E403">
+        <v>0</v>
+      </c>
+      <c r="F403">
+        <v>90</v>
+      </c>
+      <c r="G403" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
+      <c r="A404" s="2">
+        <v>46167.9375</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+      <c r="E404">
+        <v>0</v>
+      </c>
+      <c r="F404">
+        <v>91</v>
+      </c>
+      <c r="G404" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7">
+      <c r="A405" s="2">
+        <v>46167.94791666666</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+      <c r="E405">
+        <v>0</v>
+      </c>
+      <c r="F405">
+        <v>92</v>
+      </c>
+      <c r="G405" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406" s="2">
+        <v>46167.95833333334</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+      <c r="E406">
+        <v>0</v>
+      </c>
+      <c r="F406">
+        <v>93</v>
+      </c>
+      <c r="G406" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
+      <c r="A407" s="2">
+        <v>46167.96875</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>0</v>
+      </c>
+      <c r="E407">
+        <v>0</v>
+      </c>
+      <c r="F407">
+        <v>94</v>
+      </c>
+      <c r="G407" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
+      <c r="A408" s="2">
+        <v>46167.97916666666</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+      <c r="E408">
+        <v>0</v>
+      </c>
+      <c r="F408">
+        <v>95</v>
+      </c>
+      <c r="G408" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
+      <c r="A409" s="2">
+        <v>46167.98958333334</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>0</v>
+      </c>
+      <c r="E409">
+        <v>0</v>
+      </c>
+      <c r="F409">
+        <v>96</v>
+      </c>
+      <c r="G409" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.05.20261</t>
-  </si>
-  <si>
-    <t>25.05.20262</t>
-  </si>
-  <si>
-    <t>25.05.20263</t>
-  </si>
-  <si>
-    <t>25.05.20264</t>
-  </si>
-  <si>
-    <t>25.05.20265</t>
-  </si>
-  <si>
-    <t>25.05.20266</t>
-  </si>
-  <si>
-    <t>25.05.20267</t>
-  </si>
-  <si>
-    <t>25.05.20268</t>
-  </si>
-  <si>
-    <t>25.05.20269</t>
-  </si>
-  <si>
-    <t>25.05.202610</t>
-  </si>
-  <si>
-    <t>25.05.202611</t>
-  </si>
-  <si>
-    <t>25.05.202612</t>
-  </si>
-  <si>
-    <t>25.05.202613</t>
-  </si>
-  <si>
-    <t>25.05.202614</t>
-  </si>
-  <si>
-    <t>25.05.202615</t>
-  </si>
-  <si>
-    <t>25.05.202616</t>
-  </si>
-  <si>
-    <t>25.05.202617</t>
-  </si>
-  <si>
-    <t>25.05.202618</t>
-  </si>
-  <si>
-    <t>25.05.202619</t>
-  </si>
-  <si>
-    <t>25.05.202620</t>
-  </si>
-  <si>
-    <t>25.05.202621</t>
-  </si>
-  <si>
-    <t>25.05.202622</t>
-  </si>
-  <si>
-    <t>25.05.202623</t>
-  </si>
-  <si>
-    <t>25.05.202624</t>
-  </si>
-  <si>
-    <t>25.05.202625</t>
-  </si>
-  <si>
-    <t>25.05.202626</t>
-  </si>
-  <si>
-    <t>25.05.202627</t>
-  </si>
-  <si>
-    <t>25.05.202628</t>
-  </si>
-  <si>
-    <t>25.05.202629</t>
-  </si>
-  <si>
-    <t>25.05.202630</t>
-  </si>
-  <si>
-    <t>25.05.202631</t>
-  </si>
-  <si>
-    <t>25.05.202632</t>
-  </si>
-  <si>
-    <t>25.05.202633</t>
-  </si>
-  <si>
-    <t>25.05.202634</t>
-  </si>
-  <si>
-    <t>25.05.202635</t>
-  </si>
-  <si>
-    <t>25.05.202636</t>
-  </si>
-  <si>
-    <t>25.05.202637</t>
-  </si>
-  <si>
-    <t>25.05.202638</t>
-  </si>
-  <si>
-    <t>25.05.202639</t>
-  </si>
-  <si>
-    <t>25.05.202640</t>
-  </si>
-  <si>
-    <t>25.05.202641</t>
-  </si>
-  <si>
-    <t>25.05.202642</t>
-  </si>
-  <si>
-    <t>25.05.202643</t>
-  </si>
-  <si>
-    <t>25.05.202644</t>
-  </si>
-  <si>
-    <t>25.05.202645</t>
-  </si>
-  <si>
-    <t>25.05.202646</t>
-  </si>
-  <si>
-    <t>25.05.202647</t>
-  </si>
-  <si>
-    <t>25.05.202648</t>
-  </si>
-  <si>
-    <t>25.05.202649</t>
-  </si>
-  <si>
-    <t>25.05.202650</t>
-  </si>
-  <si>
-    <t>25.05.202651</t>
-  </si>
-  <si>
-    <t>25.05.202652</t>
-  </si>
-  <si>
-    <t>25.05.202653</t>
-  </si>
-  <si>
-    <t>25.05.202654</t>
-  </si>
-  <si>
-    <t>25.05.202655</t>
-  </si>
-  <si>
-    <t>25.05.202656</t>
-  </si>
-  <si>
-    <t>25.05.202657</t>
-  </si>
-  <si>
-    <t>25.05.202658</t>
-  </si>
-  <si>
-    <t>25.05.202659</t>
-  </si>
-  <si>
-    <t>25.05.202660</t>
-  </si>
-  <si>
-    <t>25.05.202661</t>
-  </si>
-  <si>
-    <t>25.05.202662</t>
-  </si>
-  <si>
-    <t>25.05.202663</t>
-  </si>
-  <si>
-    <t>25.05.202664</t>
-  </si>
-  <si>
-    <t>25.05.202665</t>
-  </si>
-  <si>
-    <t>25.05.202666</t>
-  </si>
-  <si>
-    <t>25.05.202667</t>
-  </si>
-  <si>
-    <t>25.05.202668</t>
-  </si>
-  <si>
-    <t>25.05.202669</t>
-  </si>
-  <si>
-    <t>25.05.202670</t>
-  </si>
-  <si>
-    <t>25.05.202671</t>
-  </si>
-  <si>
-    <t>25.05.202672</t>
-  </si>
-  <si>
-    <t>25.05.202673</t>
-  </si>
-  <si>
-    <t>25.05.202674</t>
-  </si>
-  <si>
-    <t>25.05.202675</t>
-  </si>
-  <si>
-    <t>25.05.202676</t>
-  </si>
-  <si>
-    <t>25.05.202677</t>
-  </si>
-  <si>
-    <t>25.05.202678</t>
-  </si>
-  <si>
-    <t>25.05.202679</t>
-  </si>
-  <si>
-    <t>25.05.202680</t>
-  </si>
-  <si>
-    <t>25.05.202681</t>
-  </si>
-  <si>
-    <t>25.05.202682</t>
-  </si>
-  <si>
-    <t>25.05.202683</t>
-  </si>
-  <si>
-    <t>25.05.202684</t>
-  </si>
-  <si>
-    <t>25.05.202685</t>
-  </si>
-  <si>
-    <t>25.05.202686</t>
-  </si>
-  <si>
-    <t>25.05.202687</t>
-  </si>
-  <si>
-    <t>25.05.202688</t>
-  </si>
-  <si>
-    <t>25.05.202689</t>
-  </si>
-  <si>
-    <t>25.05.202690</t>
-  </si>
-  <si>
-    <t>25.05.202691</t>
-  </si>
-  <si>
-    <t>25.05.202692</t>
-  </si>
-  <si>
-    <t>25.05.202693</t>
-  </si>
-  <si>
-    <t>25.05.202694</t>
-  </si>
-  <si>
-    <t>25.05.202695</t>
-  </si>
-  <si>
-    <t>25.05.202696</t>
-  </si>
-  <si>
     <t>26.05.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>26.05.202696</t>
+  </si>
+  <si>
+    <t>27.05.20261</t>
+  </si>
+  <si>
+    <t>27.05.20262</t>
+  </si>
+  <si>
+    <t>27.05.20263</t>
+  </si>
+  <si>
+    <t>27.05.20264</t>
+  </si>
+  <si>
+    <t>27.05.20265</t>
+  </si>
+  <si>
+    <t>27.05.20266</t>
+  </si>
+  <si>
+    <t>27.05.20267</t>
+  </si>
+  <si>
+    <t>27.05.20268</t>
+  </si>
+  <si>
+    <t>27.05.20269</t>
+  </si>
+  <si>
+    <t>27.05.202610</t>
+  </si>
+  <si>
+    <t>27.05.202611</t>
+  </si>
+  <si>
+    <t>27.05.202612</t>
+  </si>
+  <si>
+    <t>27.05.202613</t>
+  </si>
+  <si>
+    <t>27.05.202614</t>
+  </si>
+  <si>
+    <t>27.05.202615</t>
+  </si>
+  <si>
+    <t>27.05.202616</t>
+  </si>
+  <si>
+    <t>27.05.202617</t>
+  </si>
+  <si>
+    <t>27.05.202618</t>
+  </si>
+  <si>
+    <t>27.05.202619</t>
+  </si>
+  <si>
+    <t>27.05.202620</t>
+  </si>
+  <si>
+    <t>27.05.202621</t>
+  </si>
+  <si>
+    <t>27.05.202622</t>
+  </si>
+  <si>
+    <t>27.05.202623</t>
+  </si>
+  <si>
+    <t>27.05.202624</t>
+  </si>
+  <si>
+    <t>27.05.202625</t>
+  </si>
+  <si>
+    <t>27.05.202626</t>
+  </si>
+  <si>
+    <t>27.05.202627</t>
+  </si>
+  <si>
+    <t>27.05.202628</t>
+  </si>
+  <si>
+    <t>27.05.202629</t>
+  </si>
+  <si>
+    <t>27.05.202630</t>
+  </si>
+  <si>
+    <t>27.05.202631</t>
+  </si>
+  <si>
+    <t>27.05.202632</t>
+  </si>
+  <si>
+    <t>27.05.202633</t>
+  </si>
+  <si>
+    <t>27.05.202634</t>
+  </si>
+  <si>
+    <t>27.05.202635</t>
+  </si>
+  <si>
+    <t>27.05.202636</t>
+  </si>
+  <si>
+    <t>27.05.202637</t>
+  </si>
+  <si>
+    <t>27.05.202638</t>
+  </si>
+  <si>
+    <t>27.05.202639</t>
+  </si>
+  <si>
+    <t>27.05.202640</t>
+  </si>
+  <si>
+    <t>27.05.202641</t>
+  </si>
+  <si>
+    <t>27.05.202642</t>
+  </si>
+  <si>
+    <t>27.05.202643</t>
+  </si>
+  <si>
+    <t>27.05.202644</t>
+  </si>
+  <si>
+    <t>27.05.202645</t>
+  </si>
+  <si>
+    <t>27.05.202646</t>
+  </si>
+  <si>
+    <t>27.05.202647</t>
+  </si>
+  <si>
+    <t>27.05.202648</t>
+  </si>
+  <si>
+    <t>27.05.202649</t>
+  </si>
+  <si>
+    <t>27.05.202650</t>
+  </si>
+  <si>
+    <t>27.05.202651</t>
+  </si>
+  <si>
+    <t>27.05.202652</t>
+  </si>
+  <si>
+    <t>27.05.202653</t>
+  </si>
+  <si>
+    <t>27.05.202654</t>
+  </si>
+  <si>
+    <t>27.05.202655</t>
+  </si>
+  <si>
+    <t>27.05.202656</t>
+  </si>
+  <si>
+    <t>27.05.202657</t>
+  </si>
+  <si>
+    <t>27.05.202658</t>
+  </si>
+  <si>
+    <t>27.05.202659</t>
+  </si>
+  <si>
+    <t>27.05.202660</t>
+  </si>
+  <si>
+    <t>27.05.202661</t>
+  </si>
+  <si>
+    <t>27.05.202662</t>
+  </si>
+  <si>
+    <t>27.05.202663</t>
+  </si>
+  <si>
+    <t>27.05.202664</t>
+  </si>
+  <si>
+    <t>27.05.202665</t>
+  </si>
+  <si>
+    <t>27.05.202666</t>
+  </si>
+  <si>
+    <t>27.05.202667</t>
+  </si>
+  <si>
+    <t>27.05.202668</t>
+  </si>
+  <si>
+    <t>27.05.202669</t>
+  </si>
+  <si>
+    <t>27.05.202670</t>
+  </si>
+  <si>
+    <t>27.05.202671</t>
+  </si>
+  <si>
+    <t>27.05.202672</t>
+  </si>
+  <si>
+    <t>27.05.202673</t>
+  </si>
+  <si>
+    <t>27.05.202674</t>
+  </si>
+  <si>
+    <t>27.05.202675</t>
+  </si>
+  <si>
+    <t>27.05.202676</t>
+  </si>
+  <si>
+    <t>27.05.202677</t>
+  </si>
+  <si>
+    <t>27.05.202678</t>
+  </si>
+  <si>
+    <t>27.05.202679</t>
+  </si>
+  <si>
+    <t>27.05.202680</t>
+  </si>
+  <si>
+    <t>27.05.202681</t>
+  </si>
+  <si>
+    <t>27.05.202682</t>
+  </si>
+  <si>
+    <t>27.05.202683</t>
+  </si>
+  <si>
+    <t>27.05.202684</t>
+  </si>
+  <si>
+    <t>27.05.202685</t>
+  </si>
+  <si>
+    <t>27.05.202686</t>
+  </si>
+  <si>
+    <t>27.05.202687</t>
+  </si>
+  <si>
+    <t>27.05.202688</t>
+  </si>
+  <si>
+    <t>27.05.202689</t>
+  </si>
+  <si>
+    <t>27.05.202690</t>
+  </si>
+  <si>
+    <t>27.05.202691</t>
+  </si>
+  <si>
+    <t>27.05.202692</t>
+  </si>
+  <si>
+    <t>27.05.202693</t>
+  </si>
+  <si>
+    <t>27.05.202694</t>
+  </si>
+  <si>
+    <t>27.05.202695</t>
+  </si>
+  <si>
+    <t>27.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>8.308999999999999</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6.154</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
-        <v>12.973</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>20.041</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
-        <v>10.17</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>23.548</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>2.064</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.022</v>
+        <v>30.504</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>26.543</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>25.514</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>22.384</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>22.013</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>24.633</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>23.09</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>19.187</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>26.217</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>5.547</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>45.283</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.057</v>
+        <v>62.043</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.244</v>
+        <v>58.433</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,19 +1253,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0.323</v>
+        <v>36.912</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>43.25</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1276,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0.135</v>
+        <v>26.745</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>43.25</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>11.935</v>
+        <v>38.871</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>38.25</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,19 +1322,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>23.624</v>
+        <v>25.483</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>38.25</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1345,19 +1345,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>6.668</v>
+        <v>29.143</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>38.25</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -1368,19 +1368,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.229</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0.051</v>
+        <v>37.733</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1391,19 +1391,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.138</v>
+        <v>2.44</v>
       </c>
       <c r="C19">
-        <v>0.022</v>
+        <v>1.609</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,19 +1414,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>0.07000000000000001</v>
+        <v>4.03</v>
       </c>
       <c r="C20">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
         <v>0.315</v>
       </c>
       <c r="C21">
-        <v>0.206</v>
+        <v>0.03</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.05</v>
+        <v>0.482</v>
       </c>
       <c r="C22">
-        <v>9.083</v>
+        <v>2.197</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,19 +1483,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1.019</v>
       </c>
       <c r="C23">
-        <v>17.002</v>
+        <v>0.034</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C24">
-        <v>28.015</v>
+        <v>7.088</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>19.651</v>
+        <v>17.438</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>0.023</v>
+        <v>0.041</v>
       </c>
       <c r="C26">
-        <v>8.307</v>
+        <v>15.262</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.005</v>
+        <v>1.36</v>
       </c>
       <c r="C27">
-        <v>0.459</v>
+        <v>0.031</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.097</v>
+        <v>2.055</v>
       </c>
       <c r="C28">
-        <v>11.562</v>
+        <v>0.031</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1.108</v>
       </c>
       <c r="C29">
-        <v>36.197</v>
+        <v>0.117</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.013</v>
+        <v>3.12</v>
       </c>
       <c r="C30">
-        <v>7.198</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.278</v>
+        <v>11.232</v>
       </c>
       <c r="C31">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>4.029</v>
+        <v>35.441</v>
       </c>
       <c r="C32">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>25.494</v>
       </c>
       <c r="C33">
-        <v>9.936999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E33">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>15.223</v>
+        <v>9.089</v>
       </c>
       <c r="C34">
-        <v>2.724</v>
+        <v>1.974</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E34">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>6.218</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.002</v>
+        <v>12.789</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E35">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>1.241</v>
+        <v>0.145</v>
       </c>
       <c r="C36">
-        <v>0.825</v>
+        <v>10.619</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="E36">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>5.031</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.755</v>
+        <v>15.81</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="E37">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>0.029</v>
+        <v>8.282</v>
       </c>
       <c r="C38">
-        <v>0.844</v>
+        <v>1.544</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>33.75</v>
       </c>
       <c r="E38">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>5.825</v>
       </c>
       <c r="C39">
-        <v>20.221</v>
+        <v>0.098</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>33.75</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="C40">
-        <v>19.07</v>
+        <v>1.52</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>33.75</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>0.986</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>3.291</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E41">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>6.866</v>
+        <v>12.754</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1.619</v>
       </c>
       <c r="C43">
-        <v>3.434</v>
+        <v>7.492</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,13 +1966,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C44">
-        <v>25.446</v>
+        <v>6.823</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1989,13 +1989,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>41.503</v>
+        <v>19.137</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>10.888</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>3.562</v>
+        <v>41.186</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>3.148</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>20.583</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>14.158</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>18.853</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>12.036</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>16.468</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>61.317</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>3.651</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>68.752</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>21.896</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,16 +2150,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>7.966</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>21.483</v>
       </c>
       <c r="D52">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2173,16 +2173,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>11.432</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>32.555</v>
       </c>
       <c r="D53">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>18.606</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>30.447</v>
       </c>
       <c r="D54">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0.04</v>
+        <v>15.803</v>
       </c>
       <c r="D55">
-        <v>38.75</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2242,16 +2242,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="C56">
-        <v>19.073</v>
+        <v>1.703</v>
       </c>
       <c r="D56">
-        <v>38.75</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2265,16 +2265,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="C57">
-        <v>8.125</v>
+        <v>4.689</v>
       </c>
       <c r="D57">
-        <v>38.75</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2288,16 +2288,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C58">
-        <v>17.161</v>
+        <v>7.101</v>
       </c>
       <c r="D58">
-        <v>38.75</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="C59">
-        <v>13.224</v>
+        <v>0.074</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="C60">
-        <v>14.687</v>
+        <v>0.156</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>3.388</v>
+        <v>0.05</v>
       </c>
       <c r="C61">
-        <v>3.722</v>
+        <v>0.398</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>3.858</v>
+        <v>0.092</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>15.624</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,10 +2403,10 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>14.979</v>
+        <v>10.662</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2426,13 +2426,13 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>7.795</v>
+        <v>2.786</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2449,13 +2449,13 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>8.15</v>
+        <v>7.176</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>12.534</v>
+        <v>1.361</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>7.344</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2495,13 +2495,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>13.099</v>
+        <v>0.134</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>13.392</v>
+        <v>5.119</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2541,13 +2541,13 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>16.331</v>
+        <v>2.863</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2564,13 +2564,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.514</v>
+        <v>0.856</v>
       </c>
       <c r="C70">
-        <v>3.91</v>
+        <v>0.109</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>0.111</v>
+        <v>0.14</v>
       </c>
       <c r="C71">
-        <v>4.967</v>
+        <v>0.32</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="C72">
-        <v>3.798</v>
+        <v>0.165</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.168</v>
+        <v>0.199</v>
       </c>
       <c r="C73">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>0.051</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="C74">
-        <v>18.847</v>
+        <v>3.505</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>11.999</v>
+        <v>28.604</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>63.75</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>2.12</v>
+        <v>0.106</v>
       </c>
       <c r="C76">
-        <v>1.236</v>
+        <v>0.283</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,19 +2725,19 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>22.387</v>
+        <v>0.977</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>27.39</v>
+        <v>1.132</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>61.128</v>
+        <v>0.067</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>28.854</v>
+        <v>0.126</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>4.906</v>
+        <v>0.079</v>
       </c>
       <c r="C81">
-        <v>0.01</v>
+        <v>0.306</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>10.36</v>
+        <v>0.213</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>13.396</v>
+        <v>0.273</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>25.914</v>
+        <v>0.268</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>16.933</v>
+        <v>3.051</v>
       </c>
       <c r="C85">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>43.384</v>
+        <v>26.769</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>30.64</v>
+        <v>45.6</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>37.265</v>
+        <v>71.423</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3001,16 +3001,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>22.608</v>
+        <v>12.59</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1.944</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3024,16 +3024,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
-        <v>17.19</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>12.619</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>12.274</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>7.797</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3070,16 +3070,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>4.918</v>
+        <v>3.341</v>
       </c>
       <c r="C92">
-        <v>0.121</v>
+        <v>1.475</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.195</v>
+        <v>6.903</v>
       </c>
       <c r="C93">
-        <v>3.775</v>
+        <v>2.197</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>2.304</v>
+        <v>9.351000000000001</v>
       </c>
       <c r="C94">
-        <v>1.535</v>
+        <v>0.44</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>3.585</v>
+        <v>3.782</v>
       </c>
       <c r="C95">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>5.644</v>
       </c>
       <c r="C96">
-        <v>10.156</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="C97">
-        <v>28.947</v>
+        <v>3.27</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C98">
-        <v>6.154</v>
+        <v>3.992</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C99">
-        <v>6.154</v>
+        <v>3.992</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="C100">
-        <v>20.041</v>
+        <v>0.2</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="C101">
-        <v>20.041</v>
+        <v>0.2</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="C102">
-        <v>23.548</v>
+        <v>0.143</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="C103">
-        <v>23.548</v>
+        <v>0.143</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>1.123</v>
       </c>
       <c r="C104">
-        <v>30.504</v>
+        <v>0.039</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>1.123</v>
       </c>
       <c r="C105">
-        <v>30.504</v>
+        <v>0.039</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>1.477</v>
       </c>
       <c r="C106">
-        <v>25.514</v>
+        <v>0.012</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>1.477</v>
       </c>
       <c r="C107">
-        <v>25.514</v>
+        <v>0.012</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>4.431</v>
       </c>
       <c r="C108">
-        <v>22.013</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>4.431</v>
       </c>
       <c r="C109">
-        <v>22.013</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>8.159000000000001</v>
       </c>
       <c r="C110">
-        <v>23.09</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>8.159000000000001</v>
       </c>
       <c r="C111">
-        <v>23.09</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>5.258</v>
       </c>
       <c r="C112">
-        <v>26.217</v>
+        <v>0.021</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>5.258</v>
       </c>
       <c r="C113">
-        <v>26.217</v>
+        <v>0.021</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1.952</v>
       </c>
       <c r="C114">
-        <v>45.283</v>
+        <v>0.008</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="C115">
-        <v>62.043</v>
+        <v>0.018</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="C116">
-        <v>58.433</v>
+        <v>0.01</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,19 +3645,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>2.861</v>
       </c>
       <c r="C117">
-        <v>36.912</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>43.25</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>12</v>
@@ -3668,19 +3668,19 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>4.413</v>
       </c>
       <c r="C118">
-        <v>26.745</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>43.25</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>13</v>
@@ -3691,19 +3691,19 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>9.721</v>
       </c>
       <c r="C119">
-        <v>38.871</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>14</v>
@@ -3714,19 +3714,19 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>12.341</v>
       </c>
       <c r="C120">
-        <v>25.483</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
       </c>
       <c r="E120">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F120">
         <v>15</v>
@@ -3737,19 +3737,19 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>9.252000000000001</v>
       </c>
       <c r="C121">
-        <v>29.143</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>16</v>
@@ -3760,19 +3760,19 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="C122">
-        <v>37.733</v>
+        <v>0.019</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F122">
         <v>17</v>
@@ -3783,19 +3783,19 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B123">
-        <v>2.44</v>
+        <v>1.751</v>
       </c>
       <c r="C123">
-        <v>1.609</v>
+        <v>0.045</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F123">
         <v>18</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B124">
-        <v>4.03</v>
+        <v>8.167</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F124">
         <v>19</v>
@@ -3829,19 +3829,19 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.315</v>
+        <v>7.519</v>
       </c>
       <c r="C125">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F125">
         <v>20</v>
@@ -3852,19 +3852,19 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.482</v>
+        <v>0.646</v>
       </c>
       <c r="C126">
-        <v>2.197</v>
+        <v>0.054</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>21</v>
@@ -3875,19 +3875,19 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B127">
-        <v>1.019</v>
+        <v>0.595</v>
       </c>
       <c r="C127">
-        <v>0.034</v>
+        <v>0.057</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F127">
         <v>22</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B128">
-        <v>0.01</v>
+        <v>6.196</v>
       </c>
       <c r="C128">
-        <v>7.088</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>7.613</v>
       </c>
       <c r="C129">
-        <v>17.438</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B130">
-        <v>0.041</v>
+        <v>3.434</v>
       </c>
       <c r="C130">
-        <v>15.262</v>
+        <v>0.518</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B131">
-        <v>1.36</v>
+        <v>6.868</v>
       </c>
       <c r="C131">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>26</v>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B132">
-        <v>2.055</v>
+        <v>6.349</v>
       </c>
       <c r="C132">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>27</v>
@@ -4013,19 +4013,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B133">
-        <v>1.108</v>
+        <v>2.306</v>
       </c>
       <c r="C133">
-        <v>0.117</v>
+        <v>0.514</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>28</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B134">
-        <v>3.12</v>
+        <v>11.008</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B135">
-        <v>11.232</v>
+        <v>1.49</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>2.644</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B136">
-        <v>35.441</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>15.431</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,16 +4105,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B137">
-        <v>25.494</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>0.034</v>
+        <v>13.243</v>
       </c>
       <c r="D137">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4128,16 +4128,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B138">
-        <v>9.089</v>
+        <v>0.065</v>
       </c>
       <c r="C138">
-        <v>1.974</v>
+        <v>5.215</v>
       </c>
       <c r="D138">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4151,16 +4151,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>3.749</v>
       </c>
       <c r="C139">
-        <v>12.789</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4174,16 +4174,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B140">
-        <v>0.145</v>
+        <v>0.765</v>
       </c>
       <c r="C140">
-        <v>10.619</v>
+        <v>4.333</v>
       </c>
       <c r="D140">
-        <v>56.25</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4197,16 +4197,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>15.81</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>57.5</v>
+        <v>0</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4220,16 +4220,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B142">
-        <v>8.282</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>1.544</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>33.75</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>33.75</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>26.05.20261</t>
-  </si>
-  <si>
-    <t>26.05.20262</t>
-  </si>
-  <si>
-    <t>26.05.20263</t>
-  </si>
-  <si>
-    <t>26.05.20264</t>
-  </si>
-  <si>
-    <t>26.05.20265</t>
-  </si>
-  <si>
-    <t>26.05.20266</t>
-  </si>
-  <si>
-    <t>26.05.20267</t>
-  </si>
-  <si>
-    <t>26.05.20268</t>
-  </si>
-  <si>
-    <t>26.05.20269</t>
-  </si>
-  <si>
-    <t>26.05.202610</t>
-  </si>
-  <si>
-    <t>26.05.202611</t>
-  </si>
-  <si>
-    <t>26.05.202612</t>
-  </si>
-  <si>
-    <t>26.05.202613</t>
-  </si>
-  <si>
-    <t>26.05.202614</t>
-  </si>
-  <si>
-    <t>26.05.202615</t>
-  </si>
-  <si>
-    <t>26.05.202616</t>
-  </si>
-  <si>
-    <t>26.05.202617</t>
-  </si>
-  <si>
-    <t>26.05.202618</t>
-  </si>
-  <si>
-    <t>26.05.202619</t>
-  </si>
-  <si>
-    <t>26.05.202620</t>
-  </si>
-  <si>
-    <t>26.05.202621</t>
-  </si>
-  <si>
-    <t>26.05.202622</t>
-  </si>
-  <si>
-    <t>26.05.202623</t>
-  </si>
-  <si>
-    <t>26.05.202624</t>
-  </si>
-  <si>
-    <t>26.05.202625</t>
-  </si>
-  <si>
-    <t>26.05.202626</t>
-  </si>
-  <si>
-    <t>26.05.202627</t>
-  </si>
-  <si>
-    <t>26.05.202628</t>
-  </si>
-  <si>
-    <t>26.05.202629</t>
-  </si>
-  <si>
-    <t>26.05.202630</t>
-  </si>
-  <si>
-    <t>26.05.202631</t>
-  </si>
-  <si>
-    <t>26.05.202632</t>
-  </si>
-  <si>
-    <t>26.05.202633</t>
-  </si>
-  <si>
-    <t>26.05.202634</t>
-  </si>
-  <si>
-    <t>26.05.202635</t>
-  </si>
-  <si>
-    <t>26.05.202636</t>
-  </si>
-  <si>
-    <t>26.05.202637</t>
-  </si>
-  <si>
-    <t>26.05.202638</t>
-  </si>
-  <si>
-    <t>26.05.202639</t>
-  </si>
-  <si>
-    <t>26.05.202640</t>
-  </si>
-  <si>
-    <t>26.05.202641</t>
-  </si>
-  <si>
-    <t>26.05.202642</t>
-  </si>
-  <si>
-    <t>26.05.202643</t>
-  </si>
-  <si>
-    <t>26.05.202644</t>
-  </si>
-  <si>
-    <t>26.05.202645</t>
-  </si>
-  <si>
-    <t>26.05.202646</t>
-  </si>
-  <si>
-    <t>26.05.202647</t>
-  </si>
-  <si>
-    <t>26.05.202648</t>
-  </si>
-  <si>
-    <t>26.05.202649</t>
-  </si>
-  <si>
-    <t>26.05.202650</t>
-  </si>
-  <si>
-    <t>26.05.202651</t>
-  </si>
-  <si>
-    <t>26.05.202652</t>
-  </si>
-  <si>
-    <t>26.05.202653</t>
-  </si>
-  <si>
-    <t>26.05.202654</t>
-  </si>
-  <si>
-    <t>26.05.202655</t>
-  </si>
-  <si>
-    <t>26.05.202656</t>
-  </si>
-  <si>
-    <t>26.05.202657</t>
-  </si>
-  <si>
-    <t>26.05.202658</t>
-  </si>
-  <si>
-    <t>26.05.202659</t>
-  </si>
-  <si>
-    <t>26.05.202660</t>
-  </si>
-  <si>
-    <t>26.05.202661</t>
-  </si>
-  <si>
-    <t>26.05.202662</t>
-  </si>
-  <si>
-    <t>26.05.202663</t>
-  </si>
-  <si>
-    <t>26.05.202664</t>
-  </si>
-  <si>
-    <t>26.05.202665</t>
-  </si>
-  <si>
-    <t>26.05.202666</t>
-  </si>
-  <si>
-    <t>26.05.202667</t>
-  </si>
-  <si>
-    <t>26.05.202668</t>
-  </si>
-  <si>
-    <t>26.05.202669</t>
-  </si>
-  <si>
-    <t>26.05.202670</t>
-  </si>
-  <si>
-    <t>26.05.202671</t>
-  </si>
-  <si>
-    <t>26.05.202672</t>
-  </si>
-  <si>
-    <t>26.05.202673</t>
-  </si>
-  <si>
-    <t>26.05.202674</t>
-  </si>
-  <si>
-    <t>26.05.202675</t>
-  </si>
-  <si>
-    <t>26.05.202676</t>
-  </si>
-  <si>
-    <t>26.05.202677</t>
-  </si>
-  <si>
-    <t>26.05.202678</t>
-  </si>
-  <si>
-    <t>26.05.202679</t>
-  </si>
-  <si>
-    <t>26.05.202680</t>
-  </si>
-  <si>
-    <t>26.05.202681</t>
-  </si>
-  <si>
-    <t>26.05.202682</t>
-  </si>
-  <si>
-    <t>26.05.202683</t>
-  </si>
-  <si>
-    <t>26.05.202684</t>
-  </si>
-  <si>
-    <t>26.05.202685</t>
-  </si>
-  <si>
-    <t>26.05.202686</t>
-  </si>
-  <si>
-    <t>26.05.202687</t>
-  </si>
-  <si>
-    <t>26.05.202688</t>
-  </si>
-  <si>
-    <t>26.05.202689</t>
-  </si>
-  <si>
-    <t>26.05.202690</t>
-  </si>
-  <si>
-    <t>26.05.202691</t>
-  </si>
-  <si>
-    <t>26.05.202692</t>
-  </si>
-  <si>
-    <t>26.05.202693</t>
-  </si>
-  <si>
-    <t>26.05.202694</t>
-  </si>
-  <si>
-    <t>26.05.202695</t>
-  </si>
-  <si>
-    <t>26.05.202696</t>
-  </si>
-  <si>
     <t>27.05.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>27.05.202696</t>
+  </si>
+  <si>
+    <t>28.05.20261</t>
+  </si>
+  <si>
+    <t>28.05.20262</t>
+  </si>
+  <si>
+    <t>28.05.20263</t>
+  </si>
+  <si>
+    <t>28.05.20264</t>
+  </si>
+  <si>
+    <t>28.05.20265</t>
+  </si>
+  <si>
+    <t>28.05.20266</t>
+  </si>
+  <si>
+    <t>28.05.20267</t>
+  </si>
+  <si>
+    <t>28.05.20268</t>
+  </si>
+  <si>
+    <t>28.05.20269</t>
+  </si>
+  <si>
+    <t>28.05.202610</t>
+  </si>
+  <si>
+    <t>28.05.202611</t>
+  </si>
+  <si>
+    <t>28.05.202612</t>
+  </si>
+  <si>
+    <t>28.05.202613</t>
+  </si>
+  <si>
+    <t>28.05.202614</t>
+  </si>
+  <si>
+    <t>28.05.202615</t>
+  </si>
+  <si>
+    <t>28.05.202616</t>
+  </si>
+  <si>
+    <t>28.05.202617</t>
+  </si>
+  <si>
+    <t>28.05.202618</t>
+  </si>
+  <si>
+    <t>28.05.202619</t>
+  </si>
+  <si>
+    <t>28.05.202620</t>
+  </si>
+  <si>
+    <t>28.05.202621</t>
+  </si>
+  <si>
+    <t>28.05.202622</t>
+  </si>
+  <si>
+    <t>28.05.202623</t>
+  </si>
+  <si>
+    <t>28.05.202624</t>
+  </si>
+  <si>
+    <t>28.05.202625</t>
+  </si>
+  <si>
+    <t>28.05.202626</t>
+  </si>
+  <si>
+    <t>28.05.202627</t>
+  </si>
+  <si>
+    <t>28.05.202628</t>
+  </si>
+  <si>
+    <t>28.05.202629</t>
+  </si>
+  <si>
+    <t>28.05.202630</t>
+  </si>
+  <si>
+    <t>28.05.202631</t>
+  </si>
+  <si>
+    <t>28.05.202632</t>
+  </si>
+  <si>
+    <t>28.05.202633</t>
+  </si>
+  <si>
+    <t>28.05.202634</t>
+  </si>
+  <si>
+    <t>28.05.202635</t>
+  </si>
+  <si>
+    <t>28.05.202636</t>
+  </si>
+  <si>
+    <t>28.05.202637</t>
+  </si>
+  <si>
+    <t>28.05.202638</t>
+  </si>
+  <si>
+    <t>28.05.202639</t>
+  </si>
+  <si>
+    <t>28.05.202640</t>
+  </si>
+  <si>
+    <t>28.05.202641</t>
+  </si>
+  <si>
+    <t>28.05.202642</t>
+  </si>
+  <si>
+    <t>28.05.202643</t>
+  </si>
+  <si>
+    <t>28.05.202644</t>
+  </si>
+  <si>
+    <t>28.05.202645</t>
+  </si>
+  <si>
+    <t>28.05.202646</t>
+  </si>
+  <si>
+    <t>28.05.202647</t>
+  </si>
+  <si>
+    <t>28.05.202648</t>
+  </si>
+  <si>
+    <t>28.05.202649</t>
+  </si>
+  <si>
+    <t>28.05.202650</t>
+  </si>
+  <si>
+    <t>28.05.202651</t>
+  </si>
+  <si>
+    <t>28.05.202652</t>
+  </si>
+  <si>
+    <t>28.05.202653</t>
+  </si>
+  <si>
+    <t>28.05.202654</t>
+  </si>
+  <si>
+    <t>28.05.202655</t>
+  </si>
+  <si>
+    <t>28.05.202656</t>
+  </si>
+  <si>
+    <t>28.05.202657</t>
+  </si>
+  <si>
+    <t>28.05.202658</t>
+  </si>
+  <si>
+    <t>28.05.202659</t>
+  </si>
+  <si>
+    <t>28.05.202660</t>
+  </si>
+  <si>
+    <t>28.05.202661</t>
+  </si>
+  <si>
+    <t>28.05.202662</t>
+  </si>
+  <si>
+    <t>28.05.202663</t>
+  </si>
+  <si>
+    <t>28.05.202664</t>
+  </si>
+  <si>
+    <t>28.05.202665</t>
+  </si>
+  <si>
+    <t>28.05.202666</t>
+  </si>
+  <si>
+    <t>28.05.202667</t>
+  </si>
+  <si>
+    <t>28.05.202668</t>
+  </si>
+  <si>
+    <t>28.05.202669</t>
+  </si>
+  <si>
+    <t>28.05.202670</t>
+  </si>
+  <si>
+    <t>28.05.202671</t>
+  </si>
+  <si>
+    <t>28.05.202672</t>
+  </si>
+  <si>
+    <t>28.05.202673</t>
+  </si>
+  <si>
+    <t>28.05.202674</t>
+  </si>
+  <si>
+    <t>28.05.202675</t>
+  </si>
+  <si>
+    <t>28.05.202676</t>
+  </si>
+  <si>
+    <t>28.05.202677</t>
+  </si>
+  <si>
+    <t>28.05.202678</t>
+  </si>
+  <si>
+    <t>28.05.202679</t>
+  </si>
+  <si>
+    <t>28.05.202680</t>
+  </si>
+  <si>
+    <t>28.05.202681</t>
+  </si>
+  <si>
+    <t>28.05.202682</t>
+  </si>
+  <si>
+    <t>28.05.202683</t>
+  </si>
+  <si>
+    <t>28.05.202684</t>
+  </si>
+  <si>
+    <t>28.05.202685</t>
+  </si>
+  <si>
+    <t>28.05.202686</t>
+  </si>
+  <si>
+    <t>28.05.202687</t>
+  </si>
+  <si>
+    <t>28.05.202688</t>
+  </si>
+  <si>
+    <t>28.05.202689</t>
+  </si>
+  <si>
+    <t>28.05.202690</t>
+  </si>
+  <si>
+    <t>28.05.202691</t>
+  </si>
+  <si>
+    <t>28.05.202692</t>
+  </si>
+  <si>
+    <t>28.05.202693</t>
+  </si>
+  <si>
+    <t>28.05.202694</t>
+  </si>
+  <si>
+    <t>28.05.202695</t>
+  </si>
+  <si>
+    <t>28.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C2">
-        <v>6.154</v>
+        <v>3.992</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="C3">
-        <v>20.041</v>
+        <v>0.2</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="C4">
-        <v>23.548</v>
+        <v>0.143</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1.123</v>
       </c>
       <c r="C5">
-        <v>30.504</v>
+        <v>0.039</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1.477</v>
       </c>
       <c r="C6">
-        <v>25.514</v>
+        <v>0.012</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>4.431</v>
       </c>
       <c r="C7">
-        <v>22.013</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>8.159000000000001</v>
       </c>
       <c r="C8">
-        <v>23.09</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>5.258</v>
       </c>
       <c r="C9">
-        <v>26.217</v>
+        <v>0.021</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1.952</v>
       </c>
       <c r="C10">
-        <v>45.283</v>
+        <v>0.008</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="C11">
-        <v>62.043</v>
+        <v>0.018</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="C12">
-        <v>58.433</v>
+        <v>0.01</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,19 +1253,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2.861</v>
       </c>
       <c r="C13">
-        <v>36.912</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>43.25</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1276,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>4.413</v>
       </c>
       <c r="C14">
-        <v>26.745</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>43.25</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>9.721</v>
       </c>
       <c r="C15">
-        <v>38.871</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,19 +1322,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>12.341</v>
       </c>
       <c r="C16">
-        <v>25.483</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1345,19 +1345,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>9.252000000000001</v>
       </c>
       <c r="C17">
-        <v>29.143</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -1368,19 +1368,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="C18">
-        <v>37.733</v>
+        <v>0.019</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>35.75</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1391,19 +1391,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>2.44</v>
+        <v>1.751</v>
       </c>
       <c r="C19">
-        <v>1.609</v>
+        <v>0.045</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>4.03</v>
+        <v>8.167</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.315</v>
+        <v>7.519</v>
       </c>
       <c r="C21">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.482</v>
+        <v>0.646</v>
       </c>
       <c r="C22">
-        <v>2.197</v>
+        <v>0.054</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,19 +1483,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>1.019</v>
+        <v>0.595</v>
       </c>
       <c r="C23">
-        <v>0.034</v>
+        <v>0.057</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.01</v>
+        <v>6.196</v>
       </c>
       <c r="C24">
-        <v>7.088</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>7.613</v>
       </c>
       <c r="C25">
-        <v>17.438</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>0.041</v>
+        <v>3.434</v>
       </c>
       <c r="C26">
-        <v>15.262</v>
+        <v>0.518</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>1.36</v>
+        <v>6.868</v>
       </c>
       <c r="C27">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>2.055</v>
+        <v>6.349</v>
       </c>
       <c r="C28">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>1.108</v>
+        <v>2.306</v>
       </c>
       <c r="C29">
-        <v>0.117</v>
+        <v>0.514</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>3.12</v>
+        <v>11.008</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,13 +1667,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>11.232</v>
+        <v>1.49</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2.644</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>35.441</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>15.431</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>25.494</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.034</v>
+        <v>13.243</v>
       </c>
       <c r="D33">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>9.089</v>
+        <v>0.065</v>
       </c>
       <c r="C34">
-        <v>1.974</v>
+        <v>5.215</v>
       </c>
       <c r="D34">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>3.749</v>
       </c>
       <c r="C35">
-        <v>12.789</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.145</v>
+        <v>0.765</v>
       </c>
       <c r="C36">
-        <v>10.619</v>
+        <v>4.333</v>
       </c>
       <c r="D36">
-        <v>56.25</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +1805,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.398</v>
       </c>
       <c r="C37">
-        <v>15.81</v>
+        <v>0.92</v>
       </c>
       <c r="D37">
-        <v>57.5</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>8.282</v>
+        <v>16.676</v>
       </c>
       <c r="C38">
-        <v>1.544</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>33.75</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>5.825</v>
+        <v>22.265</v>
       </c>
       <c r="C39">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>33.75</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.488</v>
+        <v>9.138999999999999</v>
       </c>
       <c r="C40">
-        <v>1.52</v>
+        <v>0.073</v>
       </c>
       <c r="D40">
-        <v>33.75</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>7.007</v>
       </c>
       <c r="C41">
-        <v>8.585000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="D41">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1920,13 +1920,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>15.416</v>
       </c>
       <c r="C42">
-        <v>12.754</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1943,13 +1943,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>1.619</v>
+        <v>18.017</v>
       </c>
       <c r="C43">
-        <v>7.492</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>0.003</v>
+        <v>0.063</v>
       </c>
       <c r="C44">
-        <v>6.823</v>
+        <v>9.917999999999999</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1989,16 +1989,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>19.137</v>
+        <v>8.726000000000001</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2012,16 +2012,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>41.186</v>
+        <v>10.752</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2035,16 +2035,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>20.583</v>
+        <v>18.716</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>9.882</v>
       </c>
       <c r="C48">
-        <v>18.853</v>
+        <v>1.472</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>15.568</v>
       </c>
       <c r="C49">
-        <v>16.468</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2104,13 +2104,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>0.008999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="C50">
-        <v>3.651</v>
+        <v>20.949</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>21.896</v>
+        <v>24.297</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2150,13 +2150,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C52">
-        <v>21.483</v>
+        <v>5.766</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>32.555</v>
+        <v>6.118</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,13 +2196,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="C54">
-        <v>30.447</v>
+        <v>1.909</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2219,13 +2219,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1.422</v>
       </c>
       <c r="C55">
-        <v>15.803</v>
+        <v>0.067</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>0.6820000000000001</v>
+        <v>7.982</v>
       </c>
       <c r="C56">
-        <v>1.703</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.015</v>
+        <v>3.361</v>
       </c>
       <c r="C57">
-        <v>4.689</v>
+        <v>0.01</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.008999999999999999</v>
+        <v>1.751</v>
       </c>
       <c r="C58">
-        <v>7.101</v>
+        <v>0.8</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>0.28</v>
+        <v>0.239</v>
       </c>
       <c r="C59">
-        <v>0.074</v>
+        <v>0.217</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.61</v>
+        <v>4.492</v>
       </c>
       <c r="C60">
-        <v>0.156</v>
+        <v>0.587</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.05</v>
+        <v>3.446</v>
       </c>
       <c r="C61">
-        <v>0.398</v>
+        <v>0.582</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>15.624</v>
+        <v>6.814</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>10.662</v>
+        <v>0.05</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>9.433</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>2.786</v>
+        <v>0.021</v>
       </c>
       <c r="C64">
-        <v>0.005</v>
+        <v>3.217</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>7.176</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>0.048</v>
+        <v>3.541</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>1.361</v>
+        <v>0.014</v>
       </c>
       <c r="C66">
-        <v>7.344</v>
+        <v>24.103</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.134</v>
+        <v>0.411</v>
       </c>
       <c r="C67">
-        <v>1.17</v>
+        <v>0.438</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>5.119</v>
+        <v>1.746</v>
       </c>
       <c r="C68">
-        <v>0.062</v>
+        <v>5.894</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>2.863</v>
+        <v>14.213</v>
       </c>
       <c r="C69">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,13 +2564,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.856</v>
+        <v>1.255</v>
       </c>
       <c r="C70">
-        <v>0.109</v>
+        <v>0.024</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>0.14</v>
+        <v>10.261</v>
       </c>
       <c r="C71">
-        <v>0.32</v>
+        <v>0.313</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.177</v>
+        <v>27.033</v>
       </c>
       <c r="C72">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.199</v>
+        <v>55.457</v>
       </c>
       <c r="C73">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>0.07199999999999999</v>
+        <v>13.925</v>
       </c>
       <c r="C74">
-        <v>3.505</v>
+        <v>0.002</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>17.771</v>
       </c>
       <c r="C75">
-        <v>28.604</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.106</v>
+        <v>7.604</v>
       </c>
       <c r="C76">
-        <v>0.283</v>
+        <v>0.01</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>0.977</v>
+        <v>6.242</v>
       </c>
       <c r="C77">
-        <v>0.041</v>
+        <v>0.035</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.132</v>
+        <v>0.701</v>
       </c>
       <c r="C78">
-        <v>0.147</v>
+        <v>13.531</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0.25</v>
+        <v>11.837</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>0.126</v>
+        <v>0.305</v>
       </c>
       <c r="C80">
-        <v>0.143</v>
+        <v>1.551</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.079</v>
+        <v>0.279</v>
       </c>
       <c r="C81">
-        <v>0.306</v>
+        <v>0.286</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.213</v>
+        <v>0.133</v>
       </c>
       <c r="C82">
-        <v>0.106</v>
+        <v>1.126</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>0.273</v>
+        <v>0.304</v>
       </c>
       <c r="C83">
-        <v>0.025</v>
+        <v>0.131</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.268</v>
+        <v>0.294</v>
       </c>
       <c r="C84">
-        <v>0.032</v>
+        <v>0.291</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>3.051</v>
+        <v>1.042</v>
       </c>
       <c r="C85">
-        <v>0.013</v>
+        <v>0.169</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>26.769</v>
+        <v>1.609</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
-        <v>45.6</v>
+        <v>6.968</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>71.423</v>
+        <v>13.673</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3001,16 +3001,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>12.59</v>
+        <v>0.146</v>
       </c>
       <c r="C89">
-        <v>1.944</v>
+        <v>6.153</v>
       </c>
       <c r="D89">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3024,16 +3024,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>12.619</v>
+        <v>13.002</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>7.797</v>
+        <v>15.683</v>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3070,16 +3070,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
-        <v>3.341</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1.475</v>
+        <v>16.878</v>
       </c>
       <c r="D92">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3093,19 +3093,19 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
-        <v>6.903</v>
+        <v>2.622</v>
       </c>
       <c r="C93">
-        <v>2.197</v>
+        <v>7.727</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -3116,19 +3116,19 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>9.351000000000001</v>
+        <v>24.184</v>
       </c>
       <c r="C94">
-        <v>0.44</v>
+        <v>0.773</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F94">
         <v>93</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
-        <v>3.782</v>
+        <v>16.321</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F95">
         <v>94</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
-        <v>5.644</v>
+        <v>0.386</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>6.807</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>3.27</v>
+        <v>8.161</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>0.011</v>
+        <v>3.76</v>
       </c>
       <c r="C98">
-        <v>3.992</v>
+        <v>0.265</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B99">
-        <v>0.011</v>
+        <v>3.76</v>
       </c>
       <c r="C99">
-        <v>3.992</v>
+        <v>0.265</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B100">
-        <v>0.068</v>
+        <v>12.691</v>
       </c>
       <c r="C100">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B101">
-        <v>0.068</v>
+        <v>12.691</v>
       </c>
       <c r="C101">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B102">
-        <v>0.109</v>
+        <v>15.658</v>
       </c>
       <c r="C102">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B103">
-        <v>0.109</v>
+        <v>15.658</v>
       </c>
       <c r="C103">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B104">
-        <v>1.123</v>
+        <v>30.684</v>
       </c>
       <c r="C104">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B105">
-        <v>1.123</v>
+        <v>30.684</v>
       </c>
       <c r="C105">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B106">
-        <v>1.477</v>
+        <v>44.843</v>
       </c>
       <c r="C106">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B107">
-        <v>1.477</v>
+        <v>44.843</v>
       </c>
       <c r="C107">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B108">
-        <v>4.431</v>
+        <v>31.54</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B109">
-        <v>4.431</v>
+        <v>31.54</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -3484,16 +3484,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B110">
-        <v>8.159000000000001</v>
+        <v>13.831</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3507,16 +3507,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B111">
-        <v>8.159000000000001</v>
+        <v>13.831</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3530,16 +3530,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B112">
-        <v>5.258</v>
+        <v>54.44</v>
       </c>
       <c r="C112">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B113">
-        <v>5.258</v>
+        <v>54.44</v>
       </c>
       <c r="C113">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B114">
-        <v>1.952</v>
+        <v>39.174</v>
       </c>
       <c r="C114">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,16 +3599,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B115">
-        <v>0.962</v>
+        <v>66.373</v>
       </c>
       <c r="C115">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B116">
-        <v>1.69</v>
+        <v>102.889</v>
       </c>
       <c r="C116">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +3645,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B117">
-        <v>2.861</v>
+        <v>88.761</v>
       </c>
       <c r="C117">
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +3668,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B118">
-        <v>4.413</v>
+        <v>3.215</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +3691,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B119">
-        <v>9.721</v>
+        <v>0.2</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B120">
-        <v>12.341</v>
+        <v>0.122</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B121">
-        <v>9.252000000000001</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>11.874</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B122">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>0.019</v>
+        <v>27.455</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B123">
-        <v>1.751</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0.045</v>
+        <v>18.439</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B124">
-        <v>8.167</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>32.624</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>74.75</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B125">
-        <v>7.519</v>
+        <v>0.724</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>2.356</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.646</v>
+        <v>0.306</v>
       </c>
       <c r="C126">
-        <v>0.054</v>
+        <v>5.855</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>28.25</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +3875,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B127">
-        <v>0.595</v>
+        <v>5.66</v>
       </c>
       <c r="C127">
-        <v>0.057</v>
+        <v>0.045</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B128">
-        <v>6.196</v>
+        <v>27.444</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,16 +3921,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B129">
-        <v>7.613</v>
+        <v>27.66</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3944,16 +3944,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B130">
-        <v>3.434</v>
+        <v>41.436</v>
       </c>
       <c r="C130">
-        <v>0.518</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -3967,16 +3967,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B131">
-        <v>6.868</v>
+        <v>11.284</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -3990,16 +3990,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B132">
-        <v>6.349</v>
+        <v>0.018</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4013,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B133">
-        <v>2.306</v>
+        <v>0.122</v>
       </c>
       <c r="C133">
-        <v>0.514</v>
+        <v>3.637</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,16 +4036,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B134">
-        <v>11.008</v>
+        <v>0.153</v>
       </c>
       <c r="C134">
-        <v>0.025</v>
+        <v>0.697</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>64.75</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B135">
-        <v>1.49</v>
+        <v>0.146</v>
       </c>
       <c r="C135">
-        <v>2.644</v>
+        <v>20.206</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>72.25</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>15.431</v>
+        <v>15.289</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,13 +4105,13 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>13.243</v>
+        <v>11.954</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B138">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>5.215</v>
+        <v>37.576</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B139">
-        <v>3.749</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>16.481</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,19 +4174,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B140">
-        <v>0.765</v>
+        <v>1.907</v>
       </c>
       <c r="C140">
-        <v>4.333</v>
+        <v>3.17</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="F140">
         <v>35</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="F141">
         <v>36</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>27.05.20261</t>
-  </si>
-  <si>
-    <t>27.05.20262</t>
-  </si>
-  <si>
-    <t>27.05.20263</t>
-  </si>
-  <si>
-    <t>27.05.20264</t>
-  </si>
-  <si>
-    <t>27.05.20265</t>
-  </si>
-  <si>
-    <t>27.05.20266</t>
-  </si>
-  <si>
-    <t>27.05.20267</t>
-  </si>
-  <si>
-    <t>27.05.20268</t>
-  </si>
-  <si>
-    <t>27.05.20269</t>
-  </si>
-  <si>
-    <t>27.05.202610</t>
-  </si>
-  <si>
-    <t>27.05.202611</t>
-  </si>
-  <si>
-    <t>27.05.202612</t>
-  </si>
-  <si>
-    <t>27.05.202613</t>
-  </si>
-  <si>
-    <t>27.05.202614</t>
-  </si>
-  <si>
-    <t>27.05.202615</t>
-  </si>
-  <si>
-    <t>27.05.202616</t>
-  </si>
-  <si>
-    <t>27.05.202617</t>
-  </si>
-  <si>
-    <t>27.05.202618</t>
-  </si>
-  <si>
-    <t>27.05.202619</t>
-  </si>
-  <si>
-    <t>27.05.202620</t>
-  </si>
-  <si>
-    <t>27.05.202621</t>
-  </si>
-  <si>
-    <t>27.05.202622</t>
-  </si>
-  <si>
-    <t>27.05.202623</t>
-  </si>
-  <si>
-    <t>27.05.202624</t>
-  </si>
-  <si>
-    <t>27.05.202625</t>
-  </si>
-  <si>
-    <t>27.05.202626</t>
-  </si>
-  <si>
-    <t>27.05.202627</t>
-  </si>
-  <si>
-    <t>27.05.202628</t>
-  </si>
-  <si>
-    <t>27.05.202629</t>
-  </si>
-  <si>
-    <t>27.05.202630</t>
-  </si>
-  <si>
-    <t>27.05.202631</t>
-  </si>
-  <si>
-    <t>27.05.202632</t>
-  </si>
-  <si>
-    <t>27.05.202633</t>
-  </si>
-  <si>
-    <t>27.05.202634</t>
-  </si>
-  <si>
-    <t>27.05.202635</t>
-  </si>
-  <si>
-    <t>27.05.202636</t>
-  </si>
-  <si>
-    <t>27.05.202637</t>
-  </si>
-  <si>
-    <t>27.05.202638</t>
-  </si>
-  <si>
-    <t>27.05.202639</t>
-  </si>
-  <si>
-    <t>27.05.202640</t>
-  </si>
-  <si>
-    <t>27.05.202641</t>
-  </si>
-  <si>
-    <t>27.05.202642</t>
-  </si>
-  <si>
-    <t>27.05.202643</t>
-  </si>
-  <si>
-    <t>27.05.202644</t>
-  </si>
-  <si>
-    <t>27.05.202645</t>
-  </si>
-  <si>
-    <t>27.05.202646</t>
-  </si>
-  <si>
-    <t>27.05.202647</t>
-  </si>
-  <si>
-    <t>27.05.202648</t>
-  </si>
-  <si>
-    <t>27.05.202649</t>
-  </si>
-  <si>
-    <t>27.05.202650</t>
-  </si>
-  <si>
-    <t>27.05.202651</t>
-  </si>
-  <si>
-    <t>27.05.202652</t>
-  </si>
-  <si>
-    <t>27.05.202653</t>
-  </si>
-  <si>
-    <t>27.05.202654</t>
-  </si>
-  <si>
-    <t>27.05.202655</t>
-  </si>
-  <si>
-    <t>27.05.202656</t>
-  </si>
-  <si>
-    <t>27.05.202657</t>
-  </si>
-  <si>
-    <t>27.05.202658</t>
-  </si>
-  <si>
-    <t>27.05.202659</t>
-  </si>
-  <si>
-    <t>27.05.202660</t>
-  </si>
-  <si>
-    <t>27.05.202661</t>
-  </si>
-  <si>
-    <t>27.05.202662</t>
-  </si>
-  <si>
-    <t>27.05.202663</t>
-  </si>
-  <si>
-    <t>27.05.202664</t>
-  </si>
-  <si>
-    <t>27.05.202665</t>
-  </si>
-  <si>
-    <t>27.05.202666</t>
-  </si>
-  <si>
-    <t>27.05.202667</t>
-  </si>
-  <si>
-    <t>27.05.202668</t>
-  </si>
-  <si>
-    <t>27.05.202669</t>
-  </si>
-  <si>
-    <t>27.05.202670</t>
-  </si>
-  <si>
-    <t>27.05.202671</t>
-  </si>
-  <si>
-    <t>27.05.202672</t>
-  </si>
-  <si>
-    <t>27.05.202673</t>
-  </si>
-  <si>
-    <t>27.05.202674</t>
-  </si>
-  <si>
-    <t>27.05.202675</t>
-  </si>
-  <si>
-    <t>27.05.202676</t>
-  </si>
-  <si>
-    <t>27.05.202677</t>
-  </si>
-  <si>
-    <t>27.05.202678</t>
-  </si>
-  <si>
-    <t>27.05.202679</t>
-  </si>
-  <si>
-    <t>27.05.202680</t>
-  </si>
-  <si>
-    <t>27.05.202681</t>
-  </si>
-  <si>
-    <t>27.05.202682</t>
-  </si>
-  <si>
-    <t>27.05.202683</t>
-  </si>
-  <si>
-    <t>27.05.202684</t>
-  </si>
-  <si>
-    <t>27.05.202685</t>
-  </si>
-  <si>
-    <t>27.05.202686</t>
-  </si>
-  <si>
-    <t>27.05.202687</t>
-  </si>
-  <si>
-    <t>27.05.202688</t>
-  </si>
-  <si>
-    <t>27.05.202689</t>
-  </si>
-  <si>
-    <t>27.05.202690</t>
-  </si>
-  <si>
-    <t>27.05.202691</t>
-  </si>
-  <si>
-    <t>27.05.202692</t>
-  </si>
-  <si>
-    <t>27.05.202693</t>
-  </si>
-  <si>
-    <t>27.05.202694</t>
-  </si>
-  <si>
-    <t>27.05.202695</t>
-  </si>
-  <si>
-    <t>27.05.202696</t>
-  </si>
-  <si>
     <t>28.05.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>28.05.202696</t>
+  </si>
+  <si>
+    <t>29.05.20261</t>
+  </si>
+  <si>
+    <t>29.05.20262</t>
+  </si>
+  <si>
+    <t>29.05.20263</t>
+  </si>
+  <si>
+    <t>29.05.20264</t>
+  </si>
+  <si>
+    <t>29.05.20265</t>
+  </si>
+  <si>
+    <t>29.05.20266</t>
+  </si>
+  <si>
+    <t>29.05.20267</t>
+  </si>
+  <si>
+    <t>29.05.20268</t>
+  </si>
+  <si>
+    <t>29.05.20269</t>
+  </si>
+  <si>
+    <t>29.05.202610</t>
+  </si>
+  <si>
+    <t>29.05.202611</t>
+  </si>
+  <si>
+    <t>29.05.202612</t>
+  </si>
+  <si>
+    <t>29.05.202613</t>
+  </si>
+  <si>
+    <t>29.05.202614</t>
+  </si>
+  <si>
+    <t>29.05.202615</t>
+  </si>
+  <si>
+    <t>29.05.202616</t>
+  </si>
+  <si>
+    <t>29.05.202617</t>
+  </si>
+  <si>
+    <t>29.05.202618</t>
+  </si>
+  <si>
+    <t>29.05.202619</t>
+  </si>
+  <si>
+    <t>29.05.202620</t>
+  </si>
+  <si>
+    <t>29.05.202621</t>
+  </si>
+  <si>
+    <t>29.05.202622</t>
+  </si>
+  <si>
+    <t>29.05.202623</t>
+  </si>
+  <si>
+    <t>29.05.202624</t>
+  </si>
+  <si>
+    <t>29.05.202625</t>
+  </si>
+  <si>
+    <t>29.05.202626</t>
+  </si>
+  <si>
+    <t>29.05.202627</t>
+  </si>
+  <si>
+    <t>29.05.202628</t>
+  </si>
+  <si>
+    <t>29.05.202629</t>
+  </si>
+  <si>
+    <t>29.05.202630</t>
+  </si>
+  <si>
+    <t>29.05.202631</t>
+  </si>
+  <si>
+    <t>29.05.202632</t>
+  </si>
+  <si>
+    <t>29.05.202633</t>
+  </si>
+  <si>
+    <t>29.05.202634</t>
+  </si>
+  <si>
+    <t>29.05.202635</t>
+  </si>
+  <si>
+    <t>29.05.202636</t>
+  </si>
+  <si>
+    <t>29.05.202637</t>
+  </si>
+  <si>
+    <t>29.05.202638</t>
+  </si>
+  <si>
+    <t>29.05.202639</t>
+  </si>
+  <si>
+    <t>29.05.202640</t>
+  </si>
+  <si>
+    <t>29.05.202641</t>
+  </si>
+  <si>
+    <t>29.05.202642</t>
+  </si>
+  <si>
+    <t>29.05.202643</t>
+  </si>
+  <si>
+    <t>29.05.202644</t>
+  </si>
+  <si>
+    <t>29.05.202645</t>
+  </si>
+  <si>
+    <t>29.05.202646</t>
+  </si>
+  <si>
+    <t>29.05.202647</t>
+  </si>
+  <si>
+    <t>29.05.202648</t>
+  </si>
+  <si>
+    <t>29.05.202649</t>
+  </si>
+  <si>
+    <t>29.05.202650</t>
+  </si>
+  <si>
+    <t>29.05.202651</t>
+  </si>
+  <si>
+    <t>29.05.202652</t>
+  </si>
+  <si>
+    <t>29.05.202653</t>
+  </si>
+  <si>
+    <t>29.05.202654</t>
+  </si>
+  <si>
+    <t>29.05.202655</t>
+  </si>
+  <si>
+    <t>29.05.202656</t>
+  </si>
+  <si>
+    <t>29.05.202657</t>
+  </si>
+  <si>
+    <t>29.05.202658</t>
+  </si>
+  <si>
+    <t>29.05.202659</t>
+  </si>
+  <si>
+    <t>29.05.202660</t>
+  </si>
+  <si>
+    <t>29.05.202661</t>
+  </si>
+  <si>
+    <t>29.05.202662</t>
+  </si>
+  <si>
+    <t>29.05.202663</t>
+  </si>
+  <si>
+    <t>29.05.202664</t>
+  </si>
+  <si>
+    <t>29.05.202665</t>
+  </si>
+  <si>
+    <t>29.05.202666</t>
+  </si>
+  <si>
+    <t>29.05.202667</t>
+  </si>
+  <si>
+    <t>29.05.202668</t>
+  </si>
+  <si>
+    <t>29.05.202669</t>
+  </si>
+  <si>
+    <t>29.05.202670</t>
+  </si>
+  <si>
+    <t>29.05.202671</t>
+  </si>
+  <si>
+    <t>29.05.202672</t>
+  </si>
+  <si>
+    <t>29.05.202673</t>
+  </si>
+  <si>
+    <t>29.05.202674</t>
+  </si>
+  <si>
+    <t>29.05.202675</t>
+  </si>
+  <si>
+    <t>29.05.202676</t>
+  </si>
+  <si>
+    <t>29.05.202677</t>
+  </si>
+  <si>
+    <t>29.05.202678</t>
+  </si>
+  <si>
+    <t>29.05.202679</t>
+  </si>
+  <si>
+    <t>29.05.202680</t>
+  </si>
+  <si>
+    <t>29.05.202681</t>
+  </si>
+  <si>
+    <t>29.05.202682</t>
+  </si>
+  <si>
+    <t>29.05.202683</t>
+  </si>
+  <si>
+    <t>29.05.202684</t>
+  </si>
+  <si>
+    <t>29.05.202685</t>
+  </si>
+  <si>
+    <t>29.05.202686</t>
+  </si>
+  <si>
+    <t>29.05.202687</t>
+  </si>
+  <si>
+    <t>29.05.202688</t>
+  </si>
+  <si>
+    <t>29.05.202689</t>
+  </si>
+  <si>
+    <t>29.05.202690</t>
+  </si>
+  <si>
+    <t>29.05.202691</t>
+  </si>
+  <si>
+    <t>29.05.202692</t>
+  </si>
+  <si>
+    <t>29.05.202693</t>
+  </si>
+  <si>
+    <t>29.05.202694</t>
+  </si>
+  <si>
+    <t>29.05.202695</t>
+  </si>
+  <si>
+    <t>29.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>0.011</v>
+        <v>3.76</v>
       </c>
       <c r="C2">
-        <v>3.992</v>
+        <v>0.265</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.068</v>
+        <v>12.691</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.109</v>
+        <v>15.658</v>
       </c>
       <c r="C4">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>1.123</v>
+        <v>30.684</v>
       </c>
       <c r="C5">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.477</v>
+        <v>44.843</v>
       </c>
       <c r="C6">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
-        <v>4.431</v>
+        <v>31.54</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1138,16 +1138,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
-        <v>8.159000000000001</v>
+        <v>13.831</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1161,16 +1161,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
-        <v>5.258</v>
+        <v>54.44</v>
       </c>
       <c r="C9">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1184,16 +1184,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.952</v>
+        <v>39.174</v>
       </c>
       <c r="C10">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1207,16 +1207,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
-        <v>0.962</v>
+        <v>66.373</v>
       </c>
       <c r="C11">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1230,16 +1230,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.69</v>
+        <v>102.889</v>
       </c>
       <c r="C12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1253,16 +1253,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.861</v>
+        <v>88.761</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1276,16 +1276,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>4.413</v>
+        <v>3.215</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1299,16 +1299,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
-        <v>9.721</v>
+        <v>0.2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1322,16 +1322,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>12.341</v>
+        <v>0.122</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>9.252000000000001</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>11.874</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1368,16 +1368,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0.019</v>
+        <v>27.455</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1391,16 +1391,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.751</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0.045</v>
+        <v>18.439</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>8.167</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>32.624</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>74.75</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>7.519</v>
+        <v>0.724</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2.356</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1460,16 +1460,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.646</v>
+        <v>0.306</v>
       </c>
       <c r="C22">
-        <v>0.054</v>
+        <v>5.855</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>28.25</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1483,16 +1483,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>0.595</v>
+        <v>5.66</v>
       </c>
       <c r="C23">
-        <v>0.057</v>
+        <v>0.045</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1506,16 +1506,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>6.196</v>
+        <v>27.444</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1529,16 +1529,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>7.613</v>
+        <v>27.66</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1552,16 +1552,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>3.434</v>
+        <v>41.436</v>
       </c>
       <c r="C26">
-        <v>0.518</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1575,16 +1575,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>6.868</v>
+        <v>11.284</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1598,16 +1598,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>6.349</v>
+        <v>0.018</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1621,16 +1621,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>2.306</v>
+        <v>0.122</v>
       </c>
       <c r="C29">
-        <v>0.514</v>
+        <v>3.637</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1644,16 +1644,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>11.008</v>
+        <v>0.153</v>
       </c>
       <c r="C30">
-        <v>0.025</v>
+        <v>0.697</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>64.75</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1667,16 +1667,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>1.49</v>
+        <v>0.146</v>
       </c>
       <c r="C31">
-        <v>2.644</v>
+        <v>20.206</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>72.25</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>15.431</v>
+        <v>15.289</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1713,13 +1713,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>13.243</v>
+        <v>11.954</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>5.215</v>
+        <v>37.576</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1759,13 +1759,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>3.749</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>16.481</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.765</v>
+        <v>1.907</v>
       </c>
       <c r="C36">
-        <v>4.333</v>
+        <v>3.17</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.398</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="C37">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,13 +1828,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>16.676</v>
+        <v>12.315</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1851,13 +1851,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>22.265</v>
+        <v>5.132</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1874,13 +1874,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>9.138999999999999</v>
+        <v>1.342</v>
       </c>
       <c r="C40">
-        <v>0.073</v>
+        <v>0.019</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1897,13 +1897,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>7.007</v>
+        <v>0.001</v>
       </c>
       <c r="C41">
-        <v>0.013</v>
+        <v>10.341</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1920,13 +1920,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>15.416</v>
+        <v>0.957</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>16.099</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1943,13 +1943,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>18.017</v>
+        <v>0.553</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1.968</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>0.063</v>
+        <v>0.98</v>
       </c>
       <c r="C44">
-        <v>9.917999999999999</v>
+        <v>0.403</v>
       </c>
       <c r="D44">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1989,16 +1989,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C45">
-        <v>8.726000000000001</v>
+        <v>5.819</v>
       </c>
       <c r="D45">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2012,16 +2012,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>10.752</v>
+        <v>26.199</v>
       </c>
       <c r="D46">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2035,16 +2035,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>18.716</v>
+        <v>17.728</v>
       </c>
       <c r="D47">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>9.882</v>
+        <v>0.025</v>
       </c>
       <c r="C48">
-        <v>1.472</v>
+        <v>13.816</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>15.568</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>16.177</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2104,13 +2104,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>20.949</v>
+        <v>22.782</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>24.297</v>
+        <v>17.132</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2150,13 +2150,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.007</v>
+        <v>0.135</v>
       </c>
       <c r="C52">
-        <v>5.766</v>
+        <v>0.357</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>0.856</v>
       </c>
       <c r="C53">
-        <v>6.118</v>
+        <v>0.272</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,13 +2196,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.099</v>
+        <v>0.025</v>
       </c>
       <c r="C54">
-        <v>1.909</v>
+        <v>5.227</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2219,13 +2219,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>1.422</v>
+        <v>0.244</v>
       </c>
       <c r="C55">
-        <v>0.067</v>
+        <v>0.626</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>7.982</v>
+        <v>14.435</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>3.361</v>
+        <v>39.613</v>
       </c>
       <c r="C57">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>1.751</v>
+        <v>6.775</v>
       </c>
       <c r="C58">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>0.239</v>
+        <v>11.269</v>
       </c>
       <c r="C59">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>4.492</v>
+        <v>16.692</v>
       </c>
       <c r="C60">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>3.446</v>
+        <v>13.574</v>
       </c>
       <c r="C61">
-        <v>0.582</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1.916</v>
       </c>
       <c r="C62">
-        <v>6.814</v>
+        <v>1.359</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.05</v>
+        <v>5.969</v>
       </c>
       <c r="C63">
-        <v>9.433</v>
+        <v>0.094</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.021</v>
+        <v>25.905</v>
       </c>
       <c r="C64">
-        <v>3.217</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>17.624</v>
       </c>
       <c r="C65">
-        <v>3.541</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.014</v>
+        <v>4.662</v>
       </c>
       <c r="C66">
-        <v>24.103</v>
+        <v>5.218</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.411</v>
+        <v>63.451</v>
       </c>
       <c r="C67">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>1.746</v>
+        <v>33.726</v>
       </c>
       <c r="C68">
-        <v>5.894</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E68">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>14.213</v>
+        <v>4.65</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="E69">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,16 +2564,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>1.255</v>
+        <v>0.007</v>
       </c>
       <c r="C70">
-        <v>0.024</v>
+        <v>29.588</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2587,16 +2587,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>10.261</v>
+        <v>0.059</v>
       </c>
       <c r="C71">
-        <v>0.313</v>
+        <v>0.98</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>27.033</v>
+        <v>0.229</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,16 +2633,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>55.457</v>
+        <v>1.834</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>13.925</v>
+        <v>0.249</v>
       </c>
       <c r="C74">
-        <v>0.002</v>
+        <v>1.137</v>
       </c>
       <c r="D74">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>17.771</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>8.631</v>
       </c>
       <c r="D75">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>7.604</v>
+        <v>0.024</v>
       </c>
       <c r="C76">
-        <v>0.01</v>
+        <v>0.79</v>
       </c>
       <c r="D76">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>6.242</v>
+        <v>0.224</v>
       </c>
       <c r="C77">
-        <v>0.035</v>
+        <v>0.221</v>
       </c>
       <c r="D77">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.701</v>
+        <v>0.059</v>
       </c>
       <c r="C78">
-        <v>13.531</v>
+        <v>2.872</v>
       </c>
       <c r="D78">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C79">
-        <v>11.837</v>
+        <v>1.072</v>
       </c>
       <c r="D79">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>0.305</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C80">
-        <v>1.551</v>
+        <v>0.026</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.279</v>
+        <v>17.221</v>
       </c>
       <c r="C81">
-        <v>0.286</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,19 +2840,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.133</v>
+        <v>46.393</v>
       </c>
       <c r="C82">
-        <v>1.126</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2863,19 +2863,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>0.304</v>
+        <v>36.325</v>
       </c>
       <c r="C83">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.294</v>
+        <v>2.69</v>
       </c>
       <c r="C84">
-        <v>0.291</v>
+        <v>0.164</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.042</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>0.169</v>
+        <v>12.525</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>1.609</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>0.078</v>
+        <v>49.099</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>6.968</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>47.146</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
-        <v>13.673</v>
+        <v>0.232</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>0.146</v>
+        <v>7.974</v>
       </c>
       <c r="C89">
-        <v>6.153</v>
+        <v>3.379</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3024,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>33.453</v>
       </c>
       <c r="C90">
-        <v>13.002</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,19 +3047,19 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>16.247</v>
       </c>
       <c r="C91">
-        <v>15.683</v>
+        <v>0.023</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F91">
         <v>90</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="C92">
-        <v>16.878</v>
+        <v>14.426</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,19 +3093,19 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
-        <v>2.622</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>7.727</v>
+        <v>17.131</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -3116,19 +3116,19 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
-        <v>24.184</v>
+        <v>9.529</v>
       </c>
       <c r="C94">
-        <v>0.773</v>
+        <v>3.039</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>93</v>
@@ -3139,19 +3139,19 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
-        <v>16.321</v>
+        <v>0.96</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1.128</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <v>94</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.386</v>
+        <v>13.996</v>
       </c>
       <c r="C96">
-        <v>6.807</v>
+        <v>0.039</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>31.256</v>
       </c>
       <c r="C97">
-        <v>8.161</v>
+        <v>0.003</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
-        <v>3.76</v>
+        <v>31.546</v>
       </c>
       <c r="C98">
-        <v>0.265</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B99">
-        <v>3.76</v>
+        <v>31.546</v>
       </c>
       <c r="C99">
-        <v>0.265</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B100">
-        <v>12.691</v>
+        <v>43.462</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B101">
-        <v>12.691</v>
+        <v>43.462</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B102">
-        <v>15.658</v>
+        <v>49.64</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B103">
-        <v>15.658</v>
+        <v>49.64</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B104">
-        <v>30.684</v>
+        <v>42.218</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B105">
-        <v>30.684</v>
+        <v>42.218</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B106">
-        <v>44.843</v>
+        <v>15.688</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3415,16 +3415,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B107">
-        <v>44.843</v>
+        <v>15.688</v>
       </c>
       <c r="C107">
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3438,16 +3438,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B108">
-        <v>31.54</v>
+        <v>4.512</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3461,16 +3461,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B109">
-        <v>31.54</v>
+        <v>4.512</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3484,16 +3484,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B110">
-        <v>13.831</v>
+        <v>0.029</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>1.419</v>
       </c>
       <c r="D110">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3507,16 +3507,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B111">
-        <v>13.831</v>
+        <v>0.029</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1.419</v>
       </c>
       <c r="D111">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3530,16 +3530,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B112">
-        <v>54.44</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>29.667</v>
       </c>
       <c r="D112">
-        <v>87.5</v>
+        <v>26</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B113">
-        <v>54.44</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>29.667</v>
       </c>
       <c r="D113">
-        <v>87.5</v>
+        <v>26</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B114">
-        <v>39.174</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>7.923</v>
       </c>
       <c r="D114">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,16 +3599,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B115">
-        <v>66.373</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>19.674</v>
       </c>
       <c r="D115">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B116">
-        <v>102.889</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>15.394</v>
       </c>
       <c r="D116">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +3645,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B117">
-        <v>88.761</v>
+        <v>0.031</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>2.075</v>
       </c>
       <c r="D117">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +3668,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B118">
-        <v>3.215</v>
+        <v>0.078</v>
       </c>
       <c r="C118">
-        <v>0.002</v>
+        <v>3.264</v>
       </c>
       <c r="D118">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +3691,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B119">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>0.371</v>
+        <v>18.533</v>
       </c>
       <c r="D119">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B120">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0.509</v>
+        <v>29.672</v>
       </c>
       <c r="D120">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>11.874</v>
+        <v>11.815</v>
       </c>
       <c r="D121">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="C122">
-        <v>27.455</v>
+        <v>3.923</v>
       </c>
       <c r="D122">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="C123">
-        <v>18.439</v>
+        <v>1.238</v>
       </c>
       <c r="D123">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>32.624</v>
+        <v>7.847</v>
       </c>
       <c r="D124">
-        <v>74.75</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.724</v>
+        <v>0.535</v>
       </c>
       <c r="C125">
-        <v>2.356</v>
+        <v>11.444</v>
       </c>
       <c r="D125">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.306</v>
+        <v>1.458</v>
       </c>
       <c r="C126">
-        <v>5.855</v>
+        <v>0.255</v>
       </c>
       <c r="D126">
-        <v>28.25</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +3875,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B127">
-        <v>5.66</v>
+        <v>0.181</v>
       </c>
       <c r="C127">
-        <v>0.045</v>
+        <v>0.191</v>
       </c>
       <c r="D127">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B128">
-        <v>27.444</v>
+        <v>0.092</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="D128">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,16 +3921,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B129">
-        <v>27.66</v>
+        <v>0.031</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>1.984</v>
       </c>
       <c r="D129">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3944,16 +3944,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B130">
-        <v>41.436</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>13.721</v>
       </c>
       <c r="D130">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -3967,16 +3967,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B131">
-        <v>11.284</v>
+        <v>0.063</v>
       </c>
       <c r="C131">
-        <v>0.229</v>
+        <v>0.209</v>
       </c>
       <c r="D131">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -3990,16 +3990,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.018</v>
+        <v>0.076</v>
       </c>
       <c r="C132">
-        <v>6.29</v>
+        <v>1.031</v>
       </c>
       <c r="D132">
-        <v>71.75</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4013,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B133">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>3.637</v>
+        <v>16.025</v>
       </c>
       <c r="D133">
-        <v>71.75</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,16 +4036,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.153</v>
+        <v>0.03</v>
       </c>
       <c r="C134">
-        <v>0.697</v>
+        <v>3.515</v>
       </c>
       <c r="D134">
-        <v>64.75</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.146</v>
+        <v>0.211</v>
       </c>
       <c r="C135">
-        <v>20.206</v>
+        <v>5.086</v>
       </c>
       <c r="D135">
-        <v>72.25</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>15.289</v>
+        <v>13.192</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,13 +4105,13 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>11.954</v>
+        <v>23.397</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
       <c r="C138">
-        <v>37.576</v>
+        <v>2.953</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C139">
-        <v>16.481</v>
+        <v>11.268</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,19 +4174,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B140">
-        <v>1.907</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>3.17</v>
+        <v>20.062</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>35</v>
@@ -4197,19 +4197,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>28.553</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>36</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.202625</t>
-  </si>
-  <si>
-    <t>03.06.202626</t>
-  </si>
-  <si>
-    <t>03.06.202627</t>
-  </si>
-  <si>
-    <t>03.06.202628</t>
-  </si>
-  <si>
-    <t>03.06.202629</t>
-  </si>
-  <si>
-    <t>03.06.202630</t>
-  </si>
-  <si>
-    <t>03.06.202631</t>
-  </si>
-  <si>
-    <t>03.06.202632</t>
-  </si>
-  <si>
-    <t>03.06.202633</t>
-  </si>
-  <si>
-    <t>03.06.202634</t>
-  </si>
-  <si>
-    <t>03.06.202635</t>
-  </si>
-  <si>
-    <t>03.06.202636</t>
-  </si>
-  <si>
-    <t>03.06.202637</t>
-  </si>
-  <si>
-    <t>03.06.202638</t>
-  </si>
-  <si>
-    <t>03.06.202639</t>
-  </si>
-  <si>
-    <t>03.06.202640</t>
-  </si>
-  <si>
-    <t>03.06.202641</t>
-  </si>
-  <si>
-    <t>03.06.202642</t>
-  </si>
-  <si>
-    <t>03.06.202643</t>
-  </si>
-  <si>
-    <t>03.06.202644</t>
-  </si>
-  <si>
-    <t>03.06.202645</t>
-  </si>
-  <si>
-    <t>03.06.202646</t>
-  </si>
-  <si>
-    <t>03.06.202647</t>
-  </si>
-  <si>
-    <t>03.06.202648</t>
-  </si>
-  <si>
-    <t>03.06.202649</t>
-  </si>
-  <si>
-    <t>03.06.202650</t>
-  </si>
-  <si>
-    <t>03.06.202651</t>
-  </si>
-  <si>
-    <t>03.06.202652</t>
-  </si>
-  <si>
-    <t>03.06.202653</t>
-  </si>
-  <si>
-    <t>03.06.202654</t>
-  </si>
-  <si>
-    <t>03.06.202655</t>
-  </si>
-  <si>
-    <t>03.06.202656</t>
-  </si>
-  <si>
-    <t>03.06.202657</t>
-  </si>
-  <si>
-    <t>03.06.202658</t>
-  </si>
-  <si>
-    <t>03.06.202659</t>
-  </si>
-  <si>
-    <t>03.06.202660</t>
-  </si>
-  <si>
-    <t>03.06.202661</t>
-  </si>
-  <si>
-    <t>03.06.202662</t>
-  </si>
-  <si>
-    <t>03.06.202663</t>
-  </si>
-  <si>
-    <t>03.06.202664</t>
-  </si>
-  <si>
-    <t>03.06.202665</t>
-  </si>
-  <si>
-    <t>03.06.202666</t>
-  </si>
-  <si>
-    <t>03.06.202667</t>
-  </si>
-  <si>
-    <t>03.06.202668</t>
-  </si>
-  <si>
-    <t>03.06.202669</t>
-  </si>
-  <si>
-    <t>03.06.202670</t>
-  </si>
-  <si>
-    <t>03.06.202671</t>
-  </si>
-  <si>
-    <t>03.06.202672</t>
-  </si>
-  <si>
-    <t>03.06.202673</t>
-  </si>
-  <si>
-    <t>03.06.202674</t>
-  </si>
-  <si>
-    <t>03.06.202675</t>
-  </si>
-  <si>
-    <t>03.06.202676</t>
-  </si>
-  <si>
-    <t>03.06.202677</t>
-  </si>
-  <si>
-    <t>03.06.202678</t>
-  </si>
-  <si>
-    <t>03.06.202679</t>
-  </si>
-  <si>
-    <t>03.06.202680</t>
-  </si>
-  <si>
-    <t>03.06.202681</t>
-  </si>
-  <si>
-    <t>03.06.202682</t>
-  </si>
-  <si>
-    <t>03.06.202683</t>
-  </si>
-  <si>
-    <t>03.06.202684</t>
-  </si>
-  <si>
-    <t>03.06.202685</t>
-  </si>
-  <si>
-    <t>03.06.202686</t>
-  </si>
-  <si>
-    <t>03.06.202687</t>
-  </si>
-  <si>
-    <t>03.06.202688</t>
-  </si>
-  <si>
-    <t>03.06.202689</t>
-  </si>
-  <si>
-    <t>03.06.202690</t>
-  </si>
-  <si>
-    <t>03.06.202691</t>
-  </si>
-  <si>
-    <t>03.06.202692</t>
-  </si>
-  <si>
-    <t>03.06.202693</t>
-  </si>
-  <si>
-    <t>03.06.202694</t>
-  </si>
-  <si>
-    <t>03.06.202695</t>
-  </si>
-  <si>
-    <t>03.06.202696</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.202625</t>
-  </si>
-  <si>
-    <t>04.06.202626</t>
-  </si>
-  <si>
-    <t>04.06.202627</t>
-  </si>
-  <si>
-    <t>04.06.202628</t>
-  </si>
-  <si>
-    <t>04.06.202629</t>
-  </si>
-  <si>
-    <t>04.06.202630</t>
-  </si>
-  <si>
-    <t>04.06.202631</t>
-  </si>
-  <si>
-    <t>04.06.202632</t>
-  </si>
-  <si>
-    <t>04.06.202633</t>
-  </si>
-  <si>
-    <t>04.06.202634</t>
-  </si>
-  <si>
-    <t>04.06.202635</t>
-  </si>
-  <si>
-    <t>04.06.202636</t>
-  </si>
-  <si>
-    <t>04.06.202637</t>
-  </si>
-  <si>
-    <t>04.06.202638</t>
-  </si>
-  <si>
-    <t>04.06.202639</t>
-  </si>
-  <si>
-    <t>04.06.202640</t>
-  </si>
-  <si>
-    <t>04.06.202641</t>
-  </si>
-  <si>
-    <t>04.06.202642</t>
-  </si>
-  <si>
-    <t>04.06.202643</t>
-  </si>
-  <si>
-    <t>04.06.202644</t>
-  </si>
-  <si>
-    <t>04.06.202645</t>
-  </si>
-  <si>
-    <t>04.06.202646</t>
-  </si>
-  <si>
-    <t>04.06.202647</t>
-  </si>
-  <si>
-    <t>04.06.202648</t>
-  </si>
-  <si>
-    <t>04.06.202649</t>
-  </si>
-  <si>
-    <t>04.06.202650</t>
-  </si>
-  <si>
-    <t>04.06.202651</t>
-  </si>
-  <si>
-    <t>04.06.202652</t>
-  </si>
-  <si>
-    <t>04.06.202653</t>
-  </si>
-  <si>
-    <t>04.06.202654</t>
-  </si>
-  <si>
-    <t>04.06.202655</t>
-  </si>
-  <si>
-    <t>04.06.202656</t>
-  </si>
-  <si>
-    <t>04.06.202657</t>
-  </si>
-  <si>
-    <t>04.06.202658</t>
-  </si>
-  <si>
-    <t>04.06.202659</t>
-  </si>
-  <si>
-    <t>04.06.202660</t>
-  </si>
-  <si>
-    <t>04.06.202661</t>
-  </si>
-  <si>
-    <t>04.06.202662</t>
-  </si>
-  <si>
-    <t>04.06.202663</t>
-  </si>
-  <si>
-    <t>04.06.202664</t>
-  </si>
-  <si>
-    <t>04.06.202665</t>
-  </si>
-  <si>
-    <t>04.06.202666</t>
-  </si>
-  <si>
-    <t>04.06.202667</t>
-  </si>
-  <si>
-    <t>04.06.202668</t>
-  </si>
-  <si>
-    <t>04.06.202669</t>
-  </si>
-  <si>
-    <t>04.06.202670</t>
-  </si>
-  <si>
-    <t>04.06.202671</t>
-  </si>
-  <si>
-    <t>04.06.202672</t>
-  </si>
-  <si>
-    <t>04.06.202673</t>
-  </si>
-  <si>
-    <t>04.06.202674</t>
-  </si>
-  <si>
-    <t>04.06.202675</t>
-  </si>
-  <si>
-    <t>04.06.202676</t>
-  </si>
-  <si>
-    <t>04.06.202677</t>
-  </si>
-  <si>
-    <t>04.06.202678</t>
-  </si>
-  <si>
-    <t>04.06.202679</t>
-  </si>
-  <si>
-    <t>04.06.202680</t>
-  </si>
-  <si>
-    <t>04.06.202681</t>
-  </si>
-  <si>
-    <t>04.06.202682</t>
-  </si>
-  <si>
-    <t>04.06.202683</t>
-  </si>
-  <si>
-    <t>04.06.202684</t>
-  </si>
-  <si>
-    <t>04.06.202685</t>
-  </si>
-  <si>
-    <t>04.06.202686</t>
-  </si>
-  <si>
-    <t>04.06.202687</t>
-  </si>
-  <si>
-    <t>04.06.202688</t>
-  </si>
-  <si>
-    <t>04.06.202689</t>
-  </si>
-  <si>
-    <t>04.06.202690</t>
-  </si>
-  <si>
-    <t>04.06.202691</t>
-  </si>
-  <si>
-    <t>04.06.202692</t>
-  </si>
-  <si>
-    <t>04.06.202693</t>
-  </si>
-  <si>
-    <t>04.06.202694</t>
-  </si>
-  <si>
-    <t>04.06.202695</t>
-  </si>
-  <si>
-    <t>04.06.202696</t>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
+  </si>
+  <si>
+    <t>11.06.202616</t>
+  </si>
+  <si>
+    <t>11.06.202617</t>
+  </si>
+  <si>
+    <t>11.06.202618</t>
+  </si>
+  <si>
+    <t>11.06.202619</t>
+  </si>
+  <si>
+    <t>11.06.202620</t>
+  </si>
+  <si>
+    <t>11.06.202621</t>
+  </si>
+  <si>
+    <t>11.06.202622</t>
+  </si>
+  <si>
+    <t>11.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.202624</t>
+  </si>
+  <si>
+    <t>11.06.202625</t>
+  </si>
+  <si>
+    <t>11.06.202626</t>
+  </si>
+  <si>
+    <t>11.06.202627</t>
+  </si>
+  <si>
+    <t>11.06.202628</t>
+  </si>
+  <si>
+    <t>11.06.202629</t>
+  </si>
+  <si>
+    <t>11.06.202630</t>
+  </si>
+  <si>
+    <t>11.06.202631</t>
+  </si>
+  <si>
+    <t>11.06.202632</t>
+  </si>
+  <si>
+    <t>11.06.202633</t>
+  </si>
+  <si>
+    <t>11.06.202634</t>
+  </si>
+  <si>
+    <t>11.06.202635</t>
+  </si>
+  <si>
+    <t>11.06.202636</t>
+  </si>
+  <si>
+    <t>11.06.202637</t>
+  </si>
+  <si>
+    <t>11.06.202638</t>
+  </si>
+  <si>
+    <t>11.06.202639</t>
+  </si>
+  <si>
+    <t>11.06.202640</t>
+  </si>
+  <si>
+    <t>11.06.202641</t>
+  </si>
+  <si>
+    <t>11.06.202642</t>
+  </si>
+  <si>
+    <t>11.06.202643</t>
+  </si>
+  <si>
+    <t>11.06.202644</t>
+  </si>
+  <si>
+    <t>11.06.202645</t>
+  </si>
+  <si>
+    <t>11.06.202646</t>
+  </si>
+  <si>
+    <t>11.06.202647</t>
+  </si>
+  <si>
+    <t>11.06.202648</t>
+  </si>
+  <si>
+    <t>11.06.202649</t>
+  </si>
+  <si>
+    <t>11.06.202650</t>
+  </si>
+  <si>
+    <t>11.06.202651</t>
+  </si>
+  <si>
+    <t>11.06.202652</t>
+  </si>
+  <si>
+    <t>11.06.202653</t>
+  </si>
+  <si>
+    <t>11.06.202654</t>
+  </si>
+  <si>
+    <t>11.06.202655</t>
+  </si>
+  <si>
+    <t>11.06.202656</t>
+  </si>
+  <si>
+    <t>11.06.202657</t>
+  </si>
+  <si>
+    <t>11.06.202658</t>
+  </si>
+  <si>
+    <t>11.06.202659</t>
+  </si>
+  <si>
+    <t>11.06.202660</t>
+  </si>
+  <si>
+    <t>11.06.202661</t>
+  </si>
+  <si>
+    <t>11.06.202662</t>
+  </si>
+  <si>
+    <t>11.06.202663</t>
+  </si>
+  <si>
+    <t>11.06.202664</t>
+  </si>
+  <si>
+    <t>11.06.202665</t>
+  </si>
+  <si>
+    <t>11.06.202666</t>
+  </si>
+  <si>
+    <t>11.06.202667</t>
+  </si>
+  <si>
+    <t>11.06.202668</t>
+  </si>
+  <si>
+    <t>11.06.202669</t>
+  </si>
+  <si>
+    <t>11.06.202670</t>
+  </si>
+  <si>
+    <t>11.06.202671</t>
+  </si>
+  <si>
+    <t>11.06.202672</t>
+  </si>
+  <si>
+    <t>11.06.202673</t>
+  </si>
+  <si>
+    <t>11.06.202674</t>
+  </si>
+  <si>
+    <t>11.06.202675</t>
+  </si>
+  <si>
+    <t>11.06.202676</t>
+  </si>
+  <si>
+    <t>11.06.202677</t>
+  </si>
+  <si>
+    <t>11.06.202678</t>
+  </si>
+  <si>
+    <t>11.06.202679</t>
+  </si>
+  <si>
+    <t>11.06.202680</t>
+  </si>
+  <si>
+    <t>11.06.202681</t>
+  </si>
+  <si>
+    <t>11.06.202682</t>
+  </si>
+  <si>
+    <t>11.06.202683</t>
+  </si>
+  <si>
+    <t>11.06.202684</t>
+  </si>
+  <si>
+    <t>11.06.202685</t>
+  </si>
+  <si>
+    <t>11.06.202686</t>
+  </si>
+  <si>
+    <t>11.06.202687</t>
+  </si>
+  <si>
+    <t>11.06.202688</t>
+  </si>
+  <si>
+    <t>11.06.202689</t>
+  </si>
+  <si>
+    <t>11.06.202690</t>
+  </si>
+  <si>
+    <t>11.06.202691</t>
+  </si>
+  <si>
+    <t>11.06.202692</t>
+  </si>
+  <si>
+    <t>11.06.202693</t>
+  </si>
+  <si>
+    <t>11.06.202694</t>
+  </si>
+  <si>
+    <t>11.06.202695</t>
+  </si>
+  <si>
+    <t>11.06.202696</t>
+  </si>
+  <si>
+    <t>12.06.20261</t>
+  </si>
+  <si>
+    <t>12.06.20262</t>
+  </si>
+  <si>
+    <t>12.06.20263</t>
+  </si>
+  <si>
+    <t>12.06.20264</t>
+  </si>
+  <si>
+    <t>12.06.20265</t>
+  </si>
+  <si>
+    <t>12.06.20266</t>
+  </si>
+  <si>
+    <t>12.06.20267</t>
+  </si>
+  <si>
+    <t>12.06.20268</t>
+  </si>
+  <si>
+    <t>12.06.20269</t>
+  </si>
+  <si>
+    <t>12.06.202610</t>
+  </si>
+  <si>
+    <t>12.06.202611</t>
+  </si>
+  <si>
+    <t>12.06.202612</t>
+  </si>
+  <si>
+    <t>12.06.202613</t>
+  </si>
+  <si>
+    <t>12.06.202614</t>
+  </si>
+  <si>
+    <t>12.06.202615</t>
+  </si>
+  <si>
+    <t>12.06.202616</t>
+  </si>
+  <si>
+    <t>12.06.202617</t>
+  </si>
+  <si>
+    <t>12.06.202618</t>
+  </si>
+  <si>
+    <t>12.06.202619</t>
+  </si>
+  <si>
+    <t>12.06.202620</t>
+  </si>
+  <si>
+    <t>12.06.202621</t>
+  </si>
+  <si>
+    <t>12.06.202622</t>
+  </si>
+  <si>
+    <t>12.06.202623</t>
+  </si>
+  <si>
+    <t>12.06.202624</t>
+  </si>
+  <si>
+    <t>12.06.202625</t>
+  </si>
+  <si>
+    <t>12.06.202626</t>
+  </si>
+  <si>
+    <t>12.06.202627</t>
+  </si>
+  <si>
+    <t>12.06.202628</t>
+  </si>
+  <si>
+    <t>12.06.202629</t>
+  </si>
+  <si>
+    <t>12.06.202630</t>
+  </si>
+  <si>
+    <t>12.06.202631</t>
+  </si>
+  <si>
+    <t>12.06.202632</t>
+  </si>
+  <si>
+    <t>12.06.202633</t>
+  </si>
+  <si>
+    <t>12.06.202634</t>
+  </si>
+  <si>
+    <t>12.06.202635</t>
+  </si>
+  <si>
+    <t>12.06.202636</t>
+  </si>
+  <si>
+    <t>12.06.202637</t>
+  </si>
+  <si>
+    <t>12.06.202638</t>
+  </si>
+  <si>
+    <t>12.06.202639</t>
+  </si>
+  <si>
+    <t>12.06.202640</t>
+  </si>
+  <si>
+    <t>12.06.202641</t>
+  </si>
+  <si>
+    <t>12.06.202642</t>
+  </si>
+  <si>
+    <t>12.06.202643</t>
+  </si>
+  <si>
+    <t>12.06.202644</t>
+  </si>
+  <si>
+    <t>12.06.202645</t>
+  </si>
+  <si>
+    <t>12.06.202646</t>
+  </si>
+  <si>
+    <t>12.06.202647</t>
+  </si>
+  <si>
+    <t>12.06.202648</t>
+  </si>
+  <si>
+    <t>12.06.202649</t>
+  </si>
+  <si>
+    <t>12.06.202650</t>
+  </si>
+  <si>
+    <t>12.06.202651</t>
+  </si>
+  <si>
+    <t>12.06.202652</t>
+  </si>
+  <si>
+    <t>12.06.202653</t>
+  </si>
+  <si>
+    <t>12.06.202654</t>
+  </si>
+  <si>
+    <t>12.06.202655</t>
+  </si>
+  <si>
+    <t>12.06.202656</t>
+  </si>
+  <si>
+    <t>12.06.202657</t>
+  </si>
+  <si>
+    <t>12.06.202658</t>
+  </si>
+  <si>
+    <t>12.06.202659</t>
+  </si>
+  <si>
+    <t>12.06.202660</t>
+  </si>
+  <si>
+    <t>12.06.202661</t>
+  </si>
+  <si>
+    <t>12.06.202662</t>
+  </si>
+  <si>
+    <t>12.06.202663</t>
+  </si>
+  <si>
+    <t>12.06.202664</t>
+  </si>
+  <si>
+    <t>12.06.202665</t>
+  </si>
+  <si>
+    <t>12.06.202666</t>
+  </si>
+  <si>
+    <t>12.06.202667</t>
+  </si>
+  <si>
+    <t>12.06.202668</t>
+  </si>
+  <si>
+    <t>12.06.202669</t>
+  </si>
+  <si>
+    <t>12.06.202670</t>
+  </si>
+  <si>
+    <t>12.06.202671</t>
+  </si>
+  <si>
+    <t>12.06.202672</t>
+  </si>
+  <si>
+    <t>12.06.202673</t>
+  </si>
+  <si>
+    <t>12.06.202674</t>
+  </si>
+  <si>
+    <t>12.06.202675</t>
+  </si>
+  <si>
+    <t>12.06.202676</t>
+  </si>
+  <si>
+    <t>12.06.202677</t>
+  </si>
+  <si>
+    <t>12.06.202678</t>
+  </si>
+  <si>
+    <t>12.06.202679</t>
+  </si>
+  <si>
+    <t>12.06.202680</t>
+  </si>
+  <si>
+    <t>12.06.202681</t>
+  </si>
+  <si>
+    <t>12.06.202682</t>
+  </si>
+  <si>
+    <t>12.06.202683</t>
+  </si>
+  <si>
+    <t>12.06.202684</t>
+  </si>
+  <si>
+    <t>12.06.202685</t>
+  </si>
+  <si>
+    <t>12.06.202686</t>
+  </si>
+  <si>
+    <t>12.06.202687</t>
+  </si>
+  <si>
+    <t>12.06.202688</t>
+  </si>
+  <si>
+    <t>12.06.202689</t>
+  </si>
+  <si>
+    <t>12.06.202690</t>
+  </si>
+  <si>
+    <t>12.06.202691</t>
+  </si>
+  <si>
+    <t>12.06.202692</t>
+  </si>
+  <si>
+    <t>12.06.202693</t>
+  </si>
+  <si>
+    <t>12.06.202694</t>
+  </si>
+  <si>
+    <t>12.06.202695</t>
+  </si>
+  <si>
+    <t>12.06.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2">
-        <v>3.507</v>
+        <v>0.032</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1.281</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46184.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.278</v>
+        <v>0.342</v>
       </c>
       <c r="C3">
-        <v>0.1</v>
+        <v>0.035</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46184.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.059</v>
+        <v>4.527</v>
       </c>
       <c r="C4">
-        <v>0.331</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46184.03125</v>
       </c>
       <c r="B5">
-        <v>0.459</v>
+        <v>4.323</v>
       </c>
       <c r="C5">
-        <v>0.031</v>
+        <v>0.065</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46184.04166666666</v>
       </c>
       <c r="B6">
-        <v>30.848</v>
+        <v>10.684</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46184.05208333334</v>
       </c>
       <c r="B7">
-        <v>26.251</v>
+        <v>4.557</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46184.0625</v>
       </c>
       <c r="B8">
-        <v>22.261</v>
+        <v>0.215</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46184.07291666666</v>
       </c>
       <c r="B9">
-        <v>15.148</v>
+        <v>0.211</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46184.08333333334</v>
       </c>
       <c r="B10">
-        <v>21.319</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1.248</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46184.09375</v>
       </c>
       <c r="B11">
-        <v>25.563</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>4.006</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46184.10416666666</v>
       </c>
       <c r="B12">
-        <v>11.981</v>
+        <v>0.092</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.658</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46184.11458333334</v>
       </c>
       <c r="B13">
-        <v>7.108</v>
+        <v>0.25</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46184.125</v>
       </c>
       <c r="B14">
-        <v>14.645</v>
+        <v>0.196</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1.337</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46184.13541666666</v>
       </c>
       <c r="B15">
-        <v>18.47</v>
+        <v>1.121</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.543</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46184.14583333334</v>
       </c>
       <c r="B16">
-        <v>9.065</v>
+        <v>1.813</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46184.15625</v>
       </c>
       <c r="B17">
-        <v>0.029</v>
+        <v>0.216</v>
       </c>
       <c r="C17">
-        <v>2.461</v>
+        <v>0.102</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46184.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.216</v>
+        <v>0.094</v>
       </c>
       <c r="C18">
-        <v>2.899</v>
+        <v>1.46</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46184.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>2.432</v>
+        <v>5.729</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46184.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>7.355</v>
+        <v>16.251</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46184.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>5.297</v>
+        <v>3.859</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46184.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.335</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.6830000000000001</v>
+        <v>10.941</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46184.21875</v>
       </c>
       <c r="B23">
-        <v>0.126</v>
+        <v>0.04</v>
       </c>
       <c r="C23">
-        <v>0.393</v>
+        <v>0.257</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46184.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.805</v>
+        <v>5.338</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46184.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.005</v>
+        <v>0.079</v>
       </c>
       <c r="C25">
-        <v>1.068</v>
+        <v>2.65</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46184.25</v>
       </c>
       <c r="B26">
-        <v>0.004</v>
+        <v>5.995</v>
       </c>
       <c r="C26">
-        <v>8.773</v>
+        <v>1.348</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46184.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.104</v>
+        <v>11.088</v>
       </c>
       <c r="C27">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46184.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.064</v>
+        <v>5.856</v>
       </c>
       <c r="C28">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46184.28125</v>
       </c>
       <c r="B29">
-        <v>0.2</v>
+        <v>1.004</v>
       </c>
       <c r="C29">
-        <v>0.373</v>
+        <v>1.024</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,19 +1644,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46184.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.575</v>
+        <v>0.699</v>
       </c>
       <c r="C30">
-        <v>0.488</v>
+        <v>0.038</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46184.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.081</v>
+        <v>2.15</v>
       </c>
       <c r="C31">
-        <v>1.093</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46184.3125</v>
       </c>
       <c r="B32">
-        <v>0.091</v>
+        <v>11.603</v>
       </c>
       <c r="C32">
-        <v>0.396</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1713,13 +1713,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46184.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.021</v>
+        <v>6.14</v>
       </c>
       <c r="C33">
-        <v>0.444</v>
+        <v>0.032</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46184.33333333334</v>
       </c>
       <c r="B34">
+        <v>8.933999999999999</v>
+      </c>
+      <c r="C34">
         <v>0.014</v>
-      </c>
-      <c r="C34">
-        <v>2.854</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1759,13 +1759,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46184.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.849</v>
       </c>
       <c r="C35">
-        <v>14.689</v>
+        <v>0.128</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1782,13 +1782,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46184.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>0.787</v>
       </c>
       <c r="C36">
-        <v>39.5</v>
+        <v>0.094</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46184.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="C37">
-        <v>29.513</v>
+        <v>0.121</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46184.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>4.288</v>
       </c>
       <c r="C38">
-        <v>17.21</v>
+        <v>0.101</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>44.75</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="C39">
-        <v>30.916</v>
+        <v>0.473</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46184.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>9.167</v>
+        <v>3.692</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E40">
-        <v>71.25</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46184.40625</v>
       </c>
       <c r="B41">
-        <v>2.348</v>
+        <v>0.011</v>
       </c>
       <c r="C41">
-        <v>2.842</v>
+        <v>16.38</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E41">
-        <v>87.25</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46184.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.026</v>
+        <v>0.666</v>
       </c>
       <c r="C42">
-        <v>2.346</v>
+        <v>3.732</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>89.75</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46184.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.048</v>
+        <v>1.852</v>
       </c>
       <c r="C43">
-        <v>0.219</v>
+        <v>0.545</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46184.4375</v>
       </c>
       <c r="B44">
-        <v>4.374</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0.195</v>
+        <v>3.598</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>79.75</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46184.44791666666</v>
       </c>
       <c r="B45">
-        <v>9.641</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>5.048</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>79.75</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46184.45833333334</v>
       </c>
       <c r="B46">
-        <v>22.393</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>28.711</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>61.25</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46184.46875</v>
       </c>
       <c r="B47">
-        <v>7.001</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0.026</v>
+        <v>29.133</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>61.25</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46184.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.241</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>0.225</v>
+        <v>10.791</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>61.25</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46184.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.376</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0.138</v>
+        <v>16.97</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46184.5</v>
       </c>
       <c r="B50">
-        <v>0.946</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0.094</v>
+        <v>11.526</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46184.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.851</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>0.202</v>
+        <v>14.129</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2150,13 +2150,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46184.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.976</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0.387</v>
+        <v>48.878</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46184.53125</v>
       </c>
       <c r="B53">
-        <v>0.755</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1.517</v>
+        <v>25.518</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46184.54166666666</v>
       </c>
       <c r="B54">
-        <v>1.213</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C54">
-        <v>0.574</v>
+        <v>1.071</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="B55">
-        <v>4.596</v>
+        <v>0.122</v>
       </c>
       <c r="C55">
-        <v>0.007</v>
+        <v>1.656</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46184.5625</v>
       </c>
       <c r="B56">
-        <v>28.031</v>
+        <v>0.011</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>4.405</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46184.57291666666</v>
       </c>
       <c r="B57">
-        <v>8.564</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0.155</v>
+        <v>30.573</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46184.58333333334</v>
       </c>
       <c r="B58">
-        <v>2.159</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>0.08500000000000001</v>
+        <v>10.293</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46184.59375</v>
       </c>
       <c r="B59">
-        <v>2.869</v>
+        <v>0</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46184.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0.531</v>
+        <v>9.109</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46184.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.008999999999999999</v>
+        <v>0.134</v>
       </c>
       <c r="C61">
-        <v>5.938</v>
+        <v>5.1</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46184.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>37.11</v>
+        <v>18.833</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46184.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>7.128</v>
       </c>
       <c r="C63">
-        <v>43.391</v>
+        <v>0.269</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,13 +2426,13 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46184.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>26.81</v>
       </c>
       <c r="C64">
-        <v>15.444</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2449,16 +2449,16 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46184.65625</v>
       </c>
       <c r="B65">
-        <v>0.237</v>
+        <v>39.386</v>
       </c>
       <c r="C65">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2472,16 +2472,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46184.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.014</v>
+        <v>2.084</v>
       </c>
       <c r="C66">
-        <v>20.999</v>
+        <v>0.391</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2495,16 +2495,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46184.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>6.283</v>
+        <v>7.153</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2518,16 +2518,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46184.6875</v>
       </c>
       <c r="B68">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="C68">
-        <v>2.374</v>
+        <v>2.667</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2541,13 +2541,13 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46184.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="C69">
-        <v>20.565</v>
+        <v>5.847</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2564,13 +2564,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46184.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C70">
-        <v>33.821</v>
+        <v>4.687</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46184.71875</v>
       </c>
       <c r="B71">
-        <v>2.587</v>
+        <v>1.415</v>
       </c>
       <c r="C71">
-        <v>5.84</v>
+        <v>2.618</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46184.72916666666</v>
       </c>
       <c r="B72">
-        <v>3.316</v>
+        <v>0.259</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46184.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.912</v>
+        <v>10.117</v>
       </c>
       <c r="C73">
-        <v>0.063</v>
+        <v>0.189</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46184.75</v>
       </c>
       <c r="B74">
-        <v>20.787</v>
+        <v>17.855</v>
       </c>
       <c r="C74">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46184.76041666666</v>
       </c>
       <c r="B75">
-        <v>27.772</v>
+        <v>24.353</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46184.77083333334</v>
       </c>
       <c r="B76">
-        <v>31.921</v>
+        <v>11.67</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46184.78125</v>
       </c>
       <c r="B77">
-        <v>19.92</v>
+        <v>2.151</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46184.79166666666</v>
       </c>
       <c r="B78">
-        <v>3.959</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>0.001</v>
+        <v>15.39</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46184.80208333334</v>
       </c>
       <c r="B79">
-        <v>6.202</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>33.698</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46184.8125</v>
       </c>
       <c r="B80">
-        <v>7.325</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>0.064</v>
+        <v>7.555</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46184.82291666666</v>
       </c>
       <c r="B81">
-        <v>9.609999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46184.83333333334</v>
       </c>
       <c r="B82">
-        <v>1.127</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C82">
-        <v>2.075</v>
+        <v>8.281000000000001</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46184.84375</v>
       </c>
       <c r="B83">
-        <v>1.769</v>
+        <v>0.033</v>
       </c>
       <c r="C83">
-        <v>0.06</v>
+        <v>2.705</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46184.85416666666</v>
       </c>
       <c r="B84">
-        <v>7.738</v>
+        <v>0.091</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46184.86458333334</v>
       </c>
       <c r="B85">
-        <v>8.882</v>
+        <v>0.167</v>
       </c>
       <c r="C85">
-        <v>0.669</v>
+        <v>0.312</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46184.875</v>
       </c>
       <c r="B86">
-        <v>18.077</v>
+        <v>0.885</v>
       </c>
       <c r="C86">
-        <v>0.03</v>
+        <v>0.64</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46184.88541666666</v>
       </c>
       <c r="B87">
-        <v>22.405</v>
+        <v>0.015</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>0.473</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46184.89583333334</v>
       </c>
       <c r="B88">
-        <v>43.302</v>
+        <v>0.27</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,16 +3001,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46184.90625</v>
       </c>
       <c r="B89">
-        <v>8.678000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="C89">
-        <v>5.366</v>
+        <v>8.786</v>
       </c>
       <c r="D89">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3024,16 +3024,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46184.91666666666</v>
       </c>
       <c r="B90">
-        <v>9.952</v>
+        <v>2.512</v>
       </c>
       <c r="C90">
-        <v>0.8139999999999999</v>
+        <v>1.498</v>
       </c>
       <c r="D90">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46184.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.383</v>
+        <v>6.082</v>
       </c>
       <c r="C91">
-        <v>0.022</v>
+        <v>0.002</v>
       </c>
       <c r="D91">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3070,16 +3070,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46184.9375</v>
       </c>
       <c r="B92">
-        <v>15.469</v>
+        <v>6.616</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D92">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3093,16 +3093,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46184.94791666666</v>
       </c>
       <c r="B93">
-        <v>8.551</v>
+        <v>0.784</v>
       </c>
       <c r="C93">
-        <v>2.314</v>
+        <v>0.228</v>
       </c>
       <c r="D93">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3116,16 +3116,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46184.95833333334</v>
       </c>
       <c r="B94">
-        <v>6.863</v>
+        <v>3.012</v>
       </c>
       <c r="C94">
-        <v>0.8120000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="D94">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3139,16 +3139,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46184.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>4.095</v>
       </c>
       <c r="C95">
-        <v>6.066</v>
+        <v>0.098</v>
       </c>
       <c r="D95">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46184.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0.877</v>
+        <v>4.591</v>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46184.98958333334</v>
       </c>
       <c r="B97">
-        <v>5.188</v>
+        <v>0.016</v>
       </c>
       <c r="C97">
-        <v>0.359</v>
+        <v>1.633</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B98">
-        <v>1.758</v>
+        <v>0.019</v>
       </c>
       <c r="C98">
-        <v>0.161</v>
+        <v>0.365</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B99">
-        <v>1.758</v>
+        <v>0.019</v>
       </c>
       <c r="C99">
-        <v>0.161</v>
+        <v>0.365</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B100">
-        <v>0.132</v>
+        <v>1.166</v>
       </c>
       <c r="C100">
-        <v>0.262</v>
+        <v>1.968</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B101">
-        <v>0.132</v>
+        <v>1.166</v>
       </c>
       <c r="C101">
-        <v>0.262</v>
+        <v>1.968</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B102">
-        <v>0.324</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>16.453</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B103">
-        <v>0.324</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>16.453</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B104">
-        <v>0.523</v>
+        <v>0.037</v>
       </c>
       <c r="C104">
-        <v>0.027</v>
+        <v>3.427</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B105">
-        <v>0.523</v>
+        <v>0.037</v>
       </c>
       <c r="C105">
-        <v>0.027</v>
+        <v>3.427</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B106">
-        <v>2.656</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0.011</v>
+        <v>6.215</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B107">
-        <v>2.656</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>0.011</v>
+        <v>6.215</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B108">
-        <v>1.288</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>0.03</v>
+        <v>6.438</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B109">
-        <v>1.288</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>0.03</v>
+        <v>6.438</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B110">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0.089</v>
+        <v>4.238</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B111">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0.089</v>
+        <v>4.238</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B112">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0.253</v>
+        <v>8.726000000000001</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B113">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0.253</v>
+        <v>8.726000000000001</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46177.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B114">
-        <v>0.066</v>
+        <v>0.025</v>
       </c>
       <c r="C114">
-        <v>1.132</v>
+        <v>4.153</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46177.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>7.076</v>
+        <v>13.576</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46177.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B116">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>3.929</v>
+        <v>13.357</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46177.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B117">
-        <v>0.008999999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="C117">
-        <v>8.066000000000001</v>
+        <v>1.151</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46177.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="C118">
-        <v>2.694</v>
+        <v>9.071</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46177.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B119">
-        <v>0.202</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>0.308</v>
+        <v>9.272</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46177.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>2.218</v>
+        <v>5.378</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46177.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="C121">
-        <v>18.96</v>
+        <v>0.483</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46177.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B122">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="C122">
-        <v>2.865</v>
+        <v>0.344</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46177.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B123">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0.199</v>
+        <v>2.367</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46177.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B124">
-        <v>0.025</v>
+        <v>0.057</v>
       </c>
       <c r="C124">
-        <v>1.171</v>
+        <v>0.636</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46177.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B125">
-        <v>0.08400000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="C125">
-        <v>1.253</v>
+        <v>0.124</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46177.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B126">
-        <v>0.002</v>
+        <v>0.241</v>
       </c>
       <c r="C126">
-        <v>4.824</v>
+        <v>0.582</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46177.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B127">
-        <v>0.038</v>
+        <v>0.376</v>
       </c>
       <c r="C127">
-        <v>0.448</v>
+        <v>0.031</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46177.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B128">
-        <v>0.015</v>
+        <v>0.062</v>
       </c>
       <c r="C128">
-        <v>1.732</v>
+        <v>0.883</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46177.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B129">
-        <v>0.075</v>
+        <v>4.733</v>
       </c>
       <c r="C129">
-        <v>0.275</v>
+        <v>0.852</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,19 +3944,19 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46177.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B130">
-        <v>0.002</v>
+        <v>10.775</v>
       </c>
       <c r="C130">
-        <v>5.253</v>
+        <v>0.001</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F130">
         <v>25</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46177.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B131">
-        <v>0.343</v>
+        <v>11.349</v>
       </c>
       <c r="C131">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>39.25</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>26</v>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46177.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B132">
-        <v>0.311</v>
+        <v>6.712</v>
       </c>
       <c r="C132">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>39.25</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>27</v>
@@ -4013,19 +4013,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46177.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B133">
-        <v>0.301</v>
+        <v>1.15</v>
       </c>
       <c r="C133">
-        <v>0.871</v>
+        <v>0.532</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>28</v>
@@ -4036,19 +4036,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46177.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B134">
-        <v>0.028</v>
+        <v>0.219</v>
       </c>
       <c r="C134">
-        <v>4.144</v>
+        <v>1.742</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>53.25</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>29</v>
@@ -4059,19 +4059,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46177.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B135">
-        <v>0.966</v>
+        <v>0.171</v>
       </c>
       <c r="C135">
-        <v>0.059</v>
+        <v>0.88</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>53.25</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>30</v>
@@ -4082,19 +4082,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46177.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B136">
-        <v>4.366</v>
+        <v>0.104</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>3.177</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>53.25</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>31</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46177.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B137">
-        <v>1.959</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>5.494</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>53.25</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>32</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46177.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B138">
-        <v>43.369</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>26.988</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>33</v>
@@ -4151,19 +4151,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46177.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B139">
-        <v>28.098</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>39.473</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>34</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46177.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B140">
-        <v>14.283</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>50.507</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,13 +4197,13 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46177.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B141">
-        <v>4.071</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>0.003</v>
+        <v>27.842</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4220,16 +4220,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46177.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>38.898</v>
       </c>
       <c r="D142">
-        <v>74.25</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4243,13 +4243,13 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46177.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>62.21</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4266,19 +4266,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46177.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>31.205</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F144">
         <v>39</v>
@@ -4289,19 +4289,19 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46177.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>13.502</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F145">
         <v>40</v>
@@ -4312,19 +4312,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46177.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>20.319</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F146">
         <v>41</v>
@@ -4335,19 +4335,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46177.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>16.806</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F147">
         <v>42</v>
@@ -4358,19 +4358,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46177.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>5.244</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F148">
         <v>43</v>
@@ -4381,19 +4381,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46177.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>26.462</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F149">
         <v>44</v>
@@ -4404,19 +4404,19 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46177.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B150">
         <v>0</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>13.835</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F150">
         <v>45</v>
@@ -4427,19 +4427,19 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46177.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>25.903</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F151">
         <v>46</v>
@@ -4450,19 +4450,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46177.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>33.451</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F152">
         <v>47</v>
@@ -4473,19 +4473,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46177.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>2.356</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F153">
         <v>48</v>
@@ -4496,19 +4496,19 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46177.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>14.029</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -4519,13 +4519,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46177.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>0.735</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>0.928</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4542,13 +4542,13 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46177.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4565,13 +4565,13 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46177.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>0.262</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -4588,13 +4588,13 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46177.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46177.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46177.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46177.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46177.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46177.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46177.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46177.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46177.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46177.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46177.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46177.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46177.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46177.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46177.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46177.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46177.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46177.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46177.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46177.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46177.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46177.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46177.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46177.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46177.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46177.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46177.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46177.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46177.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46177.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46177.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46177.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46177.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46177.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46177.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46177.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46177.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46177.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46177.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46177.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46177.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46177.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46177.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46177.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B201">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
-  </si>
-  <si>
-    <t>11.06.202616</t>
-  </si>
-  <si>
-    <t>11.06.202617</t>
-  </si>
-  <si>
-    <t>11.06.202618</t>
-  </si>
-  <si>
-    <t>11.06.202619</t>
-  </si>
-  <si>
-    <t>11.06.202620</t>
-  </si>
-  <si>
-    <t>11.06.202621</t>
-  </si>
-  <si>
-    <t>11.06.202622</t>
-  </si>
-  <si>
-    <t>11.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.202624</t>
-  </si>
-  <si>
-    <t>11.06.202625</t>
-  </si>
-  <si>
-    <t>11.06.202626</t>
-  </si>
-  <si>
-    <t>11.06.202627</t>
-  </si>
-  <si>
-    <t>11.06.202628</t>
-  </si>
-  <si>
-    <t>11.06.202629</t>
-  </si>
-  <si>
-    <t>11.06.202630</t>
-  </si>
-  <si>
-    <t>11.06.202631</t>
-  </si>
-  <si>
-    <t>11.06.202632</t>
-  </si>
-  <si>
-    <t>11.06.202633</t>
-  </si>
-  <si>
-    <t>11.06.202634</t>
-  </si>
-  <si>
-    <t>11.06.202635</t>
-  </si>
-  <si>
-    <t>11.06.202636</t>
-  </si>
-  <si>
-    <t>11.06.202637</t>
-  </si>
-  <si>
-    <t>11.06.202638</t>
-  </si>
-  <si>
-    <t>11.06.202639</t>
-  </si>
-  <si>
-    <t>11.06.202640</t>
-  </si>
-  <si>
-    <t>11.06.202641</t>
-  </si>
-  <si>
-    <t>11.06.202642</t>
-  </si>
-  <si>
-    <t>11.06.202643</t>
-  </si>
-  <si>
-    <t>11.06.202644</t>
-  </si>
-  <si>
-    <t>11.06.202645</t>
-  </si>
-  <si>
-    <t>11.06.202646</t>
-  </si>
-  <si>
-    <t>11.06.202647</t>
-  </si>
-  <si>
-    <t>11.06.202648</t>
-  </si>
-  <si>
-    <t>11.06.202649</t>
-  </si>
-  <si>
-    <t>11.06.202650</t>
-  </si>
-  <si>
-    <t>11.06.202651</t>
-  </si>
-  <si>
-    <t>11.06.202652</t>
-  </si>
-  <si>
-    <t>11.06.202653</t>
-  </si>
-  <si>
-    <t>11.06.202654</t>
-  </si>
-  <si>
-    <t>11.06.202655</t>
-  </si>
-  <si>
-    <t>11.06.202656</t>
-  </si>
-  <si>
-    <t>11.06.202657</t>
-  </si>
-  <si>
-    <t>11.06.202658</t>
-  </si>
-  <si>
-    <t>11.06.202659</t>
-  </si>
-  <si>
-    <t>11.06.202660</t>
-  </si>
-  <si>
-    <t>11.06.202661</t>
-  </si>
-  <si>
-    <t>11.06.202662</t>
-  </si>
-  <si>
-    <t>11.06.202663</t>
-  </si>
-  <si>
-    <t>11.06.202664</t>
-  </si>
-  <si>
-    <t>11.06.202665</t>
-  </si>
-  <si>
-    <t>11.06.202666</t>
-  </si>
-  <si>
-    <t>11.06.202667</t>
-  </si>
-  <si>
-    <t>11.06.202668</t>
-  </si>
-  <si>
-    <t>11.06.202669</t>
-  </si>
-  <si>
-    <t>11.06.202670</t>
-  </si>
-  <si>
-    <t>11.06.202671</t>
-  </si>
-  <si>
-    <t>11.06.202672</t>
-  </si>
-  <si>
-    <t>11.06.202673</t>
-  </si>
-  <si>
-    <t>11.06.202674</t>
-  </si>
-  <si>
-    <t>11.06.202675</t>
-  </si>
-  <si>
-    <t>11.06.202676</t>
-  </si>
-  <si>
-    <t>11.06.202677</t>
-  </si>
-  <si>
-    <t>11.06.202678</t>
-  </si>
-  <si>
-    <t>11.06.202679</t>
-  </si>
-  <si>
-    <t>11.06.202680</t>
-  </si>
-  <si>
-    <t>11.06.202681</t>
-  </si>
-  <si>
-    <t>11.06.202682</t>
-  </si>
-  <si>
-    <t>11.06.202683</t>
-  </si>
-  <si>
-    <t>11.06.202684</t>
-  </si>
-  <si>
-    <t>11.06.202685</t>
-  </si>
-  <si>
-    <t>11.06.202686</t>
-  </si>
-  <si>
-    <t>11.06.202687</t>
-  </si>
-  <si>
-    <t>11.06.202688</t>
-  </si>
-  <si>
-    <t>11.06.202689</t>
-  </si>
-  <si>
-    <t>11.06.202690</t>
-  </si>
-  <si>
-    <t>11.06.202691</t>
-  </si>
-  <si>
-    <t>11.06.202692</t>
-  </si>
-  <si>
-    <t>11.06.202693</t>
-  </si>
-  <si>
-    <t>11.06.202694</t>
-  </si>
-  <si>
-    <t>11.06.202695</t>
-  </si>
-  <si>
-    <t>11.06.202696</t>
-  </si>
-  <si>
-    <t>12.06.20261</t>
-  </si>
-  <si>
-    <t>12.06.20262</t>
-  </si>
-  <si>
-    <t>12.06.20263</t>
-  </si>
-  <si>
-    <t>12.06.20264</t>
-  </si>
-  <si>
-    <t>12.06.20265</t>
-  </si>
-  <si>
-    <t>12.06.20266</t>
-  </si>
-  <si>
-    <t>12.06.20267</t>
-  </si>
-  <si>
-    <t>12.06.20268</t>
-  </si>
-  <si>
-    <t>12.06.20269</t>
-  </si>
-  <si>
-    <t>12.06.202610</t>
-  </si>
-  <si>
-    <t>12.06.202611</t>
-  </si>
-  <si>
-    <t>12.06.202612</t>
-  </si>
-  <si>
-    <t>12.06.202613</t>
-  </si>
-  <si>
-    <t>12.06.202614</t>
-  </si>
-  <si>
-    <t>12.06.202615</t>
-  </si>
-  <si>
-    <t>12.06.202616</t>
-  </si>
-  <si>
-    <t>12.06.202617</t>
-  </si>
-  <si>
-    <t>12.06.202618</t>
-  </si>
-  <si>
-    <t>12.06.202619</t>
-  </si>
-  <si>
-    <t>12.06.202620</t>
-  </si>
-  <si>
-    <t>12.06.202621</t>
-  </si>
-  <si>
-    <t>12.06.202622</t>
-  </si>
-  <si>
-    <t>12.06.202623</t>
-  </si>
-  <si>
-    <t>12.06.202624</t>
-  </si>
-  <si>
-    <t>12.06.202625</t>
-  </si>
-  <si>
-    <t>12.06.202626</t>
-  </si>
-  <si>
-    <t>12.06.202627</t>
-  </si>
-  <si>
-    <t>12.06.202628</t>
-  </si>
-  <si>
-    <t>12.06.202629</t>
-  </si>
-  <si>
-    <t>12.06.202630</t>
-  </si>
-  <si>
-    <t>12.06.202631</t>
-  </si>
-  <si>
-    <t>12.06.202632</t>
-  </si>
-  <si>
-    <t>12.06.202633</t>
-  </si>
-  <si>
-    <t>12.06.202634</t>
-  </si>
-  <si>
-    <t>12.06.202635</t>
-  </si>
-  <si>
-    <t>12.06.202636</t>
-  </si>
-  <si>
-    <t>12.06.202637</t>
-  </si>
-  <si>
-    <t>12.06.202638</t>
-  </si>
-  <si>
-    <t>12.06.202639</t>
-  </si>
-  <si>
-    <t>12.06.202640</t>
-  </si>
-  <si>
-    <t>12.06.202641</t>
-  </si>
-  <si>
-    <t>12.06.202642</t>
-  </si>
-  <si>
-    <t>12.06.202643</t>
-  </si>
-  <si>
-    <t>12.06.202644</t>
-  </si>
-  <si>
-    <t>12.06.202645</t>
-  </si>
-  <si>
-    <t>12.06.202646</t>
-  </si>
-  <si>
-    <t>12.06.202647</t>
-  </si>
-  <si>
-    <t>12.06.202648</t>
-  </si>
-  <si>
-    <t>12.06.202649</t>
-  </si>
-  <si>
-    <t>12.06.202650</t>
-  </si>
-  <si>
-    <t>12.06.202651</t>
-  </si>
-  <si>
-    <t>12.06.202652</t>
-  </si>
-  <si>
-    <t>12.06.202653</t>
-  </si>
-  <si>
-    <t>12.06.202654</t>
-  </si>
-  <si>
-    <t>12.06.202655</t>
-  </si>
-  <si>
-    <t>12.06.202656</t>
-  </si>
-  <si>
-    <t>12.06.202657</t>
-  </si>
-  <si>
-    <t>12.06.202658</t>
-  </si>
-  <si>
-    <t>12.06.202659</t>
-  </si>
-  <si>
-    <t>12.06.202660</t>
-  </si>
-  <si>
-    <t>12.06.202661</t>
-  </si>
-  <si>
-    <t>12.06.202662</t>
-  </si>
-  <si>
-    <t>12.06.202663</t>
-  </si>
-  <si>
-    <t>12.06.202664</t>
-  </si>
-  <si>
-    <t>12.06.202665</t>
-  </si>
-  <si>
-    <t>12.06.202666</t>
-  </si>
-  <si>
-    <t>12.06.202667</t>
-  </si>
-  <si>
-    <t>12.06.202668</t>
-  </si>
-  <si>
-    <t>12.06.202669</t>
-  </si>
-  <si>
-    <t>12.06.202670</t>
-  </si>
-  <si>
-    <t>12.06.202671</t>
-  </si>
-  <si>
-    <t>12.06.202672</t>
-  </si>
-  <si>
-    <t>12.06.202673</t>
-  </si>
-  <si>
-    <t>12.06.202674</t>
-  </si>
-  <si>
-    <t>12.06.202675</t>
-  </si>
-  <si>
-    <t>12.06.202676</t>
-  </si>
-  <si>
-    <t>12.06.202677</t>
-  </si>
-  <si>
-    <t>12.06.202678</t>
-  </si>
-  <si>
-    <t>12.06.202679</t>
-  </si>
-  <si>
-    <t>12.06.202680</t>
-  </si>
-  <si>
-    <t>12.06.202681</t>
-  </si>
-  <si>
-    <t>12.06.202682</t>
-  </si>
-  <si>
-    <t>12.06.202683</t>
-  </si>
-  <si>
-    <t>12.06.202684</t>
-  </si>
-  <si>
-    <t>12.06.202685</t>
-  </si>
-  <si>
-    <t>12.06.202686</t>
-  </si>
-  <si>
-    <t>12.06.202687</t>
-  </si>
-  <si>
-    <t>12.06.202688</t>
-  </si>
-  <si>
-    <t>12.06.202689</t>
-  </si>
-  <si>
-    <t>12.06.202690</t>
-  </si>
-  <si>
-    <t>12.06.202691</t>
-  </si>
-  <si>
-    <t>12.06.202692</t>
-  </si>
-  <si>
-    <t>12.06.202693</t>
-  </si>
-  <si>
-    <t>12.06.202694</t>
-  </si>
-  <si>
-    <t>12.06.202695</t>
-  </si>
-  <si>
-    <t>12.06.202696</t>
+    <t>09.07.20261</t>
+  </si>
+  <si>
+    <t>09.07.20262</t>
+  </si>
+  <si>
+    <t>09.07.20263</t>
+  </si>
+  <si>
+    <t>09.07.20264</t>
+  </si>
+  <si>
+    <t>09.07.20265</t>
+  </si>
+  <si>
+    <t>09.07.20266</t>
+  </si>
+  <si>
+    <t>09.07.20267</t>
+  </si>
+  <si>
+    <t>09.07.20268</t>
+  </si>
+  <si>
+    <t>09.07.20269</t>
+  </si>
+  <si>
+    <t>09.07.202610</t>
+  </si>
+  <si>
+    <t>09.07.202611</t>
+  </si>
+  <si>
+    <t>09.07.202612</t>
+  </si>
+  <si>
+    <t>09.07.202613</t>
+  </si>
+  <si>
+    <t>09.07.202614</t>
+  </si>
+  <si>
+    <t>09.07.202615</t>
+  </si>
+  <si>
+    <t>09.07.202616</t>
+  </si>
+  <si>
+    <t>09.07.202617</t>
+  </si>
+  <si>
+    <t>09.07.202618</t>
+  </si>
+  <si>
+    <t>09.07.202619</t>
+  </si>
+  <si>
+    <t>09.07.202620</t>
+  </si>
+  <si>
+    <t>09.07.202621</t>
+  </si>
+  <si>
+    <t>09.07.202622</t>
+  </si>
+  <si>
+    <t>09.07.202623</t>
+  </si>
+  <si>
+    <t>09.07.202624</t>
+  </si>
+  <si>
+    <t>09.07.202625</t>
+  </si>
+  <si>
+    <t>09.07.202626</t>
+  </si>
+  <si>
+    <t>09.07.202627</t>
+  </si>
+  <si>
+    <t>09.07.202628</t>
+  </si>
+  <si>
+    <t>09.07.202629</t>
+  </si>
+  <si>
+    <t>09.07.202630</t>
+  </si>
+  <si>
+    <t>09.07.202631</t>
+  </si>
+  <si>
+    <t>09.07.202632</t>
+  </si>
+  <si>
+    <t>09.07.202633</t>
+  </si>
+  <si>
+    <t>09.07.202634</t>
+  </si>
+  <si>
+    <t>09.07.202635</t>
+  </si>
+  <si>
+    <t>09.07.202636</t>
+  </si>
+  <si>
+    <t>09.07.202637</t>
+  </si>
+  <si>
+    <t>09.07.202638</t>
+  </si>
+  <si>
+    <t>09.07.202639</t>
+  </si>
+  <si>
+    <t>09.07.202640</t>
+  </si>
+  <si>
+    <t>09.07.202641</t>
+  </si>
+  <si>
+    <t>09.07.202642</t>
+  </si>
+  <si>
+    <t>09.07.202643</t>
+  </si>
+  <si>
+    <t>09.07.202644</t>
+  </si>
+  <si>
+    <t>09.07.202645</t>
+  </si>
+  <si>
+    <t>09.07.202646</t>
+  </si>
+  <si>
+    <t>09.07.202647</t>
+  </si>
+  <si>
+    <t>09.07.202648</t>
+  </si>
+  <si>
+    <t>09.07.202649</t>
+  </si>
+  <si>
+    <t>09.07.202650</t>
+  </si>
+  <si>
+    <t>09.07.202651</t>
+  </si>
+  <si>
+    <t>09.07.202652</t>
+  </si>
+  <si>
+    <t>09.07.202653</t>
+  </si>
+  <si>
+    <t>09.07.202654</t>
+  </si>
+  <si>
+    <t>09.07.202655</t>
+  </si>
+  <si>
+    <t>09.07.202656</t>
+  </si>
+  <si>
+    <t>09.07.202657</t>
+  </si>
+  <si>
+    <t>09.07.202658</t>
+  </si>
+  <si>
+    <t>09.07.202659</t>
+  </si>
+  <si>
+    <t>09.07.202660</t>
+  </si>
+  <si>
+    <t>09.07.202661</t>
+  </si>
+  <si>
+    <t>09.07.202662</t>
+  </si>
+  <si>
+    <t>09.07.202663</t>
+  </si>
+  <si>
+    <t>09.07.202664</t>
+  </si>
+  <si>
+    <t>09.07.202665</t>
+  </si>
+  <si>
+    <t>09.07.202666</t>
+  </si>
+  <si>
+    <t>09.07.202667</t>
+  </si>
+  <si>
+    <t>09.07.202668</t>
+  </si>
+  <si>
+    <t>09.07.202669</t>
+  </si>
+  <si>
+    <t>09.07.202670</t>
+  </si>
+  <si>
+    <t>09.07.202671</t>
+  </si>
+  <si>
+    <t>09.07.202672</t>
+  </si>
+  <si>
+    <t>09.07.202673</t>
+  </si>
+  <si>
+    <t>09.07.202674</t>
+  </si>
+  <si>
+    <t>09.07.202675</t>
+  </si>
+  <si>
+    <t>09.07.202676</t>
+  </si>
+  <si>
+    <t>09.07.202677</t>
+  </si>
+  <si>
+    <t>09.07.202678</t>
+  </si>
+  <si>
+    <t>09.07.202679</t>
+  </si>
+  <si>
+    <t>09.07.202680</t>
+  </si>
+  <si>
+    <t>09.07.202681</t>
+  </si>
+  <si>
+    <t>09.07.202682</t>
+  </si>
+  <si>
+    <t>09.07.202683</t>
+  </si>
+  <si>
+    <t>09.07.202684</t>
+  </si>
+  <si>
+    <t>09.07.202685</t>
+  </si>
+  <si>
+    <t>09.07.202686</t>
+  </si>
+  <si>
+    <t>09.07.202687</t>
+  </si>
+  <si>
+    <t>09.07.202688</t>
+  </si>
+  <si>
+    <t>09.07.202689</t>
+  </si>
+  <si>
+    <t>09.07.202690</t>
+  </si>
+  <si>
+    <t>09.07.202691</t>
+  </si>
+  <si>
+    <t>09.07.202692</t>
+  </si>
+  <si>
+    <t>09.07.202693</t>
+  </si>
+  <si>
+    <t>09.07.202694</t>
+  </si>
+  <si>
+    <t>09.07.202695</t>
+  </si>
+  <si>
+    <t>09.07.202696</t>
+  </si>
+  <si>
+    <t>10.07.20261</t>
+  </si>
+  <si>
+    <t>10.07.20262</t>
+  </si>
+  <si>
+    <t>10.07.20263</t>
+  </si>
+  <si>
+    <t>10.07.20264</t>
+  </si>
+  <si>
+    <t>10.07.20265</t>
+  </si>
+  <si>
+    <t>10.07.20266</t>
+  </si>
+  <si>
+    <t>10.07.20267</t>
+  </si>
+  <si>
+    <t>10.07.20268</t>
+  </si>
+  <si>
+    <t>10.07.20269</t>
+  </si>
+  <si>
+    <t>10.07.202610</t>
+  </si>
+  <si>
+    <t>10.07.202611</t>
+  </si>
+  <si>
+    <t>10.07.202612</t>
+  </si>
+  <si>
+    <t>10.07.202613</t>
+  </si>
+  <si>
+    <t>10.07.202614</t>
+  </si>
+  <si>
+    <t>10.07.202615</t>
+  </si>
+  <si>
+    <t>10.07.202616</t>
+  </si>
+  <si>
+    <t>10.07.202617</t>
+  </si>
+  <si>
+    <t>10.07.202618</t>
+  </si>
+  <si>
+    <t>10.07.202619</t>
+  </si>
+  <si>
+    <t>10.07.202620</t>
+  </si>
+  <si>
+    <t>10.07.202621</t>
+  </si>
+  <si>
+    <t>10.07.202622</t>
+  </si>
+  <si>
+    <t>10.07.202623</t>
+  </si>
+  <si>
+    <t>10.07.202624</t>
+  </si>
+  <si>
+    <t>10.07.202625</t>
+  </si>
+  <si>
+    <t>10.07.202626</t>
+  </si>
+  <si>
+    <t>10.07.202627</t>
+  </si>
+  <si>
+    <t>10.07.202628</t>
+  </si>
+  <si>
+    <t>10.07.202629</t>
+  </si>
+  <si>
+    <t>10.07.202630</t>
+  </si>
+  <si>
+    <t>10.07.202631</t>
+  </si>
+  <si>
+    <t>10.07.202632</t>
+  </si>
+  <si>
+    <t>10.07.202633</t>
+  </si>
+  <si>
+    <t>10.07.202634</t>
+  </si>
+  <si>
+    <t>10.07.202635</t>
+  </si>
+  <si>
+    <t>10.07.202636</t>
+  </si>
+  <si>
+    <t>10.07.202637</t>
+  </si>
+  <si>
+    <t>10.07.202638</t>
+  </si>
+  <si>
+    <t>10.07.202639</t>
+  </si>
+  <si>
+    <t>10.07.202640</t>
+  </si>
+  <si>
+    <t>10.07.202641</t>
+  </si>
+  <si>
+    <t>10.07.202642</t>
+  </si>
+  <si>
+    <t>10.07.202643</t>
+  </si>
+  <si>
+    <t>10.07.202644</t>
+  </si>
+  <si>
+    <t>10.07.202645</t>
+  </si>
+  <si>
+    <t>10.07.202646</t>
+  </si>
+  <si>
+    <t>10.07.202647</t>
+  </si>
+  <si>
+    <t>10.07.202648</t>
+  </si>
+  <si>
+    <t>10.07.202649</t>
+  </si>
+  <si>
+    <t>10.07.202650</t>
+  </si>
+  <si>
+    <t>10.07.202651</t>
+  </si>
+  <si>
+    <t>10.07.202652</t>
+  </si>
+  <si>
+    <t>10.07.202653</t>
+  </si>
+  <si>
+    <t>10.07.202654</t>
+  </si>
+  <si>
+    <t>10.07.202655</t>
+  </si>
+  <si>
+    <t>10.07.202656</t>
+  </si>
+  <si>
+    <t>10.07.202657</t>
+  </si>
+  <si>
+    <t>10.07.202658</t>
+  </si>
+  <si>
+    <t>10.07.202659</t>
+  </si>
+  <si>
+    <t>10.07.202660</t>
+  </si>
+  <si>
+    <t>10.07.202661</t>
+  </si>
+  <si>
+    <t>10.07.202662</t>
+  </si>
+  <si>
+    <t>10.07.202663</t>
+  </si>
+  <si>
+    <t>10.07.202664</t>
+  </si>
+  <si>
+    <t>10.07.202665</t>
+  </si>
+  <si>
+    <t>10.07.202666</t>
+  </si>
+  <si>
+    <t>10.07.202667</t>
+  </si>
+  <si>
+    <t>10.07.202668</t>
+  </si>
+  <si>
+    <t>10.07.202669</t>
+  </si>
+  <si>
+    <t>10.07.202670</t>
+  </si>
+  <si>
+    <t>10.07.202671</t>
+  </si>
+  <si>
+    <t>10.07.202672</t>
+  </si>
+  <si>
+    <t>10.07.202673</t>
+  </si>
+  <si>
+    <t>10.07.202674</t>
+  </si>
+  <si>
+    <t>10.07.202675</t>
+  </si>
+  <si>
+    <t>10.07.202676</t>
+  </si>
+  <si>
+    <t>10.07.202677</t>
+  </si>
+  <si>
+    <t>10.07.202678</t>
+  </si>
+  <si>
+    <t>10.07.202679</t>
+  </si>
+  <si>
+    <t>10.07.202680</t>
+  </si>
+  <si>
+    <t>10.07.202681</t>
+  </si>
+  <si>
+    <t>10.07.202682</t>
+  </si>
+  <si>
+    <t>10.07.202683</t>
+  </si>
+  <si>
+    <t>10.07.202684</t>
+  </si>
+  <si>
+    <t>10.07.202685</t>
+  </si>
+  <si>
+    <t>10.07.202686</t>
+  </si>
+  <si>
+    <t>10.07.202687</t>
+  </si>
+  <si>
+    <t>10.07.202688</t>
+  </si>
+  <si>
+    <t>10.07.202689</t>
+  </si>
+  <si>
+    <t>10.07.202690</t>
+  </si>
+  <si>
+    <t>10.07.202691</t>
+  </si>
+  <si>
+    <t>10.07.202692</t>
+  </si>
+  <si>
+    <t>10.07.202693</t>
+  </si>
+  <si>
+    <t>10.07.202694</t>
+  </si>
+  <si>
+    <t>10.07.202695</t>
+  </si>
+  <si>
+    <t>10.07.202696</t>
   </si>
 </sst>
 </file>
@@ -972,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B2">
-        <v>0.032</v>
+        <v>0.146</v>
       </c>
       <c r="C2">
-        <v>1.281</v>
+        <v>0.314</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46184.01041666666</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.342</v>
+        <v>0.763</v>
       </c>
       <c r="C3">
-        <v>0.035</v>
+        <v>1.396</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46184.02083333334</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
-        <v>4.527</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46184.03125</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
-        <v>4.323</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.065</v>
+        <v>10.547</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46184.04166666666</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
-        <v>10.684</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>3.692</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46184.05208333334</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
-        <v>4.557</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>54.574</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,19 +1138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46184.0625</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>0.215</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.38</v>
+        <v>43.413</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46184.07291666666</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.242</v>
+        <v>26.29</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1184,19 +1184,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46184.08333333334</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.07000000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="C10">
-        <v>1.248</v>
+        <v>13.058</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1207,19 +1207,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46184.09375</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="C11">
-        <v>4.006</v>
+        <v>0.131</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1230,19 +1230,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46184.10416666666</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.092</v>
+        <v>0.002</v>
       </c>
       <c r="C12">
-        <v>0.658</v>
+        <v>16.249</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1253,19 +1253,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46184.11458333334</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.115</v>
+        <v>39.624</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1276,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46184.125</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
-        <v>0.196</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>1.337</v>
+        <v>34.589</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46184.13541666666</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.121</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0.543</v>
+        <v>25.745</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,19 +1322,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46184.14583333334</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.813</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0.037</v>
+        <v>27.749</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1345,19 +1345,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46184.15625</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>0.216</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.102</v>
+        <v>31.275</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -1368,19 +1368,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46184.16666666666</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1.46</v>
+        <v>14.294</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1391,19 +1391,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46184.17708333334</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>5.729</v>
+        <v>16.403</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,19 +1414,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46184.1875</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>16.251</v>
+        <v>32.099</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46184.19791666666</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1.035</v>
       </c>
       <c r="C21">
-        <v>3.859</v>
+        <v>10.827</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46184.20833333334</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>3.011</v>
       </c>
       <c r="C22">
-        <v>10.941</v>
+        <v>0.181</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,19 +1483,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46184.21875</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>0.04</v>
+        <v>9.443</v>
       </c>
       <c r="C23">
-        <v>0.257</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -1506,19 +1506,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46184.22916666666</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C24">
-        <v>5.338</v>
+        <v>2.153</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -1529,19 +1529,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46184.23958333334</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.079</v>
+        <v>1.227</v>
       </c>
       <c r="C25">
-        <v>2.65</v>
+        <v>1.777</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -1552,19 +1552,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46184.25</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>5.995</v>
+        <v>13.932</v>
       </c>
       <c r="C26">
-        <v>1.348</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F26">
         <v>25</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46184.26041666666</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
-        <v>11.088</v>
+        <v>0.599</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1.091</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46184.27083333334</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
-        <v>5.856</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>12.484</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46184.28125</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
-        <v>1.004</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>1.024</v>
+        <v>30.94</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46184.29166666666</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.699</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.038</v>
+        <v>5.074</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,19 +1667,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46184.30208333334</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>10.536</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46184.3125</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>11.603</v>
+        <v>0.131</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>7.045</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +1713,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46184.32291666666</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>6.14</v>
+        <v>0.545</v>
       </c>
       <c r="C33">
-        <v>0.032</v>
+        <v>0.615</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46184.33333333334</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
-        <v>8.933999999999999</v>
+        <v>4.129</v>
       </c>
       <c r="C34">
-        <v>0.014</v>
+        <v>0.679</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46184.34375</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
-        <v>0.849</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.128</v>
+        <v>35.28</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46184.35416666666</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.094</v>
+        <v>15.912</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>35.25</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46184.36458333334</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.121</v>
+        <v>30.704</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>35.25</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46184.375</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
-        <v>4.288</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.101</v>
+        <v>26.314</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>25.75</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46184.38541666666</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.148</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.473</v>
+        <v>35.061</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>23.25</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46184.39583333334</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>3.692</v>
+        <v>16.117</v>
       </c>
       <c r="D40">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>61.25</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46184.40625</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>16.38</v>
+        <v>13.427</v>
       </c>
       <c r="D41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46184.41666666666</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.666</v>
+        <v>2.445</v>
       </c>
       <c r="C42">
-        <v>3.732</v>
+        <v>4.69</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46184.42708333334</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>1.852</v>
+        <v>3.677</v>
       </c>
       <c r="C43">
-        <v>0.545</v>
+        <v>0.02</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46184.4375</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>8.499000000000001</v>
       </c>
       <c r="C44">
-        <v>3.598</v>
+        <v>0.003</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46184.44791666666</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>4.386</v>
       </c>
       <c r="C45">
-        <v>5.048</v>
+        <v>0.046</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46184.45833333334</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1.061</v>
       </c>
       <c r="C46">
-        <v>28.711</v>
+        <v>0.216</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46184.46875</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>10.92</v>
       </c>
       <c r="C47">
-        <v>29.133</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46184.47916666666</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>8.124000000000001</v>
       </c>
       <c r="C48">
-        <v>10.791</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46184.48958333334</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>21.533</v>
       </c>
       <c r="C49">
-        <v>16.97</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46184.5</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1.303</v>
       </c>
       <c r="C50">
-        <v>11.526</v>
+        <v>0.056</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46184.51041666666</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>8.038</v>
       </c>
       <c r="C51">
-        <v>14.129</v>
+        <v>0.135</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,13 +2150,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46184.52083333334</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>10.206</v>
       </c>
       <c r="C52">
-        <v>48.878</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46184.53125</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>4.522</v>
       </c>
       <c r="C53">
-        <v>25.518</v>
+        <v>3.56</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46184.54166666666</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.08599999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="C54">
-        <v>1.071</v>
+        <v>8.994</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46184.55208333334</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.122</v>
+        <v>0.15</v>
       </c>
       <c r="C55">
-        <v>1.656</v>
+        <v>1.498</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46184.5625</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>0.011</v>
+        <v>0.033</v>
       </c>
       <c r="C56">
-        <v>4.405</v>
+        <v>1.354</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46184.57291666666</v>
+        <v>46212.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="C57">
-        <v>30.573</v>
+        <v>0.359</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46184.58333333334</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="C58">
-        <v>10.293</v>
+        <v>0.34</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46184.59375</v>
+        <v>46212.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1.188</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46184.60416666666</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="C60">
-        <v>9.109</v>
+        <v>4.318</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46184.61458333334</v>
+        <v>46212.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>5.1</v>
+        <v>24.207</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46184.625</v>
+        <v>46212.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="C62">
-        <v>18.833</v>
+        <v>22.134</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46184.63541666666</v>
+        <v>46212.63541666666</v>
       </c>
       <c r="B63">
-        <v>7.128</v>
+        <v>0.196</v>
       </c>
       <c r="C63">
-        <v>0.269</v>
+        <v>5.768</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,13 +2426,13 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46184.64583333334</v>
+        <v>46212.64583333334</v>
       </c>
       <c r="B64">
-        <v>26.81</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>14.072</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2449,16 +2449,16 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46184.65625</v>
+        <v>46212.65625</v>
       </c>
       <c r="B65">
-        <v>39.386</v>
+        <v>6.39</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>4.319</v>
       </c>
       <c r="D65">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2472,16 +2472,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46184.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="B66">
-        <v>2.084</v>
+        <v>5.142</v>
       </c>
       <c r="C66">
-        <v>0.391</v>
+        <v>1.221</v>
       </c>
       <c r="D66">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2495,16 +2495,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46184.67708333334</v>
+        <v>46212.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="C67">
-        <v>7.153</v>
+        <v>3.199</v>
       </c>
       <c r="D67">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2518,16 +2518,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46184.6875</v>
+        <v>46212.6875</v>
       </c>
       <c r="B68">
-        <v>0.02</v>
+        <v>2.455</v>
       </c>
       <c r="C68">
-        <v>2.667</v>
+        <v>6.106</v>
       </c>
       <c r="D68">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2541,13 +2541,13 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46184.69791666666</v>
+        <v>46212.69791666666</v>
       </c>
       <c r="B69">
-        <v>0.238</v>
+        <v>2.445</v>
       </c>
       <c r="C69">
-        <v>5.847</v>
+        <v>0.306</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2564,13 +2564,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46184.70833333334</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="B70">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>4.687</v>
+        <v>19.671</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46184.71875</v>
+        <v>46212.71875</v>
       </c>
       <c r="B71">
-        <v>1.415</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>2.618</v>
+        <v>3.571</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>29.25</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +2610,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46184.72916666666</v>
+        <v>46212.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.259</v>
+        <v>0.915</v>
       </c>
       <c r="C72">
-        <v>1.417</v>
+        <v>0.911</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>29.25</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46184.73958333334</v>
+        <v>46212.73958333334</v>
       </c>
       <c r="B73">
-        <v>10.117</v>
+        <v>3.285</v>
       </c>
       <c r="C73">
-        <v>0.189</v>
+        <v>0.035</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>29.25</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,19 +2656,19 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46184.75</v>
+        <v>46212.75</v>
       </c>
       <c r="B74">
-        <v>17.855</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>27.046</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46184.76041666666</v>
+        <v>46212.76041666666</v>
       </c>
       <c r="B75">
-        <v>24.353</v>
+        <v>0.006</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>20.866</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>33.75</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46184.77083333334</v>
+        <v>46212.77083333334</v>
       </c>
       <c r="B76">
-        <v>11.67</v>
+        <v>2.436</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>2.969</v>
       </c>
       <c r="D76">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>58.75</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,19 +2725,19 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46184.78125</v>
+        <v>46212.78125</v>
       </c>
       <c r="B77">
-        <v>2.151</v>
+        <v>11.099</v>
       </c>
       <c r="C77">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>58.75</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46184.79166666666</v>
+        <v>46212.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>13.617</v>
       </c>
       <c r="C78">
-        <v>15.39</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>58.75</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46184.80208333334</v>
+        <v>46212.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>19.712</v>
       </c>
       <c r="C79">
-        <v>33.698</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>58.75</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46184.8125</v>
+        <v>46212.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>32.044</v>
       </c>
       <c r="C80">
-        <v>7.555</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46184.82291666666</v>
+        <v>46212.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.55</v>
+        <v>9.464</v>
       </c>
       <c r="C81">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46184.83333333334</v>
+        <v>46212.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.06900000000000001</v>
+        <v>0.493</v>
       </c>
       <c r="C82">
-        <v>8.281000000000001</v>
+        <v>2.381</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46184.84375</v>
+        <v>46212.84375</v>
       </c>
       <c r="B83">
-        <v>0.033</v>
+        <v>3.286</v>
       </c>
       <c r="C83">
-        <v>2.705</v>
+        <v>0.143</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46184.85416666666</v>
+        <v>46212.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.091</v>
+        <v>0.13</v>
       </c>
       <c r="C84">
-        <v>0.242</v>
+        <v>0.236</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46184.86458333334</v>
+        <v>46212.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.167</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C85">
-        <v>0.312</v>
+        <v>0.791</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46184.875</v>
+        <v>46212.875</v>
       </c>
       <c r="B86">
-        <v>0.885</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>0.64</v>
+        <v>50.921</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,19 +2955,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46184.88541666666</v>
+        <v>46212.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>0.473</v>
+        <v>90.926</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46184.89583333334</v>
+        <v>46212.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0.158</v>
+        <v>74.521</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46184.90625</v>
+        <v>46212.90625</v>
       </c>
       <c r="B89">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>8.786</v>
+        <v>17.551</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3024,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46184.91666666666</v>
+        <v>46212.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.512</v>
+        <v>0.655</v>
       </c>
       <c r="C90">
-        <v>1.498</v>
+        <v>3.279</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,19 +3047,19 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46184.92708333334</v>
+        <v>46212.92708333334</v>
       </c>
       <c r="B91">
-        <v>6.082</v>
+        <v>5.91</v>
       </c>
       <c r="C91">
-        <v>0.002</v>
+        <v>0.191</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F91">
         <v>90</v>
@@ -3070,19 +3070,19 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46184.9375</v>
+        <v>46212.9375</v>
       </c>
       <c r="B92">
-        <v>6.616</v>
+        <v>0.445</v>
       </c>
       <c r="C92">
-        <v>0.02</v>
+        <v>0.095</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="F92">
         <v>91</v>
@@ -3093,19 +3093,19 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46184.94791666666</v>
+        <v>46212.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.784</v>
+        <v>9.631</v>
       </c>
       <c r="C93">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -3116,19 +3116,19 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46184.95833333334</v>
+        <v>46212.95833333334</v>
       </c>
       <c r="B94">
-        <v>3.012</v>
+        <v>31.601</v>
       </c>
       <c r="C94">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F94">
         <v>93</v>
@@ -3139,19 +3139,19 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46184.96875</v>
+        <v>46212.96875</v>
       </c>
       <c r="B95">
-        <v>4.095</v>
+        <v>38.601</v>
       </c>
       <c r="C95">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F95">
         <v>94</v>
@@ -3162,19 +3162,19 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46184.97916666666</v>
+        <v>46212.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>24.657</v>
       </c>
       <c r="C96">
-        <v>4.591</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -3185,19 +3185,19 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46184.98958333334</v>
+        <v>46212.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.016</v>
+        <v>26.678</v>
       </c>
       <c r="C97">
-        <v>1.633</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -3208,19 +3208,19 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="B98">
-        <v>0.019</v>
+        <v>45.538</v>
       </c>
       <c r="C98">
-        <v>0.365</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -3231,82 +3231,82 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46185</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.019</v>
+        <v>36.447</v>
       </c>
       <c r="C99">
-        <v>0.365</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46185.01041666666</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B100">
-        <v>1.166</v>
+        <v>6.768</v>
       </c>
       <c r="C100">
-        <v>1.968</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G100" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46185.01041666666</v>
+        <v>46213.03125</v>
       </c>
       <c r="B101">
-        <v>1.166</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="C101">
-        <v>1.968</v>
+        <v>1.475</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G101" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="C102">
-        <v>16.453</v>
+        <v>10.46</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3315,21 +3315,21 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G102" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>16.453</v>
+        <v>51.595</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3338,389 +3338,389 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G103" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46185.03125</v>
+        <v>46213.0625</v>
       </c>
       <c r="B104">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>3.427</v>
+        <v>61.304</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F104">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G104" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46185.03125</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B105">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>3.427</v>
+        <v>18.269</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F105">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G105" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>6.215</v>
+        <v>40.153</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>49.25</v>
       </c>
       <c r="F106">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G106" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>6.215</v>
+        <v>22.733</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F107">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G107" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>6.438</v>
+        <v>4.519</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F108">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G108" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>6.438</v>
+        <v>14.023</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F109">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G109" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46185.0625</v>
+        <v>46213.125</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>4.238</v>
+        <v>15.429</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>67.25</v>
       </c>
       <c r="F110">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G110" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46185.0625</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>4.238</v>
+        <v>7.554</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F111">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>8.726000000000001</v>
+        <v>3.829</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F112">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>8.726000000000001</v>
+        <v>14.001</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>54.25</v>
       </c>
       <c r="F113">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G113" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.025</v>
+        <v>0.411</v>
       </c>
       <c r="C114">
-        <v>4.153</v>
+        <v>1.883</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>54.25</v>
       </c>
       <c r="F114">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G114" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46185.09375</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>5.056</v>
       </c>
       <c r="C115">
-        <v>13.576</v>
+        <v>0.017</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>54.25</v>
       </c>
       <c r="F115">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G115" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="C116">
-        <v>13.357</v>
+        <v>0.066</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F116">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G116" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.55</v>
+        <v>0.374</v>
       </c>
       <c r="C117">
-        <v>1.151</v>
+        <v>0.108</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F117">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46185.125</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B118">
-        <v>0.031</v>
+        <v>9.118</v>
       </c>
       <c r="C118">
-        <v>9.071</v>
+        <v>0.002</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F118">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G118" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>4.583</v>
       </c>
       <c r="C119">
-        <v>9.272</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="F119">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G119" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="C120">
-        <v>5.378</v>
+        <v>8.582000000000001</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3729,21 +3729,21 @@
         <v>0</v>
       </c>
       <c r="F120">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46185.15625</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B121">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0.483</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3752,21 +3752,21 @@
         <v>0</v>
       </c>
       <c r="F121">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G121" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.25</v>
       </c>
       <c r="B122">
-        <v>0.003</v>
+        <v>0.151</v>
       </c>
       <c r="C122">
-        <v>0.344</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3775,21 +3775,21 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G122" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>2.367</v>
+        <v>18.275</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3798,21 +3798,21 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G123" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46185.1875</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B124">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0.636</v>
+        <v>14.175</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3821,21 +3821,21 @@
         <v>0</v>
       </c>
       <c r="F124">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G124" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.28125</v>
       </c>
       <c r="B125">
-        <v>0.6929999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="C125">
-        <v>0.124</v>
+        <v>2.012</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3844,21 +3844,21 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G125" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B126">
-        <v>0.241</v>
+        <v>0.478</v>
       </c>
       <c r="C126">
-        <v>0.582</v>
+        <v>0.573</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3867,21 +3867,21 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G126" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46185.21875</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.376</v>
+        <v>0.061</v>
       </c>
       <c r="C127">
-        <v>0.031</v>
+        <v>2.338</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3890,21 +3890,21 @@
         <v>0</v>
       </c>
       <c r="F127">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G127" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.3125</v>
       </c>
       <c r="B128">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>0.883</v>
+        <v>15.802</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3913,21 +3913,21 @@
         <v>0</v>
       </c>
       <c r="F128">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G128" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B129">
-        <v>4.733</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>0.852</v>
+        <v>38.989</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3936,21 +3936,21 @@
         <v>0</v>
       </c>
       <c r="F129">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G129" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46185.25</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B130">
-        <v>10.775</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>0.001</v>
+        <v>26.274</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3959,21 +3959,21 @@
         <v>0</v>
       </c>
       <c r="F130">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G130" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.34375</v>
       </c>
       <c r="B131">
-        <v>11.349</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>21.358</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3982,21 +3982,21 @@
         <v>0</v>
       </c>
       <c r="F131">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G131" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B132">
-        <v>6.712</v>
+        <v>0.105</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1.815</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4005,21 +4005,21 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G132" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46185.28125</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B133">
-        <v>1.15</v>
+        <v>0.055</v>
       </c>
       <c r="C133">
-        <v>0.532</v>
+        <v>11.306</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4028,21 +4028,21 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G133" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.375</v>
       </c>
       <c r="B134">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>1.742</v>
+        <v>14.277</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4051,21 +4051,21 @@
         <v>0</v>
       </c>
       <c r="F134">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G134" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B135">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>0.88</v>
+        <v>13.013</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4074,182 +4074,182 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G135" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46185.3125</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B136">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>3.177</v>
+        <v>20.271</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="F136">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G136" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>5.494</v>
+        <v>40.873</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="F137">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G137" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
       <c r="C138">
-        <v>26.988</v>
+        <v>57.036</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="F138">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G138" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46185.34375</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>39.473</v>
+        <v>25.216</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="F139">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G139" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="C140">
-        <v>50.507</v>
+        <v>10.113</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="F140">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G140" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>0.473</v>
       </c>
       <c r="C141">
-        <v>27.842</v>
+        <v>1.895</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="F141">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G141" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46185.375</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>38.898</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F142">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G142" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>62.21</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4258,274 +4258,274 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G143" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>31.205</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F144">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G144" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46185.40625</v>
+        <v>46213.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>13.502</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F145">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G145" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>20.319</v>
+        <v>0</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F146">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G146" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>16.806</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F147">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G147" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46185.4375</v>
+        <v>46213.52083333334</v>
       </c>
       <c r="B148">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>5.244</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F148">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G148" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>26.462</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F149">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G149" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46185.45833333334</v>
+        <v>46213.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
       </c>
       <c r="C150">
-        <v>13.835</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G150" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46185.46875</v>
+        <v>46213.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151">
-        <v>25.903</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F151">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G151" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46185.47916666666</v>
+        <v>46213.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>33.451</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F152">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G152" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46185.48958333334</v>
+        <v>46213.57291666666</v>
       </c>
       <c r="B153">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>2.356</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G153" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46185.5</v>
+        <v>46213.58333333334</v>
       </c>
       <c r="B154">
-        <v>14.029</v>
+        <v>0</v>
       </c>
       <c r="C154">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F154">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G154" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46185.51041666666</v>
+        <v>46213.59375</v>
       </c>
       <c r="B155">
-        <v>0.735</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>0.928</v>
+        <v>0</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4534,21 +4534,21 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G155" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46185.52083333334</v>
+        <v>46213.60416666666</v>
       </c>
       <c r="B156">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4557,21 +4557,21 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G156" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46185.53125</v>
+        <v>46213.61458333334</v>
       </c>
       <c r="B157">
-        <v>0.262</v>
+        <v>0</v>
       </c>
       <c r="C157">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -4580,21 +4580,21 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G157" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46185.54166666666</v>
+        <v>46213.625</v>
       </c>
       <c r="B158">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C158">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -4603,15 +4603,15 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G158" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46185.55208333334</v>
+        <v>46213.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4626,15 +4626,15 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G159" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46185.5625</v>
+        <v>46213.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4649,15 +4649,15 @@
         <v>0</v>
       </c>
       <c r="F160">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G160" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46185.57291666666</v>
+        <v>46213.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4672,15 +4672,15 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G161" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46185.58333333334</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4695,15 +4695,15 @@
         <v>0</v>
       </c>
       <c r="F162">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G162" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46185.59375</v>
+        <v>46213.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4718,15 +4718,15 @@
         <v>0</v>
       </c>
       <c r="F163">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G163" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46185.60416666666</v>
+        <v>46213.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4741,15 +4741,15 @@
         <v>0</v>
       </c>
       <c r="F164">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G164" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46185.61458333334</v>
+        <v>46213.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4764,15 +4764,15 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G165" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46185.625</v>
+        <v>46213.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4787,15 +4787,15 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G166" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46185.63541666666</v>
+        <v>46213.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4810,15 +4810,15 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G167" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46185.64583333334</v>
+        <v>46213.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4833,15 +4833,15 @@
         <v>0</v>
       </c>
       <c r="F168">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G168" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46185.65625</v>
+        <v>46213.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4856,15 +4856,15 @@
         <v>0</v>
       </c>
       <c r="F169">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G169" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46185.66666666666</v>
+        <v>46213.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4879,15 +4879,15 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G170" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46185.67708333334</v>
+        <v>46213.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4902,15 +4902,15 @@
         <v>0</v>
       </c>
       <c r="F171">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G171" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46185.6875</v>
+        <v>46213.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4925,15 +4925,15 @@
         <v>0</v>
       </c>
       <c r="F172">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G172" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46185.69791666666</v>
+        <v>46213.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4948,15 +4948,15 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G173" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46185.70833333334</v>
+        <v>46213.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4971,15 +4971,15 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G174" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46185.71875</v>
+        <v>46213.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4994,15 +4994,15 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G175" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46185.72916666666</v>
+        <v>46213.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5017,15 +5017,15 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G176" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46185.73958333334</v>
+        <v>46213.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5040,15 +5040,15 @@
         <v>0</v>
       </c>
       <c r="F177">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G177" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46185.75</v>
+        <v>46213.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5063,15 +5063,15 @@
         <v>0</v>
       </c>
       <c r="F178">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G178" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46185.76041666666</v>
+        <v>46213.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5086,15 +5086,15 @@
         <v>0</v>
       </c>
       <c r="F179">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G179" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46185.77083333334</v>
+        <v>46213.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5109,15 +5109,15 @@
         <v>0</v>
       </c>
       <c r="F180">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G180" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46185.78125</v>
+        <v>46213.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5132,15 +5132,15 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G181" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46185.79166666666</v>
+        <v>46213.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5155,15 +5155,15 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G182" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46185.80208333334</v>
+        <v>46213.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5178,15 +5178,15 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G183" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46185.8125</v>
+        <v>46213.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5201,15 +5201,15 @@
         <v>0</v>
       </c>
       <c r="F184">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G184" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46185.82291666666</v>
+        <v>46213.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5224,15 +5224,15 @@
         <v>0</v>
       </c>
       <c r="F185">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G185" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46185.83333333334</v>
+        <v>46213.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5247,15 +5247,15 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G186" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46185.84375</v>
+        <v>46213.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5270,15 +5270,15 @@
         <v>0</v>
       </c>
       <c r="F187">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G187" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46185.85416666666</v>
+        <v>46213.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5293,15 +5293,15 @@
         <v>0</v>
       </c>
       <c r="F188">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G188" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46185.86458333334</v>
+        <v>46213.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5316,15 +5316,15 @@
         <v>0</v>
       </c>
       <c r="F189">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G189" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46185.875</v>
+        <v>46213.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5339,15 +5339,15 @@
         <v>0</v>
       </c>
       <c r="F190">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G190" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46185.88541666666</v>
+        <v>46213.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5362,15 +5362,15 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G191" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46185.89583333334</v>
+        <v>46213.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5385,15 +5385,15 @@
         <v>0</v>
       </c>
       <c r="F192">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G192" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46185.90625</v>
+        <v>46213.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5408,193 +5408,9 @@
         <v>0</v>
       </c>
       <c r="F193">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G193" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
-      <c r="A194" s="2">
-        <v>46185.91666666666</v>
-      </c>
-      <c r="B194">
-        <v>0</v>
-      </c>
-      <c r="C194">
-        <v>0</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
-      </c>
-      <c r="E194">
-        <v>0</v>
-      </c>
-      <c r="F194">
-        <v>89</v>
-      </c>
-      <c r="G194" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
-      <c r="A195" s="2">
-        <v>46185.92708333334</v>
-      </c>
-      <c r="B195">
-        <v>0</v>
-      </c>
-      <c r="C195">
-        <v>0</v>
-      </c>
-      <c r="D195">
-        <v>0</v>
-      </c>
-      <c r="E195">
-        <v>0</v>
-      </c>
-      <c r="F195">
-        <v>90</v>
-      </c>
-      <c r="G195" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
-      <c r="A196" s="2">
-        <v>46185.9375</v>
-      </c>
-      <c r="B196">
-        <v>0</v>
-      </c>
-      <c r="C196">
-        <v>0</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="E196">
-        <v>0</v>
-      </c>
-      <c r="F196">
-        <v>91</v>
-      </c>
-      <c r="G196" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
-      <c r="A197" s="2">
-        <v>46185.94791666666</v>
-      </c>
-      <c r="B197">
-        <v>0</v>
-      </c>
-      <c r="C197">
-        <v>0</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="E197">
-        <v>0</v>
-      </c>
-      <c r="F197">
-        <v>92</v>
-      </c>
-      <c r="G197" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
-      <c r="A198" s="2">
-        <v>46185.95833333334</v>
-      </c>
-      <c r="B198">
-        <v>0</v>
-      </c>
-      <c r="C198">
-        <v>0</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="E198">
-        <v>0</v>
-      </c>
-      <c r="F198">
-        <v>93</v>
-      </c>
-      <c r="G198" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
-      <c r="A199" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B199">
-        <v>0</v>
-      </c>
-      <c r="C199">
-        <v>0</v>
-      </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="E199">
-        <v>0</v>
-      </c>
-      <c r="F199">
-        <v>94</v>
-      </c>
-      <c r="G199" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
-      <c r="A200" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B200">
-        <v>0</v>
-      </c>
-      <c r="C200">
-        <v>0</v>
-      </c>
-      <c r="D200">
-        <v>0</v>
-      </c>
-      <c r="E200">
-        <v>0</v>
-      </c>
-      <c r="F200">
-        <v>95</v>
-      </c>
-      <c r="G200" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
-      <c r="A201" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B201">
-        <v>0</v>
-      </c>
-      <c r="C201">
-        <v>0</v>
-      </c>
-      <c r="D201">
-        <v>0</v>
-      </c>
-      <c r="E201">
-        <v>0</v>
-      </c>
-      <c r="F201">
-        <v>96</v>
-      </c>
-      <c r="G201" t="s">
         <v>198</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.07.20261</t>
-  </si>
-  <si>
-    <t>09.07.20262</t>
-  </si>
-  <si>
-    <t>09.07.20263</t>
-  </si>
-  <si>
-    <t>09.07.20264</t>
-  </si>
-  <si>
-    <t>09.07.20265</t>
-  </si>
-  <si>
-    <t>09.07.20266</t>
-  </si>
-  <si>
-    <t>09.07.20267</t>
-  </si>
-  <si>
-    <t>09.07.20268</t>
-  </si>
-  <si>
-    <t>09.07.20269</t>
-  </si>
-  <si>
-    <t>09.07.202610</t>
-  </si>
-  <si>
-    <t>09.07.202611</t>
-  </si>
-  <si>
-    <t>09.07.202612</t>
-  </si>
-  <si>
-    <t>09.07.202613</t>
-  </si>
-  <si>
-    <t>09.07.202614</t>
-  </si>
-  <si>
-    <t>09.07.202615</t>
-  </si>
-  <si>
-    <t>09.07.202616</t>
-  </si>
-  <si>
-    <t>09.07.202617</t>
-  </si>
-  <si>
-    <t>09.07.202618</t>
-  </si>
-  <si>
-    <t>09.07.202619</t>
-  </si>
-  <si>
-    <t>09.07.202620</t>
-  </si>
-  <si>
-    <t>09.07.202621</t>
-  </si>
-  <si>
-    <t>09.07.202622</t>
-  </si>
-  <si>
-    <t>09.07.202623</t>
-  </si>
-  <si>
-    <t>09.07.202624</t>
-  </si>
-  <si>
-    <t>09.07.202625</t>
-  </si>
-  <si>
-    <t>09.07.202626</t>
-  </si>
-  <si>
-    <t>09.07.202627</t>
-  </si>
-  <si>
-    <t>09.07.202628</t>
-  </si>
-  <si>
-    <t>09.07.202629</t>
-  </si>
-  <si>
-    <t>09.07.202630</t>
-  </si>
-  <si>
-    <t>09.07.202631</t>
-  </si>
-  <si>
-    <t>09.07.202632</t>
-  </si>
-  <si>
-    <t>09.07.202633</t>
-  </si>
-  <si>
-    <t>09.07.202634</t>
-  </si>
-  <si>
-    <t>09.07.202635</t>
-  </si>
-  <si>
-    <t>09.07.202636</t>
-  </si>
-  <si>
-    <t>09.07.202637</t>
-  </si>
-  <si>
-    <t>09.07.202638</t>
-  </si>
-  <si>
-    <t>09.07.202639</t>
-  </si>
-  <si>
-    <t>09.07.202640</t>
-  </si>
-  <si>
-    <t>09.07.202641</t>
-  </si>
-  <si>
-    <t>09.07.202642</t>
-  </si>
-  <si>
-    <t>09.07.202643</t>
-  </si>
-  <si>
-    <t>09.07.202644</t>
-  </si>
-  <si>
-    <t>09.07.202645</t>
-  </si>
-  <si>
-    <t>09.07.202646</t>
-  </si>
-  <si>
-    <t>09.07.202647</t>
-  </si>
-  <si>
-    <t>09.07.202648</t>
-  </si>
-  <si>
-    <t>09.07.202649</t>
-  </si>
-  <si>
-    <t>09.07.202650</t>
-  </si>
-  <si>
-    <t>09.07.202651</t>
-  </si>
-  <si>
-    <t>09.07.202652</t>
-  </si>
-  <si>
-    <t>09.07.202653</t>
-  </si>
-  <si>
-    <t>09.07.202654</t>
-  </si>
-  <si>
-    <t>09.07.202655</t>
-  </si>
-  <si>
-    <t>09.07.202656</t>
-  </si>
-  <si>
-    <t>09.07.202657</t>
-  </si>
-  <si>
-    <t>09.07.202658</t>
-  </si>
-  <si>
-    <t>09.07.202659</t>
-  </si>
-  <si>
-    <t>09.07.202660</t>
-  </si>
-  <si>
-    <t>09.07.202661</t>
-  </si>
-  <si>
-    <t>09.07.202662</t>
-  </si>
-  <si>
-    <t>09.07.202663</t>
-  </si>
-  <si>
-    <t>09.07.202664</t>
-  </si>
-  <si>
-    <t>09.07.202665</t>
-  </si>
-  <si>
-    <t>09.07.202666</t>
-  </si>
-  <si>
-    <t>09.07.202667</t>
-  </si>
-  <si>
-    <t>09.07.202668</t>
-  </si>
-  <si>
-    <t>09.07.202669</t>
-  </si>
-  <si>
-    <t>09.07.202670</t>
-  </si>
-  <si>
-    <t>09.07.202671</t>
-  </si>
-  <si>
-    <t>09.07.202672</t>
-  </si>
-  <si>
-    <t>09.07.202673</t>
-  </si>
-  <si>
-    <t>09.07.202674</t>
-  </si>
-  <si>
-    <t>09.07.202675</t>
-  </si>
-  <si>
-    <t>09.07.202676</t>
-  </si>
-  <si>
-    <t>09.07.202677</t>
-  </si>
-  <si>
-    <t>09.07.202678</t>
-  </si>
-  <si>
-    <t>09.07.202679</t>
-  </si>
-  <si>
-    <t>09.07.202680</t>
-  </si>
-  <si>
-    <t>09.07.202681</t>
-  </si>
-  <si>
-    <t>09.07.202682</t>
-  </si>
-  <si>
-    <t>09.07.202683</t>
-  </si>
-  <si>
-    <t>09.07.202684</t>
-  </si>
-  <si>
-    <t>09.07.202685</t>
-  </si>
-  <si>
-    <t>09.07.202686</t>
-  </si>
-  <si>
-    <t>09.07.202687</t>
-  </si>
-  <si>
-    <t>09.07.202688</t>
-  </si>
-  <si>
-    <t>09.07.202689</t>
-  </si>
-  <si>
-    <t>09.07.202690</t>
-  </si>
-  <si>
-    <t>09.07.202691</t>
-  </si>
-  <si>
-    <t>09.07.202692</t>
-  </si>
-  <si>
-    <t>09.07.202693</t>
-  </si>
-  <si>
-    <t>09.07.202694</t>
-  </si>
-  <si>
-    <t>09.07.202695</t>
-  </si>
-  <si>
-    <t>09.07.202696</t>
-  </si>
-  <si>
     <t>10.07.20261</t>
   </si>
   <si>
@@ -611,6 +323,870 @@
   </si>
   <si>
     <t>10.07.202696</t>
+  </si>
+  <si>
+    <t>11.07.20261</t>
+  </si>
+  <si>
+    <t>11.07.20262</t>
+  </si>
+  <si>
+    <t>11.07.20263</t>
+  </si>
+  <si>
+    <t>11.07.20264</t>
+  </si>
+  <si>
+    <t>11.07.20265</t>
+  </si>
+  <si>
+    <t>11.07.20266</t>
+  </si>
+  <si>
+    <t>11.07.20267</t>
+  </si>
+  <si>
+    <t>11.07.20268</t>
+  </si>
+  <si>
+    <t>11.07.20269</t>
+  </si>
+  <si>
+    <t>11.07.202610</t>
+  </si>
+  <si>
+    <t>11.07.202611</t>
+  </si>
+  <si>
+    <t>11.07.202612</t>
+  </si>
+  <si>
+    <t>11.07.202613</t>
+  </si>
+  <si>
+    <t>11.07.202614</t>
+  </si>
+  <si>
+    <t>11.07.202615</t>
+  </si>
+  <si>
+    <t>11.07.202616</t>
+  </si>
+  <si>
+    <t>11.07.202617</t>
+  </si>
+  <si>
+    <t>11.07.202618</t>
+  </si>
+  <si>
+    <t>11.07.202619</t>
+  </si>
+  <si>
+    <t>11.07.202620</t>
+  </si>
+  <si>
+    <t>11.07.202621</t>
+  </si>
+  <si>
+    <t>11.07.202622</t>
+  </si>
+  <si>
+    <t>11.07.202623</t>
+  </si>
+  <si>
+    <t>11.07.202624</t>
+  </si>
+  <si>
+    <t>11.07.202625</t>
+  </si>
+  <si>
+    <t>11.07.202626</t>
+  </si>
+  <si>
+    <t>11.07.202627</t>
+  </si>
+  <si>
+    <t>11.07.202628</t>
+  </si>
+  <si>
+    <t>11.07.202629</t>
+  </si>
+  <si>
+    <t>11.07.202630</t>
+  </si>
+  <si>
+    <t>11.07.202631</t>
+  </si>
+  <si>
+    <t>11.07.202632</t>
+  </si>
+  <si>
+    <t>11.07.202633</t>
+  </si>
+  <si>
+    <t>11.07.202634</t>
+  </si>
+  <si>
+    <t>11.07.202635</t>
+  </si>
+  <si>
+    <t>11.07.202636</t>
+  </si>
+  <si>
+    <t>11.07.202637</t>
+  </si>
+  <si>
+    <t>11.07.202638</t>
+  </si>
+  <si>
+    <t>11.07.202639</t>
+  </si>
+  <si>
+    <t>11.07.202640</t>
+  </si>
+  <si>
+    <t>11.07.202641</t>
+  </si>
+  <si>
+    <t>11.07.202642</t>
+  </si>
+  <si>
+    <t>11.07.202643</t>
+  </si>
+  <si>
+    <t>11.07.202644</t>
+  </si>
+  <si>
+    <t>11.07.202645</t>
+  </si>
+  <si>
+    <t>11.07.202646</t>
+  </si>
+  <si>
+    <t>11.07.202647</t>
+  </si>
+  <si>
+    <t>11.07.202648</t>
+  </si>
+  <si>
+    <t>11.07.202649</t>
+  </si>
+  <si>
+    <t>11.07.202650</t>
+  </si>
+  <si>
+    <t>11.07.202651</t>
+  </si>
+  <si>
+    <t>11.07.202652</t>
+  </si>
+  <si>
+    <t>11.07.202653</t>
+  </si>
+  <si>
+    <t>11.07.202654</t>
+  </si>
+  <si>
+    <t>11.07.202655</t>
+  </si>
+  <si>
+    <t>11.07.202656</t>
+  </si>
+  <si>
+    <t>11.07.202657</t>
+  </si>
+  <si>
+    <t>11.07.202658</t>
+  </si>
+  <si>
+    <t>11.07.202659</t>
+  </si>
+  <si>
+    <t>11.07.202660</t>
+  </si>
+  <si>
+    <t>11.07.202661</t>
+  </si>
+  <si>
+    <t>11.07.202662</t>
+  </si>
+  <si>
+    <t>11.07.202663</t>
+  </si>
+  <si>
+    <t>11.07.202664</t>
+  </si>
+  <si>
+    <t>11.07.202665</t>
+  </si>
+  <si>
+    <t>11.07.202666</t>
+  </si>
+  <si>
+    <t>11.07.202667</t>
+  </si>
+  <si>
+    <t>11.07.202668</t>
+  </si>
+  <si>
+    <t>11.07.202669</t>
+  </si>
+  <si>
+    <t>11.07.202670</t>
+  </si>
+  <si>
+    <t>11.07.202671</t>
+  </si>
+  <si>
+    <t>11.07.202672</t>
+  </si>
+  <si>
+    <t>11.07.202673</t>
+  </si>
+  <si>
+    <t>11.07.202674</t>
+  </si>
+  <si>
+    <t>11.07.202675</t>
+  </si>
+  <si>
+    <t>11.07.202676</t>
+  </si>
+  <si>
+    <t>11.07.202677</t>
+  </si>
+  <si>
+    <t>11.07.202678</t>
+  </si>
+  <si>
+    <t>11.07.202679</t>
+  </si>
+  <si>
+    <t>11.07.202680</t>
+  </si>
+  <si>
+    <t>11.07.202681</t>
+  </si>
+  <si>
+    <t>11.07.202682</t>
+  </si>
+  <si>
+    <t>11.07.202683</t>
+  </si>
+  <si>
+    <t>11.07.202684</t>
+  </si>
+  <si>
+    <t>11.07.202685</t>
+  </si>
+  <si>
+    <t>11.07.202686</t>
+  </si>
+  <si>
+    <t>11.07.202687</t>
+  </si>
+  <si>
+    <t>11.07.202688</t>
+  </si>
+  <si>
+    <t>11.07.202689</t>
+  </si>
+  <si>
+    <t>11.07.202690</t>
+  </si>
+  <si>
+    <t>11.07.202691</t>
+  </si>
+  <si>
+    <t>11.07.202692</t>
+  </si>
+  <si>
+    <t>11.07.202693</t>
+  </si>
+  <si>
+    <t>11.07.202694</t>
+  </si>
+  <si>
+    <t>11.07.202695</t>
+  </si>
+  <si>
+    <t>11.07.202696</t>
+  </si>
+  <si>
+    <t>12.07.20261</t>
+  </si>
+  <si>
+    <t>12.07.20262</t>
+  </si>
+  <si>
+    <t>12.07.20263</t>
+  </si>
+  <si>
+    <t>12.07.20264</t>
+  </si>
+  <si>
+    <t>12.07.20265</t>
+  </si>
+  <si>
+    <t>12.07.20266</t>
+  </si>
+  <si>
+    <t>12.07.20267</t>
+  </si>
+  <si>
+    <t>12.07.20268</t>
+  </si>
+  <si>
+    <t>12.07.20269</t>
+  </si>
+  <si>
+    <t>12.07.202610</t>
+  </si>
+  <si>
+    <t>12.07.202611</t>
+  </si>
+  <si>
+    <t>12.07.202612</t>
+  </si>
+  <si>
+    <t>12.07.202613</t>
+  </si>
+  <si>
+    <t>12.07.202614</t>
+  </si>
+  <si>
+    <t>12.07.202615</t>
+  </si>
+  <si>
+    <t>12.07.202616</t>
+  </si>
+  <si>
+    <t>12.07.202617</t>
+  </si>
+  <si>
+    <t>12.07.202618</t>
+  </si>
+  <si>
+    <t>12.07.202619</t>
+  </si>
+  <si>
+    <t>12.07.202620</t>
+  </si>
+  <si>
+    <t>12.07.202621</t>
+  </si>
+  <si>
+    <t>12.07.202622</t>
+  </si>
+  <si>
+    <t>12.07.202623</t>
+  </si>
+  <si>
+    <t>12.07.202624</t>
+  </si>
+  <si>
+    <t>12.07.202625</t>
+  </si>
+  <si>
+    <t>12.07.202626</t>
+  </si>
+  <si>
+    <t>12.07.202627</t>
+  </si>
+  <si>
+    <t>12.07.202628</t>
+  </si>
+  <si>
+    <t>12.07.202629</t>
+  </si>
+  <si>
+    <t>12.07.202630</t>
+  </si>
+  <si>
+    <t>12.07.202631</t>
+  </si>
+  <si>
+    <t>12.07.202632</t>
+  </si>
+  <si>
+    <t>12.07.202633</t>
+  </si>
+  <si>
+    <t>12.07.202634</t>
+  </si>
+  <si>
+    <t>12.07.202635</t>
+  </si>
+  <si>
+    <t>12.07.202636</t>
+  </si>
+  <si>
+    <t>12.07.202637</t>
+  </si>
+  <si>
+    <t>12.07.202638</t>
+  </si>
+  <si>
+    <t>12.07.202639</t>
+  </si>
+  <si>
+    <t>12.07.202640</t>
+  </si>
+  <si>
+    <t>12.07.202641</t>
+  </si>
+  <si>
+    <t>12.07.202642</t>
+  </si>
+  <si>
+    <t>12.07.202643</t>
+  </si>
+  <si>
+    <t>12.07.202644</t>
+  </si>
+  <si>
+    <t>12.07.202645</t>
+  </si>
+  <si>
+    <t>12.07.202646</t>
+  </si>
+  <si>
+    <t>12.07.202647</t>
+  </si>
+  <si>
+    <t>12.07.202648</t>
+  </si>
+  <si>
+    <t>12.07.202649</t>
+  </si>
+  <si>
+    <t>12.07.202650</t>
+  </si>
+  <si>
+    <t>12.07.202651</t>
+  </si>
+  <si>
+    <t>12.07.202652</t>
+  </si>
+  <si>
+    <t>12.07.202653</t>
+  </si>
+  <si>
+    <t>12.07.202654</t>
+  </si>
+  <si>
+    <t>12.07.202655</t>
+  </si>
+  <si>
+    <t>12.07.202656</t>
+  </si>
+  <si>
+    <t>12.07.202657</t>
+  </si>
+  <si>
+    <t>12.07.202658</t>
+  </si>
+  <si>
+    <t>12.07.202659</t>
+  </si>
+  <si>
+    <t>12.07.202660</t>
+  </si>
+  <si>
+    <t>12.07.202661</t>
+  </si>
+  <si>
+    <t>12.07.202662</t>
+  </si>
+  <si>
+    <t>12.07.202663</t>
+  </si>
+  <si>
+    <t>12.07.202664</t>
+  </si>
+  <si>
+    <t>12.07.202665</t>
+  </si>
+  <si>
+    <t>12.07.202666</t>
+  </si>
+  <si>
+    <t>12.07.202667</t>
+  </si>
+  <si>
+    <t>12.07.202668</t>
+  </si>
+  <si>
+    <t>12.07.202669</t>
+  </si>
+  <si>
+    <t>12.07.202670</t>
+  </si>
+  <si>
+    <t>12.07.202671</t>
+  </si>
+  <si>
+    <t>12.07.202672</t>
+  </si>
+  <si>
+    <t>12.07.202673</t>
+  </si>
+  <si>
+    <t>12.07.202674</t>
+  </si>
+  <si>
+    <t>12.07.202675</t>
+  </si>
+  <si>
+    <t>12.07.202676</t>
+  </si>
+  <si>
+    <t>12.07.202677</t>
+  </si>
+  <si>
+    <t>12.07.202678</t>
+  </si>
+  <si>
+    <t>12.07.202679</t>
+  </si>
+  <si>
+    <t>12.07.202680</t>
+  </si>
+  <si>
+    <t>12.07.202681</t>
+  </si>
+  <si>
+    <t>12.07.202682</t>
+  </si>
+  <si>
+    <t>12.07.202683</t>
+  </si>
+  <si>
+    <t>12.07.202684</t>
+  </si>
+  <si>
+    <t>12.07.202685</t>
+  </si>
+  <si>
+    <t>12.07.202686</t>
+  </si>
+  <si>
+    <t>12.07.202687</t>
+  </si>
+  <si>
+    <t>12.07.202688</t>
+  </si>
+  <si>
+    <t>12.07.202689</t>
+  </si>
+  <si>
+    <t>12.07.202690</t>
+  </si>
+  <si>
+    <t>12.07.202691</t>
+  </si>
+  <si>
+    <t>12.07.202692</t>
+  </si>
+  <si>
+    <t>12.07.202693</t>
+  </si>
+  <si>
+    <t>12.07.202694</t>
+  </si>
+  <si>
+    <t>12.07.202695</t>
+  </si>
+  <si>
+    <t>12.07.202696</t>
+  </si>
+  <si>
+    <t>13.07.20261</t>
+  </si>
+  <si>
+    <t>13.07.20262</t>
+  </si>
+  <si>
+    <t>13.07.20263</t>
+  </si>
+  <si>
+    <t>13.07.20264</t>
+  </si>
+  <si>
+    <t>13.07.20265</t>
+  </si>
+  <si>
+    <t>13.07.20266</t>
+  </si>
+  <si>
+    <t>13.07.20267</t>
+  </si>
+  <si>
+    <t>13.07.20268</t>
+  </si>
+  <si>
+    <t>13.07.20269</t>
+  </si>
+  <si>
+    <t>13.07.202610</t>
+  </si>
+  <si>
+    <t>13.07.202611</t>
+  </si>
+  <si>
+    <t>13.07.202612</t>
+  </si>
+  <si>
+    <t>13.07.202613</t>
+  </si>
+  <si>
+    <t>13.07.202614</t>
+  </si>
+  <si>
+    <t>13.07.202615</t>
+  </si>
+  <si>
+    <t>13.07.202616</t>
+  </si>
+  <si>
+    <t>13.07.202617</t>
+  </si>
+  <si>
+    <t>13.07.202618</t>
+  </si>
+  <si>
+    <t>13.07.202619</t>
+  </si>
+  <si>
+    <t>13.07.202620</t>
+  </si>
+  <si>
+    <t>13.07.202621</t>
+  </si>
+  <si>
+    <t>13.07.202622</t>
+  </si>
+  <si>
+    <t>13.07.202623</t>
+  </si>
+  <si>
+    <t>13.07.202624</t>
+  </si>
+  <si>
+    <t>13.07.202625</t>
+  </si>
+  <si>
+    <t>13.07.202626</t>
+  </si>
+  <si>
+    <t>13.07.202627</t>
+  </si>
+  <si>
+    <t>13.07.202628</t>
+  </si>
+  <si>
+    <t>13.07.202629</t>
+  </si>
+  <si>
+    <t>13.07.202630</t>
+  </si>
+  <si>
+    <t>13.07.202631</t>
+  </si>
+  <si>
+    <t>13.07.202632</t>
+  </si>
+  <si>
+    <t>13.07.202633</t>
+  </si>
+  <si>
+    <t>13.07.202634</t>
+  </si>
+  <si>
+    <t>13.07.202635</t>
+  </si>
+  <si>
+    <t>13.07.202636</t>
+  </si>
+  <si>
+    <t>13.07.202637</t>
+  </si>
+  <si>
+    <t>13.07.202638</t>
+  </si>
+  <si>
+    <t>13.07.202639</t>
+  </si>
+  <si>
+    <t>13.07.202640</t>
+  </si>
+  <si>
+    <t>13.07.202641</t>
+  </si>
+  <si>
+    <t>13.07.202642</t>
+  </si>
+  <si>
+    <t>13.07.202643</t>
+  </si>
+  <si>
+    <t>13.07.202644</t>
+  </si>
+  <si>
+    <t>13.07.202645</t>
+  </si>
+  <si>
+    <t>13.07.202646</t>
+  </si>
+  <si>
+    <t>13.07.202647</t>
+  </si>
+  <si>
+    <t>13.07.202648</t>
+  </si>
+  <si>
+    <t>13.07.202649</t>
+  </si>
+  <si>
+    <t>13.07.202650</t>
+  </si>
+  <si>
+    <t>13.07.202651</t>
+  </si>
+  <si>
+    <t>13.07.202652</t>
+  </si>
+  <si>
+    <t>13.07.202653</t>
+  </si>
+  <si>
+    <t>13.07.202654</t>
+  </si>
+  <si>
+    <t>13.07.202655</t>
+  </si>
+  <si>
+    <t>13.07.202656</t>
+  </si>
+  <si>
+    <t>13.07.202657</t>
+  </si>
+  <si>
+    <t>13.07.202658</t>
+  </si>
+  <si>
+    <t>13.07.202659</t>
+  </si>
+  <si>
+    <t>13.07.202660</t>
+  </si>
+  <si>
+    <t>13.07.202661</t>
+  </si>
+  <si>
+    <t>13.07.202662</t>
+  </si>
+  <si>
+    <t>13.07.202663</t>
+  </si>
+  <si>
+    <t>13.07.202664</t>
+  </si>
+  <si>
+    <t>13.07.202665</t>
+  </si>
+  <si>
+    <t>13.07.202666</t>
+  </si>
+  <si>
+    <t>13.07.202667</t>
+  </si>
+  <si>
+    <t>13.07.202668</t>
+  </si>
+  <si>
+    <t>13.07.202669</t>
+  </si>
+  <si>
+    <t>13.07.202670</t>
+  </si>
+  <si>
+    <t>13.07.202671</t>
+  </si>
+  <si>
+    <t>13.07.202672</t>
+  </si>
+  <si>
+    <t>13.07.202673</t>
+  </si>
+  <si>
+    <t>13.07.202674</t>
+  </si>
+  <si>
+    <t>13.07.202675</t>
+  </si>
+  <si>
+    <t>13.07.202676</t>
+  </si>
+  <si>
+    <t>13.07.202677</t>
+  </si>
+  <si>
+    <t>13.07.202678</t>
+  </si>
+  <si>
+    <t>13.07.202679</t>
+  </si>
+  <si>
+    <t>13.07.202680</t>
+  </si>
+  <si>
+    <t>13.07.202681</t>
+  </si>
+  <si>
+    <t>13.07.202682</t>
+  </si>
+  <si>
+    <t>13.07.202683</t>
+  </si>
+  <si>
+    <t>13.07.202684</t>
+  </si>
+  <si>
+    <t>13.07.202685</t>
+  </si>
+  <si>
+    <t>13.07.202686</t>
+  </si>
+  <si>
+    <t>13.07.202687</t>
+  </si>
+  <si>
+    <t>13.07.202688</t>
+  </si>
+  <si>
+    <t>13.07.202689</t>
+  </si>
+  <si>
+    <t>13.07.202690</t>
+  </si>
+  <si>
+    <t>13.07.202691</t>
+  </si>
+  <si>
+    <t>13.07.202692</t>
+  </si>
+  <si>
+    <t>13.07.202693</t>
+  </si>
+  <si>
+    <t>13.07.202694</t>
+  </si>
+  <si>
+    <t>13.07.202695</t>
+  </si>
+  <si>
+    <t>13.07.202696</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1000,19 +1576,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B2">
-        <v>0.146</v>
+        <v>45.538</v>
       </c>
       <c r="C2">
-        <v>0.314</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1023,19 +1599,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46212.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.763</v>
+        <v>36.447</v>
       </c>
       <c r="C3">
-        <v>1.396</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1046,19 +1622,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46212.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>6.768</v>
       </c>
       <c r="C4">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1069,19 +1645,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46212.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="C5">
-        <v>10.547</v>
+        <v>1.475</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1092,13 +1668,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46212.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="C6">
-        <v>3.692</v>
+        <v>10.46</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1691,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46212.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>54.574</v>
+        <v>51.595</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,19 +1714,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46212.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>43.413</v>
+        <v>61.304</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,19 +1737,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46212.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>26.29</v>
+        <v>18.269</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1184,19 +1760,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46212.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>13.058</v>
+        <v>40.153</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>49.25</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1207,19 +1783,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46212.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.131</v>
+        <v>22.733</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1230,19 +1806,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46212.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>16.249</v>
+        <v>4.519</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1253,19 +1829,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46212.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>39.624</v>
+        <v>14.023</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1852,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46212.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>34.589</v>
+        <v>15.429</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>67.25</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1875,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46212.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>25.745</v>
+        <v>7.554</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,19 +1898,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46212.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>27.749</v>
+        <v>3.829</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1345,19 +1921,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46212.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>31.275</v>
+        <v>14.001</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>54.25</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -1368,19 +1944,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46212.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.411</v>
       </c>
       <c r="C18">
-        <v>14.294</v>
+        <v>1.883</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>54.25</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1391,19 +1967,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46212.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>5.056</v>
       </c>
       <c r="C19">
-        <v>16.403</v>
+        <v>0.017</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>54.25</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,19 +1990,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46212.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="C20">
-        <v>32.099</v>
+        <v>0.066</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,19 +2013,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46212.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.035</v>
+        <v>0.374</v>
       </c>
       <c r="C21">
-        <v>10.827</v>
+        <v>0.108</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +2036,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46212.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.011</v>
+        <v>9.118</v>
       </c>
       <c r="C22">
-        <v>0.181</v>
+        <v>0.002</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,10 +2059,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46212.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>9.443</v>
+        <v>4.583</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1495,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>26.75</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -1506,19 +2082,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46212.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="C24">
-        <v>2.153</v>
+        <v>8.582000000000001</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -1529,19 +2105,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46212.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.227</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1.777</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -1552,19 +2128,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46212.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>13.932</v>
+        <v>0.151</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>25</v>
@@ -1575,19 +2151,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46212.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.599</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1.091</v>
+        <v>18.275</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,13 +2174,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46212.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>12.484</v>
+        <v>14.175</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +2197,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46212.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="C29">
-        <v>30.94</v>
+        <v>2.012</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +2220,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46212.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="C30">
-        <v>5.074</v>
+        <v>0.573</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,19 +2243,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46212.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="C31">
-        <v>10.536</v>
+        <v>2.338</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -1690,19 +2266,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46212.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>7.045</v>
+        <v>15.802</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1713,19 +2289,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46212.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.615</v>
+        <v>38.989</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -1736,19 +2312,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46212.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B34">
-        <v>4.129</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.679</v>
+        <v>26.274</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +2335,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46212.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>35.28</v>
+        <v>21.358</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +2358,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46212.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="C36">
-        <v>15.912</v>
+        <v>1.815</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>35.25</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +2381,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46212.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="C37">
-        <v>30.704</v>
+        <v>11.306</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>35.25</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +2404,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46212.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>26.314</v>
+        <v>14.277</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>25.75</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +2427,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46212.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>35.061</v>
+        <v>13.013</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>23.25</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +2450,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46212.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>16.117</v>
+        <v>20.271</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>61.25</v>
+        <v>17.5</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +2473,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46212.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>13.427</v>
+        <v>40.873</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>62.5</v>
+        <v>17.5</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +2496,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46212.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B42">
-        <v>2.445</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>4.69</v>
+        <v>57.036</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>62.5</v>
+        <v>32.5</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +2519,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46212.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B43">
-        <v>3.677</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.02</v>
+        <v>25.216</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +2542,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46212.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>8.499000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="C44">
-        <v>0.003</v>
+        <v>10.113</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>37.5</v>
+        <v>57.5</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +2565,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46212.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B45">
-        <v>4.386</v>
+        <v>0.473</v>
       </c>
       <c r="C45">
-        <v>0.046</v>
+        <v>1.895</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>37.5</v>
+        <v>49.5</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,13 +2588,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46212.45833333334</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B46">
-        <v>1.061</v>
+        <v>5.074</v>
       </c>
       <c r="C46">
-        <v>0.216</v>
+        <v>4.034</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2035,19 +2611,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46212.46875</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>10.92</v>
+        <v>5.771</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>3.524</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>20.75</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,10 +2634,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46212.47916666666</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B48">
-        <v>8.124000000000001</v>
+        <v>4.941</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2070,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>20.75</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2657,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46212.48958333334</v>
+        <v>46213.48958333334</v>
       </c>
       <c r="B49">
-        <v>21.533</v>
+        <v>4.821</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>20.75</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2680,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46212.5</v>
+        <v>46213.5</v>
       </c>
       <c r="B50">
-        <v>1.303</v>
+        <v>6.657</v>
       </c>
       <c r="C50">
-        <v>0.056</v>
+        <v>0.023</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2703,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46212.51041666666</v>
+        <v>46213.51041666666</v>
       </c>
       <c r="B51">
-        <v>8.038</v>
+        <v>17.702</v>
       </c>
       <c r="C51">
-        <v>0.135</v>
+        <v>0.004</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,16 +2726,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46212.52083333334</v>
+        <v>46213.52083333334</v>
       </c>
       <c r="B52">
-        <v>10.206</v>
+        <v>3.194</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>38.75</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2173,16 +2749,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46212.53125</v>
+        <v>46213.53125</v>
       </c>
       <c r="B53">
-        <v>4.522</v>
+        <v>10.372</v>
       </c>
       <c r="C53">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2196,16 +2772,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46212.54166666666</v>
+        <v>46213.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.004</v>
+        <v>1.084</v>
       </c>
       <c r="C54">
-        <v>8.994</v>
+        <v>0.105</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2219,16 +2795,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46212.55208333334</v>
+        <v>46213.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="C55">
-        <v>1.498</v>
+        <v>0.429</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2242,16 +2818,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46212.5625</v>
+        <v>46213.5625</v>
       </c>
       <c r="B56">
-        <v>0.033</v>
+        <v>0.828</v>
       </c>
       <c r="C56">
-        <v>1.354</v>
+        <v>0.18</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2265,16 +2841,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46212.57291666666</v>
+        <v>46213.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.437</v>
+        <v>1.49</v>
       </c>
       <c r="C57">
-        <v>0.359</v>
+        <v>0.175</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2288,16 +2864,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46212.58333333334</v>
+        <v>46213.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.063</v>
+        <v>0.674</v>
       </c>
       <c r="C58">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2311,16 +2887,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46212.59375</v>
+        <v>46213.59375</v>
       </c>
       <c r="B59">
-        <v>1.188</v>
+        <v>0.57</v>
       </c>
       <c r="C59">
-        <v>0.047</v>
+        <v>1.148</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2334,13 +2910,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46212.60416666666</v>
+        <v>46213.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.157</v>
+        <v>0.621</v>
       </c>
       <c r="C60">
-        <v>4.318</v>
+        <v>0.225</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2933,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46212.61458333334</v>
+        <v>46213.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>9.715</v>
       </c>
       <c r="C61">
-        <v>24.207</v>
+        <v>0.039</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2956,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46212.625</v>
+        <v>46213.625</v>
       </c>
       <c r="B62">
-        <v>0.72</v>
+        <v>0.417</v>
       </c>
       <c r="C62">
-        <v>22.134</v>
+        <v>0.453</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2979,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46212.63541666666</v>
+        <v>46213.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.196</v>
+        <v>0.045</v>
       </c>
       <c r="C63">
-        <v>5.768</v>
+        <v>1.058</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,13 +3002,13 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46212.64583333334</v>
+        <v>46213.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>14.072</v>
+        <v>9.641</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2449,13 +3025,13 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46212.65625</v>
+        <v>46213.65625</v>
       </c>
       <c r="B65">
-        <v>6.39</v>
+        <v>0.443</v>
       </c>
       <c r="C65">
-        <v>4.319</v>
+        <v>2.175</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2472,13 +3048,13 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46212.66666666666</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="B66">
-        <v>5.142</v>
+        <v>0.207</v>
       </c>
       <c r="C66">
-        <v>1.221</v>
+        <v>0.65</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2495,13 +3071,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46212.67708333334</v>
+        <v>46213.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>3.199</v>
+        <v>16.212</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2518,13 +3094,13 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46212.6875</v>
+        <v>46213.6875</v>
       </c>
       <c r="B68">
-        <v>2.455</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>6.106</v>
+        <v>18.618</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2541,13 +3117,13 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46212.69791666666</v>
+        <v>46213.69791666666</v>
       </c>
       <c r="B69">
-        <v>2.445</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>0.306</v>
+        <v>28.287</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2564,13 +3140,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46212.70833333334</v>
+        <v>46213.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>19.671</v>
+        <v>91.855</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,19 +3163,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46212.71875</v>
+        <v>46213.71875</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>3.571</v>
+        <v>71.643</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>29.25</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2610,19 +3186,19 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46212.72916666666</v>
+        <v>46213.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.915</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>0.911</v>
+        <v>28.803</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>29.25</v>
+        <v>22.5</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -2633,19 +3209,19 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46212.73958333334</v>
+        <v>46213.73958333334</v>
       </c>
       <c r="B73">
-        <v>3.285</v>
+        <v>6.694</v>
       </c>
       <c r="C73">
-        <v>0.035</v>
+        <v>3.772</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>29.25</v>
+        <v>22.5</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -2656,19 +3232,19 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46212.75</v>
+        <v>46213.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="C74">
-        <v>27.046</v>
+        <v>0.123</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -2679,19 +3255,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46212.76041666666</v>
+        <v>46213.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.006</v>
+        <v>4.648</v>
       </c>
       <c r="C75">
-        <v>20.866</v>
+        <v>2.458</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>33.75</v>
+        <v>22.5</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -2702,19 +3278,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46212.77083333334</v>
+        <v>46213.77083333334</v>
       </c>
       <c r="B76">
-        <v>2.436</v>
+        <v>28.417</v>
       </c>
       <c r="C76">
-        <v>2.969</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>58.75</v>
+        <v>25</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,10 +3301,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46212.78125</v>
+        <v>46213.78125</v>
       </c>
       <c r="B77">
-        <v>11.099</v>
+        <v>19.063</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2737,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>58.75</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +3324,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46212.79166666666</v>
+        <v>46213.79166666666</v>
       </c>
       <c r="B78">
-        <v>13.617</v>
+        <v>2.056</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>58.75</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,10 +3347,10 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46212.80208333334</v>
+        <v>46213.80208333334</v>
       </c>
       <c r="B79">
-        <v>19.712</v>
+        <v>17.79</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2783,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>58.75</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,10 +3370,10 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46212.8125</v>
+        <v>46213.8125</v>
       </c>
       <c r="B80">
-        <v>32.044</v>
+        <v>7.657</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2806,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,13 +3393,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46212.82291666666</v>
+        <v>46213.82291666666</v>
       </c>
       <c r="B81">
-        <v>9.464</v>
+        <v>3.384</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,13 +3416,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46212.83333333334</v>
+        <v>46213.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.493</v>
+        <v>3.034</v>
       </c>
       <c r="C82">
-        <v>2.381</v>
+        <v>0.112</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +3439,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46212.84375</v>
+        <v>46213.84375</v>
       </c>
       <c r="B83">
-        <v>3.286</v>
+        <v>21.592</v>
       </c>
       <c r="C83">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +3462,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46212.85416666666</v>
+        <v>46213.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.13</v>
+        <v>25.342</v>
       </c>
       <c r="C84">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +3485,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46212.86458333334</v>
+        <v>46213.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.06900000000000001</v>
+        <v>15.297</v>
       </c>
       <c r="C85">
-        <v>0.791</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +3508,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46212.875</v>
+        <v>46213.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>19.959</v>
       </c>
       <c r="C86">
-        <v>50.921</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,19 +3531,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46212.88541666666</v>
+        <v>46213.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>5.859</v>
       </c>
       <c r="C87">
-        <v>90.926</v>
+        <v>0.012</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>31.5</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +3554,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46212.89583333334</v>
+        <v>46213.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>6.575</v>
       </c>
       <c r="C88">
-        <v>74.521</v>
+        <v>0.001</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>31.5</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3577,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46212.90625</v>
+        <v>46213.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>12.449</v>
       </c>
       <c r="C89">
-        <v>17.551</v>
+        <v>0.011</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3600,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46212.91666666666</v>
+        <v>46213.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.655</v>
+        <v>25.447</v>
       </c>
       <c r="C90">
-        <v>3.279</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,19 +3623,19 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46212.92708333334</v>
+        <v>46213.92708333334</v>
       </c>
       <c r="B91">
-        <v>5.91</v>
+        <v>12.342</v>
       </c>
       <c r="C91">
-        <v>0.191</v>
+        <v>0.001</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>90</v>
@@ -3070,19 +3646,19 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46212.9375</v>
+        <v>46213.9375</v>
       </c>
       <c r="B92">
-        <v>0.445</v>
+        <v>11.664</v>
       </c>
       <c r="C92">
-        <v>0.095</v>
+        <v>0.006</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>71.75</v>
+        <v>0</v>
       </c>
       <c r="F92">
         <v>91</v>
@@ -3093,10 +3669,10 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46212.94791666666</v>
+        <v>46213.94791666666</v>
       </c>
       <c r="B93">
-        <v>9.631</v>
+        <v>17.12</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -3105,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="E93">
-        <v>71.75</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -3116,10 +3692,10 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46212.95833333334</v>
+        <v>46213.95833333334</v>
       </c>
       <c r="B94">
-        <v>31.601</v>
+        <v>20.748</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3128,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>93</v>
@@ -3139,10 +3715,10 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46212.96875</v>
+        <v>46213.96875</v>
       </c>
       <c r="B95">
-        <v>38.601</v>
+        <v>12.862</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -3151,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <v>94</v>
@@ -3162,10 +3738,10 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46212.97916666666</v>
+        <v>46213.97916666666</v>
       </c>
       <c r="B96">
-        <v>24.657</v>
+        <v>33.43</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -3174,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -3185,19 +3761,19 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46212.98958333334</v>
+        <v>46213.98958333334</v>
       </c>
       <c r="B97">
-        <v>26.678</v>
+        <v>13.219</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -3208,10 +3784,10 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B98">
-        <v>45.538</v>
+        <v>13.385</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -3220,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -3231,10 +3807,10 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46213.01041666666</v>
+        <v>46214.01041666666</v>
       </c>
       <c r="B99">
-        <v>36.447</v>
+        <v>7.167</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -3243,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -3254,19 +3830,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46213.02083333334</v>
+        <v>46214.02083333334</v>
       </c>
       <c r="B100">
-        <v>6.768</v>
+        <v>0.153</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -3277,19 +3853,19 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46213.03125</v>
+        <v>46214.03125</v>
       </c>
       <c r="B101">
-        <v>0.8110000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C101">
-        <v>1.475</v>
+        <v>0.102</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>4</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46213.04166666666</v>
+        <v>46214.04166666666</v>
       </c>
       <c r="B102">
-        <v>0.028</v>
+        <v>16.725</v>
       </c>
       <c r="C102">
-        <v>10.46</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3899,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46213.05208333334</v>
+        <v>46214.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="C103">
-        <v>51.595</v>
+        <v>0.045</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,19 +3922,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46213.0625</v>
+        <v>46214.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="C104">
-        <v>61.304</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>7</v>
@@ -3369,19 +3945,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46213.07291666666</v>
+        <v>46214.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="C105">
-        <v>18.269</v>
+        <v>0.161</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>8</v>
@@ -3392,19 +3968,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46213.08333333334</v>
+        <v>46214.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>17.32</v>
       </c>
       <c r="C106">
-        <v>40.153</v>
+        <v>0.002</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>49.25</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>9</v>
@@ -3415,19 +3991,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46213.09375</v>
+        <v>46214.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>32.781</v>
       </c>
       <c r="C107">
-        <v>22.733</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>10</v>
@@ -3438,19 +4014,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46213.10416666666</v>
+        <v>46214.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>33.499</v>
       </c>
       <c r="C108">
-        <v>4.519</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>11</v>
@@ -3461,19 +4037,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46213.11458333334</v>
+        <v>46214.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>30.769</v>
       </c>
       <c r="C109">
-        <v>14.023</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>12</v>
@@ -3484,19 +4060,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46213.125</v>
+        <v>46214.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>47.133</v>
       </c>
       <c r="C110">
-        <v>15.429</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>67.25</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>13</v>
@@ -3507,19 +4083,19 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46213.13541666666</v>
+        <v>46214.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>13.119</v>
       </c>
       <c r="C111">
-        <v>7.554</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>14</v>
@@ -3530,19 +4106,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46213.14583333334</v>
+        <v>46214.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>28.274</v>
       </c>
       <c r="C112">
-        <v>3.829</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>15</v>
@@ -3553,19 +4129,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46213.15625</v>
+        <v>46214.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="C113">
-        <v>14.001</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>54.25</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>16</v>
@@ -3576,19 +4152,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46213.16666666666</v>
+        <v>46214.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.411</v>
+        <v>26.728</v>
       </c>
       <c r="C114">
-        <v>1.883</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>54.25</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>17</v>
@@ -3599,19 +4175,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46213.17708333334</v>
+        <v>46214.17708333334</v>
       </c>
       <c r="B115">
-        <v>5.056</v>
+        <v>10.633</v>
       </c>
       <c r="C115">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>54.25</v>
+        <v>0</v>
       </c>
       <c r="F115">
         <v>18</v>
@@ -3622,19 +4198,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46213.1875</v>
+        <v>46214.1875</v>
       </c>
       <c r="B116">
-        <v>1.98</v>
+        <v>0.187</v>
       </c>
       <c r="C116">
-        <v>0.066</v>
+        <v>0.051</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>19</v>
@@ -3645,19 +4221,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46213.19791666666</v>
+        <v>46214.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.374</v>
+        <v>1.164</v>
       </c>
       <c r="C117">
-        <v>0.108</v>
+        <v>0.011</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>20</v>
@@ -3668,19 +4244,19 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46213.20833333334</v>
+        <v>46214.20833333334</v>
       </c>
       <c r="B118">
-        <v>9.118</v>
+        <v>5.07</v>
       </c>
       <c r="C118">
-        <v>0.002</v>
+        <v>0.216</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>21</v>
@@ -3691,10 +4267,10 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46213.21875</v>
+        <v>46214.21875</v>
       </c>
       <c r="B119">
-        <v>4.583</v>
+        <v>8.228</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -3703,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="E119">
-        <v>26.75</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>22</v>
@@ -3714,13 +4290,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46213.22916666666</v>
+        <v>46214.22916666666</v>
       </c>
       <c r="B120">
-        <v>0.025</v>
+        <v>1.229</v>
       </c>
       <c r="C120">
-        <v>8.582000000000001</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +4313,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46213.23958333334</v>
+        <v>46214.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="C121">
-        <v>9.140000000000001</v>
+        <v>0.782</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +4336,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46213.25</v>
+        <v>46214.25</v>
       </c>
       <c r="B122">
-        <v>0.151</v>
+        <v>8.416</v>
       </c>
       <c r="C122">
-        <v>0.6929999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +4359,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46213.26041666666</v>
+        <v>46214.26041666666</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>22.688</v>
       </c>
       <c r="C123">
-        <v>18.275</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +4382,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46213.27083333334</v>
+        <v>46214.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>7.521</v>
       </c>
       <c r="C124">
-        <v>14.175</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,16 +4405,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46213.28125</v>
+        <v>46214.28125</v>
       </c>
       <c r="B125">
-        <v>0.053</v>
+        <v>0.317</v>
       </c>
       <c r="C125">
-        <v>2.012</v>
+        <v>1.851</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +4428,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46213.29166666666</v>
+        <v>46214.29166666666</v>
       </c>
       <c r="B126">
-        <v>0.478</v>
+        <v>14.218</v>
       </c>
       <c r="C126">
-        <v>0.573</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +4451,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46213.30208333334</v>
+        <v>46214.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.061</v>
+        <v>8.731999999999999</v>
       </c>
       <c r="C127">
-        <v>2.338</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +4474,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46213.3125</v>
+        <v>46214.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="C128">
-        <v>15.802</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,16 +4497,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46213.32291666666</v>
+        <v>46214.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>0.489</v>
       </c>
       <c r="C129">
-        <v>38.989</v>
+        <v>0.039</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3944,16 +4520,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46213.33333333334</v>
+        <v>46214.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>5.909</v>
       </c>
       <c r="C130">
-        <v>26.274</v>
+        <v>0.052</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -3967,16 +4543,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46213.34375</v>
+        <v>46214.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>4.315</v>
       </c>
       <c r="C131">
-        <v>21.358</v>
+        <v>2.702</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -3990,16 +4566,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46213.35416666666</v>
+        <v>46214.35416666666</v>
       </c>
       <c r="B132">
-        <v>0.105</v>
+        <v>0.017</v>
       </c>
       <c r="C132">
-        <v>1.815</v>
+        <v>6.583</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4589,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46213.36458333334</v>
+        <v>46214.36458333334</v>
       </c>
       <c r="B133">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>11.306</v>
+        <v>11.567</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,13 +4612,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46213.375</v>
+        <v>46214.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>27.178</v>
       </c>
       <c r="C134">
-        <v>14.277</v>
+        <v>0.72</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,13 +4635,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46213.38541666666</v>
+        <v>46214.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>18.774</v>
       </c>
       <c r="C135">
-        <v>13.013</v>
+        <v>0.168</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,19 +4658,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46213.39583333334</v>
+        <v>46214.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="C136">
-        <v>20.271</v>
+        <v>7.157</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>39</v>
@@ -4105,19 +4681,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46213.40625</v>
+        <v>46214.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="C137">
-        <v>40.873</v>
+        <v>0.431</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>40</v>
@@ -4128,19 +4704,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46213.41666666666</v>
+        <v>46214.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="C138">
-        <v>57.036</v>
+        <v>1.22</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>41</v>
@@ -4151,19 +4727,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46213.42708333334</v>
+        <v>46214.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>25.216</v>
+        <v>5.892</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>57.5</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>42</v>
@@ -4174,19 +4750,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46213.4375</v>
+        <v>46214.4375</v>
       </c>
       <c r="B140">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>10.113</v>
+        <v>6.354</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>57.5</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>43</v>
@@ -4197,19 +4773,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46213.44791666666</v>
+        <v>46214.44791666666</v>
       </c>
       <c r="B141">
-        <v>0.473</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>1.895</v>
+        <v>17.268</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>44</v>
@@ -4220,19 +4796,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46213.45833333334</v>
+        <v>46214.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>15.423</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>45</v>
@@ -4243,13 +4819,13 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46213.46875</v>
+        <v>46214.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>15.885</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4266,13 +4842,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46213.47916666666</v>
+        <v>46214.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4289,13 +4865,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46213.48958333334</v>
+        <v>46214.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>2.863</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>4.484</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,13 +4888,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46213.5</v>
+        <v>46214.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>4.039</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4335,13 +4911,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46213.51041666666</v>
+        <v>46214.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>0.319</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4358,13 +4934,13 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46213.52083333334</v>
+        <v>46214.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>2.002</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>5.329</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -4381,13 +4957,13 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46213.53125</v>
+        <v>46214.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>3.099</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1.448</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4404,13 +4980,13 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46213.54166666666</v>
+        <v>46214.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4427,13 +5003,13 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46213.55208333334</v>
+        <v>46214.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>9.581</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4450,13 +5026,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46213.5625</v>
+        <v>46214.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>9.994</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4473,13 +5049,13 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46213.57291666666</v>
+        <v>46214.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>11.374</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4496,13 +5072,13 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46213.58333333334</v>
+        <v>46214.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>21.096</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4519,13 +5095,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46213.59375</v>
+        <v>46214.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4542,13 +5118,13 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46213.60416666666</v>
+        <v>46214.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>12.805</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4565,13 +5141,13 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46213.61458333334</v>
+        <v>46214.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>3.899</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -4588,13 +5164,13 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46213.625</v>
+        <v>46214.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>0.792</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -4611,13 +5187,13 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46213.63541666666</v>
+        <v>46214.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -4634,13 +5210,13 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46213.64583333334</v>
+        <v>46214.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -4657,13 +5233,13 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46213.65625</v>
+        <v>46214.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>0.716</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -4680,13 +5256,13 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46213.66666666666</v>
+        <v>46214.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>1.202</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -4703,13 +5279,13 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46213.67708333334</v>
+        <v>46214.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>3.206</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -4726,13 +5302,13 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46213.6875</v>
+        <v>46214.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>2.498</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -4749,13 +5325,13 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46213.69791666666</v>
+        <v>46214.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>5.212</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>2.523</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -4772,13 +5348,13 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46213.70833333334</v>
+        <v>46214.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>10.867</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -4795,13 +5371,13 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46213.71875</v>
+        <v>46214.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -4818,13 +5394,13 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46213.72916666666</v>
+        <v>46214.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>16.714</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -4841,16 +5417,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46213.73958333334</v>
+        <v>46214.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>9.518000000000001</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -4864,16 +5440,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46213.75</v>
+        <v>46214.75</v>
       </c>
       <c r="B170">
         <v>0</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>13.261</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -4887,16 +5463,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46213.76041666666</v>
+        <v>46214.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>10.257</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -4910,16 +5486,16 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46213.77083333334</v>
+        <v>46214.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>4.059</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -4933,16 +5509,16 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46213.78125</v>
+        <v>46214.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>2.454</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -4956,16 +5532,16 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46213.79166666666</v>
+        <v>46214.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>5.184</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -4979,16 +5555,16 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46213.80208333334</v>
+        <v>46214.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5002,13 +5578,13 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46213.8125</v>
+        <v>46214.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1.508</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -5025,13 +5601,13 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46213.82291666666</v>
+        <v>46214.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>9.157</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5048,13 +5624,13 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46213.83333333334</v>
+        <v>46214.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -5071,13 +5647,13 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46213.84375</v>
+        <v>46214.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -5094,13 +5670,13 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46213.85416666666</v>
+        <v>46214.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -5117,13 +5693,13 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46213.86458333334</v>
+        <v>46214.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>1.233</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -5140,13 +5716,13 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46213.875</v>
+        <v>46214.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5163,13 +5739,13 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46213.88541666666</v>
+        <v>46214.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5186,13 +5762,13 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46213.89583333334</v>
+        <v>46214.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>0.399</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5209,13 +5785,13 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46213.90625</v>
+        <v>46214.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -5232,13 +5808,13 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46213.91666666666</v>
+        <v>46214.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -5255,13 +5831,13 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46213.92708333334</v>
+        <v>46214.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>11.576</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -5278,13 +5854,13 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46213.9375</v>
+        <v>46214.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>15.088</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -5301,13 +5877,13 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46213.94791666666</v>
+        <v>46214.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -5324,13 +5900,13 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46213.95833333334</v>
+        <v>46214.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>16.605</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -5347,13 +5923,13 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46213.96875</v>
+        <v>46214.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>14.68</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -5370,19 +5946,19 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46213.97916666666</v>
+        <v>46214.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>13.311</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F192">
         <v>95</v>
@@ -5393,25 +5969,4441 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46213.98958333334</v>
+        <v>46214.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1.672</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F193">
         <v>96</v>
       </c>
       <c r="G193" t="s">
         <v>198</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="2">
+        <v>46215</v>
+      </c>
+      <c r="B194">
+        <v>6.423</v>
+      </c>
+      <c r="C194">
+        <v>0.203</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>18</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="2">
+        <v>46215.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>3.147</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>18</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="2">
+        <v>46215.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>2.298</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>23</v>
+      </c>
+      <c r="F196">
+        <v>3</v>
+      </c>
+      <c r="G196" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="2">
+        <v>46215.03125</v>
+      </c>
+      <c r="B197">
+        <v>2.812</v>
+      </c>
+      <c r="C197">
+        <v>0.053</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>4</v>
+      </c>
+      <c r="G197" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="2">
+        <v>46215.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>1.664</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>5</v>
+      </c>
+      <c r="G198" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="2">
+        <v>46215.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>11.991</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+      <c r="F199">
+        <v>6</v>
+      </c>
+      <c r="G199" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="2">
+        <v>46215.0625</v>
+      </c>
+      <c r="B200">
+        <v>16.246</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>7</v>
+      </c>
+      <c r="G200" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="2">
+        <v>46215.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1.513</v>
+      </c>
+      <c r="C201">
+        <v>0.029</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+      <c r="F201">
+        <v>8</v>
+      </c>
+      <c r="G201" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="2">
+        <v>46215.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0.055</v>
+      </c>
+      <c r="C202">
+        <v>4.913</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>9</v>
+      </c>
+      <c r="G202" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="2">
+        <v>46215.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>13.037</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="F203">
+        <v>10</v>
+      </c>
+      <c r="G203" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="2">
+        <v>46215.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>8.269</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>11</v>
+      </c>
+      <c r="G204" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="2">
+        <v>46215.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>14.571</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>12</v>
+      </c>
+      <c r="G205" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="2">
+        <v>46215.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>20.339</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>13</v>
+      </c>
+      <c r="G206" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="2">
+        <v>46215.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>10.23</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>14</v>
+      </c>
+      <c r="G207" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="2">
+        <v>46215.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0.013</v>
+      </c>
+      <c r="C208">
+        <v>7.014</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>15</v>
+      </c>
+      <c r="G208" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="2">
+        <v>46215.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>18.847</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>16</v>
+      </c>
+      <c r="G209" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="2">
+        <v>46215.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>13.679</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>17</v>
+      </c>
+      <c r="G210" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="2">
+        <v>46215.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>26.33</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>18</v>
+      </c>
+      <c r="G211" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="2">
+        <v>46215.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>33.395</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>18.25</v>
+      </c>
+      <c r="F212">
+        <v>19</v>
+      </c>
+      <c r="G212" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="2">
+        <v>46215.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>8.064</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>36.25</v>
+      </c>
+      <c r="F213">
+        <v>20</v>
+      </c>
+      <c r="G213" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="2">
+        <v>46215.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>2.473</v>
+      </c>
+      <c r="C214">
+        <v>1.26</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>50</v>
+      </c>
+      <c r="F214">
+        <v>21</v>
+      </c>
+      <c r="G214" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="2">
+        <v>46215.21875</v>
+      </c>
+      <c r="B215">
+        <v>1.684</v>
+      </c>
+      <c r="C215">
+        <v>0.005</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>50</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="2">
+        <v>46215.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="C216">
+        <v>2.374</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>50</v>
+      </c>
+      <c r="F216">
+        <v>23</v>
+      </c>
+      <c r="G216" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="2">
+        <v>46215.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>1.876</v>
+      </c>
+      <c r="C217">
+        <v>0.399</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>50</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="2">
+        <v>46215.25</v>
+      </c>
+      <c r="B218">
+        <v>4.155</v>
+      </c>
+      <c r="C218">
+        <v>0.223</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>50</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="2">
+        <v>46215.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0.49</v>
+      </c>
+      <c r="C219">
+        <v>0.025</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>50</v>
+      </c>
+      <c r="F219">
+        <v>26</v>
+      </c>
+      <c r="G219" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="2">
+        <v>46215.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>1.591</v>
+      </c>
+      <c r="C220">
+        <v>0.028</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>50</v>
+      </c>
+      <c r="F220">
+        <v>27</v>
+      </c>
+      <c r="G220" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="2">
+        <v>46215.28125</v>
+      </c>
+      <c r="B221">
+        <v>0.242</v>
+      </c>
+      <c r="C221">
+        <v>0.058</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221">
+        <v>50</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
+        <v>46215.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>7.853</v>
+      </c>
+      <c r="C222">
+        <v>0.082</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>50</v>
+      </c>
+      <c r="F222">
+        <v>29</v>
+      </c>
+      <c r="G222" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
+        <v>46215.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>33.754</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>50</v>
+      </c>
+      <c r="F223">
+        <v>30</v>
+      </c>
+      <c r="G223" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
+        <v>46215.3125</v>
+      </c>
+      <c r="B224">
+        <v>13.037</v>
+      </c>
+      <c r="C224">
+        <v>0.063</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>31</v>
+      </c>
+      <c r="G224" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
+        <v>46215.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0.217</v>
+      </c>
+      <c r="C225">
+        <v>3.57</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>32</v>
+      </c>
+      <c r="G225" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
+        <v>46215.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>16.806</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>33</v>
+      </c>
+      <c r="G226" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
+        <v>46215.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>24.706</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>34</v>
+      </c>
+      <c r="G227" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
+        <v>46215.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>19.101</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>35</v>
+      </c>
+      <c r="G228" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
+        <v>46215.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0.016</v>
+      </c>
+      <c r="C229">
+        <v>6.09</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>36</v>
+      </c>
+      <c r="G229" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
+        <v>46215.375</v>
+      </c>
+      <c r="B230">
+        <v>0.014</v>
+      </c>
+      <c r="C230">
+        <v>5.807</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>37</v>
+      </c>
+      <c r="G230" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
+        <v>46215.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>22.08</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>38</v>
+      </c>
+      <c r="G231" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>46215.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>16.916</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>39</v>
+      </c>
+      <c r="G232" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
+        <v>46215.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>14.882</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>40</v>
+      </c>
+      <c r="G233" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
+        <v>46215.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>19.617</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>41</v>
+      </c>
+      <c r="G234" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
+        <v>46215.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0.004</v>
+      </c>
+      <c r="C235">
+        <v>12.857</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>42</v>
+      </c>
+      <c r="G235" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
+        <v>46215.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>27.019</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236">
+        <v>43</v>
+      </c>
+      <c r="G236" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="2">
+        <v>46215.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>34.948</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237">
+        <v>44</v>
+      </c>
+      <c r="G237" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="2">
+        <v>46215.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>11.075</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238">
+        <v>45</v>
+      </c>
+      <c r="G238" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="2">
+        <v>46215.46875</v>
+      </c>
+      <c r="B239">
+        <v>0.002</v>
+      </c>
+      <c r="C239">
+        <v>3.715</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>46</v>
+      </c>
+      <c r="G239" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="2">
+        <v>46215.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0.037</v>
+      </c>
+      <c r="C240">
+        <v>4.133</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>47</v>
+      </c>
+      <c r="G240" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="2">
+        <v>46215.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>6.443</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>48</v>
+      </c>
+      <c r="G241" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="2">
+        <v>46215.5</v>
+      </c>
+      <c r="B242">
+        <v>0.014</v>
+      </c>
+      <c r="C242">
+        <v>4.068</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+      <c r="F242">
+        <v>49</v>
+      </c>
+      <c r="G242" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="2">
+        <v>46215.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1.432</v>
+      </c>
+      <c r="C243">
+        <v>0.16</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>50</v>
+      </c>
+      <c r="G243" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="2">
+        <v>46215.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1.398</v>
+      </c>
+      <c r="C244">
+        <v>0.02</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>51</v>
+      </c>
+      <c r="G244" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="2">
+        <v>46215.53125</v>
+      </c>
+      <c r="B245">
+        <v>0.01</v>
+      </c>
+      <c r="C245">
+        <v>12.685</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245">
+        <v>52</v>
+      </c>
+      <c r="G245" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="2">
+        <v>46215.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0.003</v>
+      </c>
+      <c r="C246">
+        <v>6.509</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
+      <c r="F246">
+        <v>53</v>
+      </c>
+      <c r="G246" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="2">
+        <v>46215.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>2.957</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>54</v>
+      </c>
+      <c r="G247" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="2">
+        <v>46215.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>3.18</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+      <c r="F248">
+        <v>55</v>
+      </c>
+      <c r="G248" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="2">
+        <v>46215.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>10.204</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>56</v>
+      </c>
+      <c r="G249" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="2">
+        <v>46215.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>5.775</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>57</v>
+      </c>
+      <c r="G250" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="2">
+        <v>46215.59375</v>
+      </c>
+      <c r="B251">
+        <v>2.748</v>
+      </c>
+      <c r="C251">
+        <v>0.358</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>58</v>
+      </c>
+      <c r="G251" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="2">
+        <v>46215.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0.1</v>
+      </c>
+      <c r="C252">
+        <v>4.788</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>59</v>
+      </c>
+      <c r="G252" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="2">
+        <v>46215.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>0.242</v>
+      </c>
+      <c r="C253">
+        <v>3.876</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>60</v>
+      </c>
+      <c r="G253" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="2">
+        <v>46215.625</v>
+      </c>
+      <c r="B254">
+        <v>0.357</v>
+      </c>
+      <c r="C254">
+        <v>0.329</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>61</v>
+      </c>
+      <c r="G254" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="2">
+        <v>46215.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0.866</v>
+      </c>
+      <c r="C255">
+        <v>0.11</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>62</v>
+      </c>
+      <c r="G255" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="2">
+        <v>46215.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1.716</v>
+      </c>
+      <c r="C256">
+        <v>0.012</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>63</v>
+      </c>
+      <c r="G256" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="2">
+        <v>46215.65625</v>
+      </c>
+      <c r="B257">
+        <v>0.348</v>
+      </c>
+      <c r="C257">
+        <v>0.077</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>64</v>
+      </c>
+      <c r="G257" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="2">
+        <v>46215.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>0.371</v>
+      </c>
+      <c r="C258">
+        <v>0.139</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>65</v>
+      </c>
+      <c r="G258" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="2">
+        <v>46215.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0.211</v>
+      </c>
+      <c r="C259">
+        <v>0.414</v>
+      </c>
+      <c r="D259">
+        <v>25</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>66</v>
+      </c>
+      <c r="G259" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="2">
+        <v>46215.6875</v>
+      </c>
+      <c r="B260">
+        <v>19.98</v>
+      </c>
+      <c r="C260">
+        <v>0.043</v>
+      </c>
+      <c r="D260">
+        <v>50</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>67</v>
+      </c>
+      <c r="G260" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="2">
+        <v>46215.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>16.833</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>53.5</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>68</v>
+      </c>
+      <c r="G261" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="2">
+        <v>46215.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>9.063000000000001</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>73</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>69</v>
+      </c>
+      <c r="G262" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="2">
+        <v>46215.71875</v>
+      </c>
+      <c r="B263">
+        <v>0.771</v>
+      </c>
+      <c r="C263">
+        <v>0.008</v>
+      </c>
+      <c r="D263">
+        <v>73</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>70</v>
+      </c>
+      <c r="G263" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="2">
+        <v>46215.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>11.804</v>
+      </c>
+      <c r="D264">
+        <v>73</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>71</v>
+      </c>
+      <c r="G264" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="2">
+        <v>46215.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>7.35</v>
+      </c>
+      <c r="D265">
+        <v>50</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>72</v>
+      </c>
+      <c r="G265" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="2">
+        <v>46215.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>54.177</v>
+      </c>
+      <c r="D266">
+        <v>22.75</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>73</v>
+      </c>
+      <c r="G266" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="2">
+        <v>46215.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>33.283</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>74</v>
+      </c>
+      <c r="G267" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="2">
+        <v>46215.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>34.125</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>75</v>
+      </c>
+      <c r="G268" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="2">
+        <v>46215.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>8.956</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>76</v>
+      </c>
+      <c r="G269" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="2">
+        <v>46215.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>0.026</v>
+      </c>
+      <c r="C270">
+        <v>33.067</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>77</v>
+      </c>
+      <c r="G270" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="2">
+        <v>46215.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0.029</v>
+      </c>
+      <c r="C271">
+        <v>5.983</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>78</v>
+      </c>
+      <c r="G271" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="2">
+        <v>46215.8125</v>
+      </c>
+      <c r="B272">
+        <v>0.216</v>
+      </c>
+      <c r="C272">
+        <v>0.59</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>79</v>
+      </c>
+      <c r="G272" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="2">
+        <v>46215.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>2.085</v>
+      </c>
+      <c r="C273">
+        <v>0.012</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>80</v>
+      </c>
+      <c r="G273" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="2">
+        <v>46215.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0.64</v>
+      </c>
+      <c r="C274">
+        <v>5.655</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>81</v>
+      </c>
+      <c r="G274" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="2">
+        <v>46215.84375</v>
+      </c>
+      <c r="B275">
+        <v>8.345000000000001</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>82</v>
+      </c>
+      <c r="G275" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="2">
+        <v>46215.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>7.853</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>83</v>
+      </c>
+      <c r="G276" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="2">
+        <v>46215.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0.18</v>
+      </c>
+      <c r="C277">
+        <v>1.845</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>84</v>
+      </c>
+      <c r="G277" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="2">
+        <v>46215.875</v>
+      </c>
+      <c r="B278">
+        <v>0.094</v>
+      </c>
+      <c r="C278">
+        <v>0.59</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>85</v>
+      </c>
+      <c r="G278" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="2">
+        <v>46215.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0.004</v>
+      </c>
+      <c r="C279">
+        <v>2.655</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>86</v>
+      </c>
+      <c r="G279" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="2">
+        <v>46215.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>4.545</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>87</v>
+      </c>
+      <c r="G280" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="2">
+        <v>46215.90625</v>
+      </c>
+      <c r="B281">
+        <v>8.773999999999999</v>
+      </c>
+      <c r="C281">
+        <v>0.002</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>88</v>
+      </c>
+      <c r="G281" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="2">
+        <v>46215.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>1.763</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>89</v>
+      </c>
+      <c r="G282" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="2">
+        <v>46215.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0.946</v>
+      </c>
+      <c r="C283">
+        <v>0.48</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>90</v>
+      </c>
+      <c r="G283" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="2">
+        <v>46215.9375</v>
+      </c>
+      <c r="B284">
+        <v>5.539</v>
+      </c>
+      <c r="C284">
+        <v>0.118</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>91</v>
+      </c>
+      <c r="G284" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="2">
+        <v>46215.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>8.433</v>
+      </c>
+      <c r="C285">
+        <v>0.433</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>92</v>
+      </c>
+      <c r="G285" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="2">
+        <v>46215.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>3.373</v>
+      </c>
+      <c r="C286">
+        <v>0.77</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>93</v>
+      </c>
+      <c r="G286" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="2">
+        <v>46215.96875</v>
+      </c>
+      <c r="B287">
+        <v>2.303</v>
+      </c>
+      <c r="C287">
+        <v>2.301</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>94</v>
+      </c>
+      <c r="G287" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="2">
+        <v>46215.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0.786</v>
+      </c>
+      <c r="C288">
+        <v>0.007</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>95</v>
+      </c>
+      <c r="G288" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="2">
+        <v>46215.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0.111</v>
+      </c>
+      <c r="C289">
+        <v>1.3</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>96</v>
+      </c>
+      <c r="G289" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B290">
+        <v>0.033</v>
+      </c>
+      <c r="C290">
+        <v>5.36</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="2">
+        <v>46216.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>16.754</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>2</v>
+      </c>
+      <c r="G291" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="2">
+        <v>46216.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0.055</v>
+      </c>
+      <c r="C292">
+        <v>7.148</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>3</v>
+      </c>
+      <c r="G292" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="2">
+        <v>46216.03125</v>
+      </c>
+      <c r="B293">
+        <v>0.006</v>
+      </c>
+      <c r="C293">
+        <v>4.618</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>4</v>
+      </c>
+      <c r="G293" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="2">
+        <v>46216.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>40.203</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>5</v>
+      </c>
+      <c r="G294" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="2">
+        <v>46216.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>28.821</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>6</v>
+      </c>
+      <c r="G295" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="2">
+        <v>46216.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>11.155</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>7</v>
+      </c>
+      <c r="G296" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="2">
+        <v>46216.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>48.678</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>8</v>
+      </c>
+      <c r="G297" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="2">
+        <v>46216.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>26.117</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>9</v>
+      </c>
+      <c r="G298" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="2">
+        <v>46216.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>23.243</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>10</v>
+      </c>
+      <c r="G299" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="2">
+        <v>46216.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0.002</v>
+      </c>
+      <c r="C300">
+        <v>3.077</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>11</v>
+      </c>
+      <c r="G300" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="2">
+        <v>46216.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0.12</v>
+      </c>
+      <c r="C301">
+        <v>0.176</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>12</v>
+      </c>
+      <c r="G301" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="2">
+        <v>46216.125</v>
+      </c>
+      <c r="B302">
+        <v>5.823</v>
+      </c>
+      <c r="C302">
+        <v>0.076</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>13</v>
+      </c>
+      <c r="G302" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="2">
+        <v>46216.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>20.559</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>14</v>
+      </c>
+      <c r="G303" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="2">
+        <v>46216.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>2.607</v>
+      </c>
+      <c r="C304">
+        <v>0.048</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>15</v>
+      </c>
+      <c r="G304" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="2">
+        <v>46216.15625</v>
+      </c>
+      <c r="B305">
+        <v>4.989</v>
+      </c>
+      <c r="C305">
+        <v>0.003</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>16</v>
+      </c>
+      <c r="G305" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="2">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>2.398</v>
+      </c>
+      <c r="C306">
+        <v>0.002</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
+      <c r="F306">
+        <v>17</v>
+      </c>
+      <c r="G306" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="2">
+        <v>46216.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>2.536</v>
+      </c>
+      <c r="C307">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>18</v>
+      </c>
+      <c r="G307" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="2">
+        <v>46216.1875</v>
+      </c>
+      <c r="B308">
+        <v>1.729</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+      <c r="F308">
+        <v>19</v>
+      </c>
+      <c r="G308" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="2">
+        <v>46216.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0.603</v>
+      </c>
+      <c r="C309">
+        <v>0.11</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>20</v>
+      </c>
+      <c r="G309" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="2">
+        <v>46216.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>10.142</v>
+      </c>
+      <c r="C310">
+        <v>0.043</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+      <c r="F310">
+        <v>21</v>
+      </c>
+      <c r="G310" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="2">
+        <v>46216.21875</v>
+      </c>
+      <c r="B311">
+        <v>6.675</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>22</v>
+      </c>
+      <c r="G311" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="2">
+        <v>46216.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>0.386</v>
+      </c>
+      <c r="C312">
+        <v>1.817</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>23</v>
+      </c>
+      <c r="G312" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="2">
+        <v>46216.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0.178</v>
+      </c>
+      <c r="C313">
+        <v>7.733</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>24</v>
+      </c>
+      <c r="G313" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="2">
+        <v>46216.25</v>
+      </c>
+      <c r="B314">
+        <v>0.028</v>
+      </c>
+      <c r="C314">
+        <v>5.252</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>25</v>
+      </c>
+      <c r="G314" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="2">
+        <v>46216.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>13.768</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
+      <c r="F315">
+        <v>26</v>
+      </c>
+      <c r="G315" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="2">
+        <v>46216.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>3.554</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>27</v>
+      </c>
+      <c r="G316" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="2">
+        <v>46216.28125</v>
+      </c>
+      <c r="B317">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="C317">
+        <v>0.142</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>28</v>
+      </c>
+      <c r="G317" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="2">
+        <v>46216.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>0.041</v>
+      </c>
+      <c r="C318">
+        <v>6.111</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>29</v>
+      </c>
+      <c r="G318" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="2">
+        <v>46216.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C319">
+        <v>5.845</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>30</v>
+      </c>
+      <c r="G319" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="2">
+        <v>46216.3125</v>
+      </c>
+      <c r="B320">
+        <v>1.497</v>
+      </c>
+      <c r="C320">
+        <v>0.945</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>31</v>
+      </c>
+      <c r="G320" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="2">
+        <v>46216.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0.02</v>
+      </c>
+      <c r="C321">
+        <v>2.263</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>32</v>
+      </c>
+      <c r="G321" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="2">
+        <v>46216.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0.21</v>
+      </c>
+      <c r="C322">
+        <v>5.689</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>33</v>
+      </c>
+      <c r="G322" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="2">
+        <v>46216.34375</v>
+      </c>
+      <c r="B323">
+        <v>0.462</v>
+      </c>
+      <c r="C323">
+        <v>0.431</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>34</v>
+      </c>
+      <c r="G323" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="2">
+        <v>46216.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1.59</v>
+      </c>
+      <c r="C324">
+        <v>0.236</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>35</v>
+      </c>
+      <c r="G324" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" s="2">
+        <v>46216.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>9.571999999999999</v>
+      </c>
+      <c r="C325">
+        <v>5.256</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>36</v>
+      </c>
+      <c r="G325" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" s="2">
+        <v>46216.375</v>
+      </c>
+      <c r="B326">
+        <v>9.423999999999999</v>
+      </c>
+      <c r="C326">
+        <v>3.352</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>37</v>
+      </c>
+      <c r="G326" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" s="2">
+        <v>46216.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>12.11</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>38</v>
+      </c>
+      <c r="G327" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" s="2">
+        <v>46216.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>14.482</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>39</v>
+      </c>
+      <c r="G328" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" s="2">
+        <v>46216.40625</v>
+      </c>
+      <c r="B329">
+        <v>1.865</v>
+      </c>
+      <c r="C329">
+        <v>11.573</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>40</v>
+      </c>
+      <c r="G329" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" s="2">
+        <v>46216.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>29.058</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>41</v>
+      </c>
+      <c r="G330" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" s="2">
+        <v>46216.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>12.733</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>42</v>
+      </c>
+      <c r="G331" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="2">
+        <v>46216.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>4.679</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>43</v>
+      </c>
+      <c r="G332" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" s="2">
+        <v>46216.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0.244</v>
+      </c>
+      <c r="C333">
+        <v>5.139</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>44</v>
+      </c>
+      <c r="G333" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" s="2">
+        <v>46216.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>20.256</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>45</v>
+      </c>
+      <c r="G334" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" s="2">
+        <v>46216.46875</v>
+      </c>
+      <c r="B335">
+        <v>0.386</v>
+      </c>
+      <c r="C335">
+        <v>0.554</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>46</v>
+      </c>
+      <c r="G335" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="2">
+        <v>46216.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>2.999</v>
+      </c>
+      <c r="C336">
+        <v>0.109</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>47</v>
+      </c>
+      <c r="G336" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="2">
+        <v>46216.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>27.183</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>48</v>
+      </c>
+      <c r="G337" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" s="2">
+        <v>46216.5</v>
+      </c>
+      <c r="B338">
+        <v>3.864</v>
+      </c>
+      <c r="C338">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>49</v>
+      </c>
+      <c r="G338" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="2">
+        <v>46216.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>2.123</v>
+      </c>
+      <c r="C339">
+        <v>5.424</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>50</v>
+      </c>
+      <c r="G339" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="2">
+        <v>46216.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>10.893</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>51</v>
+      </c>
+      <c r="G340" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="2">
+        <v>46216.53125</v>
+      </c>
+      <c r="B341">
+        <v>0.047</v>
+      </c>
+      <c r="C341">
+        <v>4.933</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>52</v>
+      </c>
+      <c r="G341" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" s="2">
+        <v>46216.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>53</v>
+      </c>
+      <c r="G342" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" s="2">
+        <v>46216.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>0</v>
+      </c>
+      <c r="F343">
+        <v>54</v>
+      </c>
+      <c r="G343" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" s="2">
+        <v>46216.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>0</v>
+      </c>
+      <c r="F344">
+        <v>55</v>
+      </c>
+      <c r="G344" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" s="2">
+        <v>46216.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>0</v>
+      </c>
+      <c r="F345">
+        <v>56</v>
+      </c>
+      <c r="G345" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" s="2">
+        <v>46216.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>0</v>
+      </c>
+      <c r="F346">
+        <v>57</v>
+      </c>
+      <c r="G346" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" s="2">
+        <v>46216.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>0</v>
+      </c>
+      <c r="F347">
+        <v>58</v>
+      </c>
+      <c r="G347" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" s="2">
+        <v>46216.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>0</v>
+      </c>
+      <c r="F348">
+        <v>59</v>
+      </c>
+      <c r="G348" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" s="2">
+        <v>46216.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>0</v>
+      </c>
+      <c r="F349">
+        <v>60</v>
+      </c>
+      <c r="G349" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" s="2">
+        <v>46216.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>0</v>
+      </c>
+      <c r="F350">
+        <v>61</v>
+      </c>
+      <c r="G350" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" s="2">
+        <v>46216.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>0</v>
+      </c>
+      <c r="F351">
+        <v>62</v>
+      </c>
+      <c r="G351" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" s="2">
+        <v>46216.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>0</v>
+      </c>
+      <c r="F352">
+        <v>63</v>
+      </c>
+      <c r="G352" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" s="2">
+        <v>46216.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>0</v>
+      </c>
+      <c r="F353">
+        <v>64</v>
+      </c>
+      <c r="G353" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" s="2">
+        <v>46216.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>0</v>
+      </c>
+      <c r="F354">
+        <v>65</v>
+      </c>
+      <c r="G354" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" s="2">
+        <v>46216.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>0</v>
+      </c>
+      <c r="F355">
+        <v>66</v>
+      </c>
+      <c r="G355" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" s="2">
+        <v>46216.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
+      <c r="F356">
+        <v>67</v>
+      </c>
+      <c r="G356" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" s="2">
+        <v>46216.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>0</v>
+      </c>
+      <c r="F357">
+        <v>68</v>
+      </c>
+      <c r="G357" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" s="2">
+        <v>46216.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>0</v>
+      </c>
+      <c r="F358">
+        <v>69</v>
+      </c>
+      <c r="G358" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" s="2">
+        <v>46216.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>0</v>
+      </c>
+      <c r="F359">
+        <v>70</v>
+      </c>
+      <c r="G359" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" s="2">
+        <v>46216.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
+      <c r="F360">
+        <v>71</v>
+      </c>
+      <c r="G360" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" s="2">
+        <v>46216.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
+      <c r="F361">
+        <v>72</v>
+      </c>
+      <c r="G361" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" s="2">
+        <v>46216.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+      <c r="F362">
+        <v>73</v>
+      </c>
+      <c r="G362" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" s="2">
+        <v>46216.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
+      <c r="F363">
+        <v>74</v>
+      </c>
+      <c r="G363" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" s="2">
+        <v>46216.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+      <c r="F364">
+        <v>75</v>
+      </c>
+      <c r="G364" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" s="2">
+        <v>46216.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+      <c r="F365">
+        <v>76</v>
+      </c>
+      <c r="G365" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" s="2">
+        <v>46216.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+      <c r="F366">
+        <v>77</v>
+      </c>
+      <c r="G366" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="2">
+        <v>46216.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>0</v>
+      </c>
+      <c r="F367">
+        <v>78</v>
+      </c>
+      <c r="G367" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" s="2">
+        <v>46216.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>0</v>
+      </c>
+      <c r="F368">
+        <v>79</v>
+      </c>
+      <c r="G368" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" s="2">
+        <v>46216.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>0</v>
+      </c>
+      <c r="F369">
+        <v>80</v>
+      </c>
+      <c r="G369" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" s="2">
+        <v>46216.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
+      <c r="F370">
+        <v>81</v>
+      </c>
+      <c r="G370" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" s="2">
+        <v>46216.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
+      <c r="F371">
+        <v>82</v>
+      </c>
+      <c r="G371" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" s="2">
+        <v>46216.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
+      <c r="F372">
+        <v>83</v>
+      </c>
+      <c r="G372" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" s="2">
+        <v>46216.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>84</v>
+      </c>
+      <c r="G373" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" s="2">
+        <v>46216.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>85</v>
+      </c>
+      <c r="G374" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" s="2">
+        <v>46216.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>86</v>
+      </c>
+      <c r="G375" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" s="2">
+        <v>46216.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+      <c r="F376">
+        <v>87</v>
+      </c>
+      <c r="G376" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" s="2">
+        <v>46216.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+      <c r="F377">
+        <v>88</v>
+      </c>
+      <c r="G377" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" s="2">
+        <v>46216.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>89</v>
+      </c>
+      <c r="G378" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" s="2">
+        <v>46216.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+      <c r="F379">
+        <v>90</v>
+      </c>
+      <c r="G379" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" s="2">
+        <v>46216.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+      <c r="F380">
+        <v>91</v>
+      </c>
+      <c r="G380" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" s="2">
+        <v>46216.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
+      <c r="F381">
+        <v>92</v>
+      </c>
+      <c r="G381" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" s="2">
+        <v>46216.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>0</v>
+      </c>
+      <c r="F382">
+        <v>93</v>
+      </c>
+      <c r="G382" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" s="2">
+        <v>46216.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
+      <c r="F383">
+        <v>94</v>
+      </c>
+      <c r="G383" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" s="2">
+        <v>46216.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>0</v>
+      </c>
+      <c r="F384">
+        <v>95</v>
+      </c>
+      <c r="G384" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" s="2">
+        <v>46216.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
+      <c r="F385">
+        <v>96</v>
+      </c>
+      <c r="G385" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_23F921ED1FF3086809654078913CB96C4DEA1302" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2437E4F-68FC-4A3C-9927-AD934286B280}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -37,294 +56,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.07.20261</t>
-  </si>
-  <si>
-    <t>14.07.20262</t>
-  </si>
-  <si>
-    <t>14.07.20263</t>
-  </si>
-  <si>
-    <t>14.07.20264</t>
-  </si>
-  <si>
-    <t>14.07.20265</t>
-  </si>
-  <si>
-    <t>14.07.20266</t>
-  </si>
-  <si>
-    <t>14.07.20267</t>
-  </si>
-  <si>
-    <t>14.07.20268</t>
-  </si>
-  <si>
-    <t>14.07.20269</t>
-  </si>
-  <si>
-    <t>14.07.202610</t>
-  </si>
-  <si>
-    <t>14.07.202611</t>
-  </si>
-  <si>
-    <t>14.07.202612</t>
-  </si>
-  <si>
-    <t>14.07.202613</t>
-  </si>
-  <si>
-    <t>14.07.202614</t>
-  </si>
-  <si>
-    <t>14.07.202615</t>
-  </si>
-  <si>
-    <t>14.07.202616</t>
-  </si>
-  <si>
-    <t>14.07.202617</t>
-  </si>
-  <si>
-    <t>14.07.202618</t>
-  </si>
-  <si>
-    <t>14.07.202619</t>
-  </si>
-  <si>
-    <t>14.07.202620</t>
-  </si>
-  <si>
-    <t>14.07.202621</t>
-  </si>
-  <si>
-    <t>14.07.202622</t>
-  </si>
-  <si>
-    <t>14.07.202623</t>
-  </si>
-  <si>
-    <t>14.07.202624</t>
-  </si>
-  <si>
-    <t>14.07.202625</t>
-  </si>
-  <si>
-    <t>14.07.202626</t>
-  </si>
-  <si>
-    <t>14.07.202627</t>
-  </si>
-  <si>
-    <t>14.07.202628</t>
-  </si>
-  <si>
-    <t>14.07.202629</t>
-  </si>
-  <si>
-    <t>14.07.202630</t>
-  </si>
-  <si>
-    <t>14.07.202631</t>
-  </si>
-  <si>
-    <t>14.07.202632</t>
-  </si>
-  <si>
-    <t>14.07.202633</t>
-  </si>
-  <si>
-    <t>14.07.202634</t>
-  </si>
-  <si>
-    <t>14.07.202635</t>
-  </si>
-  <si>
-    <t>14.07.202636</t>
-  </si>
-  <si>
-    <t>14.07.202637</t>
-  </si>
-  <si>
-    <t>14.07.202638</t>
-  </si>
-  <si>
-    <t>14.07.202639</t>
-  </si>
-  <si>
-    <t>14.07.202640</t>
-  </si>
-  <si>
-    <t>14.07.202641</t>
-  </si>
-  <si>
-    <t>14.07.202642</t>
-  </si>
-  <si>
-    <t>14.07.202643</t>
-  </si>
-  <si>
-    <t>14.07.202644</t>
-  </si>
-  <si>
-    <t>14.07.202645</t>
-  </si>
-  <si>
-    <t>14.07.202646</t>
-  </si>
-  <si>
-    <t>14.07.202647</t>
-  </si>
-  <si>
-    <t>14.07.202648</t>
-  </si>
-  <si>
-    <t>14.07.202649</t>
-  </si>
-  <si>
-    <t>14.07.202650</t>
-  </si>
-  <si>
-    <t>14.07.202651</t>
-  </si>
-  <si>
-    <t>14.07.202652</t>
-  </si>
-  <si>
-    <t>14.07.202653</t>
-  </si>
-  <si>
-    <t>14.07.202654</t>
-  </si>
-  <si>
-    <t>14.07.202655</t>
-  </si>
-  <si>
-    <t>14.07.202656</t>
-  </si>
-  <si>
-    <t>14.07.202657</t>
-  </si>
-  <si>
-    <t>14.07.202658</t>
-  </si>
-  <si>
-    <t>14.07.202659</t>
-  </si>
-  <si>
-    <t>14.07.202660</t>
-  </si>
-  <si>
-    <t>14.07.202661</t>
-  </si>
-  <si>
-    <t>14.07.202662</t>
-  </si>
-  <si>
-    <t>14.07.202663</t>
-  </si>
-  <si>
-    <t>14.07.202664</t>
-  </si>
-  <si>
-    <t>14.07.202665</t>
-  </si>
-  <si>
-    <t>14.07.202666</t>
-  </si>
-  <si>
-    <t>14.07.202667</t>
-  </si>
-  <si>
-    <t>14.07.202668</t>
-  </si>
-  <si>
-    <t>14.07.202669</t>
-  </si>
-  <si>
-    <t>14.07.202670</t>
-  </si>
-  <si>
-    <t>14.07.202671</t>
-  </si>
-  <si>
-    <t>14.07.202672</t>
-  </si>
-  <si>
-    <t>14.07.202673</t>
-  </si>
-  <si>
-    <t>14.07.202674</t>
-  </si>
-  <si>
-    <t>14.07.202675</t>
-  </si>
-  <si>
-    <t>14.07.202676</t>
-  </si>
-  <si>
-    <t>14.07.202677</t>
-  </si>
-  <si>
-    <t>14.07.202678</t>
-  </si>
-  <si>
-    <t>14.07.202679</t>
-  </si>
-  <si>
-    <t>14.07.202680</t>
-  </si>
-  <si>
-    <t>14.07.202681</t>
-  </si>
-  <si>
-    <t>14.07.202682</t>
-  </si>
-  <si>
-    <t>14.07.202683</t>
-  </si>
-  <si>
-    <t>14.07.202684</t>
-  </si>
-  <si>
-    <t>14.07.202685</t>
-  </si>
-  <si>
-    <t>14.07.202686</t>
-  </si>
-  <si>
-    <t>14.07.202687</t>
-  </si>
-  <si>
-    <t>14.07.202688</t>
-  </si>
-  <si>
-    <t>14.07.202689</t>
-  </si>
-  <si>
-    <t>14.07.202690</t>
-  </si>
-  <si>
-    <t>14.07.202691</t>
-  </si>
-  <si>
-    <t>14.07.202692</t>
-  </si>
-  <si>
-    <t>14.07.202693</t>
-  </si>
-  <si>
-    <t>14.07.202694</t>
-  </si>
-  <si>
-    <t>14.07.202695</t>
-  </si>
-  <si>
-    <t>14.07.202696</t>
-  </si>
-  <si>
     <t>15.07.20261</t>
   </si>
   <si>
@@ -611,16 +342,304 @@
   </si>
   <si>
     <t>15.07.202696</t>
+  </si>
+  <si>
+    <t>16.07.20261</t>
+  </si>
+  <si>
+    <t>16.07.20262</t>
+  </si>
+  <si>
+    <t>16.07.20263</t>
+  </si>
+  <si>
+    <t>16.07.20264</t>
+  </si>
+  <si>
+    <t>16.07.20265</t>
+  </si>
+  <si>
+    <t>16.07.20266</t>
+  </si>
+  <si>
+    <t>16.07.20267</t>
+  </si>
+  <si>
+    <t>16.07.20268</t>
+  </si>
+  <si>
+    <t>16.07.20269</t>
+  </si>
+  <si>
+    <t>16.07.202610</t>
+  </si>
+  <si>
+    <t>16.07.202611</t>
+  </si>
+  <si>
+    <t>16.07.202612</t>
+  </si>
+  <si>
+    <t>16.07.202613</t>
+  </si>
+  <si>
+    <t>16.07.202614</t>
+  </si>
+  <si>
+    <t>16.07.202615</t>
+  </si>
+  <si>
+    <t>16.07.202616</t>
+  </si>
+  <si>
+    <t>16.07.202617</t>
+  </si>
+  <si>
+    <t>16.07.202618</t>
+  </si>
+  <si>
+    <t>16.07.202619</t>
+  </si>
+  <si>
+    <t>16.07.202620</t>
+  </si>
+  <si>
+    <t>16.07.202621</t>
+  </si>
+  <si>
+    <t>16.07.202622</t>
+  </si>
+  <si>
+    <t>16.07.202623</t>
+  </si>
+  <si>
+    <t>16.07.202624</t>
+  </si>
+  <si>
+    <t>16.07.202625</t>
+  </si>
+  <si>
+    <t>16.07.202626</t>
+  </si>
+  <si>
+    <t>16.07.202627</t>
+  </si>
+  <si>
+    <t>16.07.202628</t>
+  </si>
+  <si>
+    <t>16.07.202629</t>
+  </si>
+  <si>
+    <t>16.07.202630</t>
+  </si>
+  <si>
+    <t>16.07.202631</t>
+  </si>
+  <si>
+    <t>16.07.202632</t>
+  </si>
+  <si>
+    <t>16.07.202633</t>
+  </si>
+  <si>
+    <t>16.07.202634</t>
+  </si>
+  <si>
+    <t>16.07.202635</t>
+  </si>
+  <si>
+    <t>16.07.202636</t>
+  </si>
+  <si>
+    <t>16.07.202637</t>
+  </si>
+  <si>
+    <t>16.07.202638</t>
+  </si>
+  <si>
+    <t>16.07.202639</t>
+  </si>
+  <si>
+    <t>16.07.202640</t>
+  </si>
+  <si>
+    <t>16.07.202641</t>
+  </si>
+  <si>
+    <t>16.07.202642</t>
+  </si>
+  <si>
+    <t>16.07.202643</t>
+  </si>
+  <si>
+    <t>16.07.202644</t>
+  </si>
+  <si>
+    <t>16.07.202645</t>
+  </si>
+  <si>
+    <t>16.07.202646</t>
+  </si>
+  <si>
+    <t>16.07.202647</t>
+  </si>
+  <si>
+    <t>16.07.202648</t>
+  </si>
+  <si>
+    <t>16.07.202649</t>
+  </si>
+  <si>
+    <t>16.07.202650</t>
+  </si>
+  <si>
+    <t>16.07.202651</t>
+  </si>
+  <si>
+    <t>16.07.202652</t>
+  </si>
+  <si>
+    <t>16.07.202653</t>
+  </si>
+  <si>
+    <t>16.07.202654</t>
+  </si>
+  <si>
+    <t>16.07.202655</t>
+  </si>
+  <si>
+    <t>16.07.202656</t>
+  </si>
+  <si>
+    <t>16.07.202657</t>
+  </si>
+  <si>
+    <t>16.07.202658</t>
+  </si>
+  <si>
+    <t>16.07.202659</t>
+  </si>
+  <si>
+    <t>16.07.202660</t>
+  </si>
+  <si>
+    <t>16.07.202661</t>
+  </si>
+  <si>
+    <t>16.07.202662</t>
+  </si>
+  <si>
+    <t>16.07.202663</t>
+  </si>
+  <si>
+    <t>16.07.202664</t>
+  </si>
+  <si>
+    <t>16.07.202665</t>
+  </si>
+  <si>
+    <t>16.07.202666</t>
+  </si>
+  <si>
+    <t>16.07.202667</t>
+  </si>
+  <si>
+    <t>16.07.202668</t>
+  </si>
+  <si>
+    <t>16.07.202669</t>
+  </si>
+  <si>
+    <t>16.07.202670</t>
+  </si>
+  <si>
+    <t>16.07.202671</t>
+  </si>
+  <si>
+    <t>16.07.202672</t>
+  </si>
+  <si>
+    <t>16.07.202673</t>
+  </si>
+  <si>
+    <t>16.07.202674</t>
+  </si>
+  <si>
+    <t>16.07.202675</t>
+  </si>
+  <si>
+    <t>16.07.202676</t>
+  </si>
+  <si>
+    <t>16.07.202677</t>
+  </si>
+  <si>
+    <t>16.07.202678</t>
+  </si>
+  <si>
+    <t>16.07.202679</t>
+  </si>
+  <si>
+    <t>16.07.202680</t>
+  </si>
+  <si>
+    <t>16.07.202681</t>
+  </si>
+  <si>
+    <t>16.07.202682</t>
+  </si>
+  <si>
+    <t>16.07.202683</t>
+  </si>
+  <si>
+    <t>16.07.202684</t>
+  </si>
+  <si>
+    <t>16.07.202685</t>
+  </si>
+  <si>
+    <t>16.07.202686</t>
+  </si>
+  <si>
+    <t>16.07.202687</t>
+  </si>
+  <si>
+    <t>16.07.202688</t>
+  </si>
+  <si>
+    <t>16.07.202689</t>
+  </si>
+  <si>
+    <t>16.07.202690</t>
+  </si>
+  <si>
+    <t>16.07.202691</t>
+  </si>
+  <si>
+    <t>16.07.202692</t>
+  </si>
+  <si>
+    <t>16.07.202693</t>
+  </si>
+  <si>
+    <t>16.07.202694</t>
+  </si>
+  <si>
+    <t>16.07.202695</t>
+  </si>
+  <si>
+    <t>16.07.202696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -684,13 +703,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -728,7 +755,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -762,6 +789,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -796,9 +824,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -971,11 +1000,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G193"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -998,15 +1036,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>5.433</v>
+        <v>15.845000000000001</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1021,15 +1059,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46217.01041666666</v>
+        <v>46218.010416666657</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>3.689</v>
+        <v>12.276999999999999</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1044,15 +1082,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46217.02083333334</v>
+        <v>46218.020833333343</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>6.555</v>
+        <v>13.125999999999999</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1067,15 +1105,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46217.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>23.46</v>
+        <v>8.3710000000000004</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1090,15 +1128,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46217.04166666666</v>
+        <v>46218.041666666657</v>
       </c>
       <c r="B6">
-        <v>0.025</v>
+        <v>3.133</v>
       </c>
       <c r="C6">
-        <v>1.641</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1113,15 +1151,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46217.05208333334</v>
+        <v>46218.052083333343</v>
       </c>
       <c r="B7">
-        <v>0.06900000000000001</v>
+        <v>1.4E-2</v>
       </c>
       <c r="C7">
-        <v>1.092</v>
+        <v>4.327</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1136,15 +1174,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46217.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>6.375</v>
+        <v>8.8390000000000004</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1159,15 +1197,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46217.07291666666</v>
+        <v>46218.072916666657</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>22.15</v>
+        <v>14.608000000000001</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1182,15 +1220,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46217.08333333334</v>
+        <v>46218.083333333343</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>4.837</v>
+        <v>15.577</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1205,15 +1243,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46217.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>15.023</v>
+        <v>2.1280000000000001</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1228,15 +1266,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46217.10416666666</v>
+        <v>46218.104166666657</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1.2569999999999999</v>
       </c>
       <c r="C12">
-        <v>4.398</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1251,15 +1289,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46217.11458333334</v>
+        <v>46218.114583333343</v>
       </c>
       <c r="B13">
-        <v>0.08400000000000001</v>
+        <v>5.665</v>
       </c>
       <c r="C13">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1274,15 +1312,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46217.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>0.012</v>
+        <v>5.1550000000000002</v>
       </c>
       <c r="C14">
-        <v>2.656</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1297,15 +1335,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46217.13541666666</v>
+        <v>46218.135416666657</v>
       </c>
       <c r="B15">
-        <v>0.044</v>
+        <v>2.617</v>
       </c>
       <c r="C15">
-        <v>6.058</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1320,15 +1358,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46217.14583333334</v>
+        <v>46218.145833333343</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2.1749999999999998</v>
       </c>
       <c r="C16">
-        <v>10.7</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1343,15 +1381,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46217.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1.593</v>
       </c>
       <c r="C17">
-        <v>3.264</v>
+        <v>0.182</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1366,15 +1404,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46217.16666666666</v>
+        <v>46218.166666666657</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="C18">
-        <v>6.408</v>
+        <v>5.1669999999999998</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1389,15 +1427,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46217.17708333334</v>
+        <v>46218.177083333343</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>2.33</v>
+        <v>4.3949999999999996</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1412,15 +1450,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46217.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="C20">
-        <v>11.473</v>
+        <v>2.2509999999999999</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1435,15 +1473,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46217.19791666666</v>
+        <v>46218.197916666657</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="C21">
-        <v>14.72</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1458,15 +1496,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46217.20833333334</v>
+        <v>46218.208333333343</v>
       </c>
       <c r="B22">
-        <v>0.406</v>
+        <v>5.0940000000000003</v>
       </c>
       <c r="C22">
-        <v>4.073</v>
+        <v>0.91</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1481,15 +1519,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46217.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>0.082</v>
+        <v>4.2039999999999997</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1504,15 +1542,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46217.22916666666</v>
+        <v>46218.229166666657</v>
       </c>
       <c r="B24">
-        <v>0.039</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="C24">
-        <v>2.16</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1527,15 +1565,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46217.23958333334</v>
+        <v>46218.239583333343</v>
       </c>
       <c r="B25">
-        <v>0.3</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="C25">
-        <v>0.094</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1550,15 +1588,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46217.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>19.012</v>
+        <v>20.597000000000001</v>
       </c>
       <c r="C26">
-        <v>0.247</v>
+        <v>1.589</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1573,12 +1611,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46217.26041666666</v>
+        <v>46218.260416666657</v>
       </c>
       <c r="B27">
-        <v>34.55</v>
+        <v>42.524999999999999</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1596,12 +1634,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46217.27083333334</v>
+        <v>46218.270833333343</v>
       </c>
       <c r="B28">
-        <v>12.222</v>
+        <v>8.7949999999999999</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1619,15 +1657,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46217.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>0.5629999999999999</v>
+        <v>3.3519999999999999</v>
       </c>
       <c r="C29">
-        <v>0.09</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1642,12 +1680,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46217.29166666666</v>
+        <v>46218.291666666657</v>
       </c>
       <c r="B30">
-        <v>37.111</v>
+        <v>8.3859999999999992</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1665,15 +1703,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46217.30208333334</v>
+        <v>46218.302083333343</v>
       </c>
       <c r="B31">
-        <v>13.731</v>
+        <v>9.7189999999999994</v>
       </c>
       <c r="C31">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1688,15 +1726,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46217.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>0.02</v>
+        <v>34.899000000000001</v>
       </c>
       <c r="C32">
-        <v>8.646000000000001</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1711,18 +1749,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46217.32291666666</v>
+        <v>46218.322916666657</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="C33">
-        <v>7.896</v>
+        <v>1.492</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1734,15 +1772,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46217.33333333334</v>
+        <v>46218.333333333343</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>29.35</v>
       </c>
       <c r="C34">
-        <v>37.675</v>
+        <v>0.46</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1757,15 +1795,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46217.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>21.099</v>
       </c>
       <c r="C35">
-        <v>58.852</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1780,21 +1818,21 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46217.35416666666</v>
+        <v>46218.354166666657</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="C36">
-        <v>83.599</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>36.25</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1803,21 +1841,21 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46217.36458333334</v>
+        <v>46218.364583333343</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="C37">
-        <v>88.53100000000001</v>
+        <v>0.61199999999999999</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>49.75</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1826,21 +1864,21 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46217.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>7.0869999999999997</v>
       </c>
       <c r="C38">
-        <v>101.308</v>
+        <v>1.764</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>30.25</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1849,21 +1887,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46217.38541666666</v>
+        <v>46218.385416666657</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="C39">
-        <v>75.45699999999999</v>
+        <v>4.17</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>42.75</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1872,21 +1910,21 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46217.39583333334</v>
+        <v>46218.395833333343</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>12.773</v>
+        <v>15.78</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1895,21 +1933,21 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46217.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>32.447</v>
+        <v>12.377000000000001</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1918,15 +1956,15 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46217.41666666666</v>
+        <v>46218.416666666657</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2.3E-2</v>
       </c>
       <c r="C42">
-        <v>30.942</v>
+        <v>5.5019999999999998</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1941,15 +1979,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46217.42708333334</v>
+        <v>46218.427083333343</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2.4E-2</v>
       </c>
       <c r="C43">
-        <v>51.78</v>
+        <v>6.6539999999999999</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1964,21 +2002,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46217.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>31.926</v>
+        <v>15.755000000000001</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1987,21 +2025,21 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46217.44791666666</v>
+        <v>46218.447916666657</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>26.692</v>
+        <v>8.8580000000000005</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2010,21 +2048,21 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46217.45833333334</v>
+        <v>46218.458333333343</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>49.664</v>
+        <v>13.797000000000001</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2033,21 +2071,21 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46217.46875</v>
+        <v>46218.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>28.575</v>
+        <v>5.4640000000000004</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2056,21 +2094,21 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46217.47916666666</v>
+        <v>46218.479166666657</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>16.211</v>
+        <v>3.855</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2079,21 +2117,21 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46217.48958333334</v>
+        <v>46218.489583333343</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="C49">
-        <v>11.03</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2102,21 +2140,21 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46217.5</v>
+        <v>46218.5</v>
       </c>
       <c r="B50">
-        <v>0.038</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="C50">
-        <v>11.175</v>
+        <v>1.095</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2125,21 +2163,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46217.51041666666</v>
+        <v>46218.510416666657</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2E-3</v>
       </c>
       <c r="C51">
-        <v>8.907999999999999</v>
+        <v>4.1459999999999999</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2148,21 +2186,21 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46217.52083333334</v>
+        <v>46218.520833333343</v>
       </c>
       <c r="B52">
-        <v>0.094</v>
+        <v>1.5820000000000001</v>
       </c>
       <c r="C52">
-        <v>0.697</v>
+        <v>0.112</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2171,21 +2209,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46217.53125</v>
+        <v>46218.53125</v>
       </c>
       <c r="B53">
-        <v>0.436</v>
+        <v>0.113</v>
       </c>
       <c r="C53">
-        <v>1.331</v>
+        <v>1.0589999999999999</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2194,15 +2232,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46217.54166666666</v>
+        <v>46218.541666666657</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="C54">
-        <v>7.777</v>
+        <v>3.5089999999999999</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2217,15 +2255,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46217.55208333334</v>
+        <v>46218.552083333343</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="C55">
-        <v>36.48</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2240,21 +2278,21 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46217.5625</v>
+        <v>46218.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1.724</v>
       </c>
       <c r="C56">
-        <v>33.215</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2263,21 +2301,21 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46217.57291666666</v>
+        <v>46218.572916666657</v>
       </c>
       <c r="B57">
-        <v>0.128</v>
+        <v>8.8019999999999996</v>
       </c>
       <c r="C57">
-        <v>3.079</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2286,21 +2324,21 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46217.58333333334</v>
+        <v>46218.583333333343</v>
       </c>
       <c r="B58">
-        <v>0.057</v>
+        <v>22.064</v>
       </c>
       <c r="C58">
-        <v>4.576</v>
+        <v>2E-3</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2309,21 +2347,21 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46217.59375</v>
+        <v>46218.59375</v>
       </c>
       <c r="B59">
-        <v>0.037</v>
+        <v>76.167000000000002</v>
       </c>
       <c r="C59">
-        <v>0.751</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2332,21 +2370,21 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46217.60416666666</v>
+        <v>46218.604166666657</v>
       </c>
       <c r="B60">
-        <v>2.392</v>
+        <v>66.608999999999995</v>
       </c>
       <c r="C60">
-        <v>0.702</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2355,12 +2393,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46217.61458333334</v>
+        <v>46218.614583333343</v>
       </c>
       <c r="B61">
-        <v>7.617</v>
+        <v>54.143999999999998</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2378,15 +2416,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46217.625</v>
+        <v>46218.625</v>
       </c>
       <c r="B62">
-        <v>2.563</v>
+        <v>4.758</v>
       </c>
       <c r="C62">
-        <v>1.435</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2401,15 +2439,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46217.63541666666</v>
+        <v>46218.635416666657</v>
       </c>
       <c r="B63">
-        <v>1.434</v>
+        <v>35.192</v>
       </c>
       <c r="C63">
-        <v>2.816</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2424,18 +2462,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46217.64583333334</v>
+        <v>46218.645833333343</v>
       </c>
       <c r="B64">
-        <v>8.601000000000001</v>
+        <v>14.443</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2447,18 +2485,18 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46217.65625</v>
+        <v>46218.65625</v>
       </c>
       <c r="B65">
-        <v>1.053</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="C65">
-        <v>4.283</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2470,18 +2508,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46217.66666666666</v>
+        <v>46218.666666666657</v>
       </c>
       <c r="B66">
-        <v>2.517</v>
+        <v>0.68700000000000006</v>
       </c>
       <c r="C66">
-        <v>0.48</v>
+        <v>4.01</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2493,18 +2531,18 @@
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46217.67708333334</v>
+        <v>46218.677083333343</v>
       </c>
       <c r="B67">
-        <v>3.423</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>5.3570000000000002</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2516,18 +2554,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46217.6875</v>
+        <v>46218.6875</v>
       </c>
       <c r="B68">
-        <v>12.541</v>
+        <v>16.768000000000001</v>
       </c>
       <c r="C68">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2539,18 +2577,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46217.69791666666</v>
+        <v>46218.697916666657</v>
       </c>
       <c r="B69">
-        <v>21.783</v>
+        <v>4.8739999999999997</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2562,18 +2600,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46217.70833333334</v>
+        <v>46218.708333333343</v>
       </c>
       <c r="B70">
-        <v>20.49</v>
+        <v>0.307</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2585,18 +2623,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46217.71875</v>
+        <v>46218.71875</v>
       </c>
       <c r="B71">
-        <v>26.069</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2608,12 +2646,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46217.72916666666</v>
+        <v>46218.729166666657</v>
       </c>
       <c r="B72">
-        <v>14.278</v>
+        <v>26.081</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2631,12 +2669,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46217.73958333334</v>
+        <v>46218.739583333343</v>
       </c>
       <c r="B73">
-        <v>22.96</v>
+        <v>37.298999999999999</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2654,15 +2692,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46217.75</v>
+        <v>46218.75</v>
       </c>
       <c r="B74">
-        <v>1.11</v>
+        <v>10.090999999999999</v>
       </c>
       <c r="C74">
-        <v>9.565</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2677,15 +2715,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46217.76041666666</v>
+        <v>46218.760416666657</v>
       </c>
       <c r="B75">
-        <v>0.27</v>
+        <v>25.891999999999999</v>
       </c>
       <c r="C75">
-        <v>1.013</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2700,15 +2738,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46217.77083333334</v>
+        <v>46218.770833333343</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>53.866</v>
       </c>
       <c r="C76">
-        <v>10.836</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2723,15 +2761,15 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46217.78125</v>
+        <v>46218.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>55.61</v>
       </c>
       <c r="C77">
-        <v>11.571</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2746,18 +2784,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46217.79166666666</v>
+        <v>46218.791666666657</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>18.283000000000001</v>
       </c>
       <c r="C78">
-        <v>22.657</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2769,18 +2807,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46217.80208333334</v>
+        <v>46218.802083333343</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>11.007999999999999</v>
       </c>
       <c r="C79">
-        <v>14.174</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2792,21 +2830,21 @@
         <v>84</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46217.8125</v>
+        <v>46218.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>3.601</v>
       </c>
       <c r="C80">
-        <v>15.385</v>
+        <v>0.63500000000000001</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E80">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2815,21 +2853,21 @@
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46217.82291666666</v>
+        <v>46218.822916666657</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="C81">
-        <v>17.423</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E81">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2838,21 +2876,21 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46217.83333333334</v>
+        <v>46218.833333333343</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>1.9419999999999999</v>
       </c>
       <c r="C82">
-        <v>2.608</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="E82">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2861,21 +2899,21 @@
         <v>87</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46217.84375</v>
+        <v>46218.84375</v>
       </c>
       <c r="B83">
-        <v>0.09</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="C83">
-        <v>1.964</v>
+        <v>0.121</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="E83">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -2884,21 +2922,21 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46217.85416666666</v>
+        <v>46218.854166666657</v>
       </c>
       <c r="B84">
-        <v>1.72</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="C84">
-        <v>0.012</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E84">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>83</v>
@@ -2907,21 +2945,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46217.86458333334</v>
+        <v>46218.864583333343</v>
       </c>
       <c r="B85">
-        <v>3.601</v>
+        <v>7.8E-2</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E85">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F85">
         <v>84</v>
@@ -2930,15 +2968,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46217.875</v>
+        <v>46218.875</v>
       </c>
       <c r="B86">
-        <v>1.838</v>
+        <v>7.4729999999999999</v>
       </c>
       <c r="C86">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2953,15 +2991,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46217.88541666666</v>
+        <v>46218.885416666657</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>10.035</v>
       </c>
       <c r="C87">
-        <v>11.57</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2976,15 +3014,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46217.89583333334</v>
+        <v>46218.895833333343</v>
       </c>
       <c r="B88">
-        <v>0.004</v>
+        <v>4.5759999999999996</v>
       </c>
       <c r="C88">
-        <v>4.308</v>
+        <v>1.9E-2</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -2999,15 +3037,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46217.90625</v>
+        <v>46218.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C89">
-        <v>20.787</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3022,15 +3060,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>46217.91666666666</v>
+        <v>46218.916666666657</v>
       </c>
       <c r="B90">
-        <v>0.431</v>
+        <v>1.2E-2</v>
       </c>
       <c r="C90">
-        <v>3.343</v>
+        <v>1.7190000000000001</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3045,15 +3083,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>46217.92708333334</v>
+        <v>46218.927083333343</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C91">
-        <v>1.331</v>
+        <v>2.0750000000000002</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3068,15 +3106,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>46217.9375</v>
+        <v>46218.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>3.914</v>
+        <v>6.7519999999999998</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3091,15 +3129,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>46217.94791666666</v>
+        <v>46218.947916666657</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>19.568</v>
+        <v>18.145</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3114,15 +3152,15 @@
         <v>98</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>46217.95833333334</v>
+        <v>46218.958333333343</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>38.452</v>
+        <v>10.707000000000001</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3137,15 +3175,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>46217.96875</v>
+        <v>46218.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>9.701000000000001</v>
+        <v>9.3979999999999997</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3160,15 +3198,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>46217.97916666666</v>
+        <v>46218.979166666657</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>10.599</v>
+        <v>16.943999999999999</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3183,15 +3221,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>46217.98958333334</v>
+        <v>46218.989583333343</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>20.346</v>
+        <v>28.178999999999998</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3206,15 +3244,15 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>3.9E-2</v>
       </c>
       <c r="C98">
-        <v>15.845</v>
+        <v>6.2850000000000001</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3229,15 +3267,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>46218.01041666666</v>
+        <v>46219.010416666657</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="C99">
-        <v>12.277</v>
+        <v>1.9410000000000001</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3252,15 +3290,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>46218.02083333334</v>
+        <v>46219.020833333343</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>13.126</v>
+        <v>7.4089999999999998</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3275,15 +3313,15 @@
         <v>105</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="C101">
-        <v>8.371</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3298,15 +3336,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>46218.04166666666</v>
+        <v>46219.041666666657</v>
       </c>
       <c r="B102">
-        <v>3.133</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="C102">
-        <v>0.032</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3321,15 +3359,15 @@
         <v>107</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>46218.05208333334</v>
+        <v>46219.052083333343</v>
       </c>
       <c r="B103">
-        <v>0.014</v>
+        <v>2.0139999999999998</v>
       </c>
       <c r="C103">
-        <v>4.327</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3344,15 +3382,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>6.4969999999999999</v>
       </c>
       <c r="C104">
-        <v>8.839</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3367,15 +3405,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>46218.07291666666</v>
+        <v>46219.072916666657</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>10.239000000000001</v>
       </c>
       <c r="C105">
-        <v>14.608</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3390,15 +3428,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>46218.08333333334</v>
+        <v>46219.083333333343</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>19.329999999999998</v>
       </c>
       <c r="C106">
-        <v>15.577</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3413,15 +3451,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>8.9830000000000005</v>
       </c>
       <c r="C107">
-        <v>2.128</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3436,15 +3474,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>46218.10416666666</v>
+        <v>46219.104166666657</v>
       </c>
       <c r="B108">
-        <v>1.257</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="C108">
-        <v>0.596</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3459,15 +3497,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>46218.11458333334</v>
+        <v>46219.114583333343</v>
       </c>
       <c r="B109">
-        <v>5.665</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3482,15 +3520,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B110">
-        <v>5.155</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3505,15 +3543,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>46218.13541666666</v>
+        <v>46219.135416666657</v>
       </c>
       <c r="B111">
-        <v>2.617</v>
+        <v>1.2829999999999999</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3528,15 +3566,15 @@
         <v>116</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>46218.14583333334</v>
+        <v>46219.145833333343</v>
       </c>
       <c r="B112">
-        <v>2.175</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="C112">
-        <v>0.077</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3551,15 +3589,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B113">
-        <v>1.593</v>
+        <v>2.3460000000000001</v>
       </c>
       <c r="C113">
-        <v>0.182</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3574,15 +3612,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>46218.16666666666</v>
+        <v>46219.166666666657</v>
       </c>
       <c r="B114">
-        <v>0.041</v>
+        <v>9.7479999999999993</v>
       </c>
       <c r="C114">
-        <v>5.167</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3597,15 +3635,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>46218.17708333334</v>
+        <v>46219.177083333343</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>22.254000000000001</v>
       </c>
       <c r="C115">
-        <v>4.395</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3620,15 +3658,15 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B116">
-        <v>0.329</v>
+        <v>4.9850000000000003</v>
       </c>
       <c r="C116">
-        <v>2.251</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3643,15 +3681,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>46218.19791666666</v>
+        <v>46219.197916666657</v>
       </c>
       <c r="B117">
-        <v>0.167</v>
+        <v>14.164</v>
       </c>
       <c r="C117">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3666,15 +3704,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>46218.20833333334</v>
+        <v>46219.208333333343</v>
       </c>
       <c r="B118">
-        <v>5.094</v>
+        <v>3.8290000000000002</v>
       </c>
       <c r="C118">
-        <v>0.91</v>
+        <v>0.186</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3689,15 +3727,15 @@
         <v>123</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B119">
-        <v>4.204</v>
+        <v>1.502</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3712,15 +3750,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>46218.22916666666</v>
+        <v>46219.229166666657</v>
       </c>
       <c r="B120">
-        <v>0.845</v>
+        <v>13.106999999999999</v>
       </c>
       <c r="C120">
-        <v>0.543</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3735,15 +3773,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>46218.23958333334</v>
+        <v>46219.239583333343</v>
       </c>
       <c r="B121">
-        <v>0.148</v>
+        <v>29.491</v>
       </c>
       <c r="C121">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3758,15 +3796,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B122">
-        <v>20.597</v>
+        <v>20.815000000000001</v>
       </c>
       <c r="C122">
-        <v>1.589</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3781,12 +3819,12 @@
         <v>127</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>46218.26041666666</v>
+        <v>46219.260416666657</v>
       </c>
       <c r="B123">
-        <v>42.525</v>
+        <v>31.523</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3804,18 +3842,18 @@
         <v>128</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>46218.27083333334</v>
+        <v>46219.270833333343</v>
       </c>
       <c r="B124">
-        <v>8.795</v>
+        <v>16.516999999999999</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3827,18 +3865,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>46218.28125</v>
+        <v>46219.28125</v>
       </c>
       <c r="B125">
-        <v>3.352</v>
+        <v>15.205</v>
       </c>
       <c r="C125">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3850,18 +3888,18 @@
         <v>130</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>46218.29166666666</v>
+        <v>46219.291666666657</v>
       </c>
       <c r="B126">
-        <v>8.385999999999999</v>
+        <v>28.047999999999998</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3873,18 +3911,18 @@
         <v>131</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>46218.30208333334</v>
+        <v>46219.302083333343</v>
       </c>
       <c r="B127">
-        <v>9.718999999999999</v>
+        <v>4.242</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>2.2549999999999999</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3896,18 +3934,18 @@
         <v>132</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>46218.3125</v>
+        <v>46219.3125</v>
       </c>
       <c r="B128">
-        <v>34.899</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="C128">
-        <v>0.381</v>
+        <v>6.2830000000000004</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3919,18 +3957,18 @@
         <v>133</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>46218.32291666666</v>
+        <v>46219.322916666657</v>
       </c>
       <c r="B129">
-        <v>0.142</v>
+        <v>6.5750000000000002</v>
       </c>
       <c r="C129">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3942,18 +3980,18 @@
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>46218.33333333334</v>
+        <v>46219.333333333343</v>
       </c>
       <c r="B130">
-        <v>29.35</v>
+        <v>20.844000000000001</v>
       </c>
       <c r="C130">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -3965,18 +4003,18 @@
         <v>135</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>46218.34375</v>
+        <v>46219.34375</v>
       </c>
       <c r="B131">
-        <v>21.099</v>
+        <v>20.780999999999999</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -3988,18 +4026,18 @@
         <v>136</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>46218.35416666666</v>
+        <v>46219.354166666657</v>
       </c>
       <c r="B132">
-        <v>0.532</v>
+        <v>16.387</v>
       </c>
       <c r="C132">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4011,18 +4049,18 @@
         <v>137</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>46218.36458333334</v>
+        <v>46219.364583333343</v>
       </c>
       <c r="B133">
-        <v>0.111</v>
+        <v>5.92</v>
       </c>
       <c r="C133">
-        <v>0.612</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4034,18 +4072,18 @@
         <v>138</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>46218.375</v>
+        <v>46219.375</v>
       </c>
       <c r="B134">
-        <v>7.087</v>
+        <v>60.412999999999997</v>
       </c>
       <c r="C134">
-        <v>1.764</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4057,18 +4095,18 @@
         <v>139</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
-        <v>46218.38541666666</v>
+        <v>46219.385416666657</v>
       </c>
       <c r="B135">
-        <v>0.036</v>
+        <v>27.184999999999999</v>
       </c>
       <c r="C135">
-        <v>4.17</v>
+        <v>1.6E-2</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4080,18 +4118,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>46218.39583333334</v>
+        <v>46219.395833333343</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>4.4550000000000001</v>
       </c>
       <c r="C136">
-        <v>15.78</v>
+        <v>3.1E-2</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4103,18 +4141,18 @@
         <v>141</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="C137">
-        <v>12.377</v>
+        <v>17.277000000000001</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4126,18 +4164,18 @@
         <v>142</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>46218.41666666666</v>
+        <v>46219.416666666657</v>
       </c>
       <c r="B138">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>5.502</v>
+        <v>15.112</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4149,18 +4187,18 @@
         <v>143</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>46218.42708333334</v>
+        <v>46219.427083333343</v>
       </c>
       <c r="B139">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>6.654</v>
+        <v>7.3419999999999996</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4172,18 +4210,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>46218.4375</v>
+        <v>46219.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>15.755</v>
+        <v>22.486000000000001</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4195,18 +4233,18 @@
         <v>145</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>46218.44791666666</v>
+        <v>46219.447916666657</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>8.858000000000001</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4218,15 +4256,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>46218.45833333334</v>
+        <v>46219.458333333343</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>13.797</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4241,15 +4279,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>46218.46875</v>
+        <v>46219.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>5.464</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4264,9 +4302,9 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
-        <v>46218.47916666666</v>
+        <v>46219.479166666657</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4287,9 +4325,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>46218.48958333334</v>
+        <v>46219.489583333343</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4310,9 +4348,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
-        <v>46218.5</v>
+        <v>46219.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4333,9 +4371,9 @@
         <v>151</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
-        <v>46218.51041666666</v>
+        <v>46219.510416666657</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4356,9 +4394,9 @@
         <v>152</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
-        <v>46218.52083333334</v>
+        <v>46219.520833333343</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4379,9 +4417,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
-        <v>46218.53125</v>
+        <v>46219.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4402,9 +4440,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
-        <v>46218.54166666666</v>
+        <v>46219.541666666657</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4425,9 +4463,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
-        <v>46218.55208333334</v>
+        <v>46219.552083333343</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4448,9 +4486,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
-        <v>46218.5625</v>
+        <v>46219.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4471,9 +4509,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
-        <v>46218.57291666666</v>
+        <v>46219.572916666657</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4494,9 +4532,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
-        <v>46218.58333333334</v>
+        <v>46219.583333333343</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4517,9 +4555,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
-        <v>46218.59375</v>
+        <v>46219.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4540,9 +4578,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
-        <v>46218.60416666666</v>
+        <v>46219.604166666657</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4563,9 +4601,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
-        <v>46218.61458333334</v>
+        <v>46219.614583333343</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4586,9 +4624,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
-        <v>46218.625</v>
+        <v>46219.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4609,9 +4647,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
-        <v>46218.63541666666</v>
+        <v>46219.635416666657</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4632,9 +4670,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
-        <v>46218.64583333334</v>
+        <v>46219.645833333343</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4655,9 +4693,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
-        <v>46218.65625</v>
+        <v>46219.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4678,9 +4716,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
-        <v>46218.66666666666</v>
+        <v>46219.666666666657</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4701,9 +4739,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
-        <v>46218.67708333334</v>
+        <v>46219.677083333343</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4724,9 +4762,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
-        <v>46218.6875</v>
+        <v>46219.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4747,9 +4785,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
-        <v>46218.69791666666</v>
+        <v>46219.697916666657</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4770,9 +4808,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
-        <v>46218.70833333334</v>
+        <v>46219.708333333343</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4793,9 +4831,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
-        <v>46218.71875</v>
+        <v>46219.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4816,9 +4854,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
-        <v>46218.72916666666</v>
+        <v>46219.729166666657</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4839,9 +4877,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
-        <v>46218.73958333334</v>
+        <v>46219.739583333343</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4862,9 +4900,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
-        <v>46218.75</v>
+        <v>46219.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4885,9 +4923,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
-        <v>46218.76041666666</v>
+        <v>46219.760416666657</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4908,9 +4946,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
-        <v>46218.77083333334</v>
+        <v>46219.770833333343</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4931,9 +4969,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
-        <v>46218.78125</v>
+        <v>46219.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4954,9 +4992,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
-        <v>46218.79166666666</v>
+        <v>46219.791666666657</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4977,9 +5015,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
-        <v>46218.80208333334</v>
+        <v>46219.802083333343</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5000,9 +5038,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
-        <v>46218.8125</v>
+        <v>46219.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5023,9 +5061,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
-        <v>46218.82291666666</v>
+        <v>46219.822916666657</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5046,9 +5084,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
-        <v>46218.83333333334</v>
+        <v>46219.833333333343</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5069,9 +5107,9 @@
         <v>183</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
-        <v>46218.84375</v>
+        <v>46219.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5092,9 +5130,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>46218.85416666666</v>
+        <v>46219.854166666657</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5115,9 +5153,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>46218.86458333334</v>
+        <v>46219.864583333343</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5138,9 +5176,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>46218.875</v>
+        <v>46219.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5161,9 +5199,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>46218.88541666666</v>
+        <v>46219.885416666657</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5184,9 +5222,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>46218.89583333334</v>
+        <v>46219.895833333343</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5207,9 +5245,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>46218.90625</v>
+        <v>46219.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5230,9 +5268,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>46218.91666666666</v>
+        <v>46219.916666666657</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5253,9 +5291,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>46218.92708333334</v>
+        <v>46219.927083333343</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5276,9 +5314,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>46218.9375</v>
+        <v>46219.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5299,9 +5337,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>46218.94791666666</v>
+        <v>46219.947916666657</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5322,9 +5360,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>46218.95833333334</v>
+        <v>46219.958333333343</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5345,9 +5383,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>46218.96875</v>
+        <v>46219.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5368,9 +5406,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>46218.97916666666</v>
+        <v>46219.979166666657</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5391,9 +5429,9 @@
         <v>197</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>46218.98958333334</v>
+        <v>46219.989583333343</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>22.07.20261</t>
-  </si>
-  <si>
-    <t>22.07.20262</t>
-  </si>
-  <si>
-    <t>22.07.20263</t>
-  </si>
-  <si>
-    <t>22.07.20264</t>
-  </si>
-  <si>
-    <t>22.07.20265</t>
-  </si>
-  <si>
-    <t>22.07.20266</t>
-  </si>
-  <si>
-    <t>22.07.20267</t>
-  </si>
-  <si>
-    <t>22.07.20268</t>
-  </si>
-  <si>
-    <t>22.07.20269</t>
-  </si>
-  <si>
-    <t>22.07.202610</t>
-  </si>
-  <si>
-    <t>22.07.202611</t>
-  </si>
-  <si>
-    <t>22.07.202612</t>
-  </si>
-  <si>
-    <t>22.07.202613</t>
-  </si>
-  <si>
-    <t>22.07.202614</t>
-  </si>
-  <si>
-    <t>22.07.202615</t>
-  </si>
-  <si>
-    <t>22.07.202616</t>
-  </si>
-  <si>
-    <t>22.07.202617</t>
-  </si>
-  <si>
-    <t>22.07.202618</t>
-  </si>
-  <si>
-    <t>22.07.202619</t>
-  </si>
-  <si>
-    <t>22.07.202620</t>
-  </si>
-  <si>
-    <t>22.07.202621</t>
-  </si>
-  <si>
-    <t>22.07.202622</t>
-  </si>
-  <si>
-    <t>22.07.202623</t>
-  </si>
-  <si>
-    <t>22.07.202624</t>
-  </si>
-  <si>
-    <t>22.07.202625</t>
-  </si>
-  <si>
-    <t>22.07.202626</t>
-  </si>
-  <si>
-    <t>22.07.202627</t>
-  </si>
-  <si>
-    <t>22.07.202628</t>
-  </si>
-  <si>
-    <t>22.07.202629</t>
-  </si>
-  <si>
-    <t>22.07.202630</t>
-  </si>
-  <si>
-    <t>22.07.202631</t>
-  </si>
-  <si>
-    <t>22.07.202632</t>
-  </si>
-  <si>
-    <t>22.07.202633</t>
-  </si>
-  <si>
-    <t>22.07.202634</t>
-  </si>
-  <si>
-    <t>22.07.202635</t>
-  </si>
-  <si>
-    <t>22.07.202636</t>
-  </si>
-  <si>
-    <t>22.07.202637</t>
-  </si>
-  <si>
-    <t>22.07.202638</t>
-  </si>
-  <si>
-    <t>22.07.202639</t>
-  </si>
-  <si>
-    <t>22.07.202640</t>
-  </si>
-  <si>
-    <t>22.07.202641</t>
-  </si>
-  <si>
-    <t>22.07.202642</t>
-  </si>
-  <si>
-    <t>22.07.202643</t>
-  </si>
-  <si>
-    <t>22.07.202644</t>
-  </si>
-  <si>
-    <t>22.07.202645</t>
-  </si>
-  <si>
-    <t>22.07.202646</t>
-  </si>
-  <si>
-    <t>22.07.202647</t>
-  </si>
-  <si>
-    <t>22.07.202648</t>
-  </si>
-  <si>
-    <t>22.07.202649</t>
-  </si>
-  <si>
-    <t>22.07.202650</t>
-  </si>
-  <si>
-    <t>22.07.202651</t>
-  </si>
-  <si>
-    <t>22.07.202652</t>
-  </si>
-  <si>
-    <t>22.07.202653</t>
-  </si>
-  <si>
-    <t>22.07.202654</t>
-  </si>
-  <si>
-    <t>22.07.202655</t>
-  </si>
-  <si>
-    <t>22.07.202656</t>
-  </si>
-  <si>
-    <t>22.07.202657</t>
-  </si>
-  <si>
-    <t>22.07.202658</t>
-  </si>
-  <si>
-    <t>22.07.202659</t>
-  </si>
-  <si>
-    <t>22.07.202660</t>
-  </si>
-  <si>
-    <t>22.07.202661</t>
-  </si>
-  <si>
-    <t>22.07.202662</t>
-  </si>
-  <si>
-    <t>22.07.202663</t>
-  </si>
-  <si>
-    <t>22.07.202664</t>
-  </si>
-  <si>
-    <t>22.07.202665</t>
-  </si>
-  <si>
-    <t>22.07.202666</t>
-  </si>
-  <si>
-    <t>22.07.202667</t>
-  </si>
-  <si>
-    <t>22.07.202668</t>
-  </si>
-  <si>
-    <t>22.07.202669</t>
-  </si>
-  <si>
-    <t>22.07.202670</t>
-  </si>
-  <si>
-    <t>22.07.202671</t>
-  </si>
-  <si>
-    <t>22.07.202672</t>
-  </si>
-  <si>
-    <t>22.07.202673</t>
-  </si>
-  <si>
-    <t>22.07.202674</t>
-  </si>
-  <si>
-    <t>22.07.202675</t>
-  </si>
-  <si>
-    <t>22.07.202676</t>
-  </si>
-  <si>
-    <t>22.07.202677</t>
-  </si>
-  <si>
-    <t>22.07.202678</t>
-  </si>
-  <si>
-    <t>22.07.202679</t>
-  </si>
-  <si>
-    <t>22.07.202680</t>
-  </si>
-  <si>
-    <t>22.07.202681</t>
-  </si>
-  <si>
-    <t>22.07.202682</t>
-  </si>
-  <si>
-    <t>22.07.202683</t>
-  </si>
-  <si>
-    <t>22.07.202684</t>
-  </si>
-  <si>
-    <t>22.07.202685</t>
-  </si>
-  <si>
-    <t>22.07.202686</t>
-  </si>
-  <si>
-    <t>22.07.202687</t>
-  </si>
-  <si>
-    <t>22.07.202688</t>
-  </si>
-  <si>
-    <t>22.07.202689</t>
-  </si>
-  <si>
-    <t>22.07.202690</t>
-  </si>
-  <si>
-    <t>22.07.202691</t>
-  </si>
-  <si>
-    <t>22.07.202692</t>
-  </si>
-  <si>
-    <t>22.07.202693</t>
-  </si>
-  <si>
-    <t>22.07.202694</t>
-  </si>
-  <si>
-    <t>22.07.202695</t>
-  </si>
-  <si>
-    <t>22.07.202696</t>
-  </si>
-  <si>
     <t>23.07.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>23.07.202696</t>
+  </si>
+  <si>
+    <t>24.07.20261</t>
+  </si>
+  <si>
+    <t>24.07.20262</t>
+  </si>
+  <si>
+    <t>24.07.20263</t>
+  </si>
+  <si>
+    <t>24.07.20264</t>
+  </si>
+  <si>
+    <t>24.07.20265</t>
+  </si>
+  <si>
+    <t>24.07.20266</t>
+  </si>
+  <si>
+    <t>24.07.20267</t>
+  </si>
+  <si>
+    <t>24.07.20268</t>
+  </si>
+  <si>
+    <t>24.07.20269</t>
+  </si>
+  <si>
+    <t>24.07.202610</t>
+  </si>
+  <si>
+    <t>24.07.202611</t>
+  </si>
+  <si>
+    <t>24.07.202612</t>
+  </si>
+  <si>
+    <t>24.07.202613</t>
+  </si>
+  <si>
+    <t>24.07.202614</t>
+  </si>
+  <si>
+    <t>24.07.202615</t>
+  </si>
+  <si>
+    <t>24.07.202616</t>
+  </si>
+  <si>
+    <t>24.07.202617</t>
+  </si>
+  <si>
+    <t>24.07.202618</t>
+  </si>
+  <si>
+    <t>24.07.202619</t>
+  </si>
+  <si>
+    <t>24.07.202620</t>
+  </si>
+  <si>
+    <t>24.07.202621</t>
+  </si>
+  <si>
+    <t>24.07.202622</t>
+  </si>
+  <si>
+    <t>24.07.202623</t>
+  </si>
+  <si>
+    <t>24.07.202624</t>
+  </si>
+  <si>
+    <t>24.07.202625</t>
+  </si>
+  <si>
+    <t>24.07.202626</t>
+  </si>
+  <si>
+    <t>24.07.202627</t>
+  </si>
+  <si>
+    <t>24.07.202628</t>
+  </si>
+  <si>
+    <t>24.07.202629</t>
+  </si>
+  <si>
+    <t>24.07.202630</t>
+  </si>
+  <si>
+    <t>24.07.202631</t>
+  </si>
+  <si>
+    <t>24.07.202632</t>
+  </si>
+  <si>
+    <t>24.07.202633</t>
+  </si>
+  <si>
+    <t>24.07.202634</t>
+  </si>
+  <si>
+    <t>24.07.202635</t>
+  </si>
+  <si>
+    <t>24.07.202636</t>
+  </si>
+  <si>
+    <t>24.07.202637</t>
+  </si>
+  <si>
+    <t>24.07.202638</t>
+  </si>
+  <si>
+    <t>24.07.202639</t>
+  </si>
+  <si>
+    <t>24.07.202640</t>
+  </si>
+  <si>
+    <t>24.07.202641</t>
+  </si>
+  <si>
+    <t>24.07.202642</t>
+  </si>
+  <si>
+    <t>24.07.202643</t>
+  </si>
+  <si>
+    <t>24.07.202644</t>
+  </si>
+  <si>
+    <t>24.07.202645</t>
+  </si>
+  <si>
+    <t>24.07.202646</t>
+  </si>
+  <si>
+    <t>24.07.202647</t>
+  </si>
+  <si>
+    <t>24.07.202648</t>
+  </si>
+  <si>
+    <t>24.07.202649</t>
+  </si>
+  <si>
+    <t>24.07.202650</t>
+  </si>
+  <si>
+    <t>24.07.202651</t>
+  </si>
+  <si>
+    <t>24.07.202652</t>
+  </si>
+  <si>
+    <t>24.07.202653</t>
+  </si>
+  <si>
+    <t>24.07.202654</t>
+  </si>
+  <si>
+    <t>24.07.202655</t>
+  </si>
+  <si>
+    <t>24.07.202656</t>
+  </si>
+  <si>
+    <t>24.07.202657</t>
+  </si>
+  <si>
+    <t>24.07.202658</t>
+  </si>
+  <si>
+    <t>24.07.202659</t>
+  </si>
+  <si>
+    <t>24.07.202660</t>
+  </si>
+  <si>
+    <t>24.07.202661</t>
+  </si>
+  <si>
+    <t>24.07.202662</t>
+  </si>
+  <si>
+    <t>24.07.202663</t>
+  </si>
+  <si>
+    <t>24.07.202664</t>
+  </si>
+  <si>
+    <t>24.07.202665</t>
+  </si>
+  <si>
+    <t>24.07.202666</t>
+  </si>
+  <si>
+    <t>24.07.202667</t>
+  </si>
+  <si>
+    <t>24.07.202668</t>
+  </si>
+  <si>
+    <t>24.07.202669</t>
+  </si>
+  <si>
+    <t>24.07.202670</t>
+  </si>
+  <si>
+    <t>24.07.202671</t>
+  </si>
+  <si>
+    <t>24.07.202672</t>
+  </si>
+  <si>
+    <t>24.07.202673</t>
+  </si>
+  <si>
+    <t>24.07.202674</t>
+  </si>
+  <si>
+    <t>24.07.202675</t>
+  </si>
+  <si>
+    <t>24.07.202676</t>
+  </si>
+  <si>
+    <t>24.07.202677</t>
+  </si>
+  <si>
+    <t>24.07.202678</t>
+  </si>
+  <si>
+    <t>24.07.202679</t>
+  </si>
+  <si>
+    <t>24.07.202680</t>
+  </si>
+  <si>
+    <t>24.07.202681</t>
+  </si>
+  <si>
+    <t>24.07.202682</t>
+  </si>
+  <si>
+    <t>24.07.202683</t>
+  </si>
+  <si>
+    <t>24.07.202684</t>
+  </si>
+  <si>
+    <t>24.07.202685</t>
+  </si>
+  <si>
+    <t>24.07.202686</t>
+  </si>
+  <si>
+    <t>24.07.202687</t>
+  </si>
+  <si>
+    <t>24.07.202688</t>
+  </si>
+  <si>
+    <t>24.07.202689</t>
+  </si>
+  <si>
+    <t>24.07.202690</t>
+  </si>
+  <si>
+    <t>24.07.202691</t>
+  </si>
+  <si>
+    <t>24.07.202692</t>
+  </si>
+  <si>
+    <t>24.07.202693</t>
+  </si>
+  <si>
+    <t>24.07.202694</t>
+  </si>
+  <si>
+    <t>24.07.202695</t>
+  </si>
+  <si>
+    <t>24.07.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,19 +1000,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B2">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>4.689</v>
+        <v>14.748</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1023,19 +1023,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46225.01041666666</v>
+        <v>46226.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.113</v>
+        <v>4.877</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1046,19 +1046,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46225.02083333334</v>
+        <v>46226.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.403</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.021</v>
+        <v>13.081</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1069,19 +1069,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46225.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.122</v>
+        <v>19.554</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1092,19 +1092,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46225.04166666666</v>
+        <v>46226.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.791</v>
+        <v>0.005</v>
       </c>
       <c r="C6">
-        <v>0.027</v>
+        <v>4.126</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46225.05208333334</v>
+        <v>46226.05208333334</v>
       </c>
       <c r="B7">
-        <v>2.768</v>
+        <v>0.09</v>
       </c>
       <c r="C7">
-        <v>0.081</v>
+        <v>0.111</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1138,19 +1138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46225.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
-        <v>7.929</v>
+        <v>0.236</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46225.07291666666</v>
+        <v>46226.07291666666</v>
       </c>
       <c r="B9">
-        <v>13.579</v>
+        <v>31.795</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46225.08333333334</v>
+        <v>46226.08333333334</v>
       </c>
       <c r="B10">
-        <v>23.121</v>
+        <v>35.079</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46225.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
-        <v>6.633</v>
+        <v>30.876</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1230,19 +1230,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46225.10416666666</v>
+        <v>46226.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.262</v>
+        <v>0.417</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46225.11458333334</v>
+        <v>46226.11458333334</v>
       </c>
       <c r="B13">
-        <v>13.736</v>
+        <v>17.42</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46225.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
-        <v>21.705</v>
+        <v>21.134</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46225.13541666666</v>
+        <v>46226.13541666666</v>
       </c>
       <c r="B15">
-        <v>22.973</v>
+        <v>36.564</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,16 +1322,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46225.14583333334</v>
+        <v>46226.14583333334</v>
       </c>
       <c r="B16">
-        <v>22.587</v>
+        <v>18.23</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46225.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
-        <v>26.818</v>
+        <v>1.904</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1368,16 +1368,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46225.16666666666</v>
+        <v>46226.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.954000000000001</v>
+        <v>4.359</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1391,16 +1391,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46225.17708333334</v>
+        <v>46226.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.916</v>
+        <v>2.152</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46225.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
-        <v>3.846</v>
+        <v>2.999</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46225.19791666666</v>
+        <v>46226.19791666666</v>
       </c>
       <c r="B21">
-        <v>3.344</v>
+        <v>10.924</v>
       </c>
       <c r="C21">
-        <v>1.935</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1460,16 +1460,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46225.20833333334</v>
+        <v>46226.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.983</v>
+        <v>0.328</v>
       </c>
       <c r="C22">
-        <v>3.401</v>
+        <v>0.582</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1483,16 +1483,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46225.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>0.58</v>
+        <v>0.031</v>
       </c>
       <c r="C23">
-        <v>0.01</v>
+        <v>0.411</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46225.22916666666</v>
+        <v>46226.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.101</v>
+        <v>10.611</v>
       </c>
       <c r="C24">
-        <v>0.047</v>
+        <v>0.17</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46225.23958333334</v>
+        <v>46226.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.255</v>
+        <v>5.523</v>
       </c>
       <c r="C25">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46225.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>8.166</v>
+        <v>0.309</v>
       </c>
       <c r="C26">
-        <v>0.506</v>
+        <v>3.842</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46225.26041666666</v>
+        <v>46226.26041666666</v>
       </c>
       <c r="B27">
-        <v>15.249</v>
+        <v>1.982</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46225.27083333334</v>
+        <v>46226.27083333334</v>
       </c>
       <c r="B28">
-        <v>8.4</v>
+        <v>0.205</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46225.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>8.978999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>6.278</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46225.29166666666</v>
+        <v>46226.29166666666</v>
       </c>
       <c r="B30">
-        <v>57.236</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>10.96</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,13 +1667,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46225.30208333334</v>
+        <v>46226.30208333334</v>
       </c>
       <c r="B31">
-        <v>90.262</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>14.536</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1690,16 +1690,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46225.3125</v>
+        <v>46226.3125</v>
       </c>
       <c r="B32">
-        <v>30.563</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>12.931</v>
       </c>
       <c r="D32">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46225.32291666666</v>
+        <v>46226.32291666666</v>
       </c>
       <c r="B33">
-        <v>3.429</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.1</v>
+        <v>16.395</v>
       </c>
       <c r="D33">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46225.33333333334</v>
+        <v>46226.33333333334</v>
       </c>
       <c r="B34">
-        <v>9.654</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.309</v>
+        <v>15.747</v>
       </c>
       <c r="D34">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46225.34375</v>
+        <v>46226.34375</v>
       </c>
       <c r="B35">
-        <v>33.111</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>4.186</v>
       </c>
       <c r="D35">
-        <v>102.25</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46225.35416666666</v>
+        <v>46226.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.864</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>6.99</v>
+        <v>25.1</v>
       </c>
       <c r="D36">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +1805,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46225.36458333334</v>
+        <v>46226.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>29.813</v>
+        <v>28.17</v>
       </c>
       <c r="D37">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46225.375</v>
+        <v>46226.375</v>
       </c>
       <c r="B38">
-        <v>20.168</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>1.213</v>
+        <v>35.44</v>
       </c>
       <c r="D38">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46225.38541666666</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="B39">
-        <v>11.148</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>49.972</v>
       </c>
       <c r="D39">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46225.39583333334</v>
+        <v>46226.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.15</v>
+        <v>23.041</v>
       </c>
       <c r="D40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46225.40625</v>
+        <v>46226.40625</v>
       </c>
       <c r="B41">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>2.72</v>
+        <v>46.866</v>
       </c>
       <c r="D41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46225.41666666666</v>
+        <v>46226.41666666666</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>5.493</v>
+        <v>55.958</v>
       </c>
       <c r="D42">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46225.42708333334</v>
+        <v>46226.42708333334</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>19.34</v>
+        <v>28.126</v>
       </c>
       <c r="D43">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46225.4375</v>
+        <v>46226.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="C44">
-        <v>35.239</v>
+        <v>4.952</v>
       </c>
       <c r="D44">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46225.44791666666</v>
+        <v>46226.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>27.136</v>
+        <v>36.328</v>
       </c>
       <c r="D45">
-        <v>41.5</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46225.45833333334</v>
+        <v>46226.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>22.686</v>
+        <v>28.437</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46225.46875</v>
+        <v>46226.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C47">
-        <v>14.251</v>
+        <v>18.476</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46225.47916666666</v>
+        <v>46226.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>2.606</v>
       </c>
       <c r="C48">
-        <v>8.288</v>
+        <v>0.146</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46225.48958333334</v>
+        <v>46226.48958333334</v>
       </c>
       <c r="B49">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>0.489</v>
+        <v>8.587999999999999</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46225.5</v>
+        <v>46226.5</v>
       </c>
       <c r="B50">
-        <v>17.528</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0.585</v>
+        <v>16</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46225.51041666666</v>
+        <v>46226.51041666666</v>
       </c>
       <c r="B51">
-        <v>18.46</v>
+        <v>0.754</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,13 +2150,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46225.52083333334</v>
+        <v>46226.52083333334</v>
       </c>
       <c r="B52">
-        <v>42.109</v>
+        <v>3.604</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46225.53125</v>
+        <v>46226.53125</v>
       </c>
       <c r="B53">
-        <v>52.566</v>
+        <v>0.475</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46225.54166666666</v>
+        <v>46226.54166666666</v>
       </c>
       <c r="B54">
-        <v>78.88200000000001</v>
+        <v>0.021</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>7.484</v>
       </c>
       <c r="D54">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46225.55208333334</v>
+        <v>46226.55208333334</v>
       </c>
       <c r="B55">
-        <v>55.327</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>5.521</v>
       </c>
       <c r="D55">
-        <v>94.25</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2242,16 +2242,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46225.5625</v>
+        <v>46226.5625</v>
       </c>
       <c r="B56">
-        <v>16.871</v>
+        <v>0.011</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="D56">
-        <v>131.75</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2265,16 +2265,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46225.57291666666</v>
+        <v>46226.57291666666</v>
       </c>
       <c r="B57">
-        <v>3.243</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>1.443</v>
+        <v>36.207</v>
       </c>
       <c r="D57">
-        <v>131.75</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46225.58333333334</v>
+        <v>46226.58333333334</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>26.904</v>
+        <v>28.706</v>
       </c>
       <c r="D58">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46225.59375</v>
+        <v>46226.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>10.796</v>
+        <v>20.1</v>
       </c>
       <c r="D59">
-        <v>122.5</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46225.60416666666</v>
+        <v>46226.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>11.183</v>
+        <v>20.209</v>
       </c>
       <c r="D60">
-        <v>49.75</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46225.61458333334</v>
+        <v>46226.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>34.859</v>
+        <v>29.171</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46225.625</v>
+        <v>46226.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>12.838</v>
+        <v>42.225</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46225.63541666666</v>
+        <v>46226.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="C63">
-        <v>14.279</v>
+        <v>24.73</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46225.64583333334</v>
+        <v>46226.64583333334</v>
       </c>
       <c r="B64">
         <v>0.003</v>
       </c>
       <c r="C64">
-        <v>7.45</v>
+        <v>15.269</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46225.65625</v>
+        <v>46226.65625</v>
       </c>
       <c r="B65">
-        <v>0.025</v>
+        <v>0.468</v>
       </c>
       <c r="C65">
-        <v>4.849</v>
+        <v>0.292</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46225.66666666666</v>
+        <v>46226.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>6.946</v>
+        <v>20.441</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,13 +2495,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46225.67708333334</v>
+        <v>46226.67708333334</v>
       </c>
       <c r="B67">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>7.725</v>
+        <v>31.649</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46225.6875</v>
+        <v>46226.6875</v>
       </c>
       <c r="B68">
-        <v>0.572</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0.195</v>
+        <v>23.942</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2541,13 +2541,13 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46225.69791666666</v>
+        <v>46226.69791666666</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>13.301</v>
+        <v>17.117</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2564,13 +2564,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46225.70833333334</v>
+        <v>46226.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>18.946</v>
+        <v>51.541</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46225.71875</v>
+        <v>46226.71875</v>
       </c>
       <c r="B71">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>5.869</v>
+        <v>33.484</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46225.72916666666</v>
+        <v>46226.72916666666</v>
       </c>
       <c r="B72">
-        <v>1.706</v>
+        <v>0.362</v>
       </c>
       <c r="C72">
-        <v>0.022</v>
+        <v>3.348</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46225.73958333334</v>
+        <v>46226.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.154</v>
+        <v>1.384</v>
       </c>
       <c r="C73">
-        <v>0.411</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46225.75</v>
+        <v>46226.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C74">
-        <v>65.331</v>
+        <v>31.376</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46225.76041666666</v>
+        <v>46226.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>87.194</v>
+        <v>29.921</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46225.77083333334</v>
+        <v>46226.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>64.17400000000001</v>
+        <v>17.372</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -2725,19 +2725,19 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46225.78125</v>
+        <v>46226.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>49.486</v>
+        <v>8.18</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46225.79166666666</v>
+        <v>46226.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>53.529</v>
+        <v>20.657</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -2771,19 +2771,19 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46225.80208333334</v>
+        <v>46226.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>24.823</v>
+        <v>21.142</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46225.8125</v>
+        <v>46226.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>16.812</v>
+        <v>3.772</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46225.82291666666</v>
+        <v>46226.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.026</v>
+        <v>0.083</v>
       </c>
       <c r="C81">
-        <v>10.239</v>
+        <v>0.146</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,19 +2840,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46225.83333333334</v>
+        <v>46226.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.448</v>
+        <v>0.118</v>
       </c>
       <c r="C82">
-        <v>6.833</v>
+        <v>0.137</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2863,19 +2863,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46225.84375</v>
+        <v>46226.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="C83">
-        <v>12.645</v>
+        <v>0.038</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>31.75</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -2886,19 +2886,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46225.85416666666</v>
+        <v>46226.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.008999999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="C84">
-        <v>7.357</v>
+        <v>0.257</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>34.25</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>83</v>
@@ -2909,19 +2909,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46225.86458333334</v>
+        <v>46226.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>20.33</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>36.75</v>
+        <v>0</v>
       </c>
       <c r="F85">
         <v>84</v>
@@ -2932,19 +2932,19 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46225.875</v>
+        <v>46226.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>8.31</v>
       </c>
       <c r="C86">
-        <v>1.828</v>
+        <v>0.198</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F86">
         <v>85</v>
@@ -2955,19 +2955,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46225.88541666666</v>
+        <v>46226.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C87">
-        <v>4.119</v>
+        <v>0.674</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46225.89583333334</v>
+        <v>46226.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1.212</v>
       </c>
       <c r="C88">
-        <v>7.403</v>
+        <v>0.031</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46225.90625</v>
+        <v>46226.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="C89">
-        <v>26.48</v>
+        <v>2.69</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3024,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46225.91666666666</v>
+        <v>46226.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>17.758</v>
+        <v>5.042</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,19 +3047,19 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46225.92708333334</v>
+        <v>46226.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>22.271</v>
+        <v>1.94</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>90</v>
@@ -3070,19 +3070,19 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46225.9375</v>
+        <v>46226.9375</v>
       </c>
       <c r="B92">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>7.153</v>
+        <v>3.835</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F92">
         <v>91</v>
@@ -3093,19 +3093,19 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46225.94791666666</v>
+        <v>46226.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>12.522</v>
+        <v>8.444000000000001</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -3116,19 +3116,19 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46225.95833333334</v>
+        <v>46226.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>6.498</v>
+        <v>4.9</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>93</v>
@@ -3139,19 +3139,19 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46225.96875</v>
+        <v>46226.96875</v>
       </c>
       <c r="B95">
-        <v>2.464</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>0.137</v>
+        <v>3.589</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <v>94</v>
@@ -3162,19 +3162,19 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46225.97916666666</v>
+        <v>46226.97916666666</v>
       </c>
       <c r="B96">
-        <v>10.266</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0.035</v>
+        <v>7.324</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -3185,19 +3185,19 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46225.98958333334</v>
+        <v>46226.98958333334</v>
       </c>
       <c r="B97">
-        <v>4.709</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0.083</v>
+        <v>4.893</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -3208,19 +3208,19 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="C98">
-        <v>14.748</v>
+        <v>0.335</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -3231,19 +3231,19 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46226.01041666666</v>
+        <v>46227.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>2.177</v>
       </c>
       <c r="C99">
-        <v>4.877</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -3254,19 +3254,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46226.02083333334</v>
+        <v>46227.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>4.776</v>
       </c>
       <c r="C100">
-        <v>13.081</v>
+        <v>0.003</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -3277,19 +3277,19 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C101">
-        <v>19.554</v>
+        <v>2.427</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>4</v>
@@ -3300,19 +3300,19 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46226.04166666666</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="B102">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="C102">
-        <v>4.126</v>
+        <v>0.973</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -3323,19 +3323,19 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46226.05208333334</v>
+        <v>46227.05208333334</v>
       </c>
       <c r="B103">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0.111</v>
+        <v>8.097</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>6</v>
@@ -3346,19 +3346,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
       <c r="B104">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0.01</v>
+        <v>9.731</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>7</v>
@@ -3369,19 +3369,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46226.07291666666</v>
+        <v>46227.07291666666</v>
       </c>
       <c r="B105">
-        <v>31.795</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>12.799</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>8</v>
@@ -3392,19 +3392,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46226.08333333334</v>
+        <v>46227.08333333334</v>
       </c>
       <c r="B106">
-        <v>35.079</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>10.432</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>9</v>
@@ -3415,19 +3415,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
       <c r="B107">
-        <v>30.876</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>12.831</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>10</v>
@@ -3438,19 +3438,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46226.10416666666</v>
+        <v>46227.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>0.02</v>
+        <v>3.877</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>11</v>
@@ -3461,19 +3461,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46226.11458333334</v>
+        <v>46227.11458333334</v>
       </c>
       <c r="B109">
-        <v>17.42</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>2.064</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>12</v>
@@ -3484,19 +3484,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
       <c r="B110">
-        <v>21.134</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>5.993</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>13</v>
@@ -3507,19 +3507,19 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46226.13541666666</v>
+        <v>46227.13541666666</v>
       </c>
       <c r="B111">
-        <v>36.564</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>5.759</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>14</v>
@@ -3530,16 +3530,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46226.14583333334</v>
+        <v>46227.14583333334</v>
       </c>
       <c r="B112">
-        <v>18.23</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>17.193</v>
       </c>
       <c r="D112">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
       <c r="B113">
-        <v>1.904</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0.025</v>
+        <v>13.402</v>
       </c>
       <c r="D113">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46226.16666666666</v>
+        <v>46227.16666666666</v>
       </c>
       <c r="B114">
-        <v>4.359</v>
+        <v>3.325</v>
       </c>
       <c r="C114">
-        <v>0.034</v>
+        <v>0.598</v>
       </c>
       <c r="D114">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,16 +3599,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46226.17708333334</v>
+        <v>46227.17708333334</v>
       </c>
       <c r="B115">
-        <v>2.152</v>
+        <v>10.11</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
       <c r="B116">
-        <v>2.999</v>
+        <v>16.547</v>
       </c>
       <c r="C116">
         <v>0</v>
       </c>
       <c r="D116">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +3645,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46226.19791666666</v>
+        <v>46227.19791666666</v>
       </c>
       <c r="B117">
-        <v>10.924</v>
+        <v>3.682</v>
       </c>
       <c r="C117">
         <v>0</v>
       </c>
       <c r="D117">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +3668,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46226.20833333334</v>
+        <v>46227.20833333334</v>
       </c>
       <c r="B118">
-        <v>0.328</v>
+        <v>0.193</v>
       </c>
       <c r="C118">
-        <v>0.582</v>
+        <v>0.099</v>
       </c>
       <c r="D118">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +3691,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
       <c r="B119">
-        <v>0.031</v>
+        <v>0.066</v>
       </c>
       <c r="C119">
-        <v>0.411</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D119">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46226.22916666666</v>
+        <v>46227.22916666666</v>
       </c>
       <c r="B120">
-        <v>10.611</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0.17</v>
+        <v>11.205</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46226.23958333334</v>
+        <v>46227.23958333334</v>
       </c>
       <c r="B121">
-        <v>5.523</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>18.732</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
       <c r="B122">
-        <v>0.309</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>3.842</v>
+        <v>23.894</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46226.26041666666</v>
+        <v>46227.26041666666</v>
       </c>
       <c r="B123">
-        <v>1.982</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46226.27083333334</v>
+        <v>46227.27083333334</v>
       </c>
       <c r="B124">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0.183</v>
+        <v>43.955</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
       <c r="B125">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>6.278</v>
+        <v>58.778</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,19 +3852,19 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46226.29166666666</v>
+        <v>46227.29166666666</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="C126">
-        <v>10.96</v>
+        <v>2.627</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="F126">
         <v>29</v>
@@ -3875,19 +3875,19 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46226.30208333334</v>
+        <v>46227.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>14.536</v>
+        <v>20.396</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="F127">
         <v>30</v>
@@ -3898,19 +3898,19 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46226.3125</v>
+        <v>46227.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>22.397</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="F128">
         <v>31</v>
@@ -3921,19 +3921,19 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46226.32291666666</v>
+        <v>46227.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>22.027</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F129">
         <v>32</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46226.33333333334</v>
+        <v>46227.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F130">
         <v>33</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46226.34375</v>
+        <v>46227.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F131">
         <v>34</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46226.35416666666</v>
+        <v>46227.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46226.36458333334</v>
+        <v>46227.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -4036,7 +4036,7 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46226.375</v>
+        <v>46227.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46226.38541666666</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46226.39583333334</v>
+        <v>46227.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46226.40625</v>
+        <v>46227.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46226.41666666666</v>
+        <v>46227.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46226.42708333334</v>
+        <v>46227.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46226.4375</v>
+        <v>46227.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46226.44791666666</v>
+        <v>46227.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46226.45833333334</v>
+        <v>46227.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46226.46875</v>
+        <v>46227.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46226.47916666666</v>
+        <v>46227.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46226.48958333334</v>
+        <v>46227.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46226.5</v>
+        <v>46227.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46226.51041666666</v>
+        <v>46227.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46226.52083333334</v>
+        <v>46227.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46226.53125</v>
+        <v>46227.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46226.54166666666</v>
+        <v>46227.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46226.55208333334</v>
+        <v>46227.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46226.5625</v>
+        <v>46227.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46226.57291666666</v>
+        <v>46227.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46226.58333333334</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46226.59375</v>
+        <v>46227.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46226.60416666666</v>
+        <v>46227.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46226.61458333334</v>
+        <v>46227.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46226.625</v>
+        <v>46227.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46226.63541666666</v>
+        <v>46227.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46226.64583333334</v>
+        <v>46227.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46226.65625</v>
+        <v>46227.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46226.66666666666</v>
+        <v>46227.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46226.67708333334</v>
+        <v>46227.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46226.6875</v>
+        <v>46227.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46226.69791666666</v>
+        <v>46227.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46226.70833333334</v>
+        <v>46227.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46226.71875</v>
+        <v>46227.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46226.72916666666</v>
+        <v>46227.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46226.73958333334</v>
+        <v>46227.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46226.75</v>
+        <v>46227.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46226.76041666666</v>
+        <v>46227.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46226.77083333334</v>
+        <v>46227.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46226.78125</v>
+        <v>46227.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46226.79166666666</v>
+        <v>46227.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46226.80208333334</v>
+        <v>46227.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46226.8125</v>
+        <v>46227.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46226.82291666666</v>
+        <v>46227.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46226.83333333334</v>
+        <v>46227.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46226.84375</v>
+        <v>46227.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46226.85416666666</v>
+        <v>46227.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46226.86458333334</v>
+        <v>46227.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46226.875</v>
+        <v>46227.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46226.88541666666</v>
+        <v>46227.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46226.89583333334</v>
+        <v>46227.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46226.90625</v>
+        <v>46227.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46226.91666666666</v>
+        <v>46227.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46226.92708333334</v>
+        <v>46227.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46226.9375</v>
+        <v>46227.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46226.94791666666</v>
+        <v>46227.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46226.95833333334</v>
+        <v>46227.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46226.96875</v>
+        <v>46227.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46226.97916666666</v>
+        <v>46227.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46226.98958333334</v>
+        <v>46227.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>23.07.20261</t>
-  </si>
-  <si>
-    <t>23.07.20262</t>
-  </si>
-  <si>
-    <t>23.07.20263</t>
-  </si>
-  <si>
-    <t>23.07.20264</t>
-  </si>
-  <si>
-    <t>23.07.20265</t>
-  </si>
-  <si>
-    <t>23.07.20266</t>
-  </si>
-  <si>
-    <t>23.07.20267</t>
-  </si>
-  <si>
-    <t>23.07.20268</t>
-  </si>
-  <si>
-    <t>23.07.20269</t>
-  </si>
-  <si>
-    <t>23.07.202610</t>
-  </si>
-  <si>
-    <t>23.07.202611</t>
-  </si>
-  <si>
-    <t>23.07.202612</t>
-  </si>
-  <si>
-    <t>23.07.202613</t>
-  </si>
-  <si>
-    <t>23.07.202614</t>
-  </si>
-  <si>
-    <t>23.07.202615</t>
-  </si>
-  <si>
-    <t>23.07.202616</t>
-  </si>
-  <si>
-    <t>23.07.202617</t>
-  </si>
-  <si>
-    <t>23.07.202618</t>
-  </si>
-  <si>
-    <t>23.07.202619</t>
-  </si>
-  <si>
-    <t>23.07.202620</t>
-  </si>
-  <si>
-    <t>23.07.202621</t>
-  </si>
-  <si>
-    <t>23.07.202622</t>
-  </si>
-  <si>
-    <t>23.07.202623</t>
-  </si>
-  <si>
-    <t>23.07.202624</t>
-  </si>
-  <si>
-    <t>23.07.202625</t>
-  </si>
-  <si>
-    <t>23.07.202626</t>
-  </si>
-  <si>
-    <t>23.07.202627</t>
-  </si>
-  <si>
-    <t>23.07.202628</t>
-  </si>
-  <si>
-    <t>23.07.202629</t>
-  </si>
-  <si>
-    <t>23.07.202630</t>
-  </si>
-  <si>
-    <t>23.07.202631</t>
-  </si>
-  <si>
-    <t>23.07.202632</t>
-  </si>
-  <si>
-    <t>23.07.202633</t>
-  </si>
-  <si>
-    <t>23.07.202634</t>
-  </si>
-  <si>
-    <t>23.07.202635</t>
-  </si>
-  <si>
-    <t>23.07.202636</t>
-  </si>
-  <si>
-    <t>23.07.202637</t>
-  </si>
-  <si>
-    <t>23.07.202638</t>
-  </si>
-  <si>
-    <t>23.07.202639</t>
-  </si>
-  <si>
-    <t>23.07.202640</t>
-  </si>
-  <si>
-    <t>23.07.202641</t>
-  </si>
-  <si>
-    <t>23.07.202642</t>
-  </si>
-  <si>
-    <t>23.07.202643</t>
-  </si>
-  <si>
-    <t>23.07.202644</t>
-  </si>
-  <si>
-    <t>23.07.202645</t>
-  </si>
-  <si>
-    <t>23.07.202646</t>
-  </si>
-  <si>
-    <t>23.07.202647</t>
-  </si>
-  <si>
-    <t>23.07.202648</t>
-  </si>
-  <si>
-    <t>23.07.202649</t>
-  </si>
-  <si>
-    <t>23.07.202650</t>
-  </si>
-  <si>
-    <t>23.07.202651</t>
-  </si>
-  <si>
-    <t>23.07.202652</t>
-  </si>
-  <si>
-    <t>23.07.202653</t>
-  </si>
-  <si>
-    <t>23.07.202654</t>
-  </si>
-  <si>
-    <t>23.07.202655</t>
-  </si>
-  <si>
-    <t>23.07.202656</t>
-  </si>
-  <si>
-    <t>23.07.202657</t>
-  </si>
-  <si>
-    <t>23.07.202658</t>
-  </si>
-  <si>
-    <t>23.07.202659</t>
-  </si>
-  <si>
-    <t>23.07.202660</t>
-  </si>
-  <si>
-    <t>23.07.202661</t>
-  </si>
-  <si>
-    <t>23.07.202662</t>
-  </si>
-  <si>
-    <t>23.07.202663</t>
-  </si>
-  <si>
-    <t>23.07.202664</t>
-  </si>
-  <si>
-    <t>23.07.202665</t>
-  </si>
-  <si>
-    <t>23.07.202666</t>
-  </si>
-  <si>
-    <t>23.07.202667</t>
-  </si>
-  <si>
-    <t>23.07.202668</t>
-  </si>
-  <si>
-    <t>23.07.202669</t>
-  </si>
-  <si>
-    <t>23.07.202670</t>
-  </si>
-  <si>
-    <t>23.07.202671</t>
-  </si>
-  <si>
-    <t>23.07.202672</t>
-  </si>
-  <si>
-    <t>23.07.202673</t>
-  </si>
-  <si>
-    <t>23.07.202674</t>
-  </si>
-  <si>
-    <t>23.07.202675</t>
-  </si>
-  <si>
-    <t>23.07.202676</t>
-  </si>
-  <si>
-    <t>23.07.202677</t>
-  </si>
-  <si>
-    <t>23.07.202678</t>
-  </si>
-  <si>
-    <t>23.07.202679</t>
-  </si>
-  <si>
-    <t>23.07.202680</t>
-  </si>
-  <si>
-    <t>23.07.202681</t>
-  </si>
-  <si>
-    <t>23.07.202682</t>
-  </si>
-  <si>
-    <t>23.07.202683</t>
-  </si>
-  <si>
-    <t>23.07.202684</t>
-  </si>
-  <si>
-    <t>23.07.202685</t>
-  </si>
-  <si>
-    <t>23.07.202686</t>
-  </si>
-  <si>
-    <t>23.07.202687</t>
-  </si>
-  <si>
-    <t>23.07.202688</t>
-  </si>
-  <si>
-    <t>23.07.202689</t>
-  </si>
-  <si>
-    <t>23.07.202690</t>
-  </si>
-  <si>
-    <t>23.07.202691</t>
-  </si>
-  <si>
-    <t>23.07.202692</t>
-  </si>
-  <si>
-    <t>23.07.202693</t>
-  </si>
-  <si>
-    <t>23.07.202694</t>
-  </si>
-  <si>
-    <t>23.07.202695</t>
-  </si>
-  <si>
-    <t>23.07.202696</t>
-  </si>
-  <si>
-    <t>24.07.20261</t>
-  </si>
-  <si>
-    <t>24.07.20262</t>
-  </si>
-  <si>
-    <t>24.07.20263</t>
-  </si>
-  <si>
-    <t>24.07.20264</t>
-  </si>
-  <si>
-    <t>24.07.20265</t>
-  </si>
-  <si>
-    <t>24.07.20266</t>
-  </si>
-  <si>
-    <t>24.07.20267</t>
-  </si>
-  <si>
-    <t>24.07.20268</t>
-  </si>
-  <si>
-    <t>24.07.20269</t>
-  </si>
-  <si>
-    <t>24.07.202610</t>
-  </si>
-  <si>
-    <t>24.07.202611</t>
-  </si>
-  <si>
-    <t>24.07.202612</t>
-  </si>
-  <si>
-    <t>24.07.202613</t>
-  </si>
-  <si>
-    <t>24.07.202614</t>
-  </si>
-  <si>
-    <t>24.07.202615</t>
-  </si>
-  <si>
-    <t>24.07.202616</t>
-  </si>
-  <si>
-    <t>24.07.202617</t>
-  </si>
-  <si>
-    <t>24.07.202618</t>
-  </si>
-  <si>
-    <t>24.07.202619</t>
-  </si>
-  <si>
-    <t>24.07.202620</t>
-  </si>
-  <si>
-    <t>24.07.202621</t>
-  </si>
-  <si>
-    <t>24.07.202622</t>
-  </si>
-  <si>
-    <t>24.07.202623</t>
-  </si>
-  <si>
-    <t>24.07.202624</t>
-  </si>
-  <si>
-    <t>24.07.202625</t>
-  </si>
-  <si>
-    <t>24.07.202626</t>
-  </si>
-  <si>
-    <t>24.07.202627</t>
-  </si>
-  <si>
-    <t>24.07.202628</t>
-  </si>
-  <si>
-    <t>24.07.202629</t>
-  </si>
-  <si>
-    <t>24.07.202630</t>
-  </si>
-  <si>
-    <t>24.07.202631</t>
-  </si>
-  <si>
-    <t>24.07.202632</t>
-  </si>
-  <si>
-    <t>24.07.202633</t>
-  </si>
-  <si>
-    <t>24.07.202634</t>
-  </si>
-  <si>
-    <t>24.07.202635</t>
-  </si>
-  <si>
-    <t>24.07.202636</t>
-  </si>
-  <si>
-    <t>24.07.202637</t>
-  </si>
-  <si>
-    <t>24.07.202638</t>
-  </si>
-  <si>
-    <t>24.07.202639</t>
-  </si>
-  <si>
-    <t>24.07.202640</t>
-  </si>
-  <si>
-    <t>24.07.202641</t>
-  </si>
-  <si>
-    <t>24.07.202642</t>
-  </si>
-  <si>
-    <t>24.07.202643</t>
-  </si>
-  <si>
-    <t>24.07.202644</t>
-  </si>
-  <si>
-    <t>24.07.202645</t>
-  </si>
-  <si>
-    <t>24.07.202646</t>
-  </si>
-  <si>
-    <t>24.07.202647</t>
-  </si>
-  <si>
-    <t>24.07.202648</t>
-  </si>
-  <si>
-    <t>24.07.202649</t>
-  </si>
-  <si>
-    <t>24.07.202650</t>
-  </si>
-  <si>
-    <t>24.07.202651</t>
-  </si>
-  <si>
-    <t>24.07.202652</t>
-  </si>
-  <si>
-    <t>24.07.202653</t>
-  </si>
-  <si>
-    <t>24.07.202654</t>
-  </si>
-  <si>
-    <t>24.07.202655</t>
-  </si>
-  <si>
-    <t>24.07.202656</t>
-  </si>
-  <si>
-    <t>24.07.202657</t>
-  </si>
-  <si>
-    <t>24.07.202658</t>
-  </si>
-  <si>
-    <t>24.07.202659</t>
-  </si>
-  <si>
-    <t>24.07.202660</t>
-  </si>
-  <si>
-    <t>24.07.202661</t>
-  </si>
-  <si>
-    <t>24.07.202662</t>
-  </si>
-  <si>
-    <t>24.07.202663</t>
-  </si>
-  <si>
-    <t>24.07.202664</t>
-  </si>
-  <si>
-    <t>24.07.202665</t>
-  </si>
-  <si>
-    <t>24.07.202666</t>
-  </si>
-  <si>
-    <t>24.07.202667</t>
-  </si>
-  <si>
-    <t>24.07.202668</t>
-  </si>
-  <si>
-    <t>24.07.202669</t>
-  </si>
-  <si>
-    <t>24.07.202670</t>
-  </si>
-  <si>
-    <t>24.07.202671</t>
-  </si>
-  <si>
-    <t>24.07.202672</t>
-  </si>
-  <si>
-    <t>24.07.202673</t>
-  </si>
-  <si>
-    <t>24.07.202674</t>
-  </si>
-  <si>
-    <t>24.07.202675</t>
-  </si>
-  <si>
-    <t>24.07.202676</t>
-  </si>
-  <si>
-    <t>24.07.202677</t>
-  </si>
-  <si>
-    <t>24.07.202678</t>
-  </si>
-  <si>
-    <t>24.07.202679</t>
-  </si>
-  <si>
-    <t>24.07.202680</t>
-  </si>
-  <si>
-    <t>24.07.202681</t>
-  </si>
-  <si>
-    <t>24.07.202682</t>
-  </si>
-  <si>
-    <t>24.07.202683</t>
-  </si>
-  <si>
-    <t>24.07.202684</t>
-  </si>
-  <si>
-    <t>24.07.202685</t>
-  </si>
-  <si>
-    <t>24.07.202686</t>
-  </si>
-  <si>
-    <t>24.07.202687</t>
-  </si>
-  <si>
-    <t>24.07.202688</t>
-  </si>
-  <si>
-    <t>24.07.202689</t>
-  </si>
-  <si>
-    <t>24.07.202690</t>
-  </si>
-  <si>
-    <t>24.07.202691</t>
-  </si>
-  <si>
-    <t>24.07.202692</t>
-  </si>
-  <si>
-    <t>24.07.202693</t>
-  </si>
-  <si>
-    <t>24.07.202694</t>
-  </si>
-  <si>
-    <t>24.07.202695</t>
-  </si>
-  <si>
-    <t>24.07.202696</t>
+    <t>25.07.20261</t>
+  </si>
+  <si>
+    <t>25.07.20262</t>
+  </si>
+  <si>
+    <t>25.07.20263</t>
+  </si>
+  <si>
+    <t>25.07.20264</t>
+  </si>
+  <si>
+    <t>25.07.20265</t>
+  </si>
+  <si>
+    <t>25.07.20266</t>
+  </si>
+  <si>
+    <t>25.07.20267</t>
+  </si>
+  <si>
+    <t>25.07.20268</t>
+  </si>
+  <si>
+    <t>25.07.20269</t>
+  </si>
+  <si>
+    <t>25.07.202610</t>
+  </si>
+  <si>
+    <t>25.07.202611</t>
+  </si>
+  <si>
+    <t>25.07.202612</t>
+  </si>
+  <si>
+    <t>25.07.202613</t>
+  </si>
+  <si>
+    <t>25.07.202614</t>
+  </si>
+  <si>
+    <t>25.07.202615</t>
+  </si>
+  <si>
+    <t>25.07.202616</t>
+  </si>
+  <si>
+    <t>25.07.202617</t>
+  </si>
+  <si>
+    <t>25.07.202618</t>
+  </si>
+  <si>
+    <t>25.07.202619</t>
+  </si>
+  <si>
+    <t>25.07.202620</t>
+  </si>
+  <si>
+    <t>25.07.202621</t>
+  </si>
+  <si>
+    <t>25.07.202622</t>
+  </si>
+  <si>
+    <t>25.07.202623</t>
+  </si>
+  <si>
+    <t>25.07.202624</t>
+  </si>
+  <si>
+    <t>25.07.202625</t>
+  </si>
+  <si>
+    <t>25.07.202626</t>
+  </si>
+  <si>
+    <t>25.07.202627</t>
+  </si>
+  <si>
+    <t>25.07.202628</t>
+  </si>
+  <si>
+    <t>25.07.202629</t>
+  </si>
+  <si>
+    <t>25.07.202630</t>
+  </si>
+  <si>
+    <t>25.07.202631</t>
+  </si>
+  <si>
+    <t>25.07.202632</t>
+  </si>
+  <si>
+    <t>25.07.202633</t>
+  </si>
+  <si>
+    <t>25.07.202634</t>
+  </si>
+  <si>
+    <t>25.07.202635</t>
+  </si>
+  <si>
+    <t>25.07.202636</t>
+  </si>
+  <si>
+    <t>25.07.202637</t>
+  </si>
+  <si>
+    <t>25.07.202638</t>
+  </si>
+  <si>
+    <t>25.07.202639</t>
+  </si>
+  <si>
+    <t>25.07.202640</t>
+  </si>
+  <si>
+    <t>25.07.202641</t>
+  </si>
+  <si>
+    <t>25.07.202642</t>
+  </si>
+  <si>
+    <t>25.07.202643</t>
+  </si>
+  <si>
+    <t>25.07.202644</t>
+  </si>
+  <si>
+    <t>25.07.202645</t>
+  </si>
+  <si>
+    <t>25.07.202646</t>
+  </si>
+  <si>
+    <t>25.07.202647</t>
+  </si>
+  <si>
+    <t>25.07.202648</t>
+  </si>
+  <si>
+    <t>25.07.202649</t>
+  </si>
+  <si>
+    <t>25.07.202650</t>
+  </si>
+  <si>
+    <t>25.07.202651</t>
+  </si>
+  <si>
+    <t>25.07.202652</t>
+  </si>
+  <si>
+    <t>25.07.202653</t>
+  </si>
+  <si>
+    <t>25.07.202654</t>
+  </si>
+  <si>
+    <t>25.07.202655</t>
+  </si>
+  <si>
+    <t>25.07.202656</t>
+  </si>
+  <si>
+    <t>25.07.202657</t>
+  </si>
+  <si>
+    <t>25.07.202658</t>
+  </si>
+  <si>
+    <t>25.07.202659</t>
+  </si>
+  <si>
+    <t>25.07.202660</t>
+  </si>
+  <si>
+    <t>25.07.202661</t>
+  </si>
+  <si>
+    <t>25.07.202662</t>
+  </si>
+  <si>
+    <t>25.07.202663</t>
+  </si>
+  <si>
+    <t>25.07.202664</t>
+  </si>
+  <si>
+    <t>25.07.202665</t>
+  </si>
+  <si>
+    <t>25.07.202666</t>
+  </si>
+  <si>
+    <t>25.07.202667</t>
+  </si>
+  <si>